--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -453,9 +453,9 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1472.21</v>
+        <v>1472.207675478944</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1467.26</v>
+        <v>1467.259503206748</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1477.16</v>
+        <v>1477.15584775114</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>22689</v>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1468.66</v>
+        <v>1468.658580360648</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1461.7</v>
+        <v>1461.700522789307</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1475.62</v>
+        <v>1475.61663793199</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>9338</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1466.24</v>
+        <v>1466.24229853447</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1461.51</v>
+        <v>1461.514264591496</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1470.97</v>
+        <v>1470.970332477445</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>34468</v>
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1461.37</v>
+        <v>1461.368004535537</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1456.65</v>
+        <v>1456.653506994239</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1466.08</v>
+        <v>1466.082502076835</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>32657</v>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1457.08</v>
+        <v>1457.076266023715</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1452.47</v>
+        <v>1452.474482938546</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1461.68</v>
+        <v>1461.678049108885</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>37116</v>
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1456.98</v>
+        <v>1456.978251729867</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1452.61</v>
+        <v>1452.61003850587</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1461.35</v>
+        <v>1461.346464953865</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>27897</v>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1456.86</v>
+        <v>1456.86314699372</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1452.17</v>
+        <v>1452.173763555522</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1461.55</v>
+        <v>1461.552530431919</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>35108</v>
@@ -1412,13 +1412,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1451.07</v>
+        <v>1451.074153173372</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1443.47</v>
+        <v>1443.474834437071</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1458.67</v>
+        <v>1458.673471909673</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>5898</v>
@@ -1563,13 +1563,13 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1449.7</v>
+        <v>1449.699550404222</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1446.03</v>
+        <v>1446.029408814982</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1453.37</v>
+        <v>1453.369691993463</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>55504</v>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1446.54</v>
+        <v>1446.543676554232</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1440.86</v>
+        <v>1440.861099597588</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1452.23</v>
+        <v>1452.226253510876</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>19761</v>
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1442.97</v>
+        <v>1442.970241764861</v>
       </c>
       <c r="D12" t="n">
-        <v>1439.13</v>
+        <v>1439.129463961606</v>
       </c>
       <c r="E12" t="n">
-        <v>1446.81</v>
+        <v>1446.811019568116</v>
       </c>
       <c r="F12" t="n">
         <v>50832</v>
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1442.38</v>
+        <v>1442.380797048279</v>
       </c>
       <c r="D13" t="n">
-        <v>1436.28</v>
+        <v>1436.282240986469</v>
       </c>
       <c r="E13" t="n">
-        <v>1448.48</v>
+        <v>1448.479353110089</v>
       </c>
       <c r="F13" t="n">
         <v>12105</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1438.24</v>
+        <v>1438.241586502369</v>
       </c>
       <c r="D14" t="n">
-        <v>1430.6</v>
+        <v>1430.604704365156</v>
       </c>
       <c r="E14" t="n">
-        <v>1445.88</v>
+        <v>1445.878468639583</v>
       </c>
       <c r="F14" t="n">
         <v>5812</v>
@@ -2238,13 +2238,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1437.2</v>
+        <v>1437.202172187637</v>
       </c>
       <c r="D15" t="n">
-        <v>1432.58</v>
+        <v>1432.576431060379</v>
       </c>
       <c r="E15" t="n">
-        <v>1441.83</v>
+        <v>1441.827913314894</v>
       </c>
       <c r="F15" t="n">
         <v>36653</v>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1435.74</v>
+        <v>1435.738691173074</v>
       </c>
       <c r="D16" t="n">
-        <v>1431.16</v>
+        <v>1431.161944416463</v>
       </c>
       <c r="E16" t="n">
-        <v>1440.32</v>
+        <v>1440.315437929685</v>
       </c>
       <c r="F16" t="n">
         <v>36817</v>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1433.18</v>
+        <v>1433.180123300331</v>
       </c>
       <c r="D17" t="n">
-        <v>1428.51</v>
+        <v>1428.506660048128</v>
       </c>
       <c r="E17" t="n">
-        <v>1437.85</v>
+        <v>1437.853586552535</v>
       </c>
       <c r="F17" t="n">
         <v>35255</v>
@@ -2531,13 +2531,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1431.63</v>
+        <v>1431.630087294944</v>
       </c>
       <c r="D18" t="n">
-        <v>1425.04</v>
+        <v>1425.043897278806</v>
       </c>
       <c r="E18" t="n">
-        <v>1438.22</v>
+        <v>1438.216277311083</v>
       </c>
       <c r="F18" t="n">
         <v>8185</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1429.9</v>
+        <v>1429.899116212722</v>
       </c>
       <c r="D19" t="n">
-        <v>1426.74</v>
+        <v>1426.73618673235</v>
       </c>
       <c r="E19" t="n">
-        <v>1433.06</v>
+        <v>1433.062045693095</v>
       </c>
       <c r="F19" t="n">
         <v>62069</v>
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1426.58</v>
+        <v>1426.576527773178</v>
       </c>
       <c r="D20" t="n">
-        <v>1419.95</v>
+        <v>1419.953545055774</v>
       </c>
       <c r="E20" t="n">
-        <v>1433.2</v>
+        <v>1433.199510490583</v>
       </c>
       <c r="F20" t="n">
         <v>10782</v>
@@ -2904,13 +2904,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1425.35</v>
+        <v>1425.350944473955</v>
       </c>
       <c r="D21" t="n">
-        <v>1421.43</v>
+        <v>1421.430908835237</v>
       </c>
       <c r="E21" t="n">
-        <v>1429.27</v>
+        <v>1429.270980112672</v>
       </c>
       <c r="F21" t="n">
         <v>35637</v>
@@ -2975,13 +2975,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1425.05</v>
+        <v>1425.047995082568</v>
       </c>
       <c r="D22" t="n">
-        <v>1421.48</v>
+        <v>1421.480068111602</v>
       </c>
       <c r="E22" t="n">
-        <v>1428.62</v>
+        <v>1428.615922053535</v>
       </c>
       <c r="F22" t="n">
         <v>47254</v>
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1424.74</v>
+        <v>1424.741746523867</v>
       </c>
       <c r="D23" t="n">
-        <v>1418.19</v>
+        <v>1418.189143507586</v>
       </c>
       <c r="E23" t="n">
-        <v>1431.29</v>
+        <v>1431.294349540147</v>
       </c>
       <c r="F23" t="n">
         <v>9071</v>
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1423.17</v>
+        <v>1423.170615004773</v>
       </c>
       <c r="D24" t="n">
-        <v>1420.57</v>
+        <v>1420.572516851911</v>
       </c>
       <c r="E24" t="n">
-        <v>1425.77</v>
+        <v>1425.768713157634</v>
       </c>
       <c r="F24" t="n">
         <v>97195</v>
@@ -3268,13 +3268,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1423.14</v>
+        <v>1423.137565951007</v>
       </c>
       <c r="D25" t="n">
-        <v>1419.48</v>
+        <v>1419.480830152515</v>
       </c>
       <c r="E25" t="n">
-        <v>1426.79</v>
+        <v>1426.794301749499</v>
       </c>
       <c r="F25" t="n">
         <v>41062</v>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1422.96</v>
+        <v>1422.959285486476</v>
       </c>
       <c r="D26" t="n">
-        <v>1416.55</v>
+        <v>1416.554014403212</v>
       </c>
       <c r="E26" t="n">
-        <v>1429.36</v>
+        <v>1429.364556569741</v>
       </c>
       <c r="F26" t="n">
         <v>11921</v>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1422.23</v>
+        <v>1422.228142916504</v>
       </c>
       <c r="D27" t="n">
-        <v>1416.57</v>
+        <v>1416.56753178348</v>
       </c>
       <c r="E27" t="n">
-        <v>1427.89</v>
+        <v>1427.888754049527</v>
       </c>
       <c r="F27" t="n">
         <v>18457</v>
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1420.14</v>
+        <v>1420.139317244397</v>
       </c>
       <c r="D28" t="n">
-        <v>1412.92</v>
+        <v>1412.923166755144</v>
       </c>
       <c r="E28" t="n">
-        <v>1427.36</v>
+        <v>1427.35546773365</v>
       </c>
       <c r="F28" t="n">
         <v>8417</v>
@@ -3632,13 +3632,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1418.13</v>
+        <v>1418.131513103546</v>
       </c>
       <c r="D29" t="n">
-        <v>1408.15</v>
+        <v>1408.148778410814</v>
       </c>
       <c r="E29" t="n">
-        <v>1428.11</v>
+        <v>1428.114247796279</v>
       </c>
       <c r="F29" t="n">
         <v>3459</v>
@@ -3703,13 +3703,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1418.05</v>
+        <v>1418.05381106982</v>
       </c>
       <c r="D30" t="n">
-        <v>1411.56</v>
+        <v>1411.558838454996</v>
       </c>
       <c r="E30" t="n">
-        <v>1424.55</v>
+        <v>1424.548783684645</v>
       </c>
       <c r="F30" t="n">
         <v>11772</v>
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1417.45</v>
+        <v>1417.447098546351</v>
       </c>
       <c r="D31" t="n">
-        <v>1412.59</v>
+        <v>1412.587985969517</v>
       </c>
       <c r="E31" t="n">
-        <v>1422.31</v>
+        <v>1422.306211123185</v>
       </c>
       <c r="F31" t="n">
         <v>27627</v>
@@ -4005,13 +4005,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1417.41</v>
+        <v>1417.405847331528</v>
       </c>
       <c r="D32" t="n">
-        <v>1411.4</v>
+        <v>1411.396362758647</v>
       </c>
       <c r="E32" t="n">
-        <v>1423.42</v>
+        <v>1423.41533190441</v>
       </c>
       <c r="F32" t="n">
         <v>14954</v>
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1417.12</v>
+        <v>1417.123984658945</v>
       </c>
       <c r="D33" t="n">
-        <v>1410.51</v>
+        <v>1410.514662679633</v>
       </c>
       <c r="E33" t="n">
-        <v>1423.73</v>
+        <v>1423.733306638256</v>
       </c>
       <c r="F33" t="n">
         <v>11731</v>
@@ -4147,13 +4147,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1417.06</v>
+        <v>1417.05522082422</v>
       </c>
       <c r="D34" t="n">
-        <v>1412.66</v>
+        <v>1412.655641664229</v>
       </c>
       <c r="E34" t="n">
-        <v>1421.45</v>
+        <v>1421.45479998421</v>
       </c>
       <c r="F34" t="n">
         <v>28563</v>
@@ -4298,13 +4298,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1416.82</v>
+        <v>1416.821308531066</v>
       </c>
       <c r="D35" t="n">
-        <v>1412.48</v>
+        <v>1412.482245299455</v>
       </c>
       <c r="E35" t="n">
-        <v>1421.16</v>
+        <v>1421.160371762677</v>
       </c>
       <c r="F35" t="n">
         <v>42368</v>
@@ -4369,13 +4369,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1415.71</v>
+        <v>1415.705125997306</v>
       </c>
       <c r="D36" t="n">
-        <v>1406.08</v>
+        <v>1406.077511946972</v>
       </c>
       <c r="E36" t="n">
-        <v>1425.33</v>
+        <v>1425.33274004764</v>
       </c>
       <c r="F36" t="n">
         <v>3691</v>
@@ -4440,13 +4440,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1415.66</v>
+        <v>1415.658500889831</v>
       </c>
       <c r="D37" t="n">
-        <v>1412.08</v>
+        <v>1412.084903180666</v>
       </c>
       <c r="E37" t="n">
-        <v>1419.23</v>
+        <v>1419.232098598996</v>
       </c>
       <c r="F37" t="n">
         <v>44086</v>
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1415.44</v>
+        <v>1415.444854660351</v>
       </c>
       <c r="D38" t="n">
-        <v>1408.96</v>
+        <v>1408.95982483211</v>
       </c>
       <c r="E38" t="n">
-        <v>1421.93</v>
+        <v>1421.929884488592</v>
       </c>
       <c r="F38" t="n">
         <v>11501</v>
@@ -4742,13 +4742,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1412.91</v>
+        <v>1412.912550124611</v>
       </c>
       <c r="D39" t="n">
-        <v>1405.38</v>
+        <v>1405.375577861305</v>
       </c>
       <c r="E39" t="n">
-        <v>1420.45</v>
+        <v>1420.449522387916</v>
       </c>
       <c r="F39" t="n">
         <v>6674</v>
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1410.91</v>
+        <v>1410.911532500788</v>
       </c>
       <c r="D40" t="n">
-        <v>1406.03</v>
+        <v>1406.029601407999</v>
       </c>
       <c r="E40" t="n">
-        <v>1415.79</v>
+        <v>1415.793463593578</v>
       </c>
       <c r="F40" t="n">
         <v>24293</v>
@@ -4964,13 +4964,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1408.82</v>
+        <v>1408.822568786353</v>
       </c>
       <c r="D41" t="n">
-        <v>1404.39</v>
+        <v>1404.391183679576</v>
       </c>
       <c r="E41" t="n">
-        <v>1413.25</v>
+        <v>1413.253953893131</v>
       </c>
       <c r="F41" t="n">
         <v>27408</v>
@@ -5115,13 +5115,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1403.17</v>
+        <v>1403.173847755168</v>
       </c>
       <c r="D42" t="n">
-        <v>1398.67</v>
+        <v>1398.67350991818</v>
       </c>
       <c r="E42" t="n">
-        <v>1407.67</v>
+        <v>1407.674185592156</v>
       </c>
       <c r="F42" t="n">
         <v>38191</v>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1401.49</v>
+        <v>1401.487365892205</v>
       </c>
       <c r="D43" t="n">
-        <v>1396.72</v>
+        <v>1396.716151096404</v>
       </c>
       <c r="E43" t="n">
-        <v>1406.26</v>
+        <v>1406.258580688006</v>
       </c>
       <c r="F43" t="n">
         <v>22865</v>
@@ -5417,13 +5417,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1401.1</v>
+        <v>1401.097051746745</v>
       </c>
       <c r="D44" t="n">
-        <v>1394.73</v>
+        <v>1394.727128429446</v>
       </c>
       <c r="E44" t="n">
-        <v>1407.47</v>
+        <v>1407.466975064043</v>
       </c>
       <c r="F44" t="n">
         <v>11380</v>
@@ -5568,13 +5568,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1399.18</v>
+        <v>1399.175687136281</v>
       </c>
       <c r="D45" t="n">
-        <v>1392.64</v>
+        <v>1392.642626014682</v>
       </c>
       <c r="E45" t="n">
-        <v>1405.71</v>
+        <v>1405.70874825788</v>
       </c>
       <c r="F45" t="n">
         <v>8991</v>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1398.08</v>
+        <v>1398.080881265658</v>
       </c>
       <c r="D46" t="n">
-        <v>1393.2</v>
+        <v>1393.20501218071</v>
       </c>
       <c r="E46" t="n">
-        <v>1402.96</v>
+        <v>1402.956750350605</v>
       </c>
       <c r="F46" t="n">
         <v>18524</v>
@@ -5870,13 +5870,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1395.72</v>
+        <v>1395.722474643064</v>
       </c>
       <c r="D47" t="n">
-        <v>1388.93</v>
+        <v>1388.932869923728</v>
       </c>
       <c r="E47" t="n">
-        <v>1402.51</v>
+        <v>1402.5120793624</v>
       </c>
       <c r="F47" t="n">
         <v>7939</v>
@@ -6021,13 +6021,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1395.64</v>
+        <v>1395.635260537728</v>
       </c>
       <c r="D48" t="n">
-        <v>1391.28</v>
+        <v>1391.281168288014</v>
       </c>
       <c r="E48" t="n">
-        <v>1399.99</v>
+        <v>1399.989352787441</v>
       </c>
       <c r="F48" t="n">
         <v>29211</v>
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1395.56</v>
+        <v>1395.559211450224</v>
       </c>
       <c r="D49" t="n">
-        <v>1391.69</v>
+        <v>1391.687948359546</v>
       </c>
       <c r="E49" t="n">
-        <v>1399.43</v>
+        <v>1399.430474540903</v>
       </c>
       <c r="F49" t="n">
         <v>45491</v>
@@ -6323,13 +6323,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1394.86</v>
+        <v>1394.860818771535</v>
       </c>
       <c r="D50" t="n">
-        <v>1391.1</v>
+        <v>1391.101733121227</v>
       </c>
       <c r="E50" t="n">
-        <v>1398.62</v>
+        <v>1398.619904421843</v>
       </c>
       <c r="F50" t="n">
         <v>52274</v>
@@ -6394,13 +6394,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1392.97</v>
+        <v>1392.965679388187</v>
       </c>
       <c r="D51" t="n">
-        <v>1389.39</v>
+        <v>1389.392549894614</v>
       </c>
       <c r="E51" t="n">
-        <v>1396.54</v>
+        <v>1396.538808881761</v>
       </c>
       <c r="F51" t="n">
         <v>46660</v>
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1390.58</v>
+        <v>1390.581863305857</v>
       </c>
       <c r="D52" t="n">
-        <v>1386.57</v>
+        <v>1386.574716715496</v>
       </c>
       <c r="E52" t="n">
-        <v>1394.59</v>
+        <v>1394.589009896218</v>
       </c>
       <c r="F52" t="n">
         <v>41241</v>
@@ -6536,13 +6536,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1387.63</v>
+        <v>1387.629520020103</v>
       </c>
       <c r="D53" t="n">
-        <v>1382.68</v>
+        <v>1382.681028619063</v>
       </c>
       <c r="E53" t="n">
-        <v>1392.58</v>
+        <v>1392.578011421143</v>
       </c>
       <c r="F53" t="n">
         <v>25709</v>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1387.13</v>
+        <v>1387.134028765115</v>
       </c>
       <c r="D54" t="n">
-        <v>1380.88</v>
+        <v>1380.884562006627</v>
       </c>
       <c r="E54" t="n">
-        <v>1393.38</v>
+        <v>1393.383495523602</v>
       </c>
       <c r="F54" t="n">
         <v>10955</v>
@@ -6758,13 +6758,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1384.39</v>
+        <v>1384.392127507076</v>
       </c>
       <c r="D55" t="n">
-        <v>1379.16</v>
+        <v>1379.161432335864</v>
       </c>
       <c r="E55" t="n">
-        <v>1389.62</v>
+        <v>1389.622822678288</v>
       </c>
       <c r="F55" t="n">
         <v>17112</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1383.16</v>
+        <v>1383.163868080818</v>
       </c>
       <c r="D56" t="n">
-        <v>1378.29</v>
+        <v>1378.285326022174</v>
       </c>
       <c r="E56" t="n">
-        <v>1388.04</v>
+        <v>1388.042410139461</v>
       </c>
       <c r="F56" t="n">
         <v>23720</v>
@@ -6980,22 +6980,18 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1378.56</v>
+        <v>1378.558201143977</v>
       </c>
       <c r="D57" t="n">
-        <v>1374.19</v>
+        <v>1374.190568930903</v>
       </c>
       <c r="E57" t="n">
-        <v>1382.93</v>
+        <v>1382.925833357051</v>
       </c>
       <c r="F57" t="n">
         <v>30115</v>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Arcee AI</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -7131,13 +7127,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1377.2</v>
+        <v>1377.199349048589</v>
       </c>
       <c r="D58" t="n">
-        <v>1365.94</v>
+        <v>1365.940095082343</v>
       </c>
       <c r="E58" t="n">
-        <v>1388.46</v>
+        <v>1388.458603014836</v>
       </c>
       <c r="F58" t="n">
         <v>2802</v>
@@ -7202,13 +7198,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1374.77</v>
+        <v>1374.77089940988</v>
       </c>
       <c r="D59" t="n">
-        <v>1370.08</v>
+        <v>1370.079349684971</v>
       </c>
       <c r="E59" t="n">
-        <v>1379.46</v>
+        <v>1379.462449134789</v>
       </c>
       <c r="F59" t="n">
         <v>26259</v>
@@ -7353,13 +7349,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1373.04</v>
+        <v>1373.044550330477</v>
       </c>
       <c r="D60" t="n">
-        <v>1368.8</v>
+        <v>1368.801692474028</v>
       </c>
       <c r="E60" t="n">
-        <v>1377.29</v>
+        <v>1377.287408186926</v>
       </c>
       <c r="F60" t="n">
         <v>31066</v>
@@ -7424,13 +7420,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1369.65</v>
+        <v>1369.654349713076</v>
       </c>
       <c r="D61" t="n">
-        <v>1363.82</v>
+        <v>1363.816785655225</v>
       </c>
       <c r="E61" t="n">
-        <v>1375.49</v>
+        <v>1375.491913770928</v>
       </c>
       <c r="F61" t="n">
         <v>13686</v>
@@ -7575,22 +7571,18 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1369.13</v>
+        <v>1369.126296435841</v>
       </c>
       <c r="D62" t="n">
-        <v>1364.43</v>
+        <v>1364.426562751712</v>
       </c>
       <c r="E62" t="n">
-        <v>1373.83</v>
+        <v>1373.82603011997</v>
       </c>
       <c r="F62" t="n">
         <v>29229</v>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Arcee AI</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -7726,13 +7718,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1367.87</v>
+        <v>1367.870109355791</v>
       </c>
       <c r="D63" t="n">
-        <v>1362.07</v>
+        <v>1362.065632426707</v>
       </c>
       <c r="E63" t="n">
-        <v>1373.67</v>
+        <v>1373.674586284875</v>
       </c>
       <c r="F63" t="n">
         <v>11724</v>
@@ -7797,13 +7789,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1365.76</v>
+        <v>1365.764478565441</v>
       </c>
       <c r="D64" t="n">
-        <v>1362.09</v>
+        <v>1362.092267165797</v>
       </c>
       <c r="E64" t="n">
-        <v>1369.44</v>
+        <v>1369.436689965086</v>
       </c>
       <c r="F64" t="n">
         <v>47513</v>
@@ -7948,13 +7940,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1363.63</v>
+        <v>1363.6298318409</v>
       </c>
       <c r="D65" t="n">
-        <v>1359.36</v>
+        <v>1359.358485851574</v>
       </c>
       <c r="E65" t="n">
-        <v>1367.9</v>
+        <v>1367.901177830226</v>
       </c>
       <c r="F65" t="n">
         <v>35177</v>
@@ -8019,13 +8011,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1361.73</v>
+        <v>1361.726147940642</v>
       </c>
       <c r="D66" t="n">
-        <v>1354.46</v>
+        <v>1354.4573698466</v>
       </c>
       <c r="E66" t="n">
-        <v>1368.99</v>
+        <v>1368.994926034683</v>
       </c>
       <c r="F66" t="n">
         <v>7547</v>
@@ -8170,13 +8162,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1358.47</v>
+        <v>1358.471252976401</v>
       </c>
       <c r="D67" t="n">
-        <v>1353.73</v>
+        <v>1353.731862123469</v>
       </c>
       <c r="E67" t="n">
-        <v>1363.21</v>
+        <v>1363.210643829333</v>
       </c>
       <c r="F67" t="n">
         <v>21770</v>
@@ -8321,13 +8313,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1357.67</v>
+        <v>1357.667005273806</v>
       </c>
       <c r="D68" t="n">
-        <v>1352.47</v>
+        <v>1352.466473492829</v>
       </c>
       <c r="E68" t="n">
-        <v>1362.87</v>
+        <v>1362.867537054782</v>
       </c>
       <c r="F68" t="n">
         <v>17698</v>
@@ -8392,22 +8384,18 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1356.34</v>
+        <v>1356.33774161985</v>
       </c>
       <c r="D69" t="n">
-        <v>1347.99</v>
+        <v>1347.990914953977</v>
       </c>
       <c r="E69" t="n">
-        <v>1364.68</v>
+        <v>1364.684568285724</v>
       </c>
       <c r="F69" t="n">
         <v>5329</v>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Prime Intellect</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>MIT</t>
@@ -8543,13 +8531,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1353.95</v>
+        <v>1353.950686589983</v>
       </c>
       <c r="D70" t="n">
-        <v>1350.5</v>
+        <v>1350.503046969528</v>
       </c>
       <c r="E70" t="n">
-        <v>1357.4</v>
+        <v>1357.398326210438</v>
       </c>
       <c r="F70" t="n">
         <v>56234</v>
@@ -8614,13 +8602,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1353.56</v>
+        <v>1353.562197653564</v>
       </c>
       <c r="D71" t="n">
-        <v>1345.22</v>
+        <v>1345.217368367803</v>
       </c>
       <c r="E71" t="n">
-        <v>1361.91</v>
+        <v>1361.907026939325</v>
       </c>
       <c r="F71" t="n">
         <v>4956</v>
@@ -8685,13 +8673,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1352.62</v>
+        <v>1352.620923660646</v>
       </c>
       <c r="D72" t="n">
-        <v>1348.27</v>
+        <v>1348.27443085289</v>
       </c>
       <c r="E72" t="n">
-        <v>1356.97</v>
+        <v>1356.967416468403</v>
       </c>
       <c r="F72" t="n">
         <v>30639</v>
@@ -8836,13 +8824,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1348.45</v>
+        <v>1348.451318620989</v>
       </c>
       <c r="D73" t="n">
-        <v>1341.05</v>
+        <v>1341.047594336476</v>
       </c>
       <c r="E73" t="n">
-        <v>1355.86</v>
+        <v>1355.855042905504</v>
       </c>
       <c r="F73" t="n">
         <v>6537</v>
@@ -8907,13 +8895,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1347.43</v>
+        <v>1347.432489754107</v>
       </c>
       <c r="D74" t="n">
-        <v>1335.75</v>
+        <v>1335.746333798763</v>
       </c>
       <c r="E74" t="n">
-        <v>1359.12</v>
+        <v>1359.11864570945</v>
       </c>
       <c r="F74" t="n">
         <v>2549</v>
@@ -9058,13 +9046,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1347.26</v>
+        <v>1347.260186955363</v>
       </c>
       <c r="D75" t="n">
-        <v>1337.8</v>
+        <v>1337.801597831706</v>
       </c>
       <c r="E75" t="n">
-        <v>1356.72</v>
+        <v>1356.71877607902</v>
       </c>
       <c r="F75" t="n">
         <v>3926</v>
@@ -9209,13 +9197,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1346.39</v>
+        <v>1346.389781202702</v>
       </c>
       <c r="D76" t="n">
-        <v>1339.13</v>
+        <v>1339.131251923795</v>
       </c>
       <c r="E76" t="n">
-        <v>1353.65</v>
+        <v>1353.64831048161</v>
       </c>
       <c r="F76" t="n">
         <v>7003</v>
@@ -9280,13 +9268,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1345.98</v>
+        <v>1345.980576667275</v>
       </c>
       <c r="D77" t="n">
-        <v>1338.24</v>
+        <v>1338.241925100815</v>
       </c>
       <c r="E77" t="n">
-        <v>1353.72</v>
+        <v>1353.719228233736</v>
       </c>
       <c r="F77" t="n">
         <v>6864</v>
@@ -9431,13 +9419,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1343.06</v>
+        <v>1343.058122375561</v>
       </c>
       <c r="D78" t="n">
-        <v>1333.09</v>
+        <v>1333.091246626917</v>
       </c>
       <c r="E78" t="n">
-        <v>1353.03</v>
+        <v>1353.024998124204</v>
       </c>
       <c r="F78" t="n">
         <v>3346</v>
@@ -9582,13 +9570,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1341.88</v>
+        <v>1341.878872779034</v>
       </c>
       <c r="D79" t="n">
-        <v>1332.37</v>
+        <v>1332.370033964112</v>
       </c>
       <c r="E79" t="n">
-        <v>1351.39</v>
+        <v>1351.387711593956</v>
       </c>
       <c r="F79" t="n">
         <v>3829</v>
@@ -9733,13 +9721,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1336.16</v>
+        <v>1336.16196444838</v>
       </c>
       <c r="D80" t="n">
-        <v>1331.72</v>
+        <v>1331.723765129484</v>
       </c>
       <c r="E80" t="n">
-        <v>1340.6</v>
+        <v>1340.600163767276</v>
       </c>
       <c r="F80" t="n">
         <v>25382</v>
@@ -9884,13 +9872,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1334.69</v>
+        <v>1334.690891720765</v>
       </c>
       <c r="D81" t="n">
-        <v>1330.98</v>
+        <v>1330.982447806294</v>
       </c>
       <c r="E81" t="n">
-        <v>1338.4</v>
+        <v>1338.399335635235</v>
       </c>
       <c r="F81" t="n">
         <v>41375</v>
@@ -10035,13 +10023,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1332.86</v>
+        <v>1332.864584789327</v>
       </c>
       <c r="D82" t="n">
-        <v>1329.27</v>
+        <v>1329.272339266846</v>
       </c>
       <c r="E82" t="n">
-        <v>1336.46</v>
+        <v>1336.456830311807</v>
       </c>
       <c r="F82" t="n">
         <v>59656</v>
@@ -10186,13 +10174,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1330.08</v>
+        <v>1330.083713227149</v>
       </c>
       <c r="D83" t="n">
-        <v>1324</v>
+        <v>1324.002299491965</v>
       </c>
       <c r="E83" t="n">
-        <v>1336.17</v>
+        <v>1336.165126962332</v>
       </c>
       <c r="F83" t="n">
         <v>12217</v>
@@ -10337,13 +10325,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1328.3</v>
+        <v>1328.29661933247</v>
       </c>
       <c r="D84" t="n">
-        <v>1307</v>
+        <v>1306.99930811445</v>
       </c>
       <c r="E84" t="n">
-        <v>1349.59</v>
+        <v>1349.59393055049</v>
       </c>
       <c r="F84" t="n">
         <v>803</v>
@@ -10488,13 +10476,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1327.97</v>
+        <v>1327.969074546529</v>
       </c>
       <c r="D85" t="n">
-        <v>1315.82</v>
+        <v>1315.819495291745</v>
       </c>
       <c r="E85" t="n">
-        <v>1340.12</v>
+        <v>1340.118653801313</v>
       </c>
       <c r="F85" t="n">
         <v>2218</v>
@@ -10639,13 +10627,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1327.27</v>
+        <v>1327.268432522309</v>
       </c>
       <c r="D86" t="n">
-        <v>1322.54</v>
+        <v>1322.541300339965</v>
       </c>
       <c r="E86" t="n">
-        <v>1332</v>
+        <v>1331.995564704653</v>
       </c>
       <c r="F86" t="n">
         <v>26474</v>
@@ -10790,13 +10778,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1326.94</v>
+        <v>1326.936995789791</v>
       </c>
       <c r="D87" t="n">
-        <v>1322.69</v>
+        <v>1322.686532635555</v>
       </c>
       <c r="E87" t="n">
-        <v>1331.19</v>
+        <v>1331.187458944027</v>
       </c>
       <c r="F87" t="n">
         <v>39967</v>
@@ -10941,13 +10929,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1323.42</v>
+        <v>1323.419941391904</v>
       </c>
       <c r="D88" t="n">
-        <v>1315.15</v>
+        <v>1315.150348225536</v>
       </c>
       <c r="E88" t="n">
-        <v>1331.69</v>
+        <v>1331.689534558271</v>
       </c>
       <c r="F88" t="n">
         <v>6795</v>
@@ -11012,13 +11000,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1322.64</v>
+        <v>1322.636355202719</v>
       </c>
       <c r="D89" t="n">
-        <v>1317.93</v>
+        <v>1317.931185821038</v>
       </c>
       <c r="E89" t="n">
-        <v>1327.34</v>
+        <v>1327.3415245844</v>
       </c>
       <c r="F89" t="n">
         <v>30275</v>
@@ -11163,13 +11151,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1320.74</v>
+        <v>1320.737438599908</v>
       </c>
       <c r="D90" t="n">
-        <v>1313.52</v>
+        <v>1313.52301688618</v>
       </c>
       <c r="E90" t="n">
-        <v>1327.95</v>
+        <v>1327.951860313635</v>
       </c>
       <c r="F90" t="n">
         <v>7137</v>
@@ -11234,13 +11222,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1318.14</v>
+        <v>1318.138426141699</v>
       </c>
       <c r="D91" t="n">
-        <v>1314.67</v>
+        <v>1314.669054767298</v>
       </c>
       <c r="E91" t="n">
-        <v>1321.61</v>
+        <v>1321.607797516101</v>
       </c>
       <c r="F91" t="n">
         <v>54732</v>
@@ -11385,13 +11373,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1318.11</v>
+        <v>1318.114216429686</v>
       </c>
       <c r="D92" t="n">
-        <v>1312.97</v>
+        <v>1312.968844829356</v>
       </c>
       <c r="E92" t="n">
-        <v>1323.26</v>
+        <v>1323.259588030017</v>
       </c>
       <c r="F92" t="n">
         <v>22578</v>
@@ -11536,13 +11524,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1317.91</v>
+        <v>1317.909285753745</v>
       </c>
       <c r="D93" t="n">
-        <v>1312.21</v>
+        <v>1312.210788685309</v>
       </c>
       <c r="E93" t="n">
-        <v>1323.61</v>
+        <v>1323.607782822181</v>
       </c>
       <c r="F93" t="n">
         <v>16478</v>
@@ -11607,13 +11595,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1317.43</v>
+        <v>1317.42599810888</v>
       </c>
       <c r="D94" t="n">
-        <v>1311.06</v>
+        <v>1311.058758901932</v>
       </c>
       <c r="E94" t="n">
-        <v>1323.79</v>
+        <v>1323.793237315828</v>
       </c>
       <c r="F94" t="n">
         <v>10625</v>
@@ -11758,13 +11746,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1316.06</v>
+        <v>1316.063932428772</v>
       </c>
       <c r="D95" t="n">
-        <v>1310.52</v>
+        <v>1310.517954708409</v>
       </c>
       <c r="E95" t="n">
-        <v>1321.61</v>
+        <v>1321.609910149135</v>
       </c>
       <c r="F95" t="n">
         <v>15509</v>
@@ -11909,22 +11897,18 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1314.29</v>
+        <v>1314.285077301751</v>
       </c>
       <c r="D96" t="n">
-        <v>1309.74</v>
+        <v>1309.735588822665</v>
       </c>
       <c r="E96" t="n">
-        <v>1318.83</v>
+        <v>1318.834565780837</v>
       </c>
       <c r="F96" t="n">
         <v>24739</v>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>NexusFlow</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>NexusFlow</t>
@@ -12060,13 +12044,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1313.92</v>
+        <v>1313.915846313264</v>
       </c>
       <c r="D97" t="n">
-        <v>1309.99</v>
+        <v>1309.99229682006</v>
       </c>
       <c r="E97" t="n">
-        <v>1317.84</v>
+        <v>1317.839395806468</v>
       </c>
       <c r="F97" t="n">
         <v>45459</v>
@@ -12211,13 +12195,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1307.05</v>
+        <v>1307.052888237502</v>
       </c>
       <c r="D98" t="n">
-        <v>1302.35</v>
+        <v>1302.349344550076</v>
       </c>
       <c r="E98" t="n">
-        <v>1311.76</v>
+        <v>1311.756431924926</v>
       </c>
       <c r="F98" t="n">
         <v>24572</v>
@@ -12282,13 +12266,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1306.8</v>
+        <v>1306.797440488142</v>
       </c>
       <c r="D99" t="n">
-        <v>1296.66</v>
+        <v>1296.660146947183</v>
       </c>
       <c r="E99" t="n">
-        <v>1316.93</v>
+        <v>1316.934734029101</v>
       </c>
       <c r="F99" t="n">
         <v>4063</v>
@@ -12433,22 +12417,18 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1306.23</v>
+        <v>1306.229302396765</v>
       </c>
       <c r="D100" t="n">
-        <v>1300.56</v>
+        <v>1300.556174848534</v>
       </c>
       <c r="E100" t="n">
-        <v>1311.9</v>
+        <v>1311.902429944997</v>
       </c>
       <c r="F100" t="n">
         <v>19621</v>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>NexusFlow</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>CC-BY-NC-4.0</t>
@@ -12584,13 +12564,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1305.63</v>
+        <v>1305.631209093297</v>
       </c>
       <c r="D101" t="n">
-        <v>1297.45</v>
+        <v>1297.45333347367</v>
       </c>
       <c r="E101" t="n">
-        <v>1313.81</v>
+        <v>1313.809084712924</v>
       </c>
       <c r="F101" t="n">
         <v>5942</v>
@@ -12735,13 +12715,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1305.2</v>
+        <v>1305.200818750652</v>
       </c>
       <c r="D102" t="n">
-        <v>1300.77</v>
+        <v>1300.768103082117</v>
       </c>
       <c r="E102" t="n">
-        <v>1309.63</v>
+        <v>1309.633534419187</v>
       </c>
       <c r="F102" t="n">
         <v>28073</v>
@@ -12806,13 +12786,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1303.41</v>
+        <v>1303.408632542045</v>
       </c>
       <c r="D103" t="n">
-        <v>1298.9</v>
+        <v>1298.901575649192</v>
       </c>
       <c r="E103" t="n">
-        <v>1307.92</v>
+        <v>1307.915689434898</v>
       </c>
       <c r="F103" t="n">
         <v>33204</v>
@@ -12957,13 +12937,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1303.28</v>
+        <v>1303.280318412984</v>
       </c>
       <c r="D104" t="n">
-        <v>1293.96</v>
+        <v>1293.964877949521</v>
       </c>
       <c r="E104" t="n">
-        <v>1312.6</v>
+        <v>1312.595758876446</v>
       </c>
       <c r="F104" t="n">
         <v>4171</v>
@@ -13108,13 +13088,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1302.77</v>
+        <v>1302.765591511461</v>
       </c>
       <c r="D105" t="n">
-        <v>1298.7</v>
+        <v>1298.695327667053</v>
       </c>
       <c r="E105" t="n">
-        <v>1306.84</v>
+        <v>1306.835855355868</v>
       </c>
       <c r="F105" t="n">
         <v>39406</v>
@@ -13259,13 +13239,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1298.94</v>
+        <v>1298.938155015356</v>
       </c>
       <c r="D106" t="n">
-        <v>1291.18</v>
+        <v>1291.176072483735</v>
       </c>
       <c r="E106" t="n">
-        <v>1306.7</v>
+        <v>1306.700237546978</v>
       </c>
       <c r="F106" t="n">
         <v>7140</v>
@@ -13410,13 +13390,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1293.12</v>
+        <v>1293.121634370848</v>
       </c>
       <c r="D107" t="n">
-        <v>1289.39</v>
+        <v>1289.38880245615</v>
       </c>
       <c r="E107" t="n">
-        <v>1296.85</v>
+        <v>1296.854466285545</v>
       </c>
       <c r="F107" t="n">
         <v>55240</v>
@@ -13561,22 +13541,18 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1288.94</v>
+        <v>1288.941790653918</v>
       </c>
       <c r="D108" t="n">
-        <v>1281.64</v>
+        <v>1281.635062895248</v>
       </c>
       <c r="E108" t="n">
-        <v>1296.25</v>
+        <v>1296.248518412589</v>
       </c>
       <c r="F108" t="n">
         <v>8662</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>AI21 Labs</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>Jamba Open</t>
@@ -13632,13 +13608,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1288.77</v>
+        <v>1288.772092847751</v>
       </c>
       <c r="D109" t="n">
-        <v>1285.39</v>
+        <v>1285.39415930362</v>
       </c>
       <c r="E109" t="n">
-        <v>1292.15</v>
+        <v>1292.150026391882</v>
       </c>
       <c r="F109" t="n">
         <v>75754</v>
@@ -13783,13 +13759,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1286.82</v>
+        <v>1286.822579184289</v>
       </c>
       <c r="D110" t="n">
-        <v>1278.43</v>
+        <v>1278.428711633377</v>
       </c>
       <c r="E110" t="n">
-        <v>1295.22</v>
+        <v>1295.216446735202</v>
       </c>
       <c r="F110" t="n">
         <v>5680</v>
@@ -13934,13 +13910,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1285.91</v>
+        <v>1285.907059913281</v>
       </c>
       <c r="D111" t="n">
-        <v>1275.44</v>
+        <v>1275.438568841443</v>
       </c>
       <c r="E111" t="n">
-        <v>1296.38</v>
+        <v>1296.375550985118</v>
       </c>
       <c r="F111" t="n">
         <v>2846</v>
@@ -14085,13 +14061,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1285.81</v>
+        <v>1285.805404874266</v>
       </c>
       <c r="D112" t="n">
-        <v>1275.83</v>
+        <v>1275.832610354328</v>
       </c>
       <c r="E112" t="n">
-        <v>1295.78</v>
+        <v>1295.778199394204</v>
       </c>
       <c r="F112" t="n">
         <v>3749</v>
@@ -14236,13 +14212,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1285.01</v>
+        <v>1285.009685620031</v>
       </c>
       <c r="D113" t="n">
-        <v>1277.8</v>
+        <v>1277.799094931654</v>
       </c>
       <c r="E113" t="n">
-        <v>1292.22</v>
+        <v>1292.220276308408</v>
       </c>
       <c r="F113" t="n">
         <v>8503</v>
@@ -14387,22 +14363,18 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1279.78</v>
+        <v>1279.783673382128</v>
       </c>
       <c r="D114" t="n">
-        <v>1272.92</v>
+        <v>1272.923157934549</v>
       </c>
       <c r="E114" t="n">
-        <v>1286.64</v>
+        <v>1286.644188829707</v>
       </c>
       <c r="F114" t="n">
         <v>10072</v>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Princeton</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>MIT</t>
@@ -14538,13 +14510,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1276.43</v>
+        <v>1276.430063793639</v>
       </c>
       <c r="D115" t="n">
-        <v>1271.1</v>
+        <v>1271.10307791463</v>
       </c>
       <c r="E115" t="n">
-        <v>1281.76</v>
+        <v>1281.757049672647</v>
       </c>
       <c r="F115" t="n">
         <v>19659</v>
@@ -14689,13 +14661,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1275.82</v>
+        <v>1275.81672143464</v>
       </c>
       <c r="D116" t="n">
-        <v>1272.23</v>
+        <v>1272.229375260231</v>
       </c>
       <c r="E116" t="n">
-        <v>1279.4</v>
+        <v>1279.404067609049</v>
       </c>
       <c r="F116" t="n">
         <v>156876</v>
@@ -14840,13 +14812,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1275.73</v>
+        <v>1275.726486157192</v>
       </c>
       <c r="D117" t="n">
-        <v>1269.15</v>
+        <v>1269.149480036716</v>
       </c>
       <c r="E117" t="n">
-        <v>1282.3</v>
+        <v>1282.303492277669</v>
       </c>
       <c r="F117" t="n">
         <v>9866</v>
@@ -14991,13 +14963,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1274.02</v>
+        <v>1274.01624391297</v>
       </c>
       <c r="D118" t="n">
-        <v>1268.11</v>
+        <v>1268.111808181116</v>
       </c>
       <c r="E118" t="n">
-        <v>1279.92</v>
+        <v>1279.920679644825</v>
       </c>
       <c r="F118" t="n">
         <v>14681</v>
@@ -15142,13 +15114,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1270.32</v>
+        <v>1270.317547106389</v>
       </c>
       <c r="D119" t="n">
-        <v>1262.19</v>
+        <v>1262.190965054567</v>
       </c>
       <c r="E119" t="n">
-        <v>1278.44</v>
+        <v>1278.444129158212</v>
       </c>
       <c r="F119" t="n">
         <v>5432</v>
@@ -15293,13 +15265,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1266.81</v>
+        <v>1266.810871865221</v>
       </c>
       <c r="D120" t="n">
-        <v>1261.93</v>
+        <v>1261.925945630747</v>
       </c>
       <c r="E120" t="n">
-        <v>1271.7</v>
+        <v>1271.695798099695</v>
       </c>
       <c r="F120" t="n">
         <v>27124</v>
@@ -15444,13 +15416,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1266.28</v>
+        <v>1266.282432210059</v>
       </c>
       <c r="D121" t="n">
-        <v>1262.47</v>
+        <v>1262.467125747545</v>
       </c>
       <c r="E121" t="n">
-        <v>1270.1</v>
+        <v>1270.097738672573</v>
       </c>
       <c r="F121" t="n">
         <v>54611</v>
@@ -15595,13 +15567,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1264.36</v>
+        <v>1264.360173472154</v>
       </c>
       <c r="D122" t="n">
-        <v>1258.08</v>
+        <v>1258.079233338555</v>
       </c>
       <c r="E122" t="n">
-        <v>1270.64</v>
+        <v>1270.641113605752</v>
       </c>
       <c r="F122" t="n">
         <v>15147</v>
@@ -15746,13 +15718,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1261.02</v>
+        <v>1261.019446952845</v>
       </c>
       <c r="D123" t="n">
-        <v>1256.07</v>
+        <v>1256.072103889396</v>
       </c>
       <c r="E123" t="n">
-        <v>1265.97</v>
+        <v>1265.966790016293</v>
       </c>
       <c r="F123" t="n">
         <v>37325</v>
@@ -15897,13 +15869,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1260.97</v>
+        <v>1260.967521457678</v>
       </c>
       <c r="D124" t="n">
-        <v>1256.64</v>
+        <v>1256.642619388689</v>
       </c>
       <c r="E124" t="n">
-        <v>1265.29</v>
+        <v>1265.292423526668</v>
       </c>
       <c r="F124" t="n">
         <v>77554</v>
@@ -15968,13 +15940,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1255.95</v>
+        <v>1255.950288834706</v>
       </c>
       <c r="D125" t="n">
-        <v>1251.36</v>
+        <v>1251.359973267281</v>
       </c>
       <c r="E125" t="n">
-        <v>1260.54</v>
+        <v>1260.540604402132</v>
       </c>
       <c r="F125" t="n">
         <v>24126</v>
@@ -16119,13 +16091,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1251.3</v>
+        <v>1251.295417370818</v>
       </c>
       <c r="D126" t="n">
-        <v>1240.51</v>
+        <v>1240.511973182844</v>
       </c>
       <c r="E126" t="n">
-        <v>1262.08</v>
+        <v>1262.078861558792</v>
       </c>
       <c r="F126" t="n">
         <v>3334</v>
@@ -16270,13 +16242,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1249.54</v>
+        <v>1249.54444881744</v>
       </c>
       <c r="D127" t="n">
-        <v>1242.94</v>
+        <v>1242.942977767999</v>
       </c>
       <c r="E127" t="n">
-        <v>1256.15</v>
+        <v>1256.14591986688</v>
       </c>
       <c r="F127" t="n">
         <v>10140</v>
@@ -16421,22 +16393,18 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1239.23</v>
+        <v>1239.230712835585</v>
       </c>
       <c r="D128" t="n">
-        <v>1232</v>
+        <v>1232.003693799109</v>
       </c>
       <c r="E128" t="n">
-        <v>1246.46</v>
+        <v>1246.457731872061</v>
       </c>
       <c r="F128" t="n">
         <v>8858</v>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>AI21 Labs</t>
-        </is>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>Jamba Open</t>
@@ -16492,13 +16460,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1237.2</v>
+        <v>1237.204968749514</v>
       </c>
       <c r="D129" t="n">
-        <v>1228.11</v>
+        <v>1228.110821628372</v>
       </c>
       <c r="E129" t="n">
-        <v>1246.3</v>
+        <v>1246.299115870656</v>
       </c>
       <c r="F129" t="n">
         <v>4781</v>
@@ -16643,13 +16611,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1233.38</v>
+        <v>1233.377749165773</v>
       </c>
       <c r="D130" t="n">
-        <v>1227.82</v>
+        <v>1227.822933597336</v>
       </c>
       <c r="E130" t="n">
-        <v>1238.93</v>
+        <v>1238.932564734209</v>
       </c>
       <c r="F130" t="n">
         <v>26195</v>
@@ -16794,13 +16762,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1232.55</v>
+        <v>1232.550768822609</v>
       </c>
       <c r="D131" t="n">
-        <v>1227.27</v>
+        <v>1227.274051051495</v>
       </c>
       <c r="E131" t="n">
-        <v>1237.83</v>
+        <v>1237.827486593723</v>
       </c>
       <c r="F131" t="n">
         <v>39302</v>
@@ -16945,13 +16913,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1228.59</v>
+        <v>1228.589813820794</v>
       </c>
       <c r="D132" t="n">
-        <v>1224.03</v>
+        <v>1224.032036693407</v>
       </c>
       <c r="E132" t="n">
-        <v>1233.15</v>
+        <v>1233.147590948181</v>
       </c>
       <c r="F132" t="n">
         <v>51416</v>
@@ -17096,13 +17064,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1225.95</v>
+        <v>1225.951346560972</v>
       </c>
       <c r="D133" t="n">
-        <v>1221.17</v>
+        <v>1221.167242388945</v>
       </c>
       <c r="E133" t="n">
-        <v>1230.74</v>
+        <v>1230.735450732999</v>
       </c>
       <c r="F133" t="n">
         <v>54036</v>
@@ -17167,13 +17135,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1222.85</v>
+        <v>1222.853857613258</v>
       </c>
       <c r="D134" t="n">
-        <v>1219.12</v>
+        <v>1219.115746120595</v>
       </c>
       <c r="E134" t="n">
-        <v>1226.59</v>
+        <v>1226.591969105921</v>
       </c>
       <c r="F134" t="n">
         <v>104642</v>
@@ -17318,13 +17286,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1222.76</v>
+        <v>1222.755490901058</v>
       </c>
       <c r="D135" t="n">
-        <v>1215.78</v>
+        <v>1215.784106842436</v>
       </c>
       <c r="E135" t="n">
-        <v>1229.73</v>
+        <v>1229.726874959679</v>
       </c>
       <c r="F135" t="n">
         <v>9818</v>
@@ -17469,13 +17437,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1220.41</v>
+        <v>1220.412263994809</v>
       </c>
       <c r="D136" t="n">
-        <v>1209.73</v>
+        <v>1209.732935562839</v>
       </c>
       <c r="E136" t="n">
-        <v>1231.09</v>
+        <v>1231.09159242678</v>
       </c>
       <c r="F136" t="n">
         <v>2896</v>
@@ -17620,22 +17588,18 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1212.44</v>
+        <v>1212.444005801904</v>
       </c>
       <c r="D137" t="n">
-        <v>1207.4</v>
+        <v>1207.403983561768</v>
       </c>
       <c r="E137" t="n">
-        <v>1217.48</v>
+        <v>1217.484028042042</v>
       </c>
       <c r="F137" t="n">
         <v>24146</v>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>01 AI</t>
-        </is>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -17771,22 +17735,18 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1212</v>
+        <v>1212.003634585186</v>
       </c>
       <c r="D138" t="n">
-        <v>1201.21</v>
+        <v>1201.209252921012</v>
       </c>
       <c r="E138" t="n">
-        <v>1222.8</v>
+        <v>1222.798016249359</v>
       </c>
       <c r="F138" t="n">
         <v>4652</v>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>HuggingFace</t>
-        </is>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -17922,13 +17882,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1211.27</v>
+        <v>1211.265782926833</v>
       </c>
       <c r="D139" t="n">
-        <v>1207.12</v>
+        <v>1207.118639058419</v>
       </c>
       <c r="E139" t="n">
-        <v>1215.41</v>
+        <v>1215.412926795248</v>
       </c>
       <c r="F139" t="n">
         <v>49605</v>
@@ -18073,13 +18033,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1207.71</v>
+        <v>1207.705651625702</v>
       </c>
       <c r="D140" t="n">
-        <v>1196.6</v>
+        <v>1196.601193214617</v>
       </c>
       <c r="E140" t="n">
-        <v>1218.81</v>
+        <v>1218.810110036787</v>
       </c>
       <c r="F140" t="n">
         <v>3090</v>
@@ -18224,13 +18184,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1203.02</v>
+        <v>1203.022531107527</v>
       </c>
       <c r="D141" t="n">
-        <v>1196.9</v>
+        <v>1196.902518555894</v>
       </c>
       <c r="E141" t="n">
-        <v>1209.14</v>
+        <v>1209.142543659159</v>
       </c>
       <c r="F141" t="n">
         <v>21741</v>
@@ -18375,13 +18335,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1199.7</v>
+        <v>1199.696127365285</v>
       </c>
       <c r="D142" t="n">
-        <v>1195.61</v>
+        <v>1195.60624802813</v>
       </c>
       <c r="E142" t="n">
-        <v>1203.79</v>
+        <v>1203.78600670244</v>
       </c>
       <c r="F142" t="n">
         <v>46616</v>
@@ -18526,13 +18486,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1197.07</v>
+        <v>1197.067187405617</v>
       </c>
       <c r="D143" t="n">
-        <v>1191.91</v>
+        <v>1191.906618534913</v>
       </c>
       <c r="E143" t="n">
-        <v>1202.23</v>
+        <v>1202.227756276321</v>
       </c>
       <c r="F143" t="n">
         <v>25055</v>
@@ -18677,13 +18637,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1196.21</v>
+        <v>1196.210394471505</v>
       </c>
       <c r="D144" t="n">
-        <v>1191.94</v>
+        <v>1191.939660759416</v>
       </c>
       <c r="E144" t="n">
-        <v>1200.48</v>
+        <v>1200.481128183593</v>
       </c>
       <c r="F144" t="n">
         <v>73503</v>
@@ -18828,22 +18788,18 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1194.36</v>
+        <v>1194.363173853415</v>
       </c>
       <c r="D145" t="n">
-        <v>1188.25</v>
+        <v>1188.2480085835</v>
       </c>
       <c r="E145" t="n">
-        <v>1200.48</v>
+        <v>1200.47833912333</v>
       </c>
       <c r="F145" t="n">
         <v>32191</v>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
           <t>DBRX LICENSE</t>
@@ -18899,22 +18855,18 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1190.5</v>
+        <v>1190.497894296829</v>
       </c>
       <c r="D146" t="n">
-        <v>1183.31</v>
+        <v>1183.314302940262</v>
       </c>
       <c r="E146" t="n">
-        <v>1197.68</v>
+        <v>1197.681485653396</v>
       </c>
       <c r="F146" t="n">
         <v>9901</v>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>InternLM</t>
-        </is>
-      </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
           <t>Other</t>
@@ -19050,13 +19002,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1190.18</v>
+        <v>1190.182117120627</v>
       </c>
       <c r="D147" t="n">
-        <v>1183.06</v>
+        <v>1183.061471654926</v>
       </c>
       <c r="E147" t="n">
-        <v>1197.3</v>
+        <v>1197.302762586328</v>
       </c>
       <c r="F147" t="n">
         <v>17839</v>
@@ -19201,13 +19153,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1183.8</v>
+        <v>1183.802546091035</v>
       </c>
       <c r="D148" t="n">
-        <v>1174.36</v>
+        <v>1174.360606110852</v>
       </c>
       <c r="E148" t="n">
-        <v>1193.24</v>
+        <v>1193.244486071217</v>
       </c>
       <c r="F148" t="n">
         <v>8214</v>
@@ -19352,13 +19304,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1183.72</v>
+        <v>1183.720023500402</v>
       </c>
       <c r="D149" t="n">
-        <v>1172.23</v>
+        <v>1172.228587291428</v>
       </c>
       <c r="E149" t="n">
-        <v>1195.21</v>
+        <v>1195.211459709376</v>
       </c>
       <c r="F149" t="n">
         <v>4932</v>
@@ -19503,22 +19455,18 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1183.02</v>
+        <v>1183.01670041035</v>
       </c>
       <c r="D150" t="n">
-        <v>1176.19</v>
+        <v>1176.188204933133</v>
       </c>
       <c r="E150" t="n">
-        <v>1189.85</v>
+        <v>1189.845195887567</v>
       </c>
       <c r="F150" t="n">
         <v>15483</v>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>01 AI</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
           <t>Yi License</t>
@@ -19654,13 +19602,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1181.82</v>
+        <v>1181.820159116466</v>
       </c>
       <c r="D151" t="n">
-        <v>1173.14</v>
+        <v>1173.137711374835</v>
       </c>
       <c r="E151" t="n">
-        <v>1190.5</v>
+        <v>1190.502606858096</v>
       </c>
       <c r="F151" t="n">
         <v>6638</v>
@@ -19805,22 +19753,18 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1181.72</v>
+        <v>1181.723418815407</v>
       </c>
       <c r="D152" t="n">
-        <v>1172.06</v>
+        <v>1172.058789174337</v>
       </c>
       <c r="E152" t="n">
-        <v>1191.39</v>
+        <v>1191.388048456477</v>
       </c>
       <c r="F152" t="n">
         <v>7968</v>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>OpenChat</t>
-        </is>
-      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -19876,22 +19820,18 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1181.6</v>
+        <v>1181.598762780185</v>
       </c>
       <c r="D153" t="n">
-        <v>1173.6</v>
+        <v>1173.602502340783</v>
       </c>
       <c r="E153" t="n">
-        <v>1189.59</v>
+        <v>1189.595023219587</v>
       </c>
       <c r="F153" t="n">
         <v>12637</v>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>OpenChat</t>
-        </is>
-      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -19947,13 +19887,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1181.32</v>
+        <v>1181.31816472218</v>
       </c>
       <c r="D154" t="n">
-        <v>1175.25</v>
+        <v>1175.245767803406</v>
       </c>
       <c r="E154" t="n">
-        <v>1187.39</v>
+        <v>1187.390561640954</v>
       </c>
       <c r="F154" t="n">
         <v>23893</v>
@@ -20098,22 +20038,18 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1178.85</v>
+        <v>1178.850444994937</v>
       </c>
       <c r="D155" t="n">
-        <v>1172.94</v>
+        <v>1172.936767037113</v>
       </c>
       <c r="E155" t="n">
-        <v>1184.76</v>
+        <v>1184.764122952761</v>
       </c>
       <c r="F155" t="n">
         <v>32832</v>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -20169,13 +20105,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1178.22</v>
+        <v>1178.220822867968</v>
       </c>
       <c r="D156" t="n">
-        <v>1167.03</v>
+        <v>1167.026424089671</v>
       </c>
       <c r="E156" t="n">
-        <v>1189.42</v>
+        <v>1189.415221646264</v>
       </c>
       <c r="F156" t="n">
         <v>3188</v>
@@ -20320,22 +20256,18 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1176.88</v>
+        <v>1176.879879675181</v>
       </c>
       <c r="D157" t="n">
-        <v>1167.07</v>
+        <v>1167.069275432436</v>
       </c>
       <c r="E157" t="n">
-        <v>1186.69</v>
+        <v>1186.690483917927</v>
       </c>
       <c r="F157" t="n">
         <v>6535</v>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>AllenAI/UW</t>
-        </is>
-      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
           <t>AI2 ImpACT Low-risk</t>
@@ -20471,22 +20403,18 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1174.68</v>
+        <v>1174.676128872726</v>
       </c>
       <c r="D158" t="n">
-        <v>1164.27</v>
+        <v>1164.265969699025</v>
       </c>
       <c r="E158" t="n">
-        <v>1185.09</v>
+        <v>1185.086288046427</v>
       </c>
       <c r="F158" t="n">
         <v>5006</v>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>NousResearch</t>
-        </is>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -20622,22 +20550,18 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1171.95</v>
+        <v>1171.946087394879</v>
       </c>
       <c r="D159" t="n">
-        <v>1165.74</v>
+        <v>1165.741847072756</v>
       </c>
       <c r="E159" t="n">
-        <v>1178.15</v>
+        <v>1178.150327717003</v>
       </c>
       <c r="F159" t="n">
         <v>22479</v>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>LMSYS</t>
-        </is>
-      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
           <t>Non-commercial</t>
@@ -20773,22 +20697,18 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1170.5</v>
+        <v>1170.504695883594</v>
       </c>
       <c r="D160" t="n">
-        <v>1163.1</v>
+        <v>1163.097071907669</v>
       </c>
       <c r="E160" t="n">
-        <v>1177.91</v>
+        <v>1177.91231985952</v>
       </c>
       <c r="F160" t="n">
         <v>16056</v>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Nexusflow</t>
-        </is>
-      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -20924,13 +20844,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1170.24</v>
+        <v>1170.235104774819</v>
       </c>
       <c r="D161" t="n">
-        <v>1164.32</v>
+        <v>1164.317553471013</v>
       </c>
       <c r="E161" t="n">
-        <v>1176.15</v>
+        <v>1176.152656078626</v>
       </c>
       <c r="F161" t="n">
         <v>17766</v>
@@ -21075,13 +20995,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1169.88</v>
+        <v>1169.882439219678</v>
       </c>
       <c r="D162" t="n">
-        <v>1164.38</v>
+        <v>1164.381823463686</v>
       </c>
       <c r="E162" t="n">
-        <v>1175.38</v>
+        <v>1175.383054975669</v>
       </c>
       <c r="F162" t="n">
         <v>38492</v>
@@ -21226,22 +21146,18 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1166.57</v>
+        <v>1166.573637579728</v>
       </c>
       <c r="D163" t="n">
-        <v>1158.51</v>
+        <v>1158.508289621256</v>
       </c>
       <c r="E163" t="n">
-        <v>1174.64</v>
+        <v>1174.638985538199</v>
       </c>
       <c r="F163" t="n">
         <v>10224</v>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>UC Berkeley</t>
-        </is>
-      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
           <t>CC-BY-NC-4.0</t>
@@ -21377,13 +21293,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1166.08</v>
+        <v>1166.08215149852</v>
       </c>
       <c r="D164" t="n">
-        <v>1158.38</v>
+        <v>1158.378148591672</v>
       </c>
       <c r="E164" t="n">
-        <v>1173.79</v>
+        <v>1173.786154405367</v>
       </c>
       <c r="F164" t="n">
         <v>7936</v>
@@ -21528,22 +21444,18 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1163.7</v>
+        <v>1163.704398805056</v>
       </c>
       <c r="D165" t="n">
-        <v>1151.79</v>
+        <v>1151.786257345735</v>
       </c>
       <c r="E165" t="n">
-        <v>1175.62</v>
+        <v>1175.622540264377</v>
       </c>
       <c r="F165" t="n">
         <v>3777</v>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>NousResearch</t>
-        </is>
-      </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -21679,13 +21591,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1155.53</v>
+        <v>1155.53309364839</v>
       </c>
       <c r="D166" t="n">
-        <v>1147.14</v>
+        <v>1147.144149258665</v>
       </c>
       <c r="E166" t="n">
-        <v>1163.92</v>
+        <v>1163.922038038114</v>
       </c>
       <c r="F166" t="n">
         <v>6837</v>
@@ -21830,13 +21742,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1154.77</v>
+        <v>1154.765864950356</v>
       </c>
       <c r="D167" t="n">
-        <v>1143.27</v>
+        <v>1143.272660234482</v>
       </c>
       <c r="E167" t="n">
-        <v>1166.26</v>
+        <v>1166.259069666231</v>
       </c>
       <c r="F167" t="n">
         <v>3231</v>
@@ -21981,13 +21893,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1153.92</v>
+        <v>1153.924143134825</v>
       </c>
       <c r="D168" t="n">
-        <v>1141.32</v>
+        <v>1141.323023272286</v>
       </c>
       <c r="E168" t="n">
-        <v>1166.53</v>
+        <v>1166.525262997363</v>
       </c>
       <c r="F168" t="n">
         <v>3585</v>
@@ -22132,22 +22044,18 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1151.41</v>
+        <v>1151.412882809647</v>
       </c>
       <c r="D169" t="n">
-        <v>1138.24</v>
+        <v>1138.236839186842</v>
       </c>
       <c r="E169" t="n">
-        <v>1164.59</v>
+        <v>1164.588926432452</v>
       </c>
       <c r="F169" t="n">
         <v>4155</v>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Upstage AI</t>
-        </is>
-      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
           <t>CC-BY-NC-4.0</t>
@@ -22283,22 +22191,18 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1151.23</v>
+        <v>1151.226000154089</v>
       </c>
       <c r="D170" t="n">
-        <v>1135.89</v>
+        <v>1135.88567978101</v>
       </c>
       <c r="E170" t="n">
-        <v>1166.57</v>
+        <v>1166.566320527167</v>
       </c>
       <c r="F170" t="n">
         <v>1679</v>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Cognitive Computations</t>
-        </is>
-      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -22434,22 +22338,18 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1149.51</v>
+        <v>1149.513071381869</v>
       </c>
       <c r="D171" t="n">
-        <v>1137.26</v>
+        <v>1137.255427707771</v>
       </c>
       <c r="E171" t="n">
-        <v>1161.77</v>
+        <v>1161.770715055968</v>
       </c>
       <c r="F171" t="n">
         <v>2572</v>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>MosaicML</t>
-        </is>
-      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
           <t>CC-BY-NC-SA-4.0</t>
@@ -22585,13 +22485,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1148.55</v>
+        <v>1148.553951960516</v>
       </c>
       <c r="D172" t="n">
-        <v>1141.9</v>
+        <v>1141.901529062426</v>
       </c>
       <c r="E172" t="n">
-        <v>1155.21</v>
+        <v>1155.206374858605</v>
       </c>
       <c r="F172" t="n">
         <v>19402</v>
@@ -22736,13 +22636,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1148.45</v>
+        <v>1148.452695942355</v>
       </c>
       <c r="D173" t="n">
-        <v>1139.22</v>
+        <v>1139.219359480531</v>
       </c>
       <c r="E173" t="n">
-        <v>1157.69</v>
+        <v>1157.68603240418</v>
       </c>
       <c r="F173" t="n">
         <v>7044</v>
@@ -22887,22 +22787,18 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1146.67</v>
+        <v>1146.66685933658</v>
       </c>
       <c r="D174" t="n">
-        <v>1129.6</v>
+        <v>1129.596166951592</v>
       </c>
       <c r="E174" t="n">
-        <v>1163.74</v>
+        <v>1163.737551721568</v>
       </c>
       <c r="F174" t="n">
         <v>1295</v>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>TII</t>
-        </is>
-      </c>
+      <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
           <t>Falcon-180B TII License</t>
@@ -23038,13 +22934,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1143.01</v>
+        <v>1143.014124997003</v>
       </c>
       <c r="D175" t="n">
-        <v>1133.13</v>
+        <v>1133.125535134779</v>
       </c>
       <c r="E175" t="n">
-        <v>1152.9</v>
+        <v>1152.902714859227</v>
       </c>
       <c r="F175" t="n">
         <v>4737</v>
@@ -23189,13 +23085,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1142.26</v>
+        <v>1142.259690898371</v>
       </c>
       <c r="D176" t="n">
-        <v>1135.82</v>
+        <v>1135.820058164972</v>
       </c>
       <c r="E176" t="n">
-        <v>1148.7</v>
+        <v>1148.69932363177</v>
       </c>
       <c r="F176" t="n">
         <v>12297</v>
@@ -23340,13 +23236,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1140.65</v>
+        <v>1140.646310585229</v>
       </c>
       <c r="D177" t="n">
-        <v>1133.92</v>
+        <v>1133.920881018855</v>
       </c>
       <c r="E177" t="n">
-        <v>1147.37</v>
+        <v>1147.371740151604</v>
       </c>
       <c r="F177" t="n">
         <v>19174</v>
@@ -23491,22 +23387,18 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1140.29</v>
+        <v>1140.292985107224</v>
       </c>
       <c r="D178" t="n">
-        <v>1133.59</v>
+        <v>1133.590438552854</v>
       </c>
       <c r="E178" t="n">
-        <v>1147</v>
+        <v>1146.995531661594</v>
       </c>
       <c r="F178" t="n">
         <v>19367</v>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>LMSYS</t>
-        </is>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
           <t>Llama 2 Community</t>
@@ -23642,13 +23534,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1138</v>
+        <v>1138.003446266433</v>
       </c>
       <c r="D179" t="n">
-        <v>1127.06</v>
+        <v>1127.055861766484</v>
       </c>
       <c r="E179" t="n">
-        <v>1148.95</v>
+        <v>1148.951030766381</v>
       </c>
       <c r="F179" t="n">
         <v>4964</v>
@@ -23793,13 +23685,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1136.6</v>
+        <v>1136.604583217163</v>
       </c>
       <c r="D180" t="n">
-        <v>1127.11</v>
+        <v>1127.113183591854</v>
       </c>
       <c r="E180" t="n">
-        <v>1146.1</v>
+        <v>1146.095982842472</v>
       </c>
       <c r="F180" t="n">
         <v>8925</v>
@@ -23944,13 +23836,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1135.82</v>
+        <v>1135.818506454868</v>
       </c>
       <c r="D181" t="n">
-        <v>1126.93</v>
+        <v>1126.925489280742</v>
       </c>
       <c r="E181" t="n">
-        <v>1144.71</v>
+        <v>1144.711523628994</v>
       </c>
       <c r="F181" t="n">
         <v>7366</v>
@@ -24095,22 +23987,18 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1129.95</v>
+        <v>1129.947223028809</v>
       </c>
       <c r="D182" t="n">
-        <v>1121.11</v>
+        <v>1121.113798196514</v>
       </c>
       <c r="E182" t="n">
-        <v>1138.78</v>
+        <v>1138.780647861104</v>
       </c>
       <c r="F182" t="n">
         <v>11118</v>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>HuggingFace</t>
-        </is>
-      </c>
+      <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
           <t>MIT</t>
@@ -24246,13 +24134,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1128.65</v>
+        <v>1128.652598737695</v>
       </c>
       <c r="D183" t="n">
-        <v>1121.23</v>
+        <v>1121.227773296898</v>
       </c>
       <c r="E183" t="n">
-        <v>1136.08</v>
+        <v>1136.077424178492</v>
       </c>
       <c r="F183" t="n">
         <v>20685</v>
@@ -24397,13 +24285,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1127.39</v>
+        <v>1127.386420149625</v>
       </c>
       <c r="D184" t="n">
-        <v>1120.99</v>
+        <v>1120.987788614647</v>
       </c>
       <c r="E184" t="n">
-        <v>1133.79</v>
+        <v>1133.785051684602</v>
       </c>
       <c r="F184" t="n">
         <v>20118</v>
@@ -24548,22 +24436,18 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1126.42</v>
+        <v>1126.415937652052</v>
       </c>
       <c r="D185" t="n">
-        <v>1114.31</v>
+        <v>1114.308200390894</v>
       </c>
       <c r="E185" t="n">
-        <v>1138.52</v>
+        <v>1138.523674913211</v>
       </c>
       <c r="F185" t="n">
         <v>2921</v>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>UW</t>
-        </is>
-      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
           <t>Non-commercial</t>
@@ -24699,22 +24583,18 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1125.95</v>
+        <v>1125.949330538368</v>
       </c>
       <c r="D186" t="n">
-        <v>1110.34</v>
+        <v>1110.335459269238</v>
       </c>
       <c r="E186" t="n">
-        <v>1141.56</v>
+        <v>1141.563201807498</v>
       </c>
       <c r="F186" t="n">
         <v>1785</v>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>HuggingFace</t>
-        </is>
-      </c>
+      <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
           <t>MIT</t>
@@ -24850,22 +24730,18 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1120.36</v>
+        <v>1120.358988613759</v>
       </c>
       <c r="D187" t="n">
-        <v>1109.38</v>
+        <v>1109.377239940026</v>
       </c>
       <c r="E187" t="n">
-        <v>1131.34</v>
+        <v>1131.340737287492</v>
       </c>
       <c r="F187" t="n">
         <v>5182</v>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Together AI</t>
-        </is>
-      </c>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -25001,13 +24877,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1118.35</v>
+        <v>1118.345173417529</v>
       </c>
       <c r="D188" t="n">
-        <v>1100.19</v>
+        <v>1100.193629424732</v>
       </c>
       <c r="E188" t="n">
-        <v>1136.5</v>
+        <v>1136.496717410326</v>
       </c>
       <c r="F188" t="n">
         <v>1143</v>
@@ -25152,13 +25028,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1115.29</v>
+        <v>1115.290489185656</v>
       </c>
       <c r="D189" t="n">
-        <v>1107.56</v>
+        <v>1107.560005128725</v>
       </c>
       <c r="E189" t="n">
-        <v>1123.02</v>
+        <v>1123.020973242586</v>
       </c>
       <c r="F189" t="n">
         <v>10854</v>
@@ -25303,22 +25179,18 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1114.04</v>
+        <v>1114.04140244203</v>
       </c>
       <c r="D190" t="n">
-        <v>1104.9</v>
+        <v>1104.895133810278</v>
       </c>
       <c r="E190" t="n">
-        <v>1123.19</v>
+        <v>1123.187671073782</v>
       </c>
       <c r="F190" t="n">
         <v>6923</v>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>LMSYS</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
           <t>Llama 2 Community</t>
@@ -25454,22 +25326,18 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1113.68</v>
+        <v>1113.682560145976</v>
       </c>
       <c r="D191" t="n">
-        <v>1099.3</v>
+        <v>1099.301817389892</v>
       </c>
       <c r="E191" t="n">
-        <v>1128.06</v>
+        <v>1128.063302902059</v>
       </c>
       <c r="F191" t="n">
         <v>2199</v>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>HuggingFace</t>
-        </is>
-      </c>
+      <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -25605,13 +25473,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1110.46</v>
+        <v>1110.460213479393</v>
       </c>
       <c r="D192" t="n">
-        <v>1102.58</v>
+        <v>1102.57755552957</v>
       </c>
       <c r="E192" t="n">
-        <v>1118.34</v>
+        <v>1118.342871429216</v>
       </c>
       <c r="F192" t="n">
         <v>8045</v>
@@ -25756,13 +25624,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1109.04</v>
+        <v>1109.043230272848</v>
       </c>
       <c r="D193" t="n">
-        <v>1099.76</v>
+        <v>1099.758230021275</v>
       </c>
       <c r="E193" t="n">
-        <v>1118.33</v>
+        <v>1118.32823052442</v>
       </c>
       <c r="F193" t="n">
         <v>8977</v>
@@ -25907,13 +25775,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1107.19</v>
+        <v>1107.194490206484</v>
       </c>
       <c r="D194" t="n">
-        <v>1100.14</v>
+        <v>1100.140940638814</v>
       </c>
       <c r="E194" t="n">
-        <v>1114.25</v>
+        <v>1114.248039774155</v>
       </c>
       <c r="F194" t="n">
         <v>14148</v>
@@ -26058,13 +25926,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1092.35</v>
+        <v>1092.349609266924</v>
       </c>
       <c r="D195" t="n">
-        <v>1080.86</v>
+        <v>1080.859811695683</v>
       </c>
       <c r="E195" t="n">
-        <v>1103.84</v>
+        <v>1103.839406838165</v>
       </c>
       <c r="F195" t="n">
         <v>4780</v>
@@ -26209,13 +26077,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1089.69</v>
+        <v>1089.688550379331</v>
       </c>
       <c r="D196" t="n">
-        <v>1080.35</v>
+        <v>1080.35089119126</v>
       </c>
       <c r="E196" t="n">
-        <v>1099.03</v>
+        <v>1099.026209567402</v>
       </c>
       <c r="F196" t="n">
         <v>7597</v>
@@ -26360,13 +26228,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1073.13</v>
+        <v>1073.134544956117</v>
       </c>
       <c r="D197" t="n">
-        <v>1061.97</v>
+        <v>1061.97068050075</v>
       </c>
       <c r="E197" t="n">
-        <v>1084.3</v>
+        <v>1084.298409411484</v>
       </c>
       <c r="F197" t="n">
         <v>6328</v>
@@ -26511,22 +26379,18 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1069.74</v>
+        <v>1069.736203911552</v>
       </c>
       <c r="D198" t="n">
-        <v>1059.85</v>
+        <v>1059.847003983901</v>
       </c>
       <c r="E198" t="n">
-        <v>1079.63</v>
+        <v>1079.625403839202</v>
       </c>
       <c r="F198" t="n">
         <v>6965</v>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>UC Berkeley</t>
-        </is>
-      </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
           <t>Non-commercial</t>
@@ -26662,22 +26526,18 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1068</v>
+        <v>1067.999857506439</v>
       </c>
       <c r="D199" t="n">
-        <v>1056.54</v>
+        <v>1056.538279664763</v>
       </c>
       <c r="E199" t="n">
-        <v>1079.46</v>
+        <v>1079.461435348116</v>
       </c>
       <c r="F199" t="n">
         <v>5745</v>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Stanford</t>
-        </is>
-      </c>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
           <t>Non-commercial</t>
@@ -26813,22 +26673,18 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1065.96</v>
+        <v>1065.958099914104</v>
       </c>
       <c r="D200" t="n">
-        <v>1050.74</v>
+        <v>1050.740473985035</v>
       </c>
       <c r="E200" t="n">
-        <v>1081.18</v>
+        <v>1081.175725843173</v>
       </c>
       <c r="F200" t="n">
         <v>1743</v>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Nomic AI</t>
-        </is>
-      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
           <t>Non-commercial</t>
@@ -26964,22 +26820,18 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1061.75</v>
+        <v>1061.753767290887</v>
       </c>
       <c r="D201" t="n">
-        <v>1049.78</v>
+        <v>1049.778442243619</v>
       </c>
       <c r="E201" t="n">
-        <v>1073.73</v>
+        <v>1073.729092338155</v>
       </c>
       <c r="F201" t="n">
         <v>3924</v>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>MosaicML</t>
-        </is>
-      </c>
+      <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
           <t>CC-BY-NC-SA-4.0</t>
@@ -27115,22 +26967,18 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1055.31</v>
+        <v>1055.314578995344</v>
       </c>
       <c r="D202" t="n">
-        <v>1043.65</v>
+        <v>1043.651117920881</v>
       </c>
       <c r="E202" t="n">
-        <v>1066.98</v>
+        <v>1066.978040069808</v>
       </c>
       <c r="F202" t="n">
         <v>4658</v>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Tsinghua</t>
-        </is>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -27266,22 +27114,18 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1040.92</v>
+        <v>1040.92257637995</v>
       </c>
       <c r="D203" t="n">
-        <v>1029.53</v>
+        <v>1029.531587089981</v>
       </c>
       <c r="E203" t="n">
-        <v>1052.31</v>
+        <v>1052.313565669919</v>
       </c>
       <c r="F203" t="n">
         <v>4845</v>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>RWKV</t>
-        </is>
-      </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -27417,22 +27261,18 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1023.49</v>
+        <v>1023.493469879567</v>
       </c>
       <c r="D204" t="n">
-        <v>1009.9</v>
+        <v>1009.902673223833</v>
       </c>
       <c r="E204" t="n">
-        <v>1037.08</v>
+        <v>1037.084266535301</v>
       </c>
       <c r="F204" t="n">
         <v>2658</v>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Tsinghua</t>
-        </is>
-      </c>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
           <t>Apache-2.0</t>
@@ -27568,22 +27408,18 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1021.88</v>
+        <v>1021.878819467545</v>
       </c>
       <c r="D205" t="n">
-        <v>1011.01</v>
+        <v>1011.008609681241</v>
       </c>
       <c r="E205" t="n">
-        <v>1032.75</v>
+        <v>1032.749029253849</v>
       </c>
       <c r="F205" t="n">
         <v>6310</v>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>OpenAssistant</t>
-        </is>
-      </c>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -27719,22 +27555,18 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>994.726</v>
+        <v>994.7262750491491</v>
       </c>
       <c r="D206" t="n">
-        <v>982.1609999999999</v>
+        <v>982.1605534986397</v>
       </c>
       <c r="E206" t="n">
-        <v>1007.29</v>
+        <v>1007.291996599658</v>
       </c>
       <c r="F206" t="n">
         <v>4914</v>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Tsinghua</t>
-        </is>
-      </c>
+      <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
           <t>Non-commercial</t>
@@ -27870,22 +27702,18 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>991.097</v>
+        <v>991.0971098063198</v>
       </c>
       <c r="D207" t="n">
-        <v>978.725</v>
+        <v>978.7253999478132</v>
       </c>
       <c r="E207" t="n">
-        <v>1003.47</v>
+        <v>1003.468819664826</v>
       </c>
       <c r="F207" t="n">
         <v>4203</v>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>LMSYS</t>
-        </is>
-      </c>
+      <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
@@ -28021,22 +27849,18 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>980.422</v>
+        <v>980.4215597036718</v>
       </c>
       <c r="D208" t="n">
-        <v>966.893</v>
+        <v>966.8928360947746</v>
       </c>
       <c r="E208" t="n">
-        <v>993.95</v>
+        <v>993.9502833125689</v>
       </c>
       <c r="F208" t="n">
         <v>3412</v>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
           <t>MIT</t>
@@ -28172,13 +27996,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>972.927</v>
+        <v>972.9273596435232</v>
       </c>
       <c r="D209" t="n">
-        <v>957.131</v>
+        <v>957.1306617315804</v>
       </c>
       <c r="E209" t="n">
-        <v>988.724</v>
+        <v>988.7240575554658</v>
       </c>
       <c r="F209" t="n">
         <v>2391</v>
@@ -28323,22 +28147,18 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>951.9690000000001</v>
+        <v>951.9693471697101</v>
       </c>
       <c r="D210" t="n">
-        <v>939.241</v>
+        <v>939.2412351389871</v>
       </c>
       <c r="E210" t="n">
-        <v>964.697</v>
+        <v>964.6974592004333</v>
       </c>
       <c r="F210" t="n">
         <v>3287</v>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Stability AI</t>
-        </is>
-      </c>
+      <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
           <t>CC-BY-NC-SA-4.0</t>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1472.207675478944</v>
+        <v>1472.107858361179</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1467.259503206748</v>
+        <v>1467.327732108769</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1477.15584775114</v>
+        <v>1476.887984613589</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>22689</v>
+        <v>26549</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -742,24 +742,24 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>glm-5.2 (max)</t>
+          <t>mimo-v2.5-pro</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1468.658580360648</v>
+        <v>1466.040224970283</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1461.700522789307</v>
+        <v>1461.42118219284</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1475.61663793199</v>
+        <v>1470.659267747726</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9338</v>
+        <v>38175</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -813,24 +813,24 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>mimo-v2.5-pro</t>
+          <t>glm-5.2 (max)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1466.24229853447</v>
+        <v>1465.498606884602</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1461.514264591496</v>
+        <v>1459.067636032665</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1470.970332477445</v>
+        <v>1471.929577736539</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>34468</v>
+        <v>13442</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1461.368004535537</v>
+        <v>1461.74068977795</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1456.653506994239</v>
+        <v>1457.123847690291</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1466.082502076835</v>
+        <v>1466.35753186561</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>32657</v>
+        <v>35917</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1035,20 +1035,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>deepseek-v4-pro-thinking</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1457.076266023715</v>
+        <v>1456.7748009375</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1452.474482938546</v>
+        <v>1452.19334566606</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1461.678049108885</v>
+        <v>1461.356256208939</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>37116</v>
+        <v>39019</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1060,123 +1060,43 @@
           <t>MIT</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>3200</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>4000</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>1600</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG6" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -1190,16 +1110,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1456.978251729867</v>
+        <v>1456.661454797168</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1452.61003850587</v>
+        <v>1452.299195726941</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1461.346464953865</v>
+        <v>1461.023713867395</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>27897</v>
+        <v>27818</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1337,20 +1257,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-thinking</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1456.86314699372</v>
+        <v>1456.326754938983</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1452.173763555522</v>
+        <v>1451.820052683756</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1461.552530431919</v>
+        <v>1460.833457194211</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35108</v>
+        <v>41017</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1362,43 +1282,123 @@
           <t>MIT</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr"/>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr"/>
-      <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>3200</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH8" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1451.074153173372</v>
+        <v>1451.17487305221</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1443.474834437071</v>
+        <v>1443.571316585594</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1458.673471909673</v>
+        <v>1458.778429518825</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5898</v>
+        <v>5884</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1449.699550404222</v>
+        <v>1449.260080720811</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1446.029408814982</v>
+        <v>1445.636972805147</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1453.369691993463</v>
+        <v>1452.883188636474</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>55504</v>
+        <v>59062</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1446.543676554232</v>
+        <v>1445.323397002501</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1440.861099597588</v>
+        <v>1439.793942391817</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1452.226253510876</v>
+        <v>1450.852851613184</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>19761</v>
+        <v>23823</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1861,148 +1861,68 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>glm-4.7</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1442.970241764861</v>
+        <v>1442.510840959521</v>
       </c>
       <c r="D12" t="n">
-        <v>1439.129463961606</v>
+        <v>1436.414280989811</v>
       </c>
       <c r="E12" t="n">
-        <v>1446.811019568116</v>
+        <v>1448.607400929231</v>
       </c>
       <c r="F12" t="n">
-        <v>50832</v>
+        <v>12103</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>397</v>
-      </c>
-      <c r="J12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>794</v>
-      </c>
-      <c r="N12" t="n">
-        <v>992.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>397</v>
-      </c>
-      <c r="P12" t="n">
-        <v>496.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>248.1</v>
-      </c>
-      <c r="S12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF12" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG12" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2012,68 +1932,148 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1442.380797048279</v>
+        <v>1441.909896621309</v>
       </c>
       <c r="D13" t="n">
-        <v>1436.282240986469</v>
+        <v>1438.122835976131</v>
       </c>
       <c r="E13" t="n">
-        <v>1448.479353110089</v>
+        <v>1445.696957266486</v>
       </c>
       <c r="F13" t="n">
-        <v>12105</v>
+        <v>54262</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>397</v>
+      </c>
+      <c r="J13" t="n">
+        <v>17</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>794</v>
+      </c>
+      <c r="N13" t="n">
+        <v>992.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>397</v>
+      </c>
+      <c r="P13" t="n">
+        <v>496.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="S13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF13" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG13" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2083,148 +2083,68 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gemma-4-26b-a4b</t>
+          <t>deepseek-v4-flash-thinking</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1438.241586502369</v>
+        <v>1438.54808189884</v>
       </c>
       <c r="D14" t="n">
-        <v>1430.604704365156</v>
+        <v>1434.011317642549</v>
       </c>
       <c r="E14" t="n">
-        <v>1445.878468639583</v>
+        <v>1443.084846155132</v>
       </c>
       <c r="F14" t="n">
-        <v>5812</v>
+        <v>40631</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>26</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>52</v>
-      </c>
-      <c r="N14" t="n">
-        <v>65</v>
-      </c>
-      <c r="O14" t="n">
-        <v>26</v>
-      </c>
-      <c r="P14" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>13</v>
-      </c>
-      <c r="R14" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG14" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2234,68 +2154,148 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-thinking</t>
+          <t>gemma-4-26b-a4b</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1437.202172187637</v>
+        <v>1438.099482499473</v>
       </c>
       <c r="D15" t="n">
-        <v>1432.576431060379</v>
+        <v>1430.461506330393</v>
       </c>
       <c r="E15" t="n">
-        <v>1441.827913314894</v>
+        <v>1445.737458668552</v>
       </c>
       <c r="F15" t="n">
-        <v>36653</v>
+        <v>5806</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>26</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>52</v>
+      </c>
+      <c r="N15" t="n">
+        <v>65</v>
+      </c>
+      <c r="O15" t="n">
+        <v>26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>13</v>
+      </c>
+      <c r="R15" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG15" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1435.738691173074</v>
+        <v>1437.384736721623</v>
       </c>
       <c r="D16" t="n">
-        <v>1431.161944416463</v>
+        <v>1432.893829331606</v>
       </c>
       <c r="E16" t="n">
-        <v>1440.315437929685</v>
+        <v>1441.87564411164</v>
       </c>
       <c r="F16" t="n">
-        <v>36817</v>
+        <v>40831</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1433.180123300331</v>
+        <v>1433.77260907199</v>
       </c>
       <c r="D17" t="n">
-        <v>1428.506660048128</v>
+        <v>1429.199361892539</v>
       </c>
       <c r="E17" t="n">
-        <v>1437.853586552535</v>
+        <v>1438.345856251442</v>
       </c>
       <c r="F17" t="n">
-        <v>35255</v>
+        <v>39076</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1431.630087294944</v>
+        <v>1431.670876976295</v>
       </c>
       <c r="D18" t="n">
-        <v>1425.043897278806</v>
+        <v>1425.085664593789</v>
       </c>
       <c r="E18" t="n">
-        <v>1438.216277311083</v>
+        <v>1438.256089358802</v>
       </c>
       <c r="F18" t="n">
-        <v>8185</v>
+        <v>8179</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1429.899116212722</v>
+        <v>1429.914191972159</v>
       </c>
       <c r="D19" t="n">
-        <v>1426.73618673235</v>
+        <v>1426.755781009987</v>
       </c>
       <c r="E19" t="n">
-        <v>1433.062045693095</v>
+        <v>1433.072602934332</v>
       </c>
       <c r="F19" t="n">
-        <v>62069</v>
+        <v>62027</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1426.576527773178</v>
+        <v>1427.316632455381</v>
       </c>
       <c r="D20" t="n">
-        <v>1419.953545055774</v>
+        <v>1420.727599542166</v>
       </c>
       <c r="E20" t="n">
-        <v>1433.199510490583</v>
+        <v>1433.905665368596</v>
       </c>
       <c r="F20" t="n">
-        <v>10782</v>
+        <v>11052</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1425.350944473955</v>
+        <v>1425.33042964378</v>
       </c>
       <c r="D21" t="n">
-        <v>1421.430908835237</v>
+        <v>1421.411102254845</v>
       </c>
       <c r="E21" t="n">
-        <v>1429.270980112672</v>
+        <v>1429.249757032715</v>
       </c>
       <c r="F21" t="n">
-        <v>35637</v>
+        <v>35625</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1425.047995082568</v>
+        <v>1425.1691051298</v>
       </c>
       <c r="D22" t="n">
-        <v>1421.480068111602</v>
+        <v>1421.607387210666</v>
       </c>
       <c r="E22" t="n">
-        <v>1428.615922053535</v>
+        <v>1428.730823048934</v>
       </c>
       <c r="F22" t="n">
-        <v>47254</v>
+        <v>47243</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1424.741746523867</v>
+        <v>1424.798241490018</v>
       </c>
       <c r="D23" t="n">
-        <v>1418.189143507586</v>
+        <v>1418.244993934418</v>
       </c>
       <c r="E23" t="n">
-        <v>1431.294349540147</v>
+        <v>1431.351489045617</v>
       </c>
       <c r="F23" t="n">
-        <v>9071</v>
+        <v>9066</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1423.170615004773</v>
+        <v>1423.28720459721</v>
       </c>
       <c r="D24" t="n">
-        <v>1420.572516851911</v>
+        <v>1420.693118720603</v>
       </c>
       <c r="E24" t="n">
-        <v>1425.768713157634</v>
+        <v>1425.881290473817</v>
       </c>
       <c r="F24" t="n">
-        <v>97195</v>
+        <v>97160</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3264,68 +3264,148 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1423.137565951007</v>
+        <v>1423.090428562919</v>
       </c>
       <c r="D25" t="n">
-        <v>1419.480830152515</v>
+        <v>1415.995857165341</v>
       </c>
       <c r="E25" t="n">
-        <v>1426.794301749499</v>
+        <v>1430.184999960497</v>
       </c>
       <c r="F25" t="n">
-        <v>41062</v>
+        <v>9406</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>OpenMDW-1.1</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>550</v>
+      </c>
+      <c r="J25" t="n">
+        <v>55</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1100</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1375</v>
+      </c>
+      <c r="O25" t="n">
+        <v>550</v>
+      </c>
+      <c r="P25" t="n">
+        <v>687.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>275</v>
+      </c>
+      <c r="R25" t="n">
+        <v>343.8</v>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG25" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3335,20 +3415,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1422.959285486476</v>
+        <v>1423.061008350877</v>
       </c>
       <c r="D26" t="n">
-        <v>1416.554014403212</v>
+        <v>1419.408604929062</v>
       </c>
       <c r="E26" t="n">
-        <v>1429.364556569741</v>
+        <v>1426.713411772691</v>
       </c>
       <c r="F26" t="n">
-        <v>11921</v>
+        <v>41035</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3406,20 +3486,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>deepseek-r1-0528</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1422.228142916504</v>
+        <v>1422.853329192755</v>
       </c>
       <c r="D27" t="n">
-        <v>1416.56753178348</v>
+        <v>1416.449659184683</v>
       </c>
       <c r="E27" t="n">
-        <v>1427.888754049527</v>
+        <v>1429.256999200827</v>
       </c>
       <c r="F27" t="n">
-        <v>18457</v>
+        <v>11921</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3477,148 +3557,68 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
+          <t>deepseek-r1-0528</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1420.139317244397</v>
+        <v>1422.169290048358</v>
       </c>
       <c r="D28" t="n">
-        <v>1412.923166755144</v>
+        <v>1416.507742734381</v>
       </c>
       <c r="E28" t="n">
-        <v>1427.35546773365</v>
+        <v>1427.830837362336</v>
       </c>
       <c r="F28" t="n">
-        <v>8417</v>
+        <v>18452</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>OpenMDW-1.1</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>550</v>
-      </c>
-      <c r="J28" t="n">
-        <v>55</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>1100</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1375</v>
-      </c>
-      <c r="O28" t="n">
-        <v>550</v>
-      </c>
-      <c r="P28" t="n">
-        <v>687.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>275</v>
-      </c>
-      <c r="R28" t="n">
-        <v>343.8</v>
-      </c>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG28" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3628,68 +3628,148 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>kimi-k2-0905-preview</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1418.131513103546</v>
+        <v>1417.966472186844</v>
       </c>
       <c r="D29" t="n">
-        <v>1408.148778410814</v>
+        <v>1411.471074641325</v>
       </c>
       <c r="E29" t="n">
-        <v>1428.114247796279</v>
+        <v>1424.461869732363</v>
       </c>
       <c r="F29" t="n">
-        <v>3459</v>
+        <v>11774</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>32</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>500</v>
+      </c>
+      <c r="R29" t="n">
+        <v>625</v>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3699,148 +3779,68 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1418.05381106982</v>
+        <v>1417.841643399433</v>
       </c>
       <c r="D30" t="n">
-        <v>1411.558838454996</v>
+        <v>1407.859555967257</v>
       </c>
       <c r="E30" t="n">
-        <v>1424.548783684645</v>
+        <v>1427.823730831609</v>
       </c>
       <c r="F30" t="n">
-        <v>11772</v>
+        <v>3458</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J30" t="n">
-        <v>32</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>500</v>
-      </c>
-      <c r="R30" t="n">
-        <v>625</v>
-      </c>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG30" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3850,148 +3850,68 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1417.447098546351</v>
+        <v>1417.605435456909</v>
       </c>
       <c r="D31" t="n">
-        <v>1412.587985969517</v>
+        <v>1411.595073027615</v>
       </c>
       <c r="E31" t="n">
-        <v>1422.306211123185</v>
+        <v>1423.615797886202</v>
       </c>
       <c r="F31" t="n">
-        <v>27627</v>
+        <v>14945</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J31" t="n">
-        <v>32</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>500</v>
-      </c>
-      <c r="R31" t="n">
-        <v>625</v>
-      </c>
-      <c r="S31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG31" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4001,68 +3921,148 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1417.405847331528</v>
+        <v>1417.536146206947</v>
       </c>
       <c r="D32" t="n">
-        <v>1411.396362758647</v>
+        <v>1412.675015474713</v>
       </c>
       <c r="E32" t="n">
-        <v>1423.41533190441</v>
+        <v>1422.39727693918</v>
       </c>
       <c r="F32" t="n">
-        <v>14954</v>
+        <v>27613</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>32</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>500</v>
+      </c>
+      <c r="R32" t="n">
+        <v>625</v>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4072,68 +4072,148 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1417.123984658945</v>
+        <v>1417.24172940703</v>
       </c>
       <c r="D33" t="n">
-        <v>1410.514662679633</v>
+        <v>1412.845736188534</v>
       </c>
       <c r="E33" t="n">
-        <v>1423.733306638256</v>
+        <v>1421.637722625526</v>
       </c>
       <c r="F33" t="n">
-        <v>11731</v>
+        <v>28517</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>122</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>244</v>
+      </c>
+      <c r="N33" t="n">
+        <v>305</v>
+      </c>
+      <c r="O33" t="n">
+        <v>122</v>
+      </c>
+      <c r="P33" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>61</v>
+      </c>
+      <c r="R33" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -4143,148 +4223,68 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1417.05522082422</v>
+        <v>1417.128695579876</v>
       </c>
       <c r="D34" t="n">
-        <v>1412.655641664229</v>
+        <v>1410.518531635322</v>
       </c>
       <c r="E34" t="n">
-        <v>1421.45479998421</v>
+        <v>1423.738859524429</v>
       </c>
       <c r="F34" t="n">
-        <v>28563</v>
+        <v>11728</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>122</v>
-      </c>
-      <c r="J34" t="n">
-        <v>10</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>244</v>
-      </c>
-      <c r="N34" t="n">
-        <v>305</v>
-      </c>
-      <c r="O34" t="n">
-        <v>122</v>
-      </c>
-      <c r="P34" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>61</v>
-      </c>
-      <c r="R34" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4298,16 +4298,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1416.821308531066</v>
+        <v>1416.384879951619</v>
       </c>
       <c r="D35" t="n">
-        <v>1412.482245299455</v>
+        <v>1412.118860914579</v>
       </c>
       <c r="E35" t="n">
-        <v>1421.160371762677</v>
+        <v>1420.650898988658</v>
       </c>
       <c r="F35" t="n">
-        <v>42368</v>
+        <v>46070</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4365,68 +4365,148 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1415.705125997306</v>
+        <v>1416.199923166446</v>
       </c>
       <c r="D36" t="n">
-        <v>1406.077511946972</v>
+        <v>1412.678264229766</v>
       </c>
       <c r="E36" t="n">
-        <v>1425.33274004764</v>
+        <v>1419.721582103127</v>
       </c>
       <c r="F36" t="n">
-        <v>3691</v>
+        <v>47096</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>675</v>
+      </c>
+      <c r="J36" t="n">
+        <v>41</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>1350</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1687.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>675</v>
+      </c>
+      <c r="P36" t="n">
+        <v>843.8</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>421.9</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4436,148 +4516,68 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1415.658500889831</v>
+        <v>1415.489643325521</v>
       </c>
       <c r="D37" t="n">
-        <v>1412.084903180666</v>
+        <v>1405.866545649409</v>
       </c>
       <c r="E37" t="n">
-        <v>1419.232098598996</v>
+        <v>1425.112741001634</v>
       </c>
       <c r="F37" t="n">
-        <v>44086</v>
+        <v>3692</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>675</v>
-      </c>
-      <c r="J37" t="n">
-        <v>41</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>1350</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1687.5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>675</v>
-      </c>
-      <c r="P37" t="n">
-        <v>843.8</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>337.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>421.9</v>
-      </c>
-      <c r="S37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG37" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4591,16 +4591,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1415.444854660351</v>
+        <v>1415.427622338126</v>
       </c>
       <c r="D38" t="n">
-        <v>1408.95982483211</v>
+        <v>1408.942943392297</v>
       </c>
       <c r="E38" t="n">
-        <v>1421.929884488592</v>
+        <v>1421.912301283955</v>
       </c>
       <c r="F38" t="n">
-        <v>11501</v>
+        <v>11499</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4742,16 +4742,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1412.912550124611</v>
+        <v>1412.748916492167</v>
       </c>
       <c r="D39" t="n">
-        <v>1405.375577861305</v>
+        <v>1405.205493699792</v>
       </c>
       <c r="E39" t="n">
-        <v>1420.449522387916</v>
+        <v>1420.292339284542</v>
       </c>
       <c r="F39" t="n">
-        <v>6674</v>
+        <v>6654</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4813,16 +4813,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1410.911532500788</v>
+        <v>1410.971205932208</v>
       </c>
       <c r="D40" t="n">
-        <v>1406.029601407999</v>
+        <v>1406.088050835912</v>
       </c>
       <c r="E40" t="n">
-        <v>1415.793463593578</v>
+        <v>1415.854361028505</v>
       </c>
       <c r="F40" t="n">
-        <v>24293</v>
+        <v>24288</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4964,16 +4964,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1408.822568786353</v>
+        <v>1408.653739846502</v>
       </c>
       <c r="D41" t="n">
-        <v>1404.391183679576</v>
+        <v>1404.223858667993</v>
       </c>
       <c r="E41" t="n">
-        <v>1413.253953893131</v>
+        <v>1413.08362102501</v>
       </c>
       <c r="F41" t="n">
-        <v>27408</v>
+        <v>27358</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1403.173847755168</v>
+        <v>1403.181974517327</v>
       </c>
       <c r="D42" t="n">
-        <v>1398.67350991818</v>
+        <v>1398.680103240969</v>
       </c>
       <c r="E42" t="n">
-        <v>1407.674185592156</v>
+        <v>1407.683845793686</v>
       </c>
       <c r="F42" t="n">
-        <v>38191</v>
+        <v>38184</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5266,16 +5266,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1401.487365892205</v>
+        <v>1401.465400756505</v>
       </c>
       <c r="D43" t="n">
-        <v>1396.716151096404</v>
+        <v>1396.691414729593</v>
       </c>
       <c r="E43" t="n">
-        <v>1406.258580688006</v>
+        <v>1406.239386783417</v>
       </c>
       <c r="F43" t="n">
-        <v>22865</v>
+        <v>22855</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5417,16 +5417,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1401.097051746745</v>
+        <v>1401.281523431795</v>
       </c>
       <c r="D44" t="n">
-        <v>1394.727128429446</v>
+        <v>1394.91415679475</v>
       </c>
       <c r="E44" t="n">
-        <v>1407.466975064043</v>
+        <v>1407.64889006884</v>
       </c>
       <c r="F44" t="n">
-        <v>11380</v>
+        <v>11385</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5568,16 +5568,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1399.175687136281</v>
+        <v>1399.169496884051</v>
       </c>
       <c r="D45" t="n">
-        <v>1392.642626014682</v>
+        <v>1392.636243366153</v>
       </c>
       <c r="E45" t="n">
-        <v>1405.70874825788</v>
+        <v>1405.702750401949</v>
       </c>
       <c r="F45" t="n">
-        <v>8991</v>
+        <v>8988</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1398.080881265658</v>
+        <v>1398.169620947378</v>
       </c>
       <c r="D46" t="n">
-        <v>1393.20501218071</v>
+        <v>1393.291125231924</v>
       </c>
       <c r="E46" t="n">
-        <v>1402.956750350605</v>
+        <v>1403.048116662831</v>
       </c>
       <c r="F46" t="n">
         <v>18524</v>
@@ -5870,16 +5870,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1395.722474643064</v>
+        <v>1395.736004486441</v>
       </c>
       <c r="D47" t="n">
-        <v>1388.932869923728</v>
+        <v>1388.947724143276</v>
       </c>
       <c r="E47" t="n">
-        <v>1402.5120793624</v>
+        <v>1402.524284829607</v>
       </c>
       <c r="F47" t="n">
-        <v>7939</v>
+        <v>7943</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6017,36 +6017,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1395.635260537728</v>
+        <v>1395.647881213153</v>
       </c>
       <c r="D48" t="n">
-        <v>1391.281168288014</v>
+        <v>1391.774745932824</v>
       </c>
       <c r="E48" t="n">
-        <v>1399.989352787441</v>
+        <v>1399.521016493482</v>
       </c>
       <c r="F48" t="n">
-        <v>29211</v>
+        <v>45486</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>35</v>
+        <v>671</v>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6055,40 +6055,40 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>70</v>
+        <v>1342</v>
       </c>
       <c r="N48" t="n">
-        <v>87.5</v>
+        <v>1677.5</v>
       </c>
       <c r="O48" t="n">
-        <v>35</v>
+        <v>671</v>
       </c>
       <c r="P48" t="n">
-        <v>43.8</v>
+        <v>838.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>17.5</v>
+        <v>335.5</v>
       </c>
       <c r="R48" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="S48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>419.4</v>
+      </c>
+      <c r="S48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V48" s="5" t="inlineStr">
@@ -6096,69 +6096,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6168,36 +6168,36 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1395.559211450224</v>
+        <v>1395.560088899896</v>
       </c>
       <c r="D49" t="n">
-        <v>1391.687948359546</v>
+        <v>1391.215080317346</v>
       </c>
       <c r="E49" t="n">
-        <v>1399.430474540903</v>
+        <v>1399.905097482447</v>
       </c>
       <c r="F49" t="n">
-        <v>45491</v>
+        <v>29184</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="J49" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6206,40 +6206,40 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1342</v>
+        <v>70</v>
       </c>
       <c r="N49" t="n">
-        <v>1677.5</v>
+        <v>87.5</v>
       </c>
       <c r="O49" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="P49" t="n">
-        <v>838.8</v>
+        <v>43.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>335.5</v>
+        <v>17.5</v>
       </c>
       <c r="R49" t="n">
-        <v>419.4</v>
-      </c>
-      <c r="S49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>21.9</v>
+      </c>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V49" s="5" t="inlineStr">
@@ -6247,69 +6247,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG49" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG49" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -6323,16 +6323,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1394.860818771535</v>
+        <v>1395.153586526362</v>
       </c>
       <c r="D50" t="n">
-        <v>1391.101733121227</v>
+        <v>1391.419846506986</v>
       </c>
       <c r="E50" t="n">
-        <v>1398.619904421843</v>
+        <v>1398.887326545737</v>
       </c>
       <c r="F50" t="n">
-        <v>52274</v>
+        <v>53440</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6394,16 +6394,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1392.965679388187</v>
+        <v>1393.063916650281</v>
       </c>
       <c r="D51" t="n">
-        <v>1389.392549894614</v>
+        <v>1389.495338462046</v>
       </c>
       <c r="E51" t="n">
-        <v>1396.538808881761</v>
+        <v>1396.632494838516</v>
       </c>
       <c r="F51" t="n">
-        <v>46660</v>
+        <v>46619</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6465,16 +6465,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1390.581863305857</v>
+        <v>1390.551490069046</v>
       </c>
       <c r="D52" t="n">
-        <v>1386.574716715496</v>
+        <v>1386.551017879804</v>
       </c>
       <c r="E52" t="n">
-        <v>1394.589009896218</v>
+        <v>1394.551962258288</v>
       </c>
       <c r="F52" t="n">
-        <v>41241</v>
+        <v>41172</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6536,16 +6536,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1387.629520020103</v>
+        <v>1387.673635594953</v>
       </c>
       <c r="D53" t="n">
-        <v>1382.681028619063</v>
+        <v>1382.723742339233</v>
       </c>
       <c r="E53" t="n">
-        <v>1392.578011421143</v>
+        <v>1392.623528850673</v>
       </c>
       <c r="F53" t="n">
-        <v>25709</v>
+        <v>25692</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6687,16 +6687,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1387.134028765115</v>
+        <v>1387.146540240597</v>
       </c>
       <c r="D54" t="n">
-        <v>1380.884562006627</v>
+        <v>1380.899910006544</v>
       </c>
       <c r="E54" t="n">
-        <v>1393.383495523602</v>
+        <v>1393.393170474651</v>
       </c>
       <c r="F54" t="n">
-        <v>10955</v>
+        <v>10947</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6758,16 +6758,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1384.392127507076</v>
+        <v>1384.266715272995</v>
       </c>
       <c r="D55" t="n">
-        <v>1379.161432335864</v>
+        <v>1379.039334851279</v>
       </c>
       <c r="E55" t="n">
-        <v>1389.622822678288</v>
+        <v>1389.494095694711</v>
       </c>
       <c r="F55" t="n">
-        <v>17112</v>
+        <v>17102</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1383.163868080818</v>
+        <v>1383.232651074283</v>
       </c>
       <c r="D56" t="n">
-        <v>1378.285326022174</v>
+        <v>1378.3528864988</v>
       </c>
       <c r="E56" t="n">
-        <v>1388.042410139461</v>
+        <v>1388.112415649768</v>
       </c>
       <c r="F56" t="n">
         <v>23720</v>
@@ -6980,16 +6980,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1378.558201143977</v>
+        <v>1378.636387572678</v>
       </c>
       <c r="D57" t="n">
-        <v>1374.190568930903</v>
+        <v>1374.276733576791</v>
       </c>
       <c r="E57" t="n">
-        <v>1382.925833357051</v>
+        <v>1382.996041568566</v>
       </c>
       <c r="F57" t="n">
-        <v>30115</v>
+        <v>30083</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
@@ -7127,16 +7127,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1377.199349048589</v>
+        <v>1377.276415514598</v>
       </c>
       <c r="D58" t="n">
-        <v>1365.940095082343</v>
+        <v>1366.012803604187</v>
       </c>
       <c r="E58" t="n">
-        <v>1388.458603014836</v>
+        <v>1388.540027425009</v>
       </c>
       <c r="F58" t="n">
-        <v>2802</v>
+        <v>2800</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7198,13 +7198,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1374.77089940988</v>
+        <v>1374.900773403858</v>
       </c>
       <c r="D59" t="n">
-        <v>1370.079349684971</v>
+        <v>1370.207313447591</v>
       </c>
       <c r="E59" t="n">
-        <v>1379.462449134789</v>
+        <v>1379.594233360125</v>
       </c>
       <c r="F59" t="n">
         <v>26259</v>
@@ -7349,16 +7349,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1373.044550330477</v>
+        <v>1373.180585962494</v>
       </c>
       <c r="D60" t="n">
-        <v>1368.801692474028</v>
+        <v>1368.936729717957</v>
       </c>
       <c r="E60" t="n">
-        <v>1377.287408186926</v>
+        <v>1377.424442207031</v>
       </c>
       <c r="F60" t="n">
-        <v>31066</v>
+        <v>31061</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7420,16 +7420,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1369.654349713076</v>
+        <v>1369.627631820962</v>
       </c>
       <c r="D61" t="n">
-        <v>1363.816785655225</v>
+        <v>1363.788376436918</v>
       </c>
       <c r="E61" t="n">
-        <v>1375.491913770928</v>
+        <v>1375.466887205006</v>
       </c>
       <c r="F61" t="n">
-        <v>13686</v>
+        <v>13676</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7571,16 +7571,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1369.126296435841</v>
+        <v>1369.223153814295</v>
       </c>
       <c r="D62" t="n">
-        <v>1364.426562751712</v>
+        <v>1364.52660605285</v>
       </c>
       <c r="E62" t="n">
-        <v>1373.82603011997</v>
+        <v>1373.919701575741</v>
       </c>
       <c r="F62" t="n">
-        <v>29229</v>
+        <v>29192</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
@@ -7718,13 +7718,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1367.870109355791</v>
+        <v>1368.167694949615</v>
       </c>
       <c r="D63" t="n">
-        <v>1362.065632426707</v>
+        <v>1362.36680257171</v>
       </c>
       <c r="E63" t="n">
-        <v>1373.674586284875</v>
+        <v>1373.968587327519</v>
       </c>
       <c r="F63" t="n">
         <v>11724</v>
@@ -7789,16 +7789,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1365.764478565441</v>
+        <v>1365.835200201697</v>
       </c>
       <c r="D64" t="n">
-        <v>1362.092267165797</v>
+        <v>1362.161714874863</v>
       </c>
       <c r="E64" t="n">
-        <v>1369.436689965086</v>
+        <v>1369.508685528532</v>
       </c>
       <c r="F64" t="n">
-        <v>47513</v>
+        <v>47514</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1363.6298318409</v>
+        <v>1363.744901094685</v>
       </c>
       <c r="D65" t="n">
-        <v>1359.358485851574</v>
+        <v>1359.47230965306</v>
       </c>
       <c r="E65" t="n">
-        <v>1367.901177830226</v>
+        <v>1368.017492536311</v>
       </c>
       <c r="F65" t="n">
-        <v>35177</v>
+        <v>35170</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8011,16 +8011,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1361.726147940642</v>
+        <v>1361.425068970003</v>
       </c>
       <c r="D66" t="n">
-        <v>1354.4573698466</v>
+        <v>1354.159874680177</v>
       </c>
       <c r="E66" t="n">
-        <v>1368.994926034683</v>
+        <v>1368.690263259828</v>
       </c>
       <c r="F66" t="n">
-        <v>7547</v>
+        <v>7545</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1358.471252976401</v>
+        <v>1358.530668707208</v>
       </c>
       <c r="D67" t="n">
-        <v>1353.731862123469</v>
+        <v>1353.788396664972</v>
       </c>
       <c r="E67" t="n">
-        <v>1363.210643829333</v>
+        <v>1363.272940749443</v>
       </c>
       <c r="F67" t="n">
         <v>21770</v>
@@ -8313,16 +8313,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1357.667005273806</v>
+        <v>1357.642562968235</v>
       </c>
       <c r="D68" t="n">
-        <v>1352.466473492829</v>
+        <v>1352.441423677086</v>
       </c>
       <c r="E68" t="n">
-        <v>1362.867537054782</v>
+        <v>1362.843702259384</v>
       </c>
       <c r="F68" t="n">
-        <v>17698</v>
+        <v>17699</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8384,16 +8384,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1356.33774161985</v>
+        <v>1356.325493731292</v>
       </c>
       <c r="D69" t="n">
-        <v>1347.990914953977</v>
+        <v>1347.979912922631</v>
       </c>
       <c r="E69" t="n">
-        <v>1364.684568285724</v>
+        <v>1364.671074539953</v>
       </c>
       <c r="F69" t="n">
-        <v>5329</v>
+        <v>5328</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
@@ -8531,16 +8531,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1353.950686589983</v>
+        <v>1354.006402346084</v>
       </c>
       <c r="D70" t="n">
-        <v>1350.503046969528</v>
+        <v>1350.556897854371</v>
       </c>
       <c r="E70" t="n">
-        <v>1357.398326210438</v>
+        <v>1357.455906837796</v>
       </c>
       <c r="F70" t="n">
-        <v>56234</v>
+        <v>56224</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8602,16 +8602,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1353.562197653564</v>
+        <v>1353.603110112719</v>
       </c>
       <c r="D71" t="n">
-        <v>1345.217368367803</v>
+        <v>1345.25857108704</v>
       </c>
       <c r="E71" t="n">
-        <v>1361.907026939325</v>
+        <v>1361.947649138398</v>
       </c>
       <c r="F71" t="n">
-        <v>4956</v>
+        <v>4955</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8673,16 +8673,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1352.620923660646</v>
+        <v>1352.646285991563</v>
       </c>
       <c r="D72" t="n">
-        <v>1348.27443085289</v>
+        <v>1348.299227162875</v>
       </c>
       <c r="E72" t="n">
-        <v>1356.967416468403</v>
+        <v>1356.993344820252</v>
       </c>
       <c r="F72" t="n">
-        <v>30639</v>
+        <v>30628</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8824,16 +8824,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1348.451318620989</v>
+        <v>1348.396414563652</v>
       </c>
       <c r="D73" t="n">
-        <v>1341.047594336476</v>
+        <v>1340.993250249576</v>
       </c>
       <c r="E73" t="n">
-        <v>1355.855042905504</v>
+        <v>1355.799578877728</v>
       </c>
       <c r="F73" t="n">
-        <v>6537</v>
+        <v>6534</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8895,13 +8895,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1347.432489754107</v>
+        <v>1347.537291228422</v>
       </c>
       <c r="D74" t="n">
-        <v>1335.746333798763</v>
+        <v>1335.851592758297</v>
       </c>
       <c r="E74" t="n">
-        <v>1359.11864570945</v>
+        <v>1359.222989698546</v>
       </c>
       <c r="F74" t="n">
         <v>2549</v>
@@ -9046,13 +9046,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1347.260186955363</v>
+        <v>1347.308024279717</v>
       </c>
       <c r="D75" t="n">
-        <v>1337.801597831706</v>
+        <v>1337.849233277879</v>
       </c>
       <c r="E75" t="n">
-        <v>1356.71877607902</v>
+        <v>1356.766815281555</v>
       </c>
       <c r="F75" t="n">
         <v>3926</v>
@@ -9197,16 +9197,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1346.389781202702</v>
+        <v>1346.290301013577</v>
       </c>
       <c r="D76" t="n">
-        <v>1339.131251923795</v>
+        <v>1339.028077239387</v>
       </c>
       <c r="E76" t="n">
-        <v>1353.64831048161</v>
+        <v>1353.552524787768</v>
       </c>
       <c r="F76" t="n">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9268,16 +9268,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1345.980576667275</v>
+        <v>1346.052587611727</v>
       </c>
       <c r="D77" t="n">
-        <v>1338.241925100815</v>
+        <v>1338.314866517933</v>
       </c>
       <c r="E77" t="n">
-        <v>1353.719228233736</v>
+        <v>1353.790308705521</v>
       </c>
       <c r="F77" t="n">
-        <v>6864</v>
+        <v>6866</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9419,16 +9419,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1343.058122375561</v>
+        <v>1343.268595025537</v>
       </c>
       <c r="D78" t="n">
-        <v>1333.091246626917</v>
+        <v>1333.301031274051</v>
       </c>
       <c r="E78" t="n">
-        <v>1353.024998124204</v>
+        <v>1353.236158777022</v>
       </c>
       <c r="F78" t="n">
-        <v>3346</v>
+        <v>3344</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1341.878872779034</v>
+        <v>1341.977847764731</v>
       </c>
       <c r="D79" t="n">
-        <v>1332.370033964112</v>
+        <v>1332.468507928149</v>
       </c>
       <c r="E79" t="n">
-        <v>1351.387711593956</v>
+        <v>1351.487187601312</v>
       </c>
       <c r="F79" t="n">
         <v>3829</v>
@@ -9721,13 +9721,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1336.16196444838</v>
+        <v>1336.26252024527</v>
       </c>
       <c r="D80" t="n">
-        <v>1331.723765129484</v>
+        <v>1331.822396135999</v>
       </c>
       <c r="E80" t="n">
-        <v>1340.600163767276</v>
+        <v>1340.70264435454</v>
       </c>
       <c r="F80" t="n">
         <v>25382</v>
@@ -9872,13 +9872,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1334.690891720765</v>
+        <v>1334.801939804538</v>
       </c>
       <c r="D81" t="n">
-        <v>1330.982447806294</v>
+        <v>1331.089818759892</v>
       </c>
       <c r="E81" t="n">
-        <v>1338.399335635235</v>
+        <v>1338.514060849183</v>
       </c>
       <c r="F81" t="n">
         <v>41375</v>
@@ -10023,13 +10023,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1332.864584789327</v>
+        <v>1332.969406981425</v>
       </c>
       <c r="D82" t="n">
-        <v>1329.272339266846</v>
+        <v>1329.373960434493</v>
       </c>
       <c r="E82" t="n">
-        <v>1336.456830311807</v>
+        <v>1336.564853528359</v>
       </c>
       <c r="F82" t="n">
         <v>59656</v>
@@ -10174,16 +10174,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1330.083713227149</v>
+        <v>1330.206448461898</v>
       </c>
       <c r="D83" t="n">
-        <v>1324.002299491965</v>
+        <v>1324.126051837692</v>
       </c>
       <c r="E83" t="n">
-        <v>1336.165126962332</v>
+        <v>1336.286845086104</v>
       </c>
       <c r="F83" t="n">
-        <v>12217</v>
+        <v>12211</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10321,36 +10321,36 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1328.29661933247</v>
+        <v>1328.04601222219</v>
       </c>
       <c r="D84" t="n">
-        <v>1306.99930811445</v>
+        <v>1315.897127876131</v>
       </c>
       <c r="E84" t="n">
-        <v>1349.59393055049</v>
+        <v>1340.19489656825</v>
       </c>
       <c r="F84" t="n">
-        <v>803</v>
+        <v>2218</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="J84" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -10363,26 +10363,26 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="N84" t="n">
-        <v>20</v>
+        <v>122.5</v>
       </c>
       <c r="O84" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="P84" t="n">
-        <v>10</v>
+        <v>61.2</v>
       </c>
       <c r="Q84" t="n">
-        <v>4</v>
+        <v>24.5</v>
       </c>
       <c r="R84" t="n">
-        <v>5</v>
-      </c>
-      <c r="S84" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>30.6</v>
+      </c>
+      <c r="S84" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T84" s="6" t="inlineStr">
@@ -10395,9 +10395,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V84" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V84" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W84" s="6" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
@@ -10472,36 +10472,36 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1327.969074546529</v>
+        <v>1328.005448690092</v>
       </c>
       <c r="D85" t="n">
-        <v>1315.819495291745</v>
+        <v>1306.669983161878</v>
       </c>
       <c r="E85" t="n">
-        <v>1340.118653801313</v>
+        <v>1349.340914218306</v>
       </c>
       <c r="F85" t="n">
-        <v>2218</v>
+        <v>800</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="J85" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -10514,26 +10514,26 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="N85" t="n">
-        <v>122.5</v>
+        <v>20</v>
       </c>
       <c r="O85" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>61.2</v>
+        <v>10</v>
       </c>
       <c r="Q85" t="n">
-        <v>24.5</v>
+        <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="S85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5</v>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T85" s="6" t="inlineStr">
@@ -10546,9 +10546,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W85" s="6" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
@@ -10627,13 +10627,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1327.268432522309</v>
+        <v>1327.332326224859</v>
       </c>
       <c r="D86" t="n">
-        <v>1322.541300339965</v>
+        <v>1322.603348428152</v>
       </c>
       <c r="E86" t="n">
-        <v>1331.995564704653</v>
+        <v>1332.061304021567</v>
       </c>
       <c r="F86" t="n">
         <v>26474</v>
@@ -10778,16 +10778,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1326.936995789791</v>
+        <v>1327.091629236379</v>
       </c>
       <c r="D87" t="n">
-        <v>1322.686532635555</v>
+        <v>1322.839630592473</v>
       </c>
       <c r="E87" t="n">
-        <v>1331.187458944027</v>
+        <v>1331.343627880286</v>
       </c>
       <c r="F87" t="n">
-        <v>39967</v>
+        <v>39963</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10929,13 +10929,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1323.419941391904</v>
+        <v>1323.47409372959</v>
       </c>
       <c r="D88" t="n">
-        <v>1315.150348225536</v>
+        <v>1315.203358585569</v>
       </c>
       <c r="E88" t="n">
-        <v>1331.689534558271</v>
+        <v>1331.744828873611</v>
       </c>
       <c r="F88" t="n">
         <v>6795</v>
@@ -11000,16 +11000,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1322.636355202719</v>
+        <v>1322.81181875169</v>
       </c>
       <c r="D89" t="n">
-        <v>1317.931185821038</v>
+        <v>1318.105514675858</v>
       </c>
       <c r="E89" t="n">
-        <v>1327.3415245844</v>
+        <v>1327.518122827523</v>
       </c>
       <c r="F89" t="n">
-        <v>30275</v>
+        <v>30280</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11151,16 +11151,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1320.737438599908</v>
+        <v>1320.680205982145</v>
       </c>
       <c r="D90" t="n">
-        <v>1313.52301688618</v>
+        <v>1313.463550310309</v>
       </c>
       <c r="E90" t="n">
-        <v>1327.951860313635</v>
+        <v>1327.896861653982</v>
       </c>
       <c r="F90" t="n">
-        <v>7137</v>
+        <v>7135</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -11222,16 +11222,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1318.138426141699</v>
+        <v>1318.15072989801</v>
       </c>
       <c r="D91" t="n">
-        <v>1314.669054767298</v>
+        <v>1314.677438943718</v>
       </c>
       <c r="E91" t="n">
-        <v>1321.607797516101</v>
+        <v>1321.624020852303</v>
       </c>
       <c r="F91" t="n">
-        <v>54732</v>
+        <v>54726</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -11373,16 +11373,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1318.114216429686</v>
+        <v>1318.121312050259</v>
       </c>
       <c r="D92" t="n">
-        <v>1312.968844829356</v>
+        <v>1312.973917726672</v>
       </c>
       <c r="E92" t="n">
-        <v>1323.259588030017</v>
+        <v>1323.268706373846</v>
       </c>
       <c r="F92" t="n">
-        <v>22578</v>
+        <v>22568</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -11524,13 +11524,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1317.909285753745</v>
+        <v>1317.981924523393</v>
       </c>
       <c r="D93" t="n">
-        <v>1312.210788685309</v>
+        <v>1312.28175006122</v>
       </c>
       <c r="E93" t="n">
-        <v>1323.607782822181</v>
+        <v>1323.682098985566</v>
       </c>
       <c r="F93" t="n">
         <v>16478</v>
@@ -11595,16 +11595,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1317.42599810888</v>
+        <v>1317.430642352258</v>
       </c>
       <c r="D94" t="n">
-        <v>1311.058758901932</v>
+        <v>1311.061803153363</v>
       </c>
       <c r="E94" t="n">
-        <v>1323.793237315828</v>
+        <v>1323.799481551153</v>
       </c>
       <c r="F94" t="n">
-        <v>10625</v>
+        <v>10621</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11746,13 +11746,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1316.063932428772</v>
+        <v>1316.035119784746</v>
       </c>
       <c r="D95" t="n">
-        <v>1310.517954708409</v>
+        <v>1310.491675054855</v>
       </c>
       <c r="E95" t="n">
-        <v>1321.609910149135</v>
+        <v>1321.578564514636</v>
       </c>
       <c r="F95" t="n">
         <v>15509</v>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1314.285077301751</v>
+        <v>1314.329926956419</v>
       </c>
       <c r="D96" t="n">
-        <v>1309.735588822665</v>
+        <v>1309.777531480716</v>
       </c>
       <c r="E96" t="n">
-        <v>1318.834565780837</v>
+        <v>1318.882322432122</v>
       </c>
       <c r="F96" t="n">
         <v>24739</v>
@@ -12044,13 +12044,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1313.915846313264</v>
+        <v>1314.012736840647</v>
       </c>
       <c r="D97" t="n">
-        <v>1309.99229682006</v>
+        <v>1310.086427351651</v>
       </c>
       <c r="E97" t="n">
-        <v>1317.839395806468</v>
+        <v>1317.939046329643</v>
       </c>
       <c r="F97" t="n">
         <v>45459</v>
@@ -12195,13 +12195,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1307.052888237502</v>
+        <v>1307.122206762661</v>
       </c>
       <c r="D98" t="n">
-        <v>1302.349344550076</v>
+        <v>1302.416280085533</v>
       </c>
       <c r="E98" t="n">
-        <v>1311.756431924926</v>
+        <v>1311.828133439788</v>
       </c>
       <c r="F98" t="n">
         <v>24572</v>
@@ -12266,16 +12266,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1306.797440488142</v>
+        <v>1307.108993752688</v>
       </c>
       <c r="D99" t="n">
-        <v>1296.660146947183</v>
+        <v>1296.989138600811</v>
       </c>
       <c r="E99" t="n">
-        <v>1316.934734029101</v>
+        <v>1317.228848904566</v>
       </c>
       <c r="F99" t="n">
-        <v>4063</v>
+        <v>4067</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -12417,13 +12417,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1306.229302396765</v>
+        <v>1306.353547696021</v>
       </c>
       <c r="D100" t="n">
-        <v>1300.556174848534</v>
+        <v>1300.678851236288</v>
       </c>
       <c r="E100" t="n">
-        <v>1311.902429944997</v>
+        <v>1312.028244155753</v>
       </c>
       <c r="F100" t="n">
         <v>19621</v>
@@ -12564,16 +12564,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1305.631209093297</v>
+        <v>1305.720967433766</v>
       </c>
       <c r="D101" t="n">
-        <v>1297.45333347367</v>
+        <v>1297.544511868982</v>
       </c>
       <c r="E101" t="n">
-        <v>1313.809084712924</v>
+        <v>1313.89742299855</v>
       </c>
       <c r="F101" t="n">
-        <v>5942</v>
+        <v>5941</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12715,13 +12715,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1305.200818750652</v>
+        <v>1305.293631031866</v>
       </c>
       <c r="D102" t="n">
-        <v>1300.768103082117</v>
+        <v>1300.857587685644</v>
       </c>
       <c r="E102" t="n">
-        <v>1309.633534419187</v>
+        <v>1309.729674378089</v>
       </c>
       <c r="F102" t="n">
         <v>28073</v>
@@ -12782,36 +12782,36 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1303.408632542045</v>
+        <v>1303.384706140991</v>
       </c>
       <c r="D103" t="n">
-        <v>1298.901575649192</v>
+        <v>1294.068814703218</v>
       </c>
       <c r="E103" t="n">
-        <v>1307.915689434898</v>
+        <v>1312.700597578764</v>
       </c>
       <c r="F103" t="n">
-        <v>33204</v>
+        <v>4171</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J103" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -12824,22 +12824,22 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N103" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O103" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P103" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q103" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R103" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="S103" s="6" t="inlineStr">
         <is>
@@ -12933,36 +12933,36 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1303.280318412984</v>
+        <v>1303.354293005192</v>
       </c>
       <c r="D104" t="n">
-        <v>1293.964877949521</v>
+        <v>1298.845957373095</v>
       </c>
       <c r="E104" t="n">
-        <v>1312.595758876446</v>
+        <v>1307.862628637289</v>
       </c>
       <c r="F104" t="n">
-        <v>4171</v>
+        <v>33199</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -12975,22 +12975,22 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P104" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q104" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R104" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="S104" s="6" t="inlineStr">
         <is>
@@ -13088,13 +13088,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1302.765591511461</v>
+        <v>1302.832259162798</v>
       </c>
       <c r="D105" t="n">
-        <v>1298.695327667053</v>
+        <v>1298.758731180794</v>
       </c>
       <c r="E105" t="n">
-        <v>1306.835855355868</v>
+        <v>1306.905787144801</v>
       </c>
       <c r="F105" t="n">
         <v>39406</v>
@@ -13239,13 +13239,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1298.938155015356</v>
+        <v>1299.013342467176</v>
       </c>
       <c r="D106" t="n">
-        <v>1291.176072483735</v>
+        <v>1291.250173482085</v>
       </c>
       <c r="E106" t="n">
-        <v>1306.700237546978</v>
+        <v>1306.776511452268</v>
       </c>
       <c r="F106" t="n">
         <v>7140</v>
@@ -13390,13 +13390,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1293.121634370848</v>
+        <v>1293.209073820047</v>
       </c>
       <c r="D107" t="n">
-        <v>1289.38880245615</v>
+        <v>1289.473012749907</v>
       </c>
       <c r="E107" t="n">
-        <v>1296.854466285545</v>
+        <v>1296.945134890186</v>
       </c>
       <c r="F107" t="n">
         <v>55240</v>
@@ -13541,13 +13541,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1288.941790653918</v>
+        <v>1289.046883961437</v>
       </c>
       <c r="D108" t="n">
-        <v>1281.635062895248</v>
+        <v>1281.739234403515</v>
       </c>
       <c r="E108" t="n">
-        <v>1296.248518412589</v>
+        <v>1296.354533519359</v>
       </c>
       <c r="F108" t="n">
         <v>8662</v>
@@ -13608,13 +13608,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1288.772092847751</v>
+        <v>1288.930124148982</v>
       </c>
       <c r="D109" t="n">
-        <v>1285.39415930362</v>
+        <v>1285.548391391217</v>
       </c>
       <c r="E109" t="n">
-        <v>1292.150026391882</v>
+        <v>1292.311856906746</v>
       </c>
       <c r="F109" t="n">
         <v>75754</v>
@@ -13759,16 +13759,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1286.822579184289</v>
+        <v>1286.920363900504</v>
       </c>
       <c r="D110" t="n">
-        <v>1278.428711633377</v>
+        <v>1278.529950705316</v>
       </c>
       <c r="E110" t="n">
-        <v>1295.216446735202</v>
+        <v>1295.310777095691</v>
       </c>
       <c r="F110" t="n">
-        <v>5680</v>
+        <v>5681</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -13910,13 +13910,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1285.907059913281</v>
+        <v>1285.969923101597</v>
       </c>
       <c r="D111" t="n">
-        <v>1275.438568841443</v>
+        <v>1275.501448966889</v>
       </c>
       <c r="E111" t="n">
-        <v>1296.375550985118</v>
+        <v>1296.438397236306</v>
       </c>
       <c r="F111" t="n">
         <v>2846</v>
@@ -14061,13 +14061,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1285.805404874266</v>
+        <v>1285.920473143214</v>
       </c>
       <c r="D112" t="n">
-        <v>1275.832610354328</v>
+        <v>1275.947388069655</v>
       </c>
       <c r="E112" t="n">
-        <v>1295.778199394204</v>
+        <v>1295.893558216773</v>
       </c>
       <c r="F112" t="n">
         <v>3749</v>
@@ -14212,16 +14212,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1285.009685620031</v>
+        <v>1285.088537758943</v>
       </c>
       <c r="D113" t="n">
-        <v>1277.799094931654</v>
+        <v>1277.881669505711</v>
       </c>
       <c r="E113" t="n">
-        <v>1292.220276308408</v>
+        <v>1292.295406012176</v>
       </c>
       <c r="F113" t="n">
-        <v>8503</v>
+        <v>8499</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -14363,13 +14363,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1279.783673382128</v>
+        <v>1279.927938134399</v>
       </c>
       <c r="D114" t="n">
-        <v>1272.923157934549</v>
+        <v>1273.066562246898</v>
       </c>
       <c r="E114" t="n">
-        <v>1286.644188829707</v>
+        <v>1286.789314021901</v>
       </c>
       <c r="F114" t="n">
         <v>10072</v>
@@ -14510,13 +14510,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1276.430063793639</v>
+        <v>1276.520159967032</v>
       </c>
       <c r="D115" t="n">
-        <v>1271.10307791463</v>
+        <v>1271.192387312555</v>
       </c>
       <c r="E115" t="n">
-        <v>1281.757049672647</v>
+        <v>1281.847932621509</v>
       </c>
       <c r="F115" t="n">
         <v>19659</v>
@@ -14661,13 +14661,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1275.81672143464</v>
+        <v>1275.941123167192</v>
       </c>
       <c r="D116" t="n">
-        <v>1272.229375260231</v>
+        <v>1272.351800763617</v>
       </c>
       <c r="E116" t="n">
-        <v>1279.404067609049</v>
+        <v>1279.530445570767</v>
       </c>
       <c r="F116" t="n">
         <v>156876</v>
@@ -14812,13 +14812,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1275.726486157192</v>
+        <v>1275.811703175532</v>
       </c>
       <c r="D117" t="n">
-        <v>1269.149480036716</v>
+        <v>1269.233405485987</v>
       </c>
       <c r="E117" t="n">
-        <v>1282.303492277669</v>
+        <v>1282.390000865078</v>
       </c>
       <c r="F117" t="n">
         <v>9866</v>
@@ -14963,13 +14963,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1274.01624391297</v>
+        <v>1274.11341857605</v>
       </c>
       <c r="D118" t="n">
-        <v>1268.111808181116</v>
+        <v>1268.206617834918</v>
       </c>
       <c r="E118" t="n">
-        <v>1279.920679644825</v>
+        <v>1280.020219317181</v>
       </c>
       <c r="F118" t="n">
         <v>14681</v>
@@ -15114,13 +15114,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1270.317547106389</v>
+        <v>1270.390652830845</v>
       </c>
       <c r="D119" t="n">
-        <v>1262.190965054567</v>
+        <v>1262.262880204433</v>
       </c>
       <c r="E119" t="n">
-        <v>1278.444129158212</v>
+        <v>1278.518425457257</v>
       </c>
       <c r="F119" t="n">
         <v>5432</v>
@@ -15265,13 +15265,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1266.810871865221</v>
+        <v>1266.916315311858</v>
       </c>
       <c r="D120" t="n">
-        <v>1261.925945630747</v>
+        <v>1262.028637965971</v>
       </c>
       <c r="E120" t="n">
-        <v>1271.695798099695</v>
+        <v>1271.803992657746</v>
       </c>
       <c r="F120" t="n">
         <v>27124</v>
@@ -15416,13 +15416,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1266.282432210059</v>
+        <v>1266.442820853938</v>
       </c>
       <c r="D121" t="n">
-        <v>1262.467125747545</v>
+        <v>1262.62417427819</v>
       </c>
       <c r="E121" t="n">
-        <v>1270.097738672573</v>
+        <v>1270.261467429686</v>
       </c>
       <c r="F121" t="n">
         <v>54611</v>
@@ -15567,13 +15567,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1264.360173472154</v>
+        <v>1264.504521219612</v>
       </c>
       <c r="D122" t="n">
-        <v>1258.079233338555</v>
+        <v>1258.222965641233</v>
       </c>
       <c r="E122" t="n">
-        <v>1270.641113605752</v>
+        <v>1270.786076797992</v>
       </c>
       <c r="F122" t="n">
         <v>15147</v>
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1261.019446952845</v>
+        <v>1261.11940013247</v>
       </c>
       <c r="D123" t="n">
-        <v>1256.072103889396</v>
+        <v>1256.170407658561</v>
       </c>
       <c r="E123" t="n">
-        <v>1265.966790016293</v>
+        <v>1266.06839260638</v>
       </c>
       <c r="F123" t="n">
         <v>37325</v>
@@ -15869,13 +15869,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1260.967521457678</v>
+        <v>1261.059124275596</v>
       </c>
       <c r="D124" t="n">
-        <v>1256.642619388689</v>
+        <v>1256.732946005696</v>
       </c>
       <c r="E124" t="n">
-        <v>1265.292423526668</v>
+        <v>1265.385302545496</v>
       </c>
       <c r="F124" t="n">
         <v>77554</v>
@@ -15940,13 +15940,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1255.950288834706</v>
+        <v>1256.046194881889</v>
       </c>
       <c r="D125" t="n">
-        <v>1251.359973267281</v>
+        <v>1251.452946585492</v>
       </c>
       <c r="E125" t="n">
-        <v>1260.540604402132</v>
+        <v>1260.639443178287</v>
       </c>
       <c r="F125" t="n">
         <v>24126</v>
@@ -16091,13 +16091,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1251.295417370818</v>
+        <v>1251.381337964363</v>
       </c>
       <c r="D126" t="n">
-        <v>1240.511973182844</v>
+        <v>1240.598010746335</v>
       </c>
       <c r="E126" t="n">
-        <v>1262.078861558792</v>
+        <v>1262.16466518239</v>
       </c>
       <c r="F126" t="n">
         <v>3334</v>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1249.54444881744</v>
+        <v>1249.653941151953</v>
       </c>
       <c r="D127" t="n">
-        <v>1242.942977767999</v>
+        <v>1243.05109460931</v>
       </c>
       <c r="E127" t="n">
-        <v>1256.14591986688</v>
+        <v>1256.256787694596</v>
       </c>
       <c r="F127" t="n">
         <v>10140</v>
@@ -16393,13 +16393,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1239.230712835585</v>
+        <v>1239.349846451147</v>
       </c>
       <c r="D128" t="n">
-        <v>1232.003693799109</v>
+        <v>1232.121863552891</v>
       </c>
       <c r="E128" t="n">
-        <v>1246.457731872061</v>
+        <v>1246.577829349403</v>
       </c>
       <c r="F128" t="n">
         <v>8858</v>
@@ -16460,13 +16460,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1237.204968749514</v>
+        <v>1237.298057734616</v>
       </c>
       <c r="D129" t="n">
-        <v>1228.110821628372</v>
+        <v>1228.203464567066</v>
       </c>
       <c r="E129" t="n">
-        <v>1246.299115870656</v>
+        <v>1246.392650902166</v>
       </c>
       <c r="F129" t="n">
         <v>4781</v>
@@ -16611,13 +16611,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1233.377749165773</v>
+        <v>1233.484899424981</v>
       </c>
       <c r="D130" t="n">
-        <v>1227.822933597336</v>
+        <v>1227.929414878736</v>
       </c>
       <c r="E130" t="n">
-        <v>1238.932564734209</v>
+        <v>1239.040383971226</v>
       </c>
       <c r="F130" t="n">
         <v>26195</v>
@@ -16762,13 +16762,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1232.550768822609</v>
+        <v>1232.669439926744</v>
       </c>
       <c r="D131" t="n">
-        <v>1227.274051051495</v>
+        <v>1227.392071311897</v>
       </c>
       <c r="E131" t="n">
-        <v>1237.827486593723</v>
+        <v>1237.94680854159</v>
       </c>
       <c r="F131" t="n">
         <v>39302</v>
@@ -16913,13 +16913,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1228.589813820794</v>
+        <v>1228.698684749937</v>
       </c>
       <c r="D132" t="n">
-        <v>1224.032036693407</v>
+        <v>1224.139454958114</v>
       </c>
       <c r="E132" t="n">
-        <v>1233.147590948181</v>
+        <v>1233.257914541759</v>
       </c>
       <c r="F132" t="n">
         <v>51416</v>
@@ -17064,13 +17064,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1225.951346560972</v>
+        <v>1226.049831410564</v>
       </c>
       <c r="D133" t="n">
-        <v>1221.167242388945</v>
+        <v>1221.264703389555</v>
       </c>
       <c r="E133" t="n">
-        <v>1230.735450732999</v>
+        <v>1230.834959431574</v>
       </c>
       <c r="F133" t="n">
         <v>54036</v>
@@ -17135,13 +17135,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1222.853857613258</v>
+        <v>1222.975032649359</v>
       </c>
       <c r="D134" t="n">
-        <v>1219.115746120595</v>
+        <v>1219.235052270617</v>
       </c>
       <c r="E134" t="n">
-        <v>1226.591969105921</v>
+        <v>1226.715013028101</v>
       </c>
       <c r="F134" t="n">
         <v>104642</v>
@@ -17286,13 +17286,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1222.755490901058</v>
+        <v>1222.852504827753</v>
       </c>
       <c r="D135" t="n">
-        <v>1215.784106842436</v>
+        <v>1215.879371617388</v>
       </c>
       <c r="E135" t="n">
-        <v>1229.726874959679</v>
+        <v>1229.825638038117</v>
       </c>
       <c r="F135" t="n">
         <v>9818</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1220.412263994809</v>
+        <v>1220.468468963427</v>
       </c>
       <c r="D136" t="n">
-        <v>1209.732935562839</v>
+        <v>1209.789121796035</v>
       </c>
       <c r="E136" t="n">
-        <v>1231.09159242678</v>
+        <v>1231.147816130819</v>
       </c>
       <c r="F136" t="n">
         <v>2896</v>
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1212.444005801904</v>
+        <v>1212.510911981527</v>
       </c>
       <c r="D137" t="n">
-        <v>1207.403983561768</v>
+        <v>1207.469844925155</v>
       </c>
       <c r="E137" t="n">
-        <v>1217.484028042042</v>
+        <v>1217.551979037898</v>
       </c>
       <c r="F137" t="n">
         <v>24146</v>
@@ -17735,13 +17735,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1212.003634585186</v>
+        <v>1212.116737123765</v>
       </c>
       <c r="D138" t="n">
-        <v>1201.209252921012</v>
+        <v>1201.323150490891</v>
       </c>
       <c r="E138" t="n">
-        <v>1222.798016249359</v>
+        <v>1222.910323756639</v>
       </c>
       <c r="F138" t="n">
         <v>4652</v>
@@ -17882,13 +17882,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1211.265782926833</v>
+        <v>1211.32885833132</v>
       </c>
       <c r="D139" t="n">
-        <v>1207.118639058419</v>
+        <v>1207.178659357499</v>
       </c>
       <c r="E139" t="n">
-        <v>1215.412926795248</v>
+        <v>1215.479057305142</v>
       </c>
       <c r="F139" t="n">
         <v>49605</v>
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1207.705651625702</v>
+        <v>1207.805851643695</v>
       </c>
       <c r="D140" t="n">
-        <v>1196.601193214617</v>
+        <v>1196.701514265998</v>
       </c>
       <c r="E140" t="n">
-        <v>1218.810110036787</v>
+        <v>1218.910189021391</v>
       </c>
       <c r="F140" t="n">
         <v>3090</v>
@@ -18184,13 +18184,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1203.022531107527</v>
+        <v>1203.130688694691</v>
       </c>
       <c r="D141" t="n">
-        <v>1196.902518555894</v>
+        <v>1197.010188864301</v>
       </c>
       <c r="E141" t="n">
-        <v>1209.142543659159</v>
+        <v>1209.251188525082</v>
       </c>
       <c r="F141" t="n">
         <v>21741</v>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1199.696127365285</v>
+        <v>1199.842335997352</v>
       </c>
       <c r="D142" t="n">
-        <v>1195.60624802813</v>
+        <v>1195.749305755851</v>
       </c>
       <c r="E142" t="n">
-        <v>1203.78600670244</v>
+        <v>1203.935366238852</v>
       </c>
       <c r="F142" t="n">
         <v>46616</v>
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1197.067187405617</v>
+        <v>1197.163627400203</v>
       </c>
       <c r="D143" t="n">
-        <v>1191.906618534913</v>
+        <v>1192.001649603543</v>
       </c>
       <c r="E143" t="n">
-        <v>1202.227756276321</v>
+        <v>1202.325605196862</v>
       </c>
       <c r="F143" t="n">
         <v>25055</v>
@@ -18637,13 +18637,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1196.210394471505</v>
+        <v>1196.313012298558</v>
       </c>
       <c r="D144" t="n">
-        <v>1191.939660759416</v>
+        <v>1192.041337390137</v>
       </c>
       <c r="E144" t="n">
-        <v>1200.481128183593</v>
+        <v>1200.58468720698</v>
       </c>
       <c r="F144" t="n">
         <v>73503</v>
@@ -18788,13 +18788,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1194.363173853415</v>
+        <v>1194.488518038758</v>
       </c>
       <c r="D145" t="n">
-        <v>1188.2480085835</v>
+        <v>1188.372808544085</v>
       </c>
       <c r="E145" t="n">
-        <v>1200.47833912333</v>
+        <v>1200.604227533432</v>
       </c>
       <c r="F145" t="n">
         <v>32191</v>
@@ -18855,13 +18855,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1190.497894296829</v>
+        <v>1190.567223873004</v>
       </c>
       <c r="D146" t="n">
-        <v>1183.314302940262</v>
+        <v>1183.382579870451</v>
       </c>
       <c r="E146" t="n">
-        <v>1197.681485653396</v>
+        <v>1197.751867875557</v>
       </c>
       <c r="F146" t="n">
         <v>9901</v>
@@ -19002,13 +19002,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1190.182117120627</v>
+        <v>1190.291193337264</v>
       </c>
       <c r="D147" t="n">
-        <v>1183.061471654926</v>
+        <v>1183.170549227475</v>
       </c>
       <c r="E147" t="n">
-        <v>1197.302762586328</v>
+        <v>1197.411837447052</v>
       </c>
       <c r="F147" t="n">
         <v>17839</v>
@@ -19153,13 +19153,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1183.802546091035</v>
+        <v>1183.90694492753</v>
       </c>
       <c r="D148" t="n">
-        <v>1174.360606110852</v>
+        <v>1174.465890753196</v>
       </c>
       <c r="E148" t="n">
-        <v>1193.244486071217</v>
+        <v>1193.347999101864</v>
       </c>
       <c r="F148" t="n">
         <v>8214</v>
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1183.720023500402</v>
+        <v>1183.849122561442</v>
       </c>
       <c r="D149" t="n">
-        <v>1172.228587291428</v>
+        <v>1172.359281802511</v>
       </c>
       <c r="E149" t="n">
-        <v>1195.211459709376</v>
+        <v>1195.338963320372</v>
       </c>
       <c r="F149" t="n">
         <v>4932</v>
@@ -19455,13 +19455,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1183.01670041035</v>
+        <v>1183.11472232692</v>
       </c>
       <c r="D150" t="n">
-        <v>1176.188204933133</v>
+        <v>1176.285911375211</v>
       </c>
       <c r="E150" t="n">
-        <v>1189.845195887567</v>
+        <v>1189.943533278629</v>
       </c>
       <c r="F150" t="n">
         <v>15483</v>
@@ -19602,13 +19602,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1181.820159116466</v>
+        <v>1181.973075543749</v>
       </c>
       <c r="D151" t="n">
-        <v>1173.137711374835</v>
+        <v>1173.29043100881</v>
       </c>
       <c r="E151" t="n">
-        <v>1190.502606858096</v>
+        <v>1190.655720078689</v>
       </c>
       <c r="F151" t="n">
         <v>6638</v>
@@ -19753,13 +19753,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1181.723418815407</v>
+        <v>1181.866476526116</v>
       </c>
       <c r="D152" t="n">
-        <v>1172.058789174337</v>
+        <v>1172.202790375298</v>
       </c>
       <c r="E152" t="n">
-        <v>1191.388048456477</v>
+        <v>1191.530162676934</v>
       </c>
       <c r="F152" t="n">
         <v>7968</v>
@@ -19820,13 +19820,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1181.598762780185</v>
+        <v>1181.723527045347</v>
       </c>
       <c r="D153" t="n">
-        <v>1173.602502340783</v>
+        <v>1173.727460493775</v>
       </c>
       <c r="E153" t="n">
-        <v>1189.595023219587</v>
+        <v>1189.719593596919</v>
       </c>
       <c r="F153" t="n">
         <v>12637</v>
@@ -19887,13 +19887,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1181.31816472218</v>
+        <v>1181.523271976807</v>
       </c>
       <c r="D154" t="n">
-        <v>1175.245767803406</v>
+        <v>1175.450296622634</v>
       </c>
       <c r="E154" t="n">
-        <v>1187.390561640954</v>
+        <v>1187.59624733098</v>
       </c>
       <c r="F154" t="n">
         <v>23893</v>
@@ -20038,13 +20038,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1178.850444994937</v>
+        <v>1178.979674827644</v>
       </c>
       <c r="D155" t="n">
-        <v>1172.936767037113</v>
+        <v>1173.06546232722</v>
       </c>
       <c r="E155" t="n">
-        <v>1184.764122952761</v>
+        <v>1184.893887328067</v>
       </c>
       <c r="F155" t="n">
         <v>32832</v>
@@ -20105,13 +20105,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1178.220822867968</v>
+        <v>1178.31212589656</v>
       </c>
       <c r="D156" t="n">
-        <v>1167.026424089671</v>
+        <v>1167.118209453152</v>
       </c>
       <c r="E156" t="n">
-        <v>1189.415221646264</v>
+        <v>1189.506042339968</v>
       </c>
       <c r="F156" t="n">
         <v>3188</v>
@@ -20256,13 +20256,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1176.879879675181</v>
+        <v>1176.964035852511</v>
       </c>
       <c r="D157" t="n">
-        <v>1167.069275432436</v>
+        <v>1167.154240881899</v>
       </c>
       <c r="E157" t="n">
-        <v>1186.690483917927</v>
+        <v>1186.773830823122</v>
       </c>
       <c r="F157" t="n">
         <v>6535</v>
@@ -20403,13 +20403,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1174.676128872726</v>
+        <v>1174.815596119469</v>
       </c>
       <c r="D158" t="n">
-        <v>1164.265969699025</v>
+        <v>1164.406458927437</v>
       </c>
       <c r="E158" t="n">
-        <v>1185.086288046427</v>
+        <v>1185.224733311502</v>
       </c>
       <c r="F158" t="n">
         <v>5006</v>
@@ -20550,13 +20550,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1171.946087394879</v>
+        <v>1172.054279733948</v>
       </c>
       <c r="D159" t="n">
-        <v>1165.741847072756</v>
+        <v>1165.850237696839</v>
       </c>
       <c r="E159" t="n">
-        <v>1178.150327717003</v>
+        <v>1178.258321771058</v>
       </c>
       <c r="F159" t="n">
         <v>22479</v>
@@ -20697,13 +20697,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1170.504695883594</v>
+        <v>1170.566015569935</v>
       </c>
       <c r="D160" t="n">
-        <v>1163.097071907669</v>
+        <v>1163.158496118238</v>
       </c>
       <c r="E160" t="n">
-        <v>1177.91231985952</v>
+        <v>1177.973535021632</v>
       </c>
       <c r="F160" t="n">
         <v>16056</v>
@@ -20844,13 +20844,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1170.235104774819</v>
+        <v>1170.33501381519</v>
       </c>
       <c r="D161" t="n">
-        <v>1164.317553471013</v>
+        <v>1164.416732487892</v>
       </c>
       <c r="E161" t="n">
-        <v>1176.152656078626</v>
+        <v>1176.253295142487</v>
       </c>
       <c r="F161" t="n">
         <v>17766</v>
@@ -20995,13 +20995,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1169.882439219678</v>
+        <v>1169.973729615808</v>
       </c>
       <c r="D162" t="n">
-        <v>1164.381823463686</v>
+        <v>1164.472941460883</v>
       </c>
       <c r="E162" t="n">
-        <v>1175.383054975669</v>
+        <v>1175.474517770733</v>
       </c>
       <c r="F162" t="n">
         <v>38492</v>
@@ -21146,13 +21146,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1166.573637579728</v>
+        <v>1166.667404261073</v>
       </c>
       <c r="D163" t="n">
-        <v>1158.508289621256</v>
+        <v>1158.602212898111</v>
       </c>
       <c r="E163" t="n">
-        <v>1174.638985538199</v>
+        <v>1174.732595624035</v>
       </c>
       <c r="F163" t="n">
         <v>10224</v>
@@ -21293,13 +21293,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1166.08215149852</v>
+        <v>1166.187612889471</v>
       </c>
       <c r="D164" t="n">
-        <v>1158.378148591672</v>
+        <v>1158.482473088921</v>
       </c>
       <c r="E164" t="n">
-        <v>1173.786154405367</v>
+        <v>1173.892752690021</v>
       </c>
       <c r="F164" t="n">
         <v>7936</v>
@@ -21444,13 +21444,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1163.704398805056</v>
+        <v>1163.78871414288</v>
       </c>
       <c r="D165" t="n">
-        <v>1151.786257345735</v>
+        <v>1151.87199421171</v>
       </c>
       <c r="E165" t="n">
-        <v>1175.622540264377</v>
+        <v>1175.705434074051</v>
       </c>
       <c r="F165" t="n">
         <v>3777</v>
@@ -21591,13 +21591,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1155.53309364839</v>
+        <v>1155.662492371845</v>
       </c>
       <c r="D166" t="n">
-        <v>1147.144149258665</v>
+        <v>1147.273214938857</v>
       </c>
       <c r="E166" t="n">
-        <v>1163.922038038114</v>
+        <v>1164.051769804835</v>
       </c>
       <c r="F166" t="n">
         <v>6837</v>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1154.765864950356</v>
+        <v>1154.733626663344</v>
       </c>
       <c r="D167" t="n">
-        <v>1143.272660234482</v>
+        <v>1143.240870976528</v>
       </c>
       <c r="E167" t="n">
-        <v>1166.259069666231</v>
+        <v>1166.226382350159</v>
       </c>
       <c r="F167" t="n">
         <v>3231</v>
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1153.924143134825</v>
+        <v>1153.998724869714</v>
       </c>
       <c r="D168" t="n">
-        <v>1141.323023272286</v>
+        <v>1141.399092591781</v>
       </c>
       <c r="E168" t="n">
-        <v>1166.525262997363</v>
+        <v>1166.598357147647</v>
       </c>
       <c r="F168" t="n">
         <v>3585</v>
@@ -22044,13 +22044,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1151.412882809647</v>
+        <v>1151.51909688279</v>
       </c>
       <c r="D169" t="n">
-        <v>1138.236839186842</v>
+        <v>1138.345557946926</v>
       </c>
       <c r="E169" t="n">
-        <v>1164.588926432452</v>
+        <v>1164.692635818654</v>
       </c>
       <c r="F169" t="n">
         <v>4155</v>
@@ -22191,13 +22191,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1151.226000154089</v>
+        <v>1151.341538417299</v>
       </c>
       <c r="D170" t="n">
-        <v>1135.88567978101</v>
+        <v>1136.005447864728</v>
       </c>
       <c r="E170" t="n">
-        <v>1166.566320527167</v>
+        <v>1166.677628969869</v>
       </c>
       <c r="F170" t="n">
         <v>1679</v>
@@ -22338,13 +22338,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1149.513071381869</v>
+        <v>1149.647968230574</v>
       </c>
       <c r="D171" t="n">
-        <v>1137.255427707771</v>
+        <v>1137.393485685137</v>
       </c>
       <c r="E171" t="n">
-        <v>1161.770715055968</v>
+        <v>1161.902450776011</v>
       </c>
       <c r="F171" t="n">
         <v>2572</v>
@@ -22485,13 +22485,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1148.553951960516</v>
+        <v>1148.645517826745</v>
       </c>
       <c r="D172" t="n">
-        <v>1141.901529062426</v>
+        <v>1141.992835703825</v>
       </c>
       <c r="E172" t="n">
-        <v>1155.206374858605</v>
+        <v>1155.298199949666</v>
       </c>
       <c r="F172" t="n">
         <v>19402</v>
@@ -22636,13 +22636,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1148.452695942355</v>
+        <v>1148.570230333295</v>
       </c>
       <c r="D173" t="n">
-        <v>1139.219359480531</v>
+        <v>1139.339004278426</v>
       </c>
       <c r="E173" t="n">
-        <v>1157.68603240418</v>
+        <v>1157.801456388163</v>
       </c>
       <c r="F173" t="n">
         <v>7044</v>
@@ -22787,13 +22787,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1146.66685933658</v>
+        <v>1146.823271028101</v>
       </c>
       <c r="D174" t="n">
-        <v>1129.596166951592</v>
+        <v>1129.756909029594</v>
       </c>
       <c r="E174" t="n">
-        <v>1163.737551721568</v>
+        <v>1163.889633026609</v>
       </c>
       <c r="F174" t="n">
         <v>1295</v>
@@ -22934,13 +22934,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1143.014124997003</v>
+        <v>1143.11761354775</v>
       </c>
       <c r="D175" t="n">
-        <v>1133.125535134779</v>
+        <v>1133.229284741176</v>
       </c>
       <c r="E175" t="n">
-        <v>1152.902714859227</v>
+        <v>1153.005942354324</v>
       </c>
       <c r="F175" t="n">
         <v>4737</v>
@@ -23085,13 +23085,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1142.259690898371</v>
+        <v>1142.362142749431</v>
       </c>
       <c r="D176" t="n">
-        <v>1135.820058164972</v>
+        <v>1135.921498649002</v>
       </c>
       <c r="E176" t="n">
-        <v>1148.69932363177</v>
+        <v>1148.802786849859</v>
       </c>
       <c r="F176" t="n">
         <v>12297</v>
@@ -23236,13 +23236,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1140.646310585229</v>
+        <v>1140.741271319966</v>
       </c>
       <c r="D177" t="n">
-        <v>1133.920881018855</v>
+        <v>1134.015724875861</v>
       </c>
       <c r="E177" t="n">
-        <v>1147.371740151604</v>
+        <v>1147.466817764071</v>
       </c>
       <c r="F177" t="n">
         <v>19174</v>
@@ -23387,13 +23387,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1140.292985107224</v>
+        <v>1140.428248184629</v>
       </c>
       <c r="D178" t="n">
-        <v>1133.590438552854</v>
+        <v>1133.726180858416</v>
       </c>
       <c r="E178" t="n">
-        <v>1146.995531661594</v>
+        <v>1147.130315510842</v>
       </c>
       <c r="F178" t="n">
         <v>19367</v>
@@ -23534,13 +23534,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1138.003446266433</v>
+        <v>1138.14602355775</v>
       </c>
       <c r="D179" t="n">
-        <v>1127.055861766484</v>
+        <v>1127.199779680333</v>
       </c>
       <c r="E179" t="n">
-        <v>1148.951030766381</v>
+        <v>1149.092267435167</v>
       </c>
       <c r="F179" t="n">
         <v>4964</v>
@@ -23685,13 +23685,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1136.604583217163</v>
+        <v>1136.782803903178</v>
       </c>
       <c r="D180" t="n">
-        <v>1127.113183591854</v>
+        <v>1127.292411595278</v>
       </c>
       <c r="E180" t="n">
-        <v>1146.095982842472</v>
+        <v>1146.273196211077</v>
       </c>
       <c r="F180" t="n">
         <v>8925</v>
@@ -23836,13 +23836,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1135.818506454868</v>
+        <v>1135.933712148703</v>
       </c>
       <c r="D181" t="n">
-        <v>1126.925489280742</v>
+        <v>1127.041404839056</v>
       </c>
       <c r="E181" t="n">
-        <v>1144.711523628994</v>
+        <v>1144.826019458351</v>
       </c>
       <c r="F181" t="n">
         <v>7366</v>
@@ -23987,13 +23987,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1129.947223028809</v>
+        <v>1130.038453627508</v>
       </c>
       <c r="D182" t="n">
-        <v>1121.113798196514</v>
+        <v>1121.205870751858</v>
       </c>
       <c r="E182" t="n">
-        <v>1138.780647861104</v>
+        <v>1138.871036503159</v>
       </c>
       <c r="F182" t="n">
         <v>11118</v>
@@ -24134,13 +24134,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1128.652598737695</v>
+        <v>1128.784307228108</v>
       </c>
       <c r="D183" t="n">
-        <v>1121.227773296898</v>
+        <v>1121.359175906578</v>
       </c>
       <c r="E183" t="n">
-        <v>1136.077424178492</v>
+        <v>1136.209438549639</v>
       </c>
       <c r="F183" t="n">
         <v>20685</v>
@@ -24285,13 +24285,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1127.386420149625</v>
+        <v>1127.470419018172</v>
       </c>
       <c r="D184" t="n">
-        <v>1120.987788614647</v>
+        <v>1121.071115305211</v>
       </c>
       <c r="E184" t="n">
-        <v>1133.785051684602</v>
+        <v>1133.869722731132</v>
       </c>
       <c r="F184" t="n">
         <v>20118</v>
@@ -24436,13 +24436,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1126.415937652052</v>
+        <v>1126.529659418484</v>
       </c>
       <c r="D185" t="n">
-        <v>1114.308200390894</v>
+        <v>1114.425411254086</v>
       </c>
       <c r="E185" t="n">
-        <v>1138.523674913211</v>
+        <v>1138.633907582882</v>
       </c>
       <c r="F185" t="n">
         <v>2921</v>
@@ -24583,13 +24583,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1125.949330538368</v>
+        <v>1126.053774659557</v>
       </c>
       <c r="D186" t="n">
-        <v>1110.335459269238</v>
+        <v>1110.44435843254</v>
       </c>
       <c r="E186" t="n">
-        <v>1141.563201807498</v>
+        <v>1141.663190886574</v>
       </c>
       <c r="F186" t="n">
         <v>1785</v>
@@ -24730,13 +24730,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1120.358988613759</v>
+        <v>1120.493179586912</v>
       </c>
       <c r="D187" t="n">
-        <v>1109.377239940026</v>
+        <v>1109.512706301422</v>
       </c>
       <c r="E187" t="n">
-        <v>1131.340737287492</v>
+        <v>1131.473652872402</v>
       </c>
       <c r="F187" t="n">
         <v>5182</v>
@@ -24877,13 +24877,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1118.345173417529</v>
+        <v>1118.454567032951</v>
       </c>
       <c r="D188" t="n">
-        <v>1100.193629424732</v>
+        <v>1100.307526296979</v>
       </c>
       <c r="E188" t="n">
-        <v>1136.496717410326</v>
+        <v>1136.601607768924</v>
       </c>
       <c r="F188" t="n">
         <v>1143</v>
@@ -25028,13 +25028,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1115.290489185656</v>
+        <v>1115.507591357214</v>
       </c>
       <c r="D189" t="n">
-        <v>1107.560005128725</v>
+        <v>1107.777082241742</v>
       </c>
       <c r="E189" t="n">
-        <v>1123.020973242586</v>
+        <v>1123.238100472686</v>
       </c>
       <c r="F189" t="n">
         <v>10854</v>
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1114.04140244203</v>
+        <v>1114.177546598877</v>
       </c>
       <c r="D190" t="n">
-        <v>1104.895133810278</v>
+        <v>1105.033656582051</v>
       </c>
       <c r="E190" t="n">
-        <v>1123.187671073782</v>
+        <v>1123.321436615702</v>
       </c>
       <c r="F190" t="n">
         <v>6923</v>
@@ -25326,13 +25326,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1113.682560145976</v>
+        <v>1113.801759290102</v>
       </c>
       <c r="D191" t="n">
-        <v>1099.301817389892</v>
+        <v>1099.423366001104</v>
       </c>
       <c r="E191" t="n">
-        <v>1128.063302902059</v>
+        <v>1128.180152579101</v>
       </c>
       <c r="F191" t="n">
         <v>2199</v>
@@ -25473,13 +25473,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1110.460213479393</v>
+        <v>1110.553922125245</v>
       </c>
       <c r="D192" t="n">
-        <v>1102.57755552957</v>
+        <v>1102.670251498107</v>
       </c>
       <c r="E192" t="n">
-        <v>1118.342871429216</v>
+        <v>1118.437592752383</v>
       </c>
       <c r="F192" t="n">
         <v>8045</v>
@@ -25624,13 +25624,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1109.043230272848</v>
+        <v>1109.183629044589</v>
       </c>
       <c r="D193" t="n">
-        <v>1099.758230021275</v>
+        <v>1099.899419693563</v>
       </c>
       <c r="E193" t="n">
-        <v>1118.32823052442</v>
+        <v>1118.467838395615</v>
       </c>
       <c r="F193" t="n">
         <v>8977</v>
@@ -25775,13 +25775,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1107.194490206484</v>
+        <v>1107.280790007184</v>
       </c>
       <c r="D194" t="n">
-        <v>1100.140940638814</v>
+        <v>1100.227224213443</v>
       </c>
       <c r="E194" t="n">
-        <v>1114.248039774155</v>
+        <v>1114.334355800925</v>
       </c>
       <c r="F194" t="n">
         <v>14148</v>
@@ -25926,13 +25926,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1092.349609266924</v>
+        <v>1092.543781295998</v>
       </c>
       <c r="D195" t="n">
-        <v>1080.859811695683</v>
+        <v>1081.055774459804</v>
       </c>
       <c r="E195" t="n">
-        <v>1103.839406838165</v>
+        <v>1104.031788132193</v>
       </c>
       <c r="F195" t="n">
         <v>4780</v>
@@ -26077,13 +26077,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1089.688550379331</v>
+        <v>1089.839975050614</v>
       </c>
       <c r="D196" t="n">
-        <v>1080.35089119126</v>
+        <v>1080.50297730439</v>
       </c>
       <c r="E196" t="n">
-        <v>1099.026209567402</v>
+        <v>1099.176972796837</v>
       </c>
       <c r="F196" t="n">
         <v>7597</v>
@@ -26228,13 +26228,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1073.134544956117</v>
+        <v>1073.189110504645</v>
       </c>
       <c r="D197" t="n">
-        <v>1061.97068050075</v>
+        <v>1062.026961345288</v>
       </c>
       <c r="E197" t="n">
-        <v>1084.298409411484</v>
+        <v>1084.351259664001</v>
       </c>
       <c r="F197" t="n">
         <v>6328</v>
@@ -26379,13 +26379,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1069.736203911552</v>
+        <v>1069.864360420934</v>
       </c>
       <c r="D198" t="n">
-        <v>1059.847003983901</v>
+        <v>1059.97960563949</v>
       </c>
       <c r="E198" t="n">
-        <v>1079.625403839202</v>
+        <v>1079.749115202379</v>
       </c>
       <c r="F198" t="n">
         <v>6965</v>
@@ -26526,13 +26526,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1067.999857506439</v>
+        <v>1068.239905880886</v>
       </c>
       <c r="D199" t="n">
-        <v>1056.538279664763</v>
+        <v>1056.782798196023</v>
       </c>
       <c r="E199" t="n">
-        <v>1079.461435348116</v>
+        <v>1079.697013565748</v>
       </c>
       <c r="F199" t="n">
         <v>5745</v>
@@ -26673,13 +26673,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1065.958099914104</v>
+        <v>1066.14646598371</v>
       </c>
       <c r="D200" t="n">
-        <v>1050.740473985035</v>
+        <v>1050.934029664228</v>
       </c>
       <c r="E200" t="n">
-        <v>1081.175725843173</v>
+        <v>1081.358902303192</v>
       </c>
       <c r="F200" t="n">
         <v>1743</v>
@@ -26820,13 +26820,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1061.753767290887</v>
+        <v>1061.936734429561</v>
       </c>
       <c r="D201" t="n">
-        <v>1049.778442243619</v>
+        <v>1049.965471371426</v>
       </c>
       <c r="E201" t="n">
-        <v>1073.729092338155</v>
+        <v>1073.907997487696</v>
       </c>
       <c r="F201" t="n">
         <v>3924</v>
@@ -26967,13 +26967,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1055.314578995344</v>
+        <v>1055.445122011654</v>
       </c>
       <c r="D202" t="n">
-        <v>1043.651117920881</v>
+        <v>1043.783295044774</v>
       </c>
       <c r="E202" t="n">
-        <v>1066.978040069808</v>
+        <v>1067.106948978534</v>
       </c>
       <c r="F202" t="n">
         <v>4658</v>
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1040.92257637995</v>
+        <v>1041.076149074809</v>
       </c>
       <c r="D203" t="n">
-        <v>1029.531587089981</v>
+        <v>1029.68955970105</v>
       </c>
       <c r="E203" t="n">
-        <v>1052.313565669919</v>
+        <v>1052.462738448568</v>
       </c>
       <c r="F203" t="n">
         <v>4845</v>
@@ -27261,13 +27261,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1023.493469879567</v>
+        <v>1023.628526905701</v>
       </c>
       <c r="D204" t="n">
-        <v>1009.902673223833</v>
+        <v>1010.041004251252</v>
       </c>
       <c r="E204" t="n">
-        <v>1037.084266535301</v>
+        <v>1037.21604956015</v>
       </c>
       <c r="F204" t="n">
         <v>2658</v>
@@ -27408,13 +27408,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1021.878819467545</v>
+        <v>1022.055060337386</v>
       </c>
       <c r="D205" t="n">
-        <v>1011.008609681241</v>
+        <v>1011.189276482593</v>
       </c>
       <c r="E205" t="n">
-        <v>1032.749029253849</v>
+        <v>1032.920844192179</v>
       </c>
       <c r="F205" t="n">
         <v>6310</v>
@@ -27555,13 +27555,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>994.7262750491491</v>
+        <v>994.8430185984512</v>
       </c>
       <c r="D206" t="n">
-        <v>982.1605534986397</v>
+        <v>982.2817625553225</v>
       </c>
       <c r="E206" t="n">
-        <v>1007.291996599658</v>
+        <v>1007.40427464158</v>
       </c>
       <c r="F206" t="n">
         <v>4914</v>
@@ -27702,13 +27702,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>991.0971098063198</v>
+        <v>991.2595713199116</v>
       </c>
       <c r="D207" t="n">
-        <v>978.7253999478132</v>
+        <v>978.8927184523534</v>
       </c>
       <c r="E207" t="n">
-        <v>1003.468819664826</v>
+        <v>1003.62642418747</v>
       </c>
       <c r="F207" t="n">
         <v>4203</v>
@@ -27849,13 +27849,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>980.4215597036718</v>
+        <v>980.643070234544</v>
       </c>
       <c r="D208" t="n">
-        <v>966.8928360947746</v>
+        <v>967.1206487615407</v>
       </c>
       <c r="E208" t="n">
-        <v>993.9502833125689</v>
+        <v>994.1654917075475</v>
       </c>
       <c r="F208" t="n">
         <v>3412</v>
@@ -27996,13 +27996,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>972.9273596435232</v>
+        <v>973.176373072389</v>
       </c>
       <c r="D209" t="n">
-        <v>957.1306617315804</v>
+        <v>957.3883979920415</v>
       </c>
       <c r="E209" t="n">
-        <v>988.7240575554658</v>
+        <v>988.9643481527362</v>
       </c>
       <c r="F209" t="n">
         <v>2391</v>
@@ -28147,13 +28147,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>951.9693471697101</v>
+        <v>952.10198642199</v>
       </c>
       <c r="D210" t="n">
-        <v>939.2412351389871</v>
+        <v>939.3806712745074</v>
       </c>
       <c r="E210" t="n">
-        <v>964.6974592004333</v>
+        <v>964.8233015694727</v>
       </c>
       <c r="F210" t="n">
         <v>3287</v>
@@ -28951,7 +28951,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>glm-5.2 (max)</t>
+          <t>mimo-v2.5-pro</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -28966,7 +28966,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mimo-v2.5-pro</t>
+          <t>glm-5.2 (max)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -29004,23 +29004,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C6" t="n">
-        <v>49</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v4-pro-thinking</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29050,15 +29042,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-thinking</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>deepseek-v4-pro</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C8" t="n">
+        <v>49</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -29134,76 +29134,76 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>397</v>
-      </c>
-      <c r="C12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>glm-4.7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>qwen3.5-397b-a17b</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>397</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gemma-4-26b-a4b</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>26</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v4-flash-thinking</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-thinking</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>gemma-4-26b-a4b</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>26</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -29377,22 +29377,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>550</v>
+      </c>
+      <c r="C25" t="n">
+        <v>55</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -29407,7 +29415,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>deepseek-r1-0528</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -29422,137 +29430,129 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>550</v>
-      </c>
-      <c r="C28" t="n">
-        <v>55</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-r1-0528</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>kimi-k2-0905-preview</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C29" t="n">
+        <v>32</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kimi-k2-0905-preview</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C30" t="n">
-        <v>32</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-terminus-thinking</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C31" t="n">
-        <v>32</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>kimi-k2-0711-preview</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C32" t="n">
+        <v>32</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>122</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>122</v>
-      </c>
-      <c r="C34" t="n">
-        <v>10</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-thinking</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29574,38 +29574,38 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+          <t>mistral-large-3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>675</v>
+      </c>
+      <c r="C36" t="n">
+        <v>41</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>675</v>
-      </c>
-      <c r="C37" t="n">
-        <v>41</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-terminus</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29834,14 +29834,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>35</v>
+        <v>671</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -29850,21 +29850,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="C49" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -30550,14 +30550,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>molmo-2-8b</t>
+          <t>llama-3.3-nemotron-49b-super-v1</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="C84" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -30573,14 +30573,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>llama-3.3-nemotron-49b-super-v1</t>
+          <t>molmo-2-8b</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C85" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -30947,14 +30947,14 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C103" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -30970,14 +30970,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1472.107858361179</v>
+        <v>1471.672948071041</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1467.327732108769</v>
+        <v>1466.921540948978</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1476.887984613589</v>
+        <v>1476.424355193104</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>26549</v>
+        <v>27477</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1466.040224970283</v>
+        <v>1465.546109849084</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1461.42118219284</v>
+        <v>1460.966266207022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1470.659267747726</v>
+        <v>1470.125953491146</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38175</v>
+        <v>39035</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1465.498606884602</v>
+        <v>1465.016666611533</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1459.067636032665</v>
+        <v>1458.726403478197</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1471.929577736539</v>
+        <v>1471.306929744868</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>13442</v>
+        <v>14405</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1461.74068977795</v>
+        <v>1461.744493441397</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1457.123847690291</v>
+        <v>1457.14850147537</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1466.35753186561</v>
+        <v>1466.340485407423</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>35917</v>
+        <v>36683</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1456.7748009375</v>
+        <v>1456.756472879736</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1452.19334566606</v>
+        <v>1452.207546735543</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1461.356256208939</v>
+        <v>1461.305399023928</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>39019</v>
+        <v>39973</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1106,24 +1106,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1456.661454797168</v>
+        <v>1456.710037660649</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1452.299195726941</v>
+        <v>1452.235240424938</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1461.023713867395</v>
+        <v>1461.184834896359</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>27818</v>
+        <v>41995</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>744</v>
+        <v>1600</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1488</v>
+        <v>3200</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1860</v>
+        <v>4000</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>744</v>
+        <v>1600</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>930</v>
+        <v>2000</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>372</v>
+        <v>800</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>465</v>
+        <v>1000</v>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
@@ -1257,24 +1257,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1456.326754938983</v>
+        <v>1456.456468422132</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1451.820052683756</v>
+        <v>1452.094354326606</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1460.833457194211</v>
+        <v>1460.818582517657</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>41017</v>
+        <v>27811</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1299,22 +1299,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3200</v>
+        <v>1488</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4000</v>
+        <v>1860</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>2000</v>
+        <v>930</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>800</v>
+        <v>372</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>1000</v>
+        <v>465</v>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1451.17487305221</v>
+        <v>1451.099272351677</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1443.571316585594</v>
+        <v>1443.494701333768</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1458.778429518825</v>
+        <v>1458.703843369586</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5884</v>
+        <v>5879</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1449.260080720811</v>
+        <v>1449.288998156962</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1445.636972805147</v>
+        <v>1445.681542763508</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1452.883188636474</v>
+        <v>1452.896453550416</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>59062</v>
+        <v>59902</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1445.323397002501</v>
+        <v>1445.123927275271</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1439.793942391817</v>
+        <v>1439.660763303413</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1450.852851613184</v>
+        <v>1450.587091247129</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>23823</v>
+        <v>24727</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1442.510840959521</v>
+        <v>1442.403093356002</v>
       </c>
       <c r="D12" t="n">
-        <v>1436.414280989811</v>
+        <v>1436.307566041849</v>
       </c>
       <c r="E12" t="n">
-        <v>1448.607400929231</v>
+        <v>1448.498620670154</v>
       </c>
       <c r="F12" t="n">
         <v>12103</v>
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1441.909896621309</v>
+        <v>1441.697137608597</v>
       </c>
       <c r="D13" t="n">
-        <v>1438.122835976131</v>
+        <v>1437.931273647885</v>
       </c>
       <c r="E13" t="n">
-        <v>1445.696957266486</v>
+        <v>1445.463001569309</v>
       </c>
       <c r="F13" t="n">
-        <v>54262</v>
+        <v>55130</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1438.54808189884</v>
+        <v>1438.156477099872</v>
       </c>
       <c r="D14" t="n">
-        <v>1434.011317642549</v>
+        <v>1433.656507244368</v>
       </c>
       <c r="E14" t="n">
-        <v>1443.084846155132</v>
+        <v>1442.656446955375</v>
       </c>
       <c r="F14" t="n">
-        <v>40631</v>
+        <v>41586</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2158,16 +2158,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1438.099482499473</v>
+        <v>1438.045129479327</v>
       </c>
       <c r="D15" t="n">
-        <v>1430.461506330393</v>
+        <v>1430.403552164322</v>
       </c>
       <c r="E15" t="n">
-        <v>1445.737458668552</v>
+        <v>1445.686706794331</v>
       </c>
       <c r="F15" t="n">
-        <v>5806</v>
+        <v>5804</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1437.384736721623</v>
+        <v>1437.578738381932</v>
       </c>
       <c r="D16" t="n">
-        <v>1432.893829331606</v>
+        <v>1433.12930984224</v>
       </c>
       <c r="E16" t="n">
-        <v>1441.87564411164</v>
+        <v>1442.028166921624</v>
       </c>
       <c r="F16" t="n">
-        <v>40831</v>
+        <v>41720</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1433.77260907199</v>
+        <v>1433.214059492265</v>
       </c>
       <c r="D17" t="n">
-        <v>1429.199361892539</v>
+        <v>1428.677764799887</v>
       </c>
       <c r="E17" t="n">
-        <v>1438.345856251442</v>
+        <v>1437.750354184643</v>
       </c>
       <c r="F17" t="n">
-        <v>39076</v>
+        <v>39979</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1431.670876976295</v>
+        <v>1431.516713283509</v>
       </c>
       <c r="D18" t="n">
-        <v>1425.085664593789</v>
+        <v>1424.932187793445</v>
       </c>
       <c r="E18" t="n">
-        <v>1438.256089358802</v>
+        <v>1438.101238773573</v>
       </c>
       <c r="F18" t="n">
-        <v>8179</v>
+        <v>8177</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1429.914191972159</v>
+        <v>1429.800099375864</v>
       </c>
       <c r="D19" t="n">
-        <v>1426.755781009987</v>
+        <v>1426.6429156531</v>
       </c>
       <c r="E19" t="n">
-        <v>1433.072602934332</v>
+        <v>1432.957283098628</v>
       </c>
       <c r="F19" t="n">
-        <v>62027</v>
+        <v>62013</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1427.316632455381</v>
+        <v>1427.170573440298</v>
       </c>
       <c r="D20" t="n">
-        <v>1420.727599542166</v>
+        <v>1420.574906266342</v>
       </c>
       <c r="E20" t="n">
-        <v>1433.905665368596</v>
+        <v>1433.766240614253</v>
       </c>
       <c r="F20" t="n">
-        <v>11052</v>
+        <v>11039</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1425.33042964378</v>
+        <v>1425.266044744211</v>
       </c>
       <c r="D21" t="n">
-        <v>1421.411102254845</v>
+        <v>1421.347901304401</v>
       </c>
       <c r="E21" t="n">
-        <v>1429.249757032715</v>
+        <v>1429.184188184021</v>
       </c>
       <c r="F21" t="n">
-        <v>35625</v>
+        <v>35623</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2975,16 +2975,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1425.1691051298</v>
+        <v>1425.098737882064</v>
       </c>
       <c r="D22" t="n">
-        <v>1421.607387210666</v>
+        <v>1421.538754727402</v>
       </c>
       <c r="E22" t="n">
-        <v>1428.730823048934</v>
+        <v>1428.658721036726</v>
       </c>
       <c r="F22" t="n">
-        <v>47243</v>
+        <v>47235</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3046,16 +3046,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1424.798241490018</v>
+        <v>1424.8283772715</v>
       </c>
       <c r="D23" t="n">
-        <v>1418.244993934418</v>
+        <v>1418.274645618229</v>
       </c>
       <c r="E23" t="n">
-        <v>1431.351489045617</v>
+        <v>1431.382108924771</v>
       </c>
       <c r="F23" t="n">
-        <v>9066</v>
+        <v>9064</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3117,16 +3117,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1423.28720459721</v>
+        <v>1423.245956395019</v>
       </c>
       <c r="D24" t="n">
-        <v>1420.693118720603</v>
+        <v>1420.65274501003</v>
       </c>
       <c r="E24" t="n">
-        <v>1425.881290473817</v>
+        <v>1425.839167780008</v>
       </c>
       <c r="F24" t="n">
-        <v>97160</v>
+        <v>97147</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3264,148 +3264,68 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1423.090428562919</v>
+        <v>1423.072916368124</v>
       </c>
       <c r="D25" t="n">
-        <v>1415.995857165341</v>
+        <v>1419.422561302126</v>
       </c>
       <c r="E25" t="n">
-        <v>1430.184999960497</v>
+        <v>1426.723271434122</v>
       </c>
       <c r="F25" t="n">
-        <v>9406</v>
+        <v>41040</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>OpenMDW-1.1</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>550</v>
-      </c>
-      <c r="J25" t="n">
-        <v>55</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>1100</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1375</v>
-      </c>
-      <c r="O25" t="n">
-        <v>550</v>
-      </c>
-      <c r="P25" t="n">
-        <v>687.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>275</v>
-      </c>
-      <c r="R25" t="n">
-        <v>343.8</v>
-      </c>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3415,20 +3335,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1423.061008350877</v>
+        <v>1422.929244740499</v>
       </c>
       <c r="D26" t="n">
-        <v>1419.408604929062</v>
+        <v>1416.524837472568</v>
       </c>
       <c r="E26" t="n">
-        <v>1426.713411772691</v>
+        <v>1429.33365200843</v>
       </c>
       <c r="F26" t="n">
-        <v>41035</v>
+        <v>11918</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3486,68 +3406,148 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1422.853329192755</v>
+        <v>1422.777474358269</v>
       </c>
       <c r="D27" t="n">
-        <v>1416.449659184683</v>
+        <v>1415.675140601522</v>
       </c>
       <c r="E27" t="n">
-        <v>1429.256999200827</v>
+        <v>1429.879808115016</v>
       </c>
       <c r="F27" t="n">
-        <v>11921</v>
+        <v>9678</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>OpenMDW-1.1</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>550</v>
+      </c>
+      <c r="J27" t="n">
+        <v>55</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1100</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1375</v>
+      </c>
+      <c r="O27" t="n">
+        <v>550</v>
+      </c>
+      <c r="P27" t="n">
+        <v>687.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>275</v>
+      </c>
+      <c r="R27" t="n">
+        <v>343.8</v>
+      </c>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3561,16 +3561,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1422.169290048358</v>
+        <v>1422.138414392449</v>
       </c>
       <c r="D28" t="n">
-        <v>1416.507742734381</v>
+        <v>1416.476483895417</v>
       </c>
       <c r="E28" t="n">
-        <v>1427.830837362336</v>
+        <v>1427.800344889482</v>
       </c>
       <c r="F28" t="n">
-        <v>18452</v>
+        <v>18451</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3632,16 +3632,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1417.966472186844</v>
+        <v>1417.995953940472</v>
       </c>
       <c r="D29" t="n">
-        <v>1411.471074641325</v>
+        <v>1411.50005160245</v>
       </c>
       <c r="E29" t="n">
-        <v>1424.461869732363</v>
+        <v>1424.491856278495</v>
       </c>
       <c r="F29" t="n">
-        <v>11774</v>
+        <v>11771</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3783,16 +3783,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1417.841643399433</v>
+        <v>1417.797659472756</v>
       </c>
       <c r="D30" t="n">
-        <v>1407.859555967257</v>
+        <v>1407.819766083966</v>
       </c>
       <c r="E30" t="n">
-        <v>1427.823730831609</v>
+        <v>1427.775552861546</v>
       </c>
       <c r="F30" t="n">
-        <v>3458</v>
+        <v>3461</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1417.605435456909</v>
+        <v>1417.617957308197</v>
       </c>
       <c r="D31" t="n">
-        <v>1411.595073027615</v>
+        <v>1411.607537049387</v>
       </c>
       <c r="E31" t="n">
-        <v>1423.615797886202</v>
+        <v>1423.628377567007</v>
       </c>
       <c r="F31" t="n">
         <v>14945</v>
@@ -3925,16 +3925,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1417.536146206947</v>
+        <v>1417.455980470373</v>
       </c>
       <c r="D32" t="n">
-        <v>1412.675015474713</v>
+        <v>1412.594569602792</v>
       </c>
       <c r="E32" t="n">
-        <v>1422.39727693918</v>
+        <v>1422.317391337954</v>
       </c>
       <c r="F32" t="n">
-        <v>27613</v>
+        <v>27610</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4076,16 +4076,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1417.24172940703</v>
+        <v>1417.130879327484</v>
       </c>
       <c r="D33" t="n">
-        <v>1412.845736188534</v>
+        <v>1412.73620329392</v>
       </c>
       <c r="E33" t="n">
-        <v>1421.637722625526</v>
+        <v>1421.525555361047</v>
       </c>
       <c r="F33" t="n">
-        <v>28517</v>
+        <v>28521</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4227,16 +4227,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1417.128695579876</v>
+        <v>1417.0546476119</v>
       </c>
       <c r="D34" t="n">
-        <v>1410.518531635322</v>
+        <v>1410.443518778945</v>
       </c>
       <c r="E34" t="n">
-        <v>1423.738859524429</v>
+        <v>1423.665776444855</v>
       </c>
       <c r="F34" t="n">
-        <v>11728</v>
+        <v>11727</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4298,16 +4298,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1416.384879951619</v>
+        <v>1416.566833758328</v>
       </c>
       <c r="D35" t="n">
-        <v>1412.118860914579</v>
+        <v>1412.323620750427</v>
       </c>
       <c r="E35" t="n">
-        <v>1420.650898988658</v>
+        <v>1420.810046766228</v>
       </c>
       <c r="F35" t="n">
-        <v>46070</v>
+        <v>46888</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4369,16 +4369,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1416.199923166446</v>
+        <v>1416.243927221239</v>
       </c>
       <c r="D36" t="n">
-        <v>1412.678264229766</v>
+        <v>1412.763784391057</v>
       </c>
       <c r="E36" t="n">
-        <v>1419.721582103127</v>
+        <v>1419.724070051421</v>
       </c>
       <c r="F36" t="n">
-        <v>47096</v>
+        <v>47977</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4520,13 +4520,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1415.489643325521</v>
+        <v>1415.448445239601</v>
       </c>
       <c r="D37" t="n">
-        <v>1405.866545649409</v>
+        <v>1405.825406237269</v>
       </c>
       <c r="E37" t="n">
-        <v>1425.112741001634</v>
+        <v>1425.071484241933</v>
       </c>
       <c r="F37" t="n">
         <v>3692</v>
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1415.427622338126</v>
+        <v>1415.292196382548</v>
       </c>
       <c r="D38" t="n">
-        <v>1408.942943392297</v>
+        <v>1408.807557689727</v>
       </c>
       <c r="E38" t="n">
-        <v>1421.912301283955</v>
+        <v>1421.776835075369</v>
       </c>
       <c r="F38" t="n">
         <v>11499</v>
@@ -4742,16 +4742,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1412.748916492167</v>
+        <v>1412.667620360896</v>
       </c>
       <c r="D39" t="n">
-        <v>1405.205493699792</v>
+        <v>1405.124182656048</v>
       </c>
       <c r="E39" t="n">
-        <v>1420.292339284542</v>
+        <v>1420.211058065743</v>
       </c>
       <c r="F39" t="n">
-        <v>6654</v>
+        <v>6651</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4813,13 +4813,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1410.971205932208</v>
+        <v>1411.027582499246</v>
       </c>
       <c r="D40" t="n">
-        <v>1406.088050835912</v>
+        <v>1406.143698628535</v>
       </c>
       <c r="E40" t="n">
-        <v>1415.854361028505</v>
+        <v>1415.911466369957</v>
       </c>
       <c r="F40" t="n">
         <v>24288</v>
@@ -4964,16 +4964,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1408.653739846502</v>
+        <v>1408.600190582334</v>
       </c>
       <c r="D41" t="n">
-        <v>1404.223858667993</v>
+        <v>1404.172972168452</v>
       </c>
       <c r="E41" t="n">
-        <v>1413.08362102501</v>
+        <v>1413.027408996216</v>
       </c>
       <c r="F41" t="n">
-        <v>27358</v>
+        <v>27351</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1403.181974517327</v>
+        <v>1403.094497946317</v>
       </c>
       <c r="D42" t="n">
-        <v>1398.680103240969</v>
+        <v>1398.592532967</v>
       </c>
       <c r="E42" t="n">
-        <v>1407.683845793686</v>
+        <v>1407.596462925633</v>
       </c>
       <c r="F42" t="n">
-        <v>38184</v>
+        <v>38177</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5266,16 +5266,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1401.465400756505</v>
+        <v>1401.4042663834</v>
       </c>
       <c r="D43" t="n">
-        <v>1396.691414729593</v>
+        <v>1396.629994307515</v>
       </c>
       <c r="E43" t="n">
-        <v>1406.239386783417</v>
+        <v>1406.178538459285</v>
       </c>
       <c r="F43" t="n">
-        <v>22855</v>
+        <v>22853</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5417,16 +5417,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1401.281523431795</v>
+        <v>1401.168478546817</v>
       </c>
       <c r="D44" t="n">
-        <v>1394.91415679475</v>
+        <v>1394.803477683013</v>
       </c>
       <c r="E44" t="n">
-        <v>1407.64889006884</v>
+        <v>1407.533479410621</v>
       </c>
       <c r="F44" t="n">
-        <v>11385</v>
+        <v>11386</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5568,16 +5568,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1399.169496884051</v>
+        <v>1399.16622442724</v>
       </c>
       <c r="D45" t="n">
-        <v>1392.636243366153</v>
+        <v>1392.633498214499</v>
       </c>
       <c r="E45" t="n">
-        <v>1405.702750401949</v>
+        <v>1405.69895063998</v>
       </c>
       <c r="F45" t="n">
-        <v>8988</v>
+        <v>8989</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1398.169620947378</v>
+        <v>1398.124951860277</v>
       </c>
       <c r="D46" t="n">
-        <v>1393.291125231924</v>
+        <v>1393.245964089515</v>
       </c>
       <c r="E46" t="n">
-        <v>1403.048116662831</v>
+        <v>1403.00393963104</v>
       </c>
       <c r="F46" t="n">
         <v>18524</v>
@@ -5866,36 +5866,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1395.736004486441</v>
+        <v>1395.586068857431</v>
       </c>
       <c r="D47" t="n">
-        <v>1388.947724143276</v>
+        <v>1391.712481617209</v>
       </c>
       <c r="E47" t="n">
-        <v>1402.524284829607</v>
+        <v>1399.459656097652</v>
       </c>
       <c r="F47" t="n">
-        <v>7943</v>
+        <v>45480</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>235</v>
+        <v>671</v>
       </c>
       <c r="J47" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5904,26 +5904,26 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>470</v>
+        <v>1342</v>
       </c>
       <c r="N47" t="n">
-        <v>587.5</v>
+        <v>1677.5</v>
       </c>
       <c r="O47" t="n">
-        <v>235</v>
+        <v>671</v>
       </c>
       <c r="P47" t="n">
-        <v>293.8</v>
+        <v>838.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>117.5</v>
+        <v>335.5</v>
       </c>
       <c r="R47" t="n">
-        <v>146.9</v>
+        <v>419.4</v>
       </c>
       <c r="S47" s="5" t="inlineStr">
         <is>
@@ -5980,9 +5980,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE47" s="5" t="inlineStr">
@@ -5995,9 +5995,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG47" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
@@ -6017,36 +6017,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1395.647881213153</v>
+        <v>1395.583417681376</v>
       </c>
       <c r="D48" t="n">
-        <v>1391.774745932824</v>
+        <v>1391.240451537557</v>
       </c>
       <c r="E48" t="n">
-        <v>1399.521016493482</v>
+        <v>1399.926383825194</v>
       </c>
       <c r="F48" t="n">
-        <v>45486</v>
+        <v>29193</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="J48" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6055,40 +6055,40 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>1342</v>
+        <v>70</v>
       </c>
       <c r="N48" t="n">
-        <v>1677.5</v>
+        <v>87.5</v>
       </c>
       <c r="O48" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="P48" t="n">
-        <v>838.8</v>
+        <v>43.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>335.5</v>
+        <v>17.5</v>
       </c>
       <c r="R48" t="n">
-        <v>419.4</v>
-      </c>
-      <c r="S48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>21.9</v>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V48" s="5" t="inlineStr">
@@ -6096,69 +6096,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -6168,20 +6168,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1395.560088899896</v>
+        <v>1395.548479534433</v>
       </c>
       <c r="D49" t="n">
-        <v>1391.215080317346</v>
+        <v>1388.758229752097</v>
       </c>
       <c r="E49" t="n">
-        <v>1399.905097482447</v>
+        <v>1402.338729316769</v>
       </c>
       <c r="F49" t="n">
-        <v>29184</v>
+        <v>7940</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6210,36 +6210,36 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="N49" t="n">
-        <v>87.5</v>
+        <v>587.5</v>
       </c>
       <c r="O49" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="P49" t="n">
-        <v>43.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>17.5</v>
+        <v>117.5</v>
       </c>
       <c r="R49" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="S49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>146.9</v>
+      </c>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V49" s="5" t="inlineStr">
@@ -6247,39 +6247,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD49" s="6" t="inlineStr">
@@ -6287,14 +6287,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG49" s="6" t="inlineStr">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6323,13 +6323,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1395.153586526362</v>
+        <v>1395.123880270044</v>
       </c>
       <c r="D50" t="n">
-        <v>1391.419846506986</v>
+        <v>1391.391573561719</v>
       </c>
       <c r="E50" t="n">
-        <v>1398.887326545737</v>
+        <v>1398.856186978369</v>
       </c>
       <c r="F50" t="n">
         <v>53440</v>
@@ -6394,16 +6394,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1393.063916650281</v>
+        <v>1392.923528333367</v>
       </c>
       <c r="D51" t="n">
-        <v>1389.495338462046</v>
+        <v>1389.355842369048</v>
       </c>
       <c r="E51" t="n">
-        <v>1396.632494838516</v>
+        <v>1396.491214297686</v>
       </c>
       <c r="F51" t="n">
-        <v>46619</v>
+        <v>46608</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6465,16 +6465,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1390.551490069046</v>
+        <v>1390.574867628528</v>
       </c>
       <c r="D52" t="n">
-        <v>1386.551017879804</v>
+        <v>1386.574191026525</v>
       </c>
       <c r="E52" t="n">
-        <v>1394.551962258288</v>
+        <v>1394.575544230531</v>
       </c>
       <c r="F52" t="n">
-        <v>41172</v>
+        <v>41154</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6536,16 +6536,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1387.673635594953</v>
+        <v>1387.630707902755</v>
       </c>
       <c r="D53" t="n">
-        <v>1382.723742339233</v>
+        <v>1382.680877312194</v>
       </c>
       <c r="E53" t="n">
-        <v>1392.623528850673</v>
+        <v>1392.580538493316</v>
       </c>
       <c r="F53" t="n">
-        <v>25692</v>
+        <v>25695</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6687,16 +6687,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1387.146540240597</v>
+        <v>1387.037730461344</v>
       </c>
       <c r="D54" t="n">
-        <v>1380.899910006544</v>
+        <v>1380.791026778163</v>
       </c>
       <c r="E54" t="n">
-        <v>1393.393170474651</v>
+        <v>1393.284434144525</v>
       </c>
       <c r="F54" t="n">
-        <v>10947</v>
+        <v>10946</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6758,16 +6758,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1384.266715272995</v>
+        <v>1384.42705023816</v>
       </c>
       <c r="D55" t="n">
-        <v>1379.039334851279</v>
+        <v>1379.198933600994</v>
       </c>
       <c r="E55" t="n">
-        <v>1389.494095694711</v>
+        <v>1389.655166875326</v>
       </c>
       <c r="F55" t="n">
-        <v>17102</v>
+        <v>17095</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1383.232651074283</v>
+        <v>1383.230886667077</v>
       </c>
       <c r="D56" t="n">
-        <v>1378.3528864988</v>
+        <v>1378.3510704639</v>
       </c>
       <c r="E56" t="n">
-        <v>1388.112415649768</v>
+        <v>1388.110702870253</v>
       </c>
       <c r="F56" t="n">
-        <v>23720</v>
+        <v>23721</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -6980,16 +6980,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1378.636387572678</v>
+        <v>1378.540003352351</v>
       </c>
       <c r="D57" t="n">
-        <v>1374.276733576791</v>
+        <v>1374.182407273405</v>
       </c>
       <c r="E57" t="n">
-        <v>1382.996041568566</v>
+        <v>1382.897599431298</v>
       </c>
       <c r="F57" t="n">
-        <v>30083</v>
+        <v>30101</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
@@ -7127,16 +7127,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1377.276415514598</v>
+        <v>1377.198884109575</v>
       </c>
       <c r="D58" t="n">
-        <v>1366.012803604187</v>
+        <v>1365.941029605857</v>
       </c>
       <c r="E58" t="n">
-        <v>1388.540027425009</v>
+        <v>1388.456738613293</v>
       </c>
       <c r="F58" t="n">
-        <v>2800</v>
+        <v>2802</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7198,16 +7198,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1374.900773403858</v>
+        <v>1374.783927557598</v>
       </c>
       <c r="D59" t="n">
-        <v>1370.207313447591</v>
+        <v>1370.089873949735</v>
       </c>
       <c r="E59" t="n">
-        <v>1379.594233360125</v>
+        <v>1379.477981165462</v>
       </c>
       <c r="F59" t="n">
-        <v>26259</v>
+        <v>26256</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7349,16 +7349,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1373.180585962494</v>
+        <v>1373.049421509118</v>
       </c>
       <c r="D60" t="n">
-        <v>1368.936729717957</v>
+        <v>1368.805646401627</v>
       </c>
       <c r="E60" t="n">
-        <v>1377.424442207031</v>
+        <v>1377.293196616608</v>
       </c>
       <c r="F60" t="n">
-        <v>31061</v>
+        <v>31062</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7420,16 +7420,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1369.627631820962</v>
+        <v>1369.668644305279</v>
       </c>
       <c r="D61" t="n">
-        <v>1363.788376436918</v>
+        <v>1363.829627523533</v>
       </c>
       <c r="E61" t="n">
-        <v>1375.466887205006</v>
+        <v>1375.507661087025</v>
       </c>
       <c r="F61" t="n">
-        <v>13676</v>
+        <v>13679</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7571,16 +7571,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1369.223153814295</v>
+        <v>1369.26704946784</v>
       </c>
       <c r="D62" t="n">
-        <v>1364.52660605285</v>
+        <v>1364.57225860236</v>
       </c>
       <c r="E62" t="n">
-        <v>1373.919701575741</v>
+        <v>1373.961840333321</v>
       </c>
       <c r="F62" t="n">
-        <v>29192</v>
+        <v>29187</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
@@ -7718,16 +7718,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1368.167694949615</v>
+        <v>1368.078119118868</v>
       </c>
       <c r="D63" t="n">
-        <v>1362.36680257171</v>
+        <v>1362.27785151772</v>
       </c>
       <c r="E63" t="n">
-        <v>1373.968587327519</v>
+        <v>1373.878386720015</v>
       </c>
       <c r="F63" t="n">
-        <v>11724</v>
+        <v>11721</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7789,16 +7789,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1365.835200201697</v>
+        <v>1365.790987643491</v>
       </c>
       <c r="D64" t="n">
-        <v>1362.161714874863</v>
+        <v>1362.116633509795</v>
       </c>
       <c r="E64" t="n">
-        <v>1369.508685528532</v>
+        <v>1369.465341777187</v>
       </c>
       <c r="F64" t="n">
-        <v>47514</v>
+        <v>47507</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1363.744901094685</v>
+        <v>1363.780543546181</v>
       </c>
       <c r="D65" t="n">
-        <v>1359.47230965306</v>
+        <v>1359.507861015064</v>
       </c>
       <c r="E65" t="n">
-        <v>1368.017492536311</v>
+        <v>1368.053226077297</v>
       </c>
       <c r="F65" t="n">
-        <v>35170</v>
+        <v>35159</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8011,16 +8011,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1361.425068970003</v>
+        <v>1361.348346266037</v>
       </c>
       <c r="D66" t="n">
-        <v>1354.159874680177</v>
+        <v>1354.084175094292</v>
       </c>
       <c r="E66" t="n">
-        <v>1368.690263259828</v>
+        <v>1368.612517437782</v>
       </c>
       <c r="F66" t="n">
-        <v>7545</v>
+        <v>7548</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8162,13 +8162,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1358.530668707208</v>
+        <v>1358.496513926146</v>
       </c>
       <c r="D67" t="n">
-        <v>1353.788396664972</v>
+        <v>1353.753745830823</v>
       </c>
       <c r="E67" t="n">
-        <v>1363.272940749443</v>
+        <v>1363.239282021469</v>
       </c>
       <c r="F67" t="n">
         <v>21770</v>
@@ -8313,16 +8313,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1357.642562968235</v>
+        <v>1357.613860290777</v>
       </c>
       <c r="D68" t="n">
-        <v>1352.441423677086</v>
+        <v>1352.412391620299</v>
       </c>
       <c r="E68" t="n">
-        <v>1362.843702259384</v>
+        <v>1362.815328961256</v>
       </c>
       <c r="F68" t="n">
-        <v>17699</v>
+        <v>17694</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8384,16 +8384,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1356.325493731292</v>
+        <v>1356.409406884507</v>
       </c>
       <c r="D69" t="n">
-        <v>1347.979912922631</v>
+        <v>1348.067592519338</v>
       </c>
       <c r="E69" t="n">
-        <v>1364.671074539953</v>
+        <v>1364.751221249676</v>
       </c>
       <c r="F69" t="n">
-        <v>5328</v>
+        <v>5331</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
@@ -8531,16 +8531,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1354.006402346084</v>
+        <v>1353.951603596211</v>
       </c>
       <c r="D70" t="n">
-        <v>1350.556897854371</v>
+        <v>1350.501732611165</v>
       </c>
       <c r="E70" t="n">
-        <v>1357.455906837796</v>
+        <v>1357.401474581258</v>
       </c>
       <c r="F70" t="n">
-        <v>56224</v>
+        <v>56218</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8602,16 +8602,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1353.603110112719</v>
+        <v>1353.517011166997</v>
       </c>
       <c r="D71" t="n">
-        <v>1345.25857108704</v>
+        <v>1345.173081804342</v>
       </c>
       <c r="E71" t="n">
-        <v>1361.947649138398</v>
+        <v>1361.860940529653</v>
       </c>
       <c r="F71" t="n">
-        <v>4955</v>
+        <v>4956</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8673,16 +8673,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1352.646285991563</v>
+        <v>1352.619126607712</v>
       </c>
       <c r="D72" t="n">
-        <v>1348.299227162875</v>
+        <v>1348.271257980494</v>
       </c>
       <c r="E72" t="n">
-        <v>1356.993344820252</v>
+        <v>1356.96699523493</v>
       </c>
       <c r="F72" t="n">
-        <v>30628</v>
+        <v>30625</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8824,16 +8824,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1348.396414563652</v>
+        <v>1348.417217837832</v>
       </c>
       <c r="D73" t="n">
-        <v>1340.993250249576</v>
+        <v>1341.014132429662</v>
       </c>
       <c r="E73" t="n">
-        <v>1355.799578877728</v>
+        <v>1355.820303246003</v>
       </c>
       <c r="F73" t="n">
-        <v>6534</v>
+        <v>6533</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8895,13 +8895,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1347.537291228422</v>
+        <v>1347.484271286217</v>
       </c>
       <c r="D74" t="n">
-        <v>1335.851592758297</v>
+        <v>1335.798951615348</v>
       </c>
       <c r="E74" t="n">
-        <v>1359.222989698546</v>
+        <v>1359.169590957087</v>
       </c>
       <c r="F74" t="n">
         <v>2549</v>
@@ -9046,13 +9046,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1347.308024279717</v>
+        <v>1347.251410840752</v>
       </c>
       <c r="D75" t="n">
-        <v>1337.849233277879</v>
+        <v>1337.792798233583</v>
       </c>
       <c r="E75" t="n">
-        <v>1356.766815281555</v>
+        <v>1356.710023447923</v>
       </c>
       <c r="F75" t="n">
         <v>3926</v>
@@ -9197,16 +9197,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1346.290301013577</v>
+        <v>1346.420414556656</v>
       </c>
       <c r="D76" t="n">
-        <v>1339.028077239387</v>
+        <v>1339.159663458981</v>
       </c>
       <c r="E76" t="n">
-        <v>1353.552524787768</v>
+        <v>1353.68116565433</v>
       </c>
       <c r="F76" t="n">
-        <v>7002</v>
+        <v>6999</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9268,16 +9268,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1346.052587611727</v>
+        <v>1346.047709143095</v>
       </c>
       <c r="D77" t="n">
-        <v>1338.314866517933</v>
+        <v>1338.309281107609</v>
       </c>
       <c r="E77" t="n">
-        <v>1353.790308705521</v>
+        <v>1353.786137178581</v>
       </c>
       <c r="F77" t="n">
-        <v>6866</v>
+        <v>6864</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9419,13 +9419,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1343.268595025537</v>
+        <v>1343.221195963104</v>
       </c>
       <c r="D78" t="n">
-        <v>1333.301031274051</v>
+        <v>1333.253760123085</v>
       </c>
       <c r="E78" t="n">
-        <v>1353.236158777022</v>
+        <v>1353.188631803122</v>
       </c>
       <c r="F78" t="n">
         <v>3344</v>
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1341.977847764731</v>
+        <v>1341.915024633812</v>
       </c>
       <c r="D79" t="n">
-        <v>1332.468507928149</v>
+        <v>1332.405667932055</v>
       </c>
       <c r="E79" t="n">
-        <v>1351.487187601312</v>
+        <v>1351.424381335569</v>
       </c>
       <c r="F79" t="n">
         <v>3829</v>
@@ -9721,16 +9721,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1336.26252024527</v>
+        <v>1336.182820290693</v>
       </c>
       <c r="D80" t="n">
-        <v>1331.822396135999</v>
+        <v>1331.742064866195</v>
       </c>
       <c r="E80" t="n">
-        <v>1340.70264435454</v>
+        <v>1340.623575715191</v>
       </c>
       <c r="F80" t="n">
-        <v>25382</v>
+        <v>25377</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9872,13 +9872,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1334.801939804538</v>
+        <v>1334.792531901691</v>
       </c>
       <c r="D81" t="n">
-        <v>1331.089818759892</v>
+        <v>1331.079797469641</v>
       </c>
       <c r="E81" t="n">
-        <v>1338.514060849183</v>
+        <v>1338.50526633374</v>
       </c>
       <c r="F81" t="n">
         <v>41375</v>
@@ -10023,13 +10023,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1332.969406981425</v>
+        <v>1332.957678177016</v>
       </c>
       <c r="D82" t="n">
-        <v>1329.373960434493</v>
+        <v>1329.361851003686</v>
       </c>
       <c r="E82" t="n">
-        <v>1336.564853528359</v>
+        <v>1336.553505350346</v>
       </c>
       <c r="F82" t="n">
         <v>59656</v>
@@ -10174,16 +10174,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1330.206448461898</v>
+        <v>1330.13631594069</v>
       </c>
       <c r="D83" t="n">
-        <v>1324.126051837692</v>
+        <v>1324.056923142583</v>
       </c>
       <c r="E83" t="n">
-        <v>1336.286845086104</v>
+        <v>1336.215708738797</v>
       </c>
       <c r="F83" t="n">
-        <v>12211</v>
+        <v>12213</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10325,13 +10325,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1328.04601222219</v>
+        <v>1327.996359641116</v>
       </c>
       <c r="D84" t="n">
-        <v>1315.897127876131</v>
+        <v>1315.848114913122</v>
       </c>
       <c r="E84" t="n">
-        <v>1340.19489656825</v>
+        <v>1340.144604369111</v>
       </c>
       <c r="F84" t="n">
         <v>2218</v>
@@ -10476,16 +10476,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1328.005448690092</v>
+        <v>1327.947676337901</v>
       </c>
       <c r="D85" t="n">
-        <v>1306.669983161878</v>
+        <v>1306.630791075321</v>
       </c>
       <c r="E85" t="n">
-        <v>1349.340914218306</v>
+        <v>1349.264561600481</v>
       </c>
       <c r="F85" t="n">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -10627,16 +10627,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1327.332326224859</v>
+        <v>1327.258383450149</v>
       </c>
       <c r="D86" t="n">
-        <v>1322.603348428152</v>
+        <v>1322.529395486436</v>
       </c>
       <c r="E86" t="n">
-        <v>1332.061304021567</v>
+        <v>1331.987371413863</v>
       </c>
       <c r="F86" t="n">
-        <v>26474</v>
+        <v>26473</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10778,16 +10778,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1327.091629236379</v>
+        <v>1327.02042437264</v>
       </c>
       <c r="D87" t="n">
-        <v>1322.839630592473</v>
+        <v>1322.768474080633</v>
       </c>
       <c r="E87" t="n">
-        <v>1331.343627880286</v>
+        <v>1331.272374664646</v>
       </c>
       <c r="F87" t="n">
-        <v>39963</v>
+        <v>39958</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10929,13 +10929,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1323.47409372959</v>
+        <v>1323.44385986286</v>
       </c>
       <c r="D88" t="n">
-        <v>1315.203358585569</v>
+        <v>1315.173089228308</v>
       </c>
       <c r="E88" t="n">
-        <v>1331.744828873611</v>
+        <v>1331.714630497412</v>
       </c>
       <c r="F88" t="n">
         <v>6795</v>
@@ -11000,16 +11000,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1322.81181875169</v>
+        <v>1322.771548333306</v>
       </c>
       <c r="D89" t="n">
-        <v>1318.105514675858</v>
+        <v>1318.064081458515</v>
       </c>
       <c r="E89" t="n">
-        <v>1327.518122827523</v>
+        <v>1327.479015208097</v>
       </c>
       <c r="F89" t="n">
-        <v>30280</v>
+        <v>30274</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11151,16 +11151,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1320.680205982145</v>
+        <v>1320.723002927865</v>
       </c>
       <c r="D90" t="n">
-        <v>1313.463550310309</v>
+        <v>1313.506270183975</v>
       </c>
       <c r="E90" t="n">
-        <v>1327.896861653982</v>
+        <v>1327.939735671755</v>
       </c>
       <c r="F90" t="n">
-        <v>7135</v>
+        <v>7136</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -11222,13 +11222,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1318.15072989801</v>
+        <v>1318.15971547526</v>
       </c>
       <c r="D91" t="n">
-        <v>1314.677438943718</v>
+        <v>1314.685922411218</v>
       </c>
       <c r="E91" t="n">
-        <v>1321.624020852303</v>
+        <v>1321.633508539301</v>
       </c>
       <c r="F91" t="n">
         <v>54726</v>
@@ -11373,16 +11373,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1318.121312050259</v>
+        <v>1318.088185979913</v>
       </c>
       <c r="D92" t="n">
-        <v>1312.973917726672</v>
+        <v>1312.940496537035</v>
       </c>
       <c r="E92" t="n">
-        <v>1323.268706373846</v>
+        <v>1323.235875422792</v>
       </c>
       <c r="F92" t="n">
-        <v>22568</v>
+        <v>22565</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -11524,13 +11524,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1317.981924523393</v>
+        <v>1317.958757393124</v>
       </c>
       <c r="D93" t="n">
-        <v>1312.28175006122</v>
+        <v>1312.258436796788</v>
       </c>
       <c r="E93" t="n">
-        <v>1323.682098985566</v>
+        <v>1323.659077989459</v>
       </c>
       <c r="F93" t="n">
         <v>16478</v>
@@ -11595,16 +11595,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1317.430642352258</v>
+        <v>1317.276188931085</v>
       </c>
       <c r="D94" t="n">
-        <v>1311.061803153363</v>
+        <v>1310.906909275714</v>
       </c>
       <c r="E94" t="n">
-        <v>1323.799481551153</v>
+        <v>1323.645468586457</v>
       </c>
       <c r="F94" t="n">
-        <v>10621</v>
+        <v>10622</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11746,16 +11746,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1316.035119784746</v>
+        <v>1315.880694363219</v>
       </c>
       <c r="D95" t="n">
-        <v>1310.491675054855</v>
+        <v>1310.337181986104</v>
       </c>
       <c r="E95" t="n">
-        <v>1321.578564514636</v>
+        <v>1321.424206740334</v>
       </c>
       <c r="F95" t="n">
-        <v>15509</v>
+        <v>15503</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1314.329926956419</v>
+        <v>1314.298763713071</v>
       </c>
       <c r="D96" t="n">
-        <v>1309.777531480716</v>
+        <v>1309.74590462148</v>
       </c>
       <c r="E96" t="n">
-        <v>1318.882322432122</v>
+        <v>1318.851622804662</v>
       </c>
       <c r="F96" t="n">
         <v>24739</v>
@@ -12044,13 +12044,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1314.012736840647</v>
+        <v>1313.994950279209</v>
       </c>
       <c r="D97" t="n">
-        <v>1310.086427351651</v>
+        <v>1310.068338127179</v>
       </c>
       <c r="E97" t="n">
-        <v>1317.939046329643</v>
+        <v>1317.921562431239</v>
       </c>
       <c r="F97" t="n">
         <v>45459</v>
@@ -12191,68 +12191,148 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>deepseek-v2.5</t>
+          <t>granite-4.1-8b</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1307.122206762661</v>
+        <v>1307.268341696438</v>
       </c>
       <c r="D98" t="n">
-        <v>1302.416280085533</v>
+        <v>1297.144291997772</v>
       </c>
       <c r="E98" t="n">
-        <v>1311.828133439788</v>
+        <v>1317.392391395106</v>
       </c>
       <c r="F98" t="n">
-        <v>24572</v>
+        <v>4062</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>8</v>
+      </c>
+      <c r="J98" t="n">
+        <v>8</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
-      <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="inlineStr"/>
-      <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>16</v>
+      </c>
+      <c r="N98" t="n">
+        <v>20</v>
+      </c>
+      <c r="O98" t="n">
+        <v>8</v>
+      </c>
+      <c r="P98" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>4</v>
+      </c>
+      <c r="R98" t="n">
+        <v>5</v>
+      </c>
+      <c r="S98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12262,148 +12342,68 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>granite-4.1-8b</t>
+          <t>deepseek-v2.5</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1307.108993752688</v>
+        <v>1307.093368887914</v>
       </c>
       <c r="D99" t="n">
-        <v>1296.989138600811</v>
+        <v>1302.387171659122</v>
       </c>
       <c r="E99" t="n">
-        <v>1317.228848904566</v>
+        <v>1311.799566116707</v>
       </c>
       <c r="F99" t="n">
-        <v>4067</v>
+        <v>24572</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>8</v>
-      </c>
-      <c r="J99" t="n">
-        <v>8</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M99" t="n">
-        <v>16</v>
-      </c>
-      <c r="N99" t="n">
-        <v>20</v>
-      </c>
-      <c r="O99" t="n">
-        <v>8</v>
-      </c>
-      <c r="P99" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>4</v>
-      </c>
-      <c r="R99" t="n">
-        <v>5</v>
-      </c>
-      <c r="S99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -12417,13 +12417,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1306.353547696021</v>
+        <v>1306.304642275781</v>
       </c>
       <c r="D100" t="n">
-        <v>1300.678851236288</v>
+        <v>1300.629855887289</v>
       </c>
       <c r="E100" t="n">
-        <v>1312.028244155753</v>
+        <v>1311.979428664273</v>
       </c>
       <c r="F100" t="n">
         <v>19621</v>
@@ -12564,16 +12564,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1305.720967433766</v>
+        <v>1305.805251821463</v>
       </c>
       <c r="D101" t="n">
-        <v>1297.544511868982</v>
+        <v>1297.630628021027</v>
       </c>
       <c r="E101" t="n">
-        <v>1313.89742299855</v>
+        <v>1313.979875621899</v>
       </c>
       <c r="F101" t="n">
-        <v>5941</v>
+        <v>5939</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12715,13 +12715,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1305.293631031866</v>
+        <v>1305.271139413529</v>
       </c>
       <c r="D102" t="n">
-        <v>1300.857587685644</v>
+        <v>1300.834503950134</v>
       </c>
       <c r="E102" t="n">
-        <v>1309.729674378089</v>
+        <v>1309.707774876923</v>
       </c>
       <c r="F102" t="n">
         <v>28073</v>
@@ -12782,36 +12782,36 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1303.384706140991</v>
+        <v>1303.324636250603</v>
       </c>
       <c r="D103" t="n">
-        <v>1294.068814703218</v>
+        <v>1298.815667378354</v>
       </c>
       <c r="E103" t="n">
-        <v>1312.700597578764</v>
+        <v>1307.833605122851</v>
       </c>
       <c r="F103" t="n">
-        <v>4171</v>
+        <v>33194</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J103" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -12824,22 +12824,22 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N103" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O103" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P103" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q103" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R103" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="S103" s="6" t="inlineStr">
         <is>
@@ -12933,36 +12933,36 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1303.354293005192</v>
+        <v>1303.323468183375</v>
       </c>
       <c r="D104" t="n">
-        <v>1298.845957373095</v>
+        <v>1294.007588965932</v>
       </c>
       <c r="E104" t="n">
-        <v>1307.862628637289</v>
+        <v>1312.639347400818</v>
       </c>
       <c r="F104" t="n">
-        <v>33199</v>
+        <v>4171</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -12975,22 +12975,22 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N104" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q104" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R104" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="S104" s="6" t="inlineStr">
         <is>
@@ -13088,13 +13088,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1302.832259162798</v>
+        <v>1302.806873181308</v>
       </c>
       <c r="D105" t="n">
-        <v>1298.758731180794</v>
+        <v>1298.732852133951</v>
       </c>
       <c r="E105" t="n">
-        <v>1306.905787144801</v>
+        <v>1306.880894228664</v>
       </c>
       <c r="F105" t="n">
         <v>39406</v>
@@ -13239,13 +13239,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1299.013342467176</v>
+        <v>1298.958790412238</v>
       </c>
       <c r="D106" t="n">
-        <v>1291.250173482085</v>
+        <v>1291.195651095954</v>
       </c>
       <c r="E106" t="n">
-        <v>1306.776511452268</v>
+        <v>1306.721929728522</v>
       </c>
       <c r="F106" t="n">
         <v>7140</v>
@@ -13390,13 +13390,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1293.209073820047</v>
+        <v>1293.166824567864</v>
       </c>
       <c r="D107" t="n">
-        <v>1289.473012749907</v>
+        <v>1289.430338750998</v>
       </c>
       <c r="E107" t="n">
-        <v>1296.945134890186</v>
+        <v>1296.90331038473</v>
       </c>
       <c r="F107" t="n">
         <v>55240</v>
@@ -13541,13 +13541,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1289.046883961437</v>
+        <v>1289.027584484337</v>
       </c>
       <c r="D108" t="n">
-        <v>1281.739234403515</v>
+        <v>1281.719988504022</v>
       </c>
       <c r="E108" t="n">
-        <v>1296.354533519359</v>
+        <v>1296.335180464651</v>
       </c>
       <c r="F108" t="n">
         <v>8662</v>
@@ -13608,13 +13608,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1288.930124148982</v>
+        <v>1288.890715077887</v>
       </c>
       <c r="D109" t="n">
-        <v>1285.548391391217</v>
+        <v>1285.508403341484</v>
       </c>
       <c r="E109" t="n">
-        <v>1292.311856906746</v>
+        <v>1292.273026814291</v>
       </c>
       <c r="F109" t="n">
         <v>75754</v>
@@ -13759,16 +13759,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1286.920363900504</v>
+        <v>1286.960433619754</v>
       </c>
       <c r="D110" t="n">
-        <v>1278.529950705316</v>
+        <v>1278.569875472888</v>
       </c>
       <c r="E110" t="n">
-        <v>1295.310777095691</v>
+        <v>1295.350991766619</v>
       </c>
       <c r="F110" t="n">
-        <v>5681</v>
+        <v>5683</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -13910,13 +13910,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1285.969923101597</v>
+        <v>1285.942702967963</v>
       </c>
       <c r="D111" t="n">
-        <v>1275.501448966889</v>
+        <v>1275.474597862454</v>
       </c>
       <c r="E111" t="n">
-        <v>1296.438397236306</v>
+        <v>1296.410808073473</v>
       </c>
       <c r="F111" t="n">
         <v>2846</v>
@@ -14061,13 +14061,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1285.920473143214</v>
+        <v>1285.908192043848</v>
       </c>
       <c r="D112" t="n">
-        <v>1275.947388069655</v>
+        <v>1275.935343341351</v>
       </c>
       <c r="E112" t="n">
-        <v>1295.893558216773</v>
+        <v>1295.881040746345</v>
       </c>
       <c r="F112" t="n">
         <v>3749</v>
@@ -14212,16 +14212,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1285.088537758943</v>
+        <v>1284.934849922733</v>
       </c>
       <c r="D113" t="n">
-        <v>1277.881669505711</v>
+        <v>1277.723515676013</v>
       </c>
       <c r="E113" t="n">
-        <v>1292.295406012176</v>
+        <v>1292.146184169453</v>
       </c>
       <c r="F113" t="n">
-        <v>8499</v>
+        <v>8494</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -14363,13 +14363,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1279.927938134399</v>
+        <v>1279.878728771763</v>
       </c>
       <c r="D114" t="n">
-        <v>1273.066562246898</v>
+        <v>1273.017417649094</v>
       </c>
       <c r="E114" t="n">
-        <v>1286.789314021901</v>
+        <v>1286.740039894432</v>
       </c>
       <c r="F114" t="n">
         <v>10072</v>
@@ -14510,13 +14510,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1276.520159967032</v>
+        <v>1276.516780710132</v>
       </c>
       <c r="D115" t="n">
-        <v>1271.192387312555</v>
+        <v>1271.189265838786</v>
       </c>
       <c r="E115" t="n">
-        <v>1281.847932621509</v>
+        <v>1281.844295581477</v>
       </c>
       <c r="F115" t="n">
         <v>19659</v>
@@ -14661,13 +14661,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1275.941123167192</v>
+        <v>1275.921630421855</v>
       </c>
       <c r="D116" t="n">
-        <v>1272.351800763617</v>
+        <v>1272.33230963924</v>
       </c>
       <c r="E116" t="n">
-        <v>1279.530445570767</v>
+        <v>1279.510951204469</v>
       </c>
       <c r="F116" t="n">
         <v>156876</v>
@@ -14812,13 +14812,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1275.811703175532</v>
+        <v>1275.802282219134</v>
       </c>
       <c r="D117" t="n">
-        <v>1269.233405485987</v>
+        <v>1269.223968223452</v>
       </c>
       <c r="E117" t="n">
-        <v>1282.390000865078</v>
+        <v>1282.380596214816</v>
       </c>
       <c r="F117" t="n">
         <v>9866</v>
@@ -14963,13 +14963,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1274.11341857605</v>
+        <v>1274.08944906059</v>
       </c>
       <c r="D118" t="n">
-        <v>1268.206617834918</v>
+        <v>1268.18225126169</v>
       </c>
       <c r="E118" t="n">
-        <v>1280.020219317181</v>
+        <v>1279.996646859489</v>
       </c>
       <c r="F118" t="n">
         <v>14681</v>
@@ -15114,13 +15114,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1270.390652830845</v>
+        <v>1270.371619056968</v>
       </c>
       <c r="D119" t="n">
-        <v>1262.262880204433</v>
+        <v>1262.243837615645</v>
       </c>
       <c r="E119" t="n">
-        <v>1278.518425457257</v>
+        <v>1278.49940049829</v>
       </c>
       <c r="F119" t="n">
         <v>5432</v>
@@ -15265,13 +15265,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1266.916315311858</v>
+        <v>1266.885113812122</v>
       </c>
       <c r="D120" t="n">
-        <v>1262.028637965971</v>
+        <v>1261.997014644679</v>
       </c>
       <c r="E120" t="n">
-        <v>1271.803992657746</v>
+        <v>1271.773212979564</v>
       </c>
       <c r="F120" t="n">
         <v>27124</v>
@@ -15416,13 +15416,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1266.442820853938</v>
+        <v>1266.404041966618</v>
       </c>
       <c r="D121" t="n">
-        <v>1262.62417427819</v>
+        <v>1262.584896072565</v>
       </c>
       <c r="E121" t="n">
-        <v>1270.261467429686</v>
+        <v>1270.223187860672</v>
       </c>
       <c r="F121" t="n">
         <v>54611</v>
@@ -15567,13 +15567,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1264.504521219612</v>
+        <v>1264.494199887185</v>
       </c>
       <c r="D122" t="n">
-        <v>1258.222965641233</v>
+        <v>1258.212837293367</v>
       </c>
       <c r="E122" t="n">
-        <v>1270.786076797992</v>
+        <v>1270.775562481003</v>
       </c>
       <c r="F122" t="n">
         <v>15147</v>
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1261.11940013247</v>
+        <v>1261.111467675918</v>
       </c>
       <c r="D123" t="n">
-        <v>1256.170407658561</v>
+        <v>1256.16247892911</v>
       </c>
       <c r="E123" t="n">
-        <v>1266.06839260638</v>
+        <v>1266.060456422726</v>
       </c>
       <c r="F123" t="n">
         <v>37325</v>
@@ -15869,13 +15869,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1261.059124275596</v>
+        <v>1261.061293802424</v>
       </c>
       <c r="D124" t="n">
-        <v>1256.732946005696</v>
+        <v>1256.735303098986</v>
       </c>
       <c r="E124" t="n">
-        <v>1265.385302545496</v>
+        <v>1265.387284505862</v>
       </c>
       <c r="F124" t="n">
         <v>77554</v>
@@ -15940,13 +15940,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1256.046194881889</v>
+        <v>1256.019798493654</v>
       </c>
       <c r="D125" t="n">
-        <v>1251.452946585492</v>
+        <v>1251.426037615709</v>
       </c>
       <c r="E125" t="n">
-        <v>1260.639443178287</v>
+        <v>1260.613559371599</v>
       </c>
       <c r="F125" t="n">
         <v>24126</v>
@@ -16091,13 +16091,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1251.381337964363</v>
+        <v>1251.350734020075</v>
       </c>
       <c r="D126" t="n">
-        <v>1240.598010746335</v>
+        <v>1240.567750973722</v>
       </c>
       <c r="E126" t="n">
-        <v>1262.16466518239</v>
+        <v>1262.133717066429</v>
       </c>
       <c r="F126" t="n">
         <v>3334</v>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1249.653941151953</v>
+        <v>1249.653766752406</v>
       </c>
       <c r="D127" t="n">
-        <v>1243.05109460931</v>
+        <v>1243.050922625743</v>
       </c>
       <c r="E127" t="n">
-        <v>1256.256787694596</v>
+        <v>1256.256610879069</v>
       </c>
       <c r="F127" t="n">
         <v>10140</v>
@@ -16393,13 +16393,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1239.349846451147</v>
+        <v>1239.324705089168</v>
       </c>
       <c r="D128" t="n">
-        <v>1232.121863552891</v>
+        <v>1232.096782099571</v>
       </c>
       <c r="E128" t="n">
-        <v>1246.577829349403</v>
+        <v>1246.552628078764</v>
       </c>
       <c r="F128" t="n">
         <v>8858</v>
@@ -16460,13 +16460,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1237.298057734616</v>
+        <v>1237.277534370494</v>
       </c>
       <c r="D129" t="n">
-        <v>1228.203464567066</v>
+        <v>1228.183187896975</v>
       </c>
       <c r="E129" t="n">
-        <v>1246.392650902166</v>
+        <v>1246.371880844014</v>
       </c>
       <c r="F129" t="n">
         <v>4781</v>
@@ -16611,13 +16611,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1233.484899424981</v>
+        <v>1233.472919552751</v>
       </c>
       <c r="D130" t="n">
-        <v>1227.929414878736</v>
+        <v>1227.917734547796</v>
       </c>
       <c r="E130" t="n">
-        <v>1239.040383971226</v>
+        <v>1239.028104557706</v>
       </c>
       <c r="F130" t="n">
         <v>26195</v>
@@ -16762,13 +16762,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1232.669439926744</v>
+        <v>1232.668933856046</v>
       </c>
       <c r="D131" t="n">
-        <v>1227.392071311897</v>
+        <v>1227.391897349343</v>
       </c>
       <c r="E131" t="n">
-        <v>1237.94680854159</v>
+        <v>1237.945970362749</v>
       </c>
       <c r="F131" t="n">
         <v>39302</v>
@@ -16913,13 +16913,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1228.698684749937</v>
+        <v>1228.703235886949</v>
       </c>
       <c r="D132" t="n">
-        <v>1224.139454958114</v>
+        <v>1224.144104296275</v>
       </c>
       <c r="E132" t="n">
-        <v>1233.257914541759</v>
+        <v>1233.262367477623</v>
       </c>
       <c r="F132" t="n">
         <v>51416</v>
@@ -17064,13 +17064,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1226.049831410564</v>
+        <v>1226.054149922542</v>
       </c>
       <c r="D133" t="n">
-        <v>1221.264703389555</v>
+        <v>1221.269275194123</v>
       </c>
       <c r="E133" t="n">
-        <v>1230.834959431574</v>
+        <v>1230.839024650961</v>
       </c>
       <c r="F133" t="n">
         <v>54036</v>
@@ -17135,13 +17135,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1222.975032649359</v>
+        <v>1222.962099076614</v>
       </c>
       <c r="D134" t="n">
-        <v>1219.235052270617</v>
+        <v>1219.222148913824</v>
       </c>
       <c r="E134" t="n">
-        <v>1226.715013028101</v>
+        <v>1226.702049239404</v>
       </c>
       <c r="F134" t="n">
         <v>104642</v>
@@ -17286,13 +17286,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1222.852504827753</v>
+        <v>1222.819575184984</v>
       </c>
       <c r="D135" t="n">
-        <v>1215.879371617388</v>
+        <v>1215.846218998149</v>
       </c>
       <c r="E135" t="n">
-        <v>1229.825638038117</v>
+        <v>1229.792931371819</v>
       </c>
       <c r="F135" t="n">
         <v>9818</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1220.468468963427</v>
+        <v>1220.436162951269</v>
       </c>
       <c r="D136" t="n">
-        <v>1209.789121796035</v>
+        <v>1209.757072312812</v>
       </c>
       <c r="E136" t="n">
-        <v>1231.147816130819</v>
+        <v>1231.115253589725</v>
       </c>
       <c r="F136" t="n">
         <v>2896</v>
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1212.510911981527</v>
+        <v>1212.497493650781</v>
       </c>
       <c r="D137" t="n">
-        <v>1207.469844925155</v>
+        <v>1207.456621166331</v>
       </c>
       <c r="E137" t="n">
-        <v>1217.551979037898</v>
+        <v>1217.53836613523</v>
       </c>
       <c r="F137" t="n">
         <v>24146</v>
@@ -17735,13 +17735,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1212.116737123765</v>
+        <v>1212.12470771968</v>
       </c>
       <c r="D138" t="n">
-        <v>1201.323150490891</v>
+        <v>1201.331828520795</v>
       </c>
       <c r="E138" t="n">
-        <v>1222.910323756639</v>
+        <v>1222.917586918565</v>
       </c>
       <c r="F138" t="n">
         <v>4652</v>
@@ -17882,13 +17882,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1211.32885833132</v>
+        <v>1211.286880734513</v>
       </c>
       <c r="D139" t="n">
-        <v>1207.178659357499</v>
+        <v>1207.13628574181</v>
       </c>
       <c r="E139" t="n">
-        <v>1215.479057305142</v>
+        <v>1215.437475727217</v>
       </c>
       <c r="F139" t="n">
         <v>49605</v>
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1207.805851643695</v>
+        <v>1207.806784538892</v>
       </c>
       <c r="D140" t="n">
-        <v>1196.701514265998</v>
+        <v>1196.703001964029</v>
       </c>
       <c r="E140" t="n">
-        <v>1218.910189021391</v>
+        <v>1218.910567113756</v>
       </c>
       <c r="F140" t="n">
         <v>3090</v>
@@ -18184,13 +18184,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1203.130688694691</v>
+        <v>1203.134904209963</v>
       </c>
       <c r="D141" t="n">
-        <v>1197.010188864301</v>
+        <v>1197.014723389537</v>
       </c>
       <c r="E141" t="n">
-        <v>1209.251188525082</v>
+        <v>1209.255085030389</v>
       </c>
       <c r="F141" t="n">
         <v>21741</v>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1199.842335997352</v>
+        <v>1199.791270107351</v>
       </c>
       <c r="D142" t="n">
-        <v>1195.749305755851</v>
+        <v>1195.697771390964</v>
       </c>
       <c r="E142" t="n">
-        <v>1203.935366238852</v>
+        <v>1203.884768823739</v>
       </c>
       <c r="F142" t="n">
         <v>46616</v>
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1197.163627400203</v>
+        <v>1197.16691387965</v>
       </c>
       <c r="D143" t="n">
-        <v>1192.001649603543</v>
+        <v>1192.005007154914</v>
       </c>
       <c r="E143" t="n">
-        <v>1202.325605196862</v>
+        <v>1202.328820604387</v>
       </c>
       <c r="F143" t="n">
         <v>25055</v>
@@ -18637,13 +18637,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1196.313012298558</v>
+        <v>1196.318472809937</v>
       </c>
       <c r="D144" t="n">
-        <v>1192.041337390137</v>
+        <v>1192.047119332326</v>
       </c>
       <c r="E144" t="n">
-        <v>1200.58468720698</v>
+        <v>1200.589826287548</v>
       </c>
       <c r="F144" t="n">
         <v>73503</v>
@@ -18788,13 +18788,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1194.488518038758</v>
+        <v>1194.493905594785</v>
       </c>
       <c r="D145" t="n">
-        <v>1188.372808544085</v>
+        <v>1188.378517854811</v>
       </c>
       <c r="E145" t="n">
-        <v>1200.604227533432</v>
+        <v>1200.609293334759</v>
       </c>
       <c r="F145" t="n">
         <v>32191</v>
@@ -18855,13 +18855,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1190.567223873004</v>
+        <v>1190.54133686662</v>
       </c>
       <c r="D146" t="n">
-        <v>1183.382579870451</v>
+        <v>1183.356711411848</v>
       </c>
       <c r="E146" t="n">
-        <v>1197.751867875557</v>
+        <v>1197.725962321392</v>
       </c>
       <c r="F146" t="n">
         <v>9901</v>
@@ -19002,13 +19002,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1190.291193337264</v>
+        <v>1190.290760709918</v>
       </c>
       <c r="D147" t="n">
-        <v>1183.170549227475</v>
+        <v>1183.170562329713</v>
       </c>
       <c r="E147" t="n">
-        <v>1197.411837447052</v>
+        <v>1197.410959090123</v>
       </c>
       <c r="F147" t="n">
         <v>17839</v>
@@ -19153,13 +19153,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1183.90694492753</v>
+        <v>1183.914341479109</v>
       </c>
       <c r="D148" t="n">
-        <v>1174.465890753196</v>
+        <v>1174.474014809586</v>
       </c>
       <c r="E148" t="n">
-        <v>1193.347999101864</v>
+        <v>1193.354668148632</v>
       </c>
       <c r="F148" t="n">
         <v>8214</v>
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1183.849122561442</v>
+        <v>1183.857100892102</v>
       </c>
       <c r="D149" t="n">
-        <v>1172.359281802511</v>
+        <v>1172.368158504372</v>
       </c>
       <c r="E149" t="n">
-        <v>1195.338963320372</v>
+        <v>1195.346043279832</v>
       </c>
       <c r="F149" t="n">
         <v>4932</v>
@@ -19455,13 +19455,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1183.11472232692</v>
+        <v>1183.105074664547</v>
       </c>
       <c r="D150" t="n">
-        <v>1176.285911375211</v>
+        <v>1176.276635302301</v>
       </c>
       <c r="E150" t="n">
-        <v>1189.943533278629</v>
+        <v>1189.933514026793</v>
       </c>
       <c r="F150" t="n">
         <v>15483</v>
@@ -19602,13 +19602,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1181.973075543749</v>
+        <v>1181.979331779985</v>
       </c>
       <c r="D151" t="n">
-        <v>1173.29043100881</v>
+        <v>1173.297045016097</v>
       </c>
       <c r="E151" t="n">
-        <v>1190.655720078689</v>
+        <v>1190.661618543873</v>
       </c>
       <c r="F151" t="n">
         <v>6638</v>
@@ -19753,13 +19753,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1181.866476526116</v>
+        <v>1181.876431516388</v>
       </c>
       <c r="D152" t="n">
-        <v>1172.202790375298</v>
+        <v>1172.213477362877</v>
       </c>
       <c r="E152" t="n">
-        <v>1191.530162676934</v>
+        <v>1191.5393856699</v>
       </c>
       <c r="F152" t="n">
         <v>7968</v>
@@ -19820,13 +19820,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1181.723527045347</v>
+        <v>1181.732778670679</v>
       </c>
       <c r="D153" t="n">
-        <v>1173.727460493775</v>
+        <v>1173.737237629666</v>
       </c>
       <c r="E153" t="n">
-        <v>1189.719593596919</v>
+        <v>1189.728319711693</v>
       </c>
       <c r="F153" t="n">
         <v>12637</v>
@@ -19887,13 +19887,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1181.523271976807</v>
+        <v>1181.497912169561</v>
       </c>
       <c r="D154" t="n">
-        <v>1175.450296622634</v>
+        <v>1175.425183612632</v>
       </c>
       <c r="E154" t="n">
-        <v>1187.59624733098</v>
+        <v>1187.570640726489</v>
       </c>
       <c r="F154" t="n">
         <v>23893</v>
@@ -20038,13 +20038,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1178.979674827644</v>
+        <v>1178.989224791904</v>
       </c>
       <c r="D155" t="n">
-        <v>1173.06546232722</v>
+        <v>1173.075351553203</v>
       </c>
       <c r="E155" t="n">
-        <v>1184.893887328067</v>
+        <v>1184.903098030606</v>
       </c>
       <c r="F155" t="n">
         <v>32832</v>
@@ -20105,13 +20105,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1178.31212589656</v>
+        <v>1178.308675239534</v>
       </c>
       <c r="D156" t="n">
-        <v>1167.118209453152</v>
+        <v>1167.115290178049</v>
       </c>
       <c r="E156" t="n">
-        <v>1189.506042339968</v>
+        <v>1189.502060301019</v>
       </c>
       <c r="F156" t="n">
         <v>3188</v>
@@ -20256,13 +20256,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1176.964035852511</v>
+        <v>1176.968591590176</v>
       </c>
       <c r="D157" t="n">
-        <v>1167.154240881899</v>
+        <v>1167.159476014906</v>
       </c>
       <c r="E157" t="n">
-        <v>1186.773830823122</v>
+        <v>1186.777707165445</v>
       </c>
       <c r="F157" t="n">
         <v>6535</v>
@@ -20403,13 +20403,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1174.815596119469</v>
+        <v>1174.826335864777</v>
       </c>
       <c r="D158" t="n">
-        <v>1164.406458927437</v>
+        <v>1164.41797680344</v>
       </c>
       <c r="E158" t="n">
-        <v>1185.224733311502</v>
+        <v>1185.234694926114</v>
       </c>
       <c r="F158" t="n">
         <v>5006</v>
@@ -20550,13 +20550,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1172.054279733948</v>
+        <v>1172.062851521722</v>
       </c>
       <c r="D159" t="n">
-        <v>1165.850237696839</v>
+        <v>1165.859384358168</v>
       </c>
       <c r="E159" t="n">
-        <v>1178.258321771058</v>
+        <v>1178.266318685277</v>
       </c>
       <c r="F159" t="n">
         <v>22479</v>
@@ -20697,13 +20697,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1170.566015569935</v>
+        <v>1170.575662013345</v>
       </c>
       <c r="D160" t="n">
-        <v>1163.158496118238</v>
+        <v>1163.168601748041</v>
       </c>
       <c r="E160" t="n">
-        <v>1177.973535021632</v>
+        <v>1177.982722278649</v>
       </c>
       <c r="F160" t="n">
         <v>16056</v>
@@ -20844,13 +20844,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1170.33501381519</v>
+        <v>1170.334474643151</v>
       </c>
       <c r="D161" t="n">
-        <v>1164.416732487892</v>
+        <v>1164.416446698781</v>
       </c>
       <c r="E161" t="n">
-        <v>1176.253295142487</v>
+        <v>1176.252502587521</v>
       </c>
       <c r="F161" t="n">
         <v>17766</v>
@@ -20995,13 +20995,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1169.973729615808</v>
+        <v>1169.980247781278</v>
       </c>
       <c r="D162" t="n">
-        <v>1164.472941460883</v>
+        <v>1164.480010926931</v>
       </c>
       <c r="E162" t="n">
-        <v>1175.474517770733</v>
+        <v>1175.480484635625</v>
       </c>
       <c r="F162" t="n">
         <v>38492</v>
@@ -21146,13 +21146,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1166.667404261073</v>
+        <v>1166.674644926863</v>
       </c>
       <c r="D163" t="n">
-        <v>1158.602212898111</v>
+        <v>1158.609996556819</v>
       </c>
       <c r="E163" t="n">
-        <v>1174.732595624035</v>
+        <v>1174.739293296906</v>
       </c>
       <c r="F163" t="n">
         <v>10224</v>
@@ -21293,13 +21293,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1166.187612889471</v>
+        <v>1166.172117514411</v>
       </c>
       <c r="D164" t="n">
-        <v>1158.482473088921</v>
+        <v>1158.467136132861</v>
       </c>
       <c r="E164" t="n">
-        <v>1173.892752690021</v>
+        <v>1173.87709889596</v>
       </c>
       <c r="F164" t="n">
         <v>7936</v>
@@ -21444,13 +21444,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1163.78871414288</v>
+        <v>1163.791021038736</v>
       </c>
       <c r="D165" t="n">
-        <v>1151.87199421171</v>
+        <v>1151.875186281422</v>
       </c>
       <c r="E165" t="n">
-        <v>1175.705434074051</v>
+        <v>1175.706855796049</v>
       </c>
       <c r="F165" t="n">
         <v>3777</v>
@@ -21591,13 +21591,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1155.662492371845</v>
+        <v>1155.66814275337</v>
       </c>
       <c r="D166" t="n">
-        <v>1147.273214938857</v>
+        <v>1147.279220599137</v>
       </c>
       <c r="E166" t="n">
-        <v>1164.051769804835</v>
+        <v>1164.057064907603</v>
       </c>
       <c r="F166" t="n">
         <v>6837</v>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1154.733626663344</v>
+        <v>1154.702912014259</v>
       </c>
       <c r="D167" t="n">
-        <v>1143.240870976528</v>
+        <v>1143.21071890542</v>
       </c>
       <c r="E167" t="n">
-        <v>1166.226382350159</v>
+        <v>1166.195105123099</v>
       </c>
       <c r="F167" t="n">
         <v>3231</v>
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1153.998724869714</v>
+        <v>1153.998831181928</v>
       </c>
       <c r="D168" t="n">
-        <v>1141.399092591781</v>
+        <v>1141.400100398517</v>
       </c>
       <c r="E168" t="n">
-        <v>1166.598357147647</v>
+        <v>1166.597561965339</v>
       </c>
       <c r="F168" t="n">
         <v>3585</v>
@@ -22044,13 +22044,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1151.51909688279</v>
+        <v>1151.525296412222</v>
       </c>
       <c r="D169" t="n">
-        <v>1138.345557946926</v>
+        <v>1138.353077461914</v>
       </c>
       <c r="E169" t="n">
-        <v>1164.692635818654</v>
+        <v>1164.697515362531</v>
       </c>
       <c r="F169" t="n">
         <v>4155</v>
@@ -22191,13 +22191,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1151.341538417299</v>
+        <v>1151.34883897742</v>
       </c>
       <c r="D170" t="n">
-        <v>1136.005447864728</v>
+        <v>1136.014638825219</v>
       </c>
       <c r="E170" t="n">
-        <v>1166.677628969869</v>
+        <v>1166.683039129622</v>
       </c>
       <c r="F170" t="n">
         <v>1679</v>
@@ -22338,13 +22338,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1149.647968230574</v>
+        <v>1149.657078400146</v>
       </c>
       <c r="D171" t="n">
-        <v>1137.393485685137</v>
+        <v>1137.404150654602</v>
       </c>
       <c r="E171" t="n">
-        <v>1161.902450776011</v>
+        <v>1161.910006145691</v>
       </c>
       <c r="F171" t="n">
         <v>2572</v>
@@ -22485,13 +22485,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1148.645517826745</v>
+        <v>1148.65045279641</v>
       </c>
       <c r="D172" t="n">
-        <v>1141.992835703825</v>
+        <v>1141.998153922075</v>
       </c>
       <c r="E172" t="n">
-        <v>1155.298199949666</v>
+        <v>1155.302751670744</v>
       </c>
       <c r="F172" t="n">
         <v>19402</v>
@@ -22636,13 +22636,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1148.570230333295</v>
+        <v>1148.578604740966</v>
       </c>
       <c r="D173" t="n">
-        <v>1139.339004278426</v>
+        <v>1139.348506283676</v>
       </c>
       <c r="E173" t="n">
-        <v>1157.801456388163</v>
+        <v>1157.808703198257</v>
       </c>
       <c r="F173" t="n">
         <v>7044</v>
@@ -22787,13 +22787,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1146.823271028101</v>
+        <v>1146.833351366237</v>
       </c>
       <c r="D174" t="n">
-        <v>1129.756909029594</v>
+        <v>1129.768948755942</v>
       </c>
       <c r="E174" t="n">
-        <v>1163.889633026609</v>
+        <v>1163.897753976532</v>
       </c>
       <c r="F174" t="n">
         <v>1295</v>
@@ -22934,13 +22934,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1143.11761354775</v>
+        <v>1143.118855442564</v>
       </c>
       <c r="D175" t="n">
-        <v>1133.229284741176</v>
+        <v>1133.231065374858</v>
       </c>
       <c r="E175" t="n">
-        <v>1153.005942354324</v>
+        <v>1153.006645510271</v>
       </c>
       <c r="F175" t="n">
         <v>4737</v>
@@ -23085,13 +23085,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1142.362142749431</v>
+        <v>1142.361817623548</v>
       </c>
       <c r="D176" t="n">
-        <v>1135.921498649002</v>
+        <v>1135.92132315212</v>
       </c>
       <c r="E176" t="n">
-        <v>1148.802786849859</v>
+        <v>1148.802312094976</v>
       </c>
       <c r="F176" t="n">
         <v>12297</v>
@@ -23236,13 +23236,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1140.741271319966</v>
+        <v>1140.747869289939</v>
       </c>
       <c r="D177" t="n">
-        <v>1134.015724875861</v>
+        <v>1134.022808542059</v>
       </c>
       <c r="E177" t="n">
-        <v>1147.466817764071</v>
+        <v>1147.47293003782</v>
       </c>
       <c r="F177" t="n">
         <v>19174</v>
@@ -23387,13 +23387,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1140.428248184629</v>
+        <v>1140.436983127641</v>
       </c>
       <c r="D178" t="n">
-        <v>1133.726180858416</v>
+        <v>1133.735621970781</v>
       </c>
       <c r="E178" t="n">
-        <v>1147.130315510842</v>
+        <v>1147.1383442845</v>
       </c>
       <c r="F178" t="n">
         <v>19367</v>
@@ -23534,13 +23534,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1138.14602355775</v>
+        <v>1138.153753250204</v>
       </c>
       <c r="D179" t="n">
-        <v>1127.199779680333</v>
+        <v>1127.208409942293</v>
       </c>
       <c r="E179" t="n">
-        <v>1149.092267435167</v>
+        <v>1149.099096558115</v>
       </c>
       <c r="F179" t="n">
         <v>4964</v>
@@ -23685,13 +23685,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1136.782803903178</v>
+        <v>1136.757512706434</v>
       </c>
       <c r="D180" t="n">
-        <v>1127.292411595278</v>
+        <v>1127.267762264902</v>
       </c>
       <c r="E180" t="n">
-        <v>1146.273196211077</v>
+        <v>1146.247263147966</v>
       </c>
       <c r="F180" t="n">
         <v>8925</v>
@@ -23836,13 +23836,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1135.933712148703</v>
+        <v>1135.943389208142</v>
       </c>
       <c r="D181" t="n">
-        <v>1127.041404839056</v>
+        <v>1127.051784873793</v>
       </c>
       <c r="E181" t="n">
-        <v>1144.826019458351</v>
+        <v>1144.834993542491</v>
       </c>
       <c r="F181" t="n">
         <v>7366</v>
@@ -23987,13 +23987,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1130.038453627508</v>
+        <v>1130.044208932451</v>
       </c>
       <c r="D182" t="n">
-        <v>1121.205870751858</v>
+        <v>1121.212379472544</v>
       </c>
       <c r="E182" t="n">
-        <v>1138.871036503159</v>
+        <v>1138.876038392357</v>
       </c>
       <c r="F182" t="n">
         <v>11118</v>
@@ -24134,13 +24134,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1128.784307228108</v>
+        <v>1128.791828650755</v>
       </c>
       <c r="D183" t="n">
-        <v>1121.359175906578</v>
+        <v>1121.367095809451</v>
       </c>
       <c r="E183" t="n">
-        <v>1136.209438549639</v>
+        <v>1136.216561492058</v>
       </c>
       <c r="F183" t="n">
         <v>20685</v>
@@ -24285,13 +24285,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1127.470419018172</v>
+        <v>1127.473338155882</v>
       </c>
       <c r="D184" t="n">
-        <v>1121.071115305211</v>
+        <v>1121.074326182747</v>
       </c>
       <c r="E184" t="n">
-        <v>1133.869722731132</v>
+        <v>1133.872350129018</v>
       </c>
       <c r="F184" t="n">
         <v>20118</v>
@@ -24436,13 +24436,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1126.529659418484</v>
+        <v>1126.533909247308</v>
       </c>
       <c r="D185" t="n">
-        <v>1114.425411254086</v>
+        <v>1114.431339413602</v>
       </c>
       <c r="E185" t="n">
-        <v>1138.633907582882</v>
+        <v>1138.636479081015</v>
       </c>
       <c r="F185" t="n">
         <v>2921</v>
@@ -24583,13 +24583,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1126.053774659557</v>
+        <v>1126.060382476846</v>
       </c>
       <c r="D186" t="n">
-        <v>1110.44435843254</v>
+        <v>1110.452853672315</v>
       </c>
       <c r="E186" t="n">
-        <v>1141.663190886574</v>
+        <v>1141.667911281378</v>
       </c>
       <c r="F186" t="n">
         <v>1785</v>
@@ -24730,13 +24730,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1120.493179586912</v>
+        <v>1120.501588606252</v>
       </c>
       <c r="D187" t="n">
-        <v>1109.512706301422</v>
+        <v>1109.521975329955</v>
       </c>
       <c r="E187" t="n">
-        <v>1131.473652872402</v>
+        <v>1131.48120188255</v>
       </c>
       <c r="F187" t="n">
         <v>5182</v>
@@ -24877,13 +24877,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1118.454567032951</v>
+        <v>1118.447387079207</v>
       </c>
       <c r="D188" t="n">
-        <v>1100.307526296979</v>
+        <v>1100.30241152268</v>
       </c>
       <c r="E188" t="n">
-        <v>1136.601607768924</v>
+        <v>1136.592362635734</v>
       </c>
       <c r="F188" t="n">
         <v>1143</v>
@@ -25028,13 +25028,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1115.507591357214</v>
+        <v>1115.486390294375</v>
       </c>
       <c r="D189" t="n">
-        <v>1107.777082241742</v>
+        <v>1107.756285615586</v>
       </c>
       <c r="E189" t="n">
-        <v>1123.238100472686</v>
+        <v>1123.216494973165</v>
       </c>
       <c r="F189" t="n">
         <v>10854</v>
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1114.177546598877</v>
+        <v>1114.186497220106</v>
       </c>
       <c r="D190" t="n">
-        <v>1105.033656582051</v>
+        <v>1105.043847686649</v>
       </c>
       <c r="E190" t="n">
-        <v>1123.321436615702</v>
+        <v>1123.329146753562</v>
       </c>
       <c r="F190" t="n">
         <v>6923</v>
@@ -25326,13 +25326,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1113.801759290102</v>
+        <v>1113.803148517482</v>
       </c>
       <c r="D191" t="n">
-        <v>1099.423366001104</v>
+        <v>1099.426072137928</v>
       </c>
       <c r="E191" t="n">
-        <v>1128.180152579101</v>
+        <v>1128.180224897036</v>
       </c>
       <c r="F191" t="n">
         <v>2199</v>
@@ -25473,13 +25473,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1110.553922125245</v>
+        <v>1110.539229590034</v>
       </c>
       <c r="D192" t="n">
-        <v>1102.670251498107</v>
+        <v>1102.655760858699</v>
       </c>
       <c r="E192" t="n">
-        <v>1118.437592752383</v>
+        <v>1118.42269832137</v>
       </c>
       <c r="F192" t="n">
         <v>8045</v>
@@ -25624,13 +25624,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1109.183629044589</v>
+        <v>1109.192208363828</v>
       </c>
       <c r="D193" t="n">
-        <v>1099.899419693563</v>
+        <v>1099.908723819815</v>
       </c>
       <c r="E193" t="n">
-        <v>1118.467838395615</v>
+        <v>1118.475692907841</v>
       </c>
       <c r="F193" t="n">
         <v>8977</v>
@@ -25775,13 +25775,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1107.280790007184</v>
+        <v>1107.29133944473</v>
       </c>
       <c r="D194" t="n">
-        <v>1100.227224213443</v>
+        <v>1100.238231357189</v>
       </c>
       <c r="E194" t="n">
-        <v>1114.334355800925</v>
+        <v>1114.344447532271</v>
       </c>
       <c r="F194" t="n">
         <v>14148</v>
@@ -25926,13 +25926,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1092.543781295998</v>
+        <v>1092.523762426459</v>
       </c>
       <c r="D195" t="n">
-        <v>1081.055774459804</v>
+        <v>1081.036681789333</v>
       </c>
       <c r="E195" t="n">
-        <v>1104.031788132193</v>
+        <v>1104.010843063585</v>
       </c>
       <c r="F195" t="n">
         <v>4780</v>
@@ -26077,13 +26077,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1089.839975050614</v>
+        <v>1089.849228489257</v>
       </c>
       <c r="D196" t="n">
-        <v>1080.50297730439</v>
+        <v>1080.512925353717</v>
       </c>
       <c r="E196" t="n">
-        <v>1099.176972796837</v>
+        <v>1099.185531624797</v>
       </c>
       <c r="F196" t="n">
         <v>7597</v>
@@ -26228,13 +26228,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1073.189110504645</v>
+        <v>1073.191679136571</v>
       </c>
       <c r="D197" t="n">
-        <v>1062.026961345288</v>
+        <v>1062.030507024339</v>
       </c>
       <c r="E197" t="n">
-        <v>1084.351259664001</v>
+        <v>1084.352851248804</v>
       </c>
       <c r="F197" t="n">
         <v>6328</v>
@@ -26379,13 +26379,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1069.864360420934</v>
+        <v>1069.873809789131</v>
       </c>
       <c r="D198" t="n">
-        <v>1059.97960563949</v>
+        <v>1059.991095261403</v>
       </c>
       <c r="E198" t="n">
-        <v>1079.749115202379</v>
+        <v>1079.756524316859</v>
       </c>
       <c r="F198" t="n">
         <v>6965</v>
@@ -26526,13 +26526,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1068.239905880886</v>
+        <v>1068.256045624181</v>
       </c>
       <c r="D199" t="n">
-        <v>1056.782798196023</v>
+        <v>1056.800969114306</v>
       </c>
       <c r="E199" t="n">
-        <v>1079.697013565748</v>
+        <v>1079.711122134055</v>
       </c>
       <c r="F199" t="n">
         <v>5745</v>
@@ -26673,13 +26673,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1066.14646598371</v>
+        <v>1066.159434038247</v>
       </c>
       <c r="D200" t="n">
-        <v>1050.934029664228</v>
+        <v>1050.949347471839</v>
       </c>
       <c r="E200" t="n">
-        <v>1081.358902303192</v>
+        <v>1081.369520604655</v>
       </c>
       <c r="F200" t="n">
         <v>1743</v>
@@ -26820,13 +26820,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1061.936734429561</v>
+        <v>1061.949700436244</v>
       </c>
       <c r="D201" t="n">
-        <v>1049.965471371426</v>
+        <v>1049.980362984059</v>
       </c>
       <c r="E201" t="n">
-        <v>1073.907997487696</v>
+        <v>1073.919037888429</v>
       </c>
       <c r="F201" t="n">
         <v>3924</v>
@@ -26967,13 +26967,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1055.445122011654</v>
+        <v>1055.452151509097</v>
       </c>
       <c r="D202" t="n">
-        <v>1043.783295044774</v>
+        <v>1043.79128350054</v>
       </c>
       <c r="E202" t="n">
-        <v>1067.106948978534</v>
+        <v>1067.113019517653</v>
       </c>
       <c r="F202" t="n">
         <v>4658</v>
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1041.076149074809</v>
+        <v>1041.08747299619</v>
       </c>
       <c r="D203" t="n">
-        <v>1029.68955970105</v>
+        <v>1029.702906647721</v>
       </c>
       <c r="E203" t="n">
-        <v>1052.462738448568</v>
+        <v>1052.472039344659</v>
       </c>
       <c r="F203" t="n">
         <v>4845</v>
@@ -27261,13 +27261,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1023.628526905701</v>
+        <v>1023.636287376222</v>
       </c>
       <c r="D204" t="n">
-        <v>1010.041004251252</v>
+        <v>1010.050320451561</v>
       </c>
       <c r="E204" t="n">
-        <v>1037.21604956015</v>
+        <v>1037.222254300884</v>
       </c>
       <c r="F204" t="n">
         <v>2658</v>
@@ -27408,13 +27408,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1022.055060337386</v>
+        <v>1022.066518535631</v>
       </c>
       <c r="D205" t="n">
-        <v>1011.189276482593</v>
+        <v>1011.202796288272</v>
       </c>
       <c r="E205" t="n">
-        <v>1032.920844192179</v>
+        <v>1032.930240782989</v>
       </c>
       <c r="F205" t="n">
         <v>6310</v>
@@ -27555,13 +27555,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>994.8430185984512</v>
+        <v>994.8509597544144</v>
       </c>
       <c r="D206" t="n">
-        <v>982.2817625553225</v>
+        <v>982.2918085854837</v>
       </c>
       <c r="E206" t="n">
-        <v>1007.40427464158</v>
+        <v>1007.410110923345</v>
       </c>
       <c r="F206" t="n">
         <v>4914</v>
@@ -27702,13 +27702,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>991.2595713199116</v>
+        <v>991.2737070039473</v>
       </c>
       <c r="D207" t="n">
-        <v>978.8927184523534</v>
+        <v>978.9090338157437</v>
       </c>
       <c r="E207" t="n">
-        <v>1003.62642418747</v>
+        <v>1003.638380192151</v>
       </c>
       <c r="F207" t="n">
         <v>4203</v>
@@ -27849,13 +27849,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>980.643070234544</v>
+        <v>980.6581312307271</v>
       </c>
       <c r="D208" t="n">
-        <v>967.1206487615407</v>
+        <v>967.1384871166736</v>
       </c>
       <c r="E208" t="n">
-        <v>994.1654917075475</v>
+        <v>994.1777753447807</v>
       </c>
       <c r="F208" t="n">
         <v>3412</v>
@@ -27996,13 +27996,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>973.176373072389</v>
+        <v>973.1956192927316</v>
       </c>
       <c r="D209" t="n">
-        <v>957.3883979920415</v>
+        <v>957.4112776924085</v>
       </c>
       <c r="E209" t="n">
-        <v>988.9643481527362</v>
+        <v>988.9799608930548</v>
       </c>
       <c r="F209" t="n">
         <v>2391</v>
@@ -28147,13 +28147,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>952.10198642199</v>
+        <v>952.1121568169624</v>
       </c>
       <c r="D210" t="n">
-        <v>939.3806712745074</v>
+        <v>939.3936954940839</v>
       </c>
       <c r="E210" t="n">
-        <v>964.8233015694727</v>
+        <v>964.8306181398411</v>
       </c>
       <c r="F210" t="n">
         <v>3287</v>
@@ -29019,14 +29019,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>744</v>
+        <v>1600</v>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29042,14 +29042,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -29377,30 +29377,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>550</v>
-      </c>
-      <c r="C25" t="n">
-        <v>55</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.2-thinking</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -29415,15 +29407,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>550</v>
+      </c>
+      <c r="C27" t="n">
+        <v>55</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -29811,14 +29811,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>235</v>
+        <v>671</v>
       </c>
       <c r="C47" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -29827,21 +29827,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="C48" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -29850,21 +29850,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -30848,38 +30848,38 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>deepseek-v2.5</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+          <t>granite-4.1-8b</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>8</v>
+      </c>
+      <c r="C98" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>granite-4.1-8b</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>8</v>
-      </c>
-      <c r="C99" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>deepseek-v2.5</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -30947,14 +30947,14 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -30970,14 +30970,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1470.741190058629</v>
+        <v>1469.879131239728</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1466.0425007858</v>
+        <v>1465.270515936197</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1475.439879331458</v>
+        <v>1474.487746543259</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>28606</v>
+        <v>29919</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1468.326397857013</v>
+        <v>1469.53048413241</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1462.178780194774</v>
+        <v>1463.597366201418</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1474.474015519253</v>
+        <v>1475.463602063402</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>15642</v>
+        <v>17103</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1465.245013521255</v>
+        <v>1465.906476799099</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1460.698769368611</v>
+        <v>1461.4236671201</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1469.7912576739</v>
+        <v>1470.389286478097</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>40113</v>
+        <v>41409</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1461.207202252347</v>
+        <v>1461.169439206421</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1456.645504443753</v>
+        <v>1456.623190645149</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1465.76890006094</v>
+        <v>1465.715687767693</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>37507</v>
+        <v>37711</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1039,16 +1039,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1457.588209720437</v>
+        <v>1457.055315100001</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1453.141145465139</v>
+        <v>1452.658857365217</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1462.035273975735</v>
+        <v>1461.451772834785</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>43082</v>
+        <v>44418</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1456.576122296342</v>
+        <v>1456.667578725713</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1452.215534575276</v>
+        <v>1452.308094466471</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1460.936710017409</v>
+        <v>1461.027062984955</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>27814</v>
+        <v>27789</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1456.198282515519</v>
+        <v>1456.005721559645</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1451.675003211997</v>
+        <v>1451.543622501364</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1460.721561819042</v>
+        <v>1460.467820617927</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>40996</v>
+        <v>42294</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1450.994907176639</v>
+        <v>1450.936549214612</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1443.387339545858</v>
+        <v>1443.330198358848</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1458.602474807419</v>
+        <v>1458.542900070375</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>5879</v>
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1449.588045143301</v>
+        <v>1449.170648038773</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1445.994470205402</v>
+        <v>1445.604711356613</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1453.1816200812</v>
+        <v>1452.736584720933</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>60841</v>
+        <v>61978</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1710,36 +1710,36 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>minimax-m3</t>
+          <t>inkling</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1444.770841983863</v>
+        <v>1446.829985345391</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1439.351404747567</v>
+        <v>1438.056192542738</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1450.19027922016</v>
+        <v>1455.603778148045</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>25824</v>
+        <v>4641</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Thinky</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>MiniMax Community License</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>428</v>
+        <v>975</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -1752,22 +1752,22 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>856</v>
+        <v>1950</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1070</v>
+        <v>2437.5</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>428</v>
+        <v>975</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>535</v>
+        <v>1218.8</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>214</v>
+        <v>487.5</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>267.5</v>
+        <v>609.4</v>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
@@ -1839,9 +1839,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
@@ -1861,68 +1861,148 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
+          <t>minimax-m3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1442.21384535901</v>
+        <v>1445.041909803335</v>
       </c>
       <c r="D12" t="n">
-        <v>1436.117933440932</v>
+        <v>1439.717848987121</v>
       </c>
       <c r="E12" t="n">
-        <v>1448.309757277088</v>
+        <v>1450.365970619548</v>
       </c>
       <c r="F12" t="n">
-        <v>12098</v>
+        <v>27238</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>MiniMax Community License</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>428</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>856</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1070</v>
+      </c>
+      <c r="O12" t="n">
+        <v>428</v>
+      </c>
+      <c r="P12" t="n">
+        <v>535</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>214</v>
+      </c>
+      <c r="R12" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF12" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG12" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -1936,16 +2016,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1441.524326079095</v>
+        <v>1442.240477258664</v>
       </c>
       <c r="D13" t="n">
-        <v>1437.775868082254</v>
+        <v>1438.523694294952</v>
       </c>
       <c r="E13" t="n">
-        <v>1445.272784075935</v>
+        <v>1445.957260222375</v>
       </c>
       <c r="F13" t="n">
-        <v>56154</v>
+        <v>57410</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2083,148 +2163,68 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>inkling</t>
+          <t>glm-4.7</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1441.214798387006</v>
+        <v>1442.05871009223</v>
       </c>
       <c r="D14" t="n">
-        <v>1426.548792383121</v>
+        <v>1435.96497214086</v>
       </c>
       <c r="E14" t="n">
-        <v>1455.88080439089</v>
+        <v>1448.152448043601</v>
       </c>
       <c r="F14" t="n">
-        <v>1543</v>
+        <v>12094</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thinky</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>975</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>1950</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2437.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>975</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1218.8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>609.4</v>
-      </c>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1438.189068931017</v>
+        <v>1438.289759291584</v>
       </c>
       <c r="D15" t="n">
-        <v>1433.722568523636</v>
+        <v>1433.882542944215</v>
       </c>
       <c r="E15" t="n">
-        <v>1442.655569338398</v>
+        <v>1442.696975638952</v>
       </c>
       <c r="F15" t="n">
-        <v>42708</v>
+        <v>44034</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1438.012075043768</v>
+        <v>1438.214038403829</v>
       </c>
       <c r="D16" t="n">
-        <v>1430.368493684175</v>
+        <v>1430.571925837276</v>
       </c>
       <c r="E16" t="n">
-        <v>1445.655656403361</v>
+        <v>1445.856150970381</v>
       </c>
       <c r="F16" t="n">
-        <v>5799</v>
+        <v>5798</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1437.553103002854</v>
+        <v>1436.112599595681</v>
       </c>
       <c r="D17" t="n">
-        <v>1433.138414537732</v>
+        <v>1431.769851381784</v>
       </c>
       <c r="E17" t="n">
-        <v>1441.967791467977</v>
+        <v>1440.455347809578</v>
       </c>
       <c r="F17" t="n">
-        <v>42807</v>
+        <v>44220</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1432.470243578171</v>
+        <v>1433.056835517984</v>
       </c>
       <c r="D18" t="n">
-        <v>1427.972214084324</v>
+        <v>1428.606022597143</v>
       </c>
       <c r="E18" t="n">
-        <v>1436.968273072018</v>
+        <v>1437.507648438825</v>
       </c>
       <c r="F18" t="n">
-        <v>41017</v>
+        <v>42281</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1431.441932010222</v>
+        <v>1431.63909978811</v>
       </c>
       <c r="D19" t="n">
-        <v>1424.856931613742</v>
+        <v>1425.054790520431</v>
       </c>
       <c r="E19" t="n">
-        <v>1438.026932406702</v>
+        <v>1438.223409055789</v>
       </c>
       <c r="F19" t="n">
-        <v>8173</v>
+        <v>8177</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1429.716228942487</v>
+        <v>1429.644051745926</v>
       </c>
       <c r="D20" t="n">
-        <v>1426.560260006434</v>
+        <v>1426.489846241231</v>
       </c>
       <c r="E20" t="n">
-        <v>1432.87219787854</v>
+        <v>1432.798257250622</v>
       </c>
       <c r="F20" t="n">
-        <v>61984</v>
+        <v>61948</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2984,16 +2984,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1427.191562428613</v>
+        <v>1427.577871375094</v>
       </c>
       <c r="D21" t="n">
-        <v>1420.595674186827</v>
+        <v>1420.980190337665</v>
       </c>
       <c r="E21" t="n">
-        <v>1433.7874506704</v>
+        <v>1434.175552412522</v>
       </c>
       <c r="F21" t="n">
-        <v>11027</v>
+        <v>11011</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1425.221565518051</v>
+        <v>1425.201154062282</v>
       </c>
       <c r="D22" t="n">
-        <v>1421.303813264249</v>
+        <v>1421.283981912683</v>
       </c>
       <c r="E22" t="n">
-        <v>1429.139317771852</v>
+        <v>1429.118326211882</v>
       </c>
       <c r="F22" t="n">
-        <v>35618</v>
+        <v>35613</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3126,16 +3126,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1425.032367528319</v>
+        <v>1424.89799358709</v>
       </c>
       <c r="D23" t="n">
-        <v>1421.473351979955</v>
+        <v>1421.341148816612</v>
       </c>
       <c r="E23" t="n">
-        <v>1428.591383076683</v>
+        <v>1428.454838357569</v>
       </c>
       <c r="F23" t="n">
-        <v>47215</v>
+        <v>47211</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3197,16 +3197,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1424.880321433039</v>
+        <v>1424.690164768433</v>
       </c>
       <c r="D24" t="n">
-        <v>1418.32940678449</v>
+        <v>1418.137620319972</v>
       </c>
       <c r="E24" t="n">
-        <v>1431.431236081588</v>
+        <v>1431.242709216895</v>
       </c>
       <c r="F24" t="n">
-        <v>9069</v>
+        <v>9067</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3268,16 +3268,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1423.729829557298</v>
+        <v>1424.490243889078</v>
       </c>
       <c r="D25" t="n">
-        <v>1416.645222838009</v>
+        <v>1417.38536843817</v>
       </c>
       <c r="E25" t="n">
-        <v>1430.814436276587</v>
+        <v>1431.595119339985</v>
       </c>
       <c r="F25" t="n">
-        <v>9893</v>
+        <v>10283</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3419,16 +3419,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1423.220042388646</v>
+        <v>1423.128745521466</v>
       </c>
       <c r="D26" t="n">
-        <v>1420.627691089996</v>
+        <v>1420.537900317795</v>
       </c>
       <c r="E26" t="n">
-        <v>1425.812393687296</v>
+        <v>1425.719590725137</v>
       </c>
       <c r="F26" t="n">
-        <v>97141</v>
+        <v>97091</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1422.968460838068</v>
+        <v>1422.928020590283</v>
       </c>
       <c r="D27" t="n">
-        <v>1419.318189951522</v>
+        <v>1419.280720983351</v>
       </c>
       <c r="E27" t="n">
-        <v>1426.618731724615</v>
+        <v>1426.575320197215</v>
       </c>
       <c r="F27" t="n">
-        <v>41030</v>
+        <v>41026</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1422.831805145782</v>
+        <v>1422.703970598666</v>
       </c>
       <c r="D28" t="n">
-        <v>1416.428676685208</v>
+        <v>1416.301137623493</v>
       </c>
       <c r="E28" t="n">
-        <v>1429.234933606356</v>
+        <v>1429.10680357384</v>
       </c>
       <c r="F28" t="n">
-        <v>11915</v>
+        <v>11914</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1422.115850269336</v>
+        <v>1422.051565998299</v>
       </c>
       <c r="D29" t="n">
-        <v>1416.454179191762</v>
+        <v>1416.388909455412</v>
       </c>
       <c r="E29" t="n">
-        <v>1427.77752134691</v>
+        <v>1427.714222541186</v>
       </c>
       <c r="F29" t="n">
         <v>18452</v>
@@ -3783,16 +3783,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1417.870159813935</v>
+        <v>1417.854539850099</v>
       </c>
       <c r="D30" t="n">
-        <v>1411.375128945962</v>
+        <v>1411.358875309422</v>
       </c>
       <c r="E30" t="n">
-        <v>1424.365190681908</v>
+        <v>1424.350204390776</v>
       </c>
       <c r="F30" t="n">
-        <v>11776</v>
+        <v>11771</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3930,29 +3930,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1417.669830126632</v>
+        <v>1417.794714417735</v>
       </c>
       <c r="D31" t="n">
-        <v>1407.690011352975</v>
+        <v>1413.617532906306</v>
       </c>
       <c r="E31" t="n">
-        <v>1427.649648900288</v>
+        <v>1421.971895929164</v>
       </c>
       <c r="F31" t="n">
-        <v>3458</v>
+        <v>49135</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4001,68 +4001,148 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>kimi-k2-0711-preview</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1417.519971950627</v>
+        <v>1417.494372611832</v>
       </c>
       <c r="D32" t="n">
-        <v>1411.512082769735</v>
+        <v>1412.632699552882</v>
       </c>
       <c r="E32" t="n">
-        <v>1423.527861131518</v>
+        <v>1422.356045670781</v>
       </c>
       <c r="F32" t="n">
-        <v>14948</v>
+        <v>27605</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Moonshot</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>32</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1250</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>500</v>
+      </c>
+      <c r="R32" t="n">
+        <v>625</v>
+      </c>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG32" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4072,148 +4152,68 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1417.459903693609</v>
+        <v>1417.467976378082</v>
       </c>
       <c r="D33" t="n">
-        <v>1412.599453609775</v>
+        <v>1411.458140391373</v>
       </c>
       <c r="E33" t="n">
-        <v>1422.320353777444</v>
+        <v>1423.477812364792</v>
       </c>
       <c r="F33" t="n">
-        <v>27610</v>
+        <v>14941</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Moonshot</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J33" t="n">
-        <v>32</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>500</v>
-      </c>
-      <c r="R33" t="n">
-        <v>625</v>
-      </c>
-      <c r="S33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG33" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4223,148 +4223,68 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1417.19462255617</v>
+        <v>1417.388151131344</v>
       </c>
       <c r="D34" t="n">
-        <v>1412.800809610362</v>
+        <v>1407.405002033803</v>
       </c>
       <c r="E34" t="n">
-        <v>1421.588435501977</v>
+        <v>1427.371300228885</v>
       </c>
       <c r="F34" t="n">
-        <v>28523</v>
+        <v>3456</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>122</v>
-      </c>
-      <c r="J34" t="n">
-        <v>10</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>244</v>
-      </c>
-      <c r="N34" t="n">
-        <v>305</v>
-      </c>
-      <c r="O34" t="n">
-        <v>122</v>
-      </c>
-      <c r="P34" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>61</v>
-      </c>
-      <c r="R34" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="S34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE34" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4374,68 +4294,148 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1416.909935502992</v>
+        <v>1417.310745703428</v>
       </c>
       <c r="D35" t="n">
-        <v>1410.300110815945</v>
+        <v>1412.919452342764</v>
       </c>
       <c r="E35" t="n">
-        <v>1423.51976019004</v>
+        <v>1421.702039064092</v>
       </c>
       <c r="F35" t="n">
-        <v>11728</v>
+        <v>28501</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>122</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>244</v>
+      </c>
+      <c r="N35" t="n">
+        <v>305</v>
+      </c>
+      <c r="O35" t="n">
+        <v>122</v>
+      </c>
+      <c r="P35" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>61</v>
+      </c>
+      <c r="R35" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U35" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X35" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA35" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC35" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD35" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE35" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF35" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG35" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -4445,29 +4445,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1416.859152470561</v>
+        <v>1417.013207630177</v>
       </c>
       <c r="D36" t="n">
-        <v>1412.645026798309</v>
+        <v>1410.400984231822</v>
       </c>
       <c r="E36" t="n">
-        <v>1421.073278142812</v>
+        <v>1423.625431028531</v>
       </c>
       <c r="F36" t="n">
-        <v>47935</v>
+        <v>11723</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4520,16 +4520,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1416.172045465663</v>
+        <v>1415.325135314627</v>
       </c>
       <c r="D37" t="n">
-        <v>1412.726638855053</v>
+        <v>1411.923711597329</v>
       </c>
       <c r="E37" t="n">
-        <v>1419.617452076273</v>
+        <v>1418.726559031927</v>
       </c>
       <c r="F37" t="n">
-        <v>48922</v>
+        <v>50153</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1415.408397301467</v>
+        <v>1415.316260620056</v>
       </c>
       <c r="D38" t="n">
-        <v>1408.923765682917</v>
+        <v>1408.829547346817</v>
       </c>
       <c r="E38" t="n">
-        <v>1421.893028920018</v>
+        <v>1421.802973893296</v>
       </c>
       <c r="F38" t="n">
-        <v>11499</v>
+        <v>11498</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1415.354257108836</v>
+        <v>1415.271872557412</v>
       </c>
       <c r="D39" t="n">
-        <v>1405.732602204268</v>
+        <v>1405.647180944011</v>
       </c>
       <c r="E39" t="n">
-        <v>1424.975912013404</v>
+        <v>1424.896564170813</v>
       </c>
       <c r="F39" t="n">
-        <v>3692</v>
+        <v>3690</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1412.209724350023</v>
+        <v>1412.042888024911</v>
       </c>
       <c r="D40" t="n">
-        <v>1404.664423927768</v>
+        <v>1404.491960004872</v>
       </c>
       <c r="E40" t="n">
-        <v>1419.755024772278</v>
+        <v>1419.593816044951</v>
       </c>
       <c r="F40" t="n">
-        <v>6649</v>
+        <v>6637</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4964,16 +4964,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1411.021446053607</v>
+        <v>1410.870087399092</v>
       </c>
       <c r="D41" t="n">
-        <v>1406.138750476487</v>
+        <v>1405.986145399707</v>
       </c>
       <c r="E41" t="n">
-        <v>1415.904141630727</v>
+        <v>1415.754029398477</v>
       </c>
       <c r="F41" t="n">
-        <v>24292</v>
+        <v>24285</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1408.546188057526</v>
+        <v>1408.743226917476</v>
       </c>
       <c r="D42" t="n">
-        <v>1404.121357614388</v>
+        <v>1404.318553391284</v>
       </c>
       <c r="E42" t="n">
-        <v>1412.971018500665</v>
+        <v>1413.167900443668</v>
       </c>
       <c r="F42" t="n">
-        <v>27347</v>
+        <v>27308</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5266,16 +5266,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1403.058485448736</v>
+        <v>1403.026750033887</v>
       </c>
       <c r="D43" t="n">
-        <v>1398.556187022404</v>
+        <v>1398.523105984381</v>
       </c>
       <c r="E43" t="n">
-        <v>1407.560783875068</v>
+        <v>1407.530394083393</v>
       </c>
       <c r="F43" t="n">
-        <v>38178</v>
+        <v>38175</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5417,16 +5417,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1401.448783066975</v>
+        <v>1401.278087167683</v>
       </c>
       <c r="D44" t="n">
-        <v>1396.675246718599</v>
+        <v>1396.502583384474</v>
       </c>
       <c r="E44" t="n">
-        <v>1406.222319415351</v>
+        <v>1406.053590950892</v>
       </c>
       <c r="F44" t="n">
-        <v>22855</v>
+        <v>22853</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5568,16 +5568,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1401.221169990438</v>
+        <v>1401.229497492934</v>
       </c>
       <c r="D45" t="n">
-        <v>1394.854392418434</v>
+        <v>1394.861810842025</v>
       </c>
       <c r="E45" t="n">
-        <v>1407.587947562441</v>
+        <v>1407.597184143844</v>
       </c>
       <c r="F45" t="n">
-        <v>11386</v>
+        <v>11384</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1399.128764836569</v>
+        <v>1399.038625289758</v>
       </c>
       <c r="D46" t="n">
-        <v>1392.59602952962</v>
+        <v>1392.50464720129</v>
       </c>
       <c r="E46" t="n">
-        <v>1405.661500143518</v>
+        <v>1405.572603378226</v>
       </c>
       <c r="F46" t="n">
-        <v>8988</v>
+        <v>8985</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5870,13 +5870,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1398.128859745846</v>
+        <v>1398.100081968736</v>
       </c>
       <c r="D47" t="n">
-        <v>1393.249720364978</v>
+        <v>1393.218954982903</v>
       </c>
       <c r="E47" t="n">
-        <v>1403.007999126713</v>
+        <v>1402.981208954569</v>
       </c>
       <c r="F47" t="n">
         <v>18524</v>
@@ -6017,36 +6017,36 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1395.584691456745</v>
+        <v>1395.727191837466</v>
       </c>
       <c r="D48" t="n">
-        <v>1391.710604815362</v>
+        <v>1391.386585124081</v>
       </c>
       <c r="E48" t="n">
-        <v>1399.458778098128</v>
+        <v>1400.067798550851</v>
       </c>
       <c r="F48" t="n">
-        <v>45480</v>
+        <v>29157</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="J48" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6055,40 +6055,40 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>1342</v>
+        <v>70</v>
       </c>
       <c r="N48" t="n">
-        <v>1677.5</v>
+        <v>87.5</v>
       </c>
       <c r="O48" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="P48" t="n">
-        <v>838.8</v>
+        <v>43.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>335.5</v>
+        <v>17.5</v>
       </c>
       <c r="R48" t="n">
-        <v>419.4</v>
-      </c>
-      <c r="S48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>21.9</v>
+      </c>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V48" s="5" t="inlineStr">
@@ -6096,69 +6096,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG48" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -6168,36 +6168,36 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1395.542820804185</v>
+        <v>1395.509704625214</v>
       </c>
       <c r="D49" t="n">
-        <v>1391.199578894675</v>
+        <v>1391.635015924753</v>
       </c>
       <c r="E49" t="n">
-        <v>1399.886062713695</v>
+        <v>1399.384393325675</v>
       </c>
       <c r="F49" t="n">
-        <v>29179</v>
+        <v>45480</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>35</v>
+        <v>671</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6206,40 +6206,40 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>70</v>
+        <v>1342</v>
       </c>
       <c r="N49" t="n">
-        <v>87.5</v>
+        <v>1677.5</v>
       </c>
       <c r="O49" t="n">
-        <v>35</v>
+        <v>671</v>
       </c>
       <c r="P49" t="n">
-        <v>43.8</v>
+        <v>838.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>17.5</v>
+        <v>335.5</v>
       </c>
       <c r="R49" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="S49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>419.4</v>
+      </c>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V49" s="5" t="inlineStr">
@@ -6247,69 +6247,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG49" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6323,16 +6323,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1395.474068937085</v>
+        <v>1395.429014206356</v>
       </c>
       <c r="D50" t="n">
-        <v>1388.684616158106</v>
+        <v>1388.636389892122</v>
       </c>
       <c r="E50" t="n">
-        <v>1402.263521716063</v>
+        <v>1402.22163852059</v>
       </c>
       <c r="F50" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1395.0798492713</v>
+        <v>1394.933883143331</v>
       </c>
       <c r="D51" t="n">
-        <v>1391.354570780505</v>
+        <v>1391.231640900405</v>
       </c>
       <c r="E51" t="n">
-        <v>1398.805127762095</v>
+        <v>1398.636125386256</v>
       </c>
       <c r="F51" t="n">
-        <v>53963</v>
+        <v>55180</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1392.943214273355</v>
+        <v>1392.80694529516</v>
       </c>
       <c r="D52" t="n">
-        <v>1389.376149141134</v>
+        <v>1389.241916956919</v>
       </c>
       <c r="E52" t="n">
-        <v>1396.510279405576</v>
+        <v>1396.371973633402</v>
       </c>
       <c r="F52" t="n">
-        <v>46583</v>
+        <v>46546</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1390.504951456553</v>
+        <v>1390.567463304082</v>
       </c>
       <c r="D53" t="n">
-        <v>1386.50588540447</v>
+        <v>1386.5704950236</v>
       </c>
       <c r="E53" t="n">
-        <v>1394.504017508636</v>
+        <v>1394.564431584564</v>
       </c>
       <c r="F53" t="n">
-        <v>41138</v>
+        <v>41092</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6687,16 +6687,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1387.613312714702</v>
+        <v>1387.53239677035</v>
       </c>
       <c r="D54" t="n">
-        <v>1382.664046437723</v>
+        <v>1382.583309274739</v>
       </c>
       <c r="E54" t="n">
-        <v>1392.56257899168</v>
+        <v>1392.481484265961</v>
       </c>
       <c r="F54" t="n">
-        <v>25693</v>
+        <v>25694</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6838,16 +6838,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1387.26709040188</v>
+        <v>1387.102448057369</v>
       </c>
       <c r="D55" t="n">
-        <v>1381.018759386523</v>
+        <v>1380.855725443215</v>
       </c>
       <c r="E55" t="n">
-        <v>1393.515421417237</v>
+        <v>1393.349170671524</v>
       </c>
       <c r="F55" t="n">
-        <v>10939</v>
+        <v>10937</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1384.231589473835</v>
+        <v>1384.21773226426</v>
       </c>
       <c r="D56" t="n">
-        <v>1378.999463550722</v>
+        <v>1378.986243352277</v>
       </c>
       <c r="E56" t="n">
-        <v>1389.463715396948</v>
+        <v>1389.449221176243</v>
       </c>
       <c r="F56" t="n">
-        <v>17078</v>
+        <v>17072</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -6980,16 +6980,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1383.122097952955</v>
+        <v>1383.121583952506</v>
       </c>
       <c r="D57" t="n">
-        <v>1378.241918874738</v>
+        <v>1378.239091441849</v>
       </c>
       <c r="E57" t="n">
-        <v>1388.002277031171</v>
+        <v>1388.004076463162</v>
       </c>
       <c r="F57" t="n">
-        <v>23724</v>
+        <v>23715</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7131,16 +7131,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1378.525420715935</v>
+        <v>1378.740864981144</v>
       </c>
       <c r="D58" t="n">
-        <v>1374.168937234709</v>
+        <v>1374.387088625828</v>
       </c>
       <c r="E58" t="n">
-        <v>1382.88190419716</v>
+        <v>1383.094641336459</v>
       </c>
       <c r="F58" t="n">
-        <v>30093</v>
+        <v>30061</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
@@ -7278,16 +7278,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1377.23743000025</v>
+        <v>1377.199854797745</v>
       </c>
       <c r="D59" t="n">
-        <v>1365.986558059211</v>
+        <v>1365.94214135508</v>
       </c>
       <c r="E59" t="n">
-        <v>1388.48830194129</v>
+        <v>1388.457568240409</v>
       </c>
       <c r="F59" t="n">
-        <v>2803</v>
+        <v>2801</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7349,16 +7349,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1374.817322285282</v>
+        <v>1374.755177280887</v>
       </c>
       <c r="D60" t="n">
-        <v>1370.122569284699</v>
+        <v>1370.059113633707</v>
       </c>
       <c r="E60" t="n">
-        <v>1379.512075285864</v>
+        <v>1379.451240928068</v>
       </c>
       <c r="F60" t="n">
-        <v>26259</v>
+        <v>26257</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1373.088058543915</v>
+        <v>1373.079982997584</v>
       </c>
       <c r="D61" t="n">
-        <v>1368.8442830097</v>
+        <v>1368.835236876116</v>
       </c>
       <c r="E61" t="n">
-        <v>1377.331834078131</v>
+        <v>1377.324729119053</v>
       </c>
       <c r="F61" t="n">
-        <v>31063</v>
+        <v>31062</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7571,16 +7571,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1369.637255520228</v>
+        <v>1369.520186991673</v>
       </c>
       <c r="D62" t="n">
-        <v>1363.798083322936</v>
+        <v>1363.680122797909</v>
       </c>
       <c r="E62" t="n">
-        <v>1375.476427717519</v>
+        <v>1375.360251185437</v>
       </c>
       <c r="F62" t="n">
-        <v>13680</v>
+        <v>13678</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7722,16 +7722,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1369.23068161774</v>
+        <v>1369.386447163973</v>
       </c>
       <c r="D63" t="n">
-        <v>1364.538657148125</v>
+        <v>1364.694972410402</v>
       </c>
       <c r="E63" t="n">
-        <v>1373.922706087355</v>
+        <v>1374.077921917544</v>
       </c>
       <c r="F63" t="n">
-        <v>29175</v>
+        <v>29139</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
@@ -7869,16 +7869,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1367.887420016042</v>
+        <v>1367.93138665937</v>
       </c>
       <c r="D64" t="n">
-        <v>1362.085581719861</v>
+        <v>1362.130915570182</v>
       </c>
       <c r="E64" t="n">
-        <v>1373.689258312223</v>
+        <v>1373.731857748557</v>
       </c>
       <c r="F64" t="n">
-        <v>11713</v>
+        <v>11706</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1365.764089138668</v>
+        <v>1365.710682324167</v>
       </c>
       <c r="D65" t="n">
-        <v>1362.089943259725</v>
+        <v>1362.034235256296</v>
       </c>
       <c r="E65" t="n">
-        <v>1369.43823501761</v>
+        <v>1369.387129392039</v>
       </c>
       <c r="F65" t="n">
-        <v>47510</v>
+        <v>47500</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8091,16 +8091,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1363.69123752953</v>
+        <v>1363.754762529222</v>
       </c>
       <c r="D66" t="n">
-        <v>1359.41921302112</v>
+        <v>1359.480593352698</v>
       </c>
       <c r="E66" t="n">
-        <v>1367.963262037941</v>
+        <v>1368.028931705746</v>
       </c>
       <c r="F66" t="n">
-        <v>35159</v>
+        <v>35156</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8162,16 +8162,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1361.516271506313</v>
+        <v>1361.582549581825</v>
       </c>
       <c r="D67" t="n">
-        <v>1354.252477990577</v>
+        <v>1354.318947532643</v>
       </c>
       <c r="E67" t="n">
-        <v>1368.78006502205</v>
+        <v>1368.846151631008</v>
       </c>
       <c r="F67" t="n">
-        <v>7543</v>
+        <v>7542</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8313,13 +8313,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1358.495268520187</v>
+        <v>1358.473581082121</v>
       </c>
       <c r="D68" t="n">
-        <v>1353.752416708176</v>
+        <v>1353.728541658715</v>
       </c>
       <c r="E68" t="n">
-        <v>1363.238120332198</v>
+        <v>1363.218620505528</v>
       </c>
       <c r="F68" t="n">
         <v>21770</v>
@@ -8464,13 +8464,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1357.543543305926</v>
+        <v>1357.525691796576</v>
       </c>
       <c r="D69" t="n">
-        <v>1352.34240506563</v>
+        <v>1352.323565656812</v>
       </c>
       <c r="E69" t="n">
-        <v>1362.744681546223</v>
+        <v>1362.727817936339</v>
       </c>
       <c r="F69" t="n">
         <v>17696</v>
@@ -8535,16 +8535,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1356.21472733715</v>
+        <v>1356.251952365599</v>
       </c>
       <c r="D70" t="n">
-        <v>1347.87204123641</v>
+        <v>1347.909693287186</v>
       </c>
       <c r="E70" t="n">
-        <v>1364.55741343789</v>
+        <v>1364.594211444012</v>
       </c>
       <c r="F70" t="n">
-        <v>5328</v>
+        <v>5327</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
@@ -8682,16 +8682,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1353.957729687173</v>
+        <v>1353.91274354248</v>
       </c>
       <c r="D71" t="n">
-        <v>1350.507820422303</v>
+        <v>1350.461480579952</v>
       </c>
       <c r="E71" t="n">
-        <v>1357.407638952042</v>
+        <v>1357.364006505008</v>
       </c>
       <c r="F71" t="n">
-        <v>56218</v>
+        <v>56224</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8753,16 +8753,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1353.643452262901</v>
+        <v>1353.52977755157</v>
       </c>
       <c r="D72" t="n">
-        <v>1345.299107507602</v>
+        <v>1345.184883851595</v>
       </c>
       <c r="E72" t="n">
-        <v>1361.9877970182</v>
+        <v>1361.874671251546</v>
       </c>
       <c r="F72" t="n">
-        <v>4956</v>
+        <v>4955</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8824,16 +8824,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1352.601726544989</v>
+        <v>1352.512546944002</v>
       </c>
       <c r="D73" t="n">
-        <v>1348.254366863711</v>
+        <v>1348.162781970094</v>
       </c>
       <c r="E73" t="n">
-        <v>1356.949086226267</v>
+        <v>1356.86231191791</v>
       </c>
       <c r="F73" t="n">
-        <v>30629</v>
+        <v>30611</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8975,16 +8975,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1348.314293516044</v>
+        <v>1348.345488463941</v>
       </c>
       <c r="D74" t="n">
-        <v>1340.911544687935</v>
+        <v>1340.940352836867</v>
       </c>
       <c r="E74" t="n">
-        <v>1355.717042344153</v>
+        <v>1355.750624091015</v>
       </c>
       <c r="F74" t="n">
-        <v>6536</v>
+        <v>6533</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9046,13 +9046,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1347.482517592365</v>
+        <v>1347.453960624794</v>
       </c>
       <c r="D75" t="n">
-        <v>1335.798057424099</v>
+        <v>1335.769525788442</v>
       </c>
       <c r="E75" t="n">
-        <v>1359.166977760632</v>
+        <v>1359.138395461147</v>
       </c>
       <c r="F75" t="n">
         <v>2549</v>
@@ -9197,13 +9197,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1347.244956911642</v>
+        <v>1347.192357787633</v>
       </c>
       <c r="D76" t="n">
-        <v>1337.786899696622</v>
+        <v>1337.733915744826</v>
       </c>
       <c r="E76" t="n">
-        <v>1356.703014126661</v>
+        <v>1356.650799830439</v>
       </c>
       <c r="F76" t="n">
         <v>3926</v>
@@ -9348,16 +9348,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1346.331150361284</v>
+        <v>1346.223019693378</v>
       </c>
       <c r="D77" t="n">
-        <v>1339.070030133635</v>
+        <v>1338.959503848691</v>
       </c>
       <c r="E77" t="n">
-        <v>1353.592270588934</v>
+        <v>1353.486535538066</v>
       </c>
       <c r="F77" t="n">
-        <v>7000</v>
+        <v>6998</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9419,16 +9419,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1345.988861981743</v>
+        <v>1346.023223584868</v>
       </c>
       <c r="D78" t="n">
-        <v>1338.250589543681</v>
+        <v>1338.284325044147</v>
       </c>
       <c r="E78" t="n">
-        <v>1353.727134419805</v>
+        <v>1353.762122125589</v>
       </c>
       <c r="F78" t="n">
-        <v>6861</v>
+        <v>6860</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9570,16 +9570,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1343.126741621345</v>
+        <v>1343.157198341073</v>
       </c>
       <c r="D79" t="n">
-        <v>1333.159404838647</v>
+        <v>1333.189913320729</v>
       </c>
       <c r="E79" t="n">
-        <v>1353.094078404042</v>
+        <v>1353.124483361416</v>
       </c>
       <c r="F79" t="n">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -9721,13 +9721,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1341.925543607534</v>
+        <v>1341.872342543547</v>
       </c>
       <c r="D80" t="n">
-        <v>1332.416733606002</v>
+        <v>1332.362864293103</v>
       </c>
       <c r="E80" t="n">
-        <v>1351.434353609066</v>
+        <v>1351.381820793992</v>
       </c>
       <c r="F80" t="n">
         <v>3829</v>
@@ -9872,16 +9872,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1336.234646546191</v>
+        <v>1336.093674137507</v>
       </c>
       <c r="D81" t="n">
-        <v>1331.793762155209</v>
+        <v>1331.651382226096</v>
       </c>
       <c r="E81" t="n">
-        <v>1340.675530937174</v>
+        <v>1340.535966048918</v>
       </c>
       <c r="F81" t="n">
-        <v>25379</v>
+        <v>25376</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -10023,13 +10023,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1334.787733967406</v>
+        <v>1334.810797907552</v>
       </c>
       <c r="D82" t="n">
-        <v>1331.074853007652</v>
+        <v>1331.095207128169</v>
       </c>
       <c r="E82" t="n">
-        <v>1338.500614927161</v>
+        <v>1338.526388686935</v>
       </c>
       <c r="F82" t="n">
         <v>41375</v>
@@ -10174,13 +10174,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1332.955376075629</v>
+        <v>1332.976711191494</v>
       </c>
       <c r="D83" t="n">
-        <v>1329.35978970346</v>
+        <v>1329.378623114978</v>
       </c>
       <c r="E83" t="n">
-        <v>1336.550962447799</v>
+        <v>1336.574799268009</v>
       </c>
       <c r="F83" t="n">
         <v>59656</v>
@@ -10325,16 +10325,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1329.97150062924</v>
+        <v>1329.973502273341</v>
       </c>
       <c r="D84" t="n">
-        <v>1323.891767635931</v>
+        <v>1323.894878850461</v>
       </c>
       <c r="E84" t="n">
-        <v>1336.051233622549</v>
+        <v>1336.052125696221</v>
       </c>
       <c r="F84" t="n">
-        <v>12206</v>
+        <v>12205</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -10476,13 +10476,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1328.767244109529</v>
+        <v>1328.755372914642</v>
       </c>
       <c r="D85" t="n">
-        <v>1307.438199806921</v>
+        <v>1307.430022391315</v>
       </c>
       <c r="E85" t="n">
-        <v>1350.096288412138</v>
+        <v>1350.080723437969</v>
       </c>
       <c r="F85" t="n">
         <v>798</v>
@@ -10627,13 +10627,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1328.006568413876</v>
+        <v>1327.962455047806</v>
       </c>
       <c r="D86" t="n">
-        <v>1315.859643549373</v>
+        <v>1315.815585435525</v>
       </c>
       <c r="E86" t="n">
-        <v>1340.153493278378</v>
+        <v>1340.109324660086</v>
       </c>
       <c r="F86" t="n">
         <v>2218</v>
@@ -10778,16 +10778,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1327.188849933475</v>
+        <v>1327.172982805329</v>
       </c>
       <c r="D87" t="n">
-        <v>1322.460387539165</v>
+        <v>1322.442491969774</v>
       </c>
       <c r="E87" t="n">
-        <v>1331.917312327786</v>
+        <v>1331.903473640885</v>
       </c>
       <c r="F87" t="n">
-        <v>26472</v>
+        <v>26469</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10929,16 +10929,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1327.013067362852</v>
+        <v>1327.040043914698</v>
       </c>
       <c r="D88" t="n">
-        <v>1322.760946820626</v>
+        <v>1322.786091324946</v>
       </c>
       <c r="E88" t="n">
-        <v>1331.265187905079</v>
+        <v>1331.29399650445</v>
       </c>
       <c r="F88" t="n">
-        <v>39954</v>
+        <v>39951</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -11080,13 +11080,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1323.445673731543</v>
+        <v>1323.426458416441</v>
       </c>
       <c r="D89" t="n">
-        <v>1315.175352721092</v>
+        <v>1315.155085070072</v>
       </c>
       <c r="E89" t="n">
-        <v>1331.715994741993</v>
+        <v>1331.697831762809</v>
       </c>
       <c r="F89" t="n">
         <v>6795</v>
@@ -11151,16 +11151,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1322.710560963242</v>
+        <v>1322.796915967902</v>
       </c>
       <c r="D90" t="n">
-        <v>1318.002828625861</v>
+        <v>1318.088699444527</v>
       </c>
       <c r="E90" t="n">
-        <v>1327.418293300623</v>
+        <v>1327.505132491278</v>
       </c>
       <c r="F90" t="n">
-        <v>30276</v>
+        <v>30273</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -11302,16 +11302,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1320.771429202665</v>
+        <v>1320.624087499929</v>
       </c>
       <c r="D91" t="n">
-        <v>1313.557025008755</v>
+        <v>1313.405248617077</v>
       </c>
       <c r="E91" t="n">
-        <v>1327.985833396575</v>
+        <v>1327.842926382781</v>
       </c>
       <c r="F91" t="n">
-        <v>7137</v>
+        <v>7135</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -11373,16 +11373,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1318.160677206813</v>
+        <v>1318.176518006124</v>
       </c>
       <c r="D92" t="n">
-        <v>1314.686291292544</v>
+        <v>1314.699222004554</v>
       </c>
       <c r="E92" t="n">
-        <v>1321.635063121081</v>
+        <v>1321.653814007694</v>
       </c>
       <c r="F92" t="n">
-        <v>54723</v>
+        <v>54720</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -11524,16 +11524,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1318.142322175261</v>
+        <v>1318.040129441017</v>
       </c>
       <c r="D93" t="n">
-        <v>1312.994377182704</v>
+        <v>1312.891686370832</v>
       </c>
       <c r="E93" t="n">
-        <v>1323.290267167817</v>
+        <v>1323.188572511202</v>
       </c>
       <c r="F93" t="n">
-        <v>22571</v>
+        <v>22569</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1317.963973814271</v>
+        <v>1317.957563159107</v>
       </c>
       <c r="D94" t="n">
-        <v>1312.264010639122</v>
+        <v>1312.256142100119</v>
       </c>
       <c r="E94" t="n">
-        <v>1323.663936989418</v>
+        <v>1323.658984218095</v>
       </c>
       <c r="F94" t="n">
         <v>16478</v>
@@ -11746,16 +11746,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1317.192873371657</v>
+        <v>1317.221104840175</v>
       </c>
       <c r="D95" t="n">
-        <v>1310.822736061102</v>
+        <v>1310.850338828237</v>
       </c>
       <c r="E95" t="n">
-        <v>1323.563010682212</v>
+        <v>1323.591870852114</v>
       </c>
       <c r="F95" t="n">
-        <v>10622</v>
+        <v>10620</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -11897,16 +11897,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1315.821783108783</v>
+        <v>1315.560449204706</v>
       </c>
       <c r="D96" t="n">
-        <v>1310.279048442863</v>
+        <v>1310.019751895052</v>
       </c>
       <c r="E96" t="n">
-        <v>1321.364517774703</v>
+        <v>1321.10114651436</v>
       </c>
       <c r="F96" t="n">
-        <v>15500</v>
+        <v>15496</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -12048,13 +12048,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1314.300854535341</v>
+        <v>1314.275557966814</v>
       </c>
       <c r="D97" t="n">
-        <v>1309.747983922328</v>
+        <v>1309.720457344463</v>
       </c>
       <c r="E97" t="n">
-        <v>1318.853725148353</v>
+        <v>1318.830658589165</v>
       </c>
       <c r="F97" t="n">
         <v>24739</v>
@@ -12195,13 +12195,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1313.997796023043</v>
+        <v>1314.007561624775</v>
       </c>
       <c r="D98" t="n">
-        <v>1310.071471397061</v>
+        <v>1310.079021894053</v>
       </c>
       <c r="E98" t="n">
-        <v>1317.924120649026</v>
+        <v>1317.936101355497</v>
       </c>
       <c r="F98" t="n">
         <v>45459</v>
@@ -12342,68 +12342,148 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>deepseek-v2.5</t>
+          <t>granite-4.1-8b</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1307.094534986274</v>
+        <v>1307.430114329379</v>
       </c>
       <c r="D99" t="n">
-        <v>1302.388574849243</v>
+        <v>1297.316414981337</v>
       </c>
       <c r="E99" t="n">
-        <v>1311.800495123306</v>
+        <v>1317.54381367742</v>
       </c>
       <c r="F99" t="n">
-        <v>24572</v>
+        <v>4064</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>8</v>
+      </c>
+      <c r="J99" t="n">
+        <v>8</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
-      <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>16</v>
+      </c>
+      <c r="N99" t="n">
+        <v>20</v>
+      </c>
+      <c r="O99" t="n">
+        <v>8</v>
+      </c>
+      <c r="P99" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>4</v>
+      </c>
+      <c r="R99" t="n">
+        <v>5</v>
+      </c>
+      <c r="S99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG99" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12413,148 +12493,68 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>granite-4.1-8b</t>
+          <t>deepseek-v2.5</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1306.645755603732</v>
+        <v>1307.084285130692</v>
       </c>
       <c r="D100" t="n">
-        <v>1296.515431910697</v>
+        <v>1302.376414594843</v>
       </c>
       <c r="E100" t="n">
-        <v>1316.776079296768</v>
+        <v>1311.79215566654</v>
       </c>
       <c r="F100" t="n">
-        <v>4060</v>
+        <v>24572</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>8</v>
-      </c>
-      <c r="J100" t="n">
-        <v>8</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M100" t="n">
-        <v>16</v>
-      </c>
-      <c r="N100" t="n">
-        <v>20</v>
-      </c>
-      <c r="O100" t="n">
-        <v>8</v>
-      </c>
-      <c r="P100" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>4</v>
-      </c>
-      <c r="R100" t="n">
-        <v>5</v>
-      </c>
-      <c r="S100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG100" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1306.310065636977</v>
+        <v>1306.296123092853</v>
       </c>
       <c r="D101" t="n">
-        <v>1300.635734364681</v>
+        <v>1300.620418235285</v>
       </c>
       <c r="E101" t="n">
-        <v>1311.984396909273</v>
+        <v>1311.971827950421</v>
       </c>
       <c r="F101" t="n">
         <v>19621</v>
@@ -12715,16 +12715,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1305.673754218564</v>
+        <v>1305.562240763531</v>
       </c>
       <c r="D102" t="n">
-        <v>1297.497149477764</v>
+        <v>1297.384780669159</v>
       </c>
       <c r="E102" t="n">
-        <v>1313.850358959365</v>
+        <v>1313.739700857903</v>
       </c>
       <c r="F102" t="n">
-        <v>5939</v>
+        <v>5938</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -12866,13 +12866,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1305.272610268241</v>
+        <v>1305.271458751643</v>
       </c>
       <c r="D103" t="n">
-        <v>1300.83577439751</v>
+        <v>1300.832170817371</v>
       </c>
       <c r="E103" t="n">
-        <v>1309.709446138972</v>
+        <v>1309.710746685914</v>
       </c>
       <c r="F103" t="n">
         <v>28073</v>
@@ -12933,36 +12933,36 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1303.331142422341</v>
+        <v>1303.289010297977</v>
       </c>
       <c r="D104" t="n">
-        <v>1294.015760167415</v>
+        <v>1298.77941415298</v>
       </c>
       <c r="E104" t="n">
-        <v>1312.646524677267</v>
+        <v>1307.798606442974</v>
       </c>
       <c r="F104" t="n">
-        <v>4171</v>
+        <v>33194</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -12975,22 +12975,22 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N104" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P104" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q104" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R104" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="S104" s="6" t="inlineStr">
         <is>
@@ -13084,36 +13084,36 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1303.263282497484</v>
+        <v>1303.283904155892</v>
       </c>
       <c r="D105" t="n">
-        <v>1298.75491735912</v>
+        <v>1293.967913829794</v>
       </c>
       <c r="E105" t="n">
-        <v>1307.771647635847</v>
+        <v>1312.599894481991</v>
       </c>
       <c r="F105" t="n">
-        <v>33196</v>
+        <v>4171</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -13126,22 +13126,22 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N105" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O105" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P105" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q105" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R105" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="S105" s="6" t="inlineStr">
         <is>
@@ -13239,13 +13239,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1302.812235284832</v>
+        <v>1302.800229358561</v>
       </c>
       <c r="D106" t="n">
-        <v>1298.738246446989</v>
+        <v>1298.723736842753</v>
       </c>
       <c r="E106" t="n">
-        <v>1306.886224122674</v>
+        <v>1306.876721874369</v>
       </c>
       <c r="F106" t="n">
         <v>39406</v>
@@ -13390,13 +13390,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1298.975557559272</v>
+        <v>1298.929944664778</v>
       </c>
       <c r="D107" t="n">
-        <v>1291.212922328498</v>
+        <v>1291.166318776369</v>
       </c>
       <c r="E107" t="n">
-        <v>1306.738192790046</v>
+        <v>1306.693570553188</v>
       </c>
       <c r="F107" t="n">
         <v>7140</v>
@@ -13541,13 +13541,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1293.164339709684</v>
+        <v>1293.148439937676</v>
       </c>
       <c r="D108" t="n">
-        <v>1289.428041332737</v>
+        <v>1289.409617448781</v>
       </c>
       <c r="E108" t="n">
-        <v>1296.90063808663</v>
+        <v>1296.887262426572</v>
       </c>
       <c r="F108" t="n">
         <v>55240</v>
@@ -13692,13 +13692,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1289.032113482186</v>
+        <v>1289.042080341524</v>
       </c>
       <c r="D109" t="n">
-        <v>1281.725096331362</v>
+        <v>1281.734118395666</v>
       </c>
       <c r="E109" t="n">
-        <v>1296.339130633011</v>
+        <v>1296.350042287383</v>
       </c>
       <c r="F109" t="n">
         <v>8662</v>
@@ -13759,13 +13759,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1288.903215345834</v>
+        <v>1288.907015620166</v>
       </c>
       <c r="D110" t="n">
-        <v>1285.521007024918</v>
+        <v>1285.521877226685</v>
       </c>
       <c r="E110" t="n">
-        <v>1292.28542366675</v>
+        <v>1292.292154013646</v>
       </c>
       <c r="F110" t="n">
         <v>75754</v>
@@ -13910,16 +13910,16 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1286.835632724383</v>
+        <v>1286.96458787542</v>
       </c>
       <c r="D111" t="n">
-        <v>1278.446218319568</v>
+        <v>1278.572678956902</v>
       </c>
       <c r="E111" t="n">
-        <v>1295.225047129198</v>
+        <v>1295.356496793939</v>
       </c>
       <c r="F111" t="n">
-        <v>5685</v>
+        <v>5682</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -14057,24 +14057,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>llama-3.1-tulu-3-70b</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1285.937829093816</v>
+        <v>1285.931294653923</v>
       </c>
       <c r="D112" t="n">
-        <v>1275.470539345536</v>
+        <v>1275.958675713537</v>
       </c>
       <c r="E112" t="n">
-        <v>1296.405118842096</v>
+        <v>1295.903913594309</v>
       </c>
       <c r="F112" t="n">
-        <v>2846</v>
+        <v>3749</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -14083,10 +14083,10 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="J112" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -14099,22 +14099,22 @@
         </is>
       </c>
       <c r="M112" t="n">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="N112" t="n">
-        <v>175</v>
+        <v>127.5</v>
       </c>
       <c r="O112" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="P112" t="n">
-        <v>87.5</v>
+        <v>63.8</v>
       </c>
       <c r="Q112" t="n">
-        <v>35</v>
+        <v>25.5</v>
       </c>
       <c r="R112" t="n">
-        <v>43.8</v>
+        <v>31.9</v>
       </c>
       <c r="S112" s="5" t="inlineStr">
         <is>
@@ -14136,9 +14136,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W112" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W112" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X112" s="6" t="inlineStr">
@@ -14146,9 +14146,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y112" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y112" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z112" s="6" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -14208,24 +14208,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>llama-3.1-tulu-3-70b</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1285.903220289983</v>
+        <v>1285.92774487092</v>
       </c>
       <c r="D113" t="n">
-        <v>1275.931056116165</v>
+        <v>1275.460194503759</v>
       </c>
       <c r="E113" t="n">
-        <v>1295.8753844638</v>
+        <v>1296.395295238081</v>
       </c>
       <c r="F113" t="n">
-        <v>3749</v>
+        <v>2846</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="J113" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -14250,22 +14250,22 @@
         </is>
       </c>
       <c r="M113" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="N113" t="n">
-        <v>127.5</v>
+        <v>175</v>
       </c>
       <c r="O113" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="P113" t="n">
-        <v>63.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q113" t="n">
-        <v>25.5</v>
+        <v>35</v>
       </c>
       <c r="R113" t="n">
-        <v>31.9</v>
+        <v>43.8</v>
       </c>
       <c r="S113" s="5" t="inlineStr">
         <is>
@@ -14287,9 +14287,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W113" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W113" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X113" s="6" t="inlineStr">
@@ -14297,9 +14297,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y113" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y113" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z113" s="6" t="inlineStr">
@@ -14344,12 +14344,12 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -14363,16 +14363,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1285.010366998032</v>
+        <v>1285.006669255047</v>
       </c>
       <c r="D114" t="n">
-        <v>1277.804462552718</v>
+        <v>1277.801362054064</v>
       </c>
       <c r="E114" t="n">
-        <v>1292.216271443346</v>
+        <v>1292.21197645603</v>
       </c>
       <c r="F114" t="n">
-        <v>8499</v>
+        <v>8497</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -14514,13 +14514,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1279.88058953273</v>
+        <v>1279.877385715841</v>
       </c>
       <c r="D115" t="n">
-        <v>1273.019891064983</v>
+        <v>1273.015753651824</v>
       </c>
       <c r="E115" t="n">
-        <v>1286.741288000476</v>
+        <v>1286.739017779857</v>
       </c>
       <c r="F115" t="n">
         <v>10072</v>
@@ -14661,13 +14661,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1276.506506021466</v>
+        <v>1276.535404576134</v>
       </c>
       <c r="D116" t="n">
-        <v>1271.179857654442</v>
+        <v>1271.207840244072</v>
       </c>
       <c r="E116" t="n">
-        <v>1281.833154388489</v>
+        <v>1281.862968908196</v>
       </c>
       <c r="F116" t="n">
         <v>19659</v>
@@ -14812,13 +14812,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1275.923243482964</v>
+        <v>1275.941459756536</v>
       </c>
       <c r="D117" t="n">
-        <v>1272.334745691021</v>
+        <v>1272.351079126974</v>
       </c>
       <c r="E117" t="n">
-        <v>1279.511741274907</v>
+        <v>1279.531840386098</v>
       </c>
       <c r="F117" t="n">
         <v>156876</v>
@@ -14963,13 +14963,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1275.795195743379</v>
+        <v>1275.81408158539</v>
       </c>
       <c r="D118" t="n">
-        <v>1269.217338278412</v>
+        <v>1269.23508778787</v>
       </c>
       <c r="E118" t="n">
-        <v>1282.373053208347</v>
+        <v>1282.393075382909</v>
       </c>
       <c r="F118" t="n">
         <v>9866</v>
@@ -15114,13 +15114,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1274.088783867206</v>
+        <v>1274.087509480036</v>
       </c>
       <c r="D119" t="n">
-        <v>1268.18150469068</v>
+        <v>1268.178487552353</v>
       </c>
       <c r="E119" t="n">
-        <v>1279.996063043732</v>
+        <v>1279.996531407719</v>
       </c>
       <c r="F119" t="n">
         <v>14681</v>
@@ -15265,13 +15265,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1270.373403335803</v>
+        <v>1270.37359394284</v>
       </c>
       <c r="D120" t="n">
-        <v>1262.246031581821</v>
+        <v>1262.245198982299</v>
       </c>
       <c r="E120" t="n">
-        <v>1278.500775089784</v>
+        <v>1278.501988903381</v>
       </c>
       <c r="F120" t="n">
         <v>5432</v>
@@ -15416,13 +15416,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1266.886914571734</v>
+        <v>1266.885398243852</v>
       </c>
       <c r="D121" t="n">
-        <v>1261.998887644059</v>
+        <v>1261.995256768333</v>
       </c>
       <c r="E121" t="n">
-        <v>1271.77494149941</v>
+        <v>1271.77553971937</v>
       </c>
       <c r="F121" t="n">
         <v>27124</v>
@@ -15567,13 +15567,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1266.417537797862</v>
+        <v>1266.42232537567</v>
       </c>
       <c r="D122" t="n">
-        <v>1262.598509316881</v>
+        <v>1262.600718238703</v>
       </c>
       <c r="E122" t="n">
-        <v>1270.236566278845</v>
+        <v>1270.243932512636</v>
       </c>
       <c r="F122" t="n">
         <v>54611</v>
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1264.493219233776</v>
+        <v>1264.531528506338</v>
       </c>
       <c r="D123" t="n">
-        <v>1258.212650680514</v>
+        <v>1258.250144842287</v>
       </c>
       <c r="E123" t="n">
-        <v>1270.773787787038</v>
+        <v>1270.812912170389</v>
       </c>
       <c r="F123" t="n">
         <v>15147</v>
@@ -15869,13 +15869,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1261.095557895908</v>
+        <v>1261.128232579575</v>
       </c>
       <c r="D124" t="n">
-        <v>1256.147163580946</v>
+        <v>1256.178386137521</v>
       </c>
       <c r="E124" t="n">
-        <v>1266.04395221087</v>
+        <v>1266.078079021628</v>
       </c>
       <c r="F124" t="n">
         <v>37325</v>
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1261.048433428667</v>
+        <v>1261.085567130852</v>
       </c>
       <c r="D125" t="n">
-        <v>1256.723338939767</v>
+        <v>1256.759167635849</v>
       </c>
       <c r="E125" t="n">
-        <v>1265.373527917567</v>
+        <v>1265.411966625855</v>
       </c>
       <c r="F125" t="n">
         <v>77554</v>
@@ -16091,13 +16091,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1256.018945625945</v>
+        <v>1256.015468608403</v>
       </c>
       <c r="D126" t="n">
-        <v>1251.42504060965</v>
+        <v>1251.419381603399</v>
       </c>
       <c r="E126" t="n">
-        <v>1260.612850642241</v>
+        <v>1260.611555613408</v>
       </c>
       <c r="F126" t="n">
         <v>24126</v>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1251.334785520941</v>
+        <v>1251.331582338345</v>
       </c>
       <c r="D127" t="n">
-        <v>1240.552532190454</v>
+        <v>1240.54919450456</v>
       </c>
       <c r="E127" t="n">
-        <v>1262.117038851427</v>
+        <v>1262.113970172129</v>
       </c>
       <c r="F127" t="n">
         <v>3334</v>
@@ -16393,13 +16393,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1249.646658959251</v>
+        <v>1249.684760410396</v>
       </c>
       <c r="D128" t="n">
-        <v>1243.04428407263</v>
+        <v>1243.081241131756</v>
       </c>
       <c r="E128" t="n">
-        <v>1256.249033845871</v>
+        <v>1256.288279689035</v>
       </c>
       <c r="F128" t="n">
         <v>10140</v>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1239.333179150367</v>
+        <v>1239.33967954261</v>
       </c>
       <c r="D129" t="n">
-        <v>1232.105841357365</v>
+        <v>1232.111381205241</v>
       </c>
       <c r="E129" t="n">
-        <v>1246.560516943369</v>
+        <v>1246.567977879979</v>
       </c>
       <c r="F129" t="n">
         <v>8858</v>
@@ -16611,13 +16611,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1237.283481270324</v>
+        <v>1237.287676879146</v>
       </c>
       <c r="D130" t="n">
-        <v>1228.189868078945</v>
+        <v>1228.193498132406</v>
       </c>
       <c r="E130" t="n">
-        <v>1246.377094461702</v>
+        <v>1246.381855625886</v>
       </c>
       <c r="F130" t="n">
         <v>4781</v>
@@ -16762,13 +16762,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1233.459466635596</v>
+        <v>1233.48929453694</v>
       </c>
       <c r="D131" t="n">
-        <v>1227.905157238895</v>
+        <v>1227.934175897894</v>
       </c>
       <c r="E131" t="n">
-        <v>1239.013776032296</v>
+        <v>1239.044413175985</v>
       </c>
       <c r="F131" t="n">
         <v>26195</v>
@@ -16913,13 +16913,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1232.660018329701</v>
+        <v>1232.702647926981</v>
       </c>
       <c r="D132" t="n">
-        <v>1227.383965104348</v>
+        <v>1227.425759230322</v>
       </c>
       <c r="E132" t="n">
-        <v>1237.936071555054</v>
+        <v>1237.97953662364</v>
       </c>
       <c r="F132" t="n">
         <v>39302</v>
@@ -17064,13 +17064,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1228.688165372739</v>
+        <v>1228.736278393209</v>
       </c>
       <c r="D133" t="n">
-        <v>1224.129773484615</v>
+        <v>1224.176526455188</v>
       </c>
       <c r="E133" t="n">
-        <v>1233.246557260863</v>
+        <v>1233.296030331228</v>
       </c>
       <c r="F133" t="n">
         <v>51416</v>
@@ -17215,13 +17215,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1226.037516525316</v>
+        <v>1226.082271258559</v>
       </c>
       <c r="D134" t="n">
-        <v>1221.253543239288</v>
+        <v>1221.297222726946</v>
       </c>
       <c r="E134" t="n">
-        <v>1230.821489811344</v>
+        <v>1230.867319790172</v>
       </c>
       <c r="F134" t="n">
         <v>54036</v>
@@ -17286,13 +17286,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1222.963902064288</v>
+        <v>1222.987171849005</v>
       </c>
       <c r="D135" t="n">
-        <v>1219.224775112788</v>
+        <v>1219.246265130851</v>
       </c>
       <c r="E135" t="n">
-        <v>1226.703029015788</v>
+        <v>1226.728078567158</v>
       </c>
       <c r="F135" t="n">
         <v>104642</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1222.825313850102</v>
+        <v>1222.815214864392</v>
       </c>
       <c r="D136" t="n">
-        <v>1215.852217341414</v>
+        <v>1215.840663342441</v>
       </c>
       <c r="E136" t="n">
-        <v>1229.798410358789</v>
+        <v>1229.789766386343</v>
       </c>
       <c r="F136" t="n">
         <v>9818</v>
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1220.430730015864</v>
+        <v>1220.413522499334</v>
       </c>
       <c r="D137" t="n">
-        <v>1209.752553103617</v>
+        <v>1209.734897000563</v>
       </c>
       <c r="E137" t="n">
-        <v>1231.10890692811</v>
+        <v>1231.092147998105</v>
       </c>
       <c r="F137" t="n">
         <v>2896</v>
@@ -17739,13 +17739,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1212.487571496081</v>
+        <v>1212.497003168105</v>
       </c>
       <c r="D138" t="n">
-        <v>1207.447507650562</v>
+        <v>1207.455845948065</v>
       </c>
       <c r="E138" t="n">
-        <v>1217.527635341601</v>
+        <v>1217.538160388146</v>
       </c>
       <c r="F138" t="n">
         <v>24146</v>
@@ -17886,13 +17886,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1212.115935249027</v>
+        <v>1212.164805648458</v>
       </c>
       <c r="D139" t="n">
-        <v>1201.32431143109</v>
+        <v>1201.373415922065</v>
       </c>
       <c r="E139" t="n">
-        <v>1222.907559066965</v>
+        <v>1222.95619537485</v>
       </c>
       <c r="F139" t="n">
         <v>4652</v>
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1211.287834456233</v>
+        <v>1211.260457461596</v>
       </c>
       <c r="D140" t="n">
-        <v>1207.137409965578</v>
+        <v>1207.107666532951</v>
       </c>
       <c r="E140" t="n">
-        <v>1215.438258946887</v>
+        <v>1215.413248390241</v>
       </c>
       <c r="F140" t="n">
         <v>49605</v>
@@ -18184,13 +18184,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1207.801116463897</v>
+        <v>1207.834352510464</v>
       </c>
       <c r="D141" t="n">
-        <v>1196.698381202587</v>
+        <v>1196.73149997194</v>
       </c>
       <c r="E141" t="n">
-        <v>1218.903851725208</v>
+        <v>1218.937205048988</v>
       </c>
       <c r="F141" t="n">
         <v>3090</v>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1203.122356231796</v>
+        <v>1203.168015611272</v>
       </c>
       <c r="D142" t="n">
-        <v>1197.003040386017</v>
+        <v>1197.048048073493</v>
       </c>
       <c r="E142" t="n">
-        <v>1209.241672077575</v>
+        <v>1209.287983149052</v>
       </c>
       <c r="F142" t="n">
         <v>21741</v>
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1199.813530554552</v>
+        <v>1199.793684066829</v>
       </c>
       <c r="D143" t="n">
-        <v>1195.720153625625</v>
+        <v>1195.69788942793</v>
       </c>
       <c r="E143" t="n">
-        <v>1203.906907483479</v>
+        <v>1203.889478705729</v>
       </c>
       <c r="F143" t="n">
         <v>46616</v>
@@ -18637,13 +18637,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1197.155938349794</v>
+        <v>1197.194785507751</v>
       </c>
       <c r="D144" t="n">
-        <v>1191.994648365189</v>
+        <v>1192.032243792877</v>
       </c>
       <c r="E144" t="n">
-        <v>1202.3172283344</v>
+        <v>1202.357327222626</v>
       </c>
       <c r="F144" t="n">
         <v>25055</v>
@@ -18788,13 +18788,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1196.303773290139</v>
+        <v>1196.349905867249</v>
       </c>
       <c r="D145" t="n">
-        <v>1192.03349663649</v>
+        <v>1192.078511705842</v>
       </c>
       <c r="E145" t="n">
-        <v>1200.574049943789</v>
+        <v>1200.621300028656</v>
       </c>
       <c r="F145" t="n">
         <v>73503</v>
@@ -18939,13 +18939,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1194.478446743884</v>
+        <v>1194.534584563296</v>
       </c>
       <c r="D146" t="n">
-        <v>1188.363963503052</v>
+        <v>1188.419398476449</v>
       </c>
       <c r="E146" t="n">
-        <v>1200.592929984716</v>
+        <v>1200.649770650143</v>
       </c>
       <c r="F146" t="n">
         <v>32191</v>
@@ -19006,13 +19006,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1190.536039803778</v>
+        <v>1190.530394217006</v>
       </c>
       <c r="D147" t="n">
-        <v>1183.351991684304</v>
+        <v>1183.345309146106</v>
       </c>
       <c r="E147" t="n">
-        <v>1197.720087923253</v>
+        <v>1197.715479287907</v>
       </c>
       <c r="F147" t="n">
         <v>9901</v>
@@ -19153,13 +19153,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1190.281942704043</v>
+        <v>1190.320570839925</v>
       </c>
       <c r="D148" t="n">
-        <v>1183.162778149334</v>
+        <v>1183.201036294781</v>
       </c>
       <c r="E148" t="n">
-        <v>1197.401107258752</v>
+        <v>1197.44010538507</v>
       </c>
       <c r="F148" t="n">
         <v>17839</v>
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1183.905184041492</v>
+        <v>1183.949803225292</v>
       </c>
       <c r="D149" t="n">
-        <v>1174.466203461263</v>
+        <v>1174.511037748907</v>
       </c>
       <c r="E149" t="n">
-        <v>1193.344164621722</v>
+        <v>1193.388568701676</v>
       </c>
       <c r="F149" t="n">
         <v>8214</v>
@@ -19455,13 +19455,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1183.84163583991</v>
+        <v>1183.901775052109</v>
       </c>
       <c r="D150" t="n">
-        <v>1172.354173232444</v>
+        <v>1172.414981765907</v>
       </c>
       <c r="E150" t="n">
-        <v>1195.329098447377</v>
+        <v>1195.388568338312</v>
       </c>
       <c r="F150" t="n">
         <v>4932</v>
@@ -19606,13 +19606,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1183.094994678753</v>
+        <v>1183.120671144037</v>
       </c>
       <c r="D151" t="n">
-        <v>1176.267502795881</v>
+        <v>1176.29262675692</v>
       </c>
       <c r="E151" t="n">
-        <v>1189.922486561625</v>
+        <v>1189.948715531155</v>
       </c>
       <c r="F151" t="n">
         <v>15483</v>
@@ -19753,13 +19753,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1181.974525889217</v>
+        <v>1182.036737447477</v>
       </c>
       <c r="D152" t="n">
-        <v>1173.293139643124</v>
+        <v>1173.354931802284</v>
       </c>
       <c r="E152" t="n">
-        <v>1190.65591213531</v>
+        <v>1190.718543092671</v>
       </c>
       <c r="F152" t="n">
         <v>6638</v>
@@ -19904,13 +19904,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1181.864970577921</v>
+        <v>1181.92993259954</v>
       </c>
       <c r="D153" t="n">
-        <v>1172.203329928649</v>
+        <v>1172.268573910813</v>
       </c>
       <c r="E153" t="n">
-        <v>1191.526611227192</v>
+        <v>1191.591291288267</v>
       </c>
       <c r="F153" t="n">
         <v>7968</v>
@@ -19971,13 +19971,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1181.722732092856</v>
+        <v>1181.778462960732</v>
       </c>
       <c r="D154" t="n">
-        <v>1173.728287498741</v>
+        <v>1173.78382400874</v>
       </c>
       <c r="E154" t="n">
-        <v>1189.717176686971</v>
+        <v>1189.773101912725</v>
       </c>
       <c r="F154" t="n">
         <v>12637</v>
@@ -20038,13 +20038,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1181.512236985649</v>
+        <v>1181.549076645626</v>
       </c>
       <c r="D155" t="n">
-        <v>1175.440428094462</v>
+        <v>1175.476470349832</v>
       </c>
       <c r="E155" t="n">
-        <v>1187.584045876837</v>
+        <v>1187.621682941419</v>
       </c>
       <c r="F155" t="n">
         <v>23893</v>
@@ -20189,13 +20189,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1178.977674457516</v>
+        <v>1179.036749352651</v>
       </c>
       <c r="D156" t="n">
-        <v>1173.06472217836</v>
+        <v>1173.123100396501</v>
       </c>
       <c r="E156" t="n">
-        <v>1184.890626736671</v>
+        <v>1184.9503983088</v>
       </c>
       <c r="F156" t="n">
         <v>32832</v>
@@ -20256,13 +20256,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1178.307082228679</v>
+        <v>1178.329147545271</v>
       </c>
       <c r="D157" t="n">
-        <v>1167.114835075636</v>
+        <v>1167.136850824092</v>
       </c>
       <c r="E157" t="n">
-        <v>1189.499329381721</v>
+        <v>1189.52144426645</v>
       </c>
       <c r="F157" t="n">
         <v>3188</v>
@@ -20407,13 +20407,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1176.954265842461</v>
+        <v>1176.991416093803</v>
       </c>
       <c r="D158" t="n">
-        <v>1167.146410685479</v>
+        <v>1167.183753260422</v>
       </c>
       <c r="E158" t="n">
-        <v>1186.762120999443</v>
+        <v>1186.799078927183</v>
       </c>
       <c r="F158" t="n">
         <v>6535</v>
@@ -20554,13 +20554,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1174.816954742762</v>
+        <v>1174.879614283936</v>
       </c>
       <c r="D159" t="n">
-        <v>1164.409952259615</v>
+        <v>1164.472962161258</v>
       </c>
       <c r="E159" t="n">
-        <v>1185.22395722591</v>
+        <v>1185.286266406613</v>
       </c>
       <c r="F159" t="n">
         <v>5006</v>
@@ -20701,13 +20701,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1172.054119585737</v>
+        <v>1172.101175643518</v>
       </c>
       <c r="D160" t="n">
-        <v>1165.851912126215</v>
+        <v>1165.898660979072</v>
       </c>
       <c r="E160" t="n">
-        <v>1178.256327045259</v>
+        <v>1178.303690307964</v>
       </c>
       <c r="F160" t="n">
         <v>22479</v>
@@ -20848,13 +20848,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1170.581243683115</v>
+        <v>1170.599663900031</v>
       </c>
       <c r="D161" t="n">
-        <v>1163.175257980178</v>
+        <v>1163.19337142538</v>
       </c>
       <c r="E161" t="n">
-        <v>1177.987229386053</v>
+        <v>1178.005956374682</v>
       </c>
       <c r="F161" t="n">
         <v>16056</v>
@@ -20995,13 +20995,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1170.322636980192</v>
+        <v>1170.359674066028</v>
       </c>
       <c r="D162" t="n">
-        <v>1164.405426902094</v>
+        <v>1164.441646177115</v>
       </c>
       <c r="E162" t="n">
-        <v>1176.239847058289</v>
+        <v>1176.277701954941</v>
       </c>
       <c r="F162" t="n">
         <v>17766</v>
@@ -21146,13 +21146,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1169.978378749341</v>
+        <v>1170.011448114722</v>
       </c>
       <c r="D163" t="n">
-        <v>1164.479332231828</v>
+        <v>1164.511893987419</v>
       </c>
       <c r="E163" t="n">
-        <v>1175.477425266853</v>
+        <v>1175.511002242025</v>
       </c>
       <c r="F163" t="n">
         <v>38492</v>
@@ -21297,13 +21297,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1166.66690241618</v>
+        <v>1166.705990283283</v>
       </c>
       <c r="D164" t="n">
-        <v>1158.603408765875</v>
+        <v>1158.642270747939</v>
       </c>
       <c r="E164" t="n">
-        <v>1174.730396066486</v>
+        <v>1174.769709818627</v>
       </c>
       <c r="F164" t="n">
         <v>10224</v>
@@ -21444,13 +21444,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1166.163793994671</v>
+        <v>1166.185691722796</v>
       </c>
       <c r="D165" t="n">
-        <v>1158.459379539879</v>
+        <v>1158.480408118013</v>
       </c>
       <c r="E165" t="n">
-        <v>1173.868208449463</v>
+        <v>1173.890975327579</v>
       </c>
       <c r="F165" t="n">
         <v>7936</v>
@@ -21595,13 +21595,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1163.784526919087</v>
+        <v>1163.813791953077</v>
       </c>
       <c r="D166" t="n">
-        <v>1151.870173930395</v>
+        <v>1151.900027158201</v>
       </c>
       <c r="E166" t="n">
-        <v>1175.698879907779</v>
+        <v>1175.727556747953</v>
       </c>
       <c r="F166" t="n">
         <v>3777</v>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1155.661770388774</v>
+        <v>1155.714655846064</v>
       </c>
       <c r="D167" t="n">
-        <v>1147.273810522716</v>
+        <v>1147.326160774616</v>
       </c>
       <c r="E167" t="n">
-        <v>1164.049730254833</v>
+        <v>1164.103150917511</v>
       </c>
       <c r="F167" t="n">
         <v>6837</v>
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1154.683464769317</v>
+        <v>1154.642408726014</v>
       </c>
       <c r="D168" t="n">
-        <v>1143.192468528812</v>
+        <v>1143.15137356015</v>
       </c>
       <c r="E168" t="n">
-        <v>1166.174461009822</v>
+        <v>1166.133443891879</v>
       </c>
       <c r="F168" t="n">
         <v>3231</v>
@@ -22044,13 +22044,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1153.970920573707</v>
+        <v>1154.009573289722</v>
       </c>
       <c r="D169" t="n">
-        <v>1141.373727149175</v>
+        <v>1141.413002354806</v>
       </c>
       <c r="E169" t="n">
-        <v>1166.568113998239</v>
+        <v>1166.606144224638</v>
       </c>
       <c r="F169" t="n">
         <v>3585</v>
@@ -22195,13 +22195,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1151.508598745396</v>
+        <v>1151.55825886573</v>
       </c>
       <c r="D170" t="n">
-        <v>1138.338411148575</v>
+        <v>1138.389283663415</v>
       </c>
       <c r="E170" t="n">
-        <v>1164.678786342218</v>
+        <v>1164.727234068044</v>
       </c>
       <c r="F170" t="n">
         <v>4155</v>
@@ -22342,13 +22342,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1151.338310726896</v>
+        <v>1151.388270637974</v>
       </c>
       <c r="D171" t="n">
-        <v>1136.00697290054</v>
+        <v>1136.059026092404</v>
       </c>
       <c r="E171" t="n">
-        <v>1166.669648553253</v>
+        <v>1166.717515183545</v>
       </c>
       <c r="F171" t="n">
         <v>1679</v>
@@ -22489,13 +22489,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1149.645693531595</v>
+        <v>1149.70587488312</v>
       </c>
       <c r="D172" t="n">
-        <v>1137.395137683916</v>
+        <v>1137.456884404567</v>
       </c>
       <c r="E172" t="n">
-        <v>1161.896249379273</v>
+        <v>1161.954865361675</v>
       </c>
       <c r="F172" t="n">
         <v>2572</v>
@@ -22636,13 +22636,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1148.638006138723</v>
+        <v>1148.677398481474</v>
       </c>
       <c r="D173" t="n">
-        <v>1141.986662885367</v>
+        <v>1142.025550954698</v>
       </c>
       <c r="E173" t="n">
-        <v>1155.289349392078</v>
+        <v>1155.329246008249</v>
       </c>
       <c r="F173" t="n">
         <v>19402</v>
@@ -22787,13 +22787,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1148.568662466476</v>
+        <v>1148.619978154574</v>
       </c>
       <c r="D174" t="n">
-        <v>1139.340436740556</v>
+        <v>1139.392610225476</v>
       </c>
       <c r="E174" t="n">
-        <v>1157.796888192396</v>
+        <v>1157.847346083671</v>
       </c>
       <c r="F174" t="n">
         <v>7044</v>
@@ -22938,13 +22938,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1146.819848917881</v>
+        <v>1146.89175491363</v>
       </c>
       <c r="D175" t="n">
-        <v>1129.758383617719</v>
+        <v>1129.832500964808</v>
       </c>
       <c r="E175" t="n">
-        <v>1163.881314218044</v>
+        <v>1163.951008862453</v>
       </c>
       <c r="F175" t="n">
         <v>1295</v>
@@ -23085,13 +23085,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1143.114054070229</v>
+        <v>1143.149069716942</v>
       </c>
       <c r="D176" t="n">
-        <v>1133.227365395954</v>
+        <v>1133.262266291231</v>
       </c>
       <c r="E176" t="n">
-        <v>1153.000742744505</v>
+        <v>1153.035873142652</v>
       </c>
       <c r="F176" t="n">
         <v>4737</v>
@@ -23236,13 +23236,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1142.350224074481</v>
+        <v>1142.388440543208</v>
       </c>
       <c r="D177" t="n">
-        <v>1135.910408941166</v>
+        <v>1135.947670349859</v>
       </c>
       <c r="E177" t="n">
-        <v>1148.790039207796</v>
+        <v>1148.829210736558</v>
       </c>
       <c r="F177" t="n">
         <v>12297</v>
@@ -23387,13 +23387,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1140.747670851518</v>
+        <v>1140.781016133354</v>
       </c>
       <c r="D178" t="n">
-        <v>1134.023633360297</v>
+        <v>1134.0565978972</v>
       </c>
       <c r="E178" t="n">
-        <v>1147.47170834274</v>
+        <v>1147.505434369507</v>
       </c>
       <c r="F178" t="n">
         <v>19174</v>
@@ -23538,13 +23538,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1140.421970783404</v>
+        <v>1140.484936880385</v>
       </c>
       <c r="D179" t="n">
-        <v>1133.722007413438</v>
+        <v>1133.784866956578</v>
       </c>
       <c r="E179" t="n">
-        <v>1147.121934153369</v>
+        <v>1147.185006804193</v>
       </c>
       <c r="F179" t="n">
         <v>19367</v>
@@ -23685,13 +23685,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1138.135918281817</v>
+        <v>1138.203045656328</v>
       </c>
       <c r="D180" t="n">
-        <v>1127.19206462685</v>
+        <v>1127.259742310016</v>
       </c>
       <c r="E180" t="n">
-        <v>1149.079771936784</v>
+        <v>1149.146349002639</v>
       </c>
       <c r="F180" t="n">
         <v>4964</v>
@@ -23836,13 +23836,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1136.761602662253</v>
+        <v>1136.794775525664</v>
       </c>
       <c r="D181" t="n">
-        <v>1127.27315273746</v>
+        <v>1127.306533885397</v>
       </c>
       <c r="E181" t="n">
-        <v>1146.250052587046</v>
+        <v>1146.283017165932</v>
       </c>
       <c r="F181" t="n">
         <v>8925</v>
@@ -23987,13 +23987,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1135.936030208411</v>
+        <v>1135.98609761987</v>
       </c>
       <c r="D182" t="n">
-        <v>1127.045740323337</v>
+        <v>1127.095925848011</v>
       </c>
       <c r="E182" t="n">
-        <v>1144.826320093485</v>
+        <v>1144.876269391729</v>
       </c>
       <c r="F182" t="n">
         <v>7366</v>
@@ -24138,13 +24138,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1130.02971589047</v>
+        <v>1130.071050931823</v>
       </c>
       <c r="D183" t="n">
-        <v>1121.199266674322</v>
+        <v>1121.240796185868</v>
       </c>
       <c r="E183" t="n">
-        <v>1138.860165106618</v>
+        <v>1138.901305677778</v>
       </c>
       <c r="F183" t="n">
         <v>11118</v>
@@ -24285,13 +24285,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1128.782293232959</v>
+        <v>1128.838898512054</v>
       </c>
       <c r="D184" t="n">
-        <v>1121.358539549665</v>
+        <v>1121.414661741994</v>
       </c>
       <c r="E184" t="n">
-        <v>1136.206046916252</v>
+        <v>1136.263135282114</v>
       </c>
       <c r="F184" t="n">
         <v>20685</v>
@@ -24436,13 +24436,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1127.464228692599</v>
+        <v>1127.49624541177</v>
       </c>
       <c r="D185" t="n">
-        <v>1121.066018775343</v>
+        <v>1121.097327949778</v>
       </c>
       <c r="E185" t="n">
-        <v>1133.862438609855</v>
+        <v>1133.895162873763</v>
       </c>
       <c r="F185" t="n">
         <v>20118</v>
@@ -24587,13 +24587,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1126.514774177901</v>
+        <v>1126.566926147063</v>
       </c>
       <c r="D186" t="n">
-        <v>1114.414747818528</v>
+        <v>1114.468630274141</v>
       </c>
       <c r="E186" t="n">
-        <v>1138.614800537274</v>
+        <v>1138.665222019984</v>
       </c>
       <c r="F186" t="n">
         <v>2921</v>
@@ -24734,13 +24734,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1126.045299639682</v>
+        <v>1126.093289687969</v>
       </c>
       <c r="D187" t="n">
-        <v>1110.440573456473</v>
+        <v>1110.490817135835</v>
       </c>
       <c r="E187" t="n">
-        <v>1141.650025822891</v>
+        <v>1141.695762240102</v>
       </c>
       <c r="F187" t="n">
         <v>1785</v>
@@ -24881,13 +24881,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1120.487699765963</v>
+        <v>1120.549217988764</v>
       </c>
       <c r="D188" t="n">
-        <v>1109.50954491768</v>
+        <v>1109.57155658657</v>
       </c>
       <c r="E188" t="n">
-        <v>1131.465854614247</v>
+        <v>1131.526879390959</v>
       </c>
       <c r="F188" t="n">
         <v>5182</v>
@@ -25028,13 +25028,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1118.439686832844</v>
+        <v>1118.470915105906</v>
       </c>
       <c r="D189" t="n">
-        <v>1100.297738174124</v>
+        <v>1100.331334370407</v>
       </c>
       <c r="E189" t="n">
-        <v>1136.581635491564</v>
+        <v>1136.610495841404</v>
       </c>
       <c r="F189" t="n">
         <v>1143</v>
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1115.504242968868</v>
+        <v>1115.547332184625</v>
       </c>
       <c r="D190" t="n">
-        <v>1107.775164732298</v>
+        <v>1107.81787317542</v>
       </c>
       <c r="E190" t="n">
-        <v>1123.233321205437</v>
+        <v>1123.276791193831</v>
       </c>
       <c r="F190" t="n">
         <v>10854</v>
@@ -25330,13 +25330,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1114.173263961251</v>
+        <v>1114.235315595419</v>
       </c>
       <c r="D191" t="n">
-        <v>1105.032629607706</v>
+        <v>1105.095702272118</v>
       </c>
       <c r="E191" t="n">
-        <v>1123.313898314796</v>
+        <v>1123.374928918719</v>
       </c>
       <c r="F191" t="n">
         <v>6923</v>
@@ -25477,13 +25477,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1113.793145131287</v>
+        <v>1113.84007806664</v>
       </c>
       <c r="D192" t="n">
-        <v>1099.418179421913</v>
+        <v>1099.466229116668</v>
       </c>
       <c r="E192" t="n">
-        <v>1128.168110840661</v>
+        <v>1128.213927016613</v>
       </c>
       <c r="F192" t="n">
         <v>2199</v>
@@ -25624,13 +25624,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1110.525946052677</v>
+        <v>1110.547489565442</v>
       </c>
       <c r="D193" t="n">
-        <v>1102.643131807716</v>
+        <v>1102.663869451807</v>
       </c>
       <c r="E193" t="n">
-        <v>1118.408760297639</v>
+        <v>1118.431109679078</v>
       </c>
       <c r="F193" t="n">
         <v>8045</v>
@@ -25775,13 +25775,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1109.177241862961</v>
+        <v>1109.242231354672</v>
       </c>
       <c r="D194" t="n">
-        <v>1099.895092908219</v>
+        <v>1099.960266529778</v>
       </c>
       <c r="E194" t="n">
-        <v>1118.459390817703</v>
+        <v>1118.524196179565</v>
       </c>
       <c r="F194" t="n">
         <v>8977</v>
@@ -25926,13 +25926,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1107.29254830879</v>
+        <v>1107.325314447213</v>
       </c>
       <c r="D195" t="n">
-        <v>1100.240441253906</v>
+        <v>1100.272885750716</v>
       </c>
       <c r="E195" t="n">
-        <v>1114.344655363674</v>
+        <v>1114.377743143709</v>
       </c>
       <c r="F195" t="n">
         <v>14148</v>
@@ -26077,13 +26077,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1092.529372189552</v>
+        <v>1092.573218909389</v>
       </c>
       <c r="D196" t="n">
-        <v>1081.043895937477</v>
+        <v>1081.088481713758</v>
       </c>
       <c r="E196" t="n">
-        <v>1104.014848441626</v>
+        <v>1104.05795610502</v>
       </c>
       <c r="F196" t="n">
         <v>4780</v>
@@ -26228,13 +26228,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1089.831342735379</v>
+        <v>1089.903878887744</v>
       </c>
       <c r="D197" t="n">
-        <v>1080.4962785067</v>
+        <v>1080.568972241529</v>
       </c>
       <c r="E197" t="n">
-        <v>1099.166406964058</v>
+        <v>1099.238785533958</v>
       </c>
       <c r="F197" t="n">
         <v>7597</v>
@@ -26379,13 +26379,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1073.180679441504</v>
+        <v>1073.201287581766</v>
       </c>
       <c r="D198" t="n">
-        <v>1062.021205560146</v>
+        <v>1062.042483553581</v>
       </c>
       <c r="E198" t="n">
-        <v>1084.340153322861</v>
+        <v>1084.360091609951</v>
       </c>
       <c r="F198" t="n">
         <v>6328</v>
@@ -26530,13 +26530,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1069.862006373764</v>
+        <v>1069.91987974033</v>
       </c>
       <c r="D199" t="n">
-        <v>1059.982385083697</v>
+        <v>1060.042451746094</v>
       </c>
       <c r="E199" t="n">
-        <v>1079.741627663831</v>
+        <v>1079.797307734566</v>
       </c>
       <c r="F199" t="n">
         <v>6965</v>
@@ -26677,13 +26677,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1068.244474903341</v>
+        <v>1068.355432475025</v>
       </c>
       <c r="D200" t="n">
-        <v>1056.792359502057</v>
+        <v>1056.905657658176</v>
       </c>
       <c r="E200" t="n">
-        <v>1079.696590304626</v>
+        <v>1079.805207291873</v>
       </c>
       <c r="F200" t="n">
         <v>5745</v>
@@ -26824,13 +26824,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1066.148004662287</v>
+        <v>1066.23425767769</v>
       </c>
       <c r="D201" t="n">
-        <v>1050.941364902895</v>
+        <v>1051.03034013863</v>
       </c>
       <c r="E201" t="n">
-        <v>1081.354644421679</v>
+        <v>1081.43817521675</v>
       </c>
       <c r="F201" t="n">
         <v>1743</v>
@@ -26971,13 +26971,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1061.939316203563</v>
+        <v>1062.022522675117</v>
       </c>
       <c r="D202" t="n">
-        <v>1049.972814836583</v>
+        <v>1050.058132514864</v>
       </c>
       <c r="E202" t="n">
-        <v>1073.905817570543</v>
+        <v>1073.98691283537</v>
       </c>
       <c r="F202" t="n">
         <v>3924</v>
@@ -27118,13 +27118,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1055.433031694294</v>
+        <v>1055.495437515089</v>
       </c>
       <c r="D203" t="n">
-        <v>1043.773773845249</v>
+        <v>1043.83686773732</v>
       </c>
       <c r="E203" t="n">
-        <v>1067.09228954334</v>
+        <v>1067.154007292859</v>
       </c>
       <c r="F203" t="n">
         <v>4658</v>
@@ -27265,13 +27265,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1041.077715716008</v>
+        <v>1041.14654619993</v>
       </c>
       <c r="D204" t="n">
-        <v>1029.696160709769</v>
+        <v>1029.767212253605</v>
       </c>
       <c r="E204" t="n">
-        <v>1052.459270722246</v>
+        <v>1052.525880146256</v>
       </c>
       <c r="F204" t="n">
         <v>4845</v>
@@ -27412,13 +27412,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1023.619823554048</v>
+        <v>1023.682610909772</v>
       </c>
       <c r="D205" t="n">
-        <v>1010.036183951607</v>
+        <v>1010.10062775913</v>
       </c>
       <c r="E205" t="n">
-        <v>1037.203463156489</v>
+        <v>1037.264594060413</v>
       </c>
       <c r="F205" t="n">
         <v>2658</v>
@@ -27559,13 +27559,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1022.052713179753</v>
+        <v>1022.134024688156</v>
       </c>
       <c r="D206" t="n">
-        <v>1011.192056051469</v>
+        <v>1011.275613711912</v>
       </c>
       <c r="E206" t="n">
-        <v>1032.913370308037</v>
+        <v>1032.992435664401</v>
       </c>
       <c r="F206" t="n">
         <v>6310</v>
@@ -27706,13 +27706,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>994.8370905068468</v>
+        <v>994.8901499967722</v>
       </c>
       <c r="D207" t="n">
-        <v>982.2810650552851</v>
+        <v>982.336413622405</v>
       </c>
       <c r="E207" t="n">
-        <v>1007.393115958409</v>
+        <v>1007.443886371139</v>
       </c>
       <c r="F207" t="n">
         <v>4914</v>
@@ -27853,13 +27853,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>991.2699725905611</v>
+        <v>991.3408423493614</v>
       </c>
       <c r="D208" t="n">
-        <v>978.9085275210684</v>
+        <v>978.9818668260874</v>
       </c>
       <c r="E208" t="n">
-        <v>1003.631417660054</v>
+        <v>1003.699817872635</v>
       </c>
       <c r="F208" t="n">
         <v>4203</v>
@@ -28000,13 +28000,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>980.6450157346953</v>
+        <v>980.747498111305</v>
       </c>
       <c r="D209" t="n">
-        <v>967.1293885414509</v>
+        <v>967.2351976816037</v>
       </c>
       <c r="E209" t="n">
-        <v>994.1606429279395</v>
+        <v>994.2597985410064</v>
       </c>
       <c r="F209" t="n">
         <v>3412</v>
@@ -28147,13 +28147,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>973.193738491653</v>
+        <v>973.3035339654052</v>
       </c>
       <c r="D210" t="n">
-        <v>957.4145935622616</v>
+        <v>957.5290289555505</v>
       </c>
       <c r="E210" t="n">
-        <v>988.9728834210443</v>
+        <v>989.0780389752599</v>
       </c>
       <c r="F210" t="n">
         <v>2391</v>
@@ -28298,13 +28298,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>952.1008674954917</v>
+        <v>952.1606549650462</v>
       </c>
       <c r="D211" t="n">
-        <v>939.3865276224669</v>
+        <v>939.4498522861545</v>
       </c>
       <c r="E211" t="n">
-        <v>964.8152073685162</v>
+        <v>964.8714576439377</v>
       </c>
       <c r="F211" t="n">
         <v>3287</v>
@@ -29262,14 +29262,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>minimax-m3</t>
+          <t>inkling</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>428</v>
+        <v>975</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -29285,15 +29285,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>minimax-m3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>428</v>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -29323,23 +29331,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inkling</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>975</v>
-      </c>
-      <c r="C14" t="n">
-        <v>41</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>glm-4.7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29642,7 +29642,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -29657,83 +29657,83 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>kimi-k2-0711-preview</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C32" t="n">
+        <v>32</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kimi-k2-0711-preview</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C33" t="n">
-        <v>32</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>122</v>
-      </c>
-      <c r="C34" t="n">
-        <v>10</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-terminus-thinking</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>122</v>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -29985,14 +29985,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="C48" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -30001,21 +30001,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>35</v>
+        <v>671</v>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -31022,38 +31022,38 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>deepseek-v2.5</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+          <t>granite-4.1-8b</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>8</v>
+      </c>
+      <c r="C99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>granite-4.1-8b</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>8</v>
-      </c>
-      <c r="C100" t="n">
-        <v>8</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>deepseek-v2.5</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -31121,14 +31121,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -31144,14 +31144,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -31297,14 +31297,14 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>llama-3.1-tulu-3-70b</t>
+          <t>llama-3.1-nemotron-51b-instruct</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C112" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -31320,14 +31320,14 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-51b-instruct</t>
+          <t>llama-3.1-tulu-3-70b</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C113" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1469.879131239728</v>
+        <v>1469.645061867107</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1465.270515936197</v>
+        <v>1465.067962125951</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1474.487746543259</v>
+        <v>1474.222161608263</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>29919</v>
+        <v>30726</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1469.53048413241</v>
+        <v>1469.199078695134</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1463.597366201418</v>
+        <v>1463.356844159738</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1475.463602063402</v>
+        <v>1475.041313230531</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>17103</v>
+        <v>18017</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1465.906476799099</v>
+        <v>1466.8350955357</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1461.4236671201</v>
+        <v>1462.377573618436</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1470.389286478097</v>
+        <v>1471.292617452963</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>41409</v>
+        <v>42195</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1461.169439206421</v>
+        <v>1460.91086115393</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1456.623190645149</v>
+        <v>1456.363646207052</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1465.715687767693</v>
+        <v>1465.458076100808</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>37711</v>
+        <v>37686</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1035,24 +1035,24 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1457.055315100001</v>
+        <v>1456.662103104919</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1452.658857365217</v>
+        <v>1452.303876849965</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1461.451772834785</v>
+        <v>1461.020329359874</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>44418</v>
+        <v>27785</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -1077,22 +1077,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3200</v>
+        <v>1488</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4000</v>
+        <v>1860</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>2000</v>
+        <v>930</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>800</v>
+        <v>372</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>1000</v>
+        <v>465</v>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
@@ -1186,24 +1186,24 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1456.667578725713</v>
+        <v>1456.61188270292</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1452.308094466471</v>
+        <v>1452.240766206621</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1461.027062984955</v>
+        <v>1460.982999199218</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>27789</v>
+        <v>45278</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>744</v>
+        <v>1600</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1228,22 +1228,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1488</v>
+        <v>3200</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1860</v>
+        <v>4000</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>744</v>
+        <v>1600</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>930</v>
+        <v>2000</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>372</v>
+        <v>800</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>465</v>
+        <v>1000</v>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1456.005721559645</v>
+        <v>1455.204508770995</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1451.543622501364</v>
+        <v>1450.757783209875</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1460.467820617927</v>
+        <v>1459.651234332115</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>42294</v>
+        <v>43079</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1450.936549214612</v>
+        <v>1450.845963686926</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1443.330198358848</v>
+        <v>1443.242020440113</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1458.542900070375</v>
+        <v>1458.449906933738</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5879</v>
+        <v>5880</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1449.170648038773</v>
+        <v>1449.686152817555</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1445.604711356613</v>
+        <v>1446.130955840993</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1452.736584720933</v>
+        <v>1453.241349794117</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>61978</v>
+        <v>62688</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1446.829985345391</v>
+        <v>1444.91449535471</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1438.056192542738</v>
+        <v>1436.725777828163</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1455.603778148045</v>
+        <v>1453.103212881257</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4641</v>
+        <v>5386</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1865,16 +1865,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1445.041909803335</v>
+        <v>1444.191772600795</v>
       </c>
       <c r="D12" t="n">
-        <v>1439.717848987121</v>
+        <v>1438.89926246057</v>
       </c>
       <c r="E12" t="n">
-        <v>1450.365970619548</v>
+        <v>1449.484282741021</v>
       </c>
       <c r="F12" t="n">
-        <v>27238</v>
+        <v>28093</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1442.240477258664</v>
+        <v>1442.154161219143</v>
       </c>
       <c r="D13" t="n">
-        <v>1438.523694294952</v>
+        <v>1438.447410622318</v>
       </c>
       <c r="E13" t="n">
-        <v>1445.957260222375</v>
+        <v>1445.860911815968</v>
       </c>
       <c r="F13" t="n">
-        <v>57410</v>
+        <v>58157</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2167,16 +2167,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1442.05871009223</v>
+        <v>1442.026608224857</v>
       </c>
       <c r="D14" t="n">
-        <v>1435.96497214086</v>
+        <v>1435.932089853637</v>
       </c>
       <c r="E14" t="n">
-        <v>1448.152448043601</v>
+        <v>1448.121126596078</v>
       </c>
       <c r="F14" t="n">
-        <v>12094</v>
+        <v>12092</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1438.289759291584</v>
+        <v>1438.855493817315</v>
       </c>
       <c r="D15" t="n">
-        <v>1433.882542944215</v>
+        <v>1434.471312902198</v>
       </c>
       <c r="E15" t="n">
-        <v>1442.696975638952</v>
+        <v>1443.239674732432</v>
       </c>
       <c r="F15" t="n">
-        <v>44034</v>
+        <v>44822</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1438.214038403829</v>
+        <v>1438.096686338361</v>
       </c>
       <c r="D16" t="n">
-        <v>1430.571925837276</v>
+        <v>1430.454645637157</v>
       </c>
       <c r="E16" t="n">
-        <v>1445.856150970381</v>
+        <v>1445.738727039564</v>
       </c>
       <c r="F16" t="n">
         <v>5798</v>
@@ -2460,16 +2460,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1436.112599595681</v>
+        <v>1435.502585779531</v>
       </c>
       <c r="D17" t="n">
-        <v>1431.769851381784</v>
+        <v>1431.176121733637</v>
       </c>
       <c r="E17" t="n">
-        <v>1440.455347809578</v>
+        <v>1439.829049825425</v>
       </c>
       <c r="F17" t="n">
-        <v>44220</v>
+        <v>45050</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1433.056835517984</v>
+        <v>1432.991607718435</v>
       </c>
       <c r="D18" t="n">
-        <v>1428.606022597143</v>
+        <v>1428.568609522628</v>
       </c>
       <c r="E18" t="n">
-        <v>1437.507648438825</v>
+        <v>1437.414605914242</v>
       </c>
       <c r="F18" t="n">
-        <v>42281</v>
+        <v>43091</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1431.63909978811</v>
+        <v>1431.439956132471</v>
       </c>
       <c r="D19" t="n">
-        <v>1425.054790520431</v>
+        <v>1424.857005407584</v>
       </c>
       <c r="E19" t="n">
-        <v>1438.223409055789</v>
+        <v>1438.022906857358</v>
       </c>
       <c r="F19" t="n">
-        <v>8177</v>
+        <v>8178</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1429.644051745926</v>
+        <v>1429.739763240676</v>
       </c>
       <c r="D20" t="n">
-        <v>1426.489846241231</v>
+        <v>1426.586897014067</v>
       </c>
       <c r="E20" t="n">
-        <v>1432.798257250622</v>
+        <v>1432.892629467284</v>
       </c>
       <c r="F20" t="n">
-        <v>61948</v>
+        <v>61950</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2984,16 +2984,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1427.577871375094</v>
+        <v>1427.421118527112</v>
       </c>
       <c r="D21" t="n">
-        <v>1420.980190337665</v>
+        <v>1420.835681187804</v>
       </c>
       <c r="E21" t="n">
-        <v>1434.175552412522</v>
+        <v>1434.00655586642</v>
       </c>
       <c r="F21" t="n">
-        <v>11011</v>
+        <v>11019</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3051,68 +3051,148 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>glm-4.6</t>
+          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1425.201154062282</v>
+        <v>1425.246878033284</v>
       </c>
       <c r="D22" t="n">
-        <v>1421.283981912683</v>
+        <v>1418.165151932024</v>
       </c>
       <c r="E22" t="n">
-        <v>1429.118326211882</v>
+        <v>1432.328604134543</v>
       </c>
       <c r="F22" t="n">
-        <v>35613</v>
+        <v>10562</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>OpenMDW-1.1</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>550</v>
+      </c>
+      <c r="J22" t="n">
+        <v>55</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1375</v>
+      </c>
+      <c r="O22" t="n">
+        <v>550</v>
+      </c>
+      <c r="P22" t="n">
+        <v>687.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>275</v>
+      </c>
+      <c r="R22" t="n">
+        <v>343.8</v>
+      </c>
+      <c r="S22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG22" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3122,24 +3202,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>glm-4.6</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1424.89799358709</v>
+        <v>1425.154171031801</v>
       </c>
       <c r="D23" t="n">
-        <v>1421.341148816612</v>
+        <v>1421.236479394814</v>
       </c>
       <c r="E23" t="n">
-        <v>1428.454838357569</v>
+        <v>1429.071862668788</v>
       </c>
       <c r="F23" t="n">
-        <v>47211</v>
+        <v>35608</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3193,20 +3273,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp-thinking</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1424.690164768433</v>
+        <v>1424.922729421823</v>
       </c>
       <c r="D24" t="n">
-        <v>1418.137620319972</v>
+        <v>1421.366937615067</v>
       </c>
       <c r="E24" t="n">
-        <v>1431.242709216895</v>
+        <v>1428.478521228579</v>
       </c>
       <c r="F24" t="n">
-        <v>9067</v>
+        <v>47206</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3264,148 +3344,68 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
+          <t>deepseek-v3.2-exp-thinking</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1424.490243889078</v>
+        <v>1424.72078197068</v>
       </c>
       <c r="D25" t="n">
-        <v>1417.38536843817</v>
+        <v>1418.168156932004</v>
       </c>
       <c r="E25" t="n">
-        <v>1431.595119339985</v>
+        <v>1431.273407009356</v>
       </c>
       <c r="F25" t="n">
-        <v>10283</v>
+        <v>9069</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>OpenMDW-1.1</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>550</v>
-      </c>
-      <c r="J25" t="n">
-        <v>55</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>1100</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1375</v>
-      </c>
-      <c r="O25" t="n">
-        <v>550</v>
-      </c>
-      <c r="P25" t="n">
-        <v>687.5</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>275</v>
-      </c>
-      <c r="R25" t="n">
-        <v>343.8</v>
-      </c>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG25" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3419,16 +3419,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1423.128745521466</v>
+        <v>1423.167908726651</v>
       </c>
       <c r="D26" t="n">
-        <v>1420.537900317795</v>
+        <v>1420.577531185859</v>
       </c>
       <c r="E26" t="n">
-        <v>1425.719590725137</v>
+        <v>1425.758286267442</v>
       </c>
       <c r="F26" t="n">
-        <v>97091</v>
+        <v>97085</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1422.928020590283</v>
+        <v>1422.936775729454</v>
       </c>
       <c r="D27" t="n">
-        <v>1419.280720983351</v>
+        <v>1419.290088081844</v>
       </c>
       <c r="E27" t="n">
-        <v>1426.575320197215</v>
+        <v>1426.583463377064</v>
       </c>
       <c r="F27" t="n">
-        <v>41026</v>
+        <v>41025</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1422.703970598666</v>
+        <v>1422.677384505547</v>
       </c>
       <c r="D28" t="n">
-        <v>1416.301137623493</v>
+        <v>1416.275844462474</v>
       </c>
       <c r="E28" t="n">
-        <v>1429.10680357384</v>
+        <v>1429.07892454862</v>
       </c>
       <c r="F28" t="n">
-        <v>11914</v>
+        <v>11913</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3712,16 +3712,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1422.051565998299</v>
+        <v>1422.06080319141</v>
       </c>
       <c r="D29" t="n">
-        <v>1416.388909455412</v>
+        <v>1416.398314729554</v>
       </c>
       <c r="E29" t="n">
-        <v>1427.714222541186</v>
+        <v>1427.723291653265</v>
       </c>
       <c r="F29" t="n">
-        <v>18452</v>
+        <v>18451</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3783,16 +3783,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1417.854539850099</v>
+        <v>1417.887040680134</v>
       </c>
       <c r="D30" t="n">
-        <v>1411.358875309422</v>
+        <v>1411.388951636052</v>
       </c>
       <c r="E30" t="n">
-        <v>1424.350204390776</v>
+        <v>1424.385129724217</v>
       </c>
       <c r="F30" t="n">
-        <v>11771</v>
+        <v>11770</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3930,29 +3930,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1417.794714417735</v>
+        <v>1417.485512787523</v>
       </c>
       <c r="D31" t="n">
-        <v>1413.617532906306</v>
+        <v>1411.475593200403</v>
       </c>
       <c r="E31" t="n">
-        <v>1421.971895929164</v>
+        <v>1423.495432374643</v>
       </c>
       <c r="F31" t="n">
-        <v>49135</v>
+        <v>14943</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4005,16 +4005,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1417.494372611832</v>
+        <v>1417.465421698817</v>
       </c>
       <c r="D32" t="n">
-        <v>1412.632699552882</v>
+        <v>1412.603242076029</v>
       </c>
       <c r="E32" t="n">
-        <v>1422.356045670781</v>
+        <v>1422.327601321605</v>
       </c>
       <c r="F32" t="n">
-        <v>27605</v>
+        <v>27608</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4152,68 +4152,148 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1417.467976378082</v>
+        <v>1417.302508985613</v>
       </c>
       <c r="D33" t="n">
-        <v>1411.458140391373</v>
+        <v>1412.912164574533</v>
       </c>
       <c r="E33" t="n">
-        <v>1423.477812364792</v>
+        <v>1421.692853396693</v>
       </c>
       <c r="F33" t="n">
-        <v>14941</v>
+        <v>28504</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>122</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>244</v>
+      </c>
+      <c r="N33" t="n">
+        <v>305</v>
+      </c>
+      <c r="O33" t="n">
+        <v>122</v>
+      </c>
+      <c r="P33" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>61</v>
+      </c>
+      <c r="R33" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG33" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -4227,16 +4307,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1417.388151131344</v>
+        <v>1417.244378924961</v>
       </c>
       <c r="D34" t="n">
-        <v>1407.405002033803</v>
+        <v>1407.266197915758</v>
       </c>
       <c r="E34" t="n">
-        <v>1427.371300228885</v>
+        <v>1427.222559934165</v>
       </c>
       <c r="F34" t="n">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4294,148 +4374,68 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1417.310745703428</v>
+        <v>1417.040235153796</v>
       </c>
       <c r="D35" t="n">
-        <v>1412.919452342764</v>
+        <v>1410.428402627879</v>
       </c>
       <c r="E35" t="n">
-        <v>1421.702039064092</v>
+        <v>1423.652067679714</v>
       </c>
       <c r="F35" t="n">
-        <v>28501</v>
+        <v>11726</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>122</v>
-      </c>
-      <c r="J35" t="n">
-        <v>10</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>244</v>
-      </c>
-      <c r="N35" t="n">
-        <v>305</v>
-      </c>
-      <c r="O35" t="n">
-        <v>122</v>
-      </c>
-      <c r="P35" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>61</v>
-      </c>
-      <c r="R35" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="S35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA35" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC35" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD35" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE35" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF35" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG35" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4445,29 +4445,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1417.013207630177</v>
+        <v>1416.749237585832</v>
       </c>
       <c r="D36" t="n">
-        <v>1410.400984231822</v>
+        <v>1412.590434905026</v>
       </c>
       <c r="E36" t="n">
-        <v>1423.625431028531</v>
+        <v>1420.908040266638</v>
       </c>
       <c r="F36" t="n">
-        <v>11723</v>
+        <v>49930</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4520,16 +4520,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1415.325135314627</v>
+        <v>1415.385519177652</v>
       </c>
       <c r="D37" t="n">
-        <v>1411.923711597329</v>
+        <v>1412.004503146111</v>
       </c>
       <c r="E37" t="n">
-        <v>1418.726559031927</v>
+        <v>1418.766535209193</v>
       </c>
       <c r="F37" t="n">
-        <v>50153</v>
+        <v>50849</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4667,148 +4667,68 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>deepseek-v3.1-terminus</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1415.316260620056</v>
+        <v>1415.279967701172</v>
       </c>
       <c r="D38" t="n">
-        <v>1408.829547346817</v>
+        <v>1405.658269353508</v>
       </c>
       <c r="E38" t="n">
-        <v>1421.802973893296</v>
+        <v>1424.901666048836</v>
       </c>
       <c r="F38" t="n">
-        <v>11498</v>
+        <v>3692</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>235</v>
-      </c>
-      <c r="J38" t="n">
-        <v>22</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>470</v>
-      </c>
-      <c r="N38" t="n">
-        <v>587.5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>235</v>
-      </c>
-      <c r="P38" t="n">
-        <v>293.8</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>117.5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4818,68 +4738,148 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1415.271872557412</v>
+        <v>1415.268090068343</v>
       </c>
       <c r="D39" t="n">
-        <v>1405.647180944011</v>
+        <v>1408.782875202925</v>
       </c>
       <c r="E39" t="n">
-        <v>1424.896564170813</v>
+        <v>1421.753304933762</v>
       </c>
       <c r="F39" t="n">
-        <v>3690</v>
+        <v>11499</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>235</v>
+      </c>
+      <c r="J39" t="n">
+        <v>22</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>470</v>
+      </c>
+      <c r="N39" t="n">
+        <v>587.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>235</v>
+      </c>
+      <c r="P39" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD39" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG39" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1412.042888024911</v>
+        <v>1412.115022145458</v>
       </c>
       <c r="D40" t="n">
-        <v>1404.491960004872</v>
+        <v>1404.56260543845</v>
       </c>
       <c r="E40" t="n">
-        <v>1419.593816044951</v>
+        <v>1419.667438852465</v>
       </c>
       <c r="F40" t="n">
-        <v>6637</v>
+        <v>6634</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4964,16 +4964,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1410.870087399092</v>
+        <v>1410.925499435077</v>
       </c>
       <c r="D41" t="n">
-        <v>1405.986145399707</v>
+        <v>1406.041508267166</v>
       </c>
       <c r="E41" t="n">
-        <v>1415.754029398477</v>
+        <v>1415.809490602988</v>
       </c>
       <c r="F41" t="n">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1408.743226917476</v>
+        <v>1408.629929971069</v>
       </c>
       <c r="D42" t="n">
-        <v>1404.318553391284</v>
+        <v>1404.2053505955</v>
       </c>
       <c r="E42" t="n">
-        <v>1413.167900443668</v>
+        <v>1413.054509346639</v>
       </c>
       <c r="F42" t="n">
-        <v>27308</v>
+        <v>27314</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5266,16 +5266,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1403.026750033887</v>
+        <v>1403.008998556308</v>
       </c>
       <c r="D43" t="n">
-        <v>1398.523105984381</v>
+        <v>1398.505521967363</v>
       </c>
       <c r="E43" t="n">
-        <v>1407.530394083393</v>
+        <v>1407.512475145254</v>
       </c>
       <c r="F43" t="n">
-        <v>38175</v>
+        <v>38174</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5417,16 +5417,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1401.278087167683</v>
+        <v>1401.191746747603</v>
       </c>
       <c r="D44" t="n">
-        <v>1396.502583384474</v>
+        <v>1396.41858352292</v>
       </c>
       <c r="E44" t="n">
-        <v>1406.053590950892</v>
+        <v>1405.964909972287</v>
       </c>
       <c r="F44" t="n">
-        <v>22853</v>
+        <v>22859</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5568,16 +5568,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1401.229497492934</v>
+        <v>1401.142199318849</v>
       </c>
       <c r="D45" t="n">
-        <v>1394.861810842025</v>
+        <v>1394.776371437358</v>
       </c>
       <c r="E45" t="n">
-        <v>1407.597184143844</v>
+        <v>1407.508027200339</v>
       </c>
       <c r="F45" t="n">
-        <v>11384</v>
+        <v>11387</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5719,13 +5719,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1399.038625289758</v>
+        <v>1399.125213054004</v>
       </c>
       <c r="D46" t="n">
-        <v>1392.50464720129</v>
+        <v>1392.591455272177</v>
       </c>
       <c r="E46" t="n">
-        <v>1405.572603378226</v>
+        <v>1405.658970835831</v>
       </c>
       <c r="F46" t="n">
         <v>8985</v>
@@ -5870,13 +5870,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1398.100081968736</v>
+        <v>1398.137056740891</v>
       </c>
       <c r="D47" t="n">
-        <v>1393.218954982903</v>
+        <v>1393.255890032814</v>
       </c>
       <c r="E47" t="n">
-        <v>1402.981208954569</v>
+        <v>1403.018223448969</v>
       </c>
       <c r="F47" t="n">
         <v>18524</v>
@@ -6021,16 +6021,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1395.727191837466</v>
+        <v>1395.74834802342</v>
       </c>
       <c r="D48" t="n">
-        <v>1391.386585124081</v>
+        <v>1391.409180832079</v>
       </c>
       <c r="E48" t="n">
-        <v>1400.067798550851</v>
+        <v>1400.08751521476</v>
       </c>
       <c r="F48" t="n">
-        <v>29157</v>
+        <v>29158</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1395.509704625214</v>
+        <v>1395.598432053695</v>
       </c>
       <c r="D49" t="n">
-        <v>1391.635015924753</v>
+        <v>1391.723543164014</v>
       </c>
       <c r="E49" t="n">
-        <v>1399.384393325675</v>
+        <v>1399.473320943376</v>
       </c>
       <c r="F49" t="n">
         <v>45480</v>
@@ -6323,16 +6323,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1395.429014206356</v>
+        <v>1395.205259706208</v>
       </c>
       <c r="D50" t="n">
-        <v>1388.636389892122</v>
+        <v>1388.415725335228</v>
       </c>
       <c r="E50" t="n">
-        <v>1402.22163852059</v>
+        <v>1401.994794077189</v>
       </c>
       <c r="F50" t="n">
-        <v>7937</v>
+        <v>7941</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6474,16 +6474,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1394.933883143331</v>
+        <v>1395.121703958286</v>
       </c>
       <c r="D51" t="n">
-        <v>1391.231640900405</v>
+        <v>1391.431013033422</v>
       </c>
       <c r="E51" t="n">
-        <v>1398.636125386256</v>
+        <v>1398.812394883151</v>
       </c>
       <c r="F51" t="n">
-        <v>55180</v>
+        <v>55991</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1392.80694529516</v>
+        <v>1392.824478716531</v>
       </c>
       <c r="D52" t="n">
-        <v>1389.241916956919</v>
+        <v>1389.259741298123</v>
       </c>
       <c r="E52" t="n">
-        <v>1396.371973633402</v>
+        <v>1396.389216134939</v>
       </c>
       <c r="F52" t="n">
-        <v>46546</v>
+        <v>46549</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1390.567463304082</v>
+        <v>1390.473988329471</v>
       </c>
       <c r="D53" t="n">
-        <v>1386.5704950236</v>
+        <v>1386.478085321633</v>
       </c>
       <c r="E53" t="n">
-        <v>1394.564431584564</v>
+        <v>1394.469891337309</v>
       </c>
       <c r="F53" t="n">
-        <v>41092</v>
+        <v>41088</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1387.53239677035</v>
+        <v>1387.522716010818</v>
       </c>
       <c r="D54" t="n">
-        <v>1382.583309274739</v>
+        <v>1382.573331850739</v>
       </c>
       <c r="E54" t="n">
-        <v>1392.481484265961</v>
+        <v>1392.472100170897</v>
       </c>
       <c r="F54" t="n">
         <v>25694</v>
@@ -6838,16 +6838,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1387.102448057369</v>
+        <v>1387.092441092224</v>
       </c>
       <c r="D55" t="n">
-        <v>1380.855725443215</v>
+        <v>1380.846839065397</v>
       </c>
       <c r="E55" t="n">
-        <v>1393.349170671524</v>
+        <v>1393.33804311905</v>
       </c>
       <c r="F55" t="n">
-        <v>10937</v>
+        <v>10934</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1384.21773226426</v>
+        <v>1384.059442723391</v>
       </c>
       <c r="D56" t="n">
-        <v>1378.986243352277</v>
+        <v>1378.832497790107</v>
       </c>
       <c r="E56" t="n">
-        <v>1389.449221176243</v>
+        <v>1389.286387656675</v>
       </c>
       <c r="F56" t="n">
-        <v>17072</v>
+        <v>17083</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -6980,16 +6980,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1383.121583952506</v>
+        <v>1383.109270022562</v>
       </c>
       <c r="D57" t="n">
-        <v>1378.239091441849</v>
+        <v>1378.228394952425</v>
       </c>
       <c r="E57" t="n">
-        <v>1388.004076463162</v>
+        <v>1387.990145092699</v>
       </c>
       <c r="F57" t="n">
-        <v>23715</v>
+        <v>23718</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7131,16 +7131,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1378.740864981144</v>
+        <v>1378.504007771911</v>
       </c>
       <c r="D58" t="n">
-        <v>1374.387088625828</v>
+        <v>1374.148555532209</v>
       </c>
       <c r="E58" t="n">
-        <v>1383.094641336459</v>
+        <v>1382.859460011612</v>
       </c>
       <c r="F58" t="n">
-        <v>30061</v>
+        <v>30052</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
@@ -7278,16 +7278,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1377.199854797745</v>
+        <v>1377.245392146705</v>
       </c>
       <c r="D59" t="n">
-        <v>1365.94214135508</v>
+        <v>1365.984366590571</v>
       </c>
       <c r="E59" t="n">
-        <v>1388.457568240409</v>
+        <v>1388.50641770284</v>
       </c>
       <c r="F59" t="n">
-        <v>2801</v>
+        <v>2797</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7349,16 +7349,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1374.755177280887</v>
+        <v>1374.818431758672</v>
       </c>
       <c r="D60" t="n">
-        <v>1370.059113633707</v>
+        <v>1370.122704145862</v>
       </c>
       <c r="E60" t="n">
-        <v>1379.451240928068</v>
+        <v>1379.514159371482</v>
       </c>
       <c r="F60" t="n">
-        <v>26257</v>
+        <v>26254</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7500,13 +7500,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1373.079982997584</v>
+        <v>1372.918636184175</v>
       </c>
       <c r="D61" t="n">
-        <v>1368.835236876116</v>
+        <v>1368.67326383416</v>
       </c>
       <c r="E61" t="n">
-        <v>1377.324729119053</v>
+        <v>1377.164008534191</v>
       </c>
       <c r="F61" t="n">
         <v>31062</v>
@@ -7571,13 +7571,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1369.520186991673</v>
+        <v>1369.52270186199</v>
       </c>
       <c r="D62" t="n">
-        <v>1363.680122797909</v>
+        <v>1363.682819149285</v>
       </c>
       <c r="E62" t="n">
-        <v>1375.360251185437</v>
+        <v>1375.362584574694</v>
       </c>
       <c r="F62" t="n">
         <v>13678</v>
@@ -7722,13 +7722,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1369.386447163973</v>
+        <v>1369.390332831636</v>
       </c>
       <c r="D63" t="n">
-        <v>1364.694972410402</v>
+        <v>1364.699472013072</v>
       </c>
       <c r="E63" t="n">
-        <v>1374.077921917544</v>
+        <v>1374.0811936502</v>
       </c>
       <c r="F63" t="n">
         <v>29139</v>
@@ -7869,16 +7869,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1367.93138665937</v>
+        <v>1368.079979932808</v>
       </c>
       <c r="D64" t="n">
-        <v>1362.130915570182</v>
+        <v>1362.282571694845</v>
       </c>
       <c r="E64" t="n">
-        <v>1373.731857748557</v>
+        <v>1373.877388170771</v>
       </c>
       <c r="F64" t="n">
-        <v>11706</v>
+        <v>11719</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1365.710682324167</v>
+        <v>1365.740195183558</v>
       </c>
       <c r="D65" t="n">
-        <v>1362.034235256296</v>
+        <v>1362.064310953721</v>
       </c>
       <c r="E65" t="n">
-        <v>1369.387129392039</v>
+        <v>1369.416079413395</v>
       </c>
       <c r="F65" t="n">
-        <v>47500</v>
+        <v>47508</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8091,16 +8091,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1363.754762529222</v>
+        <v>1363.757140450509</v>
       </c>
       <c r="D66" t="n">
-        <v>1359.480593352698</v>
+        <v>1359.483534394273</v>
       </c>
       <c r="E66" t="n">
-        <v>1368.028931705746</v>
+        <v>1368.030746506746</v>
       </c>
       <c r="F66" t="n">
-        <v>35156</v>
+        <v>35163</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8162,16 +8162,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1361.582549581825</v>
+        <v>1361.561135699234</v>
       </c>
       <c r="D67" t="n">
-        <v>1354.318947532643</v>
+        <v>1354.299516579975</v>
       </c>
       <c r="E67" t="n">
-        <v>1368.846151631008</v>
+        <v>1368.822754818494</v>
       </c>
       <c r="F67" t="n">
-        <v>7542</v>
+        <v>7544</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8313,13 +8313,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1358.473581082121</v>
+        <v>1358.502830033216</v>
       </c>
       <c r="D68" t="n">
-        <v>1353.728541658715</v>
+        <v>1353.757793972289</v>
       </c>
       <c r="E68" t="n">
-        <v>1363.218620505528</v>
+        <v>1363.247866094144</v>
       </c>
       <c r="F68" t="n">
         <v>21770</v>
@@ -8464,16 +8464,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1357.525691796576</v>
+        <v>1357.507793257623</v>
       </c>
       <c r="D69" t="n">
-        <v>1352.323565656812</v>
+        <v>1352.305893579585</v>
       </c>
       <c r="E69" t="n">
-        <v>1362.727817936339</v>
+        <v>1362.70969293566</v>
       </c>
       <c r="F69" t="n">
-        <v>17696</v>
+        <v>17698</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8535,16 +8535,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1356.251952365599</v>
+        <v>1356.201502422433</v>
       </c>
       <c r="D70" t="n">
-        <v>1347.909693287186</v>
+        <v>1347.858233488323</v>
       </c>
       <c r="E70" t="n">
-        <v>1364.594211444012</v>
+        <v>1364.544771356542</v>
       </c>
       <c r="F70" t="n">
-        <v>5327</v>
+        <v>5328</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
@@ -8682,16 +8682,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1353.91274354248</v>
+        <v>1353.930131428436</v>
       </c>
       <c r="D71" t="n">
-        <v>1350.461480579952</v>
+        <v>1350.47905528907</v>
       </c>
       <c r="E71" t="n">
-        <v>1357.364006505008</v>
+        <v>1357.381207567801</v>
       </c>
       <c r="F71" t="n">
-        <v>56224</v>
+        <v>56217</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8753,16 +8753,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1353.52977755157</v>
+        <v>1353.431016284907</v>
       </c>
       <c r="D72" t="n">
-        <v>1345.184883851595</v>
+        <v>1345.08651906331</v>
       </c>
       <c r="E72" t="n">
-        <v>1361.874671251546</v>
+        <v>1361.775513506504</v>
       </c>
       <c r="F72" t="n">
-        <v>4955</v>
+        <v>4957</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8824,16 +8824,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1352.512546944002</v>
+        <v>1352.483567590135</v>
       </c>
       <c r="D73" t="n">
-        <v>1348.162781970094</v>
+        <v>1348.134053396888</v>
       </c>
       <c r="E73" t="n">
-        <v>1356.86231191791</v>
+        <v>1356.833081783382</v>
       </c>
       <c r="F73" t="n">
-        <v>30611</v>
+        <v>30615</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8975,16 +8975,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1348.345488463941</v>
+        <v>1348.309705720206</v>
       </c>
       <c r="D74" t="n">
-        <v>1340.940352836867</v>
+        <v>1340.904894389518</v>
       </c>
       <c r="E74" t="n">
-        <v>1355.750624091015</v>
+        <v>1355.714517050895</v>
       </c>
       <c r="F74" t="n">
-        <v>6533</v>
+        <v>6532</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9046,13 +9046,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1347.453960624794</v>
+        <v>1347.486758584034</v>
       </c>
       <c r="D75" t="n">
-        <v>1335.769525788442</v>
+        <v>1335.802501041766</v>
       </c>
       <c r="E75" t="n">
-        <v>1359.138395461147</v>
+        <v>1359.171016126302</v>
       </c>
       <c r="F75" t="n">
         <v>2549</v>
@@ -9197,13 +9197,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1347.192357787633</v>
+        <v>1347.20361644688</v>
       </c>
       <c r="D76" t="n">
-        <v>1337.733915744826</v>
+        <v>1337.745283803482</v>
       </c>
       <c r="E76" t="n">
-        <v>1356.650799830439</v>
+        <v>1356.661949090279</v>
       </c>
       <c r="F76" t="n">
         <v>3926</v>
@@ -9348,16 +9348,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1346.223019693378</v>
+        <v>1346.248366843437</v>
       </c>
       <c r="D77" t="n">
-        <v>1338.959503848691</v>
+        <v>1338.984509850068</v>
       </c>
       <c r="E77" t="n">
-        <v>1353.486535538066</v>
+        <v>1353.512223836806</v>
       </c>
       <c r="F77" t="n">
-        <v>6998</v>
+        <v>6997</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9419,16 +9419,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1346.023223584868</v>
+        <v>1345.944015808131</v>
       </c>
       <c r="D78" t="n">
-        <v>1338.284325044147</v>
+        <v>1338.205841447108</v>
       </c>
       <c r="E78" t="n">
-        <v>1353.762122125589</v>
+        <v>1353.682190169154</v>
       </c>
       <c r="F78" t="n">
-        <v>6860</v>
+        <v>6862</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1343.157198341073</v>
+        <v>1343.170228261069</v>
       </c>
       <c r="D79" t="n">
-        <v>1333.189913320729</v>
+        <v>1333.20308339862</v>
       </c>
       <c r="E79" t="n">
-        <v>1353.124483361416</v>
+        <v>1353.137373123519</v>
       </c>
       <c r="F79" t="n">
         <v>3344</v>
@@ -9721,13 +9721,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1341.872342543547</v>
+        <v>1341.887204698197</v>
       </c>
       <c r="D80" t="n">
-        <v>1332.362864293103</v>
+        <v>1332.377849478545</v>
       </c>
       <c r="E80" t="n">
-        <v>1351.381820793992</v>
+        <v>1351.39655991785</v>
       </c>
       <c r="F80" t="n">
         <v>3829</v>
@@ -9872,16 +9872,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1336.093674137507</v>
+        <v>1336.121138236919</v>
       </c>
       <c r="D81" t="n">
-        <v>1331.651382226096</v>
+        <v>1331.679126183227</v>
       </c>
       <c r="E81" t="n">
-        <v>1340.535966048918</v>
+        <v>1340.563150290611</v>
       </c>
       <c r="F81" t="n">
-        <v>25376</v>
+        <v>25379</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -10023,13 +10023,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1334.810797907552</v>
+        <v>1334.823705315042</v>
       </c>
       <c r="D82" t="n">
-        <v>1331.095207128169</v>
+        <v>1331.108156733898</v>
       </c>
       <c r="E82" t="n">
-        <v>1338.526388686935</v>
+        <v>1338.539253896186</v>
       </c>
       <c r="F82" t="n">
         <v>41375</v>
@@ -10174,13 +10174,13 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1332.976711191494</v>
+        <v>1332.994645925193</v>
       </c>
       <c r="D83" t="n">
-        <v>1329.378623114978</v>
+        <v>1329.396797669843</v>
       </c>
       <c r="E83" t="n">
-        <v>1336.574799268009</v>
+        <v>1336.592494180543</v>
       </c>
       <c r="F83" t="n">
         <v>59656</v>
@@ -10325,16 +10325,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1329.973502273341</v>
+        <v>1330.034408321599</v>
       </c>
       <c r="D84" t="n">
-        <v>1323.894878850461</v>
+        <v>1323.957928775754</v>
       </c>
       <c r="E84" t="n">
-        <v>1336.052125696221</v>
+        <v>1336.110887867444</v>
       </c>
       <c r="F84" t="n">
-        <v>12205</v>
+        <v>12211</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -10476,16 +10476,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1328.755372914642</v>
+        <v>1328.434124658088</v>
       </c>
       <c r="D85" t="n">
-        <v>1307.430022391315</v>
+        <v>1307.112119205039</v>
       </c>
       <c r="E85" t="n">
-        <v>1350.080723437969</v>
+        <v>1349.756130111137</v>
       </c>
       <c r="F85" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -10627,13 +10627,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1327.962455047806</v>
+        <v>1328.009045121247</v>
       </c>
       <c r="D86" t="n">
-        <v>1315.815585435525</v>
+        <v>1315.8625472777</v>
       </c>
       <c r="E86" t="n">
-        <v>1340.109324660086</v>
+        <v>1340.155542964795</v>
       </c>
       <c r="F86" t="n">
         <v>2218</v>
@@ -10778,16 +10778,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1327.172982805329</v>
+        <v>1327.216106600916</v>
       </c>
       <c r="D87" t="n">
-        <v>1322.442491969774</v>
+        <v>1322.486186026997</v>
       </c>
       <c r="E87" t="n">
-        <v>1331.903473640885</v>
+        <v>1331.946027174835</v>
       </c>
       <c r="F87" t="n">
-        <v>26469</v>
+        <v>26470</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10929,16 +10929,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1327.040043914698</v>
+        <v>1327.078836246602</v>
       </c>
       <c r="D88" t="n">
-        <v>1322.786091324946</v>
+        <v>1322.825051751384</v>
       </c>
       <c r="E88" t="n">
-        <v>1331.29399650445</v>
+        <v>1331.33262074182</v>
       </c>
       <c r="F88" t="n">
-        <v>39951</v>
+        <v>39950</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -11080,13 +11080,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1323.426458416441</v>
+        <v>1323.458053410114</v>
       </c>
       <c r="D89" t="n">
-        <v>1315.155085070072</v>
+        <v>1315.186770066311</v>
       </c>
       <c r="E89" t="n">
-        <v>1331.697831762809</v>
+        <v>1331.729336753917</v>
       </c>
       <c r="F89" t="n">
         <v>6795</v>
@@ -11151,16 +11151,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1322.796915967902</v>
+        <v>1322.709824246838</v>
       </c>
       <c r="D90" t="n">
-        <v>1318.088699444527</v>
+        <v>1318.000835779929</v>
       </c>
       <c r="E90" t="n">
-        <v>1327.505132491278</v>
+        <v>1327.418812713748</v>
       </c>
       <c r="F90" t="n">
-        <v>30273</v>
+        <v>30265</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -11302,16 +11302,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1320.624087499929</v>
+        <v>1320.643432386708</v>
       </c>
       <c r="D91" t="n">
-        <v>1313.405248617077</v>
+        <v>1313.426520454698</v>
       </c>
       <c r="E91" t="n">
-        <v>1327.842926382781</v>
+        <v>1327.860344318718</v>
       </c>
       <c r="F91" t="n">
-        <v>7135</v>
+        <v>7138</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -11373,16 +11373,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1318.176518006124</v>
+        <v>1318.154668707943</v>
       </c>
       <c r="D92" t="n">
-        <v>1314.699222004554</v>
+        <v>1314.677546208555</v>
       </c>
       <c r="E92" t="n">
-        <v>1321.653814007694</v>
+        <v>1321.631791207332</v>
       </c>
       <c r="F92" t="n">
-        <v>54720</v>
+        <v>54723</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -11524,16 +11524,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1318.040129441017</v>
+        <v>1318.039018442979</v>
       </c>
       <c r="D93" t="n">
-        <v>1312.891686370832</v>
+        <v>1312.890321506359</v>
       </c>
       <c r="E93" t="n">
-        <v>1323.188572511202</v>
+        <v>1323.187715379599</v>
       </c>
       <c r="F93" t="n">
-        <v>22569</v>
+        <v>22565</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1317.957563159107</v>
+        <v>1317.986629720632</v>
       </c>
       <c r="D94" t="n">
-        <v>1312.256142100119</v>
+        <v>1312.285413605662</v>
       </c>
       <c r="E94" t="n">
-        <v>1323.658984218095</v>
+        <v>1323.687845835602</v>
       </c>
       <c r="F94" t="n">
         <v>16478</v>
@@ -11746,16 +11746,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1317.221104840175</v>
+        <v>1317.243550806812</v>
       </c>
       <c r="D95" t="n">
-        <v>1310.850338828237</v>
+        <v>1310.872808905991</v>
       </c>
       <c r="E95" t="n">
-        <v>1323.591870852114</v>
+        <v>1323.614292707633</v>
       </c>
       <c r="F95" t="n">
-        <v>10620</v>
+        <v>10621</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -11897,16 +11897,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1315.560449204706</v>
+        <v>1315.647226874094</v>
       </c>
       <c r="D96" t="n">
-        <v>1310.019751895052</v>
+        <v>1310.10626001488</v>
       </c>
       <c r="E96" t="n">
-        <v>1321.10114651436</v>
+        <v>1321.188193733308</v>
       </c>
       <c r="F96" t="n">
-        <v>15496</v>
+        <v>15494</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -12048,13 +12048,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1314.275557966814</v>
+        <v>1314.298415782136</v>
       </c>
       <c r="D97" t="n">
-        <v>1309.720457344463</v>
+        <v>1309.743375363217</v>
       </c>
       <c r="E97" t="n">
-        <v>1318.830658589165</v>
+        <v>1318.853456201054</v>
       </c>
       <c r="F97" t="n">
         <v>24739</v>
@@ -12195,13 +12195,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1314.007561624775</v>
+        <v>1314.040264642194</v>
       </c>
       <c r="D98" t="n">
-        <v>1310.079021894053</v>
+        <v>1310.11195312341</v>
       </c>
       <c r="E98" t="n">
-        <v>1317.936101355497</v>
+        <v>1317.968576160979</v>
       </c>
       <c r="F98" t="n">
         <v>45459</v>
@@ -12342,148 +12342,68 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>granite-4.1-8b</t>
+          <t>deepseek-v2.5</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1307.430114329379</v>
+        <v>1307.120203016762</v>
       </c>
       <c r="D99" t="n">
-        <v>1297.316414981337</v>
+        <v>1302.412473082301</v>
       </c>
       <c r="E99" t="n">
-        <v>1317.54381367742</v>
+        <v>1311.827932951224</v>
       </c>
       <c r="F99" t="n">
-        <v>4064</v>
+        <v>24572</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>8</v>
-      </c>
-      <c r="J99" t="n">
-        <v>8</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M99" t="n">
-        <v>16</v>
-      </c>
-      <c r="N99" t="n">
-        <v>20</v>
-      </c>
-      <c r="O99" t="n">
-        <v>8</v>
-      </c>
-      <c r="P99" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>4</v>
-      </c>
-      <c r="R99" t="n">
-        <v>5</v>
-      </c>
-      <c r="S99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG99" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -12493,68 +12413,148 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>deepseek-v2.5</t>
+          <t>granite-4.1-8b</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1307.084285130692</v>
+        <v>1307.005583309644</v>
       </c>
       <c r="D100" t="n">
-        <v>1302.376414594843</v>
+        <v>1296.883589203281</v>
       </c>
       <c r="E100" t="n">
-        <v>1311.79215566654</v>
+        <v>1317.127577416007</v>
       </c>
       <c r="F100" t="n">
-        <v>24572</v>
+        <v>4062</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>8</v>
+      </c>
+      <c r="J100" t="n">
+        <v>8</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
-      <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
-      <c r="AC100" t="inlineStr"/>
-      <c r="AD100" t="inlineStr"/>
-      <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>16</v>
+      </c>
+      <c r="N100" t="n">
+        <v>20</v>
+      </c>
+      <c r="O100" t="n">
+        <v>8</v>
+      </c>
+      <c r="P100" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>4</v>
+      </c>
+      <c r="R100" t="n">
+        <v>5</v>
+      </c>
+      <c r="S100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1306.296123092853</v>
+        <v>1306.353434718117</v>
       </c>
       <c r="D101" t="n">
-        <v>1300.620418235285</v>
+        <v>1300.677954382722</v>
       </c>
       <c r="E101" t="n">
-        <v>1311.971827950421</v>
+        <v>1312.028915053511</v>
       </c>
       <c r="F101" t="n">
         <v>19621</v>
@@ -12715,16 +12715,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1305.562240763531</v>
+        <v>1305.598946173152</v>
       </c>
       <c r="D102" t="n">
-        <v>1297.384780669159</v>
+        <v>1297.418435565635</v>
       </c>
       <c r="E102" t="n">
-        <v>1313.739700857903</v>
+        <v>1313.77945678067</v>
       </c>
       <c r="F102" t="n">
-        <v>5938</v>
+        <v>5933</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -12866,13 +12866,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1305.271458751643</v>
+        <v>1305.297388074803</v>
       </c>
       <c r="D103" t="n">
-        <v>1300.832170817371</v>
+        <v>1300.858084159496</v>
       </c>
       <c r="E103" t="n">
-        <v>1309.710746685914</v>
+        <v>1309.73669199011</v>
       </c>
       <c r="F103" t="n">
         <v>28073</v>
@@ -12933,36 +12933,36 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1303.289010297977</v>
+        <v>1303.300873659234</v>
       </c>
       <c r="D104" t="n">
-        <v>1298.77941415298</v>
+        <v>1293.985013153311</v>
       </c>
       <c r="E104" t="n">
-        <v>1307.798606442974</v>
+        <v>1312.616734165158</v>
       </c>
       <c r="F104" t="n">
-        <v>33194</v>
+        <v>4171</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -12975,22 +12975,22 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N104" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q104" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R104" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="S104" s="6" t="inlineStr">
         <is>
@@ -13084,36 +13084,36 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1303.283904155892</v>
+        <v>1303.297076309148</v>
       </c>
       <c r="D105" t="n">
-        <v>1293.967913829794</v>
+        <v>1298.78713621594</v>
       </c>
       <c r="E105" t="n">
-        <v>1312.599894481991</v>
+        <v>1307.807016402357</v>
       </c>
       <c r="F105" t="n">
-        <v>4171</v>
+        <v>33189</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J105" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -13126,22 +13126,22 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N105" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O105" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P105" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q105" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R105" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="S105" s="6" t="inlineStr">
         <is>
@@ -13239,13 +13239,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1302.800229358561</v>
+        <v>1302.831083974547</v>
       </c>
       <c r="D106" t="n">
-        <v>1298.723736842753</v>
+        <v>1298.754691144902</v>
       </c>
       <c r="E106" t="n">
-        <v>1306.876721874369</v>
+        <v>1306.907476804191</v>
       </c>
       <c r="F106" t="n">
         <v>39406</v>
@@ -13390,13 +13390,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1298.929944664778</v>
+        <v>1298.974687739563</v>
       </c>
       <c r="D107" t="n">
-        <v>1291.166318776369</v>
+        <v>1291.211203426122</v>
       </c>
       <c r="E107" t="n">
-        <v>1306.693570553188</v>
+        <v>1306.738172053004</v>
       </c>
       <c r="F107" t="n">
         <v>7140</v>
@@ -13541,13 +13541,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1293.148439937676</v>
+        <v>1293.18067133492</v>
       </c>
       <c r="D108" t="n">
-        <v>1289.409617448781</v>
+        <v>1289.442037562299</v>
       </c>
       <c r="E108" t="n">
-        <v>1296.887262426572</v>
+        <v>1296.919305107542</v>
       </c>
       <c r="F108" t="n">
         <v>55240</v>
@@ -13692,13 +13692,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1289.042080341524</v>
+        <v>1289.085904497508</v>
       </c>
       <c r="D109" t="n">
-        <v>1281.734118395666</v>
+        <v>1281.77815588373</v>
       </c>
       <c r="E109" t="n">
-        <v>1296.350042287383</v>
+        <v>1296.393653111285</v>
       </c>
       <c r="F109" t="n">
         <v>8662</v>
@@ -13759,13 +13759,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1288.907015620166</v>
+        <v>1288.981352097969</v>
       </c>
       <c r="D110" t="n">
-        <v>1285.521877226685</v>
+        <v>1285.596444514124</v>
       </c>
       <c r="E110" t="n">
-        <v>1292.292154013646</v>
+        <v>1292.366259681815</v>
       </c>
       <c r="F110" t="n">
         <v>75754</v>
@@ -13910,13 +13910,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1286.96458787542</v>
+        <v>1287.209383352116</v>
       </c>
       <c r="D111" t="n">
-        <v>1278.572678956902</v>
+        <v>1278.819560553639</v>
       </c>
       <c r="E111" t="n">
-        <v>1295.356496793939</v>
+        <v>1295.599206150594</v>
       </c>
       <c r="F111" t="n">
         <v>5682</v>
@@ -14061,13 +14061,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1285.931294653923</v>
+        <v>1285.956701257327</v>
       </c>
       <c r="D112" t="n">
-        <v>1275.958675713537</v>
+        <v>1275.984203908687</v>
       </c>
       <c r="E112" t="n">
-        <v>1295.903913594309</v>
+        <v>1295.929198605968</v>
       </c>
       <c r="F112" t="n">
         <v>3749</v>
@@ -14212,13 +14212,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1285.92774487092</v>
+        <v>1285.93794881795</v>
       </c>
       <c r="D113" t="n">
-        <v>1275.460194503759</v>
+        <v>1275.470605249893</v>
       </c>
       <c r="E113" t="n">
-        <v>1296.395295238081</v>
+        <v>1296.405292386008</v>
       </c>
       <c r="F113" t="n">
         <v>2846</v>
@@ -14363,16 +14363,16 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1285.006669255047</v>
+        <v>1284.98964750642</v>
       </c>
       <c r="D114" t="n">
-        <v>1277.801362054064</v>
+        <v>1277.784837684343</v>
       </c>
       <c r="E114" t="n">
-        <v>1292.21197645603</v>
+        <v>1292.194457328497</v>
       </c>
       <c r="F114" t="n">
-        <v>8497</v>
+        <v>8495</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -14514,13 +14514,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1279.877385715841</v>
+        <v>1279.949627633725</v>
       </c>
       <c r="D115" t="n">
-        <v>1273.015753651824</v>
+        <v>1273.088286511277</v>
       </c>
       <c r="E115" t="n">
-        <v>1286.739017779857</v>
+        <v>1286.810968756172</v>
       </c>
       <c r="F115" t="n">
         <v>10072</v>
@@ -14661,13 +14661,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1276.535404576134</v>
+        <v>1276.537010046516</v>
       </c>
       <c r="D116" t="n">
-        <v>1271.207840244072</v>
+        <v>1271.209851694353</v>
       </c>
       <c r="E116" t="n">
-        <v>1281.862968908196</v>
+        <v>1281.864168398679</v>
       </c>
       <c r="F116" t="n">
         <v>19659</v>
@@ -14812,13 +14812,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1275.941459756536</v>
+        <v>1275.976201332212</v>
       </c>
       <c r="D117" t="n">
-        <v>1272.351079126974</v>
+        <v>1272.386364747269</v>
       </c>
       <c r="E117" t="n">
-        <v>1279.531840386098</v>
+        <v>1279.566037917155</v>
       </c>
       <c r="F117" t="n">
         <v>156876</v>
@@ -14963,13 +14963,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1275.81408158539</v>
+        <v>1275.820789276955</v>
       </c>
       <c r="D118" t="n">
-        <v>1269.23508778787</v>
+        <v>1269.241945728407</v>
       </c>
       <c r="E118" t="n">
-        <v>1282.393075382909</v>
+        <v>1282.399632825503</v>
       </c>
       <c r="F118" t="n">
         <v>9866</v>
@@ -15114,13 +15114,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1274.087509480036</v>
+        <v>1274.113179727952</v>
       </c>
       <c r="D119" t="n">
-        <v>1268.178487552353</v>
+        <v>1268.204077284541</v>
       </c>
       <c r="E119" t="n">
-        <v>1279.996531407719</v>
+        <v>1280.022282171364</v>
       </c>
       <c r="F119" t="n">
         <v>14681</v>
@@ -15265,13 +15265,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1270.37359394284</v>
+        <v>1270.398937174391</v>
       </c>
       <c r="D120" t="n">
-        <v>1262.245198982299</v>
+        <v>1262.270597357053</v>
       </c>
       <c r="E120" t="n">
-        <v>1278.501988903381</v>
+        <v>1278.527276991727</v>
       </c>
       <c r="F120" t="n">
         <v>5432</v>
@@ -15416,13 +15416,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1266.885398243852</v>
+        <v>1266.919916317122</v>
       </c>
       <c r="D121" t="n">
-        <v>1261.995256768333</v>
+        <v>1262.029848230927</v>
       </c>
       <c r="E121" t="n">
-        <v>1271.77553971937</v>
+        <v>1271.809984403317</v>
       </c>
       <c r="F121" t="n">
         <v>27124</v>
@@ -15567,13 +15567,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1266.42232537567</v>
+        <v>1266.498584505844</v>
       </c>
       <c r="D122" t="n">
-        <v>1262.600718238703</v>
+        <v>1262.677163808939</v>
       </c>
       <c r="E122" t="n">
-        <v>1270.243932512636</v>
+        <v>1270.320005202748</v>
       </c>
       <c r="F122" t="n">
         <v>54611</v>
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1264.531528506338</v>
+        <v>1264.582616138624</v>
       </c>
       <c r="D123" t="n">
-        <v>1258.250144842287</v>
+        <v>1258.301602258113</v>
       </c>
       <c r="E123" t="n">
-        <v>1270.812912170389</v>
+        <v>1270.863630019134</v>
       </c>
       <c r="F123" t="n">
         <v>15147</v>
@@ -15869,13 +15869,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1261.128232579575</v>
+        <v>1261.141657163176</v>
       </c>
       <c r="D124" t="n">
-        <v>1256.178386137521</v>
+        <v>1256.192110200353</v>
       </c>
       <c r="E124" t="n">
-        <v>1266.078079021628</v>
+        <v>1266.091204125998</v>
       </c>
       <c r="F124" t="n">
         <v>37325</v>
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1261.085567130852</v>
+        <v>1261.087122358738</v>
       </c>
       <c r="D125" t="n">
-        <v>1256.759167635849</v>
+        <v>1256.761199529766</v>
       </c>
       <c r="E125" t="n">
-        <v>1265.411966625855</v>
+        <v>1265.41304518771</v>
       </c>
       <c r="F125" t="n">
         <v>77554</v>
@@ -16091,13 +16091,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1256.015468608403</v>
+        <v>1256.042706540237</v>
       </c>
       <c r="D126" t="n">
-        <v>1251.419381603399</v>
+        <v>1251.446579916541</v>
       </c>
       <c r="E126" t="n">
-        <v>1260.611555613408</v>
+        <v>1260.638833163933</v>
       </c>
       <c r="F126" t="n">
         <v>24126</v>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1251.331582338345</v>
+        <v>1251.331426711185</v>
       </c>
       <c r="D127" t="n">
-        <v>1240.54919450456</v>
+        <v>1240.549232496322</v>
       </c>
       <c r="E127" t="n">
-        <v>1262.113970172129</v>
+        <v>1262.113620926048</v>
       </c>
       <c r="F127" t="n">
         <v>3334</v>
@@ -16393,13 +16393,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1249.684760410396</v>
+        <v>1249.699810021833</v>
       </c>
       <c r="D128" t="n">
-        <v>1243.081241131756</v>
+        <v>1243.096367169717</v>
       </c>
       <c r="E128" t="n">
-        <v>1256.288279689035</v>
+        <v>1256.30325287395</v>
       </c>
       <c r="F128" t="n">
         <v>10140</v>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1239.33967954261</v>
+        <v>1239.389853067182</v>
       </c>
       <c r="D129" t="n">
-        <v>1232.111381205241</v>
+        <v>1232.161705521466</v>
       </c>
       <c r="E129" t="n">
-        <v>1246.567977879979</v>
+        <v>1246.618000612898</v>
       </c>
       <c r="F129" t="n">
         <v>8858</v>
@@ -16611,13 +16611,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1237.287676879146</v>
+        <v>1237.324921940532</v>
       </c>
       <c r="D130" t="n">
-        <v>1228.193498132406</v>
+        <v>1228.23088326722</v>
       </c>
       <c r="E130" t="n">
-        <v>1246.381855625886</v>
+        <v>1246.418960613843</v>
       </c>
       <c r="F130" t="n">
         <v>4781</v>
@@ -16762,13 +16762,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1233.48929453694</v>
+        <v>1233.510392381876</v>
       </c>
       <c r="D131" t="n">
-        <v>1227.934175897894</v>
+        <v>1227.955632644129</v>
       </c>
       <c r="E131" t="n">
-        <v>1239.044413175985</v>
+        <v>1239.065152119623</v>
       </c>
       <c r="F131" t="n">
         <v>26195</v>
@@ -16913,13 +16913,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1232.702647926981</v>
+        <v>1232.721958557181</v>
       </c>
       <c r="D132" t="n">
-        <v>1227.425759230322</v>
+        <v>1227.44546515059</v>
       </c>
       <c r="E132" t="n">
-        <v>1237.97953662364</v>
+        <v>1237.998451963772</v>
       </c>
       <c r="F132" t="n">
         <v>39302</v>
@@ -17064,13 +17064,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1228.736278393209</v>
+        <v>1228.745268973311</v>
       </c>
       <c r="D133" t="n">
-        <v>1224.176526455188</v>
+        <v>1224.185926870647</v>
       </c>
       <c r="E133" t="n">
-        <v>1233.296030331228</v>
+        <v>1233.304611075976</v>
       </c>
       <c r="F133" t="n">
         <v>51416</v>
@@ -17215,13 +17215,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1226.082271258559</v>
+        <v>1226.085085463366</v>
       </c>
       <c r="D134" t="n">
-        <v>1221.297222726946</v>
+        <v>1221.300457080425</v>
       </c>
       <c r="E134" t="n">
-        <v>1230.867319790172</v>
+        <v>1230.869713846306</v>
       </c>
       <c r="F134" t="n">
         <v>54036</v>
@@ -17286,13 +17286,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1222.987171849005</v>
+        <v>1223.016032521025</v>
       </c>
       <c r="D135" t="n">
-        <v>1219.246265130851</v>
+        <v>1219.275630569622</v>
       </c>
       <c r="E135" t="n">
-        <v>1226.728078567158</v>
+        <v>1226.756434472428</v>
       </c>
       <c r="F135" t="n">
         <v>104642</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1222.815214864392</v>
+        <v>1222.847410861118</v>
       </c>
       <c r="D136" t="n">
-        <v>1215.840663342441</v>
+        <v>1215.872915614938</v>
       </c>
       <c r="E136" t="n">
-        <v>1229.789766386343</v>
+        <v>1229.821906107299</v>
       </c>
       <c r="F136" t="n">
         <v>9818</v>
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1220.413522499334</v>
+        <v>1220.425415607335</v>
       </c>
       <c r="D137" t="n">
-        <v>1209.734897000563</v>
+        <v>1209.747011179803</v>
       </c>
       <c r="E137" t="n">
-        <v>1231.092147998105</v>
+        <v>1231.103820034868</v>
       </c>
       <c r="F137" t="n">
         <v>2896</v>
@@ -17739,13 +17739,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1212.497003168105</v>
+        <v>1212.496651829817</v>
       </c>
       <c r="D138" t="n">
-        <v>1207.455845948065</v>
+        <v>1207.455857770213</v>
       </c>
       <c r="E138" t="n">
-        <v>1217.538160388146</v>
+        <v>1217.537445889421</v>
       </c>
       <c r="F138" t="n">
         <v>24146</v>
@@ -17886,13 +17886,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1212.164805648458</v>
+        <v>1212.176054652496</v>
       </c>
       <c r="D139" t="n">
-        <v>1201.373415922065</v>
+        <v>1201.384891965178</v>
       </c>
       <c r="E139" t="n">
-        <v>1222.95619537485</v>
+        <v>1222.967217339813</v>
       </c>
       <c r="F139" t="n">
         <v>4652</v>
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1211.260457461596</v>
+        <v>1211.288639933687</v>
       </c>
       <c r="D140" t="n">
-        <v>1207.107666532951</v>
+        <v>1207.135949337306</v>
       </c>
       <c r="E140" t="n">
-        <v>1215.413248390241</v>
+        <v>1215.441330530068</v>
       </c>
       <c r="F140" t="n">
         <v>49605</v>
@@ -18184,13 +18184,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1207.834352510464</v>
+        <v>1207.841855750669</v>
       </c>
       <c r="D141" t="n">
-        <v>1196.73149997194</v>
+        <v>1196.739036401716</v>
       </c>
       <c r="E141" t="n">
-        <v>1218.937205048988</v>
+        <v>1218.944675099623</v>
       </c>
       <c r="F141" t="n">
         <v>3090</v>
@@ -18335,13 +18335,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1203.168015611272</v>
+        <v>1203.177362017553</v>
       </c>
       <c r="D142" t="n">
-        <v>1197.048048073493</v>
+        <v>1197.057733014628</v>
       </c>
       <c r="E142" t="n">
-        <v>1209.287983149052</v>
+        <v>1209.296991020479</v>
       </c>
       <c r="F142" t="n">
         <v>21741</v>
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1199.793684066829</v>
+        <v>1199.868088299751</v>
       </c>
       <c r="D143" t="n">
-        <v>1195.69788942793</v>
+        <v>1195.772405747255</v>
       </c>
       <c r="E143" t="n">
-        <v>1203.889478705729</v>
+        <v>1203.963770852246</v>
       </c>
       <c r="F143" t="n">
         <v>46616</v>
@@ -18637,13 +18637,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1197.194785507751</v>
+        <v>1197.198154856224</v>
       </c>
       <c r="D144" t="n">
-        <v>1192.032243792877</v>
+        <v>1192.035901809736</v>
       </c>
       <c r="E144" t="n">
-        <v>1202.357327222626</v>
+        <v>1202.360407902712</v>
       </c>
       <c r="F144" t="n">
         <v>25055</v>
@@ -18788,13 +18788,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1196.349905867249</v>
+        <v>1196.354653920848</v>
       </c>
       <c r="D145" t="n">
-        <v>1192.078511705842</v>
+        <v>1192.083832418218</v>
       </c>
       <c r="E145" t="n">
-        <v>1200.621300028656</v>
+        <v>1200.625475423477</v>
       </c>
       <c r="F145" t="n">
         <v>73503</v>
@@ -18939,13 +18939,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1194.534584563296</v>
+        <v>1194.55418818871</v>
       </c>
       <c r="D146" t="n">
-        <v>1188.419398476449</v>
+        <v>1188.439334826822</v>
       </c>
       <c r="E146" t="n">
-        <v>1200.649770650143</v>
+        <v>1200.669041550597</v>
       </c>
       <c r="F146" t="n">
         <v>32191</v>
@@ -19006,13 +19006,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1190.530394217006</v>
+        <v>1190.535869049315</v>
       </c>
       <c r="D147" t="n">
-        <v>1183.345309146106</v>
+        <v>1183.350901822729</v>
       </c>
       <c r="E147" t="n">
-        <v>1197.715479287907</v>
+        <v>1197.7208362759</v>
       </c>
       <c r="F147" t="n">
         <v>9901</v>
@@ -19153,13 +19153,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1190.320570839925</v>
+        <v>1190.333275581578</v>
       </c>
       <c r="D148" t="n">
-        <v>1183.201036294781</v>
+        <v>1183.214087317131</v>
       </c>
       <c r="E148" t="n">
-        <v>1197.44010538507</v>
+        <v>1197.452463846026</v>
       </c>
       <c r="F148" t="n">
         <v>17839</v>
@@ -19304,13 +19304,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1183.949803225292</v>
+        <v>1183.955379019415</v>
       </c>
       <c r="D149" t="n">
-        <v>1174.511037748907</v>
+        <v>1174.516965739729</v>
       </c>
       <c r="E149" t="n">
-        <v>1193.388568701676</v>
+        <v>1193.393792299102</v>
       </c>
       <c r="F149" t="n">
         <v>8214</v>
@@ -19455,13 +19455,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1183.901775052109</v>
+        <v>1183.922841216324</v>
       </c>
       <c r="D150" t="n">
-        <v>1172.414981765907</v>
+        <v>1172.436530100962</v>
       </c>
       <c r="E150" t="n">
-        <v>1195.388568338312</v>
+        <v>1195.409152331687</v>
       </c>
       <c r="F150" t="n">
         <v>4932</v>
@@ -19606,13 +19606,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1183.120671144037</v>
+        <v>1183.133086119905</v>
       </c>
       <c r="D151" t="n">
-        <v>1176.29262675692</v>
+        <v>1176.305317926068</v>
       </c>
       <c r="E151" t="n">
-        <v>1189.948715531155</v>
+        <v>1189.960854313741</v>
       </c>
       <c r="F151" t="n">
         <v>15483</v>
@@ -19753,13 +19753,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1182.036737447477</v>
+        <v>1182.07559665081</v>
       </c>
       <c r="D152" t="n">
-        <v>1173.354931802284</v>
+        <v>1173.393920442858</v>
       </c>
       <c r="E152" t="n">
-        <v>1190.718543092671</v>
+        <v>1190.757272858761</v>
       </c>
       <c r="F152" t="n">
         <v>6638</v>
@@ -19904,13 +19904,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1181.92993259954</v>
+        <v>1181.959636069448</v>
       </c>
       <c r="D153" t="n">
-        <v>1172.268573910813</v>
+        <v>1172.29864212502</v>
       </c>
       <c r="E153" t="n">
-        <v>1191.591291288267</v>
+        <v>1191.620630013876</v>
       </c>
       <c r="F153" t="n">
         <v>7968</v>
@@ -19971,13 +19971,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1181.778462960732</v>
+        <v>1181.795884687911</v>
       </c>
       <c r="D154" t="n">
-        <v>1173.78382400874</v>
+        <v>1173.801525069234</v>
       </c>
       <c r="E154" t="n">
-        <v>1189.773101912725</v>
+        <v>1189.790244306587</v>
       </c>
       <c r="F154" t="n">
         <v>12637</v>
@@ -20038,13 +20038,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1181.549076645626</v>
+        <v>1181.646815702767</v>
       </c>
       <c r="D155" t="n">
-        <v>1175.476470349832</v>
+        <v>1175.57457863504</v>
       </c>
       <c r="E155" t="n">
-        <v>1187.621682941419</v>
+        <v>1187.719052770494</v>
       </c>
       <c r="F155" t="n">
         <v>23893</v>
@@ -20189,13 +20189,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1179.036749352651</v>
+        <v>1179.056584201846</v>
       </c>
       <c r="D156" t="n">
-        <v>1173.123100396501</v>
+        <v>1173.143301083737</v>
       </c>
       <c r="E156" t="n">
-        <v>1184.9503983088</v>
+        <v>1184.969867319956</v>
       </c>
       <c r="F156" t="n">
         <v>32832</v>
@@ -20256,13 +20256,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1178.329147545271</v>
+        <v>1178.334187438628</v>
       </c>
       <c r="D157" t="n">
-        <v>1167.136850824092</v>
+        <v>1167.142111474815</v>
       </c>
       <c r="E157" t="n">
-        <v>1189.52144426645</v>
+        <v>1189.526263402441</v>
       </c>
       <c r="F157" t="n">
         <v>3188</v>
@@ -20407,13 +20407,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1176.991416093803</v>
+        <v>1176.984884563527</v>
       </c>
       <c r="D158" t="n">
-        <v>1167.183753260422</v>
+        <v>1167.177546655203</v>
       </c>
       <c r="E158" t="n">
-        <v>1186.799078927183</v>
+        <v>1186.792222471852</v>
       </c>
       <c r="F158" t="n">
         <v>6535</v>
@@ -20554,13 +20554,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1174.879614283936</v>
+        <v>1174.906126841999</v>
       </c>
       <c r="D159" t="n">
-        <v>1164.472962161258</v>
+        <v>1164.499792210026</v>
       </c>
       <c r="E159" t="n">
-        <v>1185.286266406613</v>
+        <v>1185.312461473971</v>
       </c>
       <c r="F159" t="n">
         <v>5006</v>
@@ -20701,13 +20701,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1172.101175643518</v>
+        <v>1172.10842230956</v>
       </c>
       <c r="D160" t="n">
-        <v>1165.898660979072</v>
+        <v>1165.90638871703</v>
       </c>
       <c r="E160" t="n">
-        <v>1178.303690307964</v>
+        <v>1178.310455902091</v>
       </c>
       <c r="F160" t="n">
         <v>22479</v>
@@ -20848,13 +20848,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1170.599663900031</v>
+        <v>1170.575739599203</v>
       </c>
       <c r="D161" t="n">
-        <v>1163.19337142538</v>
+        <v>1163.169809529787</v>
       </c>
       <c r="E161" t="n">
-        <v>1178.005956374682</v>
+        <v>1177.981669668619</v>
       </c>
       <c r="F161" t="n">
         <v>16056</v>
@@ -20995,13 +20995,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1170.359674066028</v>
+        <v>1170.367632513862</v>
       </c>
       <c r="D162" t="n">
-        <v>1164.441646177115</v>
+        <v>1164.4499048995</v>
       </c>
       <c r="E162" t="n">
-        <v>1176.277701954941</v>
+        <v>1176.285360128225</v>
       </c>
       <c r="F162" t="n">
         <v>17766</v>
@@ -21146,13 +21146,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1170.011448114722</v>
+        <v>1170.009106781181</v>
       </c>
       <c r="D163" t="n">
-        <v>1164.511893987419</v>
+        <v>1164.510009308467</v>
       </c>
       <c r="E163" t="n">
-        <v>1175.511002242025</v>
+        <v>1175.508204253894</v>
       </c>
       <c r="F163" t="n">
         <v>38492</v>
@@ -21297,13 +21297,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1166.705990283283</v>
+        <v>1166.70482420643</v>
       </c>
       <c r="D164" t="n">
-        <v>1158.642270747939</v>
+        <v>1158.641327144767</v>
       </c>
       <c r="E164" t="n">
-        <v>1174.769709818627</v>
+        <v>1174.768321268092</v>
       </c>
       <c r="F164" t="n">
         <v>10224</v>
@@ -21444,13 +21444,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1166.185691722796</v>
+        <v>1166.207088601587</v>
       </c>
       <c r="D165" t="n">
-        <v>1158.480408118013</v>
+        <v>1158.501688826443</v>
       </c>
       <c r="E165" t="n">
-        <v>1173.890975327579</v>
+        <v>1173.91248837673</v>
       </c>
       <c r="F165" t="n">
         <v>7936</v>
@@ -21595,13 +21595,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1163.813791953077</v>
+        <v>1163.809510007954</v>
       </c>
       <c r="D166" t="n">
-        <v>1151.900027158201</v>
+        <v>1151.896085319054</v>
       </c>
       <c r="E166" t="n">
-        <v>1175.727556747953</v>
+        <v>1175.722934696854</v>
       </c>
       <c r="F166" t="n">
         <v>3777</v>
@@ -21742,13 +21742,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1155.714655846064</v>
+        <v>1155.738389554177</v>
       </c>
       <c r="D167" t="n">
-        <v>1147.326160774616</v>
+        <v>1147.349975738678</v>
       </c>
       <c r="E167" t="n">
-        <v>1164.103150917511</v>
+        <v>1164.126803369676</v>
       </c>
       <c r="F167" t="n">
         <v>6837</v>
@@ -21893,13 +21893,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1154.642408726014</v>
+        <v>1154.585515507817</v>
       </c>
       <c r="D168" t="n">
-        <v>1143.15137356015</v>
+        <v>1143.094565500618</v>
       </c>
       <c r="E168" t="n">
-        <v>1166.133443891879</v>
+        <v>1166.076465515017</v>
       </c>
       <c r="F168" t="n">
         <v>3231</v>
@@ -22044,13 +22044,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1154.009573289722</v>
+        <v>1153.998916311228</v>
       </c>
       <c r="D169" t="n">
-        <v>1141.413002354806</v>
+        <v>1141.402662308222</v>
       </c>
       <c r="E169" t="n">
-        <v>1166.606144224638</v>
+        <v>1166.595170314234</v>
       </c>
       <c r="F169" t="n">
         <v>3585</v>
@@ -22195,13 +22195,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1151.55825886573</v>
+        <v>1151.565359975859</v>
       </c>
       <c r="D170" t="n">
-        <v>1138.389283663415</v>
+        <v>1138.396900090565</v>
       </c>
       <c r="E170" t="n">
-        <v>1164.727234068044</v>
+        <v>1164.733819861154</v>
       </c>
       <c r="F170" t="n">
         <v>4155</v>
@@ -22342,13 +22342,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1151.388270637974</v>
+        <v>1151.401024379886</v>
       </c>
       <c r="D171" t="n">
-        <v>1136.059026092404</v>
+        <v>1136.072655483245</v>
       </c>
       <c r="E171" t="n">
-        <v>1166.717515183545</v>
+        <v>1166.729393276527</v>
       </c>
       <c r="F171" t="n">
         <v>1679</v>
@@ -22489,13 +22489,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1149.70587488312</v>
+        <v>1149.730565452775</v>
       </c>
       <c r="D172" t="n">
-        <v>1137.456884404567</v>
+        <v>1137.482205249682</v>
       </c>
       <c r="E172" t="n">
-        <v>1161.954865361675</v>
+        <v>1161.978925655868</v>
       </c>
       <c r="F172" t="n">
         <v>2572</v>
@@ -22636,13 +22636,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1148.677398481474</v>
+        <v>1148.67540497726</v>
       </c>
       <c r="D173" t="n">
-        <v>1142.025550954698</v>
+        <v>1142.023853903866</v>
       </c>
       <c r="E173" t="n">
-        <v>1155.329246008249</v>
+        <v>1155.326956050654</v>
       </c>
       <c r="F173" t="n">
         <v>19402</v>
@@ -22787,13 +22787,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1148.619978154574</v>
+        <v>1148.633760059952</v>
       </c>
       <c r="D174" t="n">
-        <v>1139.392610225476</v>
+        <v>1139.407099075623</v>
       </c>
       <c r="E174" t="n">
-        <v>1157.847346083671</v>
+        <v>1157.860421044282</v>
       </c>
       <c r="F174" t="n">
         <v>7044</v>
@@ -22938,13 +22938,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1146.89175491363</v>
+        <v>1146.929993756793</v>
       </c>
       <c r="D175" t="n">
-        <v>1129.832500964808</v>
+        <v>1129.87150090186</v>
       </c>
       <c r="E175" t="n">
-        <v>1163.951008862453</v>
+        <v>1163.988486611726</v>
       </c>
       <c r="F175" t="n">
         <v>1295</v>
@@ -23085,13 +23085,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1143.149069716942</v>
+        <v>1143.157833765305</v>
       </c>
       <c r="D176" t="n">
-        <v>1133.262266291231</v>
+        <v>1133.271165804363</v>
       </c>
       <c r="E176" t="n">
-        <v>1153.035873142652</v>
+        <v>1153.044501726246</v>
       </c>
       <c r="F176" t="n">
         <v>4737</v>
@@ -23236,13 +23236,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1142.388440543208</v>
+        <v>1142.398327375032</v>
       </c>
       <c r="D177" t="n">
-        <v>1135.947670349859</v>
+        <v>1135.957720453735</v>
       </c>
       <c r="E177" t="n">
-        <v>1148.829210736558</v>
+        <v>1148.838934296329</v>
       </c>
       <c r="F177" t="n">
         <v>12297</v>
@@ -23387,13 +23387,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1140.781016133354</v>
+        <v>1140.781244081818</v>
       </c>
       <c r="D178" t="n">
-        <v>1134.0565978972</v>
+        <v>1134.057148925446</v>
       </c>
       <c r="E178" t="n">
-        <v>1147.505434369507</v>
+        <v>1147.505339238191</v>
       </c>
       <c r="F178" t="n">
         <v>19174</v>
@@ -23538,13 +23538,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1140.484936880385</v>
+        <v>1140.509702386278</v>
       </c>
       <c r="D179" t="n">
-        <v>1133.784866956578</v>
+        <v>1133.810101413622</v>
       </c>
       <c r="E179" t="n">
-        <v>1147.185006804193</v>
+        <v>1147.209303358933</v>
       </c>
       <c r="F179" t="n">
         <v>19367</v>
@@ -23685,13 +23685,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1138.203045656328</v>
+        <v>1138.233220525655</v>
       </c>
       <c r="D180" t="n">
-        <v>1127.259742310016</v>
+        <v>1127.290262987027</v>
       </c>
       <c r="E180" t="n">
-        <v>1149.146349002639</v>
+        <v>1149.176178064283</v>
       </c>
       <c r="F180" t="n">
         <v>4964</v>
@@ -23836,13 +23836,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1136.794775525664</v>
+        <v>1136.873913667696</v>
       </c>
       <c r="D181" t="n">
-        <v>1127.306533885397</v>
+        <v>1127.386142102091</v>
       </c>
       <c r="E181" t="n">
-        <v>1146.283017165932</v>
+        <v>1146.361685233301</v>
       </c>
       <c r="F181" t="n">
         <v>8925</v>
@@ -23987,13 +23987,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1135.98609761987</v>
+        <v>1135.997574642708</v>
       </c>
       <c r="D182" t="n">
-        <v>1127.095925848011</v>
+        <v>1127.107721627798</v>
       </c>
       <c r="E182" t="n">
-        <v>1144.876269391729</v>
+        <v>1144.887427657618</v>
       </c>
       <c r="F182" t="n">
         <v>7366</v>
@@ -24138,13 +24138,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1130.071050931823</v>
+        <v>1130.06851929638</v>
       </c>
       <c r="D183" t="n">
-        <v>1121.240796185868</v>
+        <v>1121.238609098477</v>
       </c>
       <c r="E183" t="n">
-        <v>1138.901305677778</v>
+        <v>1138.898429494284</v>
       </c>
       <c r="F183" t="n">
         <v>11118</v>
@@ -24285,13 +24285,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1128.838898512054</v>
+        <v>1128.862256416047</v>
       </c>
       <c r="D184" t="n">
-        <v>1121.414661741994</v>
+        <v>1121.43814520883</v>
       </c>
       <c r="E184" t="n">
-        <v>1136.263135282114</v>
+        <v>1136.286367623263</v>
       </c>
       <c r="F184" t="n">
         <v>20685</v>
@@ -24436,13 +24436,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1127.49624541177</v>
+        <v>1127.492544990878</v>
       </c>
       <c r="D185" t="n">
-        <v>1121.097327949778</v>
+        <v>1121.093832796141</v>
       </c>
       <c r="E185" t="n">
-        <v>1133.895162873763</v>
+        <v>1133.891257185615</v>
       </c>
       <c r="F185" t="n">
         <v>20118</v>
@@ -24587,13 +24587,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1126.566926147063</v>
+        <v>1126.58057439454</v>
       </c>
       <c r="D186" t="n">
-        <v>1114.468630274141</v>
+        <v>1114.482995979473</v>
       </c>
       <c r="E186" t="n">
-        <v>1138.665222019984</v>
+        <v>1138.678152809608</v>
       </c>
       <c r="F186" t="n">
         <v>2921</v>
@@ -24734,13 +24734,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1126.093289687969</v>
+        <v>1126.099433364828</v>
       </c>
       <c r="D187" t="n">
-        <v>1110.490817135835</v>
+        <v>1110.497909982294</v>
       </c>
       <c r="E187" t="n">
-        <v>1141.695762240102</v>
+        <v>1141.700956747361</v>
       </c>
       <c r="F187" t="n">
         <v>1785</v>
@@ -24881,13 +24881,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1120.549217988764</v>
+        <v>1120.573373557982</v>
       </c>
       <c r="D188" t="n">
-        <v>1109.57155658657</v>
+        <v>1109.596064736505</v>
       </c>
       <c r="E188" t="n">
-        <v>1131.526879390959</v>
+        <v>1131.550682379459</v>
       </c>
       <c r="F188" t="n">
         <v>5182</v>
@@ -25028,13 +25028,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1118.470915105906</v>
+        <v>1118.489040823145</v>
       </c>
       <c r="D189" t="n">
-        <v>1100.331334370407</v>
+        <v>1100.350144155151</v>
       </c>
       <c r="E189" t="n">
-        <v>1136.610495841404</v>
+        <v>1136.627937491138</v>
       </c>
       <c r="F189" t="n">
         <v>1143</v>
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1115.547332184625</v>
+        <v>1115.646410637927</v>
       </c>
       <c r="D190" t="n">
-        <v>1107.81787317542</v>
+        <v>1107.917267258977</v>
       </c>
       <c r="E190" t="n">
-        <v>1123.276791193831</v>
+        <v>1123.375554016878</v>
       </c>
       <c r="F190" t="n">
         <v>10854</v>
@@ -25330,13 +25330,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1114.235315595419</v>
+        <v>1114.261107243349</v>
       </c>
       <c r="D191" t="n">
-        <v>1105.095702272118</v>
+        <v>1105.122235534678</v>
       </c>
       <c r="E191" t="n">
-        <v>1123.374928918719</v>
+        <v>1123.399978952019</v>
       </c>
       <c r="F191" t="n">
         <v>6923</v>
@@ -25477,13 +25477,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1113.84007806664</v>
+        <v>1113.859183734347</v>
       </c>
       <c r="D192" t="n">
-        <v>1099.466229116668</v>
+        <v>1099.48559621302</v>
       </c>
       <c r="E192" t="n">
-        <v>1128.213927016613</v>
+        <v>1128.232771255675</v>
       </c>
       <c r="F192" t="n">
         <v>2199</v>
@@ -25624,13 +25624,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1110.547489565442</v>
+        <v>1110.561119378102</v>
       </c>
       <c r="D193" t="n">
-        <v>1102.663869451807</v>
+        <v>1102.67734663956</v>
       </c>
       <c r="E193" t="n">
-        <v>1118.431109679078</v>
+        <v>1118.444892116644</v>
       </c>
       <c r="F193" t="n">
         <v>8045</v>
@@ -25775,13 +25775,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1109.242231354672</v>
+        <v>1109.270523548781</v>
       </c>
       <c r="D194" t="n">
-        <v>1099.960266529778</v>
+        <v>1099.988865926771</v>
       </c>
       <c r="E194" t="n">
-        <v>1118.524196179565</v>
+        <v>1118.552181170791</v>
       </c>
       <c r="F194" t="n">
         <v>8977</v>
@@ -25926,13 +25926,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1107.325314447213</v>
+        <v>1107.317556606873</v>
       </c>
       <c r="D195" t="n">
-        <v>1100.272885750716</v>
+        <v>1100.26545434193</v>
       </c>
       <c r="E195" t="n">
-        <v>1114.377743143709</v>
+        <v>1114.369658871817</v>
       </c>
       <c r="F195" t="n">
         <v>14148</v>
@@ -26077,13 +26077,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1092.573218909389</v>
+        <v>1092.657893370618</v>
       </c>
       <c r="D196" t="n">
-        <v>1081.088481713758</v>
+        <v>1081.173620286275</v>
       </c>
       <c r="E196" t="n">
-        <v>1104.05795610502</v>
+        <v>1104.14216645496</v>
       </c>
       <c r="F196" t="n">
         <v>4780</v>
@@ -26228,13 +26228,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1089.903878887744</v>
+        <v>1089.938385523069</v>
       </c>
       <c r="D197" t="n">
-        <v>1080.568972241529</v>
+        <v>1080.603738290152</v>
       </c>
       <c r="E197" t="n">
-        <v>1099.238785533958</v>
+        <v>1099.273032755986</v>
       </c>
       <c r="F197" t="n">
         <v>7597</v>
@@ -26379,13 +26379,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1073.201287581766</v>
+        <v>1073.176479272376</v>
       </c>
       <c r="D198" t="n">
-        <v>1062.042483553581</v>
+        <v>1062.018120192683</v>
       </c>
       <c r="E198" t="n">
-        <v>1084.360091609951</v>
+        <v>1084.334838352069</v>
       </c>
       <c r="F198" t="n">
         <v>6328</v>
@@ -26530,13 +26530,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1069.91987974033</v>
+        <v>1069.9405400771</v>
       </c>
       <c r="D199" t="n">
-        <v>1060.042451746094</v>
+        <v>1060.064091998907</v>
       </c>
       <c r="E199" t="n">
-        <v>1079.797307734566</v>
+        <v>1079.816988155294</v>
       </c>
       <c r="F199" t="n">
         <v>6965</v>
@@ -26677,13 +26677,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1068.355432475025</v>
+        <v>1068.446413438976</v>
       </c>
       <c r="D200" t="n">
-        <v>1056.905657658176</v>
+        <v>1056.997587407815</v>
       </c>
       <c r="E200" t="n">
-        <v>1079.805207291873</v>
+        <v>1079.895239470136</v>
       </c>
       <c r="F200" t="n">
         <v>5745</v>
@@ -26824,13 +26824,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1066.23425767769</v>
+        <v>1066.292596780439</v>
       </c>
       <c r="D201" t="n">
-        <v>1051.03034013863</v>
+        <v>1051.089540905444</v>
       </c>
       <c r="E201" t="n">
-        <v>1081.43817521675</v>
+        <v>1081.495652655436</v>
       </c>
       <c r="F201" t="n">
         <v>1743</v>
@@ -26971,13 +26971,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1062.022522675117</v>
+        <v>1062.077272426441</v>
       </c>
       <c r="D202" t="n">
-        <v>1050.058132514864</v>
+        <v>1050.113628028478</v>
       </c>
       <c r="E202" t="n">
-        <v>1073.98691283537</v>
+        <v>1074.040916824404</v>
       </c>
       <c r="F202" t="n">
         <v>3924</v>
@@ -27118,13 +27118,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1055.495437515089</v>
+        <v>1055.518414306162</v>
       </c>
       <c r="D203" t="n">
-        <v>1043.83686773732</v>
+        <v>1043.860239650384</v>
       </c>
       <c r="E203" t="n">
-        <v>1067.154007292859</v>
+        <v>1067.176588961939</v>
       </c>
       <c r="F203" t="n">
         <v>4658</v>
@@ -27265,13 +27265,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1041.14654619993</v>
+        <v>1041.182859963473</v>
       </c>
       <c r="D204" t="n">
-        <v>1029.767212253605</v>
+        <v>1029.804441598934</v>
       </c>
       <c r="E204" t="n">
-        <v>1052.525880146256</v>
+        <v>1052.561278328012</v>
       </c>
       <c r="F204" t="n">
         <v>4845</v>
@@ -27412,13 +27412,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1023.682610909772</v>
+        <v>1023.707907689618</v>
       </c>
       <c r="D205" t="n">
-        <v>1010.10062775913</v>
+        <v>1010.126561905521</v>
       </c>
       <c r="E205" t="n">
-        <v>1037.264594060413</v>
+        <v>1037.289253473716</v>
       </c>
       <c r="F205" t="n">
         <v>2658</v>
@@ -27559,13 +27559,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1022.134024688156</v>
+        <v>1022.185277498823</v>
       </c>
       <c r="D206" t="n">
-        <v>1011.275613711912</v>
+        <v>1011.327780247338</v>
       </c>
       <c r="E206" t="n">
-        <v>1032.992435664401</v>
+        <v>1033.042774750309</v>
       </c>
       <c r="F206" t="n">
         <v>6310</v>
@@ -27706,13 +27706,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>994.8901499967722</v>
+        <v>994.9037527003888</v>
       </c>
       <c r="D207" t="n">
-        <v>982.336413622405</v>
+        <v>982.3508002183239</v>
       </c>
       <c r="E207" t="n">
-        <v>1007.443886371139</v>
+        <v>1007.456705182454</v>
       </c>
       <c r="F207" t="n">
         <v>4914</v>
@@ -27853,13 +27853,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>991.3408423493614</v>
+        <v>991.3818794825593</v>
       </c>
       <c r="D208" t="n">
-        <v>978.9818668260874</v>
+        <v>979.0238881632874</v>
       </c>
       <c r="E208" t="n">
-        <v>1003.699817872635</v>
+        <v>1003.739870801831</v>
       </c>
       <c r="F208" t="n">
         <v>4203</v>
@@ -28000,13 +28000,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>980.747498111305</v>
+        <v>980.8271424628772</v>
       </c>
       <c r="D209" t="n">
-        <v>967.2351976816037</v>
+        <v>967.3159476513279</v>
       </c>
       <c r="E209" t="n">
-        <v>994.2597985410064</v>
+        <v>994.3383372744265</v>
       </c>
       <c r="F209" t="n">
         <v>3412</v>
@@ -28147,13 +28147,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>973.3035339654052</v>
+        <v>973.3978731456259</v>
       </c>
       <c r="D210" t="n">
-        <v>957.5290289555505</v>
+        <v>957.6248675039978</v>
       </c>
       <c r="E210" t="n">
-        <v>989.0780389752599</v>
+        <v>989.1708787872537</v>
       </c>
       <c r="F210" t="n">
         <v>2391</v>
@@ -28298,13 +28298,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>952.1606549650462</v>
+        <v>952.1845790598031</v>
       </c>
       <c r="D211" t="n">
-        <v>939.4498522861545</v>
+        <v>939.47513762324</v>
       </c>
       <c r="E211" t="n">
-        <v>964.8714576439377</v>
+        <v>964.8940204963662</v>
       </c>
       <c r="F211" t="n">
         <v>3287</v>
@@ -29155,14 +29155,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -29178,14 +29178,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>744</v>
+        <v>1600</v>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29483,22 +29483,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>glm-4.6</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>550</v>
+      </c>
+      <c r="C22" t="n">
+        <v>55</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>glm-4.6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -29513,7 +29521,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp-thinking</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -29528,23 +29536,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3-ultra-550b-a55b-nvfp4</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>550</v>
-      </c>
-      <c r="C25" t="n">
-        <v>55</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.2-exp-thinking</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29642,7 +29642,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -29680,15 +29680,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>122</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -29710,30 +29718,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>122</v>
-      </c>
-      <c r="C35" t="n">
-        <v>10</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-thinking</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -29771,38 +29771,38 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>235</v>
-      </c>
-      <c r="C38" t="n">
-        <v>22</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-terminus</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>qwen3-vl-235b-a22b-instruct</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>235</v>
+      </c>
+      <c r="C39" t="n">
+        <v>22</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -31022,38 +31022,38 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>granite-4.1-8b</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>8</v>
-      </c>
-      <c r="C99" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>deepseek-v2.5</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>deepseek-v2.5</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+          <t>granite-4.1-8b</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>8</v>
+      </c>
+      <c r="C100" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -31121,14 +31121,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C104" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -31144,14 +31144,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI213"/>
+  <dimension ref="A1:AI214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -28657,6 +28657,157 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>inkling-small</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1430.54086860102</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1419.392361439659</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1441.689375762382</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Thinky</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>266</v>
+      </c>
+      <c r="J214" t="n">
+        <v>12</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M214" t="n">
+        <v>532</v>
+      </c>
+      <c r="N214" t="n">
+        <v>665</v>
+      </c>
+      <c r="O214" t="n">
+        <v>266</v>
+      </c>
+      <c r="P214" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>133</v>
+      </c>
+      <c r="R214" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="S214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD214" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF214" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG214" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>MULTI-GPU</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>MULTI-GPU</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29269,7 +29420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -33798,6 +33949,29 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>inkling-small</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>266</v>
+      </c>
+      <c r="C214" t="n">
+        <v>12</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -452,7 +452,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1485.774405546388</v>
+        <v>1485.345656375652</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1475.752349008478</v>
+        <v>1475.317183428952</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1495.796462084298</v>
+        <v>1495.374129322353</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3559</v>
+        <v>3556</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1469.394363391151</v>
+        <v>1469.493298376792</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1463.746926107989</v>
+        <v>1464.080072686523</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1475.041800674313</v>
+        <v>1474.906524067061</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>19995</v>
+        <v>22252</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1468.665003961225</v>
+        <v>1468.787796757301</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1464.171692832164</v>
+        <v>1464.407888455876</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1473.158315090285</v>
+        <v>1473.167705058726</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>32555</v>
+        <v>34857</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1465.398789351203</v>
+        <v>1465.707904313422</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1461.018619992878</v>
+        <v>1461.42818549503</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1469.778958709528</v>
+        <v>1469.987623131815</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>43790</v>
+        <v>45910</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1460.676511918814</v>
+        <v>1460.668022792315</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1456.113463845526</v>
+        <v>1456.107550413663</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1465.239559992103</v>
+        <v>1465.228495170968</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>37350</v>
+        <v>37313</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1106,36 +1106,36 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>hy3</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1457.495483714622</v>
+        <v>1457.945178498991</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1447.151610114734</v>
+        <v>1453.741940225932</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1467.839357314512</v>
+        <v>1462.14841677205</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3267</v>
+        <v>49183</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Tencent</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>299</v>
+        <v>1600</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>598</v>
+        <v>3200</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>747.5</v>
+        <v>4000</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>299</v>
+        <v>1600</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>373.8</v>
+        <v>2000</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>149.5</v>
+        <v>800</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>186.9</v>
+        <v>1000</v>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
@@ -1235,9 +1235,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH7" s="2" t="inlineStr">
@@ -1257,24 +1257,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1457.08693259704</v>
+        <v>1456.713228047888</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1452.78705913954</v>
+        <v>1452.35250992689</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1461.386806054539</v>
+        <v>1461.073946168886</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46848</v>
+        <v>27634</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1299,22 +1299,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3200</v>
+        <v>1488</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4000</v>
+        <v>1860</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>2000</v>
+        <v>930</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>800</v>
+        <v>372</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>1000</v>
+        <v>465</v>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
@@ -1408,36 +1408,36 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>hy3</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1456.759425034792</v>
+        <v>1456.272825863887</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1452.395831183499</v>
+        <v>1446.063564853376</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1461.123018886085</v>
+        <v>1466.482086874399</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>27644</v>
+        <v>3353</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Tencent</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>744</v>
+        <v>299</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1488</v>
+        <v>598</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1860</v>
+        <v>747.5</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>744</v>
+        <v>299</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>930</v>
+        <v>373.8</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>372</v>
+        <v>149.5</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>465</v>
+        <v>186.9</v>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
@@ -1537,9 +1537,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH9" s="2" t="inlineStr">
@@ -1559,20 +1559,20 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-thinking</t>
+          <t>deepseek-v4-pro-high-preview</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1455.053614601571</v>
+        <v>1454.281052047281</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1450.682964038997</v>
+        <v>1450.018423466766</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1459.424265164145</v>
+        <v>1458.543680627796</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>44669</v>
+        <v>46859</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1451.139896406052</v>
+        <v>1450.923320417939</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1443.515880907156</v>
+        <v>1443.30225373473</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1458.763911904947</v>
+        <v>1458.544387101148</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5841</v>
+        <v>5844</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1785,16 +1785,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1450.009819260041</v>
+        <v>1450.211973033779</v>
       </c>
       <c r="D12" t="n">
-        <v>1446.492141771029</v>
+        <v>1446.743138368035</v>
       </c>
       <c r="E12" t="n">
-        <v>1453.527496749052</v>
+        <v>1453.680807699522</v>
       </c>
       <c r="F12" t="n">
-        <v>64226</v>
+        <v>66269</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1444.46252425278</v>
+        <v>1445.273158346901</v>
       </c>
       <c r="D13" t="n">
-        <v>1439.286153161065</v>
+        <v>1440.284347753107</v>
       </c>
       <c r="E13" t="n">
-        <v>1449.638895344495</v>
+        <v>1450.261968940694</v>
       </c>
       <c r="F13" t="n">
-        <v>29879</v>
+        <v>32086</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2083,148 +2083,68 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>inkling</t>
+          <t>glm-4.7</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1442.889277927068</v>
+        <v>1442.052301956197</v>
       </c>
       <c r="D14" t="n">
-        <v>1435.734219406181</v>
+        <v>1435.960229614961</v>
       </c>
       <c r="E14" t="n">
-        <v>1450.044336447954</v>
+        <v>1448.144374297434</v>
       </c>
       <c r="F14" t="n">
-        <v>7501</v>
+        <v>12090</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thinky</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>975</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>1950</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2437.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>975</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1218.8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>487.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>609.4</v>
-      </c>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG14" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2238,16 +2158,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1442.714636479838</v>
+        <v>1441.680796935525</v>
       </c>
       <c r="D15" t="n">
-        <v>1439.0495642941</v>
+        <v>1438.071228321843</v>
       </c>
       <c r="E15" t="n">
-        <v>1446.379708665575</v>
+        <v>1445.290365549207</v>
       </c>
       <c r="F15" t="n">
-        <v>59613</v>
+        <v>61760</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2385,68 +2305,148 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
+          <t>inkling</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1442.125675177104</v>
+        <v>1440.801681902524</v>
       </c>
       <c r="D16" t="n">
-        <v>1436.032681562074</v>
+        <v>1434.302480973471</v>
       </c>
       <c r="E16" t="n">
-        <v>1448.218668792133</v>
+        <v>1447.300882831577</v>
       </c>
       <c r="F16" t="n">
-        <v>12090</v>
+        <v>9873</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Thinky</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>975</v>
+      </c>
+      <c r="J16" t="n">
+        <v>41</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1950</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2437.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>975</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1218.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>609.4</v>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2460,16 +2460,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1438.323870701158</v>
+        <v>1438.496521967581</v>
       </c>
       <c r="D17" t="n">
-        <v>1430.655749624483</v>
+        <v>1430.832869107004</v>
       </c>
       <c r="E17" t="n">
-        <v>1445.991991777833</v>
+        <v>1446.160174828158</v>
       </c>
       <c r="F17" t="n">
-        <v>5754</v>
+        <v>5757</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2607,20 +2607,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-thinking</t>
+          <t>deepseek-v4-flash-high-preview</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1437.602843841923</v>
+        <v>1438.011486942368</v>
       </c>
       <c r="D18" t="n">
-        <v>1433.289337292259</v>
+        <v>1433.775584468884</v>
       </c>
       <c r="E18" t="n">
-        <v>1441.916350391587</v>
+        <v>1442.247389415852</v>
       </c>
       <c r="F18" t="n">
-        <v>46445</v>
+        <v>48387</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1435.81135419831</v>
+        <v>1435.636196971366</v>
       </c>
       <c r="D19" t="n">
-        <v>1431.554981163684</v>
+        <v>1431.46585408494</v>
       </c>
       <c r="E19" t="n">
-        <v>1440.067727232935</v>
+        <v>1439.806539857792</v>
       </c>
       <c r="F19" t="n">
-        <v>46729</v>
+        <v>48667</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1434.025756831055</v>
+        <v>1433.738517188744</v>
       </c>
       <c r="D20" t="n">
-        <v>1429.656489656634</v>
+        <v>1429.370068262624</v>
       </c>
       <c r="E20" t="n">
-        <v>1438.395024005476</v>
+        <v>1438.106966114865</v>
       </c>
       <c r="F20" t="n">
-        <v>44261</v>
+        <v>44251</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1431.382883750111</v>
+        <v>1431.593767459532</v>
       </c>
       <c r="D21" t="n">
-        <v>1424.789359939783</v>
+        <v>1425.001153762007</v>
       </c>
       <c r="E21" t="n">
-        <v>1437.976407560438</v>
+        <v>1438.186381157057</v>
       </c>
       <c r="F21" t="n">
-        <v>8146</v>
+        <v>8150</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1429.710225070652</v>
+        <v>1429.694039826392</v>
       </c>
       <c r="D22" t="n">
-        <v>1426.555059236989</v>
+        <v>1426.541450958268</v>
       </c>
       <c r="E22" t="n">
-        <v>1432.865390904315</v>
+        <v>1432.846628694515</v>
       </c>
       <c r="F22" t="n">
-        <v>61733</v>
+        <v>61710</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3206,16 +3206,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1427.385755556628</v>
+        <v>1427.291567352059</v>
       </c>
       <c r="D23" t="n">
-        <v>1420.770862915567</v>
+        <v>1420.680818932369</v>
       </c>
       <c r="E23" t="n">
-        <v>1434.00064819769</v>
+        <v>1433.902315771749</v>
       </c>
       <c r="F23" t="n">
-        <v>10917</v>
+        <v>10907</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1426.043991977681</v>
+        <v>1426.423051300756</v>
       </c>
       <c r="D24" t="n">
-        <v>1418.969599653787</v>
+        <v>1419.354476422673</v>
       </c>
       <c r="E24" t="n">
-        <v>1433.118384301576</v>
+        <v>1433.491626178839</v>
       </c>
       <c r="F24" t="n">
-        <v>10583</v>
+        <v>10588</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3424,24 +3424,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>glm-4.6</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1425.027860684494</v>
+        <v>1425.041882669078</v>
       </c>
       <c r="D25" t="n">
-        <v>1421.110808970963</v>
+        <v>1421.48712013347</v>
       </c>
       <c r="E25" t="n">
-        <v>1428.944912398026</v>
+        <v>1428.596645204686</v>
       </c>
       <c r="F25" t="n">
-        <v>35592</v>
+        <v>47008</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3495,24 +3495,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>glm-4.6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1424.950611115054</v>
+        <v>1425.024665685231</v>
       </c>
       <c r="D26" t="n">
-        <v>1421.393224028825</v>
+        <v>1421.107837436972</v>
       </c>
       <c r="E26" t="n">
-        <v>1428.507998201281</v>
+        <v>1428.941493933489</v>
       </c>
       <c r="F26" t="n">
-        <v>47019</v>
+        <v>35594</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3570,13 +3570,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1424.765768473964</v>
+        <v>1424.763750561533</v>
       </c>
       <c r="D27" t="n">
-        <v>1418.212455937631</v>
+        <v>1418.208905550342</v>
       </c>
       <c r="E27" t="n">
-        <v>1431.319081010297</v>
+        <v>1431.318595572723</v>
       </c>
       <c r="F27" t="n">
         <v>9061</v>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1423.002530222682</v>
+        <v>1422.949296038458</v>
       </c>
       <c r="D28" t="n">
-        <v>1420.410771701827</v>
+        <v>1420.359073409983</v>
       </c>
       <c r="E28" t="n">
-        <v>1425.594288743536</v>
+        <v>1425.539518666933</v>
       </c>
       <c r="F28" t="n">
-        <v>96779</v>
+        <v>96758</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3788,20 +3788,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1422.836325484809</v>
+        <v>1422.796958501995</v>
       </c>
       <c r="D29" t="n">
-        <v>1416.429969547507</v>
+        <v>1419.148252865555</v>
       </c>
       <c r="E29" t="n">
-        <v>1429.242681422111</v>
+        <v>1426.445664138435</v>
       </c>
       <c r="F29" t="n">
-        <v>11906</v>
+        <v>40836</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3859,20 +3859,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1422.716116271591</v>
+        <v>1422.627503880607</v>
       </c>
       <c r="D30" t="n">
-        <v>1419.066084706775</v>
+        <v>1416.223106665238</v>
       </c>
       <c r="E30" t="n">
-        <v>1426.366147836407</v>
+        <v>1429.031901095975</v>
       </c>
       <c r="F30" t="n">
-        <v>40851</v>
+        <v>11909</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3934,13 +3934,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1422.061262320235</v>
+        <v>1422.111566518278</v>
       </c>
       <c r="D31" t="n">
-        <v>1416.397034494981</v>
+        <v>1416.446962366653</v>
       </c>
       <c r="E31" t="n">
-        <v>1427.725490145488</v>
+        <v>1427.776170669903</v>
       </c>
       <c r="F31" t="n">
         <v>18424</v>
@@ -4005,16 +4005,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1418.05696564626</v>
+        <v>1418.122613758727</v>
       </c>
       <c r="D32" t="n">
-        <v>1411.559178508257</v>
+        <v>1411.624340539137</v>
       </c>
       <c r="E32" t="n">
-        <v>1424.554752784263</v>
+        <v>1424.620886978317</v>
       </c>
       <c r="F32" t="n">
-        <v>11765</v>
+        <v>11764</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1417.562010967345</v>
+        <v>1417.74080340313</v>
       </c>
       <c r="D33" t="n">
-        <v>1412.699357243929</v>
+        <v>1412.8776036958</v>
       </c>
       <c r="E33" t="n">
-        <v>1422.424664690761</v>
+        <v>1422.60400311046</v>
       </c>
       <c r="F33" t="n">
         <v>27592</v>
@@ -4303,20 +4303,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1417.505993808837</v>
+        <v>1417.383117900609</v>
       </c>
       <c r="D34" t="n">
-        <v>1407.522316003563</v>
+        <v>1411.372569988163</v>
       </c>
       <c r="E34" t="n">
-        <v>1427.48967161411</v>
+        <v>1423.393665813055</v>
       </c>
       <c r="F34" t="n">
-        <v>3457</v>
+        <v>14948</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4374,20 +4374,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1417.396237372655</v>
+        <v>1417.223291577337</v>
       </c>
       <c r="D35" t="n">
-        <v>1411.38625411758</v>
+        <v>1407.236255185038</v>
       </c>
       <c r="E35" t="n">
-        <v>1423.40622062773</v>
+        <v>1427.210327969637</v>
       </c>
       <c r="F35" t="n">
-        <v>14945</v>
+        <v>3454</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4445,148 +4445,68 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1416.913159013684</v>
+        <v>1416.973371263583</v>
       </c>
       <c r="D36" t="n">
-        <v>1412.512156519372</v>
+        <v>1410.359201722701</v>
       </c>
       <c r="E36" t="n">
-        <v>1421.314161507997</v>
+        <v>1423.587540804465</v>
       </c>
       <c r="F36" t="n">
-        <v>28247</v>
+        <v>11721</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>122</v>
-      </c>
-      <c r="J36" t="n">
-        <v>10</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>244</v>
-      </c>
-      <c r="N36" t="n">
-        <v>305</v>
-      </c>
-      <c r="O36" t="n">
-        <v>122</v>
-      </c>
-      <c r="P36" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>61</v>
-      </c>
-      <c r="R36" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="S36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE36" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4596,29 +4516,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1416.907139114964</v>
+        <v>1416.881453199402</v>
       </c>
       <c r="D37" t="n">
-        <v>1410.294452569983</v>
+        <v>1412.857400298902</v>
       </c>
       <c r="E37" t="n">
-        <v>1423.519825659945</v>
+        <v>1420.905506099902</v>
       </c>
       <c r="F37" t="n">
-        <v>11721</v>
+        <v>53523</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Modified MIT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4667,68 +4587,148 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1416.897483959754</v>
+        <v>1416.869922123495</v>
       </c>
       <c r="D38" t="n">
-        <v>1412.789430879787</v>
+        <v>1412.471115088277</v>
       </c>
       <c r="E38" t="n">
-        <v>1421.005537039722</v>
+        <v>1421.268729158713</v>
       </c>
       <c r="F38" t="n">
-        <v>51372</v>
+        <v>28222</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>122</v>
+      </c>
+      <c r="J38" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>244</v>
+      </c>
+      <c r="N38" t="n">
+        <v>305</v>
+      </c>
+      <c r="O38" t="n">
+        <v>122</v>
+      </c>
+      <c r="P38" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>61</v>
+      </c>
+      <c r="R38" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE38" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG38" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -4738,24 +4738,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1415.33515149389</v>
+        <v>1415.454857777998</v>
       </c>
       <c r="D39" t="n">
-        <v>1408.847425486403</v>
+        <v>1412.17381739107</v>
       </c>
       <c r="E39" t="n">
-        <v>1421.822877501378</v>
+        <v>1418.735898164926</v>
       </c>
       <c r="F39" t="n">
-        <v>11489</v>
+        <v>54560</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="J39" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4776,26 +4776,26 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>470</v>
+        <v>1350</v>
       </c>
       <c r="N39" t="n">
-        <v>587.5</v>
+        <v>1687.5</v>
       </c>
       <c r="O39" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="P39" t="n">
-        <v>293.8</v>
+        <v>843.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>117.5</v>
+        <v>337.5</v>
       </c>
       <c r="R39" t="n">
-        <v>146.9</v>
+        <v>421.9</v>
       </c>
       <c r="S39" s="5" t="inlineStr">
         <is>
@@ -4852,9 +4852,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD39" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE39" s="5" t="inlineStr">
@@ -4867,9 +4867,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG39" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG39" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH39" t="inlineStr">
@@ -4889,24 +4889,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1415.25587909478</v>
+        <v>1415.125446061452</v>
       </c>
       <c r="D40" t="n">
-        <v>1411.918005703606</v>
+        <v>1408.637969447286</v>
       </c>
       <c r="E40" t="n">
-        <v>1418.593752485953</v>
+        <v>1421.612922675617</v>
       </c>
       <c r="F40" t="n">
-        <v>52509</v>
+        <v>11490</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="J40" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -4927,26 +4927,26 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>1350</v>
+        <v>470</v>
       </c>
       <c r="N40" t="n">
-        <v>1687.5</v>
+        <v>587.5</v>
       </c>
       <c r="O40" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="P40" t="n">
-        <v>843.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>337.5</v>
+        <v>117.5</v>
       </c>
       <c r="R40" t="n">
-        <v>421.9</v>
+        <v>146.9</v>
       </c>
       <c r="S40" s="5" t="inlineStr">
         <is>
@@ -5003,9 +5003,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD40" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AD40" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AE40" s="5" t="inlineStr">
@@ -5018,9 +5018,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG40" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG40" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
@@ -5044,16 +5044,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1415.201823492472</v>
+        <v>1415.073824442247</v>
       </c>
       <c r="D41" t="n">
-        <v>1405.577312854087</v>
+        <v>1405.45069777358</v>
       </c>
       <c r="E41" t="n">
-        <v>1424.826334130857</v>
+        <v>1424.696951110915</v>
       </c>
       <c r="F41" t="n">
-        <v>3690</v>
+        <v>3691</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1412.334640377734</v>
+        <v>1412.190375312006</v>
       </c>
       <c r="D42" t="n">
-        <v>1404.760279258744</v>
+        <v>1404.606698859538</v>
       </c>
       <c r="E42" t="n">
-        <v>1419.909001496725</v>
+        <v>1419.774051764474</v>
       </c>
       <c r="F42" t="n">
-        <v>6575</v>
+        <v>6557</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5186,16 +5186,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1410.699878489258</v>
+        <v>1410.714080894664</v>
       </c>
       <c r="D43" t="n">
-        <v>1405.815656440187</v>
+        <v>1405.829374526509</v>
       </c>
       <c r="E43" t="n">
-        <v>1415.584100538327</v>
+        <v>1415.598787262819</v>
       </c>
       <c r="F43" t="n">
-        <v>24277</v>
+        <v>24280</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5337,16 +5337,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1408.091459370647</v>
+        <v>1408.039676412298</v>
       </c>
       <c r="D44" t="n">
-        <v>1403.661036729698</v>
+        <v>1403.609632313661</v>
       </c>
       <c r="E44" t="n">
-        <v>1412.521882011595</v>
+        <v>1412.469720510936</v>
       </c>
       <c r="F44" t="n">
-        <v>27096</v>
+        <v>27077</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5488,16 +5488,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1402.915985171642</v>
+        <v>1402.9095168766</v>
       </c>
       <c r="D45" t="n">
-        <v>1398.411180188265</v>
+        <v>1398.403024184455</v>
       </c>
       <c r="E45" t="n">
-        <v>1407.42079015502</v>
+        <v>1407.416009568744</v>
       </c>
       <c r="F45" t="n">
-        <v>38150</v>
+        <v>38139</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5639,16 +5639,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1401.171910641981</v>
+        <v>1401.207457057285</v>
       </c>
       <c r="D46" t="n">
-        <v>1396.395313749642</v>
+        <v>1396.432721028453</v>
       </c>
       <c r="E46" t="n">
-        <v>1405.948507534319</v>
+        <v>1405.982193086116</v>
       </c>
       <c r="F46" t="n">
-        <v>22846</v>
+        <v>22853</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1401.141774407172</v>
+        <v>1400.896411255554</v>
       </c>
       <c r="D47" t="n">
-        <v>1394.773082533033</v>
+        <v>1394.528686374463</v>
       </c>
       <c r="E47" t="n">
-        <v>1407.510466281311</v>
+        <v>1407.264136136644</v>
       </c>
       <c r="F47" t="n">
-        <v>11380</v>
+        <v>11386</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5941,16 +5941,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1398.961540542834</v>
+        <v>1398.919053741436</v>
       </c>
       <c r="D48" t="n">
-        <v>1392.426660944002</v>
+        <v>1392.383333255096</v>
       </c>
       <c r="E48" t="n">
-        <v>1405.496420141666</v>
+        <v>1405.454774227776</v>
       </c>
       <c r="F48" t="n">
-        <v>8983</v>
+        <v>8980</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6092,13 +6092,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1398.131133406981</v>
+        <v>1398.206123368104</v>
       </c>
       <c r="D49" t="n">
-        <v>1393.248637981304</v>
+        <v>1393.322227504733</v>
       </c>
       <c r="E49" t="n">
-        <v>1403.013628832658</v>
+        <v>1403.090019231475</v>
       </c>
       <c r="F49" t="n">
         <v>18524</v>
@@ -6239,36 +6239,36 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1395.556543930503</v>
+        <v>1395.531474789006</v>
       </c>
       <c r="D50" t="n">
-        <v>1388.761901363985</v>
+        <v>1391.653420675779</v>
       </c>
       <c r="E50" t="n">
-        <v>1402.351186497022</v>
+        <v>1399.409528902233</v>
       </c>
       <c r="F50" t="n">
-        <v>7931</v>
+        <v>45446</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>235</v>
+        <v>671</v>
       </c>
       <c r="J50" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6277,26 +6277,26 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>470</v>
+        <v>1342</v>
       </c>
       <c r="N50" t="n">
-        <v>587.5</v>
+        <v>1677.5</v>
       </c>
       <c r="O50" t="n">
-        <v>235</v>
+        <v>671</v>
       </c>
       <c r="P50" t="n">
-        <v>293.8</v>
+        <v>838.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>117.5</v>
+        <v>335.5</v>
       </c>
       <c r="R50" t="n">
-        <v>146.9</v>
+        <v>419.4</v>
       </c>
       <c r="S50" s="5" t="inlineStr">
         <is>
@@ -6353,9 +6353,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AD50" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AD50" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AE50" s="5" t="inlineStr">
@@ -6368,9 +6368,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG50" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG50" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -6390,36 +6390,36 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1395.488844960672</v>
+        <v>1395.494718344569</v>
       </c>
       <c r="D51" t="n">
-        <v>1391.611095024047</v>
+        <v>1391.147084041895</v>
       </c>
       <c r="E51" t="n">
-        <v>1399.366594897298</v>
+        <v>1399.842352647244</v>
       </c>
       <c r="F51" t="n">
-        <v>45444</v>
+        <v>28884</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="J51" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6428,40 +6428,40 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1342</v>
+        <v>70</v>
       </c>
       <c r="N51" t="n">
-        <v>1677.5</v>
+        <v>87.5</v>
       </c>
       <c r="O51" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="P51" t="n">
-        <v>838.8</v>
+        <v>43.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>335.5</v>
+        <v>17.5</v>
       </c>
       <c r="R51" t="n">
-        <v>419.4</v>
-      </c>
-      <c r="S51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>21.9</v>
+      </c>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V51" s="5" t="inlineStr">
@@ -6469,69 +6469,69 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG51" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -6541,20 +6541,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1395.392644038286</v>
+        <v>1395.34124332144</v>
       </c>
       <c r="D52" t="n">
-        <v>1391.041758295748</v>
+        <v>1388.550715078914</v>
       </c>
       <c r="E52" t="n">
-        <v>1399.743529780824</v>
+        <v>1402.131771563966</v>
       </c>
       <c r="F52" t="n">
-        <v>28909</v>
+        <v>7937</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6567,10 +6567,10 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6583,36 +6583,36 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="N52" t="n">
-        <v>87.5</v>
+        <v>587.5</v>
       </c>
       <c r="O52" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="P52" t="n">
-        <v>43.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>17.5</v>
+        <v>117.5</v>
       </c>
       <c r="R52" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="S52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>146.9</v>
+      </c>
+      <c r="S52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V52" s="5" t="inlineStr">
@@ -6620,39 +6620,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD52" s="6" t="inlineStr">
@@ -6660,14 +6660,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF52" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF52" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG52" s="6" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6696,16 +6696,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1394.863493766788</v>
+        <v>1394.607539408807</v>
       </c>
       <c r="D53" t="n">
-        <v>1391.196489681477</v>
+        <v>1390.944315176111</v>
       </c>
       <c r="E53" t="n">
-        <v>1398.5304978521</v>
+        <v>1398.270763641502</v>
       </c>
       <c r="F53" t="n">
-        <v>57037</v>
+        <v>57020</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6767,16 +6767,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1392.599535271364</v>
+        <v>1392.562103415771</v>
       </c>
       <c r="D54" t="n">
-        <v>1389.030120296357</v>
+        <v>1388.994648434019</v>
       </c>
       <c r="E54" t="n">
-        <v>1396.168950246371</v>
+        <v>1396.129558397523</v>
       </c>
       <c r="F54" t="n">
-        <v>46276</v>
+        <v>46264</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6838,16 +6838,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1390.083073178615</v>
+        <v>1389.928712402181</v>
       </c>
       <c r="D55" t="n">
-        <v>1386.078821673516</v>
+        <v>1385.925164571151</v>
       </c>
       <c r="E55" t="n">
-        <v>1394.087324683713</v>
+        <v>1393.932260233212</v>
       </c>
       <c r="F55" t="n">
-        <v>40783</v>
+        <v>40751</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1387.668793835836</v>
+        <v>1387.71034387502</v>
       </c>
       <c r="D56" t="n">
-        <v>1382.718426292622</v>
+        <v>1382.758754671713</v>
       </c>
       <c r="E56" t="n">
-        <v>1392.619161379049</v>
+        <v>1392.661933078329</v>
       </c>
       <c r="F56" t="n">
-        <v>25681</v>
+        <v>25689</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7060,16 +7060,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1386.9860839818</v>
+        <v>1387.005677093801</v>
       </c>
       <c r="D57" t="n">
-        <v>1380.739839481101</v>
+        <v>1380.757375096932</v>
       </c>
       <c r="E57" t="n">
-        <v>1393.2323284825</v>
+        <v>1393.253979090669</v>
       </c>
       <c r="F57" t="n">
-        <v>10928</v>
+        <v>10919</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7131,16 +7131,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1384.327495501141</v>
+        <v>1384.122634176615</v>
       </c>
       <c r="D58" t="n">
-        <v>1379.097022532456</v>
+        <v>1378.893166785581</v>
       </c>
       <c r="E58" t="n">
-        <v>1389.557968469826</v>
+        <v>1389.352101567649</v>
       </c>
       <c r="F58" t="n">
-        <v>17065</v>
+        <v>17059</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7202,16 +7202,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1383.133241802538</v>
+        <v>1383.098681285096</v>
       </c>
       <c r="D59" t="n">
-        <v>1378.251341045274</v>
+        <v>1378.216212100964</v>
       </c>
       <c r="E59" t="n">
-        <v>1388.015142559802</v>
+        <v>1387.981150469227</v>
       </c>
       <c r="F59" t="n">
-        <v>23706</v>
+        <v>23705</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1378.722384925215</v>
+        <v>1378.531349092249</v>
       </c>
       <c r="D60" t="n">
-        <v>1374.349871985544</v>
+        <v>1374.159990623141</v>
       </c>
       <c r="E60" t="n">
-        <v>1383.094897864887</v>
+        <v>1382.902707561358</v>
       </c>
       <c r="F60" t="n">
-        <v>29688</v>
+        <v>29678</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
@@ -7500,16 +7500,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1377.14957267385</v>
+        <v>1377.233302776744</v>
       </c>
       <c r="D61" t="n">
-        <v>1365.886820374312</v>
+        <v>1365.974395559374</v>
       </c>
       <c r="E61" t="n">
-        <v>1388.412324973388</v>
+        <v>1388.492209994114</v>
       </c>
       <c r="F61" t="n">
-        <v>2796</v>
+        <v>2797</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7571,16 +7571,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1374.8177093069</v>
+        <v>1374.86126220844</v>
       </c>
       <c r="D62" t="n">
-        <v>1370.121466626006</v>
+        <v>1370.164125078223</v>
       </c>
       <c r="E62" t="n">
-        <v>1379.513951987795</v>
+        <v>1379.558399338657</v>
       </c>
       <c r="F62" t="n">
-        <v>26244</v>
+        <v>26238</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7722,16 +7722,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1372.678732886349</v>
+        <v>1372.746788664577</v>
       </c>
       <c r="D63" t="n">
-        <v>1368.433695516436</v>
+        <v>1368.500964664134</v>
       </c>
       <c r="E63" t="n">
-        <v>1376.923770256261</v>
+        <v>1376.99261266502</v>
       </c>
       <c r="F63" t="n">
-        <v>31042</v>
+        <v>31054</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7793,16 +7793,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1369.324594241685</v>
+        <v>1369.324589680222</v>
       </c>
       <c r="D64" t="n">
-        <v>1363.48308219556</v>
+        <v>1363.482220805888</v>
       </c>
       <c r="E64" t="n">
-        <v>1375.166106287809</v>
+        <v>1375.166958554556</v>
       </c>
       <c r="F64" t="n">
-        <v>13674</v>
+        <v>13667</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1368.953744823716</v>
+        <v>1368.891999059175</v>
       </c>
       <c r="D65" t="n">
-        <v>1364.246249681493</v>
+        <v>1364.184139690836</v>
       </c>
       <c r="E65" t="n">
-        <v>1373.661239965939</v>
+        <v>1373.599858427514</v>
       </c>
       <c r="F65" t="n">
-        <v>28834</v>
+        <v>28817</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
@@ -8091,16 +8091,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1367.791500040027</v>
+        <v>1367.825962059829</v>
       </c>
       <c r="D66" t="n">
-        <v>1361.989017231514</v>
+        <v>1362.023061238375</v>
       </c>
       <c r="E66" t="n">
-        <v>1373.59398284854</v>
+        <v>1373.628862881282</v>
       </c>
       <c r="F66" t="n">
-        <v>11690</v>
+        <v>11679</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8162,16 +8162,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1365.748404470377</v>
+        <v>1365.904694579216</v>
       </c>
       <c r="D67" t="n">
-        <v>1362.071252448951</v>
+        <v>1362.225948536436</v>
       </c>
       <c r="E67" t="n">
-        <v>1369.425556491802</v>
+        <v>1369.583440621995</v>
       </c>
       <c r="F67" t="n">
-        <v>47471</v>
+        <v>47468</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8313,16 +8313,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1363.773278093486</v>
+        <v>1363.7724666685</v>
       </c>
       <c r="D68" t="n">
-        <v>1359.497911880833</v>
+        <v>1359.496794842024</v>
       </c>
       <c r="E68" t="n">
-        <v>1368.048644306139</v>
+        <v>1368.048138494976</v>
       </c>
       <c r="F68" t="n">
-        <v>35135</v>
+        <v>35142</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8384,16 +8384,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1360.888992993521</v>
+        <v>1360.847325108952</v>
       </c>
       <c r="D69" t="n">
-        <v>1353.608420174972</v>
+        <v>1353.568306690125</v>
       </c>
       <c r="E69" t="n">
-        <v>1368.169565812071</v>
+        <v>1368.126343527779</v>
       </c>
       <c r="F69" t="n">
-        <v>7491</v>
+        <v>7490</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8535,13 +8535,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1358.50895420256</v>
+        <v>1358.543744673714</v>
       </c>
       <c r="D70" t="n">
-        <v>1353.762704544031</v>
+        <v>1353.796034091787</v>
       </c>
       <c r="E70" t="n">
-        <v>1363.255203861089</v>
+        <v>1363.291455255642</v>
       </c>
       <c r="F70" t="n">
         <v>21770</v>
@@ -8686,16 +8686,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1357.418127629142</v>
+        <v>1357.436339158313</v>
       </c>
       <c r="D71" t="n">
-        <v>1352.214203012155</v>
+        <v>1352.232905034325</v>
       </c>
       <c r="E71" t="n">
-        <v>1362.622052246127</v>
+        <v>1362.639773282302</v>
       </c>
       <c r="F71" t="n">
-        <v>17688</v>
+        <v>17690</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8757,16 +8757,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1356.204589728338</v>
+        <v>1356.204596870842</v>
       </c>
       <c r="D72" t="n">
-        <v>1347.86250925078</v>
+        <v>1347.859031368456</v>
       </c>
       <c r="E72" t="n">
-        <v>1364.546670205896</v>
+        <v>1364.550162373227</v>
       </c>
       <c r="F72" t="n">
-        <v>5328</v>
+        <v>5326</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
@@ -8904,16 +8904,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1354.001605957323</v>
+        <v>1354.010614611382</v>
       </c>
       <c r="D73" t="n">
-        <v>1350.549457225164</v>
+        <v>1350.557283888515</v>
       </c>
       <c r="E73" t="n">
-        <v>1357.453754689482</v>
+        <v>1357.46394533425</v>
       </c>
       <c r="F73" t="n">
-        <v>56196</v>
+        <v>56195</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8975,16 +8975,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1353.374976206646</v>
+        <v>1353.337182944429</v>
       </c>
       <c r="D74" t="n">
-        <v>1345.028802968305</v>
+        <v>1344.993994519852</v>
       </c>
       <c r="E74" t="n">
-        <v>1361.721149444987</v>
+        <v>1361.680371369005</v>
       </c>
       <c r="F74" t="n">
-        <v>4955</v>
+        <v>4957</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9046,16 +9046,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1352.469084029198</v>
+        <v>1352.29334428352</v>
       </c>
       <c r="D75" t="n">
-        <v>1348.11830081005</v>
+        <v>1347.941331339142</v>
       </c>
       <c r="E75" t="n">
-        <v>1356.819867248346</v>
+        <v>1356.645357227898</v>
       </c>
       <c r="F75" t="n">
-        <v>30615</v>
+        <v>30608</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9197,16 +9197,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1348.321467877297</v>
+        <v>1348.257949584937</v>
       </c>
       <c r="D76" t="n">
-        <v>1340.91844761378</v>
+        <v>1340.852807696821</v>
       </c>
       <c r="E76" t="n">
-        <v>1355.724488140813</v>
+        <v>1355.663091473052</v>
       </c>
       <c r="F76" t="n">
-        <v>6534</v>
+        <v>6531</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9268,13 +9268,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1347.504567376575</v>
+        <v>1347.590700143598</v>
       </c>
       <c r="D77" t="n">
-        <v>1335.820835636657</v>
+        <v>1335.907018896996</v>
       </c>
       <c r="E77" t="n">
-        <v>1359.188299116492</v>
+        <v>1359.274381390201</v>
       </c>
       <c r="F77" t="n">
         <v>2549</v>
@@ -9419,13 +9419,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1347.164168093483</v>
+        <v>1347.195421202076</v>
       </c>
       <c r="D78" t="n">
-        <v>1337.705940598529</v>
+        <v>1337.736883742005</v>
       </c>
       <c r="E78" t="n">
-        <v>1356.622395588438</v>
+        <v>1356.653958662146</v>
       </c>
       <c r="F78" t="n">
         <v>3926</v>
@@ -9570,16 +9570,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1346.235195071941</v>
+        <v>1346.119286717584</v>
       </c>
       <c r="D79" t="n">
-        <v>1338.96947535862</v>
+        <v>1338.853158828177</v>
       </c>
       <c r="E79" t="n">
-        <v>1353.500914785262</v>
+        <v>1353.385414606992</v>
       </c>
       <c r="F79" t="n">
-        <v>6993</v>
+        <v>6992</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -9641,16 +9641,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1346.047826672526</v>
+        <v>1345.91811306582</v>
       </c>
       <c r="D80" t="n">
-        <v>1338.309814301355</v>
+        <v>1338.179632197768</v>
       </c>
       <c r="E80" t="n">
-        <v>1353.785839043698</v>
+        <v>1353.656593933871</v>
       </c>
       <c r="F80" t="n">
-        <v>6861</v>
+        <v>6862</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9792,13 +9792,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1343.261315720255</v>
+        <v>1343.279265618258</v>
       </c>
       <c r="D81" t="n">
-        <v>1333.297906899684</v>
+        <v>1333.315712097092</v>
       </c>
       <c r="E81" t="n">
-        <v>1353.224724540826</v>
+        <v>1353.242819139425</v>
       </c>
       <c r="F81" t="n">
         <v>3344</v>
@@ -9943,13 +9943,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1341.870345130973</v>
+        <v>1341.960471558782</v>
       </c>
       <c r="D82" t="n">
-        <v>1332.360472583658</v>
+        <v>1332.450197199104</v>
       </c>
       <c r="E82" t="n">
-        <v>1351.380217678288</v>
+        <v>1351.47074591846</v>
       </c>
       <c r="F82" t="n">
         <v>3829</v>
@@ -10094,16 +10094,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1336.079714706485</v>
+        <v>1336.094724651596</v>
       </c>
       <c r="D83" t="n">
-        <v>1331.636338226552</v>
+        <v>1331.650370807612</v>
       </c>
       <c r="E83" t="n">
-        <v>1340.523091186417</v>
+        <v>1340.53907849558</v>
       </c>
       <c r="F83" t="n">
-        <v>25366</v>
+        <v>25362</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10245,13 +10245,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1334.963274649406</v>
+        <v>1335.029510081405</v>
       </c>
       <c r="D84" t="n">
-        <v>1331.246273682105</v>
+        <v>1331.310780487382</v>
       </c>
       <c r="E84" t="n">
-        <v>1338.680275616707</v>
+        <v>1338.748239675429</v>
       </c>
       <c r="F84" t="n">
         <v>41375</v>
@@ -10396,13 +10396,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1333.127760928748</v>
+        <v>1333.190386075118</v>
       </c>
       <c r="D85" t="n">
-        <v>1329.529226560026</v>
+        <v>1329.590511712065</v>
       </c>
       <c r="E85" t="n">
-        <v>1336.726295297469</v>
+        <v>1336.790260438171</v>
       </c>
       <c r="F85" t="n">
         <v>59656</v>
@@ -10547,16 +10547,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1329.801431139705</v>
+        <v>1329.712478462061</v>
       </c>
       <c r="D86" t="n">
-        <v>1323.725073505479</v>
+        <v>1323.635766469315</v>
       </c>
       <c r="E86" t="n">
-        <v>1335.87778877393</v>
+        <v>1335.789190454808</v>
       </c>
       <c r="F86" t="n">
-        <v>12200</v>
+        <v>12197</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10698,16 +10698,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1329.277387717646</v>
+        <v>1328.929895512465</v>
       </c>
       <c r="D87" t="n">
-        <v>1307.974442903774</v>
+        <v>1307.631201431312</v>
       </c>
       <c r="E87" t="n">
-        <v>1350.580332531519</v>
+        <v>1350.228589593617</v>
       </c>
       <c r="F87" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10849,13 +10849,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1327.956722776633</v>
+        <v>1328.027388080053</v>
       </c>
       <c r="D88" t="n">
-        <v>1315.811143175403</v>
+        <v>1315.88217863855</v>
       </c>
       <c r="E88" t="n">
-        <v>1340.102302377863</v>
+        <v>1340.172597521556</v>
       </c>
       <c r="F88" t="n">
         <v>2218</v>
@@ -11000,16 +11000,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1327.188978845238</v>
+        <v>1327.315061703295</v>
       </c>
       <c r="D89" t="n">
-        <v>1322.45693012172</v>
+        <v>1322.582381333464</v>
       </c>
       <c r="E89" t="n">
-        <v>1331.921027568756</v>
+        <v>1332.047742073125</v>
       </c>
       <c r="F89" t="n">
-        <v>26450</v>
+        <v>26451</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11151,16 +11151,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1327.179373996918</v>
+        <v>1327.249101792514</v>
       </c>
       <c r="D90" t="n">
-        <v>1322.924001253549</v>
+        <v>1322.992218877837</v>
       </c>
       <c r="E90" t="n">
-        <v>1331.434746740286</v>
+        <v>1331.505984707192</v>
       </c>
       <c r="F90" t="n">
-        <v>39934</v>
+        <v>39938</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -11302,13 +11302,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1323.466394012027</v>
+        <v>1323.496998508067</v>
       </c>
       <c r="D91" t="n">
-        <v>1315.194750113874</v>
+        <v>1315.22471591538</v>
       </c>
       <c r="E91" t="n">
-        <v>1331.738037910181</v>
+        <v>1331.769281100755</v>
       </c>
       <c r="F91" t="n">
         <v>6795</v>
@@ -11373,13 +11373,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1322.80633173333</v>
+        <v>1322.927353271487</v>
       </c>
       <c r="D92" t="n">
-        <v>1318.096096730552</v>
+        <v>1318.216067233725</v>
       </c>
       <c r="E92" t="n">
-        <v>1327.516566736108</v>
+        <v>1327.638639309249</v>
       </c>
       <c r="F92" t="n">
         <v>30259</v>
@@ -11524,16 +11524,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1320.422217115226</v>
+        <v>1320.51594335373</v>
       </c>
       <c r="D93" t="n">
-        <v>1313.203710785859</v>
+        <v>1313.298597445824</v>
       </c>
       <c r="E93" t="n">
-        <v>1327.640723444594</v>
+        <v>1327.733289261635</v>
       </c>
       <c r="F93" t="n">
-        <v>7132</v>
+        <v>7137</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -11595,16 +11595,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1318.307715384113</v>
+        <v>1318.357153364021</v>
       </c>
       <c r="D94" t="n">
-        <v>1314.828093740106</v>
+        <v>1314.875151257682</v>
       </c>
       <c r="E94" t="n">
-        <v>1321.78733702812</v>
+        <v>1321.83915547036</v>
       </c>
       <c r="F94" t="n">
-        <v>54712</v>
+        <v>54709</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11746,13 +11746,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1318.056881492078</v>
+        <v>1318.157420115365</v>
       </c>
       <c r="D95" t="n">
-        <v>1312.907256444869</v>
+        <v>1313.007045752775</v>
       </c>
       <c r="E95" t="n">
-        <v>1323.206506539286</v>
+        <v>1323.307794477954</v>
       </c>
       <c r="F95" t="n">
         <v>22553</v>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1318.02237692423</v>
+        <v>1318.064676635707</v>
       </c>
       <c r="D96" t="n">
-        <v>1312.32095307992</v>
+        <v>1312.362518211149</v>
       </c>
       <c r="E96" t="n">
-        <v>1323.723800768539</v>
+        <v>1323.766835060265</v>
       </c>
       <c r="F96" t="n">
         <v>16478</v>
@@ -11968,16 +11968,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1317.286136732861</v>
+        <v>1317.305939023843</v>
       </c>
       <c r="D97" t="n">
-        <v>1310.915024625983</v>
+        <v>1310.932120797338</v>
       </c>
       <c r="E97" t="n">
-        <v>1323.657248839738</v>
+        <v>1323.679757250348</v>
       </c>
       <c r="F97" t="n">
-        <v>10621</v>
+        <v>10620</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -12119,16 +12119,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1315.580834916967</v>
+        <v>1315.338918219274</v>
       </c>
       <c r="D98" t="n">
-        <v>1310.040849646971</v>
+        <v>1309.800001373384</v>
       </c>
       <c r="E98" t="n">
-        <v>1321.120820186962</v>
+        <v>1320.877835065164</v>
       </c>
       <c r="F98" t="n">
-        <v>15492</v>
+        <v>15490</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -12270,13 +12270,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1314.295505064178</v>
+        <v>1314.311880958647</v>
       </c>
       <c r="D99" t="n">
-        <v>1309.739388643694</v>
+        <v>1309.754366959896</v>
       </c>
       <c r="E99" t="n">
-        <v>1318.851621484662</v>
+        <v>1318.869394957399</v>
       </c>
       <c r="F99" t="n">
         <v>24739</v>
@@ -12417,13 +12417,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1314.119825796294</v>
+        <v>1314.184983983982</v>
       </c>
       <c r="D100" t="n">
-        <v>1310.191040099033</v>
+        <v>1310.255014542093</v>
       </c>
       <c r="E100" t="n">
-        <v>1318.048611493554</v>
+        <v>1318.114953425871</v>
       </c>
       <c r="F100" t="n">
         <v>45459</v>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1307.145119711551</v>
+        <v>1307.186505248886</v>
       </c>
       <c r="D101" t="n">
-        <v>1302.436936283736</v>
+        <v>1302.477221668485</v>
       </c>
       <c r="E101" t="n">
-        <v>1311.853303139365</v>
+        <v>1311.895788829286</v>
       </c>
       <c r="F101" t="n">
         <v>24572</v>
@@ -12639,16 +12639,16 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1306.701380513342</v>
+        <v>1306.635195795994</v>
       </c>
       <c r="D102" t="n">
-        <v>1296.501343684375</v>
+        <v>1296.439332545961</v>
       </c>
       <c r="E102" t="n">
-        <v>1316.90141734231</v>
+        <v>1316.831059046028</v>
       </c>
       <c r="F102" t="n">
-        <v>4001</v>
+        <v>4003</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -12790,13 +12790,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1306.395652607303</v>
+        <v>1306.508723614388</v>
       </c>
       <c r="D103" t="n">
-        <v>1300.720207232563</v>
+        <v>1300.832631270113</v>
       </c>
       <c r="E103" t="n">
-        <v>1312.071097982042</v>
+        <v>1312.184815958663</v>
       </c>
       <c r="F103" t="n">
         <v>19621</v>
@@ -12937,16 +12937,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1305.52314433151</v>
+        <v>1305.456232577047</v>
       </c>
       <c r="D104" t="n">
-        <v>1297.343804614698</v>
+        <v>1297.274640947145</v>
       </c>
       <c r="E104" t="n">
-        <v>1313.702484048322</v>
+        <v>1313.637824206949</v>
       </c>
       <c r="F104" t="n">
-        <v>5931</v>
+        <v>5929</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -13088,13 +13088,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1305.356906571007</v>
+        <v>1305.419574676973</v>
       </c>
       <c r="D105" t="n">
-        <v>1300.916108587662</v>
+        <v>1300.977102264792</v>
       </c>
       <c r="E105" t="n">
-        <v>1309.797704554351</v>
+        <v>1309.862047089154</v>
       </c>
       <c r="F105" t="n">
         <v>28073</v>
@@ -13155,36 +13155,36 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1303.35283890745</v>
+        <v>1303.393478345997</v>
       </c>
       <c r="D106" t="n">
-        <v>1298.842370259404</v>
+        <v>1294.07701918975</v>
       </c>
       <c r="E106" t="n">
-        <v>1307.863307555496</v>
+        <v>1312.709937502244</v>
       </c>
       <c r="F106" t="n">
-        <v>33183</v>
+        <v>4171</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -13197,22 +13197,22 @@
         </is>
       </c>
       <c r="M106" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="N106" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O106" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="P106" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="Q106" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R106" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="S106" s="6" t="inlineStr">
         <is>
@@ -13306,36 +13306,36 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1303.299129297973</v>
+        <v>1303.358042106954</v>
       </c>
       <c r="D107" t="n">
-        <v>1293.982908442546</v>
+        <v>1298.846837008375</v>
       </c>
       <c r="E107" t="n">
-        <v>1312.6153501534</v>
+        <v>1307.869247205533</v>
       </c>
       <c r="F107" t="n">
-        <v>4171</v>
+        <v>33186</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J107" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -13348,22 +13348,22 @@
         </is>
       </c>
       <c r="M107" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O107" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="P107" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="Q107" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R107" t="n">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="S107" s="6" t="inlineStr">
         <is>
@@ -13461,13 +13461,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1302.851769625514</v>
+        <v>1302.892385838529</v>
       </c>
       <c r="D108" t="n">
-        <v>1298.774341350169</v>
+        <v>1298.813437397918</v>
       </c>
       <c r="E108" t="n">
-        <v>1306.929197900859</v>
+        <v>1306.971334279139</v>
       </c>
       <c r="F108" t="n">
         <v>39406</v>
@@ -13612,13 +13612,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1298.927209757433</v>
+        <v>1298.993419902383</v>
       </c>
       <c r="D109" t="n">
-        <v>1291.163728864531</v>
+        <v>1291.229389149604</v>
       </c>
       <c r="E109" t="n">
-        <v>1306.690690650335</v>
+        <v>1306.757450655162</v>
       </c>
       <c r="F109" t="n">
         <v>7140</v>
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1293.232466870541</v>
+        <v>1293.291930590795</v>
       </c>
       <c r="D110" t="n">
-        <v>1289.493055214273</v>
+        <v>1289.551107742676</v>
       </c>
       <c r="E110" t="n">
-        <v>1296.97187852681</v>
+        <v>1297.032753438913</v>
       </c>
       <c r="F110" t="n">
         <v>55240</v>
@@ -13914,13 +13914,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1289.154706799565</v>
+        <v>1289.235893053812</v>
       </c>
       <c r="D111" t="n">
-        <v>1281.847151052265</v>
+        <v>1281.927898129481</v>
       </c>
       <c r="E111" t="n">
-        <v>1296.462262546866</v>
+        <v>1296.543887978143</v>
       </c>
       <c r="F111" t="n">
         <v>8662</v>
@@ -13981,13 +13981,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1289.041665411433</v>
+        <v>1289.198952865954</v>
       </c>
       <c r="D112" t="n">
-        <v>1285.655681591562</v>
+        <v>1285.811466889092</v>
       </c>
       <c r="E112" t="n">
-        <v>1292.427649231304</v>
+        <v>1292.586438842816</v>
       </c>
       <c r="F112" t="n">
         <v>75754</v>
@@ -14132,16 +14132,16 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1287.331898389319</v>
+        <v>1287.464700274216</v>
       </c>
       <c r="D113" t="n">
-        <v>1278.9421269437</v>
+        <v>1279.074349577417</v>
       </c>
       <c r="E113" t="n">
-        <v>1295.721669834937</v>
+        <v>1295.855050971014</v>
       </c>
       <c r="F113" t="n">
-        <v>5676</v>
+        <v>5677</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -14283,13 +14283,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1286.101544337988</v>
+        <v>1286.17297252795</v>
       </c>
       <c r="D114" t="n">
-        <v>1276.129732279603</v>
+        <v>1276.200882088325</v>
       </c>
       <c r="E114" t="n">
-        <v>1296.073356396372</v>
+        <v>1296.145062967574</v>
       </c>
       <c r="F114" t="n">
         <v>3749</v>
@@ -14434,13 +14434,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1286.009093944304</v>
+        <v>1286.034023695829</v>
       </c>
       <c r="D115" t="n">
-        <v>1275.542593857352</v>
+        <v>1275.567412804299</v>
       </c>
       <c r="E115" t="n">
-        <v>1296.475594031256</v>
+        <v>1296.500634587359</v>
       </c>
       <c r="F115" t="n">
         <v>2846</v>
@@ -14585,16 +14585,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1285.133433798625</v>
+        <v>1285.047688103793</v>
       </c>
       <c r="D116" t="n">
-        <v>1277.928282698489</v>
+        <v>1277.837109634927</v>
       </c>
       <c r="E116" t="n">
-        <v>1292.33858489876</v>
+        <v>1292.25826657266</v>
       </c>
       <c r="F116" t="n">
-        <v>8496</v>
+        <v>8486</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -14736,13 +14736,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1280.01057812114</v>
+        <v>1280.147621227799</v>
       </c>
       <c r="D117" t="n">
-        <v>1273.149608292559</v>
+        <v>1273.286434322637</v>
       </c>
       <c r="E117" t="n">
-        <v>1286.871547949721</v>
+        <v>1287.008808132961</v>
       </c>
       <c r="F117" t="n">
         <v>10072</v>
@@ -14883,13 +14883,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1276.697567757632</v>
+        <v>1276.731253885557</v>
       </c>
       <c r="D118" t="n">
-        <v>1271.371309917728</v>
+        <v>1271.404836665339</v>
       </c>
       <c r="E118" t="n">
-        <v>1282.023825597535</v>
+        <v>1282.057671105775</v>
       </c>
       <c r="F118" t="n">
         <v>19659</v>
@@ -15034,13 +15034,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1276.094332807035</v>
+        <v>1276.18773858114</v>
       </c>
       <c r="D119" t="n">
-        <v>1272.505000760238</v>
+        <v>1272.597861062768</v>
       </c>
       <c r="E119" t="n">
-        <v>1279.683664853832</v>
+        <v>1279.777616099512</v>
       </c>
       <c r="F119" t="n">
         <v>156876</v>
@@ -15185,13 +15185,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1275.95103558558</v>
+        <v>1275.985944306855</v>
       </c>
       <c r="D120" t="n">
-        <v>1269.372217394196</v>
+        <v>1269.406510000104</v>
       </c>
       <c r="E120" t="n">
-        <v>1282.529853776966</v>
+        <v>1282.565378613605</v>
       </c>
       <c r="F120" t="n">
         <v>9866</v>
@@ -15336,13 +15336,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1274.173042683566</v>
+        <v>1274.239099123449</v>
       </c>
       <c r="D121" t="n">
-        <v>1268.26283552809</v>
+        <v>1268.327535367393</v>
       </c>
       <c r="E121" t="n">
-        <v>1280.083249839041</v>
+        <v>1280.150662879505</v>
       </c>
       <c r="F121" t="n">
         <v>14681</v>
@@ -15487,13 +15487,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1270.459590030523</v>
+        <v>1270.500189592126</v>
       </c>
       <c r="D122" t="n">
-        <v>1262.331224219045</v>
+        <v>1262.371091701494</v>
       </c>
       <c r="E122" t="n">
-        <v>1278.587955842002</v>
+        <v>1278.629287482758</v>
       </c>
       <c r="F122" t="n">
         <v>5432</v>
@@ -15638,13 +15638,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1266.995814252235</v>
+        <v>1267.074816433674</v>
       </c>
       <c r="D123" t="n">
-        <v>1262.104782665003</v>
+        <v>1262.18247110342</v>
       </c>
       <c r="E123" t="n">
-        <v>1271.886845839467</v>
+        <v>1271.967161763927</v>
       </c>
       <c r="F123" t="n">
         <v>27124</v>
@@ -15789,13 +15789,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1266.558246723564</v>
+        <v>1266.719172346277</v>
       </c>
       <c r="D124" t="n">
-        <v>1262.735852276309</v>
+        <v>1262.895428702131</v>
       </c>
       <c r="E124" t="n">
-        <v>1270.380641170819</v>
+        <v>1270.542915990423</v>
       </c>
       <c r="F124" t="n">
         <v>54611</v>
@@ -15940,13 +15940,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1264.725940980456</v>
+        <v>1264.842372616404</v>
       </c>
       <c r="D125" t="n">
-        <v>1258.445695293738</v>
+        <v>1258.561987438349</v>
       </c>
       <c r="E125" t="n">
-        <v>1271.006186667175</v>
+        <v>1271.122757794459</v>
       </c>
       <c r="F125" t="n">
         <v>15147</v>
@@ -16091,13 +16091,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1261.309619120929</v>
+        <v>1261.355759372048</v>
       </c>
       <c r="D126" t="n">
-        <v>1256.360298967619</v>
+        <v>1256.405808766476</v>
       </c>
       <c r="E126" t="n">
-        <v>1266.258939274239</v>
+        <v>1266.305709977621</v>
       </c>
       <c r="F126" t="n">
         <v>37325</v>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1261.263111801816</v>
+        <v>1261.295268092635</v>
       </c>
       <c r="D127" t="n">
-        <v>1256.938105218465</v>
+        <v>1256.969943130666</v>
       </c>
       <c r="E127" t="n">
-        <v>1265.588118385167</v>
+        <v>1265.620593054603</v>
       </c>
       <c r="F127" t="n">
         <v>77554</v>
@@ -16313,13 +16313,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1256.10527174757</v>
+        <v>1256.170583542945</v>
       </c>
       <c r="D128" t="n">
-        <v>1251.507837552984</v>
+        <v>1251.571616010566</v>
       </c>
       <c r="E128" t="n">
-        <v>1260.702705942155</v>
+        <v>1260.769551075324</v>
       </c>
       <c r="F128" t="n">
         <v>24126</v>
@@ -16464,13 +16464,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1251.437137513005</v>
+        <v>1251.477048329519</v>
       </c>
       <c r="D129" t="n">
-        <v>1240.655596935942</v>
+        <v>1240.695505669421</v>
       </c>
       <c r="E129" t="n">
-        <v>1262.218678090069</v>
+        <v>1262.258590989616</v>
       </c>
       <c r="F129" t="n">
         <v>3334</v>
@@ -16615,13 +16615,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1249.866598945454</v>
+        <v>1249.926557971563</v>
       </c>
       <c r="D130" t="n">
-        <v>1243.263166110452</v>
+        <v>1243.322368814303</v>
       </c>
       <c r="E130" t="n">
-        <v>1256.470031780456</v>
+        <v>1256.530747128823</v>
       </c>
       <c r="F130" t="n">
         <v>10140</v>
@@ -16766,13 +16766,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1239.454356383045</v>
+        <v>1239.555792313314</v>
       </c>
       <c r="D131" t="n">
-        <v>1232.226468469948</v>
+        <v>1232.32739047985</v>
       </c>
       <c r="E131" t="n">
-        <v>1246.682244296142</v>
+        <v>1246.784194146779</v>
       </c>
       <c r="F131" t="n">
         <v>8858</v>
@@ -16833,13 +16833,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1237.382539742753</v>
+        <v>1237.447722476727</v>
       </c>
       <c r="D132" t="n">
-        <v>1228.289061092582</v>
+        <v>1228.353841982179</v>
       </c>
       <c r="E132" t="n">
-        <v>1246.476018392924</v>
+        <v>1246.541602971276</v>
       </c>
       <c r="F132" t="n">
         <v>4781</v>
@@ -16984,13 +16984,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1233.668777801287</v>
+        <v>1233.727735920842</v>
       </c>
       <c r="D133" t="n">
-        <v>1228.115070312534</v>
+        <v>1228.173830930568</v>
       </c>
       <c r="E133" t="n">
-        <v>1239.22248529004</v>
+        <v>1239.281640911116</v>
       </c>
       <c r="F133" t="n">
         <v>26195</v>
@@ -17135,13 +17135,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1232.902502395055</v>
+        <v>1232.971927662224</v>
       </c>
       <c r="D134" t="n">
-        <v>1227.627135376491</v>
+        <v>1227.696389666987</v>
       </c>
       <c r="E134" t="n">
-        <v>1238.177869413619</v>
+        <v>1238.24746565746</v>
       </c>
       <c r="F134" t="n">
         <v>39302</v>
@@ -17286,13 +17286,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1228.945704876516</v>
+        <v>1228.995962353536</v>
       </c>
       <c r="D135" t="n">
-        <v>1224.386912000645</v>
+        <v>1224.436752256649</v>
       </c>
       <c r="E135" t="n">
-        <v>1233.504497752387</v>
+        <v>1233.555172450423</v>
       </c>
       <c r="F135" t="n">
         <v>51416</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1226.282017941045</v>
+        <v>1226.31836945245</v>
       </c>
       <c r="D136" t="n">
-        <v>1221.498322471871</v>
+        <v>1221.534419199625</v>
       </c>
       <c r="E136" t="n">
-        <v>1231.065713410219</v>
+        <v>1231.102319705275</v>
       </c>
       <c r="F136" t="n">
         <v>54036</v>
@@ -17508,13 +17508,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1223.14452068939</v>
+        <v>1223.230754755843</v>
       </c>
       <c r="D137" t="n">
-        <v>1219.404643561441</v>
+        <v>1219.490333039874</v>
       </c>
       <c r="E137" t="n">
-        <v>1226.884397817338</v>
+        <v>1226.971176471813</v>
       </c>
       <c r="F137" t="n">
         <v>104642</v>
@@ -17659,13 +17659,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1222.901917449975</v>
+        <v>1222.97645588098</v>
       </c>
       <c r="D138" t="n">
-        <v>1215.92672573554</v>
+        <v>1216.000366284163</v>
       </c>
       <c r="E138" t="n">
-        <v>1229.877109164411</v>
+        <v>1229.952545477797</v>
       </c>
       <c r="F138" t="n">
         <v>9818</v>
@@ -17810,13 +17810,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1220.480021062777</v>
+        <v>1220.500084405897</v>
       </c>
       <c r="D139" t="n">
-        <v>1209.802009793649</v>
+        <v>1209.821907634847</v>
       </c>
       <c r="E139" t="n">
-        <v>1231.158032331905</v>
+        <v>1231.178261176948</v>
       </c>
       <c r="F139" t="n">
         <v>2896</v>
@@ -17961,13 +17961,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1212.612054541795</v>
+        <v>1212.625041570742</v>
       </c>
       <c r="D140" t="n">
-        <v>1207.572046372246</v>
+        <v>1207.584682199224</v>
       </c>
       <c r="E140" t="n">
-        <v>1217.652062711345</v>
+        <v>1217.665400942261</v>
       </c>
       <c r="F140" t="n">
         <v>24146</v>
@@ -18108,13 +18108,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1212.368896042958</v>
+        <v>1212.427306595669</v>
       </c>
       <c r="D141" t="n">
-        <v>1201.579557733635</v>
+        <v>1201.638156921825</v>
       </c>
       <c r="E141" t="n">
-        <v>1223.15823435228</v>
+        <v>1223.216456269513</v>
       </c>
       <c r="F141" t="n">
         <v>4652</v>
@@ -18255,13 +18255,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1211.300503677557</v>
+        <v>1211.336799541512</v>
       </c>
       <c r="D142" t="n">
-        <v>1207.147019557306</v>
+        <v>1207.181862981577</v>
       </c>
       <c r="E142" t="n">
-        <v>1215.453987797808</v>
+        <v>1215.491736101447</v>
       </c>
       <c r="F142" t="n">
         <v>49605</v>
@@ -18406,13 +18406,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1208.007551740333</v>
+        <v>1208.060272913225</v>
       </c>
       <c r="D143" t="n">
-        <v>1196.905724772451</v>
+        <v>1196.958104857948</v>
       </c>
       <c r="E143" t="n">
-        <v>1219.109378708215</v>
+        <v>1219.162440968503</v>
       </c>
       <c r="F143" t="n">
         <v>3090</v>
@@ -18557,13 +18557,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1203.370178580592</v>
+        <v>1203.421493028633</v>
       </c>
       <c r="D144" t="n">
-        <v>1197.251681344511</v>
+        <v>1197.302849298218</v>
       </c>
       <c r="E144" t="n">
-        <v>1209.488675816673</v>
+        <v>1209.540136759049</v>
       </c>
       <c r="F144" t="n">
         <v>21741</v>
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1199.872014665834</v>
+        <v>1200.026949865917</v>
       </c>
       <c r="D145" t="n">
-        <v>1195.77539962084</v>
+        <v>1195.928991029798</v>
       </c>
       <c r="E145" t="n">
-        <v>1203.968629710828</v>
+        <v>1204.124908702036</v>
       </c>
       <c r="F145" t="n">
         <v>46616</v>
@@ -18859,13 +18859,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1197.375156774945</v>
+        <v>1197.413806976192</v>
       </c>
       <c r="D146" t="n">
-        <v>1192.213314987693</v>
+        <v>1192.251434152646</v>
       </c>
       <c r="E146" t="n">
-        <v>1202.536998562198</v>
+        <v>1202.576179799739</v>
       </c>
       <c r="F146" t="n">
         <v>25055</v>
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1196.551991841969</v>
+        <v>1196.594165560112</v>
       </c>
       <c r="D147" t="n">
-        <v>1192.282367846991</v>
+        <v>1192.324464401785</v>
       </c>
       <c r="E147" t="n">
-        <v>1200.821615836947</v>
+        <v>1200.863866718439</v>
       </c>
       <c r="F147" t="n">
         <v>73503</v>
@@ -19161,13 +19161,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1194.768025859627</v>
+        <v>1194.838420115288</v>
       </c>
       <c r="D148" t="n">
-        <v>1188.654153836879</v>
+        <v>1188.724401843619</v>
       </c>
       <c r="E148" t="n">
-        <v>1200.881897882374</v>
+        <v>1200.952438386958</v>
       </c>
       <c r="F148" t="n">
         <v>32191</v>
@@ -19228,13 +19228,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1190.619573286338</v>
+        <v>1190.643396400145</v>
       </c>
       <c r="D149" t="n">
-        <v>1183.434703292051</v>
+        <v>1183.457918732273</v>
       </c>
       <c r="E149" t="n">
-        <v>1197.804443280624</v>
+        <v>1197.828874068017</v>
       </c>
       <c r="F149" t="n">
         <v>9901</v>
@@ -19375,13 +19375,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1190.508175027473</v>
+        <v>1190.565303503642</v>
       </c>
       <c r="D150" t="n">
-        <v>1183.390289810298</v>
+        <v>1183.447498167749</v>
       </c>
       <c r="E150" t="n">
-        <v>1197.626060244646</v>
+        <v>1197.683108839534</v>
       </c>
       <c r="F150" t="n">
         <v>17839</v>
@@ -19526,13 +19526,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1184.14415289823</v>
+        <v>1184.218147091549</v>
       </c>
       <c r="D151" t="n">
-        <v>1172.660446714093</v>
+        <v>1172.735207541951</v>
       </c>
       <c r="E151" t="n">
-        <v>1195.627859082366</v>
+        <v>1195.701086641147</v>
       </c>
       <c r="F151" t="n">
         <v>4932</v>
@@ -19677,13 +19677,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1184.14327262331</v>
+        <v>1184.19061405536</v>
       </c>
       <c r="D152" t="n">
-        <v>1174.706925785013</v>
+        <v>1174.754601773931</v>
       </c>
       <c r="E152" t="n">
-        <v>1193.579619461606</v>
+        <v>1193.626626336788</v>
       </c>
       <c r="F152" t="n">
         <v>8214</v>
@@ -19828,13 +19828,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1183.283887064367</v>
+        <v>1183.331566672519</v>
       </c>
       <c r="D153" t="n">
-        <v>1176.457248011323</v>
+        <v>1176.504760068282</v>
       </c>
       <c r="E153" t="n">
-        <v>1190.110526117412</v>
+        <v>1190.158373276756</v>
       </c>
       <c r="F153" t="n">
         <v>15483</v>
@@ -19975,13 +19975,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1182.280739888871</v>
+        <v>1182.390872246667</v>
       </c>
       <c r="D154" t="n">
-        <v>1173.599959907248</v>
+        <v>1173.709833085193</v>
       </c>
       <c r="E154" t="n">
-        <v>1190.961519870494</v>
+        <v>1191.071911408141</v>
       </c>
       <c r="F154" t="n">
         <v>6638</v>
@@ -20126,13 +20126,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1182.182443647784</v>
+        <v>1182.276033897757</v>
       </c>
       <c r="D155" t="n">
-        <v>1172.523627680387</v>
+        <v>1172.617556093851</v>
       </c>
       <c r="E155" t="n">
-        <v>1191.84125961518</v>
+        <v>1191.934511701662</v>
       </c>
       <c r="F155" t="n">
         <v>7968</v>
@@ -20193,13 +20193,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1182.002995408644</v>
+        <v>1182.074332289564</v>
       </c>
       <c r="D156" t="n">
-        <v>1174.010065745338</v>
+        <v>1174.081455470495</v>
       </c>
       <c r="E156" t="n">
-        <v>1189.995925071952</v>
+        <v>1190.067209108633</v>
       </c>
       <c r="F156" t="n">
         <v>12637</v>
@@ -20260,13 +20260,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1181.763246786094</v>
+        <v>1181.973054725279</v>
       </c>
       <c r="D157" t="n">
-        <v>1175.691772997174</v>
+        <v>1175.901547477727</v>
       </c>
       <c r="E157" t="n">
-        <v>1187.834720575014</v>
+        <v>1188.04456197283</v>
       </c>
       <c r="F157" t="n">
         <v>23893</v>
@@ -20411,13 +20411,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1179.270925910997</v>
+        <v>1179.346675988982</v>
       </c>
       <c r="D158" t="n">
-        <v>1173.358695680804</v>
+        <v>1173.434333645892</v>
       </c>
       <c r="E158" t="n">
-        <v>1185.183156141189</v>
+        <v>1185.259018332073</v>
       </c>
       <c r="F158" t="n">
         <v>32832</v>
@@ -20478,13 +20478,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1178.473909338385</v>
+        <v>1178.520759711083</v>
       </c>
       <c r="D159" t="n">
-        <v>1167.282917112666</v>
+        <v>1167.329861216538</v>
       </c>
       <c r="E159" t="n">
-        <v>1189.664901564102</v>
+        <v>1189.711658205627</v>
       </c>
       <c r="F159" t="n">
         <v>3188</v>
@@ -20629,13 +20629,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1177.168218955832</v>
+        <v>1177.187792858355</v>
       </c>
       <c r="D160" t="n">
-        <v>1167.362843488658</v>
+        <v>1167.382697252227</v>
       </c>
       <c r="E160" t="n">
-        <v>1186.973594423005</v>
+        <v>1186.992888464483</v>
       </c>
       <c r="F160" t="n">
         <v>6535</v>
@@ -20776,13 +20776,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1175.12321271955</v>
+        <v>1175.213088178972</v>
       </c>
       <c r="D161" t="n">
-        <v>1164.719078155794</v>
+        <v>1164.809282567733</v>
       </c>
       <c r="E161" t="n">
-        <v>1185.527347283305</v>
+        <v>1185.616893790212</v>
       </c>
       <c r="F161" t="n">
         <v>5006</v>
@@ -20923,13 +20923,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1172.299918360355</v>
+        <v>1172.351735164384</v>
       </c>
       <c r="D162" t="n">
-        <v>1166.09968081652</v>
+        <v>1166.151727444851</v>
       </c>
       <c r="E162" t="n">
-        <v>1178.500155904191</v>
+        <v>1178.551742883916</v>
       </c>
       <c r="F162" t="n">
         <v>22479</v>
@@ -21070,13 +21070,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1170.702836549598</v>
+        <v>1170.704173894509</v>
       </c>
       <c r="D163" t="n">
-        <v>1163.298176352394</v>
+        <v>1163.299693908102</v>
       </c>
       <c r="E163" t="n">
-        <v>1178.107496746801</v>
+        <v>1178.108653880915</v>
       </c>
       <c r="F163" t="n">
         <v>16056</v>
@@ -21217,13 +21217,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1170.541856931837</v>
+        <v>1170.58619622776</v>
       </c>
       <c r="D164" t="n">
-        <v>1164.625028824448</v>
+        <v>1164.669063112593</v>
       </c>
       <c r="E164" t="n">
-        <v>1176.458685039225</v>
+        <v>1176.503329342926</v>
       </c>
       <c r="F164" t="n">
         <v>17766</v>
@@ -21368,13 +21368,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1170.167844936637</v>
+        <v>1170.203899738703</v>
       </c>
       <c r="D165" t="n">
-        <v>1164.670411375248</v>
+        <v>1164.706577924633</v>
       </c>
       <c r="E165" t="n">
-        <v>1175.665278498027</v>
+        <v>1175.701221552773</v>
       </c>
       <c r="F165" t="n">
         <v>38492</v>
@@ -21519,13 +21519,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1166.881818928974</v>
+        <v>1166.916751144179</v>
       </c>
       <c r="D166" t="n">
-        <v>1158.819709457441</v>
+        <v>1158.854598305493</v>
       </c>
       <c r="E166" t="n">
-        <v>1174.943928400507</v>
+        <v>1174.978903982864</v>
       </c>
       <c r="F166" t="n">
         <v>10224</v>
@@ -21666,13 +21666,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1166.34393141974</v>
+        <v>1166.405624142021</v>
       </c>
       <c r="D167" t="n">
-        <v>1158.638970699377</v>
+        <v>1158.699624548803</v>
       </c>
       <c r="E167" t="n">
-        <v>1174.048892140103</v>
+        <v>1174.11162373524</v>
       </c>
       <c r="F167" t="n">
         <v>7936</v>
@@ -21817,13 +21817,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1163.96729189253</v>
+        <v>1163.993676903861</v>
       </c>
       <c r="D168" t="n">
-        <v>1152.056331513437</v>
+        <v>1152.083210177685</v>
       </c>
       <c r="E168" t="n">
-        <v>1175.878252271622</v>
+        <v>1175.904143630037</v>
       </c>
       <c r="F168" t="n">
         <v>3777</v>
@@ -21964,13 +21964,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1155.931322470332</v>
+        <v>1156.011016003247</v>
       </c>
       <c r="D169" t="n">
-        <v>1147.543578845949</v>
+        <v>1147.622907319482</v>
       </c>
       <c r="E169" t="n">
-        <v>1164.319066094715</v>
+        <v>1164.399124687011</v>
       </c>
       <c r="F169" t="n">
         <v>6837</v>
@@ -22115,13 +22115,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1154.63362359289</v>
+        <v>1154.522950552867</v>
       </c>
       <c r="D170" t="n">
-        <v>1143.143968192938</v>
+        <v>1143.033083235367</v>
       </c>
       <c r="E170" t="n">
-        <v>1166.123278992842</v>
+        <v>1166.012817870367</v>
       </c>
       <c r="F170" t="n">
         <v>3231</v>
@@ -22266,13 +22266,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1154.202770277036</v>
+        <v>1154.203419253823</v>
       </c>
       <c r="D171" t="n">
-        <v>1141.609028389853</v>
+        <v>1141.610114704767</v>
       </c>
       <c r="E171" t="n">
-        <v>1166.796512164219</v>
+        <v>1166.796723802879</v>
       </c>
       <c r="F171" t="n">
         <v>3585</v>
@@ -22417,13 +22417,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1151.771833232377</v>
+        <v>1151.817016072938</v>
       </c>
       <c r="D172" t="n">
-        <v>1138.606821211451</v>
+        <v>1138.65310149242</v>
       </c>
       <c r="E172" t="n">
-        <v>1164.936845253304</v>
+        <v>1164.980930653455</v>
       </c>
       <c r="F172" t="n">
         <v>4155</v>
@@ -22564,13 +22564,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1151.59927855449</v>
+        <v>1151.659726407652</v>
       </c>
       <c r="D173" t="n">
-        <v>1136.275717655417</v>
+        <v>1136.338330361059</v>
       </c>
       <c r="E173" t="n">
-        <v>1166.922839453563</v>
+        <v>1166.981122454245</v>
       </c>
       <c r="F173" t="n">
         <v>1679</v>
@@ -22711,13 +22711,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1149.94656237383</v>
+        <v>1150.030477272366</v>
       </c>
       <c r="D174" t="n">
-        <v>1137.702563618277</v>
+        <v>1137.787784974516</v>
       </c>
       <c r="E174" t="n">
-        <v>1162.190561129383</v>
+        <v>1162.273169570215</v>
       </c>
       <c r="F174" t="n">
         <v>2572</v>
@@ -22854,36 +22854,36 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>mistral-7b-instruct-v0.2</t>
+          <t>wizardlm-13b</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1148.859346240334</v>
+        <v>1148.896773155809</v>
       </c>
       <c r="D175" t="n">
-        <v>1142.209035426137</v>
+        <v>1139.674559440898</v>
       </c>
       <c r="E175" t="n">
-        <v>1155.50965705453</v>
+        <v>1158.11898687072</v>
       </c>
       <c r="F175" t="n">
-        <v>19402</v>
+        <v>7044</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>Llama 2 Community</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J175" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -22896,22 +22896,22 @@
         </is>
       </c>
       <c r="M175" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="N175" t="n">
-        <v>17.5</v>
+        <v>32.5</v>
       </c>
       <c r="O175" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P175" t="n">
-        <v>8.800000000000001</v>
+        <v>16.2</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="R175" t="n">
-        <v>4.4</v>
+        <v>8.1</v>
       </c>
       <c r="S175" s="6" t="inlineStr">
         <is>
@@ -23005,36 +23005,36 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>wizardlm-13b</t>
+          <t>mistral-7b-instruct-v0.2</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1148.833636430571</v>
+        <v>1148.8892494162</v>
       </c>
       <c r="D176" t="n">
-        <v>1139.610256252784</v>
+        <v>1142.238815828768</v>
       </c>
       <c r="E176" t="n">
-        <v>1158.057016608358</v>
+        <v>1155.539683003631</v>
       </c>
       <c r="F176" t="n">
-        <v>7044</v>
+        <v>19402</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Llama 2 Community</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J176" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -23047,22 +23047,22 @@
         </is>
       </c>
       <c r="M176" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="N176" t="n">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
       <c r="O176" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P176" t="n">
-        <v>16.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q176" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="R176" t="n">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="S176" s="6" t="inlineStr">
         <is>
@@ -23160,13 +23160,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1147.166870909115</v>
+        <v>1147.275978578964</v>
       </c>
       <c r="D177" t="n">
-        <v>1130.113510825412</v>
+        <v>1130.22454496689</v>
       </c>
       <c r="E177" t="n">
-        <v>1164.220230992819</v>
+        <v>1164.327412191038</v>
       </c>
       <c r="F177" t="n">
         <v>1295</v>
@@ -23307,13 +23307,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1143.321218711691</v>
+        <v>1143.373406099685</v>
       </c>
       <c r="D178" t="n">
-        <v>1133.435836730769</v>
+        <v>1133.487927115002</v>
       </c>
       <c r="E178" t="n">
-        <v>1153.206600692615</v>
+        <v>1153.258885084369</v>
       </c>
       <c r="F178" t="n">
         <v>4737</v>
@@ -23458,13 +23458,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1142.572858631035</v>
+        <v>1142.620792010502</v>
       </c>
       <c r="D179" t="n">
-        <v>1136.132669562483</v>
+        <v>1136.180080863005</v>
       </c>
       <c r="E179" t="n">
-        <v>1149.013047699587</v>
+        <v>1149.061503158</v>
       </c>
       <c r="F179" t="n">
         <v>12297</v>
@@ -23609,13 +23609,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1140.93786831121</v>
+        <v>1140.979766178038</v>
       </c>
       <c r="D180" t="n">
-        <v>1134.215253528253</v>
+        <v>1134.257112100653</v>
       </c>
       <c r="E180" t="n">
-        <v>1147.660483094167</v>
+        <v>1147.702420255422</v>
       </c>
       <c r="F180" t="n">
         <v>19174</v>
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1140.734789213335</v>
+        <v>1140.816598391101</v>
       </c>
       <c r="D181" t="n">
-        <v>1134.037245121006</v>
+        <v>1134.119369940287</v>
       </c>
       <c r="E181" t="n">
-        <v>1147.432333305663</v>
+        <v>1147.513826841916</v>
       </c>
       <c r="F181" t="n">
         <v>19367</v>
@@ -23907,13 +23907,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1138.468411156699</v>
+        <v>1138.558077544467</v>
       </c>
       <c r="D182" t="n">
-        <v>1127.527979299865</v>
+        <v>1127.61812589466</v>
       </c>
       <c r="E182" t="n">
-        <v>1149.408843013533</v>
+        <v>1149.498029194273</v>
       </c>
       <c r="F182" t="n">
         <v>4964</v>
@@ -24058,13 +24058,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1137.001606492468</v>
+        <v>1137.170019303445</v>
       </c>
       <c r="D183" t="n">
-        <v>1127.515787202381</v>
+        <v>1127.684773453704</v>
       </c>
       <c r="E183" t="n">
-        <v>1146.487425782555</v>
+        <v>1146.655265153186</v>
       </c>
       <c r="F183" t="n">
         <v>8925</v>
@@ -24209,13 +24209,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1136.191895137294</v>
+        <v>1136.253024744906</v>
       </c>
       <c r="D184" t="n">
-        <v>1127.304005381894</v>
+        <v>1127.36537247596</v>
       </c>
       <c r="E184" t="n">
-        <v>1145.079784892694</v>
+        <v>1145.140677013852</v>
       </c>
       <c r="F184" t="n">
         <v>7366</v>
@@ -24360,13 +24360,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1130.258994827305</v>
+        <v>1130.286844840628</v>
       </c>
       <c r="D185" t="n">
-        <v>1121.431251911733</v>
+        <v>1121.459384387191</v>
       </c>
       <c r="E185" t="n">
-        <v>1139.086737742876</v>
+        <v>1139.114305294065</v>
       </c>
       <c r="F185" t="n">
         <v>11118</v>
@@ -24507,13 +24507,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1129.068213282217</v>
+        <v>1129.149731157117</v>
       </c>
       <c r="D186" t="n">
-        <v>1121.645210720893</v>
+        <v>1121.726346980094</v>
       </c>
       <c r="E186" t="n">
-        <v>1136.49121584354</v>
+        <v>1136.573115334141</v>
       </c>
       <c r="F186" t="n">
         <v>20685</v>
@@ -24658,13 +24658,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1127.655794477108</v>
+        <v>1127.680367251134</v>
       </c>
       <c r="D187" t="n">
-        <v>1121.258047733051</v>
+        <v>1121.282219644839</v>
       </c>
       <c r="E187" t="n">
-        <v>1134.053541221166</v>
+        <v>1134.078514857428</v>
       </c>
       <c r="F187" t="n">
         <v>20118</v>
@@ -24809,13 +24809,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1126.793455930139</v>
+        <v>1126.848004396768</v>
       </c>
       <c r="D188" t="n">
-        <v>1114.700554081915</v>
+        <v>1114.756615736899</v>
       </c>
       <c r="E188" t="n">
-        <v>1138.886357778362</v>
+        <v>1138.939393056638</v>
       </c>
       <c r="F188" t="n">
         <v>2921</v>
@@ -24956,13 +24956,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1126.300854235903</v>
+        <v>1126.344903458351</v>
       </c>
       <c r="D189" t="n">
-        <v>1110.704651179966</v>
+        <v>1110.750912778263</v>
       </c>
       <c r="E189" t="n">
-        <v>1141.897057291841</v>
+        <v>1141.93889413844</v>
       </c>
       <c r="F189" t="n">
         <v>1785</v>
@@ -25103,13 +25103,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1120.794554205263</v>
+        <v>1120.87580856268</v>
       </c>
       <c r="D190" t="n">
-        <v>1109.819589773776</v>
+        <v>1109.901329859134</v>
       </c>
       <c r="E190" t="n">
-        <v>1131.769518636749</v>
+        <v>1131.850287266227</v>
       </c>
       <c r="F190" t="n">
         <v>5182</v>
@@ -25250,13 +25250,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1118.646713868492</v>
+        <v>1118.708831561563</v>
       </c>
       <c r="D191" t="n">
-        <v>1100.513320770509</v>
+        <v>1100.577232003377</v>
       </c>
       <c r="E191" t="n">
-        <v>1136.780106966476</v>
+        <v>1136.840431119749</v>
       </c>
       <c r="F191" t="n">
         <v>1143</v>
@@ -25401,13 +25401,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1115.775221762893</v>
+        <v>1115.998337617055</v>
       </c>
       <c r="D192" t="n">
-        <v>1108.047106008275</v>
+        <v>1108.270322924513</v>
       </c>
       <c r="E192" t="n">
-        <v>1123.50333751751</v>
+        <v>1123.726352309597</v>
       </c>
       <c r="F192" t="n">
         <v>10854</v>
@@ -25552,13 +25552,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1114.482247678418</v>
+        <v>1114.566540182833</v>
       </c>
       <c r="D193" t="n">
-        <v>1105.347039246652</v>
+        <v>1105.432580435133</v>
       </c>
       <c r="E193" t="n">
-        <v>1123.617456110184</v>
+        <v>1123.700499930533</v>
       </c>
       <c r="F193" t="n">
         <v>6923</v>
@@ -25699,13 +25699,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1114.048303226464</v>
+        <v>1114.116918325061</v>
       </c>
       <c r="D194" t="n">
-        <v>1099.678131263508</v>
+        <v>1099.747361305707</v>
       </c>
       <c r="E194" t="n">
-        <v>1128.418475189421</v>
+        <v>1128.486475344415</v>
       </c>
       <c r="F194" t="n">
         <v>2199</v>
@@ -25846,13 +25846,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1110.704135849345</v>
+        <v>1110.747500925504</v>
       </c>
       <c r="D195" t="n">
-        <v>1102.820941937488</v>
+        <v>1102.863245804244</v>
       </c>
       <c r="E195" t="n">
-        <v>1118.587329761202</v>
+        <v>1118.631756046765</v>
       </c>
       <c r="F195" t="n">
         <v>8045</v>
@@ -25997,13 +25997,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1109.498500316355</v>
+        <v>1109.586867576937</v>
       </c>
       <c r="D196" t="n">
-        <v>1100.218887534204</v>
+        <v>1100.307475873862</v>
       </c>
       <c r="E196" t="n">
-        <v>1118.778113098505</v>
+        <v>1118.866259280011</v>
       </c>
       <c r="F196" t="n">
         <v>8977</v>
@@ -26148,13 +26148,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1107.473088271924</v>
+        <v>1107.502834542719</v>
       </c>
       <c r="D197" t="n">
-        <v>1100.422507717155</v>
+        <v>1100.452233918486</v>
       </c>
       <c r="E197" t="n">
-        <v>1114.523668826694</v>
+        <v>1114.553435166953</v>
       </c>
       <c r="F197" t="n">
         <v>14148</v>
@@ -26299,13 +26299,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1092.804626968933</v>
+        <v>1092.990651746292</v>
       </c>
       <c r="D198" t="n">
-        <v>1081.323217897081</v>
+        <v>1081.509968180352</v>
       </c>
       <c r="E198" t="n">
-        <v>1104.286036040786</v>
+        <v>1104.471335312231</v>
       </c>
       <c r="F198" t="n">
         <v>4780</v>
@@ -26450,13 +26450,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1090.182649760682</v>
+        <v>1090.282463662942</v>
       </c>
       <c r="D199" t="n">
-        <v>1080.849911056072</v>
+        <v>1080.949883812057</v>
       </c>
       <c r="E199" t="n">
-        <v>1099.515388465291</v>
+        <v>1099.615043513826</v>
       </c>
       <c r="F199" t="n">
         <v>7597</v>
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1073.328707799044</v>
+        <v>1073.313890013196</v>
       </c>
       <c r="D200" t="n">
-        <v>1062.172901224802</v>
+        <v>1062.158880099823</v>
       </c>
       <c r="E200" t="n">
-        <v>1084.484514373285</v>
+        <v>1084.46889992657</v>
       </c>
       <c r="F200" t="n">
         <v>6328</v>
@@ -26752,13 +26752,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1070.153458788845</v>
+        <v>1070.228717981051</v>
       </c>
       <c r="D201" t="n">
-        <v>1060.282890347725</v>
+        <v>1060.360196927315</v>
       </c>
       <c r="E201" t="n">
-        <v>1080.024027229964</v>
+        <v>1080.097239034787</v>
       </c>
       <c r="F201" t="n">
         <v>6965</v>
@@ -26899,13 +26899,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1068.741191234582</v>
+        <v>1068.955124866701</v>
       </c>
       <c r="D202" t="n">
-        <v>1057.298415139809</v>
+        <v>1057.514341441038</v>
       </c>
       <c r="E202" t="n">
-        <v>1080.183967329356</v>
+        <v>1080.395908292365</v>
       </c>
       <c r="F202" t="n">
         <v>5745</v>
@@ -27046,13 +27046,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1066.549025172077</v>
+        <v>1066.699103441469</v>
       </c>
       <c r="D203" t="n">
-        <v>1051.352326051299</v>
+        <v>1051.504564046378</v>
       </c>
       <c r="E203" t="n">
-        <v>1081.745724292854</v>
+        <v>1081.89364283656</v>
       </c>
       <c r="F203" t="n">
         <v>1743</v>
@@ -27193,13 +27193,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1062.327705126304</v>
+        <v>1062.471570496746</v>
       </c>
       <c r="D204" t="n">
-        <v>1050.369698749569</v>
+        <v>1050.515149839461</v>
       </c>
       <c r="E204" t="n">
-        <v>1074.285711503039</v>
+        <v>1074.427991154031</v>
       </c>
       <c r="F204" t="n">
         <v>3924</v>
@@ -27340,13 +27340,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1055.747204968532</v>
+        <v>1055.821345144438</v>
       </c>
       <c r="D205" t="n">
-        <v>1044.09174955426</v>
+        <v>1044.166495809317</v>
       </c>
       <c r="E205" t="n">
-        <v>1067.402660382803</v>
+        <v>1067.476194479559</v>
       </c>
       <c r="F205" t="n">
         <v>4658</v>
@@ -27487,13 +27487,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1041.410051827617</v>
+        <v>1041.517800726481</v>
       </c>
       <c r="D206" t="n">
-        <v>1030.037378102242</v>
+        <v>1030.147119504652</v>
       </c>
       <c r="E206" t="n">
-        <v>1052.782725552992</v>
+        <v>1052.88848194831</v>
       </c>
       <c r="F206" t="n">
         <v>4845</v>
@@ -27634,13 +27634,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1023.934392236995</v>
+        <v>1024.015360050061</v>
       </c>
       <c r="D207" t="n">
-        <v>1010.357525237471</v>
+        <v>1010.439855240852</v>
       </c>
       <c r="E207" t="n">
-        <v>1037.511259236519</v>
+        <v>1037.59086485927</v>
       </c>
       <c r="F207" t="n">
         <v>2658</v>
@@ -27781,13 +27781,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1022.437027046425</v>
+        <v>1022.570792729038</v>
       </c>
       <c r="D208" t="n">
-        <v>1011.585415231319</v>
+        <v>1011.721145582726</v>
       </c>
       <c r="E208" t="n">
-        <v>1033.288638861532</v>
+        <v>1033.42043987535</v>
       </c>
       <c r="F208" t="n">
         <v>6310</v>
@@ -27928,13 +27928,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>995.1121034784384</v>
+        <v>995.1720085238692</v>
       </c>
       <c r="D209" t="n">
-        <v>982.5650076337224</v>
+        <v>982.6267116441543</v>
       </c>
       <c r="E209" t="n">
-        <v>1007.659199323154</v>
+        <v>1007.717305403584</v>
       </c>
       <c r="F209" t="n">
         <v>4914</v>
@@ -28075,13 +28075,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>991.6038659022939</v>
+        <v>991.7255588020982</v>
       </c>
       <c r="D210" t="n">
-        <v>979.2519465762011</v>
+        <v>979.3758762200318</v>
       </c>
       <c r="E210" t="n">
-        <v>1003.955785228387</v>
+        <v>1004.075241384165</v>
       </c>
       <c r="F210" t="n">
         <v>4203</v>
@@ -28222,13 +28222,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>981.1110515483655</v>
+        <v>981.3015755415313</v>
       </c>
       <c r="D211" t="n">
-        <v>967.6075305328385</v>
+        <v>967.8007826134151</v>
       </c>
       <c r="E211" t="n">
-        <v>994.6145725638925</v>
+        <v>994.8023684696475</v>
       </c>
       <c r="F211" t="n">
         <v>3412</v>
@@ -28369,13 +28369,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>973.6801874959309</v>
+        <v>973.9081986981028</v>
       </c>
       <c r="D212" t="n">
-        <v>957.9171948357775</v>
+        <v>958.1490842147259</v>
       </c>
       <c r="E212" t="n">
-        <v>989.4431801560843</v>
+        <v>989.6673131814798</v>
       </c>
       <c r="F212" t="n">
         <v>2391</v>
@@ -28520,13 +28520,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>952.3995792220386</v>
+        <v>952.4811130028054</v>
       </c>
       <c r="D213" t="n">
-        <v>939.6982248623589</v>
+        <v>939.7829905879871</v>
       </c>
       <c r="E213" t="n">
-        <v>965.1009335817183</v>
+        <v>965.1792354176237</v>
       </c>
       <c r="F213" t="n">
         <v>3287</v>
@@ -29386,7 +29386,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -29543,14 +29543,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hy3</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>1600</v>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -29566,14 +29566,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1600</v>
+        <v>744</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -29589,14 +29589,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>hy3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>744</v>
+        <v>299</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-thinking</t>
+          <t>deepseek-v4-pro-high-preview</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -29696,23 +29696,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inkling</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>975</v>
-      </c>
-      <c r="C14" t="n">
-        <v>41</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>glm-4.7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29742,15 +29734,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>inkling</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>975</v>
+      </c>
+      <c r="C16" t="n">
+        <v>41</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -29780,7 +29780,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash-thinking</t>
+          <t>deepseek-v4-flash-high-preview</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -29917,7 +29917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>glm-4.6</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -29932,7 +29932,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>glm-4.6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -29985,7 +29985,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp</t>
+          <t>deepseek-v3.2-thinking</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -30000,7 +30000,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-thinking</t>
+          <t>deepseek-v3.2-exp</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -30076,7 +30076,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -30091,7 +30091,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -30106,30 +30106,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>122</v>
-      </c>
-      <c r="C36" t="n">
-        <v>10</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v3.1-thinking</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -30144,29 +30136,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>122</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-instruct</t>
+          <t>mistral-large-3</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>235</v>
+        <v>675</v>
       </c>
       <c r="C39" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -30175,21 +30175,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mistral-large-3</t>
+          <t>qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>675</v>
+        <v>235</v>
       </c>
       <c r="C40" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -30396,14 +30396,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>deepseek-v3-0324</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>235</v>
+        <v>671</v>
       </c>
       <c r="C50" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -30412,21 +30412,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>deepseek-v3-0324</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>671</v>
+        <v>35</v>
       </c>
       <c r="C51" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -30435,21 +30435,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -31532,14 +31532,14 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mistral-small-3.1-24b-instruct-2503</t>
+          <t>gemma-3-4b-it</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -31555,14 +31555,14 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>gemma-3-4b-it</t>
+          <t>mistral-small-3.1-24b-instruct-2503</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -33055,14 +33055,14 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>mistral-7b-instruct-v0.2</t>
+          <t>wizardlm-13b</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C175" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -33078,14 +33078,14 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>wizardlm-13b</t>
+          <t>mistral-7b-instruct-v0.2</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C176" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI214"/>
+  <dimension ref="A1:AI213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -28657,157 +28657,6 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>213</v>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>inkling-small</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>1430.54086860102</v>
-      </c>
-      <c r="D214" t="n">
-        <v>1419.392361439659</v>
-      </c>
-      <c r="E214" t="n">
-        <v>1441.689375762382</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Thinky</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I214" t="n">
-        <v>266</v>
-      </c>
-      <c r="J214" t="n">
-        <v>12</v>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M214" t="n">
-        <v>532</v>
-      </c>
-      <c r="N214" t="n">
-        <v>665</v>
-      </c>
-      <c r="O214" t="n">
-        <v>266</v>
-      </c>
-      <c r="P214" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="Q214" t="n">
-        <v>133</v>
-      </c>
-      <c r="R214" t="n">
-        <v>166.2</v>
-      </c>
-      <c r="S214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD214" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF214" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG214" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>MULTI-GPU</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>MULTI-GPU</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29420,7 +29269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:E213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -33949,29 +33798,6 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>inkling-small</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>266</v>
-      </c>
-      <c r="C214" t="n">
-        <v>12</v>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1485.345656375652</v>
+        <v>1485.377522527264</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1475.317183428952</v>
+        <v>1478.766674703977</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1495.374129322353</v>
+        <v>1491.988370350551</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3556</v>
+        <v>9861</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1469.493298376792</v>
+        <v>1470.962091290482</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1464.080072686523</v>
+        <v>1465.740706561287</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1474.906524067061</v>
+        <v>1476.183476019678</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>22252</v>
+        <v>24250</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1468.787796757301</v>
+        <v>1467.791094188054</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1464.407888455876</v>
+        <v>1463.508846885975</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1473.167705058726</v>
+        <v>1472.073341490133</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>34857</v>
+        <v>36716</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1465.707904313422</v>
+        <v>1467.036237456892</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1461.42818549503</v>
+        <v>1462.823672745802</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1469.987623131815</v>
+        <v>1471.248802167981</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45910</v>
+        <v>47805</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1460.668022792315</v>
+        <v>1460.678752423233</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1456.107550413663</v>
+        <v>1456.117940816292</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1465.228495170968</v>
+        <v>1465.239564030173</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>37313</v>
+        <v>37236</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1457.945178498991</v>
+        <v>1457.065732077355</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1453.741940225932</v>
+        <v>1452.943188038061</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1462.14841677205</v>
+        <v>1461.18827611665</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>49183</v>
+        <v>51266</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1456.713228047888</v>
+        <v>1456.714915505148</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1452.35250992689</v>
+        <v>1452.354289194695</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1461.073946168886</v>
+        <v>1461.075541815601</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>27634</v>
+        <v>27591</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1408,148 +1408,68 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>hy3</t>
+          <t>deepseek-v4-pro-high-preview</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1456.272825863887</v>
+        <v>1455.503814443174</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1446.063564853376</v>
+        <v>1451.321939385599</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1466.482086874399</v>
+        <v>1459.685689500748</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3353</v>
+        <v>48756</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Tencent</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>299</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>598</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>747.5</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>299</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>373.8</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>186.9</v>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG9" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -1559,68 +1479,148 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-high-preview</t>
+          <t>hy3</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1454.281052047281</v>
+        <v>1453.024951260133</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1450.018423466766</v>
+        <v>1443.50771455588</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1458.543680627796</v>
+        <v>1462.542187964386</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46859</v>
+        <v>3941</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Tencent</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="2" t="inlineStr"/>
-      <c r="V10" s="2" t="inlineStr"/>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="inlineStr"/>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr"/>
-      <c r="AD10" s="2" t="inlineStr"/>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>598</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>373.8</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1450.923320417939</v>
+        <v>1450.936442746539</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1443.30225373473</v>
+        <v>1443.316714936892</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1458.544387101148</v>
+        <v>1458.556170556186</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5844</v>
+        <v>5839</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1785,16 +1785,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1450.211973033779</v>
+        <v>1450.652525515051</v>
       </c>
       <c r="D12" t="n">
-        <v>1446.743138368035</v>
+        <v>1447.226184953219</v>
       </c>
       <c r="E12" t="n">
-        <v>1453.680807699522</v>
+        <v>1454.078866076883</v>
       </c>
       <c r="F12" t="n">
-        <v>66269</v>
+        <v>68179</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1445.273158346901</v>
+        <v>1444.667445276487</v>
       </c>
       <c r="D13" t="n">
-        <v>1440.284347753107</v>
+        <v>1439.847014214772</v>
       </c>
       <c r="E13" t="n">
-        <v>1450.261968940694</v>
+        <v>1449.487876338202</v>
       </c>
       <c r="F13" t="n">
-        <v>32086</v>
+        <v>34343</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2083,68 +2083,148 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
+          <t>qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1442.052301956197</v>
+        <v>1442.161789472189</v>
       </c>
       <c r="D14" t="n">
-        <v>1435.960229614961</v>
+        <v>1438.595885706468</v>
       </c>
       <c r="E14" t="n">
-        <v>1448.144374297434</v>
+        <v>1445.72769323791</v>
       </c>
       <c r="F14" t="n">
-        <v>12090</v>
+        <v>63719</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>397</v>
+      </c>
+      <c r="J14" t="n">
+        <v>17</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>794</v>
+      </c>
+      <c r="N14" t="n">
+        <v>992.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>397</v>
+      </c>
+      <c r="P14" t="n">
+        <v>496.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF14" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -2154,148 +2234,68 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
+          <t>glm-4.7</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1441.680796935525</v>
+        <v>1441.79514255132</v>
       </c>
       <c r="D15" t="n">
-        <v>1438.071228321843</v>
+        <v>1435.703421053587</v>
       </c>
       <c r="E15" t="n">
-        <v>1445.290365549207</v>
+        <v>1447.886864049053</v>
       </c>
       <c r="F15" t="n">
-        <v>61760</v>
+        <v>12077</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>397</v>
-      </c>
-      <c r="J15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>794</v>
-      </c>
-      <c r="N15" t="n">
-        <v>992.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>397</v>
-      </c>
-      <c r="P15" t="n">
-        <v>496.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>248.1</v>
-      </c>
-      <c r="S15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF15" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG15" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1440.801681902524</v>
+        <v>1441.527839083271</v>
       </c>
       <c r="D16" t="n">
-        <v>1434.302480973471</v>
+        <v>1435.428070102887</v>
       </c>
       <c r="E16" t="n">
-        <v>1447.300882831577</v>
+        <v>1447.627608063657</v>
       </c>
       <c r="F16" t="n">
-        <v>9873</v>
+        <v>12086</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1438.496521967581</v>
+        <v>1438.235296738034</v>
       </c>
       <c r="D17" t="n">
-        <v>1430.832869107004</v>
+        <v>1430.570981878278</v>
       </c>
       <c r="E17" t="n">
-        <v>1446.160174828158</v>
+        <v>1445.899611597791</v>
       </c>
       <c r="F17" t="n">
-        <v>5757</v>
+        <v>5755</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1438.011486942368</v>
+        <v>1437.717360214792</v>
       </c>
       <c r="D18" t="n">
-        <v>1433.775584468884</v>
+        <v>1433.479325825433</v>
       </c>
       <c r="E18" t="n">
-        <v>1442.247389415852</v>
+        <v>1441.955394604151</v>
       </c>
       <c r="F18" t="n">
-        <v>48387</v>
+        <v>48316</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1435.636196971366</v>
+        <v>1435.785156266306</v>
       </c>
       <c r="D19" t="n">
-        <v>1431.46585408494</v>
+        <v>1431.613864736831</v>
       </c>
       <c r="E19" t="n">
-        <v>1439.806539857792</v>
+        <v>1439.956447795781</v>
       </c>
       <c r="F19" t="n">
-        <v>48667</v>
+        <v>48561</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2833,16 +2833,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1433.738517188744</v>
+        <v>1434.001827808326</v>
       </c>
       <c r="D20" t="n">
-        <v>1429.370068262624</v>
+        <v>1429.632309596683</v>
       </c>
       <c r="E20" t="n">
-        <v>1438.106966114865</v>
+        <v>1438.371346019968</v>
       </c>
       <c r="F20" t="n">
-        <v>44251</v>
+        <v>44200</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1431.593767459532</v>
+        <v>1431.272072455097</v>
       </c>
       <c r="D21" t="n">
-        <v>1425.001153762007</v>
+        <v>1424.676136014599</v>
       </c>
       <c r="E21" t="n">
-        <v>1438.186381157057</v>
+        <v>1437.868008895594</v>
       </c>
       <c r="F21" t="n">
-        <v>8150</v>
+        <v>8138</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1429.694039826392</v>
+        <v>1429.6830658247</v>
       </c>
       <c r="D22" t="n">
-        <v>1426.541450958268</v>
+        <v>1426.532360194698</v>
       </c>
       <c r="E22" t="n">
-        <v>1432.846628694515</v>
+        <v>1432.833771454702</v>
       </c>
       <c r="F22" t="n">
-        <v>61710</v>
+        <v>61677</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3206,16 +3206,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1427.291567352059</v>
+        <v>1427.181317553498</v>
       </c>
       <c r="D23" t="n">
-        <v>1420.680818932369</v>
+        <v>1420.562225622656</v>
       </c>
       <c r="E23" t="n">
-        <v>1433.902315771749</v>
+        <v>1433.80040948434</v>
       </c>
       <c r="F23" t="n">
-        <v>10907</v>
+        <v>10887</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1426.423051300756</v>
+        <v>1426.017483719051</v>
       </c>
       <c r="D24" t="n">
-        <v>1419.354476422673</v>
+        <v>1418.950513735908</v>
       </c>
       <c r="E24" t="n">
-        <v>1433.491626178839</v>
+        <v>1433.084453702194</v>
       </c>
       <c r="F24" t="n">
-        <v>10588</v>
+        <v>10564</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1425.041882669078</v>
+        <v>1425.045998137786</v>
       </c>
       <c r="D25" t="n">
-        <v>1421.48712013347</v>
+        <v>1421.492798290604</v>
       </c>
       <c r="E25" t="n">
-        <v>1428.596645204686</v>
+        <v>1428.599197984968</v>
       </c>
       <c r="F25" t="n">
-        <v>47008</v>
+        <v>46999</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3499,16 +3499,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1425.024665685231</v>
+        <v>1424.966824305186</v>
       </c>
       <c r="D26" t="n">
-        <v>1421.107837436972</v>
+        <v>1421.051392817139</v>
       </c>
       <c r="E26" t="n">
-        <v>1428.941493933489</v>
+        <v>1428.882255793233</v>
       </c>
       <c r="F26" t="n">
-        <v>35594</v>
+        <v>35589</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3570,16 +3570,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1424.763750561533</v>
+        <v>1424.873232754823</v>
       </c>
       <c r="D27" t="n">
-        <v>1418.208905550342</v>
+        <v>1418.318772879777</v>
       </c>
       <c r="E27" t="n">
-        <v>1431.318595572723</v>
+        <v>1431.427692629869</v>
       </c>
       <c r="F27" t="n">
-        <v>9061</v>
+        <v>9051</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1422.949296038458</v>
+        <v>1422.859703868179</v>
       </c>
       <c r="D28" t="n">
-        <v>1420.359073409983</v>
+        <v>1420.271151654624</v>
       </c>
       <c r="E28" t="n">
-        <v>1425.539518666933</v>
+        <v>1425.448256081735</v>
       </c>
       <c r="F28" t="n">
-        <v>96758</v>
+        <v>96721</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3792,16 +3792,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1422.796958501995</v>
+        <v>1422.701207372426</v>
       </c>
       <c r="D29" t="n">
-        <v>1419.148252865555</v>
+        <v>1419.054767145682</v>
       </c>
       <c r="E29" t="n">
-        <v>1426.445664138435</v>
+        <v>1426.347647599171</v>
       </c>
       <c r="F29" t="n">
-        <v>40836</v>
+        <v>40832</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3863,16 +3863,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1422.627503880607</v>
+        <v>1422.515727151379</v>
       </c>
       <c r="D30" t="n">
-        <v>1416.223106665238</v>
+        <v>1416.111557273904</v>
       </c>
       <c r="E30" t="n">
-        <v>1429.031901095975</v>
+        <v>1428.919897028855</v>
       </c>
       <c r="F30" t="n">
-        <v>11909</v>
+        <v>11902</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3934,16 +3934,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1422.111566518278</v>
+        <v>1422.066395590956</v>
       </c>
       <c r="D31" t="n">
-        <v>1416.446962366653</v>
+        <v>1416.401941495682</v>
       </c>
       <c r="E31" t="n">
-        <v>1427.776170669903</v>
+        <v>1427.730849686231</v>
       </c>
       <c r="F31" t="n">
-        <v>18424</v>
+        <v>18422</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4005,16 +4005,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1418.122613758727</v>
+        <v>1418.079528292461</v>
       </c>
       <c r="D32" t="n">
-        <v>1411.624340539137</v>
+        <v>1411.580736305735</v>
       </c>
       <c r="E32" t="n">
-        <v>1424.620886978317</v>
+        <v>1424.578320279187</v>
       </c>
       <c r="F32" t="n">
-        <v>11764</v>
+        <v>11756</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1417.74080340313</v>
+        <v>1417.656592481575</v>
       </c>
       <c r="D33" t="n">
-        <v>1412.8776036958</v>
+        <v>1412.792474658414</v>
       </c>
       <c r="E33" t="n">
-        <v>1422.60400311046</v>
+        <v>1422.520710304736</v>
       </c>
       <c r="F33" t="n">
-        <v>27592</v>
+        <v>27589</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4307,16 +4307,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1417.383117900609</v>
+        <v>1417.551037813057</v>
       </c>
       <c r="D34" t="n">
-        <v>1411.372569988163</v>
+        <v>1411.541234942481</v>
       </c>
       <c r="E34" t="n">
-        <v>1423.393665813055</v>
+        <v>1423.560840683633</v>
       </c>
       <c r="F34" t="n">
-        <v>14948</v>
+        <v>14942</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4378,13 +4378,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1417.223291577337</v>
+        <v>1417.258847001883</v>
       </c>
       <c r="D35" t="n">
-        <v>1407.236255185038</v>
+        <v>1407.27300036846</v>
       </c>
       <c r="E35" t="n">
-        <v>1427.210327969637</v>
+        <v>1427.244693635306</v>
       </c>
       <c r="F35" t="n">
         <v>3454</v>
@@ -4445,68 +4445,148 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
+          <t>qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1416.973371263583</v>
+        <v>1416.936775856845</v>
       </c>
       <c r="D36" t="n">
-        <v>1410.359201722701</v>
+        <v>1412.537135515936</v>
       </c>
       <c r="E36" t="n">
-        <v>1423.587540804465</v>
+        <v>1421.336416197753</v>
       </c>
       <c r="F36" t="n">
-        <v>11721</v>
+        <v>28208</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>122</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>244</v>
+      </c>
+      <c r="N36" t="n">
+        <v>305</v>
+      </c>
+      <c r="O36" t="n">
+        <v>122</v>
+      </c>
+      <c r="P36" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>61</v>
+      </c>
+      <c r="R36" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="S36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG36" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -4516,29 +4596,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1416.881453199402</v>
+        <v>1416.869526832639</v>
       </c>
       <c r="D37" t="n">
-        <v>1412.857400298902</v>
+        <v>1410.256886685721</v>
       </c>
       <c r="E37" t="n">
-        <v>1420.905506099902</v>
+        <v>1423.482166979557</v>
       </c>
       <c r="F37" t="n">
-        <v>53523</v>
+        <v>11715</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4587,148 +4667,68 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
+          <t>minimax-m2.7</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1416.869922123495</v>
+        <v>1415.984907846438</v>
       </c>
       <c r="D38" t="n">
-        <v>1412.471115088277</v>
+        <v>1412.025290897402</v>
       </c>
       <c r="E38" t="n">
-        <v>1421.268729158713</v>
+        <v>1419.944524795474</v>
       </c>
       <c r="F38" t="n">
-        <v>28222</v>
+        <v>55513</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>122</v>
-      </c>
-      <c r="J38" t="n">
-        <v>10</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>244</v>
-      </c>
-      <c r="N38" t="n">
-        <v>305</v>
-      </c>
-      <c r="O38" t="n">
-        <v>122</v>
-      </c>
-      <c r="P38" t="n">
-        <v>152.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>61</v>
-      </c>
-      <c r="R38" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="S38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE38" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG38" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -4742,16 +4742,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1415.454857777998</v>
+        <v>1415.289085687362</v>
       </c>
       <c r="D39" t="n">
-        <v>1412.17381739107</v>
+        <v>1412.06247676162</v>
       </c>
       <c r="E39" t="n">
-        <v>1418.735898164926</v>
+        <v>1418.515694613105</v>
       </c>
       <c r="F39" t="n">
-        <v>54560</v>
+        <v>56503</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1415.125446061452</v>
+        <v>1415.215021805383</v>
       </c>
       <c r="D40" t="n">
-        <v>1408.637969447286</v>
+        <v>1408.729022130754</v>
       </c>
       <c r="E40" t="n">
-        <v>1421.612922675617</v>
+        <v>1421.701021480012</v>
       </c>
       <c r="F40" t="n">
-        <v>11490</v>
+        <v>11483</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5044,16 +5044,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1415.073824442247</v>
+        <v>1415.006306186865</v>
       </c>
       <c r="D41" t="n">
-        <v>1405.45069777358</v>
+        <v>1405.381256500062</v>
       </c>
       <c r="E41" t="n">
-        <v>1424.696951110915</v>
+        <v>1424.631355873669</v>
       </c>
       <c r="F41" t="n">
-        <v>3691</v>
+        <v>3688</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1412.190375312006</v>
+        <v>1411.907571490907</v>
       </c>
       <c r="D42" t="n">
-        <v>1404.606698859538</v>
+        <v>1404.32269911738</v>
       </c>
       <c r="E42" t="n">
-        <v>1419.774051764474</v>
+        <v>1419.492443864434</v>
       </c>
       <c r="F42" t="n">
-        <v>6557</v>
+        <v>6555</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5186,16 +5186,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1410.714080894664</v>
+        <v>1410.79367599156</v>
       </c>
       <c r="D43" t="n">
-        <v>1405.829374526509</v>
+        <v>1405.908294933934</v>
       </c>
       <c r="E43" t="n">
-        <v>1415.598787262819</v>
+        <v>1415.679057049185</v>
       </c>
       <c r="F43" t="n">
-        <v>24280</v>
+        <v>24269</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5337,16 +5337,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1408.039676412298</v>
+        <v>1407.931936471984</v>
       </c>
       <c r="D44" t="n">
-        <v>1403.609632313661</v>
+        <v>1403.502540006912</v>
       </c>
       <c r="E44" t="n">
-        <v>1412.469720510936</v>
+        <v>1412.361332937056</v>
       </c>
       <c r="F44" t="n">
-        <v>27077</v>
+        <v>27052</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5488,16 +5488,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1402.9095168766</v>
+        <v>1402.884349905579</v>
       </c>
       <c r="D45" t="n">
-        <v>1398.403024184455</v>
+        <v>1398.379320248687</v>
       </c>
       <c r="E45" t="n">
-        <v>1407.416009568744</v>
+        <v>1407.389379562471</v>
       </c>
       <c r="F45" t="n">
-        <v>38139</v>
+        <v>38137</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5639,16 +5639,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1401.207457057285</v>
+        <v>1401.109161953541</v>
       </c>
       <c r="D46" t="n">
-        <v>1396.432721028453</v>
+        <v>1396.334669164683</v>
       </c>
       <c r="E46" t="n">
-        <v>1405.982193086116</v>
+        <v>1405.8836547424</v>
       </c>
       <c r="F46" t="n">
-        <v>22853</v>
+        <v>22846</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1400.896411255554</v>
+        <v>1400.79406557966</v>
       </c>
       <c r="D47" t="n">
-        <v>1394.528686374463</v>
+        <v>1394.427047107624</v>
       </c>
       <c r="E47" t="n">
-        <v>1407.264136136644</v>
+        <v>1407.161084051696</v>
       </c>
       <c r="F47" t="n">
-        <v>11386</v>
+        <v>11379</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5941,16 +5941,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1398.919053741436</v>
+        <v>1398.894107291662</v>
       </c>
       <c r="D48" t="n">
-        <v>1392.383333255096</v>
+        <v>1392.357514024557</v>
       </c>
       <c r="E48" t="n">
-        <v>1405.454774227776</v>
+        <v>1405.430700558767</v>
       </c>
       <c r="F48" t="n">
-        <v>8980</v>
+        <v>8975</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6092,13 +6092,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1398.206123368104</v>
+        <v>1398.227107850234</v>
       </c>
       <c r="D49" t="n">
-        <v>1393.322227504733</v>
+        <v>1393.342889165214</v>
       </c>
       <c r="E49" t="n">
-        <v>1403.090019231475</v>
+        <v>1403.111326535255</v>
       </c>
       <c r="F49" t="n">
         <v>18524</v>
@@ -6243,16 +6243,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1395.531474789006</v>
+        <v>1395.632024753726</v>
       </c>
       <c r="D50" t="n">
-        <v>1391.653420675779</v>
+        <v>1391.753749688411</v>
       </c>
       <c r="E50" t="n">
-        <v>1399.409528902233</v>
+        <v>1399.510299819041</v>
       </c>
       <c r="F50" t="n">
-        <v>45446</v>
+        <v>45445</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6390,20 +6390,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1395.494718344569</v>
+        <v>1395.414913272661</v>
       </c>
       <c r="D51" t="n">
-        <v>1391.147084041895</v>
+        <v>1388.624316820163</v>
       </c>
       <c r="E51" t="n">
-        <v>1399.842352647244</v>
+        <v>1402.20550972516</v>
       </c>
       <c r="F51" t="n">
-        <v>28884</v>
+        <v>7934</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6432,36 +6432,36 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="N51" t="n">
-        <v>87.5</v>
+        <v>587.5</v>
       </c>
       <c r="O51" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="P51" t="n">
-        <v>43.8</v>
+        <v>293.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>17.5</v>
+        <v>117.5</v>
       </c>
       <c r="R51" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="S51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>146.9</v>
+      </c>
+      <c r="S51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V51" s="5" t="inlineStr">
@@ -6469,39 +6469,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD51" s="6" t="inlineStr">
@@ -6509,14 +6509,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF51" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF51" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG51" s="6" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -6541,20 +6541,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1395.34124332144</v>
+        <v>1395.348416229161</v>
       </c>
       <c r="D52" t="n">
-        <v>1388.550715078914</v>
+        <v>1391.002145587559</v>
       </c>
       <c r="E52" t="n">
-        <v>1402.131771563966</v>
+        <v>1399.694686870763</v>
       </c>
       <c r="F52" t="n">
-        <v>7937</v>
+        <v>28864</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6567,10 +6567,10 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="J52" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6583,36 +6583,36 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>470</v>
+        <v>70</v>
       </c>
       <c r="N52" t="n">
-        <v>587.5</v>
+        <v>87.5</v>
       </c>
       <c r="O52" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="P52" t="n">
-        <v>293.8</v>
+        <v>43.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>117.5</v>
+        <v>17.5</v>
       </c>
       <c r="R52" t="n">
-        <v>146.9</v>
-      </c>
-      <c r="S52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>21.9</v>
+      </c>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="V52" s="5" t="inlineStr">
@@ -6620,39 +6620,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="W52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD52" s="6" t="inlineStr">
@@ -6660,14 +6660,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF52" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG52" s="6" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -6696,16 +6696,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1394.607539408807</v>
+        <v>1394.28710212318</v>
       </c>
       <c r="D53" t="n">
-        <v>1390.944315176111</v>
+        <v>1390.625668091438</v>
       </c>
       <c r="E53" t="n">
-        <v>1398.270763641502</v>
+        <v>1397.948536154922</v>
       </c>
       <c r="F53" t="n">
-        <v>57020</v>
+        <v>56979</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6767,16 +6767,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1392.562103415771</v>
+        <v>1392.531488449084</v>
       </c>
       <c r="D54" t="n">
-        <v>1388.994648434019</v>
+        <v>1388.966609338905</v>
       </c>
       <c r="E54" t="n">
-        <v>1396.129558397523</v>
+        <v>1396.096367559263</v>
       </c>
       <c r="F54" t="n">
-        <v>46264</v>
+        <v>46248</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6838,16 +6838,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1389.928712402181</v>
+        <v>1389.877903153386</v>
       </c>
       <c r="D55" t="n">
-        <v>1385.925164571151</v>
+        <v>1385.874678090451</v>
       </c>
       <c r="E55" t="n">
-        <v>1393.932260233212</v>
+        <v>1393.881128216321</v>
       </c>
       <c r="F55" t="n">
-        <v>40751</v>
+        <v>40688</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1387.71034387502</v>
+        <v>1387.679003601059</v>
       </c>
       <c r="D56" t="n">
-        <v>1382.758754671713</v>
+        <v>1382.728632509004</v>
       </c>
       <c r="E56" t="n">
-        <v>1392.661933078329</v>
+        <v>1392.629374693114</v>
       </c>
       <c r="F56" t="n">
-        <v>25689</v>
+        <v>25674</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7060,16 +7060,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1387.005677093801</v>
+        <v>1386.960265868219</v>
       </c>
       <c r="D57" t="n">
-        <v>1380.757375096932</v>
+        <v>1380.710601952581</v>
       </c>
       <c r="E57" t="n">
-        <v>1393.253979090669</v>
+        <v>1393.209929783857</v>
       </c>
       <c r="F57" t="n">
-        <v>10919</v>
+        <v>10909</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7131,16 +7131,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1384.122634176615</v>
+        <v>1384.165924343735</v>
       </c>
       <c r="D58" t="n">
-        <v>1378.893166785581</v>
+        <v>1378.936968529053</v>
       </c>
       <c r="E58" t="n">
-        <v>1389.352101567649</v>
+        <v>1389.394880158417</v>
       </c>
       <c r="F58" t="n">
-        <v>17059</v>
+        <v>17057</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7202,16 +7202,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1383.098681285096</v>
+        <v>1383.050891228715</v>
       </c>
       <c r="D59" t="n">
-        <v>1378.216212100964</v>
+        <v>1378.168690880779</v>
       </c>
       <c r="E59" t="n">
-        <v>1387.981150469227</v>
+        <v>1387.93309157665</v>
       </c>
       <c r="F59" t="n">
-        <v>23705</v>
+        <v>23691</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1378.531349092249</v>
+        <v>1378.554193362657</v>
       </c>
       <c r="D60" t="n">
-        <v>1374.159990623141</v>
+        <v>1374.183714391111</v>
       </c>
       <c r="E60" t="n">
-        <v>1382.902707561358</v>
+        <v>1382.924672334203</v>
       </c>
       <c r="F60" t="n">
-        <v>29678</v>
+        <v>29651</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
@@ -7500,13 +7500,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1377.233302776744</v>
+        <v>1377.340683229159</v>
       </c>
       <c r="D61" t="n">
-        <v>1365.974395559374</v>
+        <v>1366.083697189853</v>
       </c>
       <c r="E61" t="n">
-        <v>1388.492209994114</v>
+        <v>1388.597669268464</v>
       </c>
       <c r="F61" t="n">
         <v>2797</v>
@@ -7571,16 +7571,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1374.86126220844</v>
+        <v>1374.780044191727</v>
       </c>
       <c r="D62" t="n">
-        <v>1370.164125078223</v>
+        <v>1370.083138687447</v>
       </c>
       <c r="E62" t="n">
-        <v>1379.558399338657</v>
+        <v>1379.476949696008</v>
       </c>
       <c r="F62" t="n">
-        <v>26238</v>
+        <v>26241</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7722,16 +7722,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1372.746788664577</v>
+        <v>1372.717280659492</v>
       </c>
       <c r="D63" t="n">
-        <v>1368.500964664134</v>
+        <v>1368.471822958773</v>
       </c>
       <c r="E63" t="n">
-        <v>1376.99261266502</v>
+        <v>1376.962738360211</v>
       </c>
       <c r="F63" t="n">
-        <v>31054</v>
+        <v>31040</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7793,16 +7793,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1369.324589680222</v>
+        <v>1369.113879311151</v>
       </c>
       <c r="D64" t="n">
-        <v>1363.482220805888</v>
+        <v>1363.270561274409</v>
       </c>
       <c r="E64" t="n">
-        <v>1375.166958554556</v>
+        <v>1374.957197347893</v>
       </c>
       <c r="F64" t="n">
-        <v>13667</v>
+        <v>13661</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7944,16 +7944,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1368.891999059175</v>
+        <v>1368.667195077082</v>
       </c>
       <c r="D65" t="n">
-        <v>1364.184139690836</v>
+        <v>1363.958506114793</v>
       </c>
       <c r="E65" t="n">
-        <v>1373.599858427514</v>
+        <v>1373.375884039372</v>
       </c>
       <c r="F65" t="n">
-        <v>28817</v>
+        <v>28771</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
@@ -8091,16 +8091,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1367.825962059829</v>
+        <v>1367.749722899547</v>
       </c>
       <c r="D66" t="n">
-        <v>1362.023061238375</v>
+        <v>1361.947228763604</v>
       </c>
       <c r="E66" t="n">
-        <v>1373.628862881282</v>
+        <v>1373.552217035489</v>
       </c>
       <c r="F66" t="n">
-        <v>11679</v>
+        <v>11678</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -8162,16 +8162,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1365.904694579216</v>
+        <v>1365.831837326881</v>
       </c>
       <c r="D67" t="n">
-        <v>1362.225948536436</v>
+        <v>1362.152508306438</v>
       </c>
       <c r="E67" t="n">
-        <v>1369.583440621995</v>
+        <v>1369.511166347325</v>
       </c>
       <c r="F67" t="n">
-        <v>47468</v>
+        <v>47453</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8313,16 +8313,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1363.7724666685</v>
+        <v>1363.81670914292</v>
       </c>
       <c r="D68" t="n">
-        <v>1359.496794842024</v>
+        <v>1359.540137129859</v>
       </c>
       <c r="E68" t="n">
-        <v>1368.048138494976</v>
+        <v>1368.09328115598</v>
       </c>
       <c r="F68" t="n">
-        <v>35142</v>
+        <v>35117</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8384,16 +8384,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1360.847325108952</v>
+        <v>1360.838434251668</v>
       </c>
       <c r="D69" t="n">
-        <v>1353.568306690125</v>
+        <v>1353.559710130692</v>
       </c>
       <c r="E69" t="n">
-        <v>1368.126343527779</v>
+        <v>1368.117158372645</v>
       </c>
       <c r="F69" t="n">
-        <v>7490</v>
+        <v>7484</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8535,13 +8535,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1358.543744673714</v>
+        <v>1358.561181792063</v>
       </c>
       <c r="D70" t="n">
-        <v>1353.796034091787</v>
+        <v>1353.813226986431</v>
       </c>
       <c r="E70" t="n">
-        <v>1363.291455255642</v>
+        <v>1363.309136597695</v>
       </c>
       <c r="F70" t="n">
         <v>21770</v>
@@ -8686,16 +8686,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1357.436339158313</v>
+        <v>1357.556814860938</v>
       </c>
       <c r="D71" t="n">
-        <v>1352.232905034325</v>
+        <v>1352.352878252538</v>
       </c>
       <c r="E71" t="n">
-        <v>1362.639773282302</v>
+        <v>1362.760751469337</v>
       </c>
       <c r="F71" t="n">
-        <v>17690</v>
+        <v>17685</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8757,16 +8757,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1356.204596870842</v>
+        <v>1356.17461058088</v>
       </c>
       <c r="D72" t="n">
-        <v>1347.859031368456</v>
+        <v>1347.831317894486</v>
       </c>
       <c r="E72" t="n">
-        <v>1364.550162373227</v>
+        <v>1364.517903267274</v>
       </c>
       <c r="F72" t="n">
-        <v>5326</v>
+        <v>5323</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
@@ -8904,16 +8904,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1354.010614611382</v>
+        <v>1353.924997128996</v>
       </c>
       <c r="D73" t="n">
-        <v>1350.557283888515</v>
+        <v>1350.471079367362</v>
       </c>
       <c r="E73" t="n">
-        <v>1357.46394533425</v>
+        <v>1357.378914890631</v>
       </c>
       <c r="F73" t="n">
-        <v>56195</v>
+        <v>56175</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8975,16 +8975,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1353.337182944429</v>
+        <v>1353.55917912144</v>
       </c>
       <c r="D74" t="n">
-        <v>1344.993994519852</v>
+        <v>1345.214328380881</v>
       </c>
       <c r="E74" t="n">
-        <v>1361.680371369005</v>
+        <v>1361.904029862</v>
       </c>
       <c r="F74" t="n">
-        <v>4957</v>
+        <v>4953</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9046,16 +9046,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1352.29334428352</v>
+        <v>1352.452193835237</v>
       </c>
       <c r="D75" t="n">
-        <v>1347.941331339142</v>
+        <v>1348.100491649308</v>
       </c>
       <c r="E75" t="n">
-        <v>1356.645357227898</v>
+        <v>1356.803896021166</v>
       </c>
       <c r="F75" t="n">
-        <v>30608</v>
+        <v>30594</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9197,13 +9197,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1348.257949584937</v>
+        <v>1348.573879063204</v>
       </c>
       <c r="D76" t="n">
-        <v>1340.852807696821</v>
+        <v>1341.170333782281</v>
       </c>
       <c r="E76" t="n">
-        <v>1355.663091473052</v>
+        <v>1355.977424344128</v>
       </c>
       <c r="F76" t="n">
         <v>6531</v>
@@ -9268,13 +9268,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1347.590700143598</v>
+        <v>1347.601162217428</v>
       </c>
       <c r="D77" t="n">
-        <v>1335.907018896996</v>
+        <v>1335.919111499706</v>
       </c>
       <c r="E77" t="n">
-        <v>1359.274381390201</v>
+        <v>1359.28321293515</v>
       </c>
       <c r="F77" t="n">
         <v>2549</v>
@@ -9419,13 +9419,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1347.195421202076</v>
+        <v>1347.213817987915</v>
       </c>
       <c r="D78" t="n">
-        <v>1337.736883742005</v>
+        <v>1337.756263538787</v>
       </c>
       <c r="E78" t="n">
-        <v>1356.653958662146</v>
+        <v>1356.671372437042</v>
       </c>
       <c r="F78" t="n">
         <v>3926</v>
@@ -9570,16 +9570,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1346.119286717584</v>
+        <v>1346.234085231346</v>
       </c>
       <c r="D79" t="n">
-        <v>1338.853158828177</v>
+        <v>1338.968432967506</v>
       </c>
       <c r="E79" t="n">
-        <v>1353.385414606992</v>
+        <v>1353.499737495186</v>
       </c>
       <c r="F79" t="n">
-        <v>6992</v>
+        <v>6993</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -9641,16 +9641,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1345.91811306582</v>
+        <v>1346.048835282142</v>
       </c>
       <c r="D80" t="n">
-        <v>1338.179632197768</v>
+        <v>1338.310665162486</v>
       </c>
       <c r="E80" t="n">
-        <v>1353.656593933871</v>
+        <v>1353.787005401798</v>
       </c>
       <c r="F80" t="n">
-        <v>6862</v>
+        <v>6859</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9792,16 +9792,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1343.279265618258</v>
+        <v>1343.361832307397</v>
       </c>
       <c r="D81" t="n">
-        <v>1333.315712097092</v>
+        <v>1333.394730878859</v>
       </c>
       <c r="E81" t="n">
-        <v>1353.242819139425</v>
+        <v>1353.328933735936</v>
       </c>
       <c r="F81" t="n">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -9943,13 +9943,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1341.960471558782</v>
+        <v>1341.997715041407</v>
       </c>
       <c r="D82" t="n">
-        <v>1332.450197199104</v>
+        <v>1332.488447424185</v>
       </c>
       <c r="E82" t="n">
-        <v>1351.47074591846</v>
+        <v>1351.506982658629</v>
       </c>
       <c r="F82" t="n">
         <v>3829</v>
@@ -10094,16 +10094,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1336.094724651596</v>
+        <v>1336.086348546096</v>
       </c>
       <c r="D83" t="n">
-        <v>1331.650370807612</v>
+        <v>1331.640944414484</v>
       </c>
       <c r="E83" t="n">
-        <v>1340.53907849558</v>
+        <v>1340.531752677708</v>
       </c>
       <c r="F83" t="n">
-        <v>25362</v>
+        <v>25361</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10245,13 +10245,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1335.029510081405</v>
+        <v>1335.02089630113</v>
       </c>
       <c r="D84" t="n">
-        <v>1331.310780487382</v>
+        <v>1331.301794496439</v>
       </c>
       <c r="E84" t="n">
-        <v>1338.748239675429</v>
+        <v>1338.739998105821</v>
       </c>
       <c r="F84" t="n">
         <v>41375</v>
@@ -10396,13 +10396,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1333.190386075118</v>
+        <v>1333.185800269097</v>
       </c>
       <c r="D85" t="n">
-        <v>1329.590511712065</v>
+        <v>1329.586110786646</v>
       </c>
       <c r="E85" t="n">
-        <v>1336.790260438171</v>
+        <v>1336.785489751549</v>
       </c>
       <c r="F85" t="n">
         <v>59656</v>
@@ -10547,16 +10547,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1329.712478462061</v>
+        <v>1329.685258639875</v>
       </c>
       <c r="D86" t="n">
-        <v>1323.635766469315</v>
+        <v>1323.609789128288</v>
       </c>
       <c r="E86" t="n">
-        <v>1335.789190454808</v>
+        <v>1335.760728151462</v>
       </c>
       <c r="F86" t="n">
-        <v>12197</v>
+        <v>12195</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10698,13 +10698,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1328.929895512465</v>
+        <v>1328.912153254818</v>
       </c>
       <c r="D87" t="n">
-        <v>1307.631201431312</v>
+        <v>1307.622118113833</v>
       </c>
       <c r="E87" t="n">
-        <v>1350.228589593617</v>
+        <v>1350.202188395802</v>
       </c>
       <c r="F87" t="n">
         <v>800</v>
@@ -10849,13 +10849,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1328.027388080053</v>
+        <v>1328.059527907601</v>
       </c>
       <c r="D88" t="n">
-        <v>1315.88217863855</v>
+        <v>1315.916418937978</v>
       </c>
       <c r="E88" t="n">
-        <v>1340.172597521556</v>
+        <v>1340.202636877223</v>
       </c>
       <c r="F88" t="n">
         <v>2218</v>
@@ -11000,16 +11000,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1327.315061703295</v>
+        <v>1327.32740774207</v>
       </c>
       <c r="D89" t="n">
-        <v>1322.582381333464</v>
+        <v>1322.594520764111</v>
       </c>
       <c r="E89" t="n">
-        <v>1332.047742073125</v>
+        <v>1332.060294720029</v>
       </c>
       <c r="F89" t="n">
-        <v>26451</v>
+        <v>26448</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11151,16 +11151,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1327.249101792514</v>
+        <v>1327.200229743097</v>
       </c>
       <c r="D90" t="n">
-        <v>1322.992218877837</v>
+        <v>1322.943091560933</v>
       </c>
       <c r="E90" t="n">
-        <v>1331.505984707192</v>
+        <v>1331.45736792526</v>
       </c>
       <c r="F90" t="n">
-        <v>39938</v>
+        <v>39928</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -11302,13 +11302,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1323.496998508067</v>
+        <v>1323.513340982781</v>
       </c>
       <c r="D91" t="n">
-        <v>1315.22471591538</v>
+        <v>1315.241746951406</v>
       </c>
       <c r="E91" t="n">
-        <v>1331.769281100755</v>
+        <v>1331.784935014155</v>
       </c>
       <c r="F91" t="n">
         <v>6795</v>
@@ -11373,16 +11373,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1322.927353271487</v>
+        <v>1322.950706981142</v>
       </c>
       <c r="D92" t="n">
-        <v>1318.216067233725</v>
+        <v>1318.240456709915</v>
       </c>
       <c r="E92" t="n">
-        <v>1327.638639309249</v>
+        <v>1327.660957252369</v>
       </c>
       <c r="F92" t="n">
-        <v>30259</v>
+        <v>30251</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -11524,16 +11524,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1320.51594335373</v>
+        <v>1320.500488937261</v>
       </c>
       <c r="D93" t="n">
-        <v>1313.298597445824</v>
+        <v>1313.280990212966</v>
       </c>
       <c r="E93" t="n">
-        <v>1327.733289261635</v>
+        <v>1327.719987661556</v>
       </c>
       <c r="F93" t="n">
-        <v>7137</v>
+        <v>7129</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -11595,16 +11595,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1318.357153364021</v>
+        <v>1318.309405197381</v>
       </c>
       <c r="D94" t="n">
-        <v>1314.875151257682</v>
+        <v>1314.826698734568</v>
       </c>
       <c r="E94" t="n">
-        <v>1321.83915547036</v>
+        <v>1321.792111660195</v>
       </c>
       <c r="F94" t="n">
-        <v>54709</v>
+        <v>54698</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11746,13 +11746,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1318.157420115365</v>
+        <v>1318.19822206586</v>
       </c>
       <c r="D95" t="n">
-        <v>1313.007045752775</v>
+        <v>1313.048523829343</v>
       </c>
       <c r="E95" t="n">
-        <v>1323.307794477954</v>
+        <v>1323.347920302377</v>
       </c>
       <c r="F95" t="n">
         <v>22553</v>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1318.064676635707</v>
+        <v>1318.081018810257</v>
       </c>
       <c r="D96" t="n">
-        <v>1312.362518211149</v>
+        <v>1312.37930774187</v>
       </c>
       <c r="E96" t="n">
-        <v>1323.766835060265</v>
+        <v>1323.782729878644</v>
       </c>
       <c r="F96" t="n">
         <v>16478</v>
@@ -11968,16 +11968,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1317.305939023843</v>
+        <v>1317.397779894674</v>
       </c>
       <c r="D97" t="n">
-        <v>1310.932120797338</v>
+        <v>1311.025175840396</v>
       </c>
       <c r="E97" t="n">
-        <v>1323.679757250348</v>
+        <v>1323.770383948953</v>
       </c>
       <c r="F97" t="n">
-        <v>10620</v>
+        <v>10618</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -12119,16 +12119,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1315.338918219274</v>
+        <v>1315.395456563953</v>
       </c>
       <c r="D98" t="n">
-        <v>1309.800001373384</v>
+        <v>1309.857918601493</v>
       </c>
       <c r="E98" t="n">
-        <v>1320.877835065164</v>
+        <v>1320.932994526413</v>
       </c>
       <c r="F98" t="n">
-        <v>15490</v>
+        <v>15489</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -12270,13 +12270,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1314.311880958647</v>
+        <v>1314.333590452273</v>
       </c>
       <c r="D99" t="n">
-        <v>1309.754366959896</v>
+        <v>1309.775897478905</v>
       </c>
       <c r="E99" t="n">
-        <v>1318.869394957399</v>
+        <v>1318.891283425641</v>
       </c>
       <c r="F99" t="n">
         <v>24739</v>
@@ -12417,13 +12417,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1314.184983983982</v>
+        <v>1314.190573301074</v>
       </c>
       <c r="D100" t="n">
-        <v>1310.255014542093</v>
+        <v>1310.260844627718</v>
       </c>
       <c r="E100" t="n">
-        <v>1318.114953425871</v>
+        <v>1318.120301974429</v>
       </c>
       <c r="F100" t="n">
         <v>45459</v>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1307.186505248886</v>
+        <v>1307.200422776109</v>
       </c>
       <c r="D101" t="n">
-        <v>1302.477221668485</v>
+        <v>1302.491363980142</v>
       </c>
       <c r="E101" t="n">
-        <v>1311.895788829286</v>
+        <v>1311.909481572075</v>
       </c>
       <c r="F101" t="n">
         <v>24572</v>
@@ -12635,36 +12635,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>granite-4.1-8b</t>
+          <t>athene-70b-0725</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1306.635195795994</v>
+        <v>1306.52694207679</v>
       </c>
       <c r="D102" t="n">
-        <v>1296.439332545961</v>
+        <v>1300.851496297477</v>
       </c>
       <c r="E102" t="n">
-        <v>1316.831059046028</v>
+        <v>1312.202387856104</v>
       </c>
       <c r="F102" t="n">
-        <v>4003</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
+        <v>19621</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>CC-BY-NC-4.0</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="J102" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -12677,26 +12673,26 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="N102" t="n">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="O102" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="P102" t="n">
-        <v>10</v>
+        <v>87.5</v>
       </c>
       <c r="Q102" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="R102" t="n">
-        <v>5</v>
-      </c>
-      <c r="S102" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>43.8</v>
+      </c>
+      <c r="S102" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T102" s="6" t="inlineStr">
@@ -12709,14 +12705,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V102" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W102" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V102" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W102" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="X102" s="6" t="inlineStr">
@@ -12724,9 +12720,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y102" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="Y102" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="Z102" s="6" t="inlineStr">
@@ -12771,12 +12767,12 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -12786,32 +12782,36 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>athene-70b-0725</t>
+          <t>granite-4.1-8b</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1306.508723614388</v>
+        <v>1305.832301922998</v>
       </c>
       <c r="D103" t="n">
-        <v>1300.832631270113</v>
+        <v>1295.618699054704</v>
       </c>
       <c r="E103" t="n">
-        <v>1312.184815958663</v>
+        <v>1316.045904791292</v>
       </c>
       <c r="F103" t="n">
-        <v>19621</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
+        <v>3995</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J103" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -12824,26 +12824,26 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="N103" t="n">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="O103" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="P103" t="n">
-        <v>87.5</v>
+        <v>10</v>
       </c>
       <c r="Q103" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="R103" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S103" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>5</v>
+      </c>
+      <c r="S103" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T103" s="6" t="inlineStr">
@@ -12856,14 +12856,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V103" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W103" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="V103" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W103" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X103" s="6" t="inlineStr">
@@ -12871,9 +12871,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y103" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="Y103" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z103" s="6" t="inlineStr">
@@ -12918,12 +12918,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -12937,16 +12937,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1305.456232577047</v>
+        <v>1305.487847497267</v>
       </c>
       <c r="D104" t="n">
-        <v>1297.274640947145</v>
+        <v>1297.308024400034</v>
       </c>
       <c r="E104" t="n">
-        <v>1313.637824206949</v>
+        <v>1313.667670594501</v>
       </c>
       <c r="F104" t="n">
-        <v>5929</v>
+        <v>5930</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -13088,13 +13088,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1305.419574676973</v>
+        <v>1305.427357624802</v>
       </c>
       <c r="D105" t="n">
-        <v>1300.977102264792</v>
+        <v>1300.984409857412</v>
       </c>
       <c r="E105" t="n">
-        <v>1309.862047089154</v>
+        <v>1309.870305392192</v>
       </c>
       <c r="F105" t="n">
         <v>28073</v>
@@ -13159,13 +13159,13 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1303.393478345997</v>
+        <v>1303.425248002746</v>
       </c>
       <c r="D106" t="n">
-        <v>1294.07701918975</v>
+        <v>1294.109631976236</v>
       </c>
       <c r="E106" t="n">
-        <v>1312.709937502244</v>
+        <v>1312.740864029255</v>
       </c>
       <c r="F106" t="n">
         <v>4171</v>
@@ -13310,16 +13310,16 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1303.358042106954</v>
+        <v>1303.339731276281</v>
       </c>
       <c r="D107" t="n">
-        <v>1298.846837008375</v>
+        <v>1298.828960974894</v>
       </c>
       <c r="E107" t="n">
-        <v>1307.869247205533</v>
+        <v>1307.850501577668</v>
       </c>
       <c r="F107" t="n">
-        <v>33186</v>
+        <v>33180</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -13461,13 +13461,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1302.892385838529</v>
+        <v>1302.910147434514</v>
       </c>
       <c r="D108" t="n">
-        <v>1298.813437397918</v>
+        <v>1298.83105312402</v>
       </c>
       <c r="E108" t="n">
-        <v>1306.971334279139</v>
+        <v>1306.989241745008</v>
       </c>
       <c r="F108" t="n">
         <v>39406</v>
@@ -13612,13 +13612,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1298.993419902383</v>
+        <v>1299.039578569611</v>
       </c>
       <c r="D109" t="n">
-        <v>1291.229389149604</v>
+        <v>1291.276313241589</v>
       </c>
       <c r="E109" t="n">
-        <v>1306.757450655162</v>
+        <v>1306.802843897632</v>
       </c>
       <c r="F109" t="n">
         <v>7140</v>
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1293.291930590795</v>
+        <v>1293.305174559335</v>
       </c>
       <c r="D110" t="n">
-        <v>1289.551107742676</v>
+        <v>1289.564442624953</v>
       </c>
       <c r="E110" t="n">
-        <v>1297.032753438913</v>
+        <v>1297.045906493717</v>
       </c>
       <c r="F110" t="n">
         <v>55240</v>
@@ -13914,13 +13914,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1289.235893053812</v>
+        <v>1289.241450144373</v>
       </c>
       <c r="D111" t="n">
-        <v>1281.927898129481</v>
+        <v>1281.93432277372</v>
       </c>
       <c r="E111" t="n">
-        <v>1296.543887978143</v>
+        <v>1296.548577515026</v>
       </c>
       <c r="F111" t="n">
         <v>8662</v>
@@ -13981,13 +13981,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1289.198952865954</v>
+        <v>1289.214115081854</v>
       </c>
       <c r="D112" t="n">
-        <v>1285.811466889092</v>
+        <v>1285.826570163851</v>
       </c>
       <c r="E112" t="n">
-        <v>1292.586438842816</v>
+        <v>1292.601659999857</v>
       </c>
       <c r="F112" t="n">
         <v>75754</v>
@@ -14132,13 +14132,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1287.464700274216</v>
+        <v>1287.269982741277</v>
       </c>
       <c r="D113" t="n">
-        <v>1279.074349577417</v>
+        <v>1278.881089258432</v>
       </c>
       <c r="E113" t="n">
-        <v>1295.855050971014</v>
+        <v>1295.658876224121</v>
       </c>
       <c r="F113" t="n">
         <v>5677</v>
@@ -14283,13 +14283,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1286.17297252795</v>
+        <v>1286.16374422045</v>
       </c>
       <c r="D114" t="n">
-        <v>1276.200882088325</v>
+        <v>1276.192790087336</v>
       </c>
       <c r="E114" t="n">
-        <v>1296.145062967574</v>
+        <v>1296.134698353563</v>
       </c>
       <c r="F114" t="n">
         <v>3749</v>
@@ -14434,13 +14434,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1286.034023695829</v>
+        <v>1286.040933665017</v>
       </c>
       <c r="D115" t="n">
-        <v>1275.567412804299</v>
+        <v>1275.575595398012</v>
       </c>
       <c r="E115" t="n">
-        <v>1296.500634587359</v>
+        <v>1296.506271932022</v>
       </c>
       <c r="F115" t="n">
         <v>2846</v>
@@ -14585,16 +14585,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1285.047688103793</v>
+        <v>1285.21454142164</v>
       </c>
       <c r="D116" t="n">
-        <v>1277.837109634927</v>
+        <v>1278.008529122735</v>
       </c>
       <c r="E116" t="n">
-        <v>1292.25826657266</v>
+        <v>1292.420553720545</v>
       </c>
       <c r="F116" t="n">
-        <v>8486</v>
+        <v>8485</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -14736,13 +14736,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1280.147621227799</v>
+        <v>1280.156362472173</v>
       </c>
       <c r="D117" t="n">
-        <v>1273.286434322637</v>
+        <v>1273.296062498382</v>
       </c>
       <c r="E117" t="n">
-        <v>1287.008808132961</v>
+        <v>1287.016662445965</v>
       </c>
       <c r="F117" t="n">
         <v>10072</v>
@@ -14883,13 +14883,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1276.731253885557</v>
+        <v>1276.716613924695</v>
       </c>
       <c r="D118" t="n">
-        <v>1271.404836665339</v>
+        <v>1271.391424869748</v>
       </c>
       <c r="E118" t="n">
-        <v>1282.057671105775</v>
+        <v>1282.041802979642</v>
       </c>
       <c r="F118" t="n">
         <v>19659</v>
@@ -15034,13 +15034,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1276.18773858114</v>
+        <v>1276.187441257277</v>
       </c>
       <c r="D119" t="n">
-        <v>1272.597861062768</v>
+        <v>1272.598573510292</v>
       </c>
       <c r="E119" t="n">
-        <v>1279.777616099512</v>
+        <v>1279.776309004262</v>
       </c>
       <c r="F119" t="n">
         <v>156876</v>
@@ -15185,13 +15185,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1275.985944306855</v>
+        <v>1275.97900034829</v>
       </c>
       <c r="D120" t="n">
-        <v>1269.406510000104</v>
+        <v>1269.400240215633</v>
       </c>
       <c r="E120" t="n">
-        <v>1282.565378613605</v>
+        <v>1282.557760480946</v>
       </c>
       <c r="F120" t="n">
         <v>9866</v>
@@ -15336,13 +15336,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1274.239099123449</v>
+        <v>1274.244547822102</v>
       </c>
       <c r="D121" t="n">
-        <v>1268.327535367393</v>
+        <v>1268.332819184363</v>
       </c>
       <c r="E121" t="n">
-        <v>1280.150662879505</v>
+        <v>1280.156276459841</v>
       </c>
       <c r="F121" t="n">
         <v>14681</v>
@@ -15487,13 +15487,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1270.500189592126</v>
+        <v>1270.508620958174</v>
       </c>
       <c r="D122" t="n">
-        <v>1262.371091701494</v>
+        <v>1262.380174990531</v>
       </c>
       <c r="E122" t="n">
-        <v>1278.629287482758</v>
+        <v>1278.637066925815</v>
       </c>
       <c r="F122" t="n">
         <v>5432</v>
@@ -15638,13 +15638,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1267.074816433674</v>
+        <v>1267.084113427125</v>
       </c>
       <c r="D123" t="n">
-        <v>1262.18247110342</v>
+        <v>1262.191769074185</v>
       </c>
       <c r="E123" t="n">
-        <v>1271.967161763927</v>
+        <v>1271.976457780065</v>
       </c>
       <c r="F123" t="n">
         <v>27124</v>
@@ -15789,13 +15789,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1266.719172346277</v>
+        <v>1266.734632089877</v>
       </c>
       <c r="D124" t="n">
-        <v>1262.895428702131</v>
+        <v>1262.910886460293</v>
       </c>
       <c r="E124" t="n">
-        <v>1270.542915990423</v>
+        <v>1270.558377719461</v>
       </c>
       <c r="F124" t="n">
         <v>54611</v>
@@ -15940,13 +15940,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1264.842372616404</v>
+        <v>1264.828465418645</v>
       </c>
       <c r="D125" t="n">
-        <v>1258.561987438349</v>
+        <v>1258.549243632277</v>
       </c>
       <c r="E125" t="n">
-        <v>1271.122757794459</v>
+        <v>1271.107687205013</v>
       </c>
       <c r="F125" t="n">
         <v>15147</v>
@@ -16091,13 +16091,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1261.355759372048</v>
+        <v>1261.333413738873</v>
       </c>
       <c r="D126" t="n">
-        <v>1256.405808766476</v>
+        <v>1256.384268554421</v>
       </c>
       <c r="E126" t="n">
-        <v>1266.305709977621</v>
+        <v>1266.282558923325</v>
       </c>
       <c r="F126" t="n">
         <v>37325</v>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1261.295268092635</v>
+        <v>1261.273999122569</v>
       </c>
       <c r="D127" t="n">
-        <v>1256.969943130666</v>
+        <v>1256.949933774233</v>
       </c>
       <c r="E127" t="n">
-        <v>1265.620593054603</v>
+        <v>1265.598064470906</v>
       </c>
       <c r="F127" t="n">
         <v>77554</v>
@@ -16313,13 +16313,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1256.170583542945</v>
+        <v>1256.17752478752</v>
       </c>
       <c r="D128" t="n">
-        <v>1251.571616010566</v>
+        <v>1251.578203176834</v>
       </c>
       <c r="E128" t="n">
-        <v>1260.769551075324</v>
+        <v>1260.776846398205</v>
       </c>
       <c r="F128" t="n">
         <v>24126</v>
@@ -16464,13 +16464,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1251.477048329519</v>
+        <v>1251.467182644776</v>
       </c>
       <c r="D129" t="n">
-        <v>1240.695505669421</v>
+        <v>1240.686860650781</v>
       </c>
       <c r="E129" t="n">
-        <v>1262.258590989616</v>
+        <v>1262.247504638771</v>
       </c>
       <c r="F129" t="n">
         <v>3334</v>
@@ -16615,13 +16615,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1249.926557971563</v>
+        <v>1249.909405766342</v>
       </c>
       <c r="D130" t="n">
-        <v>1243.322368814303</v>
+        <v>1243.305971348437</v>
       </c>
       <c r="E130" t="n">
-        <v>1256.530747128823</v>
+        <v>1256.512840184248</v>
       </c>
       <c r="F130" t="n">
         <v>10140</v>
@@ -16766,13 +16766,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1239.555792313314</v>
+        <v>1239.566451674401</v>
       </c>
       <c r="D131" t="n">
-        <v>1232.32739047985</v>
+        <v>1232.33894494617</v>
       </c>
       <c r="E131" t="n">
-        <v>1246.784194146779</v>
+        <v>1246.793958402632</v>
       </c>
       <c r="F131" t="n">
         <v>8858</v>
@@ -16833,13 +16833,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1237.447722476727</v>
+        <v>1237.459261988635</v>
       </c>
       <c r="D132" t="n">
-        <v>1228.353841982179</v>
+        <v>1228.366573964813</v>
       </c>
       <c r="E132" t="n">
-        <v>1246.541602971276</v>
+        <v>1246.551950012456</v>
       </c>
       <c r="F132" t="n">
         <v>4781</v>
@@ -16984,13 +16984,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1233.727735920842</v>
+        <v>1233.708578159137</v>
       </c>
       <c r="D133" t="n">
-        <v>1228.173830930568</v>
+        <v>1228.155917761668</v>
       </c>
       <c r="E133" t="n">
-        <v>1239.281640911116</v>
+        <v>1239.261238556607</v>
       </c>
       <c r="F133" t="n">
         <v>26195</v>
@@ -17135,13 +17135,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1232.971927662224</v>
+        <v>1232.950465782236</v>
       </c>
       <c r="D134" t="n">
-        <v>1227.696389666987</v>
+        <v>1227.676368948566</v>
       </c>
       <c r="E134" t="n">
-        <v>1238.24746565746</v>
+        <v>1238.224562615907</v>
       </c>
       <c r="F134" t="n">
         <v>39302</v>
@@ -17286,13 +17286,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1228.995962353536</v>
+        <v>1228.966788173956</v>
       </c>
       <c r="D135" t="n">
-        <v>1224.436752256649</v>
+        <v>1224.408616650664</v>
       </c>
       <c r="E135" t="n">
-        <v>1233.555172450423</v>
+        <v>1233.524959697248</v>
       </c>
       <c r="F135" t="n">
         <v>51416</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1226.31836945245</v>
+        <v>1226.289786814488</v>
       </c>
       <c r="D136" t="n">
-        <v>1221.534419199625</v>
+        <v>1221.507134514854</v>
       </c>
       <c r="E136" t="n">
-        <v>1231.102319705275</v>
+        <v>1231.072439114122</v>
       </c>
       <c r="F136" t="n">
         <v>54036</v>
@@ -17508,13 +17508,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1223.230754755843</v>
+        <v>1223.228328480363</v>
       </c>
       <c r="D137" t="n">
-        <v>1219.490333039874</v>
+        <v>1219.488948951043</v>
       </c>
       <c r="E137" t="n">
-        <v>1226.971176471813</v>
+        <v>1226.967708009682</v>
       </c>
       <c r="F137" t="n">
         <v>104642</v>
@@ -17659,13 +17659,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1222.97645588098</v>
+        <v>1222.99272401346</v>
       </c>
       <c r="D138" t="n">
-        <v>1216.000366284163</v>
+        <v>1216.017005474353</v>
       </c>
       <c r="E138" t="n">
-        <v>1229.952545477797</v>
+        <v>1229.968442552567</v>
       </c>
       <c r="F138" t="n">
         <v>9818</v>
@@ -17810,13 +17810,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1220.500084405897</v>
+        <v>1220.509861942495</v>
       </c>
       <c r="D139" t="n">
-        <v>1209.821907634847</v>
+        <v>1209.833231743344</v>
       </c>
       <c r="E139" t="n">
-        <v>1231.178261176948</v>
+        <v>1231.186492141645</v>
       </c>
       <c r="F139" t="n">
         <v>2896</v>
@@ -17961,13 +17961,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1212.625041570742</v>
+        <v>1212.620491675383</v>
       </c>
       <c r="D140" t="n">
-        <v>1207.584682199224</v>
+        <v>1207.581252631792</v>
       </c>
       <c r="E140" t="n">
-        <v>1217.665400942261</v>
+        <v>1217.659730718973</v>
       </c>
       <c r="F140" t="n">
         <v>24146</v>
@@ -18108,13 +18108,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1212.427306595669</v>
+        <v>1212.403160769067</v>
       </c>
       <c r="D141" t="n">
-        <v>1201.638156921825</v>
+        <v>1201.616053331695</v>
       </c>
       <c r="E141" t="n">
-        <v>1223.216456269513</v>
+        <v>1223.19026820644</v>
       </c>
       <c r="F141" t="n">
         <v>4652</v>
@@ -18255,13 +18255,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1211.336799541512</v>
+        <v>1211.358960897282</v>
       </c>
       <c r="D142" t="n">
-        <v>1207.181862981577</v>
+        <v>1207.204127047534</v>
       </c>
       <c r="E142" t="n">
-        <v>1215.491736101447</v>
+        <v>1215.51379474703</v>
       </c>
       <c r="F142" t="n">
         <v>49605</v>
@@ -18406,13 +18406,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1208.060272913225</v>
+        <v>1208.044719220894</v>
       </c>
       <c r="D143" t="n">
-        <v>1196.958104857948</v>
+        <v>1196.944325277417</v>
       </c>
       <c r="E143" t="n">
-        <v>1219.162440968503</v>
+        <v>1219.145113164371</v>
       </c>
       <c r="F143" t="n">
         <v>3090</v>
@@ -18557,13 +18557,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1203.421493028633</v>
+        <v>1203.395751427293</v>
       </c>
       <c r="D144" t="n">
-        <v>1197.302849298218</v>
+        <v>1197.278421168965</v>
       </c>
       <c r="E144" t="n">
-        <v>1209.540136759049</v>
+        <v>1209.51308168562</v>
       </c>
       <c r="F144" t="n">
         <v>21741</v>
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1200.026949865917</v>
+        <v>1200.062882453652</v>
       </c>
       <c r="D145" t="n">
-        <v>1195.928991029798</v>
+        <v>1195.9649969287</v>
       </c>
       <c r="E145" t="n">
-        <v>1204.124908702036</v>
+        <v>1204.160767978603</v>
       </c>
       <c r="F145" t="n">
         <v>46616</v>
@@ -18859,13 +18859,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1197.413806976192</v>
+        <v>1197.3933225258</v>
       </c>
       <c r="D146" t="n">
-        <v>1192.251434152646</v>
+        <v>1192.2318345448</v>
       </c>
       <c r="E146" t="n">
-        <v>1202.576179799739</v>
+        <v>1202.554810506801</v>
       </c>
       <c r="F146" t="n">
         <v>25055</v>
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1196.594165560112</v>
+        <v>1196.566451135913</v>
       </c>
       <c r="D147" t="n">
-        <v>1192.324464401785</v>
+        <v>1192.298269419652</v>
       </c>
       <c r="E147" t="n">
-        <v>1200.863866718439</v>
+        <v>1200.834632852175</v>
       </c>
       <c r="F147" t="n">
         <v>73503</v>
@@ -19161,13 +19161,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1194.838420115288</v>
+        <v>1194.804222117504</v>
       </c>
       <c r="D148" t="n">
-        <v>1188.724401843619</v>
+        <v>1188.69156634938</v>
       </c>
       <c r="E148" t="n">
-        <v>1200.952438386958</v>
+        <v>1200.916877885628</v>
       </c>
       <c r="F148" t="n">
         <v>32191</v>
@@ -19228,13 +19228,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1190.643396400145</v>
+        <v>1190.650753041289</v>
       </c>
       <c r="D149" t="n">
-        <v>1183.457918732273</v>
+        <v>1183.466211493196</v>
       </c>
       <c r="E149" t="n">
-        <v>1197.828874068017</v>
+        <v>1197.835294589382</v>
       </c>
       <c r="F149" t="n">
         <v>9901</v>
@@ -19375,13 +19375,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1190.565303503642</v>
+        <v>1190.546228182721</v>
       </c>
       <c r="D150" t="n">
-        <v>1183.447498167749</v>
+        <v>1183.429984698257</v>
       </c>
       <c r="E150" t="n">
-        <v>1197.683108839534</v>
+        <v>1197.662471667185</v>
       </c>
       <c r="F150" t="n">
         <v>17839</v>
@@ -19526,13 +19526,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1184.218147091549</v>
+        <v>1184.181598238365</v>
       </c>
       <c r="D151" t="n">
-        <v>1172.735207541951</v>
+        <v>1172.700995466145</v>
       </c>
       <c r="E151" t="n">
-        <v>1195.701086641147</v>
+        <v>1195.662201010585</v>
       </c>
       <c r="F151" t="n">
         <v>4932</v>
@@ -19677,13 +19677,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1184.19061405536</v>
+        <v>1184.168442528137</v>
       </c>
       <c r="D152" t="n">
-        <v>1174.754601773931</v>
+        <v>1174.734583791451</v>
       </c>
       <c r="E152" t="n">
-        <v>1193.626626336788</v>
+        <v>1193.602301264823</v>
       </c>
       <c r="F152" t="n">
         <v>8214</v>
@@ -19828,13 +19828,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1183.331566672519</v>
+        <v>1183.317938071624</v>
       </c>
       <c r="D153" t="n">
-        <v>1176.504760068282</v>
+        <v>1176.492569157835</v>
       </c>
       <c r="E153" t="n">
-        <v>1190.158373276756</v>
+        <v>1190.143306985413</v>
       </c>
       <c r="F153" t="n">
         <v>15483</v>
@@ -19975,13 +19975,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1182.390872246667</v>
+        <v>1182.363574186334</v>
       </c>
       <c r="D154" t="n">
-        <v>1173.709833085193</v>
+        <v>1173.684052724132</v>
       </c>
       <c r="E154" t="n">
-        <v>1191.071911408141</v>
+        <v>1191.043095648536</v>
       </c>
       <c r="F154" t="n">
         <v>6638</v>
@@ -20126,13 +20126,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1182.276033897757</v>
+        <v>1182.24018190267</v>
       </c>
       <c r="D155" t="n">
-        <v>1172.617556093851</v>
+        <v>1172.583835227948</v>
       </c>
       <c r="E155" t="n">
-        <v>1191.934511701662</v>
+        <v>1191.896528577393</v>
       </c>
       <c r="F155" t="n">
         <v>7968</v>
@@ -20193,13 +20193,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1182.074332289564</v>
+        <v>1182.045172770987</v>
       </c>
       <c r="D156" t="n">
-        <v>1174.081455470495</v>
+        <v>1174.054026963467</v>
       </c>
       <c r="E156" t="n">
-        <v>1190.067209108633</v>
+        <v>1190.036318578507</v>
       </c>
       <c r="F156" t="n">
         <v>12637</v>
@@ -20260,13 +20260,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1181.973054725279</v>
+        <v>1181.971282924098</v>
       </c>
       <c r="D157" t="n">
-        <v>1175.901547477727</v>
+        <v>1175.901147701599</v>
       </c>
       <c r="E157" t="n">
-        <v>1188.04456197283</v>
+        <v>1188.041418146597</v>
       </c>
       <c r="F157" t="n">
         <v>23893</v>
@@ -20411,13 +20411,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1179.346675988982</v>
+        <v>1179.314422097027</v>
       </c>
       <c r="D158" t="n">
-        <v>1173.434333645892</v>
+        <v>1173.403463200546</v>
       </c>
       <c r="E158" t="n">
-        <v>1185.259018332073</v>
+        <v>1185.225380993508</v>
       </c>
       <c r="F158" t="n">
         <v>32832</v>
@@ -20478,13 +20478,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1178.520759711083</v>
+        <v>1178.514615756643</v>
       </c>
       <c r="D159" t="n">
-        <v>1167.329861216538</v>
+        <v>1167.325574108047</v>
       </c>
       <c r="E159" t="n">
-        <v>1189.711658205627</v>
+        <v>1189.703657405239</v>
       </c>
       <c r="F159" t="n">
         <v>3188</v>
@@ -20629,13 +20629,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1177.187792858355</v>
+        <v>1177.165430965268</v>
       </c>
       <c r="D160" t="n">
-        <v>1167.382697252227</v>
+        <v>1167.362373231954</v>
       </c>
       <c r="E160" t="n">
-        <v>1186.992888464483</v>
+        <v>1186.968488698581</v>
       </c>
       <c r="F160" t="n">
         <v>6535</v>
@@ -20776,13 +20776,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1175.213088178972</v>
+        <v>1175.180507143233</v>
       </c>
       <c r="D161" t="n">
-        <v>1164.809282567733</v>
+        <v>1164.778905662874</v>
       </c>
       <c r="E161" t="n">
-        <v>1185.616893790212</v>
+        <v>1185.582108623592</v>
       </c>
       <c r="F161" t="n">
         <v>5006</v>
@@ -20923,13 +20923,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1172.351735164384</v>
+        <v>1172.328703342149</v>
       </c>
       <c r="D162" t="n">
-        <v>1166.151727444851</v>
+        <v>1166.130612397519</v>
       </c>
       <c r="E162" t="n">
-        <v>1178.551742883916</v>
+        <v>1178.526794286779</v>
       </c>
       <c r="F162" t="n">
         <v>22479</v>
@@ -21070,13 +21070,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1170.704173894509</v>
+        <v>1170.710280229546</v>
       </c>
       <c r="D163" t="n">
-        <v>1163.299693908102</v>
+        <v>1163.307475557157</v>
       </c>
       <c r="E163" t="n">
-        <v>1178.108653880915</v>
+        <v>1178.113084901936</v>
       </c>
       <c r="F163" t="n">
         <v>16056</v>
@@ -21217,13 +21217,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1170.58619622776</v>
+        <v>1170.565622836931</v>
       </c>
       <c r="D164" t="n">
-        <v>1164.669063112593</v>
+        <v>1164.649734907423</v>
       </c>
       <c r="E164" t="n">
-        <v>1176.503329342926</v>
+        <v>1176.481510766439</v>
       </c>
       <c r="F164" t="n">
         <v>17766</v>
@@ -21368,13 +21368,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1170.203899738703</v>
+        <v>1170.194688514894</v>
       </c>
       <c r="D165" t="n">
-        <v>1164.706577924633</v>
+        <v>1164.69908669597</v>
       </c>
       <c r="E165" t="n">
-        <v>1175.701221552773</v>
+        <v>1175.690290333817</v>
       </c>
       <c r="F165" t="n">
         <v>38492</v>
@@ -21519,13 +21519,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1166.916751144179</v>
+        <v>1166.899044005276</v>
       </c>
       <c r="D166" t="n">
-        <v>1158.854598305493</v>
+        <v>1158.838740034456</v>
       </c>
       <c r="E166" t="n">
-        <v>1174.978903982864</v>
+        <v>1174.959347976097</v>
       </c>
       <c r="F166" t="n">
         <v>10224</v>
@@ -21666,13 +21666,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1166.405624142021</v>
+        <v>1166.395353763837</v>
       </c>
       <c r="D167" t="n">
-        <v>1158.699624548803</v>
+        <v>1158.69039184626</v>
       </c>
       <c r="E167" t="n">
-        <v>1174.11162373524</v>
+        <v>1174.100315681414</v>
       </c>
       <c r="F167" t="n">
         <v>7936</v>
@@ -21817,13 +21817,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1163.993676903861</v>
+        <v>1163.982269224309</v>
       </c>
       <c r="D168" t="n">
-        <v>1152.083210177685</v>
+        <v>1152.074211488591</v>
       </c>
       <c r="E168" t="n">
-        <v>1175.904143630037</v>
+        <v>1175.890326960028</v>
       </c>
       <c r="F168" t="n">
         <v>3777</v>
@@ -21964,13 +21964,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1156.011016003247</v>
+        <v>1155.987839146449</v>
       </c>
       <c r="D169" t="n">
-        <v>1147.622907319482</v>
+        <v>1147.601347789836</v>
       </c>
       <c r="E169" t="n">
-        <v>1164.399124687011</v>
+        <v>1164.374330503063</v>
       </c>
       <c r="F169" t="n">
         <v>6837</v>
@@ -22115,13 +22115,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1154.522950552867</v>
+        <v>1154.538627868883</v>
       </c>
       <c r="D170" t="n">
-        <v>1143.033083235367</v>
+        <v>1143.050898364031</v>
       </c>
       <c r="E170" t="n">
-        <v>1166.012817870367</v>
+        <v>1166.026357373735</v>
       </c>
       <c r="F170" t="n">
         <v>3231</v>
@@ -22266,13 +22266,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1154.203419253823</v>
+        <v>1154.168277937763</v>
       </c>
       <c r="D171" t="n">
-        <v>1141.610114704767</v>
+        <v>1141.577544706196</v>
       </c>
       <c r="E171" t="n">
-        <v>1166.796723802879</v>
+        <v>1166.759011169329</v>
       </c>
       <c r="F171" t="n">
         <v>3585</v>
@@ -22417,13 +22417,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1151.817016072938</v>
+        <v>1151.785363979989</v>
       </c>
       <c r="D172" t="n">
-        <v>1138.65310149242</v>
+        <v>1138.624651945862</v>
       </c>
       <c r="E172" t="n">
-        <v>1164.980930653455</v>
+        <v>1164.946076014116</v>
       </c>
       <c r="F172" t="n">
         <v>4155</v>
@@ -22564,13 +22564,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1151.659726407652</v>
+        <v>1151.633244345956</v>
       </c>
       <c r="D173" t="n">
-        <v>1136.338330361059</v>
+        <v>1136.316255161651</v>
       </c>
       <c r="E173" t="n">
-        <v>1166.981122454245</v>
+        <v>1166.95023353026</v>
       </c>
       <c r="F173" t="n">
         <v>1679</v>
@@ -22711,13 +22711,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1150.030477272366</v>
+        <v>1149.997405494991</v>
       </c>
       <c r="D174" t="n">
-        <v>1137.787784974516</v>
+        <v>1137.758529705216</v>
       </c>
       <c r="E174" t="n">
-        <v>1162.273169570215</v>
+        <v>1162.236281284766</v>
       </c>
       <c r="F174" t="n">
         <v>2572</v>
@@ -22858,13 +22858,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1148.896773155809</v>
+        <v>1148.870036366034</v>
       </c>
       <c r="D175" t="n">
-        <v>1139.674559440898</v>
+        <v>1139.650692807025</v>
       </c>
       <c r="E175" t="n">
-        <v>1158.11898687072</v>
+        <v>1158.089379925043</v>
       </c>
       <c r="F175" t="n">
         <v>7044</v>
@@ -23009,13 +23009,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1148.8892494162</v>
+        <v>1148.867303792576</v>
       </c>
       <c r="D176" t="n">
-        <v>1142.238815828768</v>
+        <v>1142.218375658084</v>
       </c>
       <c r="E176" t="n">
-        <v>1155.539683003631</v>
+        <v>1155.516231927068</v>
       </c>
       <c r="F176" t="n">
         <v>19402</v>
@@ -23160,13 +23160,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1147.275978578964</v>
+        <v>1147.234219848685</v>
       </c>
       <c r="D177" t="n">
-        <v>1130.22454496689</v>
+        <v>1130.187466172479</v>
       </c>
       <c r="E177" t="n">
-        <v>1164.327412191038</v>
+        <v>1164.280973524892</v>
       </c>
       <c r="F177" t="n">
         <v>1295</v>
@@ -23307,13 +23307,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1143.373406099685</v>
+        <v>1143.36001715476</v>
       </c>
       <c r="D178" t="n">
-        <v>1133.487927115002</v>
+        <v>1133.476335311987</v>
       </c>
       <c r="E178" t="n">
-        <v>1153.258885084369</v>
+        <v>1153.243698997533</v>
       </c>
       <c r="F178" t="n">
         <v>4737</v>
@@ -23458,13 +23458,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1142.620792010502</v>
+        <v>1142.59966375206</v>
       </c>
       <c r="D179" t="n">
-        <v>1136.180080863005</v>
+        <v>1136.160008332982</v>
       </c>
       <c r="E179" t="n">
-        <v>1149.061503158</v>
+        <v>1149.039319171138</v>
       </c>
       <c r="F179" t="n">
         <v>12297</v>
@@ -23609,13 +23609,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1140.979766178038</v>
+        <v>1140.971779084485</v>
       </c>
       <c r="D180" t="n">
-        <v>1134.257112100653</v>
+        <v>1134.25068109293</v>
       </c>
       <c r="E180" t="n">
-        <v>1147.702420255422</v>
+        <v>1147.692877076041</v>
       </c>
       <c r="F180" t="n">
         <v>19174</v>
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1140.816598391101</v>
+        <v>1140.778869042684</v>
       </c>
       <c r="D181" t="n">
-        <v>1134.119369940287</v>
+        <v>1134.083778245236</v>
       </c>
       <c r="E181" t="n">
-        <v>1147.513826841916</v>
+        <v>1147.473959840132</v>
       </c>
       <c r="F181" t="n">
         <v>19367</v>
@@ -23907,13 +23907,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1138.558077544467</v>
+        <v>1138.515327872445</v>
       </c>
       <c r="D182" t="n">
-        <v>1127.61812589466</v>
+        <v>1127.577776699073</v>
       </c>
       <c r="E182" t="n">
-        <v>1149.498029194273</v>
+        <v>1149.452879045817</v>
       </c>
       <c r="F182" t="n">
         <v>4964</v>
@@ -24058,13 +24058,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1137.170019303445</v>
+        <v>1137.161696601576</v>
       </c>
       <c r="D183" t="n">
-        <v>1127.684773453704</v>
+        <v>1127.67849432563</v>
       </c>
       <c r="E183" t="n">
-        <v>1146.655265153186</v>
+        <v>1146.644898877522</v>
       </c>
       <c r="F183" t="n">
         <v>8925</v>
@@ -24209,13 +24209,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1136.253024744906</v>
+        <v>1136.229409247875</v>
       </c>
       <c r="D184" t="n">
-        <v>1127.36537247596</v>
+        <v>1127.343854290809</v>
       </c>
       <c r="E184" t="n">
-        <v>1145.140677013852</v>
+        <v>1145.11496420494</v>
       </c>
       <c r="F184" t="n">
         <v>7366</v>
@@ -24360,13 +24360,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1130.286844840628</v>
+        <v>1130.26198725591</v>
       </c>
       <c r="D185" t="n">
-        <v>1121.459384387191</v>
+        <v>1121.436743122026</v>
       </c>
       <c r="E185" t="n">
-        <v>1139.114305294065</v>
+        <v>1139.087231389793</v>
       </c>
       <c r="F185" t="n">
         <v>11118</v>
@@ -24507,13 +24507,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1129.149731157117</v>
+        <v>1129.120341103187</v>
       </c>
       <c r="D186" t="n">
-        <v>1121.726346980094</v>
+        <v>1121.698603775696</v>
       </c>
       <c r="E186" t="n">
-        <v>1136.573115334141</v>
+        <v>1136.542078430678</v>
       </c>
       <c r="F186" t="n">
         <v>20685</v>
@@ -24658,13 +24658,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1127.680367251134</v>
+        <v>1127.665265658267</v>
       </c>
       <c r="D187" t="n">
-        <v>1121.282219644839</v>
+        <v>1121.26839005549</v>
       </c>
       <c r="E187" t="n">
-        <v>1134.078514857428</v>
+        <v>1134.062141261044</v>
       </c>
       <c r="F187" t="n">
         <v>20118</v>
@@ -24809,13 +24809,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1126.848004396768</v>
+        <v>1126.81258877153</v>
       </c>
       <c r="D188" t="n">
-        <v>1114.756615736899</v>
+        <v>1114.725254817789</v>
       </c>
       <c r="E188" t="n">
-        <v>1138.939393056638</v>
+        <v>1138.89992272527</v>
       </c>
       <c r="F188" t="n">
         <v>2921</v>
@@ -24956,13 +24956,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1126.344903458351</v>
+        <v>1126.315594625628</v>
       </c>
       <c r="D189" t="n">
-        <v>1110.750912778263</v>
+        <v>1110.726000330116</v>
       </c>
       <c r="E189" t="n">
-        <v>1141.93889413844</v>
+        <v>1141.905188921139</v>
       </c>
       <c r="F189" t="n">
         <v>1785</v>
@@ -25103,13 +25103,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1120.87580856268</v>
+        <v>1120.839860259288</v>
       </c>
       <c r="D190" t="n">
-        <v>1109.901329859134</v>
+        <v>1109.867720765239</v>
       </c>
       <c r="E190" t="n">
-        <v>1131.850287266227</v>
+        <v>1131.811999753338</v>
       </c>
       <c r="F190" t="n">
         <v>5182</v>
@@ -25250,13 +25250,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1118.708831561563</v>
+        <v>1118.694057695314</v>
       </c>
       <c r="D191" t="n">
-        <v>1100.577232003377</v>
+        <v>1100.567347200059</v>
       </c>
       <c r="E191" t="n">
-        <v>1136.840431119749</v>
+        <v>1136.82076819057</v>
       </c>
       <c r="F191" t="n">
         <v>1143</v>
@@ -25401,13 +25401,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1115.998337617055</v>
+        <v>1115.996529987857</v>
       </c>
       <c r="D192" t="n">
-        <v>1108.270322924513</v>
+        <v>1108.270106690822</v>
       </c>
       <c r="E192" t="n">
-        <v>1123.726352309597</v>
+        <v>1123.722953284893</v>
       </c>
       <c r="F192" t="n">
         <v>10854</v>
@@ -25552,13 +25552,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1114.566540182833</v>
+        <v>1114.530699160232</v>
       </c>
       <c r="D193" t="n">
-        <v>1105.432580435133</v>
+        <v>1105.399862056004</v>
       </c>
       <c r="E193" t="n">
-        <v>1123.700499930533</v>
+        <v>1123.66153626446</v>
       </c>
       <c r="F193" t="n">
         <v>6923</v>
@@ -25699,13 +25699,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1114.116918325061</v>
+        <v>1114.09237553453</v>
       </c>
       <c r="D194" t="n">
-        <v>1099.747361305707</v>
+        <v>1099.726372191225</v>
       </c>
       <c r="E194" t="n">
-        <v>1128.486475344415</v>
+        <v>1128.458378877835</v>
       </c>
       <c r="F194" t="n">
         <v>2199</v>
@@ -25846,13 +25846,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1110.747500925504</v>
+        <v>1110.73337915718</v>
       </c>
       <c r="D195" t="n">
-        <v>1102.863245804244</v>
+        <v>1102.850354874291</v>
       </c>
       <c r="E195" t="n">
-        <v>1118.631756046765</v>
+        <v>1118.616403440068</v>
       </c>
       <c r="F195" t="n">
         <v>8045</v>
@@ -25997,13 +25997,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1109.586867576937</v>
+        <v>1109.547927864534</v>
       </c>
       <c r="D196" t="n">
-        <v>1100.307475873862</v>
+        <v>1100.270707136779</v>
       </c>
       <c r="E196" t="n">
-        <v>1118.866259280011</v>
+        <v>1118.825148592289</v>
       </c>
       <c r="F196" t="n">
         <v>8977</v>
@@ -26148,13 +26148,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1107.502834542719</v>
+        <v>1107.496799659809</v>
       </c>
       <c r="D197" t="n">
-        <v>1100.452233918486</v>
+        <v>1100.447792172211</v>
       </c>
       <c r="E197" t="n">
-        <v>1114.553435166953</v>
+        <v>1114.545807147407</v>
       </c>
       <c r="F197" t="n">
         <v>14148</v>
@@ -26299,13 +26299,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1092.990651746292</v>
+        <v>1092.978060717724</v>
       </c>
       <c r="D198" t="n">
-        <v>1081.509968180352</v>
+        <v>1081.500023700154</v>
       </c>
       <c r="E198" t="n">
-        <v>1104.471335312231</v>
+        <v>1104.456097735294</v>
       </c>
       <c r="F198" t="n">
         <v>4780</v>
@@ -26450,13 +26450,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1090.282463662942</v>
+        <v>1090.236891886567</v>
       </c>
       <c r="D199" t="n">
-        <v>1080.949883812057</v>
+        <v>1080.906328224564</v>
       </c>
       <c r="E199" t="n">
-        <v>1099.615043513826</v>
+        <v>1099.56745554857</v>
       </c>
       <c r="F199" t="n">
         <v>7597</v>
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1073.313890013196</v>
+        <v>1073.303947457442</v>
       </c>
       <c r="D200" t="n">
-        <v>1062.158880099823</v>
+        <v>1062.151639209076</v>
       </c>
       <c r="E200" t="n">
-        <v>1084.46889992657</v>
+        <v>1084.456255705807</v>
       </c>
       <c r="F200" t="n">
         <v>6328</v>
@@ -26752,13 +26752,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1070.228717981051</v>
+        <v>1070.196516754975</v>
       </c>
       <c r="D201" t="n">
-        <v>1060.360196927315</v>
+        <v>1060.332899612244</v>
       </c>
       <c r="E201" t="n">
-        <v>1080.097239034787</v>
+        <v>1080.060133897706</v>
       </c>
       <c r="F201" t="n">
         <v>6965</v>
@@ -26899,13 +26899,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1068.955124866701</v>
+        <v>1068.892479244509</v>
       </c>
       <c r="D202" t="n">
-        <v>1057.514341441038</v>
+        <v>1057.45651138124</v>
       </c>
       <c r="E202" t="n">
-        <v>1080.395908292365</v>
+        <v>1080.328447107778</v>
       </c>
       <c r="F202" t="n">
         <v>5745</v>
@@ -27046,13 +27046,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1066.699103441469</v>
+        <v>1066.650968091456</v>
       </c>
       <c r="D203" t="n">
-        <v>1051.504564046378</v>
+        <v>1051.462001054196</v>
       </c>
       <c r="E203" t="n">
-        <v>1081.89364283656</v>
+        <v>1081.839935128716</v>
       </c>
       <c r="F203" t="n">
         <v>1743</v>
@@ -27193,13 +27193,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1062.471570496746</v>
+        <v>1062.426017700593</v>
       </c>
       <c r="D204" t="n">
-        <v>1050.515149839461</v>
+        <v>1050.474244789412</v>
       </c>
       <c r="E204" t="n">
-        <v>1074.427991154031</v>
+        <v>1074.377790611773</v>
       </c>
       <c r="F204" t="n">
         <v>3924</v>
@@ -27340,13 +27340,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1055.821345144438</v>
+        <v>1055.780318419843</v>
       </c>
       <c r="D205" t="n">
-        <v>1044.166495809317</v>
+        <v>1044.128099520369</v>
       </c>
       <c r="E205" t="n">
-        <v>1067.476194479559</v>
+        <v>1067.432537319318</v>
       </c>
       <c r="F205" t="n">
         <v>4658</v>
@@ -27487,13 +27487,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1041.517800726481</v>
+        <v>1041.481097007839</v>
       </c>
       <c r="D206" t="n">
-        <v>1030.147119504652</v>
+        <v>1030.115195944468</v>
       </c>
       <c r="E206" t="n">
-        <v>1052.88848194831</v>
+        <v>1052.84699807121</v>
       </c>
       <c r="F206" t="n">
         <v>4845</v>
@@ -27634,13 +27634,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1024.015360050061</v>
+        <v>1023.976493147093</v>
       </c>
       <c r="D207" t="n">
-        <v>1010.439855240852</v>
+        <v>1010.404756291177</v>
       </c>
       <c r="E207" t="n">
-        <v>1037.59086485927</v>
+        <v>1037.54823000301</v>
       </c>
       <c r="F207" t="n">
         <v>2658</v>
@@ -27781,13 +27781,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1022.570792729038</v>
+        <v>1022.52335579856</v>
       </c>
       <c r="D208" t="n">
-        <v>1011.721145582726</v>
+        <v>1011.678606456661</v>
       </c>
       <c r="E208" t="n">
-        <v>1033.42043987535</v>
+        <v>1033.36810514046</v>
       </c>
       <c r="F208" t="n">
         <v>6310</v>
@@ -27928,13 +27928,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>995.1720085238692</v>
+        <v>995.1408976129484</v>
       </c>
       <c r="D209" t="n">
-        <v>982.6267116441543</v>
+        <v>982.6006515354721</v>
       </c>
       <c r="E209" t="n">
-        <v>1007.717305403584</v>
+        <v>1007.681143690425</v>
       </c>
       <c r="F209" t="n">
         <v>4914</v>
@@ -28075,13 +28075,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>991.7255588020982</v>
+        <v>991.6930994476862</v>
       </c>
       <c r="D210" t="n">
-        <v>979.3758762200318</v>
+        <v>979.3485325208255</v>
       </c>
       <c r="E210" t="n">
-        <v>1004.075241384165</v>
+        <v>1004.037666374547</v>
       </c>
       <c r="F210" t="n">
         <v>4203</v>
@@ -28222,13 +28222,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>981.3015755415313</v>
+        <v>981.2421710001014</v>
       </c>
       <c r="D211" t="n">
-        <v>967.8007826134151</v>
+        <v>967.7478704775899</v>
       </c>
       <c r="E211" t="n">
-        <v>994.8023684696475</v>
+        <v>994.736471522613</v>
       </c>
       <c r="F211" t="n">
         <v>3412</v>
@@ -28369,13 +28369,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>973.9081986981028</v>
+        <v>973.8547346559869</v>
       </c>
       <c r="D212" t="n">
-        <v>958.1490842147259</v>
+        <v>958.1039791243002</v>
       </c>
       <c r="E212" t="n">
-        <v>989.6673131814798</v>
+        <v>989.6054901876736</v>
       </c>
       <c r="F212" t="n">
         <v>2391</v>
@@ -28520,13 +28520,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>952.4811130028054</v>
+        <v>952.4479437638612</v>
       </c>
       <c r="D213" t="n">
-        <v>939.7829905879871</v>
+        <v>939.7563249171093</v>
       </c>
       <c r="E213" t="n">
-        <v>965.1792354176237</v>
+        <v>965.1395626106132</v>
       </c>
       <c r="F213" t="n">
         <v>3287</v>
@@ -29235,7 +29235,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -29438,38 +29438,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hy3</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>299</v>
-      </c>
-      <c r="C9" t="n">
-        <v>21</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v4-pro-high-preview</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro-high-preview</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>hy3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>299</v>
+      </c>
+      <c r="C10" t="n">
+        <v>21</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -29545,38 +29545,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>glm-4.7</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>qwen3.5-397b-a17b</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>397</v>
+      </c>
+      <c r="C14" t="n">
+        <v>17</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen3.5-397b-a17b</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>397</v>
-      </c>
-      <c r="C15" t="n">
-        <v>17</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>glm-4.7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29955,22 +29955,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-thinking</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+          <t>qwen3.5-122b-a10b</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>122</v>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>minimax-m2.7</t>
+          <t>deepseek-v3.1-thinking</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -29985,23 +29993,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>qwen3.5-122b-a10b</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>122</v>
-      </c>
-      <c r="C38" t="n">
-        <v>10</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>minimax-m2.7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -30268,14 +30268,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>qwen3.5-35b-a3b</t>
+          <t>qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>35</v>
+        <v>235</v>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -30291,14 +30291,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>qwen3-vl-235b-a22b-thinking</t>
+          <t>qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>235</v>
+        <v>35</v>
       </c>
       <c r="C52" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -31297,14 +31297,14 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>granite-4.1-8b</t>
+          <t>athene-70b-0725</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="C102" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -31320,14 +31320,14 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>athene-70b-0725</t>
+          <t>granite-4.1-8b</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="C103" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI216"/>
+  <dimension ref="A1:AI217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1486.750316014924</v>
+        <v>1488.781129842411</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1480.505797386725</v>
+        <v>1482.581166629291</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1492.994834643124</v>
+        <v>1494.981093055532</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11706</v>
+        <v>11969</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1470.279936412868</v>
+        <v>1470.984140727889</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1465.24539702994</v>
+        <v>1465.949215433624</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1475.314475795796</v>
+        <v>1476.019066022154</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>26703</v>
+        <v>26973</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1467.622040487751</v>
+        <v>1467.686386330761</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1463.488656369796</v>
+        <v>1463.566002403167</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1471.755424605707</v>
+        <v>1471.806770258356</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>50408</v>
+        <v>50731</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1466.585401445206</v>
+        <v>1467.395097692272</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1462.389053654117</v>
+        <v>1463.202872616917</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1470.781749236296</v>
+        <v>1471.587322767627</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>38905</v>
+        <v>39164</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1460.415836531118</v>
+        <v>1460.583891761103</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1455.874246009636</v>
+        <v>1456.042531162494</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1464.957427052601</v>
+        <v>1465.125252359712</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>37629</v>
+        <v>37613</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1458.022911482255</v>
+        <v>1458.176772613855</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1453.991744593816</v>
+        <v>1454.158913646344</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1462.054078370694</v>
+        <v>1462.194631581366</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>54048</v>
+        <v>54397</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1257,36 +1257,36 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>hy3</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1457.24484341368</v>
+        <v>1456.799693065835</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1448.37132070278</v>
+        <v>1452.458607304444</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1466.118366124579</v>
+        <v>1461.140778827227</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4648</v>
+        <v>27883</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Tencent</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>299</v>
+        <v>744</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
@@ -1299,22 +1299,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>598</v>
+        <v>1488</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>747.5</v>
+        <v>1860</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>299</v>
+        <v>744</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>373.8</v>
+        <v>930</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>149.5</v>
+        <v>372</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>186.9</v>
+        <v>465</v>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
@@ -1386,9 +1386,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH8" s="2" t="inlineStr">
@@ -1408,36 +1408,36 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>hy3</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1456.869255708922</v>
+        <v>1456.524907034572</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1452.526812777813</v>
+        <v>1447.666614862341</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1461.211698640031</v>
+        <v>1465.383199206803</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>27889</v>
+        <v>4664</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>Tencent</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>744</v>
+        <v>299</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1488</v>
+        <v>598</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1860</v>
+        <v>747.5</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>744</v>
+        <v>299</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>930</v>
+        <v>373.8</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>372</v>
+        <v>149.5</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>465</v>
+        <v>186.9</v>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
@@ -1537,9 +1537,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AG9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH9" s="2" t="inlineStr">
@@ -1563,16 +1563,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1455.92935205497</v>
+        <v>1455.512709132197</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1451.83320560914</v>
+        <v>1451.427221695185</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1460.025498500801</v>
+        <v>1459.598196569208</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>51483</v>
+        <v>51759</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1451.386151318299</v>
+        <v>1451.493605209364</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1443.799262036608</v>
+        <v>1443.904527578624</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1458.973040599989</v>
+        <v>1459.082682840104</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5904</v>
+        <v>5899</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1785,16 +1785,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1450.194501754211</v>
+        <v>1450.22204456523</v>
       </c>
       <c r="D12" t="n">
-        <v>1446.821847600555</v>
+        <v>1446.853979054858</v>
       </c>
       <c r="E12" t="n">
-        <v>1453.567155907866</v>
+        <v>1453.590110075603</v>
       </c>
       <c r="F12" t="n">
-        <v>70899</v>
+        <v>71065</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1443.33952385701</v>
+        <v>1443.644753299098</v>
       </c>
       <c r="D13" t="n">
-        <v>1438.665409466678</v>
+        <v>1438.986544927424</v>
       </c>
       <c r="E13" t="n">
-        <v>1448.013638247342</v>
+        <v>1448.302961670772</v>
       </c>
       <c r="F13" t="n">
-        <v>36969</v>
+        <v>37312</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1442.14330794641</v>
+        <v>1442.170447360424</v>
       </c>
       <c r="D14" t="n">
-        <v>1436.363167327271</v>
+        <v>1436.415771583655</v>
       </c>
       <c r="E14" t="n">
-        <v>1447.923448565549</v>
+        <v>1447.925123137192</v>
       </c>
       <c r="F14" t="n">
-        <v>14370</v>
+        <v>14695</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1442.066087075144</v>
+        <v>1441.846092163549</v>
       </c>
       <c r="D15" t="n">
-        <v>1438.552758197553</v>
+        <v>1438.343719178855</v>
       </c>
       <c r="E15" t="n">
-        <v>1445.579415952736</v>
+        <v>1445.348465148244</v>
       </c>
       <c r="F15" t="n">
-        <v>66437</v>
+        <v>66749</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2389,16 +2389,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1441.549025617567</v>
+        <v>1441.663908153963</v>
       </c>
       <c r="D16" t="n">
-        <v>1435.481516161933</v>
+        <v>1435.59598162204</v>
       </c>
       <c r="E16" t="n">
-        <v>1447.6165350732</v>
+        <v>1447.731834685887</v>
       </c>
       <c r="F16" t="n">
-        <v>12163</v>
+        <v>12162</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1438.302457804794</v>
+        <v>1438.212764136864</v>
       </c>
       <c r="D17" t="n">
-        <v>1430.675620920412</v>
+        <v>1430.58882374482</v>
       </c>
       <c r="E17" t="n">
-        <v>1445.929294689176</v>
+        <v>1445.836704528907</v>
       </c>
       <c r="F17" t="n">
-        <v>5810</v>
+        <v>5812</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1438.136096665946</v>
+        <v>1438.174645013408</v>
       </c>
       <c r="D18" t="n">
-        <v>1433.916243069547</v>
+        <v>1433.955712045503</v>
       </c>
       <c r="E18" t="n">
-        <v>1442.355950262345</v>
+        <v>1442.393577981313</v>
       </c>
       <c r="F18" t="n">
-        <v>48801</v>
+        <v>48807</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1435.357777574535</v>
+        <v>1435.419988918741</v>
       </c>
       <c r="D19" t="n">
-        <v>1431.204240383302</v>
+        <v>1431.268144067271</v>
       </c>
       <c r="E19" t="n">
-        <v>1439.511314765769</v>
+        <v>1439.57183377021</v>
       </c>
       <c r="F19" t="n">
-        <v>49111</v>
+        <v>49112</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1433.977929645352</v>
+        <v>1434.048796919047</v>
       </c>
       <c r="D20" t="n">
-        <v>1429.62777123051</v>
+        <v>1429.699581593459</v>
       </c>
       <c r="E20" t="n">
-        <v>1438.328088060193</v>
+        <v>1438.398012244634</v>
       </c>
       <c r="F20" t="n">
         <v>44647</v>
@@ -2904,16 +2904,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1430.839644509637</v>
+        <v>1430.72627297411</v>
       </c>
       <c r="D21" t="n">
-        <v>1424.261713471091</v>
+        <v>1424.148328576661</v>
       </c>
       <c r="E21" t="n">
-        <v>1437.417575548183</v>
+        <v>1437.304217371558</v>
       </c>
       <c r="F21" t="n">
-        <v>8192</v>
+        <v>8191</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1429.780702145006</v>
+        <v>1429.800599217875</v>
       </c>
       <c r="D22" t="n">
-        <v>1426.642486775718</v>
+        <v>1426.662805332744</v>
       </c>
       <c r="E22" t="n">
-        <v>1432.918917514293</v>
+        <v>1432.938393103007</v>
       </c>
       <c r="F22" t="n">
-        <v>62155</v>
+        <v>62149</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3206,16 +3206,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1426.942084125205</v>
+        <v>1427.197722840135</v>
       </c>
       <c r="D23" t="n">
-        <v>1420.376405455631</v>
+        <v>1420.630255455473</v>
       </c>
       <c r="E23" t="n">
-        <v>1433.507762794779</v>
+        <v>1433.765190224797</v>
       </c>
       <c r="F23" t="n">
-        <v>11024</v>
+        <v>11022</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1426.492437640138</v>
+        <v>1426.677769709305</v>
       </c>
       <c r="D24" t="n">
-        <v>1419.465490462946</v>
+        <v>1419.651597339411</v>
       </c>
       <c r="E24" t="n">
-        <v>1433.51938481733</v>
+        <v>1433.7039420792</v>
       </c>
       <c r="F24" t="n">
-        <v>10713</v>
+        <v>10712</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1425.90603701527</v>
+        <v>1425.934611127851</v>
       </c>
       <c r="D25" t="n">
-        <v>1415.993696120363</v>
+        <v>1416.018462261762</v>
       </c>
       <c r="E25" t="n">
-        <v>1435.818377910178</v>
+        <v>1435.850759993939</v>
       </c>
       <c r="F25" t="n">
-        <v>3736</v>
+        <v>3733</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3579,16 +3579,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1425.092200110333</v>
+        <v>1425.23029689488</v>
       </c>
       <c r="D26" t="n">
-        <v>1421.554158512147</v>
+        <v>1421.691757656985</v>
       </c>
       <c r="E26" t="n">
-        <v>1428.630241708518</v>
+        <v>1428.768836132775</v>
       </c>
       <c r="F26" t="n">
-        <v>47343</v>
+        <v>47336</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3650,16 +3650,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1425.077419658865</v>
+        <v>1425.004079583965</v>
       </c>
       <c r="D27" t="n">
-        <v>1418.541650141569</v>
+        <v>1418.468749154236</v>
       </c>
       <c r="E27" t="n">
-        <v>1431.613189176162</v>
+        <v>1431.539410013693</v>
       </c>
       <c r="F27" t="n">
-        <v>9114</v>
+        <v>9115</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3721,16 +3721,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1424.388430133969</v>
+        <v>1424.420417052967</v>
       </c>
       <c r="D28" t="n">
-        <v>1420.483302246218</v>
+        <v>1420.51562892585</v>
       </c>
       <c r="E28" t="n">
-        <v>1428.293558021719</v>
+        <v>1428.325205180084</v>
       </c>
       <c r="F28" t="n">
-        <v>35846</v>
+        <v>35848</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3792,16 +3792,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1422.935618351748</v>
+        <v>1422.955322778806</v>
       </c>
       <c r="D29" t="n">
-        <v>1420.35745872589</v>
+        <v>1420.377637627182</v>
       </c>
       <c r="E29" t="n">
-        <v>1425.513777977606</v>
+        <v>1425.533007930429</v>
       </c>
       <c r="F29" t="n">
-        <v>97499</v>
+        <v>97483</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3943,16 +3943,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1422.562457158232</v>
+        <v>1422.670723879759</v>
       </c>
       <c r="D30" t="n">
-        <v>1418.929143226669</v>
+        <v>1419.037752544667</v>
       </c>
       <c r="E30" t="n">
-        <v>1426.195771089795</v>
+        <v>1426.30369521485</v>
       </c>
       <c r="F30" t="n">
-        <v>41163</v>
+        <v>41153</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4014,16 +4014,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1422.426598002306</v>
+        <v>1422.56667898811</v>
       </c>
       <c r="D31" t="n">
-        <v>1416.039765755811</v>
+        <v>1416.17937450977</v>
       </c>
       <c r="E31" t="n">
-        <v>1428.813430248801</v>
+        <v>1428.95398346645</v>
       </c>
       <c r="F31" t="n">
-        <v>11988</v>
+        <v>11987</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4085,13 +4085,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1421.916788957516</v>
+        <v>1421.915381022731</v>
       </c>
       <c r="D32" t="n">
-        <v>1416.265628702251</v>
+        <v>1416.265005510908</v>
       </c>
       <c r="E32" t="n">
-        <v>1427.56794921278</v>
+        <v>1427.565756534553</v>
       </c>
       <c r="F32" t="n">
         <v>18501</v>
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1417.814338507811</v>
+        <v>1417.87640260337</v>
       </c>
       <c r="D33" t="n">
-        <v>1412.955896829034</v>
+        <v>1413.017484856932</v>
       </c>
       <c r="E33" t="n">
-        <v>1422.672780186588</v>
+        <v>1422.735320349808</v>
       </c>
       <c r="F33" t="n">
-        <v>27743</v>
+        <v>27741</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4307,16 +4307,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1417.637930986025</v>
+        <v>1417.856722386957</v>
       </c>
       <c r="D34" t="n">
-        <v>1411.151604728243</v>
+        <v>1411.369523560387</v>
       </c>
       <c r="E34" t="n">
-        <v>1424.124257243807</v>
+        <v>1424.343921213528</v>
       </c>
       <c r="F34" t="n">
-        <v>11825</v>
+        <v>11817</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4458,16 +4458,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1417.300704623699</v>
+        <v>1417.429458106913</v>
       </c>
       <c r="D35" t="n">
-        <v>1407.341181849424</v>
+        <v>1407.460559389956</v>
       </c>
       <c r="E35" t="n">
-        <v>1427.260227397974</v>
+        <v>1427.39835682387</v>
       </c>
       <c r="F35" t="n">
-        <v>3471</v>
+        <v>3464</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4529,16 +4529,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1417.258773047277</v>
+        <v>1417.212828370766</v>
       </c>
       <c r="D36" t="n">
-        <v>1411.261768144359</v>
+        <v>1411.216567142342</v>
       </c>
       <c r="E36" t="n">
-        <v>1423.255777950196</v>
+        <v>1423.209089599189</v>
       </c>
       <c r="F36" t="n">
-        <v>15027</v>
+        <v>15030</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4600,16 +4600,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1417.168826161181</v>
+        <v>1417.173009789125</v>
       </c>
       <c r="D37" t="n">
-        <v>1412.790210638337</v>
+        <v>1412.795691420858</v>
       </c>
       <c r="E37" t="n">
-        <v>1421.547441684026</v>
+        <v>1421.550328157393</v>
       </c>
       <c r="F37" t="n">
-        <v>28453</v>
+        <v>28449</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4751,16 +4751,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1416.256279544759</v>
+        <v>1416.470487256729</v>
       </c>
       <c r="D38" t="n">
-        <v>1409.655508708854</v>
+        <v>1409.8693783303</v>
       </c>
       <c r="E38" t="n">
-        <v>1422.857050380664</v>
+        <v>1423.071596183158</v>
       </c>
       <c r="F38" t="n">
-        <v>11797</v>
+        <v>11799</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4822,16 +4822,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1415.916302341394</v>
+        <v>1416.194240525814</v>
       </c>
       <c r="D39" t="n">
-        <v>1412.037002078692</v>
+        <v>1412.328046567709</v>
       </c>
       <c r="E39" t="n">
-        <v>1419.795602604097</v>
+        <v>1420.060434483918</v>
       </c>
       <c r="F39" t="n">
-        <v>58105</v>
+        <v>58418</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4893,16 +4893,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1414.871908076779</v>
+        <v>1414.689377300087</v>
       </c>
       <c r="D40" t="n">
-        <v>1411.69676617585</v>
+        <v>1411.520072590979</v>
       </c>
       <c r="E40" t="n">
-        <v>1418.047049977708</v>
+        <v>1417.858682009196</v>
       </c>
       <c r="F40" t="n">
-        <v>59005</v>
+        <v>59309</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5044,16 +5044,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1414.532327478801</v>
+        <v>1414.63403709797</v>
       </c>
       <c r="D41" t="n">
-        <v>1404.932694923452</v>
+        <v>1405.031839869112</v>
       </c>
       <c r="E41" t="n">
-        <v>1424.13196003415</v>
+        <v>1424.236234326828</v>
       </c>
       <c r="F41" t="n">
-        <v>3703</v>
+        <v>3701</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1414.333312521727</v>
+        <v>1414.41689180958</v>
       </c>
       <c r="D42" t="n">
-        <v>1407.870757781198</v>
+        <v>1407.951173226773</v>
       </c>
       <c r="E42" t="n">
-        <v>1420.795867262256</v>
+        <v>1420.882610392388</v>
       </c>
       <c r="F42" t="n">
-        <v>11565</v>
+        <v>11561</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5266,16 +5266,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1413.00554548076</v>
+        <v>1412.913966449644</v>
       </c>
       <c r="D43" t="n">
-        <v>1405.465989672353</v>
+        <v>1405.37556868389</v>
       </c>
       <c r="E43" t="n">
-        <v>1420.545101289167</v>
+        <v>1420.452364215398</v>
       </c>
       <c r="F43" t="n">
-        <v>6622</v>
+        <v>6624</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5337,16 +5337,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1411.188277940802</v>
+        <v>1411.280122547108</v>
       </c>
       <c r="D44" t="n">
-        <v>1406.316225825879</v>
+        <v>1406.405926568109</v>
       </c>
       <c r="E44" t="n">
-        <v>1416.060330055724</v>
+        <v>1416.154318526108</v>
       </c>
       <c r="F44" t="n">
-        <v>24430</v>
+        <v>24424</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5488,16 +5488,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1407.970944584401</v>
+        <v>1408.028117379305</v>
       </c>
       <c r="D45" t="n">
-        <v>1403.564215289899</v>
+        <v>1403.623808364765</v>
       </c>
       <c r="E45" t="n">
-        <v>1412.377673878904</v>
+        <v>1412.432426393845</v>
       </c>
       <c r="F45" t="n">
-        <v>27326</v>
+        <v>27333</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5639,16 +5639,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1402.603132402493</v>
+        <v>1402.595823457058</v>
       </c>
       <c r="D46" t="n">
-        <v>1398.102814615921</v>
+        <v>1398.095276960725</v>
       </c>
       <c r="E46" t="n">
-        <v>1407.103450189066</v>
+        <v>1407.096369953392</v>
       </c>
       <c r="F46" t="n">
-        <v>38298</v>
+        <v>38301</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1400.902380538676</v>
+        <v>1400.999081629521</v>
       </c>
       <c r="D47" t="n">
-        <v>1394.540735777302</v>
+        <v>1394.63899214124</v>
       </c>
       <c r="E47" t="n">
-        <v>1407.264025300049</v>
+        <v>1407.359171117803</v>
       </c>
       <c r="F47" t="n">
-        <v>11430</v>
+        <v>11431</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5941,16 +5941,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1400.844674692593</v>
+        <v>1400.72122720662</v>
       </c>
       <c r="D48" t="n">
-        <v>1396.084302601447</v>
+        <v>1395.962337576605</v>
       </c>
       <c r="E48" t="n">
-        <v>1405.60504678374</v>
+        <v>1405.480116836634</v>
       </c>
       <c r="F48" t="n">
-        <v>23014</v>
+        <v>23025</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6092,13 +6092,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1399.054252885672</v>
+        <v>1399.090849194745</v>
       </c>
       <c r="D49" t="n">
-        <v>1392.530486903531</v>
+        <v>1392.56727936563</v>
       </c>
       <c r="E49" t="n">
-        <v>1405.578018867813</v>
+        <v>1405.61441902386</v>
       </c>
       <c r="F49" t="n">
         <v>9019</v>
@@ -6243,13 +6243,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1398.182824630345</v>
+        <v>1398.176706696287</v>
       </c>
       <c r="D50" t="n">
-        <v>1393.297618018656</v>
+        <v>1393.29130668382</v>
       </c>
       <c r="E50" t="n">
-        <v>1403.068031242034</v>
+        <v>1403.062106708753</v>
       </c>
       <c r="F50" t="n">
         <v>18524</v>
@@ -6394,16 +6394,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1395.635461094635</v>
+        <v>1395.594257860655</v>
       </c>
       <c r="D51" t="n">
-        <v>1391.763423293164</v>
+        <v>1391.722350820527</v>
       </c>
       <c r="E51" t="n">
-        <v>1399.507498896105</v>
+        <v>1399.466164900784</v>
       </c>
       <c r="F51" t="n">
-        <v>45622</v>
+        <v>45629</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6545,16 +6545,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1395.488727576861</v>
+        <v>1395.492551949713</v>
       </c>
       <c r="D52" t="n">
-        <v>1391.161717937355</v>
+        <v>1391.167164885522</v>
       </c>
       <c r="E52" t="n">
-        <v>1399.815737216367</v>
+        <v>1399.817939013904</v>
       </c>
       <c r="F52" t="n">
-        <v>29135</v>
+        <v>29130</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6696,16 +6696,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1395.133503156681</v>
+        <v>1395.06216111191</v>
       </c>
       <c r="D53" t="n">
-        <v>1388.362773919311</v>
+        <v>1388.291742791544</v>
       </c>
       <c r="E53" t="n">
-        <v>1401.904232394051</v>
+        <v>1401.832579432275</v>
       </c>
       <c r="F53" t="n">
-        <v>7991</v>
+        <v>7988</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6847,16 +6847,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1394.584867146508</v>
+        <v>1394.52903687099</v>
       </c>
       <c r="D54" t="n">
-        <v>1390.941507023424</v>
+        <v>1390.88647061009</v>
       </c>
       <c r="E54" t="n">
-        <v>1398.228227269592</v>
+        <v>1398.17160313189</v>
       </c>
       <c r="F54" t="n">
-        <v>57538</v>
+        <v>57512</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1392.440202240106</v>
+        <v>1392.520872337639</v>
       </c>
       <c r="D55" t="n">
-        <v>1388.887537864686</v>
+        <v>1388.96916113672</v>
       </c>
       <c r="E55" t="n">
-        <v>1395.992866615525</v>
+        <v>1396.072583538557</v>
       </c>
       <c r="F55" t="n">
-        <v>46627</v>
+        <v>46634</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6989,16 +6989,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1390.271620120879</v>
+        <v>1390.225133612003</v>
       </c>
       <c r="D56" t="n">
-        <v>1386.288720151519</v>
+        <v>1386.24269121247</v>
       </c>
       <c r="E56" t="n">
-        <v>1394.254520090238</v>
+        <v>1394.207576011536</v>
       </c>
       <c r="F56" t="n">
-        <v>41074</v>
+        <v>41071</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7060,16 +7060,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1387.901748558186</v>
+        <v>1387.72706278512</v>
       </c>
       <c r="D57" t="n">
-        <v>1382.959479267039</v>
+        <v>1382.78474389059</v>
       </c>
       <c r="E57" t="n">
-        <v>1392.844017849334</v>
+        <v>1392.669381679651</v>
       </c>
       <c r="F57" t="n">
-        <v>25813</v>
+        <v>25814</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7211,16 +7211,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1386.457517575759</v>
+        <v>1386.258961508395</v>
       </c>
       <c r="D58" t="n">
-        <v>1380.220120033652</v>
+        <v>1380.019989405598</v>
       </c>
       <c r="E58" t="n">
-        <v>1392.694915117866</v>
+        <v>1392.497933611191</v>
       </c>
       <c r="F58" t="n">
-        <v>10993</v>
+        <v>10990</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7282,16 +7282,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1384.054799361758</v>
+        <v>1384.112575877281</v>
       </c>
       <c r="D59" t="n">
-        <v>1378.838914558725</v>
+        <v>1378.896613901841</v>
       </c>
       <c r="E59" t="n">
-        <v>1389.270684164791</v>
+        <v>1389.328537852721</v>
       </c>
       <c r="F59" t="n">
-        <v>17167</v>
+        <v>17164</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1383.35314132877</v>
+        <v>1383.259943713025</v>
       </c>
       <c r="D60" t="n">
-        <v>1378.480150021088</v>
+        <v>1378.386538202013</v>
       </c>
       <c r="E60" t="n">
-        <v>1388.226132636451</v>
+        <v>1388.133349224037</v>
       </c>
       <c r="F60" t="n">
-        <v>23848</v>
+        <v>23847</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7504,16 +7504,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1378.637021536235</v>
+        <v>1378.705934323486</v>
       </c>
       <c r="D61" t="n">
-        <v>1374.286561915323</v>
+        <v>1374.354370099727</v>
       </c>
       <c r="E61" t="n">
-        <v>1382.987481157146</v>
+        <v>1383.057498547244</v>
       </c>
       <c r="F61" t="n">
-        <v>29920</v>
+        <v>29909</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
@@ -7651,16 +7651,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1377.119074652247</v>
+        <v>1377.146180669873</v>
       </c>
       <c r="D62" t="n">
-        <v>1365.893589347446</v>
+        <v>1365.92103480203</v>
       </c>
       <c r="E62" t="n">
-        <v>1388.344559957049</v>
+        <v>1388.371326537716</v>
       </c>
       <c r="F62" t="n">
-        <v>2818</v>
+        <v>2819</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7722,13 +7722,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1374.787040405134</v>
+        <v>1374.845794875521</v>
       </c>
       <c r="D63" t="n">
-        <v>1370.09860598681</v>
+        <v>1370.156782506758</v>
       </c>
       <c r="E63" t="n">
-        <v>1379.475474823458</v>
+        <v>1379.534807244283</v>
       </c>
       <c r="F63" t="n">
         <v>26344</v>
@@ -7873,16 +7873,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1372.856788036608</v>
+        <v>1373.025922432196</v>
       </c>
       <c r="D64" t="n">
-        <v>1368.621063961076</v>
+        <v>1368.789558527176</v>
       </c>
       <c r="E64" t="n">
-        <v>1377.092512112141</v>
+        <v>1377.262286337217</v>
       </c>
       <c r="F64" t="n">
-        <v>31212</v>
+        <v>31220</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7940,73 +7940,69 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-thinking</t>
+          <t>trinity-large-thinking</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1369.244017508598</v>
+        <v>1369.223743305673</v>
       </c>
       <c r="D65" t="n">
-        <v>1363.416893122094</v>
+        <v>1364.540212185374</v>
       </c>
       <c r="E65" t="n">
-        <v>1375.071141895102</v>
+        <v>1373.907274425973</v>
       </c>
       <c r="F65" t="n">
-        <v>13757</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Alibaba</t>
-        </is>
-      </c>
+        <v>29034</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="N65" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="O65" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P65" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="Q65" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="R65" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="S65" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T65" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="T65" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="U65" s="6" t="inlineStr">
@@ -8044,9 +8040,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB65" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AB65" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AC65" s="6" t="inlineStr">
@@ -8076,12 +8072,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -8091,69 +8087,73 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>trinity-large-thinking</t>
+          <t>qwen3-next-80b-a3b-thinking</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1369.090118039954</v>
+        <v>1369.059340890126</v>
       </c>
       <c r="D66" t="n">
-        <v>1364.40553172455</v>
+        <v>1363.232952669638</v>
       </c>
       <c r="E66" t="n">
-        <v>1373.774704355359</v>
+        <v>1374.885729110616</v>
       </c>
       <c r="F66" t="n">
-        <v>29036</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
+        <v>13764</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J66" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="N66" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="O66" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P66" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="Q66" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R66" t="n">
-        <v>43.8</v>
+        <v>50</v>
       </c>
       <c r="S66" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="U66" s="6" t="inlineStr">
@@ -8191,9 +8191,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB66" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AB66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AC66" s="6" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>B300 SXM</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>H200 SXM</t>
         </is>
       </c>
     </row>
@@ -8242,16 +8242,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1367.349823219879</v>
+        <v>1367.416697121738</v>
       </c>
       <c r="D67" t="n">
-        <v>1361.566525930128</v>
+        <v>1361.633871702928</v>
       </c>
       <c r="E67" t="n">
-        <v>1373.133120509631</v>
+        <v>1373.199522540547</v>
       </c>
       <c r="F67" t="n">
-        <v>11757</v>
+        <v>11755</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8313,16 +8313,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1365.838258053205</v>
+        <v>1365.86565088486</v>
       </c>
       <c r="D68" t="n">
-        <v>1362.162552116624</v>
+        <v>1362.189851093661</v>
       </c>
       <c r="E68" t="n">
-        <v>1369.513963989785</v>
+        <v>1369.541450676059</v>
       </c>
       <c r="F68" t="n">
-        <v>47582</v>
+        <v>47585</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -8464,16 +8464,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1363.267455994777</v>
+        <v>1363.263954863842</v>
       </c>
       <c r="D69" t="n">
-        <v>1359.000254369595</v>
+        <v>1358.996690328642</v>
       </c>
       <c r="E69" t="n">
-        <v>1367.534657619958</v>
+        <v>1367.531219399041</v>
       </c>
       <c r="F69" t="n">
-        <v>35268</v>
+        <v>35269</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8535,16 +8535,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1360.496510525931</v>
+        <v>1360.473454689219</v>
       </c>
       <c r="D70" t="n">
-        <v>1353.234712506502</v>
+        <v>1353.2127342937</v>
       </c>
       <c r="E70" t="n">
-        <v>1367.758308545359</v>
+        <v>1367.734175084738</v>
       </c>
       <c r="F70" t="n">
-        <v>7535</v>
+        <v>7536</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8686,13 +8686,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1358.531627429615</v>
+        <v>1358.508010135937</v>
       </c>
       <c r="D71" t="n">
-        <v>1353.78270479922</v>
+        <v>1353.758938246473</v>
       </c>
       <c r="E71" t="n">
-        <v>1363.280550060011</v>
+        <v>1363.2570820254</v>
       </c>
       <c r="F71" t="n">
         <v>21770</v>
@@ -8837,16 +8837,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1357.149426492113</v>
+        <v>1357.104607028476</v>
       </c>
       <c r="D72" t="n">
-        <v>1351.952187396498</v>
+        <v>1351.907278144278</v>
       </c>
       <c r="E72" t="n">
-        <v>1362.346665587729</v>
+        <v>1362.301935912674</v>
       </c>
       <c r="F72" t="n">
-        <v>17771</v>
+        <v>17770</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8908,16 +8908,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1355.788312195036</v>
+        <v>1355.863890981623</v>
       </c>
       <c r="D73" t="n">
-        <v>1347.489155620709</v>
+        <v>1347.56304922341</v>
       </c>
       <c r="E73" t="n">
-        <v>1364.087468769362</v>
+        <v>1364.164732739836</v>
       </c>
       <c r="F73" t="n">
-        <v>5367</v>
+        <v>5364</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
@@ -9055,16 +9055,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1353.906194134383</v>
+        <v>1353.902862247206</v>
       </c>
       <c r="D74" t="n">
-        <v>1350.456186508316</v>
+        <v>1350.452381844408</v>
       </c>
       <c r="E74" t="n">
-        <v>1357.356201760449</v>
+        <v>1357.353342650004</v>
       </c>
       <c r="F74" t="n">
-        <v>56430</v>
+        <v>56431</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9126,16 +9126,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1353.416686039485</v>
+        <v>1353.387257216849</v>
       </c>
       <c r="D75" t="n">
-        <v>1345.086506770956</v>
+        <v>1345.056040317238</v>
       </c>
       <c r="E75" t="n">
-        <v>1361.746865308015</v>
+        <v>1361.718474116461</v>
       </c>
       <c r="F75" t="n">
-        <v>4973</v>
+        <v>4971</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9197,16 +9197,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1352.244176770489</v>
+        <v>1352.22563277945</v>
       </c>
       <c r="D76" t="n">
-        <v>1347.901363391055</v>
+        <v>1347.882677710242</v>
       </c>
       <c r="E76" t="n">
-        <v>1356.586990149923</v>
+        <v>1356.568587848659</v>
       </c>
       <c r="F76" t="n">
-        <v>30773</v>
+        <v>30775</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9348,16 +9348,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1348.324222844411</v>
+        <v>1348.472205819739</v>
       </c>
       <c r="D77" t="n">
-        <v>1340.932909139328</v>
+        <v>1341.078934693782</v>
       </c>
       <c r="E77" t="n">
-        <v>1355.715536549495</v>
+        <v>1355.865476945696</v>
       </c>
       <c r="F77" t="n">
-        <v>6563</v>
+        <v>6560</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9415,20 +9415,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1347.543736684946</v>
+        <v>1348.398056720802</v>
       </c>
       <c r="D78" t="n">
-        <v>1335.861120631825</v>
+        <v>1337.371413663934</v>
       </c>
       <c r="E78" t="n">
-        <v>1359.226352738066</v>
+        <v>1359.424699777671</v>
       </c>
       <c r="F78" t="n">
-        <v>2549</v>
+        <v>3282</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9437,18 +9437,18 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Nvidia Open Model</t>
+          <t>OpenMDW-1.1</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>253</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>253</v>
+        <v>3</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -9457,76 +9457,76 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>506</v>
+        <v>60</v>
       </c>
       <c r="N78" t="n">
-        <v>632.5</v>
+        <v>75</v>
       </c>
       <c r="O78" t="n">
-        <v>253</v>
+        <v>30</v>
       </c>
       <c r="P78" t="n">
-        <v>316.2</v>
+        <v>37.5</v>
       </c>
       <c r="Q78" t="n">
-        <v>126.5</v>
+        <v>15</v>
       </c>
       <c r="R78" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="S78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>18.8</v>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD78" s="6" t="inlineStr">
@@ -9534,14 +9534,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF78" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG78" s="6" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -9566,36 +9566,36 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1347.119267002607</v>
+        <v>1347.546579247577</v>
       </c>
       <c r="D79" t="n">
-        <v>1337.661459391887</v>
+        <v>1335.864197635284</v>
       </c>
       <c r="E79" t="n">
-        <v>1356.577074613326</v>
+        <v>1359.228960859871</v>
       </c>
       <c r="F79" t="n">
-        <v>3926</v>
+        <v>2549</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Nvidia Open Model</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="J79" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -9608,76 +9608,76 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>64</v>
+        <v>506</v>
       </c>
       <c r="N79" t="n">
-        <v>80</v>
+        <v>632.5</v>
       </c>
       <c r="O79" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="P79" t="n">
-        <v>40</v>
+        <v>316.2</v>
       </c>
       <c r="Q79" t="n">
-        <v>16</v>
+        <v>126.5</v>
       </c>
       <c r="R79" t="n">
-        <v>20</v>
-      </c>
-      <c r="S79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>158.1</v>
+      </c>
+      <c r="S79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD79" s="6" t="inlineStr">
@@ -9685,14 +9685,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF79" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF79" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG79" s="6" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -9717,68 +9717,148 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ling-flash-2.0</t>
+          <t>qwen3-32b</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1346.081810962993</v>
+        <v>1347.113666887958</v>
       </c>
       <c r="D80" t="n">
-        <v>1338.838862622206</v>
+        <v>1337.655891051511</v>
       </c>
       <c r="E80" t="n">
-        <v>1353.32475930378</v>
+        <v>1356.571442724404</v>
       </c>
       <c r="F80" t="n">
-        <v>7036</v>
+        <v>3926</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ant Group</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>32</v>
+      </c>
+      <c r="J80" t="n">
+        <v>32</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>64</v>
+      </c>
+      <c r="N80" t="n">
+        <v>80</v>
+      </c>
+      <c r="O80" t="n">
+        <v>32</v>
+      </c>
+      <c r="P80" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>16</v>
+      </c>
+      <c r="R80" t="n">
+        <v>20</v>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -9788,148 +9868,68 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>minimax-m2</t>
+          <t>ling-flash-2.0</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1345.793527385536</v>
+        <v>1346.052382401732</v>
       </c>
       <c r="D81" t="n">
-        <v>1338.087183895654</v>
+        <v>1338.811369426294</v>
       </c>
       <c r="E81" t="n">
-        <v>1353.499870875417</v>
+        <v>1353.29339537717</v>
       </c>
       <c r="F81" t="n">
-        <v>6913</v>
+        <v>7036</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MiniMax</t>
+          <t>Ant Group</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>230</v>
-      </c>
-      <c r="J81" t="n">
-        <v>10</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>460</v>
-      </c>
-      <c r="N81" t="n">
-        <v>575</v>
-      </c>
-      <c r="O81" t="n">
-        <v>230</v>
-      </c>
-      <c r="P81" t="n">
-        <v>287.5</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>115</v>
-      </c>
-      <c r="R81" t="n">
-        <v>143.8</v>
-      </c>
-      <c r="S81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>B300 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -9939,78 +9939,78 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nvidia-llama-3.3-nemotron-super-49b-v1.5</t>
+          <t>minimax-m2</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1343.317606439004</v>
+        <v>1345.554649777467</v>
       </c>
       <c r="D82" t="n">
-        <v>1333.375800037085</v>
+        <v>1337.849230229168</v>
       </c>
       <c r="E82" t="n">
-        <v>1353.259412840923</v>
+        <v>1353.260069325765</v>
       </c>
       <c r="F82" t="n">
-        <v>3359</v>
+        <v>6911</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>MiniMax</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Nvidia Open</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>49</v>
+        <v>230</v>
       </c>
       <c r="J82" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>98</v>
+        <v>460</v>
       </c>
       <c r="N82" t="n">
-        <v>122.5</v>
+        <v>575</v>
       </c>
       <c r="O82" t="n">
-        <v>49</v>
+        <v>230</v>
       </c>
       <c r="P82" t="n">
-        <v>61.2</v>
+        <v>287.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>24.5</v>
+        <v>115</v>
       </c>
       <c r="R82" t="n">
-        <v>30.6</v>
+        <v>143.8</v>
       </c>
       <c r="S82" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="T82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="T82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="V82" s="5" t="inlineStr">
@@ -10018,39 +10018,39 @@
           <t>No</t>
         </is>
       </c>
-      <c r="W82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="W82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD82" s="6" t="inlineStr">
@@ -10058,9 +10058,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE82" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AF82" s="6" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>H200 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>B300 SXM</t>
         </is>
       </c>
     </row>
@@ -10090,36 +10090,36 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>nvidia-llama-3.3-nemotron-super-49b-v1.5</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1341.904188117967</v>
+        <v>1343.128985383885</v>
       </c>
       <c r="D83" t="n">
-        <v>1332.394359284799</v>
+        <v>1333.187194806712</v>
       </c>
       <c r="E83" t="n">
-        <v>1351.414016951135</v>
+        <v>1353.070775961059</v>
       </c>
       <c r="F83" t="n">
-        <v>3829</v>
+        <v>3361</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Nvidia Open</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="J83" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -10132,26 +10132,26 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="N83" t="n">
-        <v>30</v>
+        <v>122.5</v>
       </c>
       <c r="O83" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="P83" t="n">
-        <v>15</v>
+        <v>61.2</v>
       </c>
       <c r="Q83" t="n">
-        <v>6</v>
+        <v>24.5</v>
       </c>
       <c r="R83" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S83" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>30.6</v>
+      </c>
+      <c r="S83" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="T83" s="6" t="inlineStr">
@@ -10164,9 +10164,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="V83" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="V83" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="W83" s="6" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>H200 SXM</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
@@ -10241,36 +10241,36 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>qwq-32b</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1335.870261437378</v>
+        <v>1341.913000567475</v>
       </c>
       <c r="D84" t="n">
-        <v>1331.429788500937</v>
+        <v>1332.403229855955</v>
       </c>
       <c r="E84" t="n">
-        <v>1340.31073437382</v>
+        <v>1351.422771278995</v>
       </c>
       <c r="F84" t="n">
-        <v>25444</v>
+        <v>3829</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J84" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -10283,22 +10283,22 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="N84" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="O84" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="P84" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="Q84" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R84" t="n">
-        <v>20</v>
+        <v>7.5</v>
       </c>
       <c r="S84" s="6" t="inlineStr">
         <is>
@@ -10392,36 +10392,36 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>llama-3.1-405b-instruct-bf16</t>
+          <t>qwq-32b</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1335.031642369924</v>
+        <v>1335.762100088099</v>
       </c>
       <c r="D85" t="n">
-        <v>1331.31148117295</v>
+        <v>1331.322023826646</v>
       </c>
       <c r="E85" t="n">
-        <v>1338.751803566898</v>
+        <v>1340.202176349553</v>
       </c>
       <c r="F85" t="n">
-        <v>41375</v>
+        <v>25443</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Llama 3.1 Community</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>405</v>
+        <v>32</v>
       </c>
       <c r="J85" t="n">
-        <v>405</v>
+        <v>32</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -10434,91 +10434,91 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>810</v>
+        <v>64</v>
       </c>
       <c r="N85" t="n">
-        <v>1012.5</v>
+        <v>80</v>
       </c>
       <c r="O85" t="n">
-        <v>405</v>
+        <v>32</v>
       </c>
       <c r="P85" t="n">
-        <v>506.2</v>
+        <v>40</v>
       </c>
       <c r="Q85" t="n">
-        <v>202.5</v>
+        <v>16</v>
       </c>
       <c r="R85" t="n">
-        <v>253.1</v>
-      </c>
-      <c r="S85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF85" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>20</v>
+      </c>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF85" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG85" s="6" t="inlineStr">
@@ -10528,12 +10528,12 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -10543,40 +10543,40 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+          <t>llama-3.1-405b-instruct-bf16</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1334.55861184463</v>
+        <v>1335.017598892682</v>
       </c>
       <c r="D86" t="n">
-        <v>1319.39558793289</v>
+        <v>1331.297296059037</v>
       </c>
       <c r="E86" t="n">
-        <v>1349.72163575637</v>
+        <v>1338.737901726328</v>
       </c>
       <c r="F86" t="n">
-        <v>1661</v>
+        <v>41375</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>OpenMDW-1.1</t>
+          <t>Llama 3.1 Community</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>30</v>
+        <v>405</v>
       </c>
       <c r="J86" t="n">
-        <v>3</v>
+        <v>405</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -10585,91 +10585,91 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N86" t="n">
-        <v>75</v>
+        <v>1012.5</v>
       </c>
       <c r="O86" t="n">
-        <v>30</v>
+        <v>405</v>
       </c>
       <c r="P86" t="n">
-        <v>37.5</v>
+        <v>506.2</v>
       </c>
       <c r="Q86" t="n">
-        <v>15</v>
+        <v>202.5</v>
       </c>
       <c r="R86" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF86" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>253.1</v>
+      </c>
+      <c r="S86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF86" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG86" s="6" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -10698,13 +10698,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1333.203543160049</v>
+        <v>1333.186912119569</v>
       </c>
       <c r="D87" t="n">
-        <v>1329.603159849965</v>
+        <v>1329.586581450126</v>
       </c>
       <c r="E87" t="n">
-        <v>1336.803926470134</v>
+        <v>1336.787242789012</v>
       </c>
       <c r="F87" t="n">
         <v>59656</v>
@@ -10849,16 +10849,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1329.43214844393</v>
+        <v>1329.471715816662</v>
       </c>
       <c r="D88" t="n">
-        <v>1323.368600145345</v>
+        <v>1323.409232515008</v>
       </c>
       <c r="E88" t="n">
-        <v>1335.495696742515</v>
+        <v>1335.534199118316</v>
       </c>
       <c r="F88" t="n">
-        <v>12275</v>
+        <v>12274</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -11000,16 +11000,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1329.341203462077</v>
+        <v>1329.001999892636</v>
       </c>
       <c r="D89" t="n">
-        <v>1308.118323312647</v>
+        <v>1307.800884489684</v>
       </c>
       <c r="E89" t="n">
-        <v>1350.564083611506</v>
+        <v>1350.203115295589</v>
       </c>
       <c r="F89" t="n">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -11151,13 +11151,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1328.006429887963</v>
+        <v>1327.992306376368</v>
       </c>
       <c r="D90" t="n">
-        <v>1315.86371565473</v>
+        <v>1315.849936466128</v>
       </c>
       <c r="E90" t="n">
-        <v>1340.149144121196</v>
+        <v>1340.134676286607</v>
       </c>
       <c r="F90" t="n">
         <v>2218</v>
@@ -11302,16 +11302,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1327.058407199629</v>
+        <v>1327.092664583822</v>
       </c>
       <c r="D91" t="n">
-        <v>1322.330542056414</v>
+        <v>1322.364696765349</v>
       </c>
       <c r="E91" t="n">
-        <v>1331.786272342842</v>
+        <v>1331.820632402295</v>
       </c>
       <c r="F91" t="n">
-        <v>26559</v>
+        <v>26562</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -11453,16 +11453,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1327.034880747436</v>
+        <v>1326.991686295978</v>
       </c>
       <c r="D92" t="n">
-        <v>1322.782289640437</v>
+        <v>1322.739166002127</v>
       </c>
       <c r="E92" t="n">
-        <v>1331.287471854434</v>
+        <v>1331.244206589829</v>
       </c>
       <c r="F92" t="n">
-        <v>40067</v>
+        <v>40064</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -11604,13 +11604,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1323.482424600847</v>
+        <v>1323.455232665951</v>
       </c>
       <c r="D93" t="n">
-        <v>1315.210447207715</v>
+        <v>1315.183296113074</v>
       </c>
       <c r="E93" t="n">
-        <v>1331.754401993978</v>
+        <v>1331.727169218829</v>
       </c>
       <c r="F93" t="n">
         <v>6795</v>
@@ -11675,16 +11675,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1322.425966465583</v>
+        <v>1322.488814460064</v>
       </c>
       <c r="D94" t="n">
-        <v>1317.719069969138</v>
+        <v>1317.782354263005</v>
       </c>
       <c r="E94" t="n">
-        <v>1327.132862962028</v>
+        <v>1327.195274657123</v>
       </c>
       <c r="F94" t="n">
-        <v>30397</v>
+        <v>30402</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11826,16 +11826,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1320.177426990843</v>
+        <v>1320.332677645817</v>
       </c>
       <c r="D95" t="n">
-        <v>1312.970006987932</v>
+        <v>1313.123407727231</v>
       </c>
       <c r="E95" t="n">
-        <v>1327.384846993755</v>
+        <v>1327.541947564403</v>
       </c>
       <c r="F95" t="n">
-        <v>7168</v>
+        <v>7165</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1318.243707660145</v>
+        <v>1318.232446879652</v>
       </c>
       <c r="D96" t="n">
-        <v>1314.761949894531</v>
+        <v>1314.750427895114</v>
       </c>
       <c r="E96" t="n">
-        <v>1321.725465425758</v>
+        <v>1321.714465864191</v>
       </c>
       <c r="F96" t="n">
         <v>54774</v>
@@ -12048,16 +12048,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1318.151559214733</v>
+        <v>1318.163492026871</v>
       </c>
       <c r="D97" t="n">
-        <v>1313.004990195966</v>
+        <v>1313.017137446835</v>
       </c>
       <c r="E97" t="n">
-        <v>1323.298128233501</v>
+        <v>1323.309846606908</v>
       </c>
       <c r="F97" t="n">
-        <v>22634</v>
+        <v>22635</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1318.073657522992</v>
+        <v>1318.048880593991</v>
       </c>
       <c r="D98" t="n">
-        <v>1312.371558178</v>
+        <v>1312.346874954489</v>
       </c>
       <c r="E98" t="n">
-        <v>1323.775756867983</v>
+        <v>1323.750886233493</v>
       </c>
       <c r="F98" t="n">
         <v>16478</v>
@@ -12270,16 +12270,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1317.541371224137</v>
+        <v>1317.539733964846</v>
       </c>
       <c r="D99" t="n">
-        <v>1311.18390723637</v>
+        <v>1311.182076042779</v>
       </c>
       <c r="E99" t="n">
-        <v>1323.898835211904</v>
+        <v>1323.897391886914</v>
       </c>
       <c r="F99" t="n">
-        <v>10678</v>
+        <v>10679</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -12421,16 +12421,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1315.161414047918</v>
+        <v>1315.132114554928</v>
       </c>
       <c r="D100" t="n">
-        <v>1309.639202123842</v>
+        <v>1309.610402381432</v>
       </c>
       <c r="E100" t="n">
-        <v>1320.683625971994</v>
+        <v>1320.653826728425</v>
       </c>
       <c r="F100" t="n">
-        <v>15588</v>
+        <v>15590</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -12572,13 +12572,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1314.295876216817</v>
+        <v>1314.264962244463</v>
       </c>
       <c r="D101" t="n">
-        <v>1309.737296244629</v>
+        <v>1309.706285338249</v>
       </c>
       <c r="E101" t="n">
-        <v>1318.854456189005</v>
+        <v>1318.823639150676</v>
       </c>
       <c r="F101" t="n">
         <v>24739</v>
@@ -12719,13 +12719,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1314.204018064579</v>
+        <v>1314.186255637364</v>
       </c>
       <c r="D102" t="n">
-        <v>1310.273635276407</v>
+        <v>1310.255936934789</v>
       </c>
       <c r="E102" t="n">
-        <v>1318.13440085275</v>
+        <v>1318.116574339938</v>
       </c>
       <c r="F102" t="n">
         <v>45459</v>
@@ -12870,13 +12870,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1307.194116520049</v>
+        <v>1307.169398899233</v>
       </c>
       <c r="D103" t="n">
-        <v>1302.484442943059</v>
+        <v>1302.459746725154</v>
       </c>
       <c r="E103" t="n">
-        <v>1311.90379009704</v>
+        <v>1311.879051073312</v>
       </c>
       <c r="F103" t="n">
         <v>24572</v>
@@ -12941,13 +12941,13 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1306.532649339426</v>
+        <v>1306.531379171373</v>
       </c>
       <c r="D104" t="n">
-        <v>1300.856960261314</v>
+        <v>1300.855802017237</v>
       </c>
       <c r="E104" t="n">
-        <v>1312.208338417538</v>
+        <v>1312.206956325509</v>
       </c>
       <c r="F104" t="n">
         <v>19621</v>
@@ -13088,16 +13088,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1305.660263602398</v>
+        <v>1305.891030049224</v>
       </c>
       <c r="D105" t="n">
-        <v>1295.483269187836</v>
+        <v>1295.714548752533</v>
       </c>
       <c r="E105" t="n">
-        <v>1315.837258016959</v>
+        <v>1316.067511345916</v>
       </c>
       <c r="F105" t="n">
-        <v>4031</v>
+        <v>4029</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -13235,68 +13235,148 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>mistral-large-2411</t>
+          <t>olmo-3-32b-think</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1305.411776332344</v>
+        <v>1305.397427367169</v>
       </c>
       <c r="D106" t="n">
-        <v>1300.967647765456</v>
+        <v>1297.234128559373</v>
       </c>
       <c r="E106" t="n">
-        <v>1309.855904899232</v>
+        <v>1313.560726174965</v>
       </c>
       <c r="F106" t="n">
-        <v>28073</v>
+        <v>5966</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Ai2</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>MRL</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>32</v>
+      </c>
+      <c r="J106" t="n">
+        <v>32</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
-      <c r="AB106" t="inlineStr"/>
-      <c r="AC106" t="inlineStr"/>
-      <c r="AD106" t="inlineStr"/>
-      <c r="AE106" t="inlineStr"/>
-      <c r="AF106" t="inlineStr"/>
-      <c r="AG106" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>64</v>
+      </c>
+      <c r="N106" t="n">
+        <v>80</v>
+      </c>
+      <c r="O106" t="n">
+        <v>32</v>
+      </c>
+      <c r="P106" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>16</v>
+      </c>
+      <c r="R106" t="n">
+        <v>20</v>
+      </c>
+      <c r="S106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -13306,148 +13386,68 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>olmo-3-32b-think</t>
+          <t>mistral-large-2411</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1305.259667589349</v>
+        <v>1305.39650343423</v>
       </c>
       <c r="D107" t="n">
-        <v>1297.09709942591</v>
+        <v>1300.95216906097</v>
       </c>
       <c r="E107" t="n">
-        <v>1313.422235752788</v>
+        <v>1309.84083780749</v>
       </c>
       <c r="F107" t="n">
-        <v>5967</v>
+        <v>28073</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ai2</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>32</v>
-      </c>
-      <c r="J107" t="n">
-        <v>32</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MRL</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M107" t="n">
-        <v>64</v>
-      </c>
-      <c r="N107" t="n">
-        <v>80</v>
-      </c>
-      <c r="O107" t="n">
-        <v>32</v>
-      </c>
-      <c r="P107" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>16</v>
-      </c>
-      <c r="R107" t="n">
-        <v>20</v>
-      </c>
-      <c r="S107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG107" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
+      <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -13461,16 +13461,16 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1303.403691955116</v>
+        <v>1303.52365345722</v>
       </c>
       <c r="D108" t="n">
-        <v>1298.899436760331</v>
+        <v>1299.020001354138</v>
       </c>
       <c r="E108" t="n">
-        <v>1307.9079471499</v>
+        <v>1308.027305560304</v>
       </c>
       <c r="F108" t="n">
-        <v>33317</v>
+        <v>33315</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -13612,13 +13612,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1303.338662241036</v>
+        <v>1303.348790843517</v>
       </c>
       <c r="D109" t="n">
-        <v>1294.022656548439</v>
+        <v>1294.032847896395</v>
       </c>
       <c r="E109" t="n">
-        <v>1312.654667933634</v>
+        <v>1312.66473379064</v>
       </c>
       <c r="F109" t="n">
         <v>4171</v>
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1302.891094845612</v>
+        <v>1302.866026746174</v>
       </c>
       <c r="D110" t="n">
-        <v>1298.811044436995</v>
+        <v>1298.785900380629</v>
       </c>
       <c r="E110" t="n">
-        <v>1306.971145254228</v>
+        <v>1306.946153111719</v>
       </c>
       <c r="F110" t="n">
         <v>39406</v>
@@ -13914,13 +13914,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1298.996840045141</v>
+        <v>1298.980177502928</v>
       </c>
       <c r="D111" t="n">
-        <v>1291.233384785894</v>
+        <v>1291.216808159209</v>
       </c>
       <c r="E111" t="n">
-        <v>1306.760295304388</v>
+        <v>1306.743546846646</v>
       </c>
       <c r="F111" t="n">
         <v>7140</v>
@@ -14065,13 +14065,13 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1293.293291397517</v>
+        <v>1293.2773340231</v>
       </c>
       <c r="D112" t="n">
-        <v>1289.551731405219</v>
+        <v>1289.535772505926</v>
       </c>
       <c r="E112" t="n">
-        <v>1297.034851389814</v>
+        <v>1297.018895540274</v>
       </c>
       <c r="F112" t="n">
         <v>55240</v>
@@ -14216,13 +14216,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1289.261240370127</v>
+        <v>1289.247670959448</v>
       </c>
       <c r="D113" t="n">
-        <v>1281.953960850186</v>
+        <v>1281.94053947878</v>
       </c>
       <c r="E113" t="n">
-        <v>1296.568519890069</v>
+        <v>1296.554802440116</v>
       </c>
       <c r="F113" t="n">
         <v>8662</v>
@@ -14283,13 +14283,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1289.235784876286</v>
+        <v>1289.245644445079</v>
       </c>
       <c r="D114" t="n">
-        <v>1285.847360838937</v>
+        <v>1285.857180670793</v>
       </c>
       <c r="E114" t="n">
-        <v>1292.624208913635</v>
+        <v>1292.634108219364</v>
       </c>
       <c r="F114" t="n">
         <v>75754</v>
@@ -14434,16 +14434,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1286.585910597176</v>
+        <v>1287.008028511682</v>
       </c>
       <c r="D115" t="n">
-        <v>1278.217730607273</v>
+        <v>1278.643933063635</v>
       </c>
       <c r="E115" t="n">
-        <v>1294.95409058708</v>
+        <v>1295.372123959728</v>
       </c>
       <c r="F115" t="n">
-        <v>5720</v>
+        <v>5722</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -14585,13 +14585,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1286.197355015997</v>
+        <v>1286.182754395246</v>
       </c>
       <c r="D116" t="n">
-        <v>1276.226522351771</v>
+        <v>1276.212109227021</v>
       </c>
       <c r="E116" t="n">
-        <v>1296.168187680224</v>
+        <v>1296.153399563471</v>
       </c>
       <c r="F116" t="n">
         <v>3749</v>
@@ -14736,13 +14736,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1286.019028031513</v>
+        <v>1285.993212512633</v>
       </c>
       <c r="D117" t="n">
-        <v>1275.55395886096</v>
+        <v>1275.528365775848</v>
       </c>
       <c r="E117" t="n">
-        <v>1296.484097202067</v>
+        <v>1296.458059249417</v>
       </c>
       <c r="F117" t="n">
         <v>2846</v>
@@ -14887,16 +14887,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1285.040637247358</v>
+        <v>1285.162277325502</v>
       </c>
       <c r="D118" t="n">
-        <v>1277.859306965295</v>
+        <v>1277.978671827901</v>
       </c>
       <c r="E118" t="n">
-        <v>1292.221967529422</v>
+        <v>1292.345882823103</v>
       </c>
       <c r="F118" t="n">
-        <v>8556</v>
+        <v>8551</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -15038,13 +15038,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1280.182673746894</v>
+        <v>1280.188091980458</v>
       </c>
       <c r="D119" t="n">
-        <v>1273.322401569155</v>
+        <v>1273.328020288122</v>
       </c>
       <c r="E119" t="n">
-        <v>1287.042945924633</v>
+        <v>1287.048163672794</v>
       </c>
       <c r="F119" t="n">
         <v>10072</v>
@@ -15185,13 +15185,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1276.742187172593</v>
+        <v>1276.718000300793</v>
       </c>
       <c r="D120" t="n">
-        <v>1271.417274208809</v>
+        <v>1271.39341330589</v>
       </c>
       <c r="E120" t="n">
-        <v>1282.067100136377</v>
+        <v>1282.042587295695</v>
       </c>
       <c r="F120" t="n">
         <v>19659</v>
@@ -15336,13 +15336,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1276.215403967223</v>
+        <v>1276.207456035149</v>
       </c>
       <c r="D121" t="n">
-        <v>1272.626426256043</v>
+        <v>1272.618812551476</v>
       </c>
       <c r="E121" t="n">
-        <v>1279.804381678403</v>
+        <v>1279.796099518823</v>
       </c>
       <c r="F121" t="n">
         <v>156876</v>
@@ -15487,13 +15487,13 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1275.994395247733</v>
+        <v>1275.970267182646</v>
       </c>
       <c r="D122" t="n">
-        <v>1269.415398883267</v>
+        <v>1269.39137769014</v>
       </c>
       <c r="E122" t="n">
-        <v>1282.573391612199</v>
+        <v>1282.549156675152</v>
       </c>
       <c r="F122" t="n">
         <v>9866</v>
@@ -15638,13 +15638,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1274.226172511242</v>
+        <v>1274.213083835784</v>
       </c>
       <c r="D123" t="n">
-        <v>1268.313533227676</v>
+        <v>1268.30026626207</v>
       </c>
       <c r="E123" t="n">
-        <v>1280.138811794807</v>
+        <v>1280.125901409498</v>
       </c>
       <c r="F123" t="n">
         <v>14681</v>
@@ -15789,13 +15789,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1270.504565945038</v>
+        <v>1270.479790144968</v>
       </c>
       <c r="D124" t="n">
-        <v>1262.37580822142</v>
+        <v>1262.351079327728</v>
       </c>
       <c r="E124" t="n">
-        <v>1278.633323668656</v>
+        <v>1278.608500962207</v>
       </c>
       <c r="F124" t="n">
         <v>5432</v>
@@ -15940,13 +15940,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1267.080813512308</v>
+        <v>1267.069303633542</v>
       </c>
       <c r="D125" t="n">
-        <v>1262.187660209432</v>
+        <v>1262.176081625002</v>
       </c>
       <c r="E125" t="n">
-        <v>1271.973966815184</v>
+        <v>1271.962525642081</v>
       </c>
       <c r="F125" t="n">
         <v>27124</v>
@@ -16091,13 +16091,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1266.758149646088</v>
+        <v>1266.76875061256</v>
       </c>
       <c r="D126" t="n">
-        <v>1262.933621641178</v>
+        <v>1262.944177068923</v>
       </c>
       <c r="E126" t="n">
-        <v>1270.582677650998</v>
+        <v>1270.593324156197</v>
       </c>
       <c r="F126" t="n">
         <v>54611</v>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1264.886639787378</v>
+        <v>1264.883676560127</v>
       </c>
       <c r="D127" t="n">
-        <v>1258.607577808377</v>
+        <v>1258.604903844916</v>
       </c>
       <c r="E127" t="n">
-        <v>1271.16570176638</v>
+        <v>1271.162449275338</v>
       </c>
       <c r="F127" t="n">
         <v>15147</v>
@@ -16393,13 +16393,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1261.372194235678</v>
+        <v>1261.351985125685</v>
       </c>
       <c r="D128" t="n">
-        <v>1256.422880693191</v>
+        <v>1256.40285769823</v>
       </c>
       <c r="E128" t="n">
-        <v>1266.321507778165</v>
+        <v>1266.30111255314</v>
       </c>
       <c r="F128" t="n">
         <v>37325</v>
@@ -16544,13 +16544,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1261.309644966367</v>
+        <v>1261.284659139727</v>
       </c>
       <c r="D129" t="n">
-        <v>1256.985799371722</v>
+        <v>1256.961167329298</v>
       </c>
       <c r="E129" t="n">
-        <v>1265.633490561011</v>
+        <v>1265.608150950156</v>
       </c>
       <c r="F129" t="n">
         <v>77554</v>
@@ -16615,13 +16615,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1256.161766198998</v>
+        <v>1256.147318464701</v>
       </c>
       <c r="D130" t="n">
-        <v>1251.561442221454</v>
+        <v>1251.546816805643</v>
       </c>
       <c r="E130" t="n">
-        <v>1260.762090176542</v>
+        <v>1260.74782012376</v>
       </c>
       <c r="F130" t="n">
         <v>24126</v>
@@ -16766,13 +16766,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1251.433949374829</v>
+        <v>1251.42244921075</v>
       </c>
       <c r="D131" t="n">
-        <v>1240.653688521884</v>
+        <v>1240.642332536387</v>
       </c>
       <c r="E131" t="n">
-        <v>1262.214210227774</v>
+        <v>1262.202565885113</v>
       </c>
       <c r="F131" t="n">
         <v>3334</v>
@@ -16917,13 +16917,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1249.948686615397</v>
+        <v>1249.93084182217</v>
       </c>
       <c r="D132" t="n">
-        <v>1243.344994479791</v>
+        <v>1243.327220038958</v>
       </c>
       <c r="E132" t="n">
-        <v>1256.552378751002</v>
+        <v>1256.534463605382</v>
       </c>
       <c r="F132" t="n">
         <v>10140</v>
@@ -17068,13 +17068,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1239.585280418048</v>
+        <v>1239.577881677708</v>
       </c>
       <c r="D133" t="n">
-        <v>1232.35759058679</v>
+        <v>1232.350326776956</v>
       </c>
       <c r="E133" t="n">
-        <v>1246.812970249306</v>
+        <v>1246.805436578459</v>
       </c>
       <c r="F133" t="n">
         <v>8858</v>
@@ -17135,13 +17135,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1237.466107250028</v>
+        <v>1237.447455346247</v>
       </c>
       <c r="D134" t="n">
-        <v>1228.373460026722</v>
+        <v>1228.354971959276</v>
       </c>
       <c r="E134" t="n">
-        <v>1246.558754473336</v>
+        <v>1246.539938733219</v>
       </c>
       <c r="F134" t="n">
         <v>4781</v>
@@ -17286,13 +17286,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1233.747422442671</v>
+        <v>1233.73068258685</v>
       </c>
       <c r="D135" t="n">
-        <v>1228.195026076811</v>
+        <v>1228.17859702916</v>
       </c>
       <c r="E135" t="n">
-        <v>1239.299818808531</v>
+        <v>1239.28276814454</v>
       </c>
       <c r="F135" t="n">
         <v>26195</v>
@@ -17437,13 +17437,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1232.998881461725</v>
+        <v>1232.983982346298</v>
       </c>
       <c r="D136" t="n">
-        <v>1227.725104811513</v>
+        <v>1227.710549683439</v>
       </c>
       <c r="E136" t="n">
-        <v>1238.272658111938</v>
+        <v>1238.257415009157</v>
       </c>
       <c r="F136" t="n">
         <v>39302</v>
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1229.018417261755</v>
+        <v>1228.998600157647</v>
       </c>
       <c r="D137" t="n">
-        <v>1224.46034756855</v>
+        <v>1224.440809340181</v>
       </c>
       <c r="E137" t="n">
-        <v>1233.576486954959</v>
+        <v>1233.556390975114</v>
       </c>
       <c r="F137" t="n">
         <v>51416</v>
@@ -17739,13 +17739,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1226.336017986081</v>
+        <v>1226.312531859611</v>
       </c>
       <c r="D138" t="n">
-        <v>1221.55364051116</v>
+        <v>1221.530484949586</v>
       </c>
       <c r="E138" t="n">
-        <v>1231.118395461002</v>
+        <v>1231.094578769635</v>
       </c>
       <c r="F138" t="n">
         <v>54036</v>
@@ -17810,13 +17810,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1223.257864285247</v>
+        <v>1223.247462094905</v>
       </c>
       <c r="D139" t="n">
-        <v>1219.518397022124</v>
+        <v>1219.508317655488</v>
       </c>
       <c r="E139" t="n">
-        <v>1226.99733154837</v>
+        <v>1226.986606534323</v>
       </c>
       <c r="F139" t="n">
         <v>104642</v>
@@ -17961,13 +17961,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1222.976266641242</v>
+        <v>1222.963510617166</v>
       </c>
       <c r="D140" t="n">
-        <v>1215.999948245125</v>
+        <v>1215.987168873119</v>
       </c>
       <c r="E140" t="n">
-        <v>1229.952585037359</v>
+        <v>1229.939852361213</v>
       </c>
       <c r="F140" t="n">
         <v>9818</v>
@@ -18112,13 +18112,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1220.481597174947</v>
+        <v>1220.454733247285</v>
       </c>
       <c r="D141" t="n">
-        <v>1209.805032774893</v>
+        <v>1209.778394450424</v>
       </c>
       <c r="E141" t="n">
-        <v>1231.158161575001</v>
+        <v>1231.131072044146</v>
       </c>
       <c r="F141" t="n">
         <v>2896</v>
@@ -18263,13 +18263,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1212.624646895381</v>
+        <v>1212.594894255344</v>
       </c>
       <c r="D142" t="n">
-        <v>1207.585513331289</v>
+        <v>1207.556047315652</v>
       </c>
       <c r="E142" t="n">
-        <v>1217.663780459473</v>
+        <v>1217.633741195037</v>
       </c>
       <c r="F142" t="n">
         <v>24146</v>
@@ -18410,13 +18410,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1212.453120110565</v>
+        <v>1212.434571019802</v>
       </c>
       <c r="D143" t="n">
-        <v>1201.666716825485</v>
+        <v>1201.648537609596</v>
       </c>
       <c r="E143" t="n">
-        <v>1223.239523395644</v>
+        <v>1223.220604430009</v>
       </c>
       <c r="F143" t="n">
         <v>4652</v>
@@ -18557,13 +18557,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1211.330889113191</v>
+        <v>1211.307223187769</v>
       </c>
       <c r="D144" t="n">
-        <v>1207.175188870493</v>
+        <v>1207.151479022463</v>
       </c>
       <c r="E144" t="n">
-        <v>1215.48658935589</v>
+        <v>1215.462967353076</v>
       </c>
       <c r="F144" t="n">
         <v>49605</v>
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1208.065173763156</v>
+        <v>1208.046053227772</v>
       </c>
       <c r="D145" t="n">
-        <v>1196.96505240168</v>
+        <v>1196.946122164</v>
       </c>
       <c r="E145" t="n">
-        <v>1219.165295124632</v>
+        <v>1219.145984291544</v>
       </c>
       <c r="F145" t="n">
         <v>3090</v>
@@ -18859,13 +18859,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1203.44355875821</v>
+        <v>1203.423723984732</v>
       </c>
       <c r="D146" t="n">
-        <v>1197.326609347513</v>
+        <v>1197.307083416286</v>
       </c>
       <c r="E146" t="n">
-        <v>1209.560508168907</v>
+        <v>1209.540364553178</v>
       </c>
       <c r="F146" t="n">
         <v>21741</v>
@@ -19010,13 +19010,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1200.056255940968</v>
+        <v>1200.065399251806</v>
       </c>
       <c r="D147" t="n">
-        <v>1195.95764306909</v>
+        <v>1195.966710543175</v>
       </c>
       <c r="E147" t="n">
-        <v>1204.154868812845</v>
+        <v>1204.164087960436</v>
       </c>
       <c r="F147" t="n">
         <v>46616</v>
@@ -19161,13 +19161,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1197.430304081479</v>
+        <v>1197.406930066381</v>
       </c>
       <c r="D148" t="n">
-        <v>1192.268814437454</v>
+        <v>1192.245643526382</v>
       </c>
       <c r="E148" t="n">
-        <v>1202.591793725504</v>
+        <v>1202.56821660638</v>
       </c>
       <c r="F148" t="n">
         <v>25055</v>
@@ -19312,13 +19312,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1196.613715318406</v>
+        <v>1196.591563592367</v>
       </c>
       <c r="D149" t="n">
-        <v>1192.345973924116</v>
+        <v>1192.324255860263</v>
       </c>
       <c r="E149" t="n">
-        <v>1200.881456712697</v>
+        <v>1200.858871324471</v>
       </c>
       <c r="F149" t="n">
         <v>73503</v>
@@ -19463,13 +19463,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1194.869592108415</v>
+        <v>1194.855144449444</v>
       </c>
       <c r="D150" t="n">
-        <v>1188.757252681653</v>
+        <v>1188.743105668236</v>
       </c>
       <c r="E150" t="n">
-        <v>1200.981931535176</v>
+        <v>1200.967183230651</v>
       </c>
       <c r="F150" t="n">
         <v>32191</v>
@@ -19530,13 +19530,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1190.639952326726</v>
+        <v>1190.613875874978</v>
       </c>
       <c r="D151" t="n">
-        <v>1183.455157471803</v>
+        <v>1183.429201122127</v>
       </c>
       <c r="E151" t="n">
-        <v>1197.82474718165</v>
+        <v>1197.798550627828</v>
       </c>
       <c r="F151" t="n">
         <v>9901</v>
@@ -19677,13 +19677,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1190.587168565895</v>
+        <v>1190.568947517813</v>
       </c>
       <c r="D152" t="n">
-        <v>1183.471384920846</v>
+        <v>1183.45352010727</v>
       </c>
       <c r="E152" t="n">
-        <v>1197.702952210944</v>
+        <v>1197.684374928356</v>
       </c>
       <c r="F152" t="n">
         <v>17839</v>
@@ -19828,13 +19828,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1184.251734746276</v>
+        <v>1184.238090619048</v>
       </c>
       <c r="D153" t="n">
-        <v>1172.772348273964</v>
+        <v>1172.759265613051</v>
       </c>
       <c r="E153" t="n">
-        <v>1195.731121218588</v>
+        <v>1195.716915625046</v>
       </c>
       <c r="F153" t="n">
         <v>4932</v>
@@ -19979,13 +19979,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1184.21138445616</v>
+        <v>1184.189896298091</v>
       </c>
       <c r="D154" t="n">
-        <v>1174.778354463818</v>
+        <v>1174.757313301403</v>
       </c>
       <c r="E154" t="n">
-        <v>1193.644414448501</v>
+        <v>1193.622479294779</v>
       </c>
       <c r="F154" t="n">
         <v>8214</v>
@@ -20130,13 +20130,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1183.346325671491</v>
+        <v>1183.326192445377</v>
       </c>
       <c r="D155" t="n">
-        <v>1176.521233046519</v>
+        <v>1176.50139211559</v>
       </c>
       <c r="E155" t="n">
-        <v>1190.171418296463</v>
+        <v>1190.150992775164</v>
       </c>
       <c r="F155" t="n">
         <v>15483</v>
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1182.437988034403</v>
+        <v>1182.432660156082</v>
       </c>
       <c r="D156" t="n">
-        <v>1173.7586997726</v>
+        <v>1173.75360568054</v>
       </c>
       <c r="E156" t="n">
-        <v>1191.117276296206</v>
+        <v>1191.111714631623</v>
       </c>
       <c r="F156" t="n">
         <v>6638</v>
@@ -20428,13 +20428,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1182.31769593714</v>
+        <v>1182.308727599118</v>
       </c>
       <c r="D157" t="n">
-        <v>1172.662259032911</v>
+        <v>1172.653738306396</v>
       </c>
       <c r="E157" t="n">
-        <v>1191.97313284137</v>
+        <v>1191.96371689184</v>
       </c>
       <c r="F157" t="n">
         <v>7968</v>
@@ -20495,13 +20495,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1182.106090192474</v>
+        <v>1182.091086315385</v>
       </c>
       <c r="D158" t="n">
-        <v>1174.115465360798</v>
+        <v>1174.100800745372</v>
       </c>
       <c r="E158" t="n">
-        <v>1190.09671502415</v>
+        <v>1190.081371885398</v>
       </c>
       <c r="F158" t="n">
         <v>12637</v>
@@ -20562,13 +20562,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1182.044563297082</v>
+        <v>1182.066809312749</v>
       </c>
       <c r="D159" t="n">
-        <v>1175.974699872598</v>
+        <v>1175.997238857899</v>
       </c>
       <c r="E159" t="n">
-        <v>1188.114426721565</v>
+        <v>1188.136379767599</v>
       </c>
       <c r="F159" t="n">
         <v>23893</v>
@@ -20713,13 +20713,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1179.380867815527</v>
+        <v>1179.367211041221</v>
       </c>
       <c r="D160" t="n">
-        <v>1173.470294662636</v>
+        <v>1173.456957493315</v>
       </c>
       <c r="E160" t="n">
-        <v>1185.291440968418</v>
+        <v>1185.277464589127</v>
       </c>
       <c r="F160" t="n">
         <v>32832</v>
@@ -20780,13 +20780,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1178.520372497244</v>
+        <v>1178.49955605377</v>
       </c>
       <c r="D161" t="n">
-        <v>1167.331733641782</v>
+        <v>1167.311236971967</v>
       </c>
       <c r="E161" t="n">
-        <v>1189.709011352707</v>
+        <v>1189.687875135574</v>
       </c>
       <c r="F161" t="n">
         <v>3188</v>
@@ -20931,13 +20931,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1177.197035735856</v>
+        <v>1177.168733436678</v>
       </c>
       <c r="D162" t="n">
-        <v>1167.39476718385</v>
+        <v>1167.366882481796</v>
       </c>
       <c r="E162" t="n">
-        <v>1186.999304287861</v>
+        <v>1186.970584391559</v>
       </c>
       <c r="F162" t="n">
         <v>6535</v>
@@ -21078,13 +21078,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1175.252956192025</v>
+        <v>1175.242762692708</v>
       </c>
       <c r="D163" t="n">
-        <v>1164.852251931965</v>
+        <v>1164.842497193406</v>
       </c>
       <c r="E163" t="n">
-        <v>1185.653660452084</v>
+        <v>1185.643028192011</v>
       </c>
       <c r="F163" t="n">
         <v>5006</v>
@@ -21225,13 +21225,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1172.374676484133</v>
+        <v>1172.354241301882</v>
       </c>
       <c r="D164" t="n">
-        <v>1166.177308038003</v>
+        <v>1166.157336604361</v>
       </c>
       <c r="E164" t="n">
-        <v>1178.572044930264</v>
+        <v>1178.551145999404</v>
       </c>
       <c r="F164" t="n">
         <v>22479</v>
@@ -21372,13 +21372,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1170.70338009248</v>
+        <v>1170.667965748125</v>
       </c>
       <c r="D165" t="n">
-        <v>1163.301131329324</v>
+        <v>1163.266087384102</v>
       </c>
       <c r="E165" t="n">
-        <v>1178.105628855635</v>
+        <v>1178.069844112149</v>
       </c>
       <c r="F165" t="n">
         <v>16056</v>
@@ -21519,13 +21519,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1170.60335180501</v>
+        <v>1170.58185043105</v>
       </c>
       <c r="D166" t="n">
-        <v>1164.687689788857</v>
+        <v>1164.666457601335</v>
       </c>
       <c r="E166" t="n">
-        <v>1176.519013821163</v>
+        <v>1176.497243260765</v>
       </c>
       <c r="F166" t="n">
         <v>17766</v>
@@ -21670,13 +21670,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1170.218005575508</v>
+        <v>1170.192874392491</v>
       </c>
       <c r="D167" t="n">
-        <v>1164.723043152129</v>
+        <v>1164.698346285267</v>
       </c>
       <c r="E167" t="n">
-        <v>1175.712967998888</v>
+        <v>1175.687402499716</v>
       </c>
       <c r="F167" t="n">
         <v>38492</v>
@@ -21821,13 +21821,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1166.932032958529</v>
+        <v>1166.907044711196</v>
       </c>
       <c r="D168" t="n">
-        <v>1158.87216845471</v>
+        <v>1158.847500861529</v>
       </c>
       <c r="E168" t="n">
-        <v>1174.991897462348</v>
+        <v>1174.966588560864</v>
       </c>
       <c r="F168" t="n">
         <v>10224</v>
@@ -21968,13 +21968,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1166.42231975306</v>
+        <v>1166.406216386473</v>
       </c>
       <c r="D169" t="n">
-        <v>1158.717122955695</v>
+        <v>1158.701031188398</v>
       </c>
       <c r="E169" t="n">
-        <v>1174.127516550424</v>
+        <v>1174.111401584549</v>
       </c>
       <c r="F169" t="n">
         <v>7936</v>
@@ -22119,13 +22119,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1164.003211796991</v>
+        <v>1163.976176724553</v>
       </c>
       <c r="D170" t="n">
-        <v>1152.096189338549</v>
+        <v>1152.069645784496</v>
       </c>
       <c r="E170" t="n">
-        <v>1175.910234255434</v>
+        <v>1175.88270766461</v>
       </c>
       <c r="F170" t="n">
         <v>3777</v>
@@ -22266,13 +22266,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1156.045478354869</v>
+        <v>1156.032082945341</v>
       </c>
       <c r="D171" t="n">
-        <v>1147.65907582923</v>
+        <v>1147.64588818966</v>
       </c>
       <c r="E171" t="n">
-        <v>1164.431880880508</v>
+        <v>1164.418277701022</v>
       </c>
       <c r="F171" t="n">
         <v>6837</v>
@@ -22417,13 +22417,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1154.461219354765</v>
+        <v>1154.400132270769</v>
       </c>
       <c r="D172" t="n">
-        <v>1142.973993490816</v>
+        <v>1142.91316986604</v>
       </c>
       <c r="E172" t="n">
-        <v>1165.948445218715</v>
+        <v>1165.887094675498</v>
       </c>
       <c r="F172" t="n">
         <v>3231</v>
@@ -22568,13 +22568,13 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1154.206128699705</v>
+        <v>1154.174304891183</v>
       </c>
       <c r="D173" t="n">
-        <v>1141.616440126552</v>
+        <v>1141.58510448071</v>
       </c>
       <c r="E173" t="n">
-        <v>1166.795817272858</v>
+        <v>1166.763505301656</v>
       </c>
       <c r="F173" t="n">
         <v>3585</v>
@@ -22719,13 +22719,13 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1151.838051978234</v>
+        <v>1151.816875504225</v>
       </c>
       <c r="D174" t="n">
-        <v>1138.67893221515</v>
+        <v>1138.658465453124</v>
       </c>
       <c r="E174" t="n">
-        <v>1164.997171741317</v>
+        <v>1164.975285555326</v>
       </c>
       <c r="F174" t="n">
         <v>4155</v>
@@ -22866,13 +22866,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1151.68609104845</v>
+        <v>1151.66833332258</v>
       </c>
       <c r="D175" t="n">
-        <v>1136.371519127474</v>
+        <v>1136.354850402486</v>
       </c>
       <c r="E175" t="n">
-        <v>1167.000662969425</v>
+        <v>1166.981816242673</v>
       </c>
       <c r="F175" t="n">
         <v>1679</v>
@@ -23013,13 +23013,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1150.0672209269</v>
+        <v>1150.055535320106</v>
       </c>
       <c r="D176" t="n">
-        <v>1137.830352451958</v>
+        <v>1137.819519601378</v>
       </c>
       <c r="E176" t="n">
-        <v>1162.304089401842</v>
+        <v>1162.291551038834</v>
       </c>
       <c r="F176" t="n">
         <v>2572</v>
@@ -23160,13 +23160,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1148.924419947758</v>
+        <v>1148.907033321366</v>
       </c>
       <c r="D177" t="n">
-        <v>1139.706650510637</v>
+        <v>1139.69001231348</v>
       </c>
       <c r="E177" t="n">
-        <v>1158.142189384879</v>
+        <v>1158.124054329252</v>
       </c>
       <c r="F177" t="n">
         <v>7044</v>
@@ -23311,13 +23311,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1148.902622261068</v>
+        <v>1148.876949721773</v>
       </c>
       <c r="D178" t="n">
-        <v>1142.254102856958</v>
+        <v>1142.22874329765</v>
       </c>
       <c r="E178" t="n">
-        <v>1155.551141665178</v>
+        <v>1155.525156145896</v>
       </c>
       <c r="F178" t="n">
         <v>19402</v>
@@ -23462,13 +23462,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1147.32429926823</v>
+        <v>1147.319734124503</v>
       </c>
       <c r="D179" t="n">
-        <v>1130.280012775483</v>
+        <v>1130.276506931695</v>
       </c>
       <c r="E179" t="n">
-        <v>1164.368585760977</v>
+        <v>1164.362961317312</v>
       </c>
       <c r="F179" t="n">
         <v>1295</v>
@@ -23609,13 +23609,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1143.392946547477</v>
+        <v>1143.372832721902</v>
       </c>
       <c r="D180" t="n">
-        <v>1133.509624503082</v>
+        <v>1133.489784166001</v>
       </c>
       <c r="E180" t="n">
-        <v>1153.276268591871</v>
+        <v>1153.255881277803</v>
       </c>
       <c r="F180" t="n">
         <v>4737</v>
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1142.640254925844</v>
+        <v>1142.619635102863</v>
       </c>
       <c r="D181" t="n">
-        <v>1136.200548571138</v>
+        <v>1136.180092602999</v>
       </c>
       <c r="E181" t="n">
-        <v>1149.07996128055</v>
+        <v>1149.059177602726</v>
       </c>
       <c r="F181" t="n">
         <v>12297</v>
@@ -23911,13 +23911,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1140.995896708133</v>
+        <v>1140.972149081718</v>
       </c>
       <c r="D182" t="n">
-        <v>1134.27532311083</v>
+        <v>1134.2519136479</v>
       </c>
       <c r="E182" t="n">
-        <v>1147.716470305436</v>
+        <v>1147.692384515536</v>
       </c>
       <c r="F182" t="n">
         <v>19174</v>
@@ -24062,13 +24062,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1140.85352135284</v>
+        <v>1140.841716888269</v>
       </c>
       <c r="D183" t="n">
-        <v>1134.159265859235</v>
+        <v>1134.147949755175</v>
       </c>
       <c r="E183" t="n">
-        <v>1147.547776846444</v>
+        <v>1147.535484021363</v>
       </c>
       <c r="F183" t="n">
         <v>19367</v>
@@ -24209,13 +24209,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1138.598601331636</v>
+        <v>1138.589376990497</v>
       </c>
       <c r="D184" t="n">
-        <v>1127.662109324747</v>
+        <v>1127.653377825704</v>
       </c>
       <c r="E184" t="n">
-        <v>1149.535093338526</v>
+        <v>1149.525376155289</v>
       </c>
       <c r="F184" t="n">
         <v>4964</v>
@@ -24360,13 +24360,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1137.2266125538</v>
+        <v>1137.238642897926</v>
       </c>
       <c r="D185" t="n">
-        <v>1127.744278024996</v>
+        <v>1127.756797805339</v>
       </c>
       <c r="E185" t="n">
-        <v>1146.708947082604</v>
+        <v>1146.720487990513</v>
       </c>
       <c r="F185" t="n">
         <v>8925</v>
@@ -24511,13 +24511,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1136.280014038984</v>
+        <v>1136.261905784617</v>
       </c>
       <c r="D186" t="n">
-        <v>1127.395215063307</v>
+        <v>1127.377525630599</v>
       </c>
       <c r="E186" t="n">
-        <v>1145.16481301466</v>
+        <v>1145.146285938635</v>
       </c>
       <c r="F186" t="n">
         <v>7366</v>
@@ -24662,13 +24662,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1130.299979449383</v>
+        <v>1130.273835625071</v>
       </c>
       <c r="D187" t="n">
-        <v>1121.475589683584</v>
+        <v>1121.449896119204</v>
       </c>
       <c r="E187" t="n">
-        <v>1139.124369215182</v>
+        <v>1139.097775130939</v>
       </c>
       <c r="F187" t="n">
         <v>11118</v>
@@ -24809,13 +24809,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1129.185097457615</v>
+        <v>1129.172967493554</v>
       </c>
       <c r="D188" t="n">
-        <v>1121.763604971363</v>
+        <v>1121.751707959214</v>
       </c>
       <c r="E188" t="n">
-        <v>1136.606589943866</v>
+        <v>1136.594227027894</v>
       </c>
       <c r="F188" t="n">
         <v>20685</v>
@@ -24960,13 +24960,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1127.690163895436</v>
+        <v>1127.662731891379</v>
       </c>
       <c r="D189" t="n">
-        <v>1121.293519650797</v>
+        <v>1121.266314862212</v>
       </c>
       <c r="E189" t="n">
-        <v>1134.086808140076</v>
+        <v>1134.059148920547</v>
       </c>
       <c r="F189" t="n">
         <v>20118</v>
@@ -25111,13 +25111,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1126.872333392656</v>
+        <v>1126.853700725926</v>
       </c>
       <c r="D190" t="n">
-        <v>1114.787186580653</v>
+        <v>1114.769485873998</v>
       </c>
       <c r="E190" t="n">
-        <v>1138.957480204658</v>
+        <v>1138.937915577854</v>
       </c>
       <c r="F190" t="n">
         <v>2921</v>
@@ -25258,13 +25258,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1126.365119532261</v>
+        <v>1126.34331988057</v>
       </c>
       <c r="D191" t="n">
-        <v>1110.778203920142</v>
+        <v>1110.757542364106</v>
       </c>
       <c r="E191" t="n">
-        <v>1141.952035144379</v>
+        <v>1141.929097397034</v>
       </c>
       <c r="F191" t="n">
         <v>1785</v>
@@ -25405,13 +25405,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1120.912177039618</v>
+        <v>1120.900290827178</v>
       </c>
       <c r="D192" t="n">
-        <v>1109.941030272765</v>
+        <v>1109.929626764746</v>
       </c>
       <c r="E192" t="n">
-        <v>1131.883323806471</v>
+        <v>1131.870954889611</v>
       </c>
       <c r="F192" t="n">
         <v>5182</v>
@@ -25552,13 +25552,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1118.730043403176</v>
+        <v>1118.713383091307</v>
       </c>
       <c r="D193" t="n">
-        <v>1100.605897113507</v>
+        <v>1100.590296049065</v>
       </c>
       <c r="E193" t="n">
-        <v>1136.854189692845</v>
+        <v>1136.836470133549</v>
       </c>
       <c r="F193" t="n">
         <v>1143</v>
@@ -25703,13 +25703,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1116.075614339549</v>
+        <v>1116.101284356123</v>
       </c>
       <c r="D194" t="n">
-        <v>1108.349604292614</v>
+        <v>1108.375582076986</v>
       </c>
       <c r="E194" t="n">
-        <v>1123.801624386484</v>
+        <v>1123.82698663526</v>
       </c>
       <c r="F194" t="n">
         <v>10854</v>
@@ -25854,13 +25854,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1114.603972648095</v>
+        <v>1114.592570464733</v>
       </c>
       <c r="D195" t="n">
-        <v>1105.474888752285</v>
+        <v>1105.46428898133</v>
       </c>
       <c r="E195" t="n">
-        <v>1123.733056543906</v>
+        <v>1123.720851948136</v>
       </c>
       <c r="F195" t="n">
         <v>6923</v>
@@ -26001,13 +26001,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1114.13996339811</v>
+        <v>1114.124365465726</v>
       </c>
       <c r="D196" t="n">
-        <v>1099.775417229947</v>
+        <v>1099.760447908592</v>
       </c>
       <c r="E196" t="n">
-        <v>1128.504509566273</v>
+        <v>1128.488283022859</v>
       </c>
       <c r="F196" t="n">
         <v>2199</v>
@@ -26148,13 +26148,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1110.758105114054</v>
+        <v>1110.737343833558</v>
       </c>
       <c r="D197" t="n">
-        <v>1102.874869368939</v>
+        <v>1102.854131402523</v>
       </c>
       <c r="E197" t="n">
-        <v>1118.64134085917</v>
+        <v>1118.620556264593</v>
       </c>
       <c r="F197" t="n">
         <v>8045</v>
@@ -26299,13 +26299,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1109.626514118438</v>
+        <v>1109.616575315032</v>
       </c>
       <c r="D198" t="n">
-        <v>1100.350088620015</v>
+        <v>1100.340567039906</v>
       </c>
       <c r="E198" t="n">
-        <v>1118.90293961686</v>
+        <v>1118.892583590158</v>
       </c>
       <c r="F198" t="n">
         <v>8977</v>
@@ -26450,13 +26450,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1107.515153075813</v>
+        <v>1107.487710188019</v>
       </c>
       <c r="D199" t="n">
-        <v>1100.466724338635</v>
+        <v>1100.439623938939</v>
       </c>
       <c r="E199" t="n">
-        <v>1114.563581812991</v>
+        <v>1114.5357964371</v>
       </c>
       <c r="F199" t="n">
         <v>14148</v>
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1093.055978010971</v>
+        <v>1093.072305056416</v>
       </c>
       <c r="D200" t="n">
-        <v>1081.579219336536</v>
+        <v>1081.596132307966</v>
       </c>
       <c r="E200" t="n">
-        <v>1104.532736685406</v>
+        <v>1104.548477804866</v>
       </c>
       <c r="F200" t="n">
         <v>4780</v>
@@ -26752,13 +26752,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1090.32781424412</v>
+        <v>1090.321235847598</v>
       </c>
       <c r="D201" t="n">
-        <v>1080.998006923021</v>
+        <v>1080.991805275675</v>
       </c>
       <c r="E201" t="n">
-        <v>1099.657621565218</v>
+        <v>1099.650666419522</v>
       </c>
       <c r="F201" t="n">
         <v>7597</v>
@@ -26903,13 +26903,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1073.307316444936</v>
+        <v>1073.269481896536</v>
       </c>
       <c r="D202" t="n">
-        <v>1062.156171495257</v>
+        <v>1062.118924155343</v>
       </c>
       <c r="E202" t="n">
-        <v>1084.458461394615</v>
+        <v>1084.420039637729</v>
       </c>
       <c r="F202" t="n">
         <v>6328</v>
@@ -27054,13 +27054,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1070.261881340131</v>
+        <v>1070.247584145379</v>
       </c>
       <c r="D203" t="n">
-        <v>1060.401082589991</v>
+        <v>1060.387981945125</v>
       </c>
       <c r="E203" t="n">
-        <v>1080.122680090271</v>
+        <v>1080.107186345633</v>
       </c>
       <c r="F203" t="n">
         <v>6965</v>
@@ -27201,13 +27201,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1069.048968986363</v>
+        <v>1069.071650730846</v>
       </c>
       <c r="D204" t="n">
-        <v>1057.616015402897</v>
+        <v>1057.639847791463</v>
       </c>
       <c r="E204" t="n">
-        <v>1080.481922569829</v>
+        <v>1080.503453670228</v>
       </c>
       <c r="F204" t="n">
         <v>5745</v>
@@ -27348,13 +27348,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1066.764814962292</v>
+        <v>1066.770513284424</v>
       </c>
       <c r="D205" t="n">
-        <v>1051.578865383609</v>
+        <v>1051.585790549941</v>
       </c>
       <c r="E205" t="n">
-        <v>1081.950764540976</v>
+        <v>1081.955236018908</v>
       </c>
       <c r="F205" t="n">
         <v>1743</v>
@@ -27495,13 +27495,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1062.534487684919</v>
+        <v>1062.538457554123</v>
       </c>
       <c r="D206" t="n">
-        <v>1050.585325964913</v>
+        <v>1050.590328008926</v>
       </c>
       <c r="E206" t="n">
-        <v>1074.483649404924</v>
+        <v>1074.48658709932</v>
       </c>
       <c r="F206" t="n">
         <v>3924</v>
@@ -27642,13 +27642,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1055.855443548986</v>
+        <v>1055.842089891471</v>
       </c>
       <c r="D207" t="n">
-        <v>1044.204395067386</v>
+        <v>1044.19158793636</v>
       </c>
       <c r="E207" t="n">
-        <v>1067.506492030586</v>
+        <v>1067.492591846582</v>
       </c>
       <c r="F207" t="n">
         <v>4658</v>
@@ -27789,13 +27789,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1041.564891258314</v>
+        <v>1041.55904380473</v>
       </c>
       <c r="D208" t="n">
-        <v>1030.201743528554</v>
+        <v>1030.197042054218</v>
       </c>
       <c r="E208" t="n">
-        <v>1052.928038988075</v>
+        <v>1052.921045555242</v>
       </c>
       <c r="F208" t="n">
         <v>4845</v>
@@ -27936,13 +27936,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1024.051849342354</v>
+        <v>1024.039929659971</v>
       </c>
       <c r="D209" t="n">
-        <v>1010.482197825551</v>
+        <v>1010.47114047892</v>
       </c>
       <c r="E209" t="n">
-        <v>1037.621500859157</v>
+        <v>1037.608718841022</v>
       </c>
       <c r="F209" t="n">
         <v>2658</v>
@@ -28083,13 +28083,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1022.629761237314</v>
+        <v>1022.631231394809</v>
       </c>
       <c r="D210" t="n">
-        <v>1011.787827257166</v>
+        <v>1011.790450921208</v>
       </c>
       <c r="E210" t="n">
-        <v>1033.471695217462</v>
+        <v>1033.472011868411</v>
       </c>
       <c r="F210" t="n">
         <v>6310</v>
@@ -28230,13 +28230,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>995.1986843602249</v>
+        <v>995.1804323039546</v>
       </c>
       <c r="D211" t="n">
-        <v>982.6611261278277</v>
+        <v>982.6439821247475</v>
       </c>
       <c r="E211" t="n">
-        <v>1007.736242592622</v>
+        <v>1007.716882483162</v>
       </c>
       <c r="F211" t="n">
         <v>4914</v>
@@ -28377,13 +28377,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>991.778269111108</v>
+        <v>991.7752752502361</v>
       </c>
       <c r="D212" t="n">
-        <v>979.4366527454755</v>
+        <v>979.4348844254764</v>
       </c>
       <c r="E212" t="n">
-        <v>1004.11988547674</v>
+        <v>1004.115666074996</v>
       </c>
       <c r="F212" t="n">
         <v>4203</v>
@@ -28524,13 +28524,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>981.3847574013749</v>
+        <v>981.4010331421644</v>
       </c>
       <c r="D213" t="n">
-        <v>967.8942018802869</v>
+        <v>967.9119588200974</v>
       </c>
       <c r="E213" t="n">
-        <v>994.8753129224629</v>
+        <v>994.8901074642315</v>
       </c>
       <c r="F213" t="n">
         <v>3412</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>974.0077756864913</v>
+        <v>974.0317059594072</v>
       </c>
       <c r="D214" t="n">
-        <v>958.2620424621969</v>
+        <v>958.2879013181919</v>
       </c>
       <c r="E214" t="n">
-        <v>989.7535089107856</v>
+        <v>989.7755106006223</v>
       </c>
       <c r="F214" t="n">
         <v>2391</v>
@@ -28822,13 +28822,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>952.5167835945748</v>
+        <v>952.5038134659906</v>
       </c>
       <c r="D215" t="n">
-        <v>939.8292123845387</v>
+        <v>939.8178897987268</v>
       </c>
       <c r="E215" t="n">
-        <v>965.2043548046111</v>
+        <v>965.1897371332541</v>
       </c>
       <c r="F215" t="n">
         <v>3287</v>
@@ -29107,6 +29107,77 @@
       <c r="AI216" t="inlineStr">
         <is>
           <t>MULTI-GPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro-max-20260813</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1465.492488356346</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1455.401129536509</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1475.583847176184</v>
+      </c>
+      <c r="F217" t="n">
+        <v>897</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
+      <c r="AE217" t="inlineStr"/>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -29688,7 +29759,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -29722,7 +29793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E216"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -29868,14 +29939,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hy3</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>299</v>
+        <v>744</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -29891,14 +29962,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>hy3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>744</v>
+        <v>299</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30987,46 +31058,46 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>qwen3-next-80b-a3b-thinking</t>
+          <t>trinity-large-thinking</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>trinity-large-thinking</t>
+          <t>qwen3-next-80b-a3b-thinking</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C66" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -31238,18 +31309,18 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>llama-3.1-nemotron-ultra-253b-v1</t>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>253</v>
+        <v>30</v>
       </c>
       <c r="C78" t="n">
-        <v>253</v>
+        <v>3</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -31261,14 +31332,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>qwen3-32b</t>
+          <t>llama-3.1-nemotron-ultra-253b-v1</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="C79" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -31284,75 +31355,75 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ling-flash-2.0</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
+          <t>qwen3-32b</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>32</v>
+      </c>
+      <c r="C80" t="n">
+        <v>32</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>minimax-m2</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>230</v>
-      </c>
-      <c r="C81" t="n">
-        <v>10</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>ling-flash-2.0</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nvidia-llama-3.3-nemotron-super-49b-v1.5</t>
+          <t>minimax-m2</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>49</v>
+        <v>230</v>
       </c>
       <c r="C82" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>nvidia-llama-3.3-nemotron-super-49b-v1.5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -31368,14 +31439,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>qwq-32b</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C84" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -31391,14 +31462,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>llama-3.1-405b-instruct-bf16</t>
+          <t>qwq-32b</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>405</v>
+        <v>32</v>
       </c>
       <c r="C85" t="n">
-        <v>405</v>
+        <v>32</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -31414,18 +31485,18 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+          <t>llama-3.1-405b-instruct-bf16</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>30</v>
+        <v>405</v>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>405</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -31842,38 +31913,38 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mistral-large-2411</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+          <t>olmo-3-32b-think</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>32</v>
+      </c>
+      <c r="C106" t="n">
+        <v>32</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>olmo-3-32b-think</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>32</v>
-      </c>
-      <c r="C107" t="n">
-        <v>32</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>mistral-large-2411</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -34320,6 +34391,21 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>deepseek-v4-pro-max-20260813</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI217"/>
+  <dimension ref="A1:AI216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -28965,217 +28965,66 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>inkling-small</t>
+          <t>deepseek-v4-pro-max-20260813</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1430.54086860102</v>
+        <v>1465.492488356346</v>
       </c>
       <c r="D216" t="n">
-        <v>1419.392361439659</v>
+        <v>1455.401129536509</v>
       </c>
       <c r="E216" t="n">
-        <v>1441.689375762382</v>
+        <v>1475.583847176184</v>
       </c>
       <c r="F216" t="n">
-        <v>0</v>
+        <v>897</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Thinky</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I216" t="n">
-        <v>266</v>
-      </c>
-      <c r="J216" t="n">
-        <v>12</v>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M216" t="n">
-        <v>532</v>
-      </c>
-      <c r="N216" t="n">
-        <v>665</v>
-      </c>
-      <c r="O216" t="n">
-        <v>266</v>
-      </c>
-      <c r="P216" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>133</v>
-      </c>
-      <c r="R216" t="n">
-        <v>166.2</v>
-      </c>
-      <c r="S216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD216" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF216" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG216" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="inlineStr"/>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
-        <is>
-          <t>MULTI-GPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>216</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro-max-20260813</t>
-        </is>
-      </c>
-      <c r="C217" t="n">
-        <v>1465.492488356346</v>
-      </c>
-      <c r="D217" t="n">
-        <v>1455.401129536509</v>
-      </c>
-      <c r="E217" t="n">
-        <v>1475.583847176184</v>
-      </c>
-      <c r="F217" t="n">
-        <v>897</v>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>DeepSeek</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
-      <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr"/>
-      <c r="T217" t="inlineStr"/>
-      <c r="U217" t="inlineStr"/>
-      <c r="V217" t="inlineStr"/>
-      <c r="W217" t="inlineStr"/>
-      <c r="X217" t="inlineStr"/>
-      <c r="Y217" t="inlineStr"/>
-      <c r="Z217" t="inlineStr"/>
-      <c r="AA217" t="inlineStr"/>
-      <c r="AB217" t="inlineStr"/>
-      <c r="AC217" t="inlineStr"/>
-      <c r="AD217" t="inlineStr"/>
-      <c r="AE217" t="inlineStr"/>
-      <c r="AF217" t="inlineStr"/>
-      <c r="AG217" t="inlineStr"/>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
@@ -29793,7 +29642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E217"/>
+  <dimension ref="A1:E216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -34371,36 +34220,13 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>inkling-small</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>266</v>
-      </c>
-      <c r="C216" t="n">
-        <v>12</v>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>deepseek-v4-pro-max-20260813</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
-        <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>deepseek-v4-pro-max-20260813</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -1274,14 +1274,14 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1600</v>
+        <v>1.6</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>49</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1290,106 +1290,106 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3200</v>
+        <v>3.2</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>1600</v>
+        <v>1.6</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>800</v>
+        <v>0.8</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG9" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>1</v>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH9" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -29420,7 +29420,7 @@
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -29487,18 +29487,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>77.5</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr"/>
     </row>
@@ -29522,18 +29522,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>38.8</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -29557,18 +29557,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>19.4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -29592,18 +29592,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>77.5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -29627,18 +29627,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F6" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38.8</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -29666,18 +29666,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19.4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr"/>
     </row>
@@ -29701,18 +29701,18 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>77.5</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr"/>
     </row>
@@ -29736,18 +29736,18 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>38.8</v>
+        <v>2</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -29771,18 +29771,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19.4</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -29806,18 +29806,18 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>77.5</v>
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -29841,18 +29841,18 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -29860,7 +29860,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>38.8</v>
+        <v>2</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -29876,18 +29876,18 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19.4</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -29911,18 +29911,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>77.5</v>
+        <v>4</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
@@ -29946,18 +29946,18 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>gemma-4-31b</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>31</v>
+        <v>1.6</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>38.8</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -29981,26 +29981,26 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>hy3</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>299</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>186.9</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -30172,14 +30172,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1600</v>
+        <v>1.6</v>
       </c>
       <c r="C9" t="n">
         <v>49</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/arena_enrichment/output/arena_leaderboard_enriched.xlsx
+++ b/arena_enrichment/output/arena_leaderboard_enriched.xlsx
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1488.938463022559</v>
+        <v>1488.665886033902</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1483.46874654783</v>
+        <v>1483.205187717827</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1494.408179497288</v>
+        <v>1494.126584349978</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>17908</v>
+        <v>18090</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1482.129191265623</v>
+        <v>1482.037220401277</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1474.746512836062</v>
+        <v>1474.736212870429</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1489.511869695184</v>
+        <v>1489.338227932125</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>7454</v>
+        <v>7668</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1473.116492603806</v>
+        <v>1474.158893733737</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1464.010958773296</v>
+        <v>1465.235327727741</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1482.222026434317</v>
+        <v>1483.082459739734</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4451</v>
+        <v>4672</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1471.659696255785</v>
+        <v>1471.71832610685</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1466.933759251172</v>
+        <v>1467.002566744019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1476.385633260399</v>
+        <v>1476.434085469681</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>33790</v>
+        <v>33966</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1468.136959851305</v>
+        <v>1468.10691960819</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1464.219269506827</v>
+        <v>1464.194761746623</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1472.054650195784</v>
+        <v>1472.019077469758</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>57461</v>
+        <v>57649</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1030,16 +1030,16 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1466.06563534681</v>
+        <v>1466.022472518296</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1462.085224279033</v>
+        <v>1462.043615977159</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1470.046046414588</v>
+        <v>1470.001329059433</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45449</v>
+        <v>45650</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1460.67915642332</v>
+        <v>1460.733218906034</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1456.1456784119</v>
+        <v>1456.200751454959</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1465.21263443474</v>
+        <v>1465.265686357108</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>37575</v>
+        <v>37568</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1459.372508321856</v>
+        <v>1459.610747744802</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1451.138867095898</v>
+        <v>1451.434361034411</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1467.606149547813</v>
+        <v>1467.787134455192</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5436</v>
+        <v>5557</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1319,24 +1319,24 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1457.866228466089</v>
+        <v>1457.817816303858</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1453.516493146279</v>
+        <v>1453.809076034083</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1462.215963785899</v>
+        <v>1461.826556573632</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>27638</v>
+        <v>54225</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1345,14 +1345,14 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>744</v>
+        <v>1.6</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1361,106 +1361,106 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1488</v>
+        <v>3.2</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1860</v>
+        <v>4</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>744</v>
+        <v>1.6</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>930</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>372</v>
+        <v>0.8</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>465</v>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AG10" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>1</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG10" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH10" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -1470,24 +1470,24 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1457.76300186358</v>
+        <v>1457.772757077609</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1453.753920148797</v>
+        <v>1453.424887253887</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1461.772083578364</v>
+        <v>1462.120626901331</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>54246</v>
+        <v>27647</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1496,14 +1496,14 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1.6</v>
+        <v>744</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1512,106 +1512,106 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3.2</v>
+        <v>1488</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>4</v>
+        <v>1860</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>1.6</v>
+        <v>744</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>2</v>
+        <v>930</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>0.8</v>
+        <v>372</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>465</v>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AH11" s="2" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -1625,16 +1625,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1455.306939033913</v>
+        <v>1455.386212253014</v>
       </c>
       <c r="D12" t="n">
-        <v>1447.672122361283</v>
+        <v>1447.771064169729</v>
       </c>
       <c r="E12" t="n">
-        <v>1462.941755706543</v>
+        <v>1463.0013603363</v>
       </c>
       <c r="F12" t="n">
-        <v>6918</v>
+        <v>6958</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1455.077912291178</v>
+        <v>1455.094668017135</v>
       </c>
       <c r="D13" t="n">
-        <v>1450.998651788605</v>
+        <v>1451.015592753582</v>
       </c>
       <c r="E13" t="n">
-        <v>1459.157172793751</v>
+        <v>1459.173743280688</v>
       </c>
       <c r="F13" t="n">
-        <v>51598</v>
+        <v>51569</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1847,16 +1847,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1451.327061315536</v>
+        <v>1451.281433176619</v>
       </c>
       <c r="D14" t="n">
-        <v>1443.7465934551</v>
+        <v>1443.702103401629</v>
       </c>
       <c r="E14" t="n">
-        <v>1458.907529175972</v>
+        <v>1458.860762951609</v>
       </c>
       <c r="F14" t="n">
-        <v>5901</v>
+        <v>5898</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1998,16 +1998,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1450.525368593949</v>
+        <v>1450.582684957285</v>
       </c>
       <c r="D15" t="n">
-        <v>1447.159869242665</v>
+        <v>1447.218622033372</v>
       </c>
       <c r="E15" t="n">
-        <v>1453.890867945234</v>
+        <v>1453.946747881198</v>
       </c>
       <c r="F15" t="n">
-        <v>70600</v>
+        <v>70586</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2149,16 +2149,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1442.842796783572</v>
+        <v>1442.948226795447</v>
       </c>
       <c r="D16" t="n">
-        <v>1438.490598574398</v>
+        <v>1438.5995446697</v>
       </c>
       <c r="E16" t="n">
-        <v>1447.194994992746</v>
+        <v>1447.296908921194</v>
       </c>
       <c r="F16" t="n">
-        <v>44600</v>
+        <v>44829</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2300,16 +2300,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1441.72505719257</v>
+        <v>1441.807288836225</v>
       </c>
       <c r="D17" t="n">
-        <v>1435.595192680216</v>
+        <v>1435.679247265646</v>
       </c>
       <c r="E17" t="n">
-        <v>1447.854921704925</v>
+        <v>1447.935330406804</v>
       </c>
       <c r="F17" t="n">
-        <v>11885</v>
+        <v>11889</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2371,16 +2371,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1441.3140756072</v>
+        <v>1441.105158531244</v>
       </c>
       <c r="D18" t="n">
-        <v>1437.935523100142</v>
+        <v>1437.730749133564</v>
       </c>
       <c r="E18" t="n">
-        <v>1444.692628114258</v>
+        <v>1444.479567928924</v>
       </c>
       <c r="F18" t="n">
-        <v>73433</v>
+        <v>73640</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2522,16 +2522,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1439.511080944053</v>
+        <v>1439.422559892806</v>
       </c>
       <c r="D19" t="n">
-        <v>1434.364139930738</v>
+        <v>1434.285650229928</v>
       </c>
       <c r="E19" t="n">
-        <v>1444.658021957369</v>
+        <v>1444.559469555684</v>
       </c>
       <c r="F19" t="n">
-        <v>22010</v>
+        <v>22229</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2673,16 +2673,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1438.453523376247</v>
+        <v>1438.471074508256</v>
       </c>
       <c r="D20" t="n">
-        <v>1434.243098794973</v>
+        <v>1434.262458348344</v>
       </c>
       <c r="E20" t="n">
-        <v>1442.663947957521</v>
+        <v>1442.679690668169</v>
       </c>
       <c r="F20" t="n">
-        <v>48699</v>
+        <v>48691</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2744,13 +2744,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1438.224077786462</v>
+        <v>1438.447897777446</v>
       </c>
       <c r="D21" t="n">
-        <v>1430.606724030429</v>
+        <v>1430.830372592205</v>
       </c>
       <c r="E21" t="n">
-        <v>1445.841431542494</v>
+        <v>1446.065422962686</v>
       </c>
       <c r="F21" t="n">
         <v>5813</v>
@@ -2891,118 +2891,118 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash</t>
+          <t>qwen3.8-27b</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1435.770591206617</v>
+        <v>1435.892662659902</v>
       </c>
       <c r="D22" t="n">
-        <v>1431.621513521148</v>
+        <v>1428.349245209735</v>
       </c>
       <c r="E22" t="n">
-        <v>1439.919668892086</v>
+        <v>1443.436080110069</v>
       </c>
       <c r="F22" t="n">
-        <v>48969</v>
+        <v>6913</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DeepSeek</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>284</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>568</v>
+        <v>54</v>
       </c>
       <c r="N22" t="n">
-        <v>710</v>
+        <v>67.5</v>
       </c>
       <c r="O22" t="n">
-        <v>284</v>
+        <v>27</v>
       </c>
       <c r="P22" t="n">
-        <v>355</v>
+        <v>33.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>142</v>
+        <v>13.5</v>
       </c>
       <c r="R22" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AB22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+        <v>16.9</v>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AD22" s="6" t="inlineStr">
@@ -3010,14 +3010,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF22" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="AE22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF22" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AG22" s="6" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -3042,118 +3042,118 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qwen3.8-27b</t>
+          <t>deepseek-v4-flash</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1435.140316738947</v>
+        <v>1435.749787126345</v>
       </c>
       <c r="D23" t="n">
-        <v>1427.49846909902</v>
+        <v>1431.601496220304</v>
       </c>
       <c r="E23" t="n">
-        <v>1442.782164378874</v>
+        <v>1439.898078032386</v>
       </c>
       <c r="F23" t="n">
-        <v>6679</v>
+        <v>48950</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>DeepSeek</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>284</v>
       </c>
       <c r="J23" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>54</v>
+        <v>568</v>
       </c>
       <c r="N23" t="n">
-        <v>67.5</v>
+        <v>710</v>
       </c>
       <c r="O23" t="n">
-        <v>27</v>
+        <v>284</v>
       </c>
       <c r="P23" t="n">
-        <v>33.8</v>
+        <v>355</v>
       </c>
       <c r="Q23" t="n">
-        <v>13.5</v>
+        <v>142</v>
       </c>
       <c r="R23" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+        <v>177.5</v>
+      </c>
+      <c r="S23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD23" s="6" t="inlineStr">
@@ -3161,14 +3161,14 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AE23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF23" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="AE23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF23" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AG23" s="6" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
     </row>
@@ -3197,16 +3197,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1433.832995655677</v>
+        <v>1433.809003966227</v>
       </c>
       <c r="D24" t="n">
-        <v>1429.491227090713</v>
+        <v>1429.469052372057</v>
       </c>
       <c r="E24" t="n">
-        <v>1438.17476422064</v>
+        <v>1438.148955560398</v>
       </c>
       <c r="F24" t="n">
-        <v>44543</v>
+        <v>44530</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3268,16 +3268,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1430.870749429192</v>
+        <v>1430.955172750993</v>
       </c>
       <c r="D25" t="n">
-        <v>1424.227808296084</v>
+        <v>1424.314088558133</v>
       </c>
       <c r="E25" t="n">
-        <v>1437.5136905623</v>
+        <v>1437.596256943852</v>
       </c>
       <c r="F25" t="n">
-        <v>7996</v>
+        <v>7998</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3419,16 +3419,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1430.220295377518</v>
+        <v>1430.115126710223</v>
       </c>
       <c r="D26" t="n">
-        <v>1427.071272343893</v>
+        <v>1426.966313898473</v>
       </c>
       <c r="E26" t="n">
-        <v>1433.369318411143</v>
+        <v>1433.263939521972</v>
       </c>
       <c r="F26" t="n">
-        <v>61127</v>
+        <v>61122</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3566,68 +3566,148 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mistral-medium-3.5</t>
+          <t>muse-glimmer</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1426.903028719408</v>
+        <v>1427.342906486615</v>
       </c>
       <c r="D27" t="n">
-        <v>1420.343810056366</v>
+        <v>1417.385438341717</v>
       </c>
       <c r="E27" t="n">
-        <v>1433.46224738245</v>
+        <v>1437.300374631514</v>
       </c>
       <c r="F27" t="n">
-        <v>11013</v>
+        <v>3693</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mistral</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Modified MIT</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>30</v>
+      </c>
+      <c r="J27" t="n">
+        <v>30</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
+          <t>aa_single_scrape</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>60</v>
+      </c>
+      <c r="N27" t="n">
+        <v>75</v>
+      </c>
+      <c r="O27" t="n">
+        <v>30</v>
+      </c>
+      <c r="P27" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>15</v>
+      </c>
+      <c r="R27" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG27" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -3637,148 +3717,68 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>muse-glimmer</t>
+          <t>mistral-medium-3.5</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1426.897696725807</v>
+        <v>1426.87033355163</v>
       </c>
       <c r="D28" t="n">
-        <v>1416.936891388976</v>
+        <v>1420.313203199711</v>
       </c>
       <c r="E28" t="n">
-        <v>1436.858502062638</v>
+        <v>1433.427463903548</v>
       </c>
       <c r="F28" t="n">
-        <v>3696</v>
+        <v>11017</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Mistral</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>30</v>
-      </c>
-      <c r="J28" t="n">
-        <v>30</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>Modified MIT</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>60</v>
-      </c>
-      <c r="N28" t="n">
-        <v>75</v>
-      </c>
-      <c r="O28" t="n">
-        <v>30</v>
-      </c>
-      <c r="P28" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>15</v>
-      </c>
-      <c r="R28" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG28" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -3792,16 +3792,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1426.130466597657</v>
+        <v>1426.11440715613</v>
       </c>
       <c r="D29" t="n">
-        <v>1419.116592857176</v>
+        <v>1419.102507629283</v>
       </c>
       <c r="E29" t="n">
-        <v>1433.144340338138</v>
+        <v>1433.126306682977</v>
       </c>
       <c r="F29" t="n">
-        <v>10708</v>
+        <v>10700</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3939,20 +3939,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp-thinking</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1425.333995646502</v>
+        <v>1425.246363997378</v>
       </c>
       <c r="D30" t="n">
-        <v>1418.742871315725</v>
+        <v>1421.692817433109</v>
       </c>
       <c r="E30" t="n">
-        <v>1431.92511997728</v>
+        <v>1428.799910561647</v>
       </c>
       <c r="F30" t="n">
-        <v>8906</v>
+        <v>46493</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4010,20 +4010,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>deepseek-v3.2-exp-thinking</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1425.210307544576</v>
+        <v>1425.243130881452</v>
       </c>
       <c r="D31" t="n">
-        <v>1421.655841780749</v>
+        <v>1418.653145255571</v>
       </c>
       <c r="E31" t="n">
-        <v>1428.764773308403</v>
+        <v>1431.833116507334</v>
       </c>
       <c r="F31" t="n">
-        <v>46480</v>
+        <v>8910</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4085,16 +4085,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1424.791379398886</v>
+        <v>1424.844033220861</v>
       </c>
       <c r="D32" t="n">
-        <v>1420.854589663218</v>
+        <v>1420.908497903825</v>
       </c>
       <c r="E32" t="n">
-        <v>1428.728169134554</v>
+        <v>1428.779568537897</v>
       </c>
       <c r="F32" t="n">
-        <v>35061</v>
+        <v>35068</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1423.118701586004</v>
+        <v>1423.079593721165</v>
       </c>
       <c r="D33" t="n">
-        <v>1420.528978298093</v>
+        <v>1420.490485891395</v>
       </c>
       <c r="E33" t="n">
-        <v>1425.708424873915</v>
+        <v>1425.668701550934</v>
       </c>
       <c r="F33" t="n">
-        <v>95683</v>
+        <v>95700</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4307,16 +4307,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1422.523637094675</v>
+        <v>1422.535125802745</v>
       </c>
       <c r="D34" t="n">
-        <v>1418.877781476955</v>
+        <v>1418.890324291238</v>
       </c>
       <c r="E34" t="n">
-        <v>1426.169492712396</v>
+        <v>1426.179927314252</v>
       </c>
       <c r="F34" t="n">
-        <v>40511</v>
+        <v>40520</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4378,16 +4378,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1422.371706627692</v>
+        <v>1422.382169161325</v>
       </c>
       <c r="D35" t="n">
-        <v>1415.939876950802</v>
+        <v>1415.951777098976</v>
       </c>
       <c r="E35" t="n">
-        <v>1428.803536304583</v>
+        <v>1428.812561223675</v>
       </c>
       <c r="F35" t="n">
-        <v>11760</v>
+        <v>11756</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4449,16 +4449,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1421.427698781465</v>
+        <v>1421.344373538141</v>
       </c>
       <c r="D36" t="n">
-        <v>1415.737263073168</v>
+        <v>1415.655191227588</v>
       </c>
       <c r="E36" t="n">
-        <v>1427.118134489762</v>
+        <v>1427.033555848694</v>
       </c>
       <c r="F36" t="n">
-        <v>18086</v>
+        <v>18092</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4520,16 +4520,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1417.864678121545</v>
+        <v>1417.903373481502</v>
       </c>
       <c r="D37" t="n">
-        <v>1411.328853375104</v>
+        <v>1411.371323883529</v>
       </c>
       <c r="E37" t="n">
-        <v>1424.400502867986</v>
+        <v>1424.435423079475</v>
       </c>
       <c r="F37" t="n">
-        <v>11564</v>
+        <v>11569</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4671,16 +4671,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1417.651730366579</v>
+        <v>1417.615346318356</v>
       </c>
       <c r="D38" t="n">
-        <v>1412.745893019402</v>
+        <v>1412.710185393468</v>
       </c>
       <c r="E38" t="n">
-        <v>1422.557567713757</v>
+        <v>1422.520507243245</v>
       </c>
       <c r="F38" t="n">
-        <v>27025</v>
+        <v>27033</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4818,20 +4818,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1417.372782232585</v>
+        <v>1417.527989564742</v>
       </c>
       <c r="D39" t="n">
-        <v>1411.312854624151</v>
+        <v>1407.419548749323</v>
       </c>
       <c r="E39" t="n">
-        <v>1423.43270984102</v>
+        <v>1427.636430380162</v>
       </c>
       <c r="F39" t="n">
-        <v>14603</v>
+        <v>3372</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4889,20 +4889,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1417.10718139759</v>
+        <v>1417.356674435795</v>
       </c>
       <c r="D40" t="n">
-        <v>1406.997517714453</v>
+        <v>1411.296254564015</v>
       </c>
       <c r="E40" t="n">
-        <v>1427.216845080726</v>
+        <v>1423.417094307574</v>
       </c>
       <c r="F40" t="n">
-        <v>3371</v>
+        <v>14609</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4964,16 +4964,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1417.093472083194</v>
+        <v>1417.148835746234</v>
       </c>
       <c r="D41" t="n">
-        <v>1412.714324737258</v>
+        <v>1412.770467002569</v>
       </c>
       <c r="E41" t="n">
-        <v>1421.47261942913</v>
+        <v>1421.527204489898</v>
       </c>
       <c r="F41" t="n">
-        <v>28375</v>
+        <v>28376</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5115,16 +5115,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1416.017414935887</v>
+        <v>1415.971593215663</v>
       </c>
       <c r="D42" t="n">
-        <v>1409.344087348869</v>
+        <v>1409.299408752092</v>
       </c>
       <c r="E42" t="n">
-        <v>1422.690742522904</v>
+        <v>1422.643777679233</v>
       </c>
       <c r="F42" t="n">
-        <v>11455</v>
+        <v>11463</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5186,16 +5186,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1415.882818405958</v>
+        <v>1415.362127894317</v>
       </c>
       <c r="D43" t="n">
-        <v>1412.189363332233</v>
+        <v>1411.67524348707</v>
       </c>
       <c r="E43" t="n">
-        <v>1419.576273479683</v>
+        <v>1419.049012301565</v>
       </c>
       <c r="F43" t="n">
-        <v>65458</v>
+        <v>65655</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -5257,16 +5257,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1414.550586686681</v>
+        <v>1414.666822951892</v>
       </c>
       <c r="D44" t="n">
-        <v>1404.840185096027</v>
+        <v>1404.953461895842</v>
       </c>
       <c r="E44" t="n">
-        <v>1424.260988277336</v>
+        <v>1424.380184007942</v>
       </c>
       <c r="F44" t="n">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5328,16 +5328,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1413.89398778636</v>
+        <v>1413.949549407518</v>
       </c>
       <c r="D45" t="n">
-        <v>1407.333369390594</v>
+        <v>1407.385016697986</v>
       </c>
       <c r="E45" t="n">
-        <v>1420.454606182126</v>
+        <v>1420.514082117049</v>
       </c>
       <c r="F45" t="n">
-        <v>11227</v>
+        <v>11222</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5479,16 +5479,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1413.535703281903</v>
+        <v>1413.666792434062</v>
       </c>
       <c r="D46" t="n">
-        <v>1410.456010550939</v>
+        <v>1410.588930851427</v>
       </c>
       <c r="E46" t="n">
-        <v>1416.615396012867</v>
+        <v>1416.744654016697</v>
       </c>
       <c r="F46" t="n">
-        <v>65380</v>
+        <v>65587</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1412.735994004378</v>
+        <v>1413.130394686112</v>
       </c>
       <c r="D47" t="n">
-        <v>1405.194865686226</v>
+        <v>1405.587979146018</v>
       </c>
       <c r="E47" t="n">
-        <v>1420.27712232253</v>
+        <v>1420.672810226205</v>
       </c>
       <c r="F47" t="n">
-        <v>6616</v>
+        <v>6611</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -5701,16 +5701,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1411.263003524781</v>
+        <v>1411.319522179833</v>
       </c>
       <c r="D48" t="n">
-        <v>1406.327478083023</v>
+        <v>1406.382780882573</v>
       </c>
       <c r="E48" t="n">
-        <v>1416.198528966538</v>
+        <v>1416.256263477093</v>
       </c>
       <c r="F48" t="n">
-        <v>23712</v>
+        <v>23715</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1407.953869554962</v>
+        <v>1407.966766683707</v>
       </c>
       <c r="D49" t="n">
-        <v>1403.551390482184</v>
+        <v>1403.565192776308</v>
       </c>
       <c r="E49" t="n">
-        <v>1412.356348627739</v>
+        <v>1412.368340591105</v>
       </c>
       <c r="F49" t="n">
-        <v>27246</v>
+        <v>27238</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6003,16 +6003,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1405.80821439439</v>
+        <v>1406.655281058057</v>
       </c>
       <c r="D50" t="n">
-        <v>1399.983918612954</v>
+        <v>1400.838849347376</v>
       </c>
       <c r="E50" t="n">
-        <v>1411.632510175826</v>
+        <v>1412.471712768738</v>
       </c>
       <c r="F50" t="n">
-        <v>14980</v>
+        <v>15183</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6154,16 +6154,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1402.457239819281</v>
+        <v>1402.494687351098</v>
       </c>
       <c r="D51" t="n">
-        <v>1397.922045465299</v>
+        <v>1397.959793424478</v>
       </c>
       <c r="E51" t="n">
-        <v>1406.992434173264</v>
+        <v>1407.029581277719</v>
       </c>
       <c r="F51" t="n">
-        <v>37369</v>
+        <v>37389</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6305,16 +6305,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1401.547130521026</v>
+        <v>1401.498097883057</v>
       </c>
       <c r="D52" t="n">
-        <v>1395.127295006255</v>
+        <v>1395.076869314036</v>
       </c>
       <c r="E52" t="n">
-        <v>1407.966966035797</v>
+        <v>1407.919326452079</v>
       </c>
       <c r="F52" t="n">
-        <v>11167</v>
+        <v>11161</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -6456,16 +6456,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1400.042006927405</v>
+        <v>1399.893523873951</v>
       </c>
       <c r="D53" t="n">
-        <v>1393.457423030769</v>
+        <v>1393.309755962865</v>
       </c>
       <c r="E53" t="n">
-        <v>1406.626590824041</v>
+        <v>1406.477291785038</v>
       </c>
       <c r="F53" t="n">
-        <v>8796</v>
+        <v>8800</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -6607,16 +6607,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1399.312146206359</v>
+        <v>1399.20975899605</v>
       </c>
       <c r="D54" t="n">
-        <v>1394.514167893208</v>
+        <v>1394.412414462375</v>
       </c>
       <c r="E54" t="n">
-        <v>1404.110124519511</v>
+        <v>1404.007103529726</v>
       </c>
       <c r="F54" t="n">
-        <v>22519</v>
+        <v>22532</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -6758,13 +6758,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1397.990294035833</v>
+        <v>1397.965457715761</v>
       </c>
       <c r="D55" t="n">
-        <v>1393.098859920192</v>
+        <v>1393.073562584658</v>
       </c>
       <c r="E55" t="n">
-        <v>1402.881728151474</v>
+        <v>1402.857352846863</v>
       </c>
       <c r="F55" t="n">
         <v>18524</v>
@@ -6909,16 +6909,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1395.700162030741</v>
+        <v>1395.689263728557</v>
       </c>
       <c r="D56" t="n">
-        <v>1391.799304708283</v>
+        <v>1391.788111652646</v>
       </c>
       <c r="E56" t="n">
-        <v>1399.601019353199</v>
+        <v>1399.590415804468</v>
       </c>
       <c r="F56" t="n">
-        <v>44782</v>
+        <v>44795</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7060,16 +7060,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1395.27122027855</v>
+        <v>1395.152072704465</v>
       </c>
       <c r="D57" t="n">
-        <v>1390.944093782798</v>
+        <v>1390.826474014134</v>
       </c>
       <c r="E57" t="n">
-        <v>1399.598346774301</v>
+        <v>1399.477671394796</v>
       </c>
       <c r="F57" t="n">
-        <v>29066</v>
+        <v>29065</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7211,16 +7211,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1395.117063699141</v>
+        <v>1395.026311194179</v>
       </c>
       <c r="D58" t="n">
-        <v>1388.265770609971</v>
+        <v>1388.172606024478</v>
       </c>
       <c r="E58" t="n">
-        <v>1401.968356788311</v>
+        <v>1401.88001636388</v>
       </c>
       <c r="F58" t="n">
-        <v>7790</v>
+        <v>7785</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7362,16 +7362,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1394.339053613666</v>
+        <v>1394.397905661524</v>
       </c>
       <c r="D59" t="n">
-        <v>1390.698199232089</v>
+        <v>1390.75828568975</v>
       </c>
       <c r="E59" t="n">
-        <v>1397.979907995244</v>
+        <v>1398.037525633298</v>
       </c>
       <c r="F59" t="n">
-        <v>57222</v>
+        <v>57212</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7433,13 +7433,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1392.098883413943</v>
+        <v>1392.147607146731</v>
       </c>
       <c r="D60" t="n">
-        <v>1388.540981605215</v>
+        <v>1388.590632639008</v>
       </c>
       <c r="E60" t="n">
-        <v>1395.65678522267</v>
+        <v>1395.704581654454</v>
       </c>
       <c r="F60" t="n">
         <v>46158</v>
@@ -7504,16 +7504,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1390.4968250427</v>
+        <v>1390.544675228802</v>
       </c>
       <c r="D61" t="n">
-        <v>1386.513561727209</v>
+        <v>1386.562972708816</v>
       </c>
       <c r="E61" t="n">
-        <v>1394.48008835819</v>
+        <v>1394.526377748789</v>
       </c>
       <c r="F61" t="n">
-        <v>40885</v>
+        <v>40884</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -7575,16 +7575,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1387.441542010756</v>
+        <v>1387.320876996123</v>
       </c>
       <c r="D62" t="n">
-        <v>1382.451430159133</v>
+        <v>1382.332264275607</v>
       </c>
       <c r="E62" t="n">
-        <v>1392.431653862379</v>
+        <v>1392.309489716639</v>
       </c>
       <c r="F62" t="n">
-        <v>25084</v>
+        <v>25092</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7726,16 +7726,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1386.065236078298</v>
+        <v>1386.123074510912</v>
       </c>
       <c r="D63" t="n">
-        <v>1379.786244983308</v>
+        <v>1379.844595539349</v>
       </c>
       <c r="E63" t="n">
-        <v>1392.344227173288</v>
+        <v>1392.401553482475</v>
       </c>
       <c r="F63" t="n">
-        <v>10747</v>
+        <v>10749</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7797,16 +7797,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1383.819449791477</v>
+        <v>1383.813212285447</v>
       </c>
       <c r="D64" t="n">
-        <v>1378.559207769105</v>
+        <v>1378.553053257682</v>
       </c>
       <c r="E64" t="n">
-        <v>1389.079691813849</v>
+        <v>1389.073371313212</v>
       </c>
       <c r="F64" t="n">
-        <v>16642</v>
+        <v>16633</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7868,16 +7868,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1382.304786045849</v>
+        <v>1382.301897843598</v>
       </c>
       <c r="D65" t="n">
-        <v>1377.384972617436</v>
+        <v>1377.381852974151</v>
       </c>
       <c r="E65" t="n">
-        <v>1387.224599474262</v>
+        <v>1387.221942713045</v>
       </c>
       <c r="F65" t="n">
-        <v>23221</v>
+        <v>23224</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8015,68 +8015,144 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>glm-4.6v</t>
+          <t>trinity-large-preview</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1378.443750902083</v>
+        <v>1378.537498233289</v>
       </c>
       <c r="D66" t="n">
-        <v>1367.113928564708</v>
+        <v>1374.177162141875</v>
       </c>
       <c r="E66" t="n">
-        <v>1389.773573239458</v>
+        <v>1382.897834324703</v>
       </c>
       <c r="F66" t="n">
-        <v>2763</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Z.ai</t>
-        </is>
-      </c>
+        <v>29771</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>70</v>
+      </c>
+      <c r="J66" t="n">
+        <v>70</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr"/>
-      <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>140</v>
+      </c>
+      <c r="N66" t="n">
+        <v>175</v>
+      </c>
+      <c r="O66" t="n">
+        <v>70</v>
+      </c>
+      <c r="P66" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>35</v>
+      </c>
+      <c r="R66" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="S66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>RTX PRO 6000</t>
         </is>
       </c>
     </row>
@@ -8086,144 +8162,68 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
+          <t>glm-4.6v</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1378.440442181666</v>
+        <v>1378.431625527792</v>
       </c>
       <c r="D67" t="n">
-        <v>1374.079992993386</v>
+        <v>1367.099714630365</v>
       </c>
       <c r="E67" t="n">
-        <v>1382.800891369946</v>
+        <v>1389.763536425219</v>
       </c>
       <c r="F67" t="n">
-        <v>29777</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
+        <v>2762</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Z.ai</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I67" t="n">
-        <v>70</v>
-      </c>
-      <c r="J67" t="n">
-        <v>70</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>140</v>
-      </c>
-      <c r="N67" t="n">
-        <v>175</v>
-      </c>
-      <c r="O67" t="n">
-        <v>70</v>
-      </c>
-      <c r="P67" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>35</v>
-      </c>
-      <c r="R67" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S67" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V67" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W67" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y67" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG67" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>RTX PRO 6000</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -8237,13 +8237,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1374.962848826957</v>
+        <v>1374.944304906852</v>
       </c>
       <c r="D68" t="n">
-        <v>1370.25290603963</v>
+        <v>1370.234558495804</v>
       </c>
       <c r="E68" t="n">
-        <v>1379.672791614285</v>
+        <v>1379.654051317899</v>
       </c>
       <c r="F68" t="n">
         <v>25864</v>
@@ -8388,16 +8388,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1373.259406441145</v>
+        <v>1373.173540772824</v>
       </c>
       <c r="D69" t="n">
-        <v>1368.984282034578</v>
+        <v>1368.899163076836</v>
       </c>
       <c r="E69" t="n">
-        <v>1377.534530847713</v>
+        <v>1377.447918468813</v>
       </c>
       <c r="F69" t="n">
-        <v>30374</v>
+        <v>30372</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8459,16 +8459,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1369.141300361268</v>
+        <v>1369.123836934921</v>
       </c>
       <c r="D70" t="n">
-        <v>1364.461881030497</v>
+        <v>1364.444807115879</v>
       </c>
       <c r="E70" t="n">
-        <v>1373.820719692038</v>
+        <v>1373.802866753962</v>
       </c>
       <c r="F70" t="n">
-        <v>28994</v>
+        <v>28989</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
@@ -8606,16 +8606,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1368.900086273736</v>
+        <v>1369.04054922982</v>
       </c>
       <c r="D71" t="n">
-        <v>1363.01821559451</v>
+        <v>1363.159418941422</v>
       </c>
       <c r="E71" t="n">
-        <v>1374.781956952962</v>
+        <v>1374.921679518218</v>
       </c>
       <c r="F71" t="n">
-        <v>13385</v>
+        <v>13391</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -8757,16 +8757,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1366.471290242415</v>
+        <v>1366.437698722293</v>
       </c>
       <c r="D72" t="n">
-        <v>1360.648708223333</v>
+        <v>1360.617003708495</v>
       </c>
       <c r="E72" t="n">
-        <v>1372.293872261497</v>
+        <v>1372.258393736091</v>
       </c>
       <c r="F72" t="n">
-        <v>11512</v>
+        <v>11514</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8828,16 +8828,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1365.201306584492</v>
+        <v>1365.11390272527</v>
       </c>
       <c r="D73" t="n">
-        <v>1361.491052290143</v>
+        <v>1361.402559559941</v>
       </c>
       <c r="E73" t="n">
-        <v>1368.911560878842</v>
+        <v>1368.825245890598</v>
       </c>
       <c r="F73" t="n">
-        <v>46433</v>
+        <v>46421</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -8979,16 +8979,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1363.80762723625</v>
+        <v>1363.767168273628</v>
       </c>
       <c r="D74" t="n">
-        <v>1359.493064456687</v>
+        <v>1359.455235999532</v>
       </c>
       <c r="E74" t="n">
-        <v>1368.122190015815</v>
+        <v>1368.079100547724</v>
       </c>
       <c r="F74" t="n">
-        <v>34026</v>
+        <v>34038</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9050,16 +9050,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1360.627595044921</v>
+        <v>1360.694841395509</v>
       </c>
       <c r="D75" t="n">
-        <v>1353.343983755249</v>
+        <v>1353.411295148286</v>
       </c>
       <c r="E75" t="n">
-        <v>1367.911206334594</v>
+        <v>1367.978387642733</v>
       </c>
       <c r="F75" t="n">
-        <v>7461</v>
+        <v>7458</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9201,13 +9201,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1358.267578531644</v>
+        <v>1358.260272984386</v>
       </c>
       <c r="D76" t="n">
-        <v>1353.512473755369</v>
+        <v>1353.504689681726</v>
       </c>
       <c r="E76" t="n">
-        <v>1363.022683307918</v>
+        <v>1363.015856287046</v>
       </c>
       <c r="F76" t="n">
         <v>21770</v>
@@ -9352,16 +9352,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1356.752379751028</v>
+        <v>1356.67560925081</v>
       </c>
       <c r="D77" t="n">
-        <v>1351.523291295819</v>
+        <v>1351.445934558047</v>
       </c>
       <c r="E77" t="n">
-        <v>1361.981468206238</v>
+        <v>1361.905283943573</v>
       </c>
       <c r="F77" t="n">
-        <v>17398</v>
+        <v>17399</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9423,16 +9423,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1356.116788723851</v>
+        <v>1356.161000135791</v>
       </c>
       <c r="D78" t="n">
-        <v>1347.765377666125</v>
+        <v>1347.81211010352</v>
       </c>
       <c r="E78" t="n">
-        <v>1364.468199781577</v>
+        <v>1364.509890168063</v>
       </c>
       <c r="F78" t="n">
-        <v>5283</v>
+        <v>5284</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
@@ -9566,68 +9566,148 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>command-a-03-2025</t>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1353.622800375309</v>
+        <v>1355.399274718349</v>
       </c>
       <c r="D79" t="n">
-        <v>1350.14429652817</v>
+        <v>1346.14580346526</v>
       </c>
       <c r="E79" t="n">
-        <v>1357.101304222449</v>
+        <v>1364.652745971439</v>
       </c>
       <c r="F79" t="n">
-        <v>55438</v>
+        <v>4814</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cohere</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CC-BY-NC-4.0</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+          <t>OpenMDW-1.1</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>30</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
-      <c r="AC79" t="inlineStr"/>
-      <c r="AD79" t="inlineStr"/>
-      <c r="AE79" t="inlineStr"/>
-      <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>60</v>
+      </c>
+      <c r="N79" t="n">
+        <v>75</v>
+      </c>
+      <c r="O79" t="n">
+        <v>30</v>
+      </c>
+      <c r="P79" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>15</v>
+      </c>
+      <c r="R79" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG79" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -9637,148 +9717,68 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+          <t>command-a-03-2025</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1352.968171269</v>
+        <v>1353.612237603953</v>
       </c>
       <c r="D80" t="n">
-        <v>1343.487362520563</v>
+        <v>1350.133915516033</v>
       </c>
       <c r="E80" t="n">
-        <v>1362.448980017438</v>
+        <v>1357.090559691874</v>
       </c>
       <c r="F80" t="n">
-        <v>4570</v>
+        <v>55449</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Cohere</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>OpenMDW-1.1</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>30</v>
-      </c>
-      <c r="J80" t="n">
-        <v>3</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>CC-BY-NC-4.0</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>60</v>
-      </c>
-      <c r="N80" t="n">
-        <v>75</v>
-      </c>
-      <c r="O80" t="n">
-        <v>30</v>
-      </c>
-      <c r="P80" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>15</v>
-      </c>
-      <c r="R80" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG80" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -9788,148 +9788,68 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
+          <t>glm-4.5v</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1352.410124451177</v>
+        <v>1352.500983410942</v>
       </c>
       <c r="D81" t="n">
-        <v>1348.016432315643</v>
+        <v>1344.059797342657</v>
       </c>
       <c r="E81" t="n">
-        <v>1356.803816586711</v>
+        <v>1360.942169479226</v>
       </c>
       <c r="F81" t="n">
-        <v>29936</v>
+        <v>4817</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Z.ai</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>117</v>
-      </c>
-      <c r="J81" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>override</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>234</v>
-      </c>
-      <c r="N81" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="O81" t="n">
-        <v>117</v>
-      </c>
-      <c r="P81" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="R81" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="S81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="U81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AC81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE81" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AF81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG81" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>MULTI-GPU</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>B200 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -9939,68 +9859,148 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>glm-4.5v</t>
+          <t>gpt-oss-120b</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1352.398392703332</v>
+        <v>1352.447968129115</v>
       </c>
       <c r="D82" t="n">
-        <v>1343.956458994422</v>
+        <v>1348.055850038018</v>
       </c>
       <c r="E82" t="n">
-        <v>1360.840326412243</v>
+        <v>1356.840086220212</v>
       </c>
       <c r="F82" t="n">
-        <v>4818</v>
+        <v>29955</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Z.ai</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+          <t>Apache 2.0</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>117</v>
+      </c>
+      <c r="J82" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="inlineStr"/>
-      <c r="AD82" t="inlineStr"/>
-      <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="inlineStr"/>
+          <t>override</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>234</v>
+      </c>
+      <c r="N82" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="O82" t="n">
+        <v>117</v>
+      </c>
+      <c r="P82" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="R82" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="S82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE82" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>MULTI-GPU</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>B200 SXM</t>
         </is>
       </c>
     </row>
@@ -10014,16 +10014,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1349.509564243267</v>
+        <v>1349.431960397002</v>
       </c>
       <c r="D83" t="n">
-        <v>1341.988284373313</v>
+        <v>1341.910519978439</v>
       </c>
       <c r="E83" t="n">
-        <v>1357.03084411322</v>
+        <v>1356.953400815564</v>
       </c>
       <c r="F83" t="n">
-        <v>6275</v>
+        <v>6277</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1347.481260492005</v>
+        <v>1347.451823549309</v>
       </c>
       <c r="D84" t="n">
-        <v>1335.797243493361</v>
+        <v>1335.76818621472</v>
       </c>
       <c r="E84" t="n">
-        <v>1359.165277490648</v>
+        <v>1359.135460883897</v>
       </c>
       <c r="F84" t="n">
         <v>2549</v>
@@ -10236,13 +10236,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1346.934435443555</v>
+        <v>1346.924393141263</v>
       </c>
       <c r="D85" t="n">
-        <v>1337.474127524757</v>
+        <v>1337.46425417983</v>
       </c>
       <c r="E85" t="n">
-        <v>1356.394743362353</v>
+        <v>1356.384532102697</v>
       </c>
       <c r="F85" t="n">
         <v>3926</v>
@@ -10387,16 +10387,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1345.667034566513</v>
+        <v>1345.677723525864</v>
       </c>
       <c r="D86" t="n">
-        <v>1337.898313647385</v>
+        <v>1337.91742299973</v>
       </c>
       <c r="E86" t="n">
-        <v>1353.435755485641</v>
+        <v>1353.438024051998</v>
       </c>
       <c r="F86" t="n">
-        <v>6744</v>
+        <v>6752</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -10538,16 +10538,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1344.197532958503</v>
+        <v>1344.187713813393</v>
       </c>
       <c r="D87" t="n">
-        <v>1336.866675474094</v>
+        <v>1336.856160738365</v>
       </c>
       <c r="E87" t="n">
-        <v>1351.528390442911</v>
+        <v>1351.51926688842</v>
       </c>
       <c r="F87" t="n">
-        <v>6851</v>
+        <v>6853</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10609,16 +10609,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1343.163096206467</v>
+        <v>1343.073505028064</v>
       </c>
       <c r="D88" t="n">
-        <v>1333.14766799309</v>
+        <v>1333.057892015936</v>
       </c>
       <c r="E88" t="n">
-        <v>1353.178524419844</v>
+        <v>1353.089118040192</v>
       </c>
       <c r="F88" t="n">
-        <v>3315</v>
+        <v>3316</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -10756,36 +10756,36 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>granite-4.2-30b</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1341.72195778195</v>
+        <v>1341.723521319255</v>
       </c>
       <c r="D89" t="n">
-        <v>1332.20928308356</v>
+        <v>1331.056592919411</v>
       </c>
       <c r="E89" t="n">
-        <v>1351.234632480339</v>
+        <v>1352.390449719099</v>
       </c>
       <c r="F89" t="n">
-        <v>3829</v>
+        <v>3275</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Apache 2.0</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J89" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -10798,22 +10798,22 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="N89" t="n">
+        <v>75</v>
+      </c>
+      <c r="O89" t="n">
         <v>30</v>
       </c>
-      <c r="O89" t="n">
-        <v>12</v>
-      </c>
       <c r="P89" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="Q89" t="n">
         <v>15</v>
       </c>
-      <c r="Q89" t="n">
-        <v>6</v>
-      </c>
       <c r="R89" t="n">
-        <v>7.5</v>
+        <v>18.8</v>
       </c>
       <c r="S89" s="6" t="inlineStr">
         <is>
@@ -10907,64 +10907,64 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>granite-4.2-30b</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1341.471052867725</v>
+        <v>1341.676585012394</v>
       </c>
       <c r="D90" t="n">
-        <v>1330.811452072384</v>
+        <v>1332.16400228032</v>
       </c>
       <c r="E90" t="n">
-        <v>1352.130653663066</v>
+        <v>1351.189167744468</v>
       </c>
       <c r="F90" t="n">
-        <v>3282</v>
+        <v>3829</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Apache 2.0</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="I90" t="n">
+        <v>12</v>
+      </c>
+      <c r="J90" t="n">
+        <v>12</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>24</v>
+      </c>
+      <c r="N90" t="n">
         <v>30</v>
       </c>
-      <c r="J90" t="n">
-        <v>30</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
-        <v>60</v>
-      </c>
-      <c r="N90" t="n">
-        <v>75</v>
-      </c>
       <c r="O90" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>37.5</v>
+        <v>15</v>
       </c>
       <c r="Q90" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="R90" t="n">
-        <v>18.8</v>
+        <v>7.5</v>
       </c>
       <c r="S90" s="6" t="inlineStr">
         <is>
@@ -11062,16 +11062,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1335.740710495485</v>
+        <v>1335.754642577765</v>
       </c>
       <c r="D91" t="n">
-        <v>1331.275695897201</v>
+        <v>1331.289724238274</v>
       </c>
       <c r="E91" t="n">
-        <v>1340.205725093768</v>
+        <v>1340.219560917256</v>
       </c>
       <c r="F91" t="n">
-        <v>25096</v>
+        <v>25092</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -11213,13 +11213,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1334.946280208841</v>
+        <v>1334.9225268381</v>
       </c>
       <c r="D92" t="n">
-        <v>1331.218497667765</v>
+        <v>1331.194025663783</v>
       </c>
       <c r="E92" t="n">
-        <v>1338.674062749915</v>
+        <v>1338.651028012417</v>
       </c>
       <c r="F92" t="n">
         <v>41375</v>
@@ -11364,13 +11364,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1333.085461667852</v>
+        <v>1333.063208746596</v>
       </c>
       <c r="D93" t="n">
-        <v>1329.479385328551</v>
+        <v>1329.45654558669</v>
       </c>
       <c r="E93" t="n">
-        <v>1336.691538007152</v>
+        <v>1336.669871906503</v>
       </c>
       <c r="F93" t="n">
         <v>59656</v>
@@ -11515,16 +11515,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1329.980209955524</v>
+        <v>1329.961552152115</v>
       </c>
       <c r="D94" t="n">
-        <v>1323.762402245032</v>
+        <v>1323.74476965971</v>
       </c>
       <c r="E94" t="n">
-        <v>1336.198017666016</v>
+        <v>1336.178334644521</v>
       </c>
       <c r="F94" t="n">
-        <v>11459</v>
+        <v>11460</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -11666,13 +11666,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1327.721283488711</v>
+        <v>1327.700863872633</v>
       </c>
       <c r="D95" t="n">
-        <v>1315.580064437695</v>
+        <v>1315.560221181454</v>
       </c>
       <c r="E95" t="n">
-        <v>1339.862502539728</v>
+        <v>1339.841506563811</v>
       </c>
       <c r="F95" t="n">
         <v>2218</v>
@@ -11817,13 +11817,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1327.583052841634</v>
+        <v>1327.648041547274</v>
       </c>
       <c r="D96" t="n">
-        <v>1306.188921701319</v>
+        <v>1306.255851062808</v>
       </c>
       <c r="E96" t="n">
-        <v>1348.977183981949</v>
+        <v>1349.04023203174</v>
       </c>
       <c r="F96" t="n">
         <v>792</v>
@@ -11968,16 +11968,16 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1326.852406095596</v>
+        <v>1326.846648339264</v>
       </c>
       <c r="D97" t="n">
-        <v>1322.095537255906</v>
+        <v>1322.090882758874</v>
       </c>
       <c r="E97" t="n">
-        <v>1331.609274935284</v>
+        <v>1331.602413919654</v>
       </c>
       <c r="F97" t="n">
-        <v>26088</v>
+        <v>26092</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -12119,16 +12119,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1326.706568838224</v>
+        <v>1326.658387306242</v>
       </c>
       <c r="D98" t="n">
-        <v>1322.425398571675</v>
+        <v>1322.37753481112</v>
       </c>
       <c r="E98" t="n">
-        <v>1330.987739104774</v>
+        <v>1330.939239801364</v>
       </c>
       <c r="F98" t="n">
-        <v>39357</v>
+        <v>39360</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -12270,13 +12270,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1323.206926938407</v>
+        <v>1323.206248295465</v>
       </c>
       <c r="D99" t="n">
-        <v>1314.932657917836</v>
+        <v>1314.932007463577</v>
       </c>
       <c r="E99" t="n">
-        <v>1331.481195958977</v>
+        <v>1331.480489127352</v>
       </c>
       <c r="F99" t="n">
         <v>6795</v>
@@ -12341,16 +12341,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1321.317204236085</v>
+        <v>1321.308817639012</v>
       </c>
       <c r="D100" t="n">
-        <v>1316.579506128851</v>
+        <v>1316.570642090148</v>
       </c>
       <c r="E100" t="n">
-        <v>1326.054902343318</v>
+        <v>1326.046993187876</v>
       </c>
       <c r="F100" t="n">
-        <v>29740</v>
+        <v>29747</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -12492,16 +12492,16 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1321.035427690608</v>
+        <v>1321.080349427358</v>
       </c>
       <c r="D101" t="n">
-        <v>1313.722724182099</v>
+        <v>1313.76696362306</v>
       </c>
       <c r="E101" t="n">
-        <v>1328.348131199116</v>
+        <v>1328.393735231656</v>
       </c>
       <c r="F101" t="n">
-        <v>6904</v>
+        <v>6902</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12563,13 +12563,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1317.850325713302</v>
+        <v>1317.847585678413</v>
       </c>
       <c r="D102" t="n">
-        <v>1312.14533867716</v>
+        <v>1312.142355769472</v>
       </c>
       <c r="E102" t="n">
-        <v>1323.555312749444</v>
+        <v>1323.552815587354</v>
       </c>
       <c r="F102" t="n">
         <v>16478</v>
@@ -12634,16 +12634,16 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1317.497865105295</v>
+        <v>1317.442321307522</v>
       </c>
       <c r="D103" t="n">
-        <v>1313.995880420835</v>
+        <v>1313.939606921149</v>
       </c>
       <c r="E103" t="n">
-        <v>1320.999849789755</v>
+        <v>1320.945035693896</v>
       </c>
       <c r="F103" t="n">
-        <v>54410</v>
+        <v>54415</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -12785,16 +12785,16 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1317.319959256563</v>
+        <v>1317.205753447251</v>
       </c>
       <c r="D104" t="n">
-        <v>1312.131158909651</v>
+        <v>1312.016773623952</v>
       </c>
       <c r="E104" t="n">
-        <v>1322.508759603476</v>
+        <v>1322.39473327055</v>
       </c>
       <c r="F104" t="n">
-        <v>22082</v>
+        <v>22087</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -12936,16 +12936,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1317.250863265355</v>
+        <v>1317.123202523288</v>
       </c>
       <c r="D105" t="n">
-        <v>1310.833897135104</v>
+        <v>1310.7060379689</v>
       </c>
       <c r="E105" t="n">
-        <v>1323.667829395606</v>
+        <v>1323.540367077675</v>
       </c>
       <c r="F105" t="n">
-        <v>10386</v>
+        <v>10394</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -13087,16 +13087,16 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1314.368905779374</v>
+        <v>1314.230889539897</v>
       </c>
       <c r="D106" t="n">
-        <v>1308.825718881021</v>
+        <v>1308.689903681595</v>
       </c>
       <c r="E106" t="n">
-        <v>1319.912092677726</v>
+        <v>1319.771875398199</v>
       </c>
       <c r="F106" t="n">
-        <v>15335</v>
+        <v>15332</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1314.047457098706</v>
+        <v>1314.033073144253</v>
       </c>
       <c r="D107" t="n">
-        <v>1310.112285917637</v>
+        <v>1310.097424818662</v>
       </c>
       <c r="E107" t="n">
-        <v>1317.982628279775</v>
+        <v>1317.968721469844</v>
       </c>
       <c r="F107" t="n">
         <v>45459</v>
@@ -13389,13 +13389,13 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1313.995866900369</v>
+        <v>1314.000062729031</v>
       </c>
       <c r="D108" t="n">
-        <v>1309.431411900572</v>
+        <v>1309.435114681852</v>
       </c>
       <c r="E108" t="n">
-        <v>1318.560321900166</v>
+        <v>1318.565010776209</v>
       </c>
       <c r="F108" t="n">
         <v>24739</v>
@@ -13536,13 +13536,13 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1306.963751551183</v>
+        <v>1306.959232826789</v>
       </c>
       <c r="D109" t="n">
-        <v>1302.249836284709</v>
+        <v>1302.244951212745</v>
       </c>
       <c r="E109" t="n">
-        <v>1311.677666817657</v>
+        <v>1311.673514440833</v>
       </c>
       <c r="F109" t="n">
         <v>24572</v>
@@ -13607,16 +13607,16 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1306.734713579627</v>
+        <v>1306.709136147982</v>
       </c>
       <c r="D110" t="n">
-        <v>1298.421443330236</v>
+        <v>1298.398779139484</v>
       </c>
       <c r="E110" t="n">
-        <v>1315.047983829018</v>
+        <v>1315.019493156479</v>
       </c>
       <c r="F110" t="n">
-        <v>5681</v>
+        <v>5683</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -13758,13 +13758,13 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1306.340005443542</v>
+        <v>1306.287094234793</v>
       </c>
       <c r="D111" t="n">
-        <v>1300.66202992143</v>
+        <v>1300.608935104206</v>
       </c>
       <c r="E111" t="n">
-        <v>1312.017980965655</v>
+        <v>1311.965253365381</v>
       </c>
       <c r="F111" t="n">
         <v>19621</v>
@@ -13905,16 +13905,16 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1305.820008893611</v>
+        <v>1306.000838572719</v>
       </c>
       <c r="D112" t="n">
-        <v>1295.648872695265</v>
+        <v>1295.826149626821</v>
       </c>
       <c r="E112" t="n">
-        <v>1315.991145091956</v>
+        <v>1316.175527518616</v>
       </c>
       <c r="F112" t="n">
-        <v>4033</v>
+        <v>4028</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -14056,13 +14056,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1305.266100867725</v>
+        <v>1305.250400425412</v>
       </c>
       <c r="D113" t="n">
-        <v>1300.814669324405</v>
+        <v>1300.798378594199</v>
       </c>
       <c r="E113" t="n">
-        <v>1309.717532411046</v>
+        <v>1309.702422256626</v>
       </c>
       <c r="F113" t="n">
         <v>28073</v>
@@ -14127,13 +14127,13 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1303.173554542392</v>
+        <v>1303.124929527203</v>
       </c>
       <c r="D114" t="n">
-        <v>1293.8548803904</v>
+        <v>1293.806248893482</v>
       </c>
       <c r="E114" t="n">
-        <v>1312.492228694383</v>
+        <v>1312.443610160924</v>
       </c>
       <c r="F114" t="n">
         <v>4171</v>
@@ -14278,16 +14278,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1303.006044065844</v>
+        <v>1302.990799554622</v>
       </c>
       <c r="D115" t="n">
-        <v>1298.459127161307</v>
+        <v>1298.443216781805</v>
       </c>
       <c r="E115" t="n">
-        <v>1307.552960970381</v>
+        <v>1307.53838232744</v>
       </c>
       <c r="F115" t="n">
-        <v>32625</v>
+        <v>32630</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -14429,13 +14429,13 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1302.645059702568</v>
+        <v>1302.643717546731</v>
       </c>
       <c r="D116" t="n">
-        <v>1298.558766524306</v>
+        <v>1298.556859375575</v>
       </c>
       <c r="E116" t="n">
-        <v>1306.73135288083</v>
+        <v>1306.730575717886</v>
       </c>
       <c r="F116" t="n">
         <v>39406</v>
@@ -14580,13 +14580,13 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1298.66518100243</v>
+        <v>1298.641342228313</v>
       </c>
       <c r="D117" t="n">
-        <v>1290.900075383647</v>
+        <v>1290.87627432368</v>
       </c>
       <c r="E117" t="n">
-        <v>1306.430286621213</v>
+        <v>1306.406410132946</v>
       </c>
       <c r="F117" t="n">
         <v>7140</v>
@@ -14731,16 +14731,16 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1295.435344691637</v>
+        <v>1295.660142589472</v>
       </c>
       <c r="D118" t="n">
-        <v>1283.635808869999</v>
+        <v>1283.862999887335</v>
       </c>
       <c r="E118" t="n">
-        <v>1307.234880513275</v>
+        <v>1307.457285291609</v>
       </c>
       <c r="F118" t="n">
-        <v>3098</v>
+        <v>3093</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -14882,13 +14882,13 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1293.066795028085</v>
+        <v>1293.033926802914</v>
       </c>
       <c r="D119" t="n">
-        <v>1289.319417887349</v>
+        <v>1289.286005614855</v>
       </c>
       <c r="E119" t="n">
-        <v>1296.814172168822</v>
+        <v>1296.781847990974</v>
       </c>
       <c r="F119" t="n">
         <v>55240</v>
@@ -15029,148 +15029,64 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>gemma-2-27b-it</t>
+          <t>jamba-1.5-large</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1289.118120808381</v>
+        <v>1289.091340450951</v>
       </c>
       <c r="D120" t="n">
-        <v>1285.722592121889</v>
+        <v>1281.782884537108</v>
       </c>
       <c r="E120" t="n">
-        <v>1292.513649494872</v>
+        <v>1296.399796364793</v>
       </c>
       <c r="F120" t="n">
-        <v>75754</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
+        <v>8662</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Gemma license</t>
-        </is>
-      </c>
-      <c r="I120" t="n">
-        <v>27</v>
-      </c>
-      <c r="J120" t="n">
-        <v>27</v>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>Jamba Open</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>name_parsing</t>
-        </is>
-      </c>
-      <c r="M120" t="n">
-        <v>54</v>
-      </c>
-      <c r="N120" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="O120" t="n">
-        <v>27</v>
-      </c>
-      <c r="P120" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="R120" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="V120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AC120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AD120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AE120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AF120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG120" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>H100 SXM</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -15180,64 +15096,148 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>jamba-1.5-large</t>
+          <t>gemma-2-27b-it</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1289.109534347264</v>
+        <v>1289.059199397091</v>
       </c>
       <c r="D121" t="n">
-        <v>1281.801080455246</v>
+        <v>1285.662922198359</v>
       </c>
       <c r="E121" t="n">
-        <v>1296.417988239282</v>
+        <v>1292.455476595823</v>
       </c>
       <c r="F121" t="n">
-        <v>8662</v>
-      </c>
-      <c r="G121" t="inlineStr"/>
+        <v>75754</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Jamba Open</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
+          <t>Gemma license</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>27</v>
+      </c>
+      <c r="J121" t="n">
+        <v>27</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
-      <c r="Y121" t="inlineStr"/>
-      <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr"/>
-      <c r="AB121" t="inlineStr"/>
-      <c r="AC121" t="inlineStr"/>
-      <c r="AD121" t="inlineStr"/>
-      <c r="AE121" t="inlineStr"/>
-      <c r="AF121" t="inlineStr"/>
-      <c r="AG121" t="inlineStr"/>
+          <t>name_parsing</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>54</v>
+      </c>
+      <c r="N121" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O121" t="n">
+        <v>27</v>
+      </c>
+      <c r="P121" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="R121" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="V121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AA121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AD121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AG121" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>H100 SXM</t>
         </is>
       </c>
     </row>
@@ -15251,16 +15251,16 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1288.434815790594</v>
+        <v>1288.404014558849</v>
       </c>
       <c r="D122" t="n">
-        <v>1277.046932491405</v>
+        <v>1277.011436186798</v>
       </c>
       <c r="E122" t="n">
-        <v>1299.822699089783</v>
+        <v>1299.7965929309</v>
       </c>
       <c r="F122" t="n">
-        <v>3117</v>
+        <v>3111</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -15402,13 +15402,13 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1286.115835476216</v>
+        <v>1286.090323786814</v>
       </c>
       <c r="D123" t="n">
-        <v>1276.145117745804</v>
+        <v>1276.119774433271</v>
       </c>
       <c r="E123" t="n">
-        <v>1296.086553206628</v>
+        <v>1296.060873140357</v>
       </c>
       <c r="F123" t="n">
         <v>3749</v>
@@ -15553,13 +15553,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1285.786098799394</v>
+        <v>1285.771760639062</v>
       </c>
       <c r="D124" t="n">
-        <v>1275.321865953442</v>
+        <v>1275.307820836928</v>
       </c>
       <c r="E124" t="n">
-        <v>1296.250331645347</v>
+        <v>1296.235700441197</v>
       </c>
       <c r="F124" t="n">
         <v>2846</v>
@@ -15704,16 +15704,16 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1285.728755366072</v>
+        <v>1285.644485192174</v>
       </c>
       <c r="D125" t="n">
-        <v>1278.39240910897</v>
+        <v>1278.314998643072</v>
       </c>
       <c r="E125" t="n">
-        <v>1293.065101623175</v>
+        <v>1292.973971741275</v>
       </c>
       <c r="F125" t="n">
-        <v>8111</v>
+        <v>8116</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -15855,16 +15855,16 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1285.417198352508</v>
+        <v>1285.396977026848</v>
       </c>
       <c r="D126" t="n">
-        <v>1276.922863328203</v>
+        <v>1276.90101253903</v>
       </c>
       <c r="E126" t="n">
-        <v>1293.911533376812</v>
+        <v>1293.892941514667</v>
       </c>
       <c r="F126" t="n">
-        <v>5534</v>
+        <v>5535</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -16006,13 +16006,13 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1280.044034093289</v>
+        <v>1279.981600717899</v>
       </c>
       <c r="D127" t="n">
-        <v>1273.182813332156</v>
+        <v>1273.120287431976</v>
       </c>
       <c r="E127" t="n">
-        <v>1286.905254854421</v>
+        <v>1286.842914003822</v>
       </c>
       <c r="F127" t="n">
         <v>10072</v>
@@ -16153,13 +16153,13 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1276.636318807759</v>
+        <v>1276.623672445884</v>
       </c>
       <c r="D128" t="n">
-        <v>1271.311282018093</v>
+        <v>1271.298586755558</v>
       </c>
       <c r="E128" t="n">
-        <v>1281.961355597426</v>
+        <v>1281.94875813621</v>
       </c>
       <c r="F128" t="n">
         <v>19659</v>
@@ -16304,13 +16304,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1276.105357679155</v>
+        <v>1276.069736882596</v>
       </c>
       <c r="D129" t="n">
-        <v>1272.514070496431</v>
+        <v>1272.478067361396</v>
       </c>
       <c r="E129" t="n">
-        <v>1279.69664486188</v>
+        <v>1279.661406403796</v>
       </c>
       <c r="F129" t="n">
         <v>156876</v>
@@ -16455,13 +16455,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1275.854584144255</v>
+        <v>1275.842609301897</v>
       </c>
       <c r="D130" t="n">
-        <v>1269.273625862053</v>
+        <v>1269.261550652281</v>
       </c>
       <c r="E130" t="n">
-        <v>1282.435542426458</v>
+        <v>1282.423667951512</v>
       </c>
       <c r="F130" t="n">
         <v>9866</v>
@@ -16606,13 +16606,13 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1274.10722336438</v>
+        <v>1274.089131891822</v>
       </c>
       <c r="D131" t="n">
-        <v>1268.188942280256</v>
+        <v>1268.170516099121</v>
       </c>
       <c r="E131" t="n">
-        <v>1280.025504448504</v>
+        <v>1280.007747684524</v>
       </c>
       <c r="F131" t="n">
         <v>14681</v>
@@ -16757,13 +16757,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1270.300392397695</v>
+        <v>1270.295837849088</v>
       </c>
       <c r="D132" t="n">
-        <v>1262.169767145494</v>
+        <v>1262.165224267148</v>
       </c>
       <c r="E132" t="n">
-        <v>1278.431017649896</v>
+        <v>1278.426451431027</v>
       </c>
       <c r="F132" t="n">
         <v>5432</v>
@@ -16908,13 +16908,13 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1266.902631787072</v>
+        <v>1266.869855233148</v>
       </c>
       <c r="D133" t="n">
-        <v>1262.00409723009</v>
+        <v>1261.970886219025</v>
       </c>
       <c r="E133" t="n">
-        <v>1271.801166344055</v>
+        <v>1271.76882424727</v>
       </c>
       <c r="F133" t="n">
         <v>27124</v>
@@ -17059,13 +17059,13 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1266.644827570699</v>
+        <v>1266.585794984461</v>
       </c>
       <c r="D134" t="n">
-        <v>1262.813996807179</v>
+        <v>1262.754336647203</v>
       </c>
       <c r="E134" t="n">
-        <v>1270.475658334218</v>
+        <v>1270.417253321718</v>
       </c>
       <c r="F134" t="n">
         <v>54611</v>
@@ -17210,13 +17210,13 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1264.852540433521</v>
+        <v>1264.816728573648</v>
       </c>
       <c r="D135" t="n">
-        <v>1258.573396091156</v>
+        <v>1258.537556089165</v>
       </c>
       <c r="E135" t="n">
-        <v>1271.131684775886</v>
+        <v>1271.09590105813</v>
       </c>
       <c r="F135" t="n">
         <v>15147</v>
@@ -17361,13 +17361,13 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1261.294253736855</v>
+        <v>1261.273397805251</v>
       </c>
       <c r="D136" t="n">
-        <v>1256.342835037673</v>
+        <v>1256.321774245477</v>
       </c>
       <c r="E136" t="n">
-        <v>1266.245672436037</v>
+        <v>1266.225021365026</v>
       </c>
       <c r="F136" t="n">
         <v>37325</v>
@@ -17512,13 +17512,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1261.228692388486</v>
+        <v>1261.219152154729</v>
       </c>
       <c r="D137" t="n">
-        <v>1256.904101013761</v>
+        <v>1256.894372174982</v>
       </c>
       <c r="E137" t="n">
-        <v>1265.553283763211</v>
+        <v>1265.543932134475</v>
       </c>
       <c r="F137" t="n">
         <v>77554</v>
@@ -17583,13 +17583,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1255.997630178452</v>
+        <v>1255.975655120886</v>
       </c>
       <c r="D138" t="n">
-        <v>1251.390784012423</v>
+        <v>1251.368300020978</v>
       </c>
       <c r="E138" t="n">
-        <v>1260.604476344481</v>
+        <v>1260.583010220794</v>
       </c>
       <c r="F138" t="n">
         <v>24126</v>
@@ -17734,13 +17734,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1251.337478265041</v>
+        <v>1251.314254460628</v>
       </c>
       <c r="D139" t="n">
-        <v>1240.556505273594</v>
+        <v>1240.533526300885</v>
       </c>
       <c r="E139" t="n">
-        <v>1262.118451256488</v>
+        <v>1262.094982620371</v>
       </c>
       <c r="F139" t="n">
         <v>3334</v>
@@ -17885,13 +17885,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1249.882746432991</v>
+        <v>1249.865544544262</v>
       </c>
       <c r="D140" t="n">
-        <v>1243.276962486933</v>
+        <v>1243.25972746284</v>
       </c>
       <c r="E140" t="n">
-        <v>1256.488530379049</v>
+        <v>1256.471361625685</v>
       </c>
       <c r="F140" t="n">
         <v>10140</v>
@@ -18036,13 +18036,13 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1239.434343919755</v>
+        <v>1239.404666198154</v>
       </c>
       <c r="D141" t="n">
-        <v>1232.2054318118</v>
+        <v>1232.175763138669</v>
       </c>
       <c r="E141" t="n">
-        <v>1246.66325602771</v>
+        <v>1246.633569257638</v>
       </c>
       <c r="F141" t="n">
         <v>8858</v>
@@ -18103,13 +18103,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1237.291107885866</v>
+        <v>1237.280317239418</v>
       </c>
       <c r="D142" t="n">
-        <v>1228.198329676281</v>
+        <v>1228.187782557742</v>
       </c>
       <c r="E142" t="n">
-        <v>1246.38388609545</v>
+        <v>1246.372851921094</v>
       </c>
       <c r="F142" t="n">
         <v>4781</v>
@@ -18254,13 +18254,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1233.66833761618</v>
+        <v>1233.642417011406</v>
       </c>
       <c r="D143" t="n">
-        <v>1228.116145098048</v>
+        <v>1228.090243061351</v>
       </c>
       <c r="E143" t="n">
-        <v>1239.220530134312</v>
+        <v>1239.19459096146</v>
       </c>
       <c r="F143" t="n">
         <v>26195</v>
@@ -18405,13 +18405,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1232.957507050015</v>
+        <v>1232.934695624009</v>
       </c>
       <c r="D144" t="n">
-        <v>1227.684099458795</v>
+        <v>1227.661328154131</v>
       </c>
       <c r="E144" t="n">
-        <v>1238.230914641235</v>
+        <v>1238.208063093886</v>
       </c>
       <c r="F144" t="n">
         <v>39302</v>
@@ -18556,13 +18556,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1228.986520138528</v>
+        <v>1228.969496610941</v>
       </c>
       <c r="D145" t="n">
-        <v>1224.42699753211</v>
+        <v>1224.409755123904</v>
       </c>
       <c r="E145" t="n">
-        <v>1233.546042744946</v>
+        <v>1233.529238097978</v>
       </c>
       <c r="F145" t="n">
         <v>51416</v>
@@ -18707,13 +18707,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1226.286260547877</v>
+        <v>1226.273465187792</v>
       </c>
       <c r="D146" t="n">
-        <v>1221.503516704724</v>
+        <v>1221.490640274749</v>
       </c>
       <c r="E146" t="n">
-        <v>1231.069004391029</v>
+        <v>1231.056290100835</v>
       </c>
       <c r="F146" t="n">
         <v>54036</v>
@@ -18778,13 +18778,13 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1223.156379274212</v>
+        <v>1223.126765751408</v>
       </c>
       <c r="D147" t="n">
-        <v>1219.414790978684</v>
+        <v>1219.384844286222</v>
       </c>
       <c r="E147" t="n">
-        <v>1226.897967569741</v>
+        <v>1226.868687216593</v>
       </c>
       <c r="F147" t="n">
         <v>104642</v>
@@ -18929,13 +18929,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1222.765120617019</v>
+        <v>1222.735570711818</v>
       </c>
       <c r="D148" t="n">
-        <v>1215.785195027722</v>
+        <v>1215.755479378481</v>
       </c>
       <c r="E148" t="n">
-        <v>1229.745046206315</v>
+        <v>1229.715662045156</v>
       </c>
       <c r="F148" t="n">
         <v>9818</v>
@@ -19080,13 +19080,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1220.225509499669</v>
+        <v>1220.211618098502</v>
       </c>
       <c r="D149" t="n">
-        <v>1209.549265988193</v>
+        <v>1209.535697795586</v>
       </c>
       <c r="E149" t="n">
-        <v>1230.901753011146</v>
+        <v>1230.887538401417</v>
       </c>
       <c r="F149" t="n">
         <v>2896</v>
@@ -19231,13 +19231,13 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1212.446151005757</v>
+        <v>1212.439668103614</v>
       </c>
       <c r="D150" t="n">
-        <v>1207.406395840776</v>
+        <v>1207.39983726898</v>
       </c>
       <c r="E150" t="n">
-        <v>1217.485906170738</v>
+        <v>1217.479498938248</v>
       </c>
       <c r="F150" t="n">
         <v>24146</v>
@@ -19378,13 +19378,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1212.420641252319</v>
+        <v>1212.406503358705</v>
       </c>
       <c r="D151" t="n">
-        <v>1201.637402915973</v>
+        <v>1201.623817596054</v>
       </c>
       <c r="E151" t="n">
-        <v>1223.203879588666</v>
+        <v>1223.189189121355</v>
       </c>
       <c r="F151" t="n">
         <v>4652</v>
@@ -19525,13 +19525,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1211.047473067359</v>
+        <v>1211.030996432712</v>
       </c>
       <c r="D152" t="n">
-        <v>1206.88628667367</v>
+        <v>1206.869373969921</v>
       </c>
       <c r="E152" t="n">
-        <v>1215.208659461047</v>
+        <v>1215.192618895502</v>
       </c>
       <c r="F152" t="n">
         <v>49605</v>
@@ -19676,13 +19676,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1207.979842175411</v>
+        <v>1207.964470653874</v>
       </c>
       <c r="D153" t="n">
-        <v>1196.880856693795</v>
+        <v>1196.866081847157</v>
       </c>
       <c r="E153" t="n">
-        <v>1219.078827657027</v>
+        <v>1219.062859460591</v>
       </c>
       <c r="F153" t="n">
         <v>3090</v>
@@ -19827,13 +19827,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1203.402378486245</v>
+        <v>1203.386417807445</v>
       </c>
       <c r="D154" t="n">
-        <v>1197.286020249989</v>
+        <v>1197.270114397957</v>
       </c>
       <c r="E154" t="n">
-        <v>1209.518736722501</v>
+        <v>1209.502721216933</v>
       </c>
       <c r="F154" t="n">
         <v>21741</v>
@@ -19978,13 +19978,13 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1199.854549243203</v>
+        <v>1199.795792097394</v>
       </c>
       <c r="D155" t="n">
-        <v>1195.749934933482</v>
+        <v>1195.690647983603</v>
       </c>
       <c r="E155" t="n">
-        <v>1203.959163552923</v>
+        <v>1203.900936211185</v>
       </c>
       <c r="F155" t="n">
         <v>46616</v>
@@ -20129,13 +20129,13 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1197.356235082887</v>
+        <v>1197.34567354508</v>
       </c>
       <c r="D156" t="n">
-        <v>1192.193176759375</v>
+        <v>1192.182457253475</v>
       </c>
       <c r="E156" t="n">
-        <v>1202.519293406399</v>
+        <v>1202.508889836686</v>
       </c>
       <c r="F156" t="n">
         <v>25055</v>
@@ -20280,13 +20280,13 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1196.569937303253</v>
+        <v>1196.556595949152</v>
       </c>
       <c r="D157" t="n">
-        <v>1192.302291921005</v>
+        <v>1192.288834253628</v>
       </c>
       <c r="E157" t="n">
-        <v>1200.8375826855</v>
+        <v>1200.824357644676</v>
       </c>
       <c r="F157" t="n">
         <v>73503</v>
@@ -20431,13 +20431,13 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1194.877373069489</v>
+        <v>1194.853714806351</v>
       </c>
       <c r="D158" t="n">
-        <v>1188.765382686409</v>
+        <v>1188.741801510942</v>
       </c>
       <c r="E158" t="n">
-        <v>1200.989363452569</v>
+        <v>1200.96562810176</v>
       </c>
       <c r="F158" t="n">
         <v>32191</v>
@@ -20498,13 +20498,13 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1190.525075729197</v>
+        <v>1190.506537114265</v>
       </c>
       <c r="D159" t="n">
-        <v>1183.410755734486</v>
+        <v>1183.392411995846</v>
       </c>
       <c r="E159" t="n">
-        <v>1197.639395723909</v>
+        <v>1197.620662232685</v>
       </c>
       <c r="F159" t="n">
         <v>17839</v>
@@ -20649,13 +20649,13 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1190.420290857452</v>
+        <v>1190.404502024063</v>
       </c>
       <c r="D160" t="n">
-        <v>1183.233915193193</v>
+        <v>1183.218135871466</v>
       </c>
       <c r="E160" t="n">
-        <v>1197.606666521711</v>
+        <v>1197.59086817666</v>
       </c>
       <c r="F160" t="n">
         <v>9901</v>
@@ -20796,13 +20796,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1184.2747474779</v>
+        <v>1184.251389196355</v>
       </c>
       <c r="D161" t="n">
-        <v>1172.800569156978</v>
+        <v>1172.777767151404</v>
       </c>
       <c r="E161" t="n">
-        <v>1195.748925798823</v>
+        <v>1195.725011241307</v>
       </c>
       <c r="F161" t="n">
         <v>4932</v>
@@ -20947,13 +20947,13 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1184.159821320393</v>
+        <v>1184.148819021026</v>
       </c>
       <c r="D162" t="n">
-        <v>1174.730423208998</v>
+        <v>1174.719910695748</v>
       </c>
       <c r="E162" t="n">
-        <v>1193.589219431789</v>
+        <v>1193.577727346304</v>
       </c>
       <c r="F162" t="n">
         <v>8214</v>
@@ -21098,13 +21098,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1183.242360797468</v>
+        <v>1183.222615969913</v>
       </c>
       <c r="D163" t="n">
-        <v>1176.41812108213</v>
+        <v>1176.39855854081</v>
       </c>
       <c r="E163" t="n">
-        <v>1190.066600512806</v>
+        <v>1190.046673399016</v>
       </c>
       <c r="F163" t="n">
         <v>15483</v>
@@ -21245,13 +21245,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1182.481328473207</v>
+        <v>1182.451574514483</v>
       </c>
       <c r="D164" t="n">
-        <v>1173.802496745646</v>
+        <v>1173.773018749697</v>
       </c>
       <c r="E164" t="n">
-        <v>1191.160160200768</v>
+        <v>1191.130130279269</v>
       </c>
       <c r="F164" t="n">
         <v>6638</v>
@@ -21396,13 +21396,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1182.3627277193</v>
+        <v>1182.335776177579</v>
       </c>
       <c r="D165" t="n">
-        <v>1172.711123556845</v>
+        <v>1172.68466048618</v>
       </c>
       <c r="E165" t="n">
-        <v>1192.014331881755</v>
+        <v>1191.986891868978</v>
       </c>
       <c r="F165" t="n">
         <v>7968</v>
@@ -21463,13 +21463,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1182.105477979542</v>
+        <v>1182.086354799941</v>
       </c>
       <c r="D166" t="n">
-        <v>1174.116753719134</v>
+        <v>1174.097957584814</v>
       </c>
       <c r="E166" t="n">
-        <v>1190.09420223995</v>
+        <v>1190.074752015068</v>
       </c>
       <c r="F166" t="n">
         <v>12637</v>
@@ -21530,13 +21530,13 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1182.056398501286</v>
+        <v>1181.986553128395</v>
       </c>
       <c r="D167" t="n">
-        <v>1175.986482545039</v>
+        <v>1175.916662769369</v>
       </c>
       <c r="E167" t="n">
-        <v>1188.126314457533</v>
+        <v>1188.05644348742</v>
       </c>
       <c r="F167" t="n">
         <v>23893</v>
@@ -21681,13 +21681,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>1179.394778932712</v>
+        <v>1179.373339980233</v>
       </c>
       <c r="D168" t="n">
-        <v>1173.484657372349</v>
+        <v>1173.463283485891</v>
       </c>
       <c r="E168" t="n">
-        <v>1185.304900493074</v>
+        <v>1185.283396474575</v>
       </c>
       <c r="F168" t="n">
         <v>32832</v>
@@ -21748,13 +21748,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>1178.392085264075</v>
+        <v>1178.378852534002</v>
       </c>
       <c r="D169" t="n">
-        <v>1167.205057936518</v>
+        <v>1167.192276307484</v>
       </c>
       <c r="E169" t="n">
-        <v>1189.579112591633</v>
+        <v>1189.56542876052</v>
       </c>
       <c r="F169" t="n">
         <v>3188</v>
@@ -21899,13 +21899,13 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1177.111276542059</v>
+        <v>1177.105773445689</v>
       </c>
       <c r="D170" t="n">
-        <v>1167.312415307036</v>
+        <v>1167.307375734286</v>
       </c>
       <c r="E170" t="n">
-        <v>1186.910137777082</v>
+        <v>1186.904171157092</v>
       </c>
       <c r="F170" t="n">
         <v>6535</v>
@@ -22046,13 +22046,13 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1175.285264726896</v>
+        <v>1175.260799675366</v>
       </c>
       <c r="D171" t="n">
-        <v>1164.888521397657</v>
+        <v>1164.86461390607</v>
       </c>
       <c r="E171" t="n">
-        <v>1185.682008056136</v>
+        <v>1185.656985444663</v>
       </c>
       <c r="F171" t="n">
         <v>5006</v>
@@ -22193,13 +22193,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1172.332403315702</v>
+        <v>1172.320630360132</v>
       </c>
       <c r="D172" t="n">
-        <v>1166.137428184435</v>
+        <v>1166.125883141603</v>
       </c>
       <c r="E172" t="n">
-        <v>1178.52737844697</v>
+        <v>1178.515377578662</v>
       </c>
       <c r="F172" t="n">
         <v>22479</v>
@@ -22336,36 +22336,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>phi-3-small-8k-instruct</t>
+          <t>starling-lm-7b-beta</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1170.530815724491</v>
+        <v>1170.531782661748</v>
       </c>
       <c r="D173" t="n">
-        <v>1164.615116157212</v>
+        <v>1163.131383229103</v>
       </c>
       <c r="E173" t="n">
-        <v>1176.44651529177</v>
+        <v>1177.932182094394</v>
       </c>
       <c r="F173" t="n">
-        <v>17766</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
+        <v>16056</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J173" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -22374,26 +22370,26 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
       <c r="M173" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="N173" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="O173" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="P173" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R173" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="S173" s="6" t="inlineStr">
         <is>
@@ -22487,32 +22483,36 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>starling-lm-7b-beta</t>
+          <t>phi-3-small-8k-instruct</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1170.518070105438</v>
+        <v>1170.515931848825</v>
       </c>
       <c r="D174" t="n">
-        <v>1163.117453146877</v>
+        <v>1164.600271289059</v>
       </c>
       <c r="E174" t="n">
-        <v>1177.918687063999</v>
+        <v>1176.431592408592</v>
       </c>
       <c r="F174" t="n">
-        <v>16056</v>
-      </c>
-      <c r="G174" t="inlineStr"/>
+        <v>17766</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J174" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -22521,26 +22521,26 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
       <c r="M174" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="N174" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="O174" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="P174" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R174" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="S174" s="6" t="inlineStr">
         <is>
@@ -22638,13 +22638,13 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1170.112876518916</v>
+        <v>1170.109103585048</v>
       </c>
       <c r="D175" t="n">
-        <v>1164.619645096357</v>
+        <v>1164.616028809766</v>
       </c>
       <c r="E175" t="n">
-        <v>1175.606107941475</v>
+        <v>1175.602178360331</v>
       </c>
       <c r="F175" t="n">
         <v>38492</v>
@@ -22789,13 +22789,13 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1166.852746164366</v>
+        <v>1166.846807972465</v>
       </c>
       <c r="D176" t="n">
-        <v>1158.794705112369</v>
+        <v>1158.789164431311</v>
       </c>
       <c r="E176" t="n">
-        <v>1174.910787216363</v>
+        <v>1174.904451513619</v>
       </c>
       <c r="F176" t="n">
         <v>10224</v>
@@ -22936,13 +22936,13 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1166.313917619419</v>
+        <v>1166.287790348787</v>
       </c>
       <c r="D177" t="n">
-        <v>1158.607485494001</v>
+        <v>1158.581619904138</v>
       </c>
       <c r="E177" t="n">
-        <v>1174.020349744837</v>
+        <v>1173.993960793436</v>
       </c>
       <c r="F177" t="n">
         <v>7936</v>
@@ -23087,13 +23087,13 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1163.887710327243</v>
+        <v>1163.882957958669</v>
       </c>
       <c r="D178" t="n">
-        <v>1151.985495460394</v>
+        <v>1151.981399680546</v>
       </c>
       <c r="E178" t="n">
-        <v>1175.789925194091</v>
+        <v>1175.784516236791</v>
       </c>
       <c r="F178" t="n">
         <v>3777</v>
@@ -23234,13 +23234,13 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1156.04138928207</v>
+        <v>1156.021227745077</v>
       </c>
       <c r="D179" t="n">
-        <v>1147.655007865984</v>
+        <v>1147.635180577277</v>
       </c>
       <c r="E179" t="n">
-        <v>1164.427770698157</v>
+        <v>1164.407274912878</v>
       </c>
       <c r="F179" t="n">
         <v>6837</v>
@@ -23385,13 +23385,13 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1154.131886534535</v>
+        <v>1154.123816980824</v>
       </c>
       <c r="D180" t="n">
-        <v>1141.547164695196</v>
+        <v>1141.539819411566</v>
       </c>
       <c r="E180" t="n">
-        <v>1166.716608373873</v>
+        <v>1166.707814550082</v>
       </c>
       <c r="F180" t="n">
         <v>3585</v>
@@ -23536,13 +23536,13 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1154.055857649049</v>
+        <v>1154.078627165174</v>
       </c>
       <c r="D181" t="n">
-        <v>1142.57087462862</v>
+        <v>1142.594263470734</v>
       </c>
       <c r="E181" t="n">
-        <v>1165.540840669477</v>
+        <v>1165.562990859615</v>
       </c>
       <c r="F181" t="n">
         <v>3231</v>
@@ -23687,13 +23687,13 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1151.81133996872</v>
+        <v>1151.79651979424</v>
       </c>
       <c r="D182" t="n">
-        <v>1138.659672977452</v>
+        <v>1138.645795451158</v>
       </c>
       <c r="E182" t="n">
-        <v>1164.963006959988</v>
+        <v>1164.947244137322</v>
       </c>
       <c r="F182" t="n">
         <v>4155</v>
@@ -23834,13 +23834,13 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1151.662107445586</v>
+        <v>1151.64572836599</v>
       </c>
       <c r="D183" t="n">
-        <v>1136.358899069555</v>
+        <v>1136.343789967797</v>
       </c>
       <c r="E183" t="n">
-        <v>1166.965315821617</v>
+        <v>1166.947666764183</v>
       </c>
       <c r="F183" t="n">
         <v>1679</v>
@@ -23981,13 +23981,13 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1150.091461037761</v>
+        <v>1150.067530679249</v>
       </c>
       <c r="D184" t="n">
-        <v>1137.863963269395</v>
+        <v>1137.841140663509</v>
       </c>
       <c r="E184" t="n">
-        <v>1162.318958806128</v>
+        <v>1162.29392069499</v>
       </c>
       <c r="F184" t="n">
         <v>2572</v>
@@ -24128,13 +24128,13 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1148.905235183901</v>
+        <v>1148.888941112815</v>
       </c>
       <c r="D185" t="n">
-        <v>1139.69420590743</v>
+        <v>1139.678537765582</v>
       </c>
       <c r="E185" t="n">
-        <v>1158.116264460372</v>
+        <v>1158.099344460049</v>
       </c>
       <c r="F185" t="n">
         <v>7044</v>
@@ -24279,13 +24279,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1148.827650174701</v>
+        <v>1148.819640898128</v>
       </c>
       <c r="D186" t="n">
-        <v>1142.180186420879</v>
+        <v>1142.172342485669</v>
       </c>
       <c r="E186" t="n">
-        <v>1155.475113928523</v>
+        <v>1155.466939310586</v>
       </c>
       <c r="F186" t="n">
         <v>19402</v>
@@ -24430,13 +24430,13 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1147.404409181477</v>
+        <v>1147.370855782385</v>
       </c>
       <c r="D187" t="n">
-        <v>1130.371971360601</v>
+        <v>1130.339850031735</v>
       </c>
       <c r="E187" t="n">
-        <v>1164.436847002353</v>
+        <v>1164.401861533034</v>
       </c>
       <c r="F187" t="n">
         <v>1295</v>
@@ -24577,13 +24577,13 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1143.31034983349</v>
+        <v>1143.296757643593</v>
       </c>
       <c r="D188" t="n">
-        <v>1133.428845334767</v>
+        <v>1133.415721927965</v>
       </c>
       <c r="E188" t="n">
-        <v>1153.191854332214</v>
+        <v>1153.177793359221</v>
       </c>
       <c r="F188" t="n">
         <v>4737</v>
@@ -24728,13 +24728,13 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1142.571787045976</v>
+        <v>1142.55599443337</v>
       </c>
       <c r="D189" t="n">
-        <v>1136.131047760059</v>
+        <v>1136.115300493168</v>
       </c>
       <c r="E189" t="n">
-        <v>1149.012526331893</v>
+        <v>1148.996688373571</v>
       </c>
       <c r="F189" t="n">
         <v>12297</v>
@@ -24879,13 +24879,13 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1140.893408219981</v>
+        <v>1140.888540998748</v>
       </c>
       <c r="D190" t="n">
-        <v>1134.174431718627</v>
+        <v>1134.169788084315</v>
       </c>
       <c r="E190" t="n">
-        <v>1147.612384721334</v>
+        <v>1147.607293913182</v>
       </c>
       <c r="F190" t="n">
         <v>19174</v>
@@ -25030,13 +25030,13 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1140.889354057772</v>
+        <v>1140.863976810264</v>
       </c>
       <c r="D191" t="n">
-        <v>1134.198184866663</v>
+        <v>1134.173163929877</v>
       </c>
       <c r="E191" t="n">
-        <v>1147.580523248881</v>
+        <v>1147.55478969065</v>
       </c>
       <c r="F191" t="n">
         <v>19367</v>
@@ -25177,13 +25177,13 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1138.657161320731</v>
+        <v>1138.627033507035</v>
       </c>
       <c r="D192" t="n">
-        <v>1127.725420417256</v>
+        <v>1127.695928598459</v>
       </c>
       <c r="E192" t="n">
-        <v>1149.588902224206</v>
+        <v>1149.55813841561</v>
       </c>
       <c r="F192" t="n">
         <v>4964</v>
@@ -25328,13 +25328,13 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1137.213445016502</v>
+        <v>1137.152654330613</v>
       </c>
       <c r="D193" t="n">
-        <v>1127.734668175517</v>
+        <v>1127.67424136921</v>
       </c>
       <c r="E193" t="n">
-        <v>1146.692221857486</v>
+        <v>1146.631067292016</v>
       </c>
       <c r="F193" t="n">
         <v>8925</v>
@@ -25479,13 +25479,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>1136.251418514805</v>
+        <v>1136.237711016062</v>
       </c>
       <c r="D194" t="n">
-        <v>1127.369885857637</v>
+        <v>1127.35665529004</v>
       </c>
       <c r="E194" t="n">
-        <v>1145.132951171973</v>
+        <v>1145.118766742085</v>
       </c>
       <c r="F194" t="n">
         <v>7366</v>
@@ -25630,13 +25630,13 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1130.232684623355</v>
+        <v>1130.224823564407</v>
       </c>
       <c r="D195" t="n">
-        <v>1121.411997118674</v>
+        <v>1121.404646068699</v>
       </c>
       <c r="E195" t="n">
-        <v>1139.053372128035</v>
+        <v>1139.045001060114</v>
       </c>
       <c r="F195" t="n">
         <v>11118</v>
@@ -25777,13 +25777,13 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1129.193292927399</v>
+        <v>1129.170202571456</v>
       </c>
       <c r="D196" t="n">
-        <v>1121.772583985141</v>
+        <v>1121.749820028616</v>
       </c>
       <c r="E196" t="n">
-        <v>1136.614001869656</v>
+        <v>1136.590585114295</v>
       </c>
       <c r="F196" t="n">
         <v>20685</v>
@@ -25928,13 +25928,13 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1127.583885958627</v>
+        <v>1127.579574227072</v>
       </c>
       <c r="D197" t="n">
-        <v>1121.187389166386</v>
+        <v>1121.183208863932</v>
       </c>
       <c r="E197" t="n">
-        <v>1133.980382750869</v>
+        <v>1133.975939590213</v>
       </c>
       <c r="F197" t="n">
         <v>20118</v>
@@ -26079,13 +26079,13 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>1126.863660467597</v>
+        <v>1126.843807919246</v>
       </c>
       <c r="D198" t="n">
-        <v>1114.788708150581</v>
+        <v>1114.770026622935</v>
       </c>
       <c r="E198" t="n">
-        <v>1138.938612784614</v>
+        <v>1138.917589215557</v>
       </c>
       <c r="F198" t="n">
         <v>2921</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1126.330223056773</v>
+        <v>1126.316997427382</v>
       </c>
       <c r="D199" t="n">
-        <v>1110.755557710512</v>
+        <v>1110.743540652165</v>
       </c>
       <c r="E199" t="n">
-        <v>1141.904888403035</v>
+        <v>1141.890454202599</v>
       </c>
       <c r="F199" t="n">
         <v>1785</v>
@@ -26373,13 +26373,13 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1120.941861454221</v>
+        <v>1120.916975013879</v>
       </c>
       <c r="D200" t="n">
-        <v>1109.975174379201</v>
+        <v>1109.950900108701</v>
       </c>
       <c r="E200" t="n">
-        <v>1131.908548529241</v>
+        <v>1131.883049919056</v>
       </c>
       <c r="F200" t="n">
         <v>5182</v>
@@ -26520,13 +26520,13 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1118.649403150878</v>
+        <v>1118.626624798905</v>
       </c>
       <c r="D201" t="n">
-        <v>1100.537740982204</v>
+        <v>1100.516538240452</v>
       </c>
       <c r="E201" t="n">
-        <v>1136.761065319552</v>
+        <v>1136.736711357358</v>
       </c>
       <c r="F201" t="n">
         <v>1143</v>
@@ -26671,13 +26671,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>1116.110452580265</v>
+        <v>1116.037687553297</v>
       </c>
       <c r="D202" t="n">
-        <v>1108.385509359763</v>
+        <v>1108.312976918753</v>
       </c>
       <c r="E202" t="n">
-        <v>1123.835395800766</v>
+        <v>1123.762398187842</v>
       </c>
       <c r="F202" t="n">
         <v>10854</v>
@@ -26822,13 +26822,13 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>1114.6367076374</v>
+        <v>1114.611805704405</v>
       </c>
       <c r="D203" t="n">
-        <v>1105.515165392402</v>
+        <v>1105.490973496755</v>
       </c>
       <c r="E203" t="n">
-        <v>1123.758249882398</v>
+        <v>1123.732637912055</v>
       </c>
       <c r="F203" t="n">
         <v>6923</v>
@@ -26969,13 +26969,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1114.107968814244</v>
+        <v>1114.086164863774</v>
       </c>
       <c r="D204" t="n">
-        <v>1099.750183771077</v>
+        <v>1099.729461035165</v>
       </c>
       <c r="E204" t="n">
-        <v>1128.46575385741</v>
+        <v>1128.442868692383</v>
       </c>
       <c r="F204" t="n">
         <v>2199</v>
@@ -27116,13 +27116,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>1110.641917477648</v>
+        <v>1110.62031245341</v>
       </c>
       <c r="D205" t="n">
-        <v>1102.757741555441</v>
+        <v>1102.736463415518</v>
       </c>
       <c r="E205" t="n">
-        <v>1118.526093399854</v>
+        <v>1118.504161491302</v>
       </c>
       <c r="F205" t="n">
         <v>8045</v>
@@ -27267,13 +27267,13 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1109.673290686938</v>
+        <v>1109.645517003407</v>
       </c>
       <c r="D206" t="n">
-        <v>1100.400328105088</v>
+        <v>1100.373075336176</v>
       </c>
       <c r="E206" t="n">
-        <v>1118.946253268789</v>
+        <v>1118.917958670639</v>
       </c>
       <c r="F206" t="n">
         <v>8977</v>
@@ -27418,13 +27418,13 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1107.399493495408</v>
+        <v>1107.401792964381</v>
       </c>
       <c r="D207" t="n">
-        <v>1100.352842572389</v>
+        <v>1100.355359691245</v>
       </c>
       <c r="E207" t="n">
-        <v>1114.446144418428</v>
+        <v>1114.448226237518</v>
       </c>
       <c r="F207" t="n">
         <v>14148</v>
@@ -27569,13 +27569,13 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1093.084143046719</v>
+        <v>1093.019706520359</v>
       </c>
       <c r="D208" t="n">
-        <v>1081.613042857368</v>
+        <v>1081.549243877899</v>
       </c>
       <c r="E208" t="n">
-        <v>1104.55524323607</v>
+        <v>1104.490169162818</v>
       </c>
       <c r="F208" t="n">
         <v>4780</v>
@@ -27720,13 +27720,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1090.408819907109</v>
+        <v>1090.375673809858</v>
       </c>
       <c r="D209" t="n">
-        <v>1081.082099331448</v>
+        <v>1081.049451636732</v>
       </c>
       <c r="E209" t="n">
-        <v>1099.73554048277</v>
+        <v>1099.701895982984</v>
       </c>
       <c r="F209" t="n">
         <v>7597</v>
@@ -27871,13 +27871,13 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1073.142409689137</v>
+        <v>1073.149685508246</v>
       </c>
       <c r="D210" t="n">
-        <v>1061.996538235513</v>
+        <v>1062.004495662195</v>
       </c>
       <c r="E210" t="n">
-        <v>1084.288281142761</v>
+        <v>1084.294875354297</v>
       </c>
       <c r="F210" t="n">
         <v>6328</v>
@@ -28022,13 +28022,13 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1070.273410549598</v>
+        <v>1070.252910605779</v>
       </c>
       <c r="D211" t="n">
-        <v>1060.425477550894</v>
+        <v>1060.406312705691</v>
       </c>
       <c r="E211" t="n">
-        <v>1080.121343548303</v>
+        <v>1080.099508505867</v>
       </c>
       <c r="F211" t="n">
         <v>6965</v>
@@ -28169,13 +28169,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1069.316553977443</v>
+        <v>1069.251273889766</v>
       </c>
       <c r="D212" t="n">
-        <v>1057.896709868055</v>
+        <v>1057.832772782423</v>
       </c>
       <c r="E212" t="n">
-        <v>1080.736398086832</v>
+        <v>1080.669774997109</v>
       </c>
       <c r="F212" t="n">
         <v>5745</v>
@@ -28316,13 +28316,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1066.913199839474</v>
+        <v>1066.868439985982</v>
       </c>
       <c r="D213" t="n">
-        <v>1051.741655286315</v>
+        <v>1051.698641237133</v>
       </c>
       <c r="E213" t="n">
-        <v>1082.084744392634</v>
+        <v>1082.038238734831</v>
       </c>
       <c r="F213" t="n">
         <v>1743</v>
@@ -28463,13 +28463,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>1062.667976968397</v>
+        <v>1062.625947310965</v>
       </c>
       <c r="D214" t="n">
-        <v>1050.730862800254</v>
+        <v>1050.690212692673</v>
       </c>
       <c r="E214" t="n">
-        <v>1074.60509113654</v>
+        <v>1074.561681929257</v>
       </c>
       <c r="F214" t="n">
         <v>3924</v>
@@ -28610,13 +28610,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>1055.890177259885</v>
+        <v>1055.864633349612</v>
       </c>
       <c r="D215" t="n">
-        <v>1044.244509877774</v>
+        <v>1044.219661589534</v>
       </c>
       <c r="E215" t="n">
-        <v>1067.535844641996</v>
+        <v>1067.509605109691</v>
       </c>
       <c r="F215" t="n">
         <v>4658</v>
@@ -28757,13 +28757,13 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>1041.628957624046</v>
+        <v>1041.599089181371</v>
       </c>
       <c r="D216" t="n">
-        <v>1030.278452308738</v>
+        <v>1030.249939791281</v>
       </c>
       <c r="E216" t="n">
-        <v>1052.979462939353</v>
+        <v>1052.94823857146</v>
       </c>
       <c r="F216" t="n">
         <v>4845</v>
@@ -28904,13 +28904,13 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1024.089015301668</v>
+        <v>1024.062841253166</v>
       </c>
       <c r="D217" t="n">
-        <v>1010.529012050838</v>
+        <v>1010.503927298625</v>
       </c>
       <c r="E217" t="n">
-        <v>1037.649018552497</v>
+        <v>1037.621755207708</v>
       </c>
       <c r="F217" t="n">
         <v>2658</v>
@@ -29051,13 +29051,13 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1022.755401555846</v>
+        <v>1022.714571045078</v>
       </c>
       <c r="D218" t="n">
-        <v>1011.926306483196</v>
+        <v>1011.886871569478</v>
       </c>
       <c r="E218" t="n">
-        <v>1033.584496628496</v>
+        <v>1033.542270520678</v>
       </c>
       <c r="F218" t="n">
         <v>6310</v>
@@ -29198,13 +29198,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>995.1878631499429</v>
+        <v>995.1708619886572</v>
       </c>
       <c r="D219" t="n">
-        <v>982.6631610021896</v>
+        <v>982.6477018308153</v>
       </c>
       <c r="E219" t="n">
-        <v>1007.712565297696</v>
+        <v>1007.694022146499</v>
       </c>
       <c r="F219" t="n">
         <v>4914</v>
@@ -29345,13 +29345,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>991.8488435414806</v>
+        <v>991.8189030651299</v>
       </c>
       <c r="D220" t="n">
-        <v>979.5208773133553</v>
+        <v>979.4924165836071</v>
       </c>
       <c r="E220" t="n">
-        <v>1004.176809769606</v>
+        <v>1004.145389546653</v>
       </c>
       <c r="F220" t="n">
         <v>4203</v>
@@ -29492,13 +29492,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>981.6126290601555</v>
+        <v>981.5544184680153</v>
       </c>
       <c r="D221" t="n">
-        <v>968.1394862852535</v>
+        <v>968.0832673150201</v>
       </c>
       <c r="E221" t="n">
-        <v>995.0857718350576</v>
+        <v>995.0255696210106</v>
       </c>
       <c r="F221" t="n">
         <v>3412</v>
@@ -29639,13 +29639,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>974.2676718505024</v>
+        <v>974.2040248359287</v>
       </c>
       <c r="D222" t="n">
-        <v>958.5452200677626</v>
+        <v>958.4841637740108</v>
       </c>
       <c r="E222" t="n">
-        <v>989.9901236332424</v>
+        <v>989.9238858978467</v>
       </c>
       <c r="F222" t="n">
         <v>2391</v>
@@ -29790,13 +29790,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>952.5375096860412</v>
+        <v>952.5161402031642</v>
       </c>
       <c r="D223" t="n">
-        <v>939.8685462902399</v>
+        <v>939.8490592452166</v>
       </c>
       <c r="E223" t="n">
-        <v>965.2064730818424</v>
+        <v>965.1832211611118</v>
       </c>
       <c r="F223" t="n">
         <v>3287</v>
@@ -30011,7 +30011,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -30081,7 +30081,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -30707,18 +30707,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>glm-5</t>
+          <t>deepseek-v4-pro</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>744</v>
+        <v>1.6</v>
       </c>
       <c r="C10" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -30730,18 +30730,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>deepseek-v4-pro</t>
+          <t>glm-5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.6</v>
+        <v>744</v>
       </c>
       <c r="C11" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -30959,46 +30959,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>deepseek-v4-flash</t>
+          <t>qwen3.8-27b</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>284</v>
+        <v>27</v>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>moe</t>
+          <t>dense</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen3.8-27b</t>
+          <t>deepseek-v4-flash</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27</v>
+        <v>284</v>
       </c>
       <c r="C23" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>dense</t>
+          <t>moe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
@@ -31066,38 +31066,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mistral-medium-3.5</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>muse-glimmer</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>30</v>
+      </c>
+      <c r="C27" t="n">
+        <v>30</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>aa_single_scrape</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>muse-glimmer</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>30</v>
-      </c>
-      <c r="C28" t="n">
-        <v>30</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>mistral-medium-3.5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>aa_single_scrape</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>deepseek-v3.2-exp-thinking</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t>deepseek-v3.2-exp-thinking</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>deepseek-v3.1</t>
+          <t>deepseek-v3.1-terminus-thinking</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -31301,7 +31301,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>deepseek-v3.1-terminus-thinking</t>
+          <t>deepseek-v3.1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -31819,38 +31819,38 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>glm-4.6v</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+          <t>trinity-large-preview</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>70</v>
+      </c>
+      <c r="C66" t="n">
+        <v>70</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>trinity-large-preview</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>70</v>
-      </c>
-      <c r="C67" t="n">
-        <v>70</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>glm-4.6v</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -32078,76 +32078,76 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>command-a-03-2025</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>30</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nvidia-nemotron-3.5-lightning-30b-a3b-nvfp4</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>30</v>
-      </c>
-      <c r="C80" t="n">
-        <v>3</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>command-a-03-2025</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>gpt-oss-120b</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>117</v>
-      </c>
-      <c r="C81" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>moe</t>
-        </is>
-      </c>
+          <t>glm-4.5v</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>glm-4.5v</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+          <t>gpt-oss-120b</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>117</v>
+      </c>
+      <c r="C82" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>moe</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>override</t>
         </is>
       </c>
     </row>
@@ -32276,14 +32276,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>gemma-3-12b-it</t>
+          <t>granite-4.2-30b</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C89" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -32299,14 +32299,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>granite-4.2-30b</t>
+          <t>gemma-3-12b-it</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C90" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -32949,38 +32949,38 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>gemma-2-27b-it</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>27</v>
-      </c>
-      <c r="C120" t="n">
-        <v>27</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>dense</t>
-        </is>
-      </c>
+          <t>jamba-1.5-large</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>jamba-1.5-large</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+          <t>gemma-2-27b-it</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>27</v>
+      </c>
+      <c r="C121" t="n">
+        <v>27</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>dense</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
@@ -34104,14 +34104,14 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>phi-3-small-8k-instruct</t>
+          <t>starling-lm-7b-beta</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="C173" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -34120,21 +34120,21 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>name_parsing</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>starling-lm-7b-beta</t>
+          <t>phi-3-small-8k-instruct</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="C174" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>name_parsing</t>
+          <t>override</t>
         </is>
       </c>
     </row>
